--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -401,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O217"/>
+  <dimension ref="A1:V188"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,22 +445,43 @@
       <c r="O1" t="str">
         <v>market_status</v>
       </c>
+      <c r="P1" t="str">
+        <v>series</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>series_cn</v>
+      </c>
+      <c r="R1" t="str">
+        <v>water_type</v>
+      </c>
+      <c r="S1" t="str">
+        <v>description</v>
+      </c>
+      <c r="T1" t="str">
+        <v>source_url</v>
+      </c>
+      <c r="U1" t="str">
+        <v>main_image_url</v>
+      </c>
+      <c r="V1" t="str">
+        <v>local_image_path</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SRE5000</v>
+        <v>SRE1000</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>TIAGRA</v>
+        <v>STELLA SW</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -473,16 +490,16 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>images/shimano_reels/TIAGRA_main.jpg</v>
+        <v>images/shimano_reels/STELLA SW_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -491,7 +508,7 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>¥3,801 - ¥8,316</v>
+        <v>¥5,966 - ¥9,307</v>
       </c>
       <c r="O2" t="str">
         <v>在售</v>
@@ -499,13 +516,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SRE5001</v>
+        <v>SRE1001</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>TALICA</v>
+        <v>BB-X TECHNIUM FIRE BLOOD</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -520,16 +537,16 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I3" t="str">
-        <v>images/shimano_reels/TALICA_main.jpg</v>
+        <v>images/shimano_reels/BB-X TECHNIUM FIRE BLOOD_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -538,7 +555,7 @@
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>¥3,938 - ¥6,783</v>
+        <v>¥5,775</v>
       </c>
       <c r="O3" t="str">
         <v>在售</v>
@@ -546,13 +563,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SRE5002</v>
+        <v>SRE1002</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="str">
-        <v>EXSENCE DC</v>
+        <v>BB-X TECHNIUM</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -567,16 +584,16 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I4" t="str">
-        <v>images/shimano_reels/EXSENCE DC_main.jpg</v>
+        <v>images/shimano_reels/BB-X TECHNIUM_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -585,7 +602,7 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>¥4,284</v>
+        <v>¥5,765</v>
       </c>
       <c r="O4" t="str">
         <v>在售</v>
@@ -593,13 +610,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SRE5003</v>
+        <v>SRE1003</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="str">
-        <v>ANTARES DC</v>
+        <v>KISU SPECIAL 45</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -614,16 +631,16 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I5" t="str">
-        <v>images/shimano_reels/ANTARES DC_main.jpg</v>
+        <v>images/shimano_reels/KISU SPECIAL 45_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -632,7 +649,7 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>¥4,284</v>
+        <v>¥5,489</v>
       </c>
       <c r="O5" t="str">
         <v>在售</v>
@@ -640,19 +657,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SRE5004</v>
+        <v>SRE1004</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>ANTARES DC MD</v>
+        <v>AERO TECHNIUM MGS XTD</v>
       </c>
       <c r="D6" t="str">
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>2023</v>
+        <v/>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -661,16 +678,16 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I6" t="str">
-        <v>images/shimano_reels/ANTARES DC MD_main.png</v>
+        <v>images/shimano_reels/AERO TECHNIUM MGS XTD_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -679,7 +696,7 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>¥4,253</v>
+        <v>¥5,250</v>
       </c>
       <c r="O6" t="str">
         <v>在售</v>
@@ -687,13 +704,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SRE5005</v>
+        <v>SRE1005</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>OCEA JIGGER 4000/4000HG</v>
+        <v>AERO TECHNIUM MGS XSD</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -708,16 +725,16 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I7" t="str">
-        <v>images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpg</v>
+        <v>images/shimano_reels/AERO TECHNIUM MGS XSD_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -726,7 +743,7 @@
         <v/>
       </c>
       <c r="N7" t="str">
-        <v>¥3,969</v>
+        <v>¥5,250</v>
       </c>
       <c r="O7" t="str">
         <v>在售</v>
@@ -734,13 +751,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SRE5006</v>
+        <v>SRE1006</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>CALCUTTA CONQUEST DC</v>
+        <v>STELLA</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -755,16 +772,16 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I8" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST DC_main.jpg</v>
+        <v>images/shimano_reels/STELLA_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -773,7 +790,7 @@
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>¥3,730 - ¥3,885</v>
+        <v>¥4,473 - ¥4,840</v>
       </c>
       <c r="O8" t="str">
         <v>在售</v>
@@ -781,13 +798,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SRE5007</v>
+        <v>SRE1007</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="str">
-        <v>OCEA JIGGER LD</v>
+        <v>EXSENCE</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -802,16 +819,16 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I9" t="str">
-        <v>images/shimano_reels/OCEA JIGGER LD_main.jpg</v>
+        <v>images/shimano_reels/EXSENCE_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -820,7 +837,7 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>¥3,864</v>
+        <v>¥3,350 - ¥3,990</v>
       </c>
       <c r="O9" t="str">
         <v>在售</v>
@@ -828,13 +845,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SRE5008</v>
+        <v>SRE1008</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>OCEA JIGGER F CUSTOM</v>
+        <v>TWINPOWER SW</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -849,16 +866,16 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I10" t="str">
-        <v>images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpg</v>
+        <v>images/shimano_reels/TWINPOWER SW_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -867,7 +884,7 @@
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>¥3,360 - ¥3,843</v>
+        <v>¥3,339 - ¥3,969</v>
       </c>
       <c r="O10" t="str">
         <v>在售</v>
@@ -875,13 +892,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SRE5009</v>
+        <v>SRE1009</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="str">
-        <v>OCEA CONQUEST CT</v>
+        <v>POWER AERO XTC</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -896,16 +913,16 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I11" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST CT_main.jpg</v>
+        <v>images/shimano_reels/POWER AERO XTC_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -914,7 +931,7 @@
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>¥3,780</v>
+        <v>¥3,880</v>
       </c>
       <c r="O11" t="str">
         <v>在售</v>
@@ -922,13 +939,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SRE5010</v>
+        <v>SRE1010</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="str">
-        <v>KAIKON</v>
+        <v>POWER AERO XSC</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -943,16 +960,16 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I12" t="str">
-        <v>images/shimano_reels/KAIKON_main.jpg</v>
+        <v>images/shimano_reels/POWER AERO XSC_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -961,7 +978,7 @@
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>¥3,567 - ¥3,688</v>
+        <v>¥3,880</v>
       </c>
       <c r="O12" t="str">
         <v>在售</v>
@@ -969,13 +986,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SRE5011</v>
+        <v>SRE1011</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="str">
-        <v>ANTARES</v>
+        <v>BB-X HYPER FORCE TYPE2</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -990,16 +1007,16 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I13" t="str">
-        <v>images/shimano_reels/ANTARES_main.jpg</v>
+        <v>images/shimano_reels/BB-X HYPER FORCE TYPE2_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1008,7 +1025,7 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>¥3,465</v>
+        <v>¥3,596</v>
       </c>
       <c r="O13" t="str">
         <v>在售</v>
@@ -1016,13 +1033,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SRE5012</v>
+        <v>SRE1012</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>OCEA JIGGER</v>
+        <v>FLIEGEN</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -1037,16 +1054,16 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I14" t="str">
-        <v>images/shimano_reels/OCEA JIGGER_main.jpg</v>
+        <v>images/shimano_reels/FLIEGEN_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1055,7 +1072,7 @@
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>¥3,045 - ¥3,392</v>
+        <v>¥3,392 - ¥3,497</v>
       </c>
       <c r="O14" t="str">
         <v>在售</v>
@@ -1063,13 +1080,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SRE5013</v>
+        <v>SRE1013</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="str">
-        <v>CALCUTTA CONQUEST MD</v>
+        <v>Vanquish CE</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -1084,16 +1101,16 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I15" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST MD_main.jpg</v>
+        <v>images/shimano_reels/Vanquish CE_main.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1102,7 +1119,7 @@
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>¥3,380</v>
+        <v>¥3,332 - ¥3,379</v>
       </c>
       <c r="O15" t="str">
         <v>在售</v>
@@ -1110,19 +1127,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SRE5014</v>
+        <v>SRE1014</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="str">
-        <v>CALCUTTA CONQUEST BFS LIMITED</v>
+        <v>Vanquish</v>
       </c>
       <c r="D16" t="str">
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>2026</v>
+        <v/>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1131,16 +1148,16 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I16" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpg</v>
+        <v>images/shimano_reels/Vanquish_main.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1149,7 +1166,7 @@
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>¥3,360</v>
+        <v>¥3,203 - ¥3,329</v>
       </c>
       <c r="O16" t="str">
         <v>在售</v>
@@ -1157,13 +1174,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SRE5015</v>
+        <v>SRE1015</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="str">
-        <v>Metanium DC</v>
+        <v>SARAGOSA SW</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -1178,16 +1195,16 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I17" t="str">
-        <v>images/shimano_reels/Metanium DC_main.jpg</v>
+        <v>images/shimano_reels/SARAGOSA SW_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1196,7 +1213,7 @@
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>¥3,255</v>
+        <v>¥2,142 - ¥3,299</v>
       </c>
       <c r="O17" t="str">
         <v>在售</v>
@@ -1204,13 +1221,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SRE5016</v>
+        <v>SRE1016</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>CALCUTTA CONQUEST</v>
+        <v>BB-X HYPER FORCE</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -1225,16 +1242,16 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I18" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST_main.jpg</v>
+        <v>images/shimano_reels/BB-X HYPER FORCE_main.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1243,7 +1260,7 @@
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>¥3,129 - ¥3,255</v>
+        <v>¥2,754 - ¥3,162</v>
       </c>
       <c r="O18" t="str">
         <v>在售</v>
@@ -1251,13 +1268,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SRE5017</v>
+        <v>SRE1017</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="str">
-        <v>OCEA CONQUEST</v>
+        <v>BB-X Remare</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -1272,16 +1289,16 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I19" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST_main.jpg</v>
+        <v>images/shimano_reels/BB-X Remare_main.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1290,7 +1307,7 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>¥3,129 - ¥3,245</v>
+        <v>¥3,024 - ¥3,129</v>
       </c>
       <c r="O19" t="str">
         <v>在售</v>
@@ -1298,13 +1315,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SRE5018</v>
+        <v>SRE1018</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="str">
-        <v>CALCUTTA CONQUEST SHALLOW EDITION</v>
+        <v>TWINPOWER</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -1319,16 +1336,16 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I20" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpg</v>
+        <v>images/shimano_reels/TWINPOWER_main.jpg</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1337,7 +1354,7 @@
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>¥3,129</v>
+        <v>¥2,772 - ¥2,946</v>
       </c>
       <c r="O20" t="str">
         <v>在售</v>
@@ -1345,13 +1362,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SRE5019</v>
+        <v>SRE1019</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="str">
-        <v>CALCUTTA CONQUEST BFS</v>
+        <v>TWINPOWER XD</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -1366,16 +1383,16 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I21" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpg</v>
+        <v>images/shimano_reels/TWINPOWER XD_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1384,7 +1401,7 @@
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>¥3,129</v>
+        <v>¥2,835 - ¥2,940</v>
       </c>
       <c r="O21" t="str">
         <v>在售</v>
@@ -1392,13 +1409,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SRE5020</v>
+        <v>SRE1020</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>OCEA CONQUEST FT</v>
+        <v>HYPER FORCE LB</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -1413,16 +1430,16 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I22" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST FT_main.jpg</v>
+        <v>images/shimano_reels/HYPER FORCE LB_main.jpg</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1431,7 +1448,7 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>¥3,050</v>
+        <v>¥2,742 - ¥2,907</v>
       </c>
       <c r="O22" t="str">
         <v>在售</v>
@@ -1439,13 +1456,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SRE5021</v>
+        <v>SRE1021</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="str">
-        <v>ALDEBARAN DC</v>
+        <v>POWER AERO TD</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -1460,16 +1477,16 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I23" t="str">
-        <v>images/shimano_reels/ALDEBARAN DC_main.jpg</v>
+        <v>images/shimano_reels/POWER AERO TD_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1478,7 +1495,7 @@
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>¥3,045</v>
+        <v>¥2,770</v>
       </c>
       <c r="O23" t="str">
         <v>在售</v>
@@ -1486,13 +1503,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SRE5022</v>
+        <v>SRE1022</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="str">
-        <v>STILE</v>
+        <v>ULTEGRA XR BIG PIT XTD</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -1507,16 +1524,16 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I24" t="str">
-        <v>images/shimano_reels/STILE_main.jpg</v>
+        <v>images/shimano_reels/ULTEGRA XR BIG PIT XTD_main.jpg</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1525,7 +1542,7 @@
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>¥2,700</v>
+        <v>¥2,621</v>
       </c>
       <c r="O24" t="str">
         <v>在售</v>
@@ -1533,13 +1550,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SRE5023</v>
+        <v>SRE1023</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="str">
-        <v>BARCHETTA PREMIUM</v>
+        <v>ULTEGRA XR BIG PIT XSD</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -1554,16 +1571,16 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I25" t="str">
-        <v>images/shimano_reels/BARCHETTA PREMIUM_main.jpg</v>
+        <v>images/shimano_reels/ULTEGRA XR BIG PIT XSD_main.jpg</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1572,7 +1589,7 @@
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>¥2,504 - ¥2,680</v>
+        <v>¥2,621</v>
       </c>
       <c r="O25" t="str">
         <v>在售</v>
@@ -1580,13 +1597,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SRE5024</v>
+        <v>SRE1024</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="str">
-        <v>GRAPPLER PREMIUM</v>
+        <v>BB-X HYPER FORCE 1700/C2000</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -1601,16 +1618,16 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I26" t="str">
-        <v>images/shimano_reels/GRAPPLER PREMIUM_main.jpg</v>
+        <v>images/shimano_reels/BB-X HYPER FORCE 1700_C2000_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1619,7 +1636,7 @@
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>¥2,674</v>
+        <v>¥2,573</v>
       </c>
       <c r="O26" t="str">
         <v>在售</v>
@@ -1627,13 +1644,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SRE5025</v>
+        <v>SRE1025</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="str">
-        <v>ALDEBARAN BFS</v>
+        <v>BB-X Rinkai SP</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -1648,16 +1665,16 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I27" t="str">
-        <v>images/shimano_reels/ALDEBARAN BFS_main.jpg</v>
+        <v>images/shimano_reels/BB-X Rinkai SP_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1666,7 +1683,7 @@
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>¥2,604</v>
+        <v>¥2,499</v>
       </c>
       <c r="O27" t="str">
         <v>在售</v>
@@ -1674,13 +1691,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SRE5026</v>
+        <v>SRE1026</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="str">
-        <v>ALDEBARAN MGL</v>
+        <v>EXSENCE XR</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1695,16 +1712,16 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I28" t="str">
-        <v>images/shimano_reels/ALDEBARAN MGL_main.jpg</v>
+        <v>images/shimano_reels/EXSENCE XR_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1713,7 +1730,7 @@
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>¥2,562</v>
+        <v>¥2,281 - ¥2,398</v>
       </c>
       <c r="O28" t="str">
         <v>在售</v>
@@ -1721,13 +1738,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SRE5027</v>
+        <v>SRE1027</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="str">
-        <v>Metanium SHALLOW EDITION</v>
+        <v>STRADIC SW</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -1742,16 +1759,16 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I29" t="str">
-        <v>images/shimano_reels/Metanium SHALLOW EDITION_main.jpg</v>
+        <v>images/shimano_reels/STRADIC SW_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1760,7 +1777,7 @@
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>¥2,457</v>
+        <v>¥1,885 - ¥2,340</v>
       </c>
       <c r="O29" t="str">
         <v>在售</v>
@@ -1768,13 +1785,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SRE5028</v>
+        <v>SRE1028</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="str">
-        <v>Metanium</v>
+        <v>Sephia XR</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1789,16 +1806,16 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I30" t="str">
-        <v>images/shimano_reels/Metanium_main.jpg</v>
+        <v>images/shimano_reels/Sephia XR_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1807,7 +1824,7 @@
         <v/>
       </c>
       <c r="N30" t="str">
-        <v>¥2,457</v>
+        <v>¥2,100 - ¥2,310</v>
       </c>
       <c r="O30" t="str">
         <v>在售</v>
@@ -1815,13 +1832,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SRE5029</v>
+        <v>SRE1029</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="str">
-        <v>SPEEDMASTER 石鲷</v>
+        <v>SUSTAIN</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1836,16 +1853,16 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I31" t="str">
-        <v>images/shimano_reels/SPEEDMASTER 石鲷_main.jpg</v>
+        <v>images/shimano_reels/SUSTAIN_main.jpg</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1854,7 +1871,7 @@
         <v/>
       </c>
       <c r="N31" t="str">
-        <v>¥2,340 - ¥2,450</v>
+        <v>¥2,100 - ¥2,205</v>
       </c>
       <c r="O31" t="str">
         <v>在售</v>
@@ -1862,13 +1879,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SRE5030</v>
+        <v>SRE1030</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="str">
-        <v>TYRNOS</v>
+        <v>Soare XR</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1883,16 +1900,16 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I32" t="str">
-        <v>images/shimano_reels/TYRNOS_main.jpg</v>
+        <v>images/shimano_reels/Soare XR_main.jpg</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1901,7 +1918,7 @@
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>¥2,235 - ¥2,351</v>
+        <v>¥1,898 - ¥2,100</v>
       </c>
       <c r="O32" t="str">
         <v>在售</v>
@@ -1909,13 +1926,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SRE5031</v>
+        <v>SRE1031</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="str">
-        <v>EXSENCE DC SS</v>
+        <v>CARDIFF XR</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1930,16 +1947,16 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I33" t="str">
-        <v>images/shimano_reels/EXSENCE DC SS_main.jpg</v>
+        <v>images/shimano_reels/CARDIFF XR_main.jpg</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1948,7 +1965,7 @@
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>¥2,310</v>
+        <v>¥2,092</v>
       </c>
       <c r="O33" t="str">
         <v>在售</v>
@@ -1956,13 +1973,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SRE5032</v>
+        <v>SRE1032</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="str">
-        <v>TRANX 400</v>
+        <v>BB-X DESPINA</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -1977,16 +1994,16 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I34" t="str">
-        <v>images/shimano_reels/TRANX 400_main.jpg</v>
+        <v>images/shimano_reels/BB-X DESPINA_main.jpg</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1995,7 +2012,7 @@
         <v/>
       </c>
       <c r="N34" t="str">
-        <v>¥2,205</v>
+        <v>¥2,079</v>
       </c>
       <c r="O34" t="str">
         <v>在售</v>
@@ -2003,13 +2020,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SRE5033</v>
+        <v>SRE1033</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="str">
-        <v>Bantam</v>
+        <v>BULL‘S EYE</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -2024,16 +2041,16 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I35" t="str">
-        <v>images/shimano_reels/Bantam_main.jpg</v>
+        <v>images/shimano_reels/BULL‘S EYE_main.jpg</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -2042,7 +2059,7 @@
         <v/>
       </c>
       <c r="N35" t="str">
-        <v>¥2,184</v>
+        <v>¥1,722 - ¥2,048</v>
       </c>
       <c r="O35" t="str">
         <v>在售</v>
@@ -2050,13 +2067,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SRE5034</v>
+        <v>SRE1034</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="str">
-        <v>TRANX 300</v>
+        <v>COMPLEX XR</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -2071,16 +2088,16 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I36" t="str">
-        <v>images/shimano_reels/TRANX 300_main.jpg</v>
+        <v>images/shimano_reels/COMPLEX XR_main.jpg</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2089,7 +2106,7 @@
         <v/>
       </c>
       <c r="N36" t="str">
-        <v>¥2,142</v>
+        <v>¥1,982 - ¥2,035</v>
       </c>
       <c r="O36" t="str">
         <v>在售</v>
@@ -2097,13 +2114,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SRE5035</v>
+        <v>SRE1035</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="str">
-        <v>BAYGAME</v>
+        <v>BAITRUNNER CI4+ XTB</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -2118,16 +2135,16 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I37" t="str">
-        <v>images/shimano_reels/BAYGAME_main.jpg</v>
+        <v>images/shimano_reels/BAITRUNNER CI4+ XTB_main.jpg</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2136,7 +2153,7 @@
         <v/>
       </c>
       <c r="N37" t="str">
-        <v>¥1,762 - ¥2,100</v>
+        <v>¥1,773 - ¥1,828</v>
       </c>
       <c r="O37" t="str">
         <v>在售</v>
@@ -2144,13 +2161,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SRE5036</v>
+        <v>SRE1036</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="str">
-        <v>GRAPPLER</v>
+        <v>SURF LEADER</v>
       </c>
       <c r="D38" t="str">
         <v/>
@@ -2165,16 +2182,16 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I38" t="str">
-        <v>images/shimano_reels/GRAPPLER_main.jpg</v>
+        <v>images/shimano_reels/SURF LEADER_main.png</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2183,7 +2200,7 @@
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>¥1,875 - ¥2,050</v>
+        <v>¥1,714 - ¥1,821</v>
       </c>
       <c r="O38" t="str">
         <v>在售</v>
@@ -2191,13 +2208,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SRE5037</v>
+        <v>SRE1037</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="str">
-        <v>BARCHETTA F CUSTOM</v>
+        <v>Sephia SS</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -2212,16 +2229,16 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I39" t="str">
-        <v>images/shimano_reels/BARCHETTA F CUSTOM_main.jpg</v>
+        <v>images/shimano_reels/Sephia SS_main.jpg</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2230,7 +2247,7 @@
         <v/>
       </c>
       <c r="N39" t="str">
-        <v>¥2,023</v>
+        <v>¥1,522 - ¥1,666</v>
       </c>
       <c r="O39" t="str">
         <v>在售</v>
@@ -2238,19 +2255,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SRE5038</v>
+        <v>SRE1038</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="str">
-        <v>Scorpion DC MD</v>
+        <v>VANFORD</v>
       </c>
       <c r="D40" t="str">
         <v/>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="F40" t="str">
         <v/>
@@ -2259,16 +2276,16 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I40" t="str">
-        <v>images/shimano_reels/Scorpion DC MD_main.jpg</v>
+        <v>images/shimano_reels/VANFORD_main.jpg</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2277,7 +2294,7 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>¥2,004</v>
+        <v>¥1,460 - ¥1,543</v>
       </c>
       <c r="O40" t="str">
         <v>在售</v>
@@ -2285,13 +2302,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SRE5039</v>
+        <v>SRE1039</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="str">
-        <v>SLX DC XT</v>
+        <v>ULTEGRA XS</v>
       </c>
       <c r="D41" t="str">
         <v/>
@@ -2306,16 +2323,16 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I41" t="str">
-        <v>images/shimano_reels/SLX DC XT_main.jpg</v>
+        <v>images/shimano_reels/ULTEGRA XS_main.jpg</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2324,7 +2341,7 @@
         <v/>
       </c>
       <c r="N41" t="str">
-        <v>¥1,966</v>
+        <v>¥1,497</v>
       </c>
       <c r="O41" t="str">
         <v>在售</v>
@@ -2332,13 +2349,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SRE5040</v>
+        <v>SRE1040</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="str">
-        <v>Scorpion DC</v>
+        <v>ULTEGRA XT</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -2353,16 +2370,16 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I42" t="str">
-        <v>images/shimano_reels/Scorpion DC_main.jpg</v>
+        <v>images/shimano_reels/ULTEGRA XT_main.jpg</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2371,7 +2388,7 @@
         <v/>
       </c>
       <c r="N42" t="str">
-        <v>¥1,950</v>
+        <v>¥1,497</v>
       </c>
       <c r="O42" t="str">
         <v>在售</v>
@@ -2379,13 +2396,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SRE5041</v>
+        <v>SRE1041</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" t="str">
-        <v>Scorpion MD 300</v>
+        <v>BB-X LARISSA</v>
       </c>
       <c r="D43" t="str">
         <v/>
@@ -2400,16 +2417,16 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I43" t="str">
-        <v>images/shimano_reels/Scorpion MD 300_main.jpg</v>
+        <v>images/shimano_reels/BB-X LARISSA_main.jpg</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2418,7 +2435,7 @@
         <v/>
       </c>
       <c r="N43" t="str">
-        <v>¥1,928</v>
+        <v>¥1,449</v>
       </c>
       <c r="O43" t="str">
         <v>在售</v>
@@ -2426,13 +2443,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SRE5042</v>
+        <v>SRE1042</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="str">
-        <v>GRAPPLER CT</v>
+        <v>SPHEROS SW</v>
       </c>
       <c r="D44" t="str">
         <v/>
@@ -2447,16 +2464,16 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I44" t="str">
-        <v>images/shimano_reels/GRAPPLER CT_main.jpg</v>
+        <v>images/shimano_reels/SPHEROS SW_main.jpg</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2465,7 +2482,7 @@
         <v/>
       </c>
       <c r="N44" t="str">
-        <v>¥1,827</v>
+        <v>¥934 - ¥1,436</v>
       </c>
       <c r="O44" t="str">
         <v>在售</v>
@@ -2473,13 +2490,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SRE5043</v>
+        <v>SRE1043</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" t="str">
-        <v>CURADO DC</v>
+        <v>SPEEDMASTER XTD</v>
       </c>
       <c r="D45" t="str">
         <v/>
@@ -2494,16 +2511,16 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I45" t="str">
-        <v>images/shimano_reels/CURADO DC_main.jpg</v>
+        <v>images/shimano_reels/SPEEDMASTER XTD_main.jpg</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2512,7 +2529,7 @@
         <v/>
       </c>
       <c r="N45" t="str">
-        <v>¥1,725 - ¥1,821</v>
+        <v>¥1,336</v>
       </c>
       <c r="O45" t="str">
         <v>在售</v>
@@ -2520,13 +2537,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SRE5044</v>
+        <v>SRE1044</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="str">
-        <v>CHINUMATIC</v>
+        <v>STRADIC</v>
       </c>
       <c r="D46" t="str">
         <v/>
@@ -2541,16 +2558,16 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I46" t="str">
-        <v>images/shimano_reels/CHINUMATIC_main.jpg</v>
+        <v>images/shimano_reels/STRADIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2559,7 +2576,7 @@
         <v/>
       </c>
       <c r="N46" t="str">
-        <v>¥688 - ¥1,754</v>
+        <v>¥1,179 - ¥1,318</v>
       </c>
       <c r="O46" t="str">
         <v>在售</v>
@@ -2567,13 +2584,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SRE5045</v>
+        <v>SRE1045</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="str">
-        <v>Stephano SS</v>
+        <v>SUPER AERO SpinJoy</v>
       </c>
       <c r="D47" t="str">
         <v/>
@@ -2588,16 +2605,16 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I47" t="str">
-        <v>images/shimano_reels/Stephano SS_main.jpg</v>
+        <v>images/shimano_reels/SUPER AERO SpinJoy_main.jpg</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2606,7 +2623,7 @@
         <v/>
       </c>
       <c r="N47" t="str">
-        <v>¥1,619</v>
+        <v>¥1,145 - ¥1,292</v>
       </c>
       <c r="O47" t="str">
         <v>在售</v>
@@ -2614,13 +2631,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SRE5046</v>
+        <v>SRE1046</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="str">
-        <v>STILE SS</v>
+        <v>SPEEDMASTER XSD</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -2635,16 +2652,16 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I48" t="str">
-        <v>images/shimano_reels/STILE SS_main.jpg</v>
+        <v>images/shimano_reels/SPEEDMASTER XSD_main.jpg</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2653,7 +2670,7 @@
         <v/>
       </c>
       <c r="N48" t="str">
-        <v>¥1,619</v>
+        <v>¥1,260</v>
       </c>
       <c r="O48" t="str">
         <v>在售</v>
@@ -2661,13 +2678,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SRE5047</v>
+        <v>SRE1047</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="str">
-        <v>Scorpion MD 200</v>
+        <v>Sephia BB</v>
       </c>
       <c r="D49" t="str">
         <v/>
@@ -2682,16 +2699,16 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I49" t="str">
-        <v>images/shimano_reels/Scorpion MD 200_main.jpg</v>
+        <v>images/shimano_reels/Sephia BB_main.jpg</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2700,7 +2717,7 @@
         <v/>
       </c>
       <c r="N49" t="str">
-        <v>¥1,607</v>
+        <v>¥1,051 - ¥1,229</v>
       </c>
       <c r="O49" t="str">
         <v>在售</v>
@@ -2708,13 +2725,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SRE5048</v>
+        <v>SRE1048</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="str">
-        <v>TORIUM</v>
+        <v>EXSENCE BB</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -2729,16 +2746,16 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I50" t="str">
-        <v>images/shimano_reels/TORIUM_main.jpg</v>
+        <v>images/shimano_reels/EXSENCE BB_main.jpg</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2747,7 +2764,7 @@
         <v/>
       </c>
       <c r="N50" t="str">
-        <v>¥1,607</v>
+        <v>¥1,168 - ¥1,221</v>
       </c>
       <c r="O50" t="str">
         <v>在售</v>
@@ -2755,13 +2772,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SRE5049</v>
+        <v>SRE1049</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51" t="str">
-        <v>TRANX 200</v>
+        <v>AERO XR</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -2776,16 +2793,16 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I51" t="str">
-        <v>images/shimano_reels/TRANX 200_main.jpg</v>
+        <v>images/shimano_reels/AERO XR_main.jpg</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2794,7 +2811,7 @@
         <v/>
       </c>
       <c r="N51" t="str">
-        <v>¥1,607</v>
+        <v>¥1,071 - ¥1,168</v>
       </c>
       <c r="O51" t="str">
         <v>在售</v>
@@ -2802,13 +2819,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SRE5050</v>
+        <v>SRE1050</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="str">
-        <v>TRANX</v>
+        <v>ULTEGRA</v>
       </c>
       <c r="D52" t="str">
         <v/>
@@ -2823,16 +2840,16 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I52" t="str">
-        <v>images/shimano_reels/TRANX_main.jpg</v>
+        <v>images/shimano_reels/ULTEGRA_main.jpg</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2841,7 +2858,7 @@
         <v/>
       </c>
       <c r="N52" t="str">
-        <v>¥1,478</v>
+        <v>¥964 - ¥1,126</v>
       </c>
       <c r="O52" t="str">
         <v>在售</v>
@@ -2849,13 +2866,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SRE5051</v>
+        <v>SRE1051</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" t="str">
-        <v>BARCHETTA</v>
+        <v>Soare BB</v>
       </c>
       <c r="D53" t="str">
         <v/>
@@ -2870,16 +2887,16 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I53" t="str">
-        <v>images/shimano_reels/BARCHETTA_main.jpg</v>
+        <v>images/shimano_reels/Soare BB_main.jpg</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2888,7 +2905,7 @@
         <v/>
       </c>
       <c r="N53" t="str">
-        <v>¥1,405 - ¥1,473</v>
+        <v>¥1,031 - ¥1,061</v>
       </c>
       <c r="O53" t="str">
         <v>在售</v>
@@ -2896,13 +2913,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SRE5052</v>
+        <v>SRE1052</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" t="str">
-        <v>BARCHETTA SC</v>
+        <v>AERLEX XTC</v>
       </c>
       <c r="D54" t="str">
         <v/>
@@ -2917,16 +2934,16 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I54" t="str">
-        <v>images/shimano_reels/BARCHETTA SC_main.jpg</v>
+        <v>images/shimano_reels/AERLEX XTC_main.jpg</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2935,7 +2952,7 @@
         <v/>
       </c>
       <c r="N54" t="str">
-        <v>¥1,376 - ¥1,470</v>
+        <v>¥1,050</v>
       </c>
       <c r="O54" t="str">
         <v>在售</v>
@@ -2943,13 +2960,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SRE5053</v>
+        <v>SRE1053</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="str">
-        <v>SLX DC</v>
+        <v>AERLEX XSC</v>
       </c>
       <c r="D55" t="str">
         <v/>
@@ -2964,16 +2981,16 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I55" t="str">
-        <v>images/shimano_reels/SLX DC_main.jpg</v>
+        <v>images/shimano_reels/AERLEX XSC_main.jpg</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2982,7 +2999,7 @@
         <v/>
       </c>
       <c r="N55" t="str">
-        <v>¥1,425</v>
+        <v>¥1,050</v>
       </c>
       <c r="O55" t="str">
         <v>在售</v>
@@ -2990,13 +3007,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SRE5054</v>
+        <v>SRE1054</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56" t="str">
-        <v>CURADO</v>
+        <v>AERO</v>
       </c>
       <c r="D56" t="str">
         <v/>
@@ -3011,16 +3028,16 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I56" t="str">
-        <v>images/shimano_reels/CURADO_main.jpg</v>
+        <v>images/shimano_reels/AERO_main.jpg</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -3029,7 +3046,7 @@
         <v/>
       </c>
       <c r="N56" t="str">
-        <v>¥1,254 - ¥1,307</v>
+        <v>¥869 - ¥976</v>
       </c>
       <c r="O56" t="str">
         <v>在售</v>
@@ -3037,13 +3054,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SRE5055</v>
+        <v>SRE1055</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="str">
-        <v>CURADO 150</v>
+        <v>MIRAVEL</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -3058,16 +3075,16 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I57" t="str">
-        <v>images/shimano_reels/CURADO 150_main.jpg</v>
+        <v>images/shimano_reels/MIRAVEL_main.jpg</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -3076,7 +3093,7 @@
         <v/>
       </c>
       <c r="N57" t="str">
-        <v>¥1,286</v>
+        <v>¥857 - ¥922</v>
       </c>
       <c r="O57" t="str">
         <v>在售</v>
@@ -3084,13 +3101,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SRE5056</v>
+        <v>SRE1056</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" t="str">
-        <v>CURADO MGL</v>
+        <v>NASCI</v>
       </c>
       <c r="D58" t="str">
         <v/>
@@ -3105,16 +3122,16 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I58" t="str">
-        <v>images/shimano_reels/CURADO MGL_main.jpg</v>
+        <v>images/shimano_reels/NASCI_main.jpg</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -3123,7 +3140,7 @@
         <v/>
       </c>
       <c r="N58" t="str">
-        <v>¥1,239 - ¥1,254</v>
+        <v>¥672 - ¥735</v>
       </c>
       <c r="O58" t="str">
         <v>在售</v>
@@ -3131,13 +3148,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SRE5057</v>
+        <v>SRE1057</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="str">
-        <v>CURADO BFS</v>
+        <v>SOCORRO SW</v>
       </c>
       <c r="D59" t="str">
         <v/>
@@ -3152,16 +3169,16 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I59" t="str">
-        <v>images/shimano_reels/CURADO BFS_main.jpg</v>
+        <v>images/shimano_reels/SOCORRO SW_main.jpg</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3170,7 +3187,7 @@
         <v/>
       </c>
       <c r="N59" t="str">
-        <v>¥1,204</v>
+        <v>¥735</v>
       </c>
       <c r="O59" t="str">
         <v>在售</v>
@@ -3178,13 +3195,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SRE5058</v>
+        <v>SRE1058</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60" t="str">
-        <v>SLX</v>
+        <v>AERO BB</v>
       </c>
       <c r="D60" t="str">
         <v/>
@@ -3199,16 +3216,16 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I60" t="str">
-        <v>images/shimano_reels/SLX_main.jpg</v>
+        <v>images/shimano_reels/AERO BB_main.jpg</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3217,7 +3234,7 @@
         <v/>
       </c>
       <c r="N60" t="str">
-        <v>¥697 - ¥1,181</v>
+        <v>¥515 - ¥622</v>
       </c>
       <c r="O60" t="str">
         <v>在售</v>
@@ -3225,13 +3242,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SRE5059</v>
+        <v>SRE1059</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61" t="str">
-        <v>BARCHETTA BB</v>
+        <v>SAHARA</v>
       </c>
       <c r="D61" t="str">
         <v/>
@@ -3246,16 +3263,16 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I61" t="str">
-        <v>images/shimano_reels/BARCHETTA BB_main.jpg</v>
+        <v>images/shimano_reels/SAHARA_main.jpg</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3264,7 +3281,7 @@
         <v/>
       </c>
       <c r="N61" t="str">
-        <v>¥1,046 - ¥1,091</v>
+        <v>¥552 - ¥622</v>
       </c>
       <c r="O61" t="str">
         <v>在售</v>
@@ -3272,13 +3289,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SRE5060</v>
+        <v>SRE1060</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="str">
-        <v>SLX BFS</v>
+        <v>ACTIVECAST</v>
       </c>
       <c r="D62" t="str">
         <v/>
@@ -3293,16 +3310,16 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I62" t="str">
-        <v>images/shimano_reels/SLX BFS_main.jpg</v>
+        <v>images/shimano_reels/ACTIVECAST_main.jpg</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3311,7 +3328,7 @@
         <v/>
       </c>
       <c r="N62" t="str">
-        <v>¥1,048</v>
+        <v>¥541 - ¥563</v>
       </c>
       <c r="O62" t="str">
         <v>在售</v>
@@ -3319,13 +3336,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SRE5061</v>
+        <v>SRE1061</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" t="str">
-        <v>GRAPPLER BB</v>
+        <v>SEDONA</v>
       </c>
       <c r="D63" t="str">
         <v/>
@@ -3340,16 +3357,16 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I63" t="str">
-        <v>images/shimano_reels/GRAPPLER BB_main.jpg</v>
+        <v>images/shimano_reels/SEDONA_main.jpg</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3358,7 +3375,7 @@
         <v/>
       </c>
       <c r="N63" t="str">
-        <v>¥925</v>
+        <v>¥411 - ¥557</v>
       </c>
       <c r="O63" t="str">
         <v>在售</v>
@@ -3366,13 +3383,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SRE5062</v>
+        <v>SRE1062</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64" t="str">
-        <v>SLX XT</v>
+        <v>ALIVIO</v>
       </c>
       <c r="D64" t="str">
         <v/>
@@ -3387,16 +3404,16 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I64" t="str">
-        <v>images/shimano_reels/SLX XT_main.jpg</v>
+        <v>images/shimano_reels/ALIVIO_main.jpg</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3405,7 +3422,7 @@
         <v/>
       </c>
       <c r="N64" t="str">
-        <v>¥861 - ¥879</v>
+        <v>¥394 - ¥422</v>
       </c>
       <c r="O64" t="str">
         <v>在售</v>
@@ -3413,13 +3430,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SRE5063</v>
+        <v>SRE1063</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="str">
-        <v>小船</v>
+        <v>NEXAVE</v>
       </c>
       <c r="D65" t="str">
         <v/>
@@ -3434,16 +3451,16 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I65" t="str">
-        <v>images/shimano_reels/小船_main.jpg</v>
+        <v>images/shimano_reels/NEXAVE_main.jpg</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3452,7 +3469,7 @@
         <v/>
       </c>
       <c r="N65" t="str">
-        <v>¥746 - ¥851</v>
+        <v>¥347 - ¥419</v>
       </c>
       <c r="O65" t="str">
         <v>在售</v>
@@ -3460,13 +3477,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SRE5064</v>
+        <v>SRE1064</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66" t="str">
-        <v>CARDIFF</v>
+        <v>CATANA</v>
       </c>
       <c r="D66" t="str">
         <v/>
@@ -3481,16 +3498,16 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I66" t="str">
-        <v>images/shimano_reels/CARDIFF_main.jpg</v>
+        <v>images/shimano_reels/CATANA_main.jpg</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3499,7 +3516,7 @@
         <v/>
       </c>
       <c r="N66" t="str">
-        <v>¥693 - ¥830</v>
+        <v>¥290 - ¥333</v>
       </c>
       <c r="O66" t="str">
         <v>在售</v>
@@ -3507,13 +3524,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SRE5065</v>
+        <v>SRE1065</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67" t="str">
-        <v>幻风 XT</v>
+        <v>SIENNA</v>
       </c>
       <c r="D67" t="str">
         <v/>
@@ -3528,16 +3545,16 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I67" t="str">
-        <v>images/shimano_reels/幻风 XT_main.jpg</v>
+        <v>images/shimano_reels/SIENNA_main.jpg</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3546,7 +3563,7 @@
         <v/>
       </c>
       <c r="N67" t="str">
-        <v>¥719</v>
+        <v>¥216 - ¥237</v>
       </c>
       <c r="O67" t="str">
         <v>在售</v>
@@ -3554,13 +3571,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SRE5066</v>
+        <v>SRE1066</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" t="str">
-        <v>TITANOS FUNE GT</v>
+        <v>FX</v>
       </c>
       <c r="D68" t="str">
         <v/>
@@ -3575,16 +3592,16 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="I68" t="str">
-        <v>images/shimano_reels/TITANOS FUNE GT_main.jpg</v>
+        <v>images/shimano_reels/FX_main.jpg</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3593,7 +3610,7 @@
         <v/>
       </c>
       <c r="N68" t="str">
-        <v>¥583 - ¥678</v>
+        <v>¥179 - ¥200</v>
       </c>
       <c r="O68" t="str">
         <v>在售</v>
@@ -3601,13 +3618,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SRE5067</v>
+        <v>SRE5000</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69" t="str">
-        <v>BASS ONE XT</v>
+        <v>TIAGRA</v>
       </c>
       <c r="D69" t="str">
         <v/>
@@ -3625,13 +3642,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I69" t="str">
-        <v>images/shimano_reels/BASS ONE XT_main.jpg</v>
+        <v>images/shimano_reels/TIAGRA_main.jpg</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3640,7 +3657,7 @@
         <v/>
       </c>
       <c r="N69" t="str">
-        <v>¥590</v>
+        <v>¥3,801 - ¥8,316</v>
       </c>
       <c r="O69" t="str">
         <v>在售</v>
@@ -3648,13 +3665,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SRE5068</v>
+        <v>SRE5001</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" t="str">
-        <v>CAIUS</v>
+        <v>TALICA</v>
       </c>
       <c r="D70" t="str">
         <v/>
@@ -3672,13 +3689,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I70" t="str">
-        <v>images/shimano_reels/CAIUS_main.jpg</v>
+        <v>images/shimano_reels/TALICA_main.jpg</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3687,7 +3704,7 @@
         <v/>
       </c>
       <c r="N70" t="str">
-        <v>¥580</v>
+        <v>¥3,938 - ¥6,783</v>
       </c>
       <c r="O70" t="str">
         <v>在售</v>
@@ -3695,13 +3712,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SRE5069</v>
+        <v>SRE5002</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71" t="str">
-        <v>BASS RISE</v>
+        <v>EXSENCE DC</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -3719,13 +3736,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I71" t="str">
-        <v>images/shimano_reels/BASS RISE_main.jpg</v>
+        <v>images/shimano_reels/EXSENCE DC_main.jpg</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3734,7 +3751,7 @@
         <v/>
       </c>
       <c r="N71" t="str">
-        <v>¥509 - ¥521</v>
+        <v>¥4,284</v>
       </c>
       <c r="O71" t="str">
         <v>在售</v>
@@ -3742,13 +3759,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SRE5070</v>
+        <v>SRE5003</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72" t="str">
-        <v>幻风</v>
+        <v>ANTARES DC</v>
       </c>
       <c r="D72" t="str">
         <v/>
@@ -3766,13 +3783,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I72" t="str">
-        <v>images/shimano_reels/幻风_main.jpg</v>
+        <v>images/shimano_reels/ANTARES DC_main.jpg</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3781,7 +3798,7 @@
         <v/>
       </c>
       <c r="N72" t="str">
-        <v>¥469</v>
+        <v>¥4,284</v>
       </c>
       <c r="O72" t="str">
         <v>在售</v>
@@ -3789,19 +3806,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SRE5071</v>
+        <v>SRE5004</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73" t="str">
-        <v>CHINU SPECIAL</v>
+        <v>ANTARES DC MD</v>
       </c>
       <c r="D73" t="str">
         <v/>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>2023</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -3813,13 +3830,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I73" t="str">
-        <v>images/shimano_reels/CHINU SPECIAL_main.jpg</v>
+        <v>images/shimano_reels/ANTARES DC MD_main.png</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3828,7 +3845,7 @@
         <v/>
       </c>
       <c r="N73" t="str">
-        <v>¥275 - ¥303</v>
+        <v>¥4,253</v>
       </c>
       <c r="O73" t="str">
         <v>在售</v>
@@ -3836,19 +3853,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SRE1000</v>
+        <v>SRE5005</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74" t="str">
-        <v>STELLA SW</v>
+        <v>OCEA JIGGER 4000/4000HG</v>
       </c>
       <c r="D74" t="str">
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>2026</v>
+        <v/>
       </c>
       <c r="F74" t="str">
         <v/>
@@ -3857,16 +3874,16 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I74" t="str">
-        <v>images/shimano_reels/STELLA SW_main.jpg</v>
+        <v>images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpg</v>
       </c>
       <c r="J74" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K74" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -3875,7 +3892,7 @@
         <v/>
       </c>
       <c r="N74" t="str">
-        <v>¥5,966 - ¥9,307</v>
+        <v>¥3,969</v>
       </c>
       <c r="O74" t="str">
         <v>在售</v>
@@ -3883,13 +3900,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SRE1001</v>
+        <v>SRE5006</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75" t="str">
-        <v>BB-X TECHNIUM FIRE BLOOD</v>
+        <v>CALCUTTA CONQUEST DC</v>
       </c>
       <c r="D75" t="str">
         <v/>
@@ -3904,16 +3921,16 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I75" t="str">
-        <v>images/shimano_reels/BB-X TECHNIUM FIRE BLOOD_main.jpg</v>
+        <v>images/shimano_reels/CALCUTTA CONQUEST DC_main.jpg</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K75" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -3922,7 +3939,7 @@
         <v/>
       </c>
       <c r="N75" t="str">
-        <v>¥5,775</v>
+        <v>¥3,730 - ¥3,885</v>
       </c>
       <c r="O75" t="str">
         <v>在售</v>
@@ -3930,13 +3947,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SRE1002</v>
+        <v>SRE5007</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76" t="str">
-        <v>BB-X TECHNIUM</v>
+        <v>OCEA JIGGER LD</v>
       </c>
       <c r="D76" t="str">
         <v/>
@@ -3951,16 +3968,16 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I76" t="str">
-        <v>images/shimano_reels/BB-X TECHNIUM_main.jpg</v>
+        <v>images/shimano_reels/OCEA JIGGER LD_main.jpg</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K76" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -3969,7 +3986,7 @@
         <v/>
       </c>
       <c r="N76" t="str">
-        <v>¥5,765</v>
+        <v>¥3,864</v>
       </c>
       <c r="O76" t="str">
         <v>在售</v>
@@ -3977,13 +3994,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SRE1003</v>
+        <v>SRE5008</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77" t="str">
-        <v>KISU SPECIAL 45</v>
+        <v>OCEA JIGGER F CUSTOM</v>
       </c>
       <c r="D77" t="str">
         <v/>
@@ -3998,16 +4015,16 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I77" t="str">
-        <v>images/shimano_reels/KISU SPECIAL 45_main.jpg</v>
+        <v>images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpg</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K77" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -4016,7 +4033,7 @@
         <v/>
       </c>
       <c r="N77" t="str">
-        <v>¥5,489</v>
+        <v>¥3,360 - ¥3,843</v>
       </c>
       <c r="O77" t="str">
         <v>在售</v>
@@ -4024,13 +4041,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SRE1004</v>
+        <v>SRE5009</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78" t="str">
-        <v>AERO TECHNIUM MGS XTD</v>
+        <v>OCEA CONQUEST CT</v>
       </c>
       <c r="D78" t="str">
         <v/>
@@ -4045,16 +4062,16 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I78" t="str">
-        <v>images/shimano_reels/AERO TECHNIUM MGS XTD_main.jpg</v>
+        <v>images/shimano_reels/OCEA CONQUEST CT_main.jpg</v>
       </c>
       <c r="J78" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K78" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -4063,7 +4080,7 @@
         <v/>
       </c>
       <c r="N78" t="str">
-        <v>¥5,250</v>
+        <v>¥3,780</v>
       </c>
       <c r="O78" t="str">
         <v>在售</v>
@@ -4071,13 +4088,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SRE1005</v>
+        <v>SRE5010</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79" t="str">
-        <v>AERO TECHNIUM MGS XSD</v>
+        <v>KAIKON</v>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -4092,16 +4109,16 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I79" t="str">
-        <v>images/shimano_reels/AERO TECHNIUM MGS XSD_main.jpg</v>
+        <v>images/shimano_reels/KAIKON_main.jpg</v>
       </c>
       <c r="J79" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K79" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -4110,7 +4127,7 @@
         <v/>
       </c>
       <c r="N79" t="str">
-        <v>¥5,250</v>
+        <v>¥3,567 - ¥3,688</v>
       </c>
       <c r="O79" t="str">
         <v>在售</v>
@@ -4118,13 +4135,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SRE1006</v>
+        <v>SRE5011</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80" t="str">
-        <v>STELLA</v>
+        <v>ANTARES</v>
       </c>
       <c r="D80" t="str">
         <v/>
@@ -4139,16 +4156,16 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I80" t="str">
-        <v>images/shimano_reels/STELLA_main.jpg</v>
+        <v>images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="J80" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K80" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -4157,7 +4174,7 @@
         <v/>
       </c>
       <c r="N80" t="str">
-        <v>¥4,473 - ¥4,840</v>
+        <v>¥3,465</v>
       </c>
       <c r="O80" t="str">
         <v>在售</v>
@@ -4165,13 +4182,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SRE1007</v>
+        <v>SRE5012</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81" t="str">
-        <v>EXSENCE</v>
+        <v>OCEA JIGGER</v>
       </c>
       <c r="D81" t="str">
         <v/>
@@ -4186,16 +4203,16 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I81" t="str">
-        <v>images/shimano_reels/EXSENCE_main.jpg</v>
+        <v>images/shimano_reels/OCEA JIGGER_main.jpg</v>
       </c>
       <c r="J81" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K81" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -4204,7 +4221,7 @@
         <v/>
       </c>
       <c r="N81" t="str">
-        <v>¥3,350 - ¥3,990</v>
+        <v>¥3,045 - ¥3,392</v>
       </c>
       <c r="O81" t="str">
         <v>在售</v>
@@ -4212,13 +4229,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SRE1008</v>
+        <v>SRE5013</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82" t="str">
-        <v>TWINPOWER SW</v>
+        <v>CALCUTTA CONQUEST MD</v>
       </c>
       <c r="D82" t="str">
         <v/>
@@ -4233,16 +4250,16 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I82" t="str">
-        <v>images/shimano_reels/TWINPOWER SW_main.jpg</v>
+        <v>images/shimano_reels/CALCUTTA CONQUEST MD_main.jpg</v>
       </c>
       <c r="J82" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K82" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -4251,7 +4268,7 @@
         <v/>
       </c>
       <c r="N82" t="str">
-        <v>¥3,339 - ¥3,969</v>
+        <v>¥3,380</v>
       </c>
       <c r="O82" t="str">
         <v>在售</v>
@@ -4259,19 +4276,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SRE1009</v>
+        <v>SRE5014</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83" t="str">
-        <v>POWER AERO XTC</v>
+        <v>CALCUTTA CONQUEST BFS LIMITED</v>
       </c>
       <c r="D83" t="str">
         <v/>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>2026</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -4280,16 +4297,16 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I83" t="str">
-        <v>images/shimano_reels/POWER AERO XTC_main.jpg</v>
+        <v>images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpg</v>
       </c>
       <c r="J83" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K83" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -4298,7 +4315,7 @@
         <v/>
       </c>
       <c r="N83" t="str">
-        <v>¥3,880</v>
+        <v>¥3,360</v>
       </c>
       <c r="O83" t="str">
         <v>在售</v>
@@ -4306,13 +4323,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SRE1010</v>
+        <v>SRE5015</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84" t="str">
-        <v>POWER AERO XSC</v>
+        <v>Metanium DC</v>
       </c>
       <c r="D84" t="str">
         <v/>
@@ -4327,16 +4344,16 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I84" t="str">
-        <v>images/shimano_reels/POWER AERO XSC_main.jpg</v>
+        <v>images/shimano_reels/Metanium DC_main.jpg</v>
       </c>
       <c r="J84" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K84" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -4345,7 +4362,7 @@
         <v/>
       </c>
       <c r="N84" t="str">
-        <v>¥3,880</v>
+        <v>¥3,255</v>
       </c>
       <c r="O84" t="str">
         <v>在售</v>
@@ -4353,13 +4370,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SRE1011</v>
+        <v>SRE5016</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85" t="str">
-        <v>BB-X HYPER FORCE TYPE2</v>
+        <v>CALCUTTA CONQUEST</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -4374,16 +4391,16 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I85" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE TYPE2_main.jpg</v>
+        <v>images/shimano_reels/CALCUTTA CONQUEST_main.jpg</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K85" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -4392,7 +4409,7 @@
         <v/>
       </c>
       <c r="N85" t="str">
-        <v>¥3,596</v>
+        <v>¥3,129 - ¥3,255</v>
       </c>
       <c r="O85" t="str">
         <v>在售</v>
@@ -4400,13 +4417,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SRE1012</v>
+        <v>SRE5017</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86" t="str">
-        <v>FLIEGEN</v>
+        <v>OCEA CONQUEST</v>
       </c>
       <c r="D86" t="str">
         <v/>
@@ -4421,16 +4438,16 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I86" t="str">
-        <v>images/shimano_reels/FLIEGEN_main.jpg</v>
+        <v>images/shimano_reels/OCEA CONQUEST_main.jpg</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K86" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -4439,7 +4456,7 @@
         <v/>
       </c>
       <c r="N86" t="str">
-        <v>¥3,392 - ¥3,497</v>
+        <v>¥3,129 - ¥3,245</v>
       </c>
       <c r="O86" t="str">
         <v>在售</v>
@@ -4447,13 +4464,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SRE1013</v>
+        <v>SRE5018</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87" t="str">
-        <v>Vanquish CE</v>
+        <v>CALCUTTA CONQUEST SHALLOW EDITION</v>
       </c>
       <c r="D87" t="str">
         <v/>
@@ -4468,16 +4485,16 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I87" t="str">
-        <v>images/shimano_reels/Vanquish CE_main.jpg</v>
+        <v>images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K87" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -4486,7 +4503,7 @@
         <v/>
       </c>
       <c r="N87" t="str">
-        <v>¥3,332 - ¥3,379</v>
+        <v>¥3,129</v>
       </c>
       <c r="O87" t="str">
         <v>在售</v>
@@ -4494,13 +4511,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SRE1014</v>
+        <v>SRE5019</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88" t="str">
-        <v>Vanquish</v>
+        <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="D88" t="str">
         <v/>
@@ -4515,16 +4532,16 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I88" t="str">
-        <v>images/shimano_reels/Vanquish_main.jpg</v>
+        <v>images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpg</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K88" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -4533,7 +4550,7 @@
         <v/>
       </c>
       <c r="N88" t="str">
-        <v>¥3,203 - ¥3,329</v>
+        <v>¥3,129</v>
       </c>
       <c r="O88" t="str">
         <v>在售</v>
@@ -4541,13 +4558,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SRE1015</v>
+        <v>SRE5020</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89" t="str">
-        <v>SARAGOSA SW</v>
+        <v>OCEA CONQUEST FT</v>
       </c>
       <c r="D89" t="str">
         <v/>
@@ -4562,16 +4579,16 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I89" t="str">
-        <v>images/shimano_reels/SARAGOSA SW_main.jpg</v>
+        <v>images/shimano_reels/OCEA CONQUEST FT_main.jpg</v>
       </c>
       <c r="J89" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K89" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -4580,7 +4597,7 @@
         <v/>
       </c>
       <c r="N89" t="str">
-        <v>¥2,142 - ¥3,299</v>
+        <v>¥3,050</v>
       </c>
       <c r="O89" t="str">
         <v>在售</v>
@@ -4588,13 +4605,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SRE1016</v>
+        <v>SRE5021</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90" t="str">
-        <v>BB-X HYPER FORCE</v>
+        <v>ALDEBARAN DC</v>
       </c>
       <c r="D90" t="str">
         <v/>
@@ -4609,16 +4626,16 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I90" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE_main.jpg</v>
+        <v>images/shimano_reels/ALDEBARAN DC_main.jpg</v>
       </c>
       <c r="J90" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K90" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -4627,7 +4644,7 @@
         <v/>
       </c>
       <c r="N90" t="str">
-        <v>¥2,754 - ¥3,162</v>
+        <v>¥3,045</v>
       </c>
       <c r="O90" t="str">
         <v>在售</v>
@@ -4635,13 +4652,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SRE1017</v>
+        <v>SRE5022</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91" t="str">
-        <v>BB-X Remare</v>
+        <v>STILE</v>
       </c>
       <c r="D91" t="str">
         <v/>
@@ -4656,16 +4673,16 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I91" t="str">
-        <v>images/shimano_reels/BB-X Remare_main.jpg</v>
+        <v>images/shimano_reels/STILE_main.jpg</v>
       </c>
       <c r="J91" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K91" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -4674,7 +4691,7 @@
         <v/>
       </c>
       <c r="N91" t="str">
-        <v>¥3,024 - ¥3,129</v>
+        <v>¥2,700</v>
       </c>
       <c r="O91" t="str">
         <v>在售</v>
@@ -4682,13 +4699,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SRE1018</v>
+        <v>SRE5023</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92" t="str">
-        <v>TWINPOWER</v>
+        <v>BARCHETTA PREMIUM</v>
       </c>
       <c r="D92" t="str">
         <v/>
@@ -4703,16 +4720,16 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I92" t="str">
-        <v>images/shimano_reels/TWINPOWER_main.jpg</v>
+        <v>images/shimano_reels/BARCHETTA PREMIUM_main.jpg</v>
       </c>
       <c r="J92" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K92" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -4721,7 +4738,7 @@
         <v/>
       </c>
       <c r="N92" t="str">
-        <v>¥2,772 - ¥2,946</v>
+        <v>¥2,504 - ¥2,680</v>
       </c>
       <c r="O92" t="str">
         <v>在售</v>
@@ -4729,13 +4746,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SRE1019</v>
+        <v>SRE5024</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93" t="str">
-        <v>TWINPOWER XD</v>
+        <v>GRAPPLER PREMIUM</v>
       </c>
       <c r="D93" t="str">
         <v/>
@@ -4750,16 +4767,16 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I93" t="str">
-        <v>images/shimano_reels/TWINPOWER XD_main.jpg</v>
+        <v>images/shimano_reels/GRAPPLER PREMIUM_main.jpg</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K93" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -4768,7 +4785,7 @@
         <v/>
       </c>
       <c r="N93" t="str">
-        <v>¥2,835 - ¥2,940</v>
+        <v>¥2,674</v>
       </c>
       <c r="O93" t="str">
         <v>在售</v>
@@ -4776,13 +4793,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SRE1020</v>
+        <v>SRE5025</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94" t="str">
-        <v>HYPER FORCE LB</v>
+        <v>ALDEBARAN BFS</v>
       </c>
       <c r="D94" t="str">
         <v/>
@@ -4797,16 +4814,16 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I94" t="str">
-        <v>images/shimano_reels/HYPER FORCE LB_main.jpg</v>
+        <v>images/shimano_reels/ALDEBARAN BFS_main.jpg</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K94" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -4815,7 +4832,7 @@
         <v/>
       </c>
       <c r="N94" t="str">
-        <v>¥2,742 - ¥2,907</v>
+        <v>¥2,604</v>
       </c>
       <c r="O94" t="str">
         <v>在售</v>
@@ -4823,13 +4840,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SRE1021</v>
+        <v>SRE5026</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95" t="str">
-        <v>POWER AERO TD</v>
+        <v>ALDEBARAN MGL</v>
       </c>
       <c r="D95" t="str">
         <v/>
@@ -4844,16 +4861,16 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I95" t="str">
-        <v>images/shimano_reels/POWER AERO TD_main.jpg</v>
+        <v>images/shimano_reels/ALDEBARAN MGL_main.jpg</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K95" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -4862,7 +4879,7 @@
         <v/>
       </c>
       <c r="N95" t="str">
-        <v>¥2,770</v>
+        <v>¥2,562</v>
       </c>
       <c r="O95" t="str">
         <v>在售</v>
@@ -4870,13 +4887,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SRE1022</v>
+        <v>SRE5027</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96" t="str">
-        <v>ULTEGRA XR BIG PIT XTD</v>
+        <v>Metanium SHALLOW EDITION</v>
       </c>
       <c r="D96" t="str">
         <v/>
@@ -4891,16 +4908,16 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I96" t="str">
-        <v>images/shimano_reels/ULTEGRA XR BIG PIT XTD_main.jpg</v>
+        <v>images/shimano_reels/Metanium SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K96" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -4909,7 +4926,7 @@
         <v/>
       </c>
       <c r="N96" t="str">
-        <v>¥2,621</v>
+        <v>¥2,457</v>
       </c>
       <c r="O96" t="str">
         <v>在售</v>
@@ -4917,13 +4934,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SRE1023</v>
+        <v>SRE5028</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97" t="str">
-        <v>ULTEGRA XR BIG PIT XSD</v>
+        <v>Metanium</v>
       </c>
       <c r="D97" t="str">
         <v/>
@@ -4938,16 +4955,16 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I97" t="str">
-        <v>images/shimano_reels/ULTEGRA XR BIG PIT XSD_main.jpg</v>
+        <v>images/shimano_reels/Metanium_main.jpg</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K97" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -4956,7 +4973,7 @@
         <v/>
       </c>
       <c r="N97" t="str">
-        <v>¥2,621</v>
+        <v>¥2,457</v>
       </c>
       <c r="O97" t="str">
         <v>在售</v>
@@ -4964,13 +4981,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SRE1024</v>
+        <v>SRE5029</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" t="str">
-        <v>BB-X HYPER FORCE 1700/C2000</v>
+        <v>SPEEDMASTER 石鲷</v>
       </c>
       <c r="D98" t="str">
         <v/>
@@ -4985,16 +5002,16 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I98" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE 1700_C2000_main.jpg</v>
+        <v>images/shimano_reels/SPEEDMASTER 石鲷_main.jpg</v>
       </c>
       <c r="J98" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K98" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L98" t="str">
         <v/>
@@ -5003,7 +5020,7 @@
         <v/>
       </c>
       <c r="N98" t="str">
-        <v>¥2,573</v>
+        <v>¥2,340 - ¥2,450</v>
       </c>
       <c r="O98" t="str">
         <v>在售</v>
@@ -5011,13 +5028,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SRE1025</v>
+        <v>SRE5030</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99" t="str">
-        <v>BB-X Rinkai SP</v>
+        <v>TYRNOS</v>
       </c>
       <c r="D99" t="str">
         <v/>
@@ -5032,16 +5049,16 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I99" t="str">
-        <v>images/shimano_reels/BB-X Rinkai SP_main.jpg</v>
+        <v>images/shimano_reels/TYRNOS_main.jpg</v>
       </c>
       <c r="J99" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K99" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L99" t="str">
         <v/>
@@ -5050,7 +5067,7 @@
         <v/>
       </c>
       <c r="N99" t="str">
-        <v>¥2,499</v>
+        <v>¥2,235 - ¥2,351</v>
       </c>
       <c r="O99" t="str">
         <v>在售</v>
@@ -5058,13 +5075,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SRE1026</v>
+        <v>SRE5031</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100" t="str">
-        <v>EXSENCE XR</v>
+        <v>EXSENCE DC SS</v>
       </c>
       <c r="D100" t="str">
         <v/>
@@ -5079,16 +5096,16 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I100" t="str">
-        <v>images/shimano_reels/EXSENCE XR_main.jpg</v>
+        <v>images/shimano_reels/EXSENCE DC SS_main.jpg</v>
       </c>
       <c r="J100" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K100" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L100" t="str">
         <v/>
@@ -5097,7 +5114,7 @@
         <v/>
       </c>
       <c r="N100" t="str">
-        <v>¥2,281 - ¥2,398</v>
+        <v>¥2,310</v>
       </c>
       <c r="O100" t="str">
         <v>在售</v>
@@ -5105,13 +5122,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SRE1027</v>
+        <v>SRE5032</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101" t="str">
-        <v>STRADIC SW</v>
+        <v>TRANX 400</v>
       </c>
       <c r="D101" t="str">
         <v/>
@@ -5126,16 +5143,16 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I101" t="str">
-        <v>images/shimano_reels/STRADIC SW_main.jpg</v>
+        <v>images/shimano_reels/TRANX 400_main.jpg</v>
       </c>
       <c r="J101" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K101" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L101" t="str">
         <v/>
@@ -5144,7 +5161,7 @@
         <v/>
       </c>
       <c r="N101" t="str">
-        <v>¥1,885 - ¥2,340</v>
+        <v>¥2,205</v>
       </c>
       <c r="O101" t="str">
         <v>在售</v>
@@ -5152,13 +5169,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SRE1028</v>
+        <v>SRE5033</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102" t="str">
-        <v>Sephia XR</v>
+        <v>Bantam</v>
       </c>
       <c r="D102" t="str">
         <v/>
@@ -5173,16 +5190,16 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I102" t="str">
-        <v>images/shimano_reels/Sephia XR_main.jpg</v>
+        <v>images/shimano_reels/Bantam_main.jpg</v>
       </c>
       <c r="J102" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K102" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L102" t="str">
         <v/>
@@ -5191,7 +5208,7 @@
         <v/>
       </c>
       <c r="N102" t="str">
-        <v>¥2,100 - ¥2,310</v>
+        <v>¥2,184</v>
       </c>
       <c r="O102" t="str">
         <v>在售</v>
@@ -5199,13 +5216,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SRE1029</v>
+        <v>SRE5034</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103" t="str">
-        <v>SUSTAIN</v>
+        <v>TRANX 300</v>
       </c>
       <c r="D103" t="str">
         <v/>
@@ -5220,16 +5237,16 @@
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I103" t="str">
-        <v>images/shimano_reels/SUSTAIN_main.jpg</v>
+        <v>images/shimano_reels/TRANX 300_main.jpg</v>
       </c>
       <c r="J103" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K103" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -5238,7 +5255,7 @@
         <v/>
       </c>
       <c r="N103" t="str">
-        <v>¥2,100 - ¥2,205</v>
+        <v>¥2,142</v>
       </c>
       <c r="O103" t="str">
         <v>在售</v>
@@ -5246,13 +5263,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SRE1030</v>
+        <v>SRE5035</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104" t="str">
-        <v>Soare XR</v>
+        <v>BAYGAME</v>
       </c>
       <c r="D104" t="str">
         <v/>
@@ -5267,16 +5284,16 @@
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I104" t="str">
-        <v>images/shimano_reels/Soare XR_main.jpg</v>
+        <v>images/shimano_reels/BAYGAME_main.jpg</v>
       </c>
       <c r="J104" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K104" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L104" t="str">
         <v/>
@@ -5285,7 +5302,7 @@
         <v/>
       </c>
       <c r="N104" t="str">
-        <v>¥1,898 - ¥2,100</v>
+        <v>¥1,762 - ¥2,100</v>
       </c>
       <c r="O104" t="str">
         <v>在售</v>
@@ -5293,13 +5310,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SRE1031</v>
+        <v>SRE5036</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105" t="str">
-        <v>CARDIFF XR</v>
+        <v>GRAPPLER</v>
       </c>
       <c r="D105" t="str">
         <v/>
@@ -5314,16 +5331,16 @@
         <v/>
       </c>
       <c r="H105" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I105" t="str">
-        <v>images/shimano_reels/CARDIFF XR_main.jpg</v>
+        <v>images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J105" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K105" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L105" t="str">
         <v/>
@@ -5332,7 +5349,7 @@
         <v/>
       </c>
       <c r="N105" t="str">
-        <v>¥2,092</v>
+        <v>¥1,875 - ¥2,050</v>
       </c>
       <c r="O105" t="str">
         <v>在售</v>
@@ -5340,13 +5357,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SRE1032</v>
+        <v>SRE5037</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106" t="str">
-        <v>BB-X DESPINA</v>
+        <v>BARCHETTA F CUSTOM</v>
       </c>
       <c r="D106" t="str">
         <v/>
@@ -5361,16 +5378,16 @@
         <v/>
       </c>
       <c r="H106" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I106" t="str">
-        <v>images/shimano_reels/BB-X DESPINA_main.jpg</v>
+        <v>images/shimano_reels/BARCHETTA F CUSTOM_main.jpg</v>
       </c>
       <c r="J106" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K106" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L106" t="str">
         <v/>
@@ -5379,7 +5396,7 @@
         <v/>
       </c>
       <c r="N106" t="str">
-        <v>¥2,079</v>
+        <v>¥2,023</v>
       </c>
       <c r="O106" t="str">
         <v>在售</v>
@@ -5387,13 +5404,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SRE1033</v>
+        <v>SRE5038</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107" t="str">
-        <v>BULL‘S EYE</v>
+        <v>Scorpion DC MD</v>
       </c>
       <c r="D107" t="str">
         <v/>
@@ -5408,16 +5425,16 @@
         <v/>
       </c>
       <c r="H107" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I107" t="str">
-        <v>images/shimano_reels/BULL‘S EYE_main.jpg</v>
+        <v>images/shimano_reels/Scorpion DC MD_main.jpg</v>
       </c>
       <c r="J107" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K107" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -5426,7 +5443,7 @@
         <v/>
       </c>
       <c r="N107" t="str">
-        <v>¥1,722 - ¥2,048</v>
+        <v>¥2,004</v>
       </c>
       <c r="O107" t="str">
         <v>在售</v>
@@ -5434,13 +5451,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SRE1034</v>
+        <v>SRE5039</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108" t="str">
-        <v>COMPLEX XR</v>
+        <v>SLX DC XT</v>
       </c>
       <c r="D108" t="str">
         <v/>
@@ -5455,16 +5472,16 @@
         <v/>
       </c>
       <c r="H108" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I108" t="str">
-        <v>images/shimano_reels/COMPLEX XR_main.jpg</v>
+        <v>images/shimano_reels/SLX DC XT_main.jpg</v>
       </c>
       <c r="J108" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K108" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L108" t="str">
         <v/>
@@ -5473,7 +5490,7 @@
         <v/>
       </c>
       <c r="N108" t="str">
-        <v>¥1,982 - ¥2,035</v>
+        <v>¥1,966</v>
       </c>
       <c r="O108" t="str">
         <v>在售</v>
@@ -5481,13 +5498,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SRE1035</v>
+        <v>SRE5040</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109" t="str">
-        <v>BAITRUNNER CI4+ XTB</v>
+        <v>Scorpion DC</v>
       </c>
       <c r="D109" t="str">
         <v/>
@@ -5502,16 +5519,16 @@
         <v/>
       </c>
       <c r="H109" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I109" t="str">
-        <v>images/shimano_reels/BAITRUNNER CI4+ XTB_main.jpg</v>
+        <v>images/shimano_reels/Scorpion DC_main.jpg</v>
       </c>
       <c r="J109" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K109" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L109" t="str">
         <v/>
@@ -5520,7 +5537,7 @@
         <v/>
       </c>
       <c r="N109" t="str">
-        <v>¥1,773 - ¥1,828</v>
+        <v>¥1,950</v>
       </c>
       <c r="O109" t="str">
         <v>在售</v>
@@ -5528,13 +5545,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SRE1036</v>
+        <v>SRE5041</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110" t="str">
-        <v>SURF LEADER</v>
+        <v>Scorpion MD 300</v>
       </c>
       <c r="D110" t="str">
         <v/>
@@ -5549,16 +5566,16 @@
         <v/>
       </c>
       <c r="H110" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I110" t="str">
-        <v>images/shimano_reels/SURF LEADER_main.png</v>
+        <v>images/shimano_reels/Scorpion MD 300_main.jpg</v>
       </c>
       <c r="J110" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K110" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L110" t="str">
         <v/>
@@ -5567,7 +5584,7 @@
         <v/>
       </c>
       <c r="N110" t="str">
-        <v>¥1,714 - ¥1,821</v>
+        <v>¥1,928</v>
       </c>
       <c r="O110" t="str">
         <v>在售</v>
@@ -5575,13 +5592,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SRE1037</v>
+        <v>SRE5042</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111" t="str">
-        <v>Sephia SS</v>
+        <v>GRAPPLER CT</v>
       </c>
       <c r="D111" t="str">
         <v/>
@@ -5596,16 +5613,16 @@
         <v/>
       </c>
       <c r="H111" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I111" t="str">
-        <v>images/shimano_reels/Sephia SS_main.jpg</v>
+        <v>images/shimano_reels/GRAPPLER CT_main.jpg</v>
       </c>
       <c r="J111" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K111" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -5614,7 +5631,7 @@
         <v/>
       </c>
       <c r="N111" t="str">
-        <v>¥1,522 - ¥1,666</v>
+        <v>¥1,827</v>
       </c>
       <c r="O111" t="str">
         <v>在售</v>
@@ -5622,19 +5639,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SRE1038</v>
+        <v>SRE5043</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112" t="str">
-        <v>VANFORD</v>
+        <v>CURADO DC</v>
       </c>
       <c r="D112" t="str">
         <v/>
       </c>
       <c r="E112" t="str">
-        <v>2024</v>
+        <v/>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -5643,16 +5660,16 @@
         <v/>
       </c>
       <c r="H112" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I112" t="str">
-        <v>images/shimano_reels/VANFORD_main.jpg</v>
+        <v>images/shimano_reels/CURADO DC_main.jpg</v>
       </c>
       <c r="J112" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K112" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L112" t="str">
         <v/>
@@ -5661,7 +5678,7 @@
         <v/>
       </c>
       <c r="N112" t="str">
-        <v>¥1,460 - ¥1,543</v>
+        <v>¥1,725 - ¥1,821</v>
       </c>
       <c r="O112" t="str">
         <v>在售</v>
@@ -5669,13 +5686,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SRE1039</v>
+        <v>SRE5044</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113" t="str">
-        <v>ULTEGRA XS</v>
+        <v>CHINUMATIC</v>
       </c>
       <c r="D113" t="str">
         <v/>
@@ -5690,16 +5707,16 @@
         <v/>
       </c>
       <c r="H113" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I113" t="str">
-        <v>images/shimano_reels/ULTEGRA XS_main.jpg</v>
+        <v>images/shimano_reels/CHINUMATIC_main.jpg</v>
       </c>
       <c r="J113" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K113" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L113" t="str">
         <v/>
@@ -5708,7 +5725,7 @@
         <v/>
       </c>
       <c r="N113" t="str">
-        <v>¥1,497</v>
+        <v>¥688 - ¥1,754</v>
       </c>
       <c r="O113" t="str">
         <v>在售</v>
@@ -5716,13 +5733,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SRE1040</v>
+        <v>SRE5045</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114" t="str">
-        <v>ULTEGRA XT</v>
+        <v>Stephano SS</v>
       </c>
       <c r="D114" t="str">
         <v/>
@@ -5737,16 +5754,16 @@
         <v/>
       </c>
       <c r="H114" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I114" t="str">
-        <v>images/shimano_reels/ULTEGRA XT_main.jpg</v>
+        <v>images/shimano_reels/Stephano SS_main.jpg</v>
       </c>
       <c r="J114" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K114" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L114" t="str">
         <v/>
@@ -5755,7 +5772,7 @@
         <v/>
       </c>
       <c r="N114" t="str">
-        <v>¥1,497</v>
+        <v>¥1,619</v>
       </c>
       <c r="O114" t="str">
         <v>在售</v>
@@ -5763,13 +5780,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SRE1041</v>
+        <v>SRE5046</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115" t="str">
-        <v>BB-X LARISSA</v>
+        <v>STILE SS</v>
       </c>
       <c r="D115" t="str">
         <v/>
@@ -5784,16 +5801,16 @@
         <v/>
       </c>
       <c r="H115" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I115" t="str">
-        <v>images/shimano_reels/BB-X LARISSA_main.jpg</v>
+        <v>images/shimano_reels/STILE SS_main.jpg</v>
       </c>
       <c r="J115" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K115" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L115" t="str">
         <v/>
@@ -5802,7 +5819,7 @@
         <v/>
       </c>
       <c r="N115" t="str">
-        <v>¥1,449</v>
+        <v>¥1,619</v>
       </c>
       <c r="O115" t="str">
         <v>在售</v>
@@ -5810,13 +5827,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SRE1042</v>
+        <v>SRE5047</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116" t="str">
-        <v>SPHEROS SW</v>
+        <v>Scorpion MD 200</v>
       </c>
       <c r="D116" t="str">
         <v/>
@@ -5831,16 +5848,16 @@
         <v/>
       </c>
       <c r="H116" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I116" t="str">
-        <v>images/shimano_reels/SPHEROS SW_main.jpg</v>
+        <v>images/shimano_reels/Scorpion MD 200_main.jpg</v>
       </c>
       <c r="J116" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K116" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L116" t="str">
         <v/>
@@ -5849,7 +5866,7 @@
         <v/>
       </c>
       <c r="N116" t="str">
-        <v>¥934 - ¥1,436</v>
+        <v>¥1,607</v>
       </c>
       <c r="O116" t="str">
         <v>在售</v>
@@ -5857,13 +5874,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SRE1043</v>
+        <v>SRE5048</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117" t="str">
-        <v>SPEEDMASTER XTD</v>
+        <v>TORIUM</v>
       </c>
       <c r="D117" t="str">
         <v/>
@@ -5878,16 +5895,16 @@
         <v/>
       </c>
       <c r="H117" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I117" t="str">
-        <v>images/shimano_reels/SPEEDMASTER XTD_main.jpg</v>
+        <v>images/shimano_reels/TORIUM_main.jpg</v>
       </c>
       <c r="J117" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K117" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L117" t="str">
         <v/>
@@ -5896,7 +5913,7 @@
         <v/>
       </c>
       <c r="N117" t="str">
-        <v>¥1,336</v>
+        <v>¥1,607</v>
       </c>
       <c r="O117" t="str">
         <v>在售</v>
@@ -5904,13 +5921,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SRE1044</v>
+        <v>SRE5049</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118" t="str">
-        <v>STRADIC</v>
+        <v>TRANX 200</v>
       </c>
       <c r="D118" t="str">
         <v/>
@@ -5925,16 +5942,16 @@
         <v/>
       </c>
       <c r="H118" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I118" t="str">
-        <v>images/shimano_reels/STRADIC_main.jpg</v>
+        <v>images/shimano_reels/TRANX 200_main.jpg</v>
       </c>
       <c r="J118" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K118" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L118" t="str">
         <v/>
@@ -5943,7 +5960,7 @@
         <v/>
       </c>
       <c r="N118" t="str">
-        <v>¥1,179 - ¥1,318</v>
+        <v>¥1,607</v>
       </c>
       <c r="O118" t="str">
         <v>在售</v>
@@ -5951,13 +5968,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SRE1045</v>
+        <v>SRE5050</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119" t="str">
-        <v>SUPER AERO SpinJoy</v>
+        <v>TRANX</v>
       </c>
       <c r="D119" t="str">
         <v/>
@@ -5972,16 +5989,16 @@
         <v/>
       </c>
       <c r="H119" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I119" t="str">
-        <v>images/shimano_reels/SUPER AERO SpinJoy_main.jpg</v>
+        <v>images/shimano_reels/TRANX_main.jpg</v>
       </c>
       <c r="J119" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K119" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L119" t="str">
         <v/>
@@ -5990,7 +6007,7 @@
         <v/>
       </c>
       <c r="N119" t="str">
-        <v>¥1,145 - ¥1,292</v>
+        <v>¥1,478</v>
       </c>
       <c r="O119" t="str">
         <v>在售</v>
@@ -5998,13 +6015,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SRE1046</v>
+        <v>SRE5051</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120" t="str">
-        <v>SPEEDMASTER XSD</v>
+        <v>BARCHETTA</v>
       </c>
       <c r="D120" t="str">
         <v/>
@@ -6019,16 +6036,16 @@
         <v/>
       </c>
       <c r="H120" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I120" t="str">
-        <v>images/shimano_reels/SPEEDMASTER XSD_main.jpg</v>
+        <v>images/shimano_reels/BARCHETTA_main.jpg</v>
       </c>
       <c r="J120" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K120" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L120" t="str">
         <v/>
@@ -6037,7 +6054,7 @@
         <v/>
       </c>
       <c r="N120" t="str">
-        <v>¥1,260</v>
+        <v>¥1,405 - ¥1,473</v>
       </c>
       <c r="O120" t="str">
         <v>在售</v>
@@ -6045,13 +6062,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SRE1047</v>
+        <v>SRE5052</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121" t="str">
-        <v>Sephia BB</v>
+        <v>BARCHETTA SC</v>
       </c>
       <c r="D121" t="str">
         <v/>
@@ -6066,16 +6083,16 @@
         <v/>
       </c>
       <c r="H121" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I121" t="str">
-        <v>images/shimano_reels/Sephia BB_main.jpg</v>
+        <v>images/shimano_reels/BARCHETTA SC_main.jpg</v>
       </c>
       <c r="J121" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K121" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L121" t="str">
         <v/>
@@ -6084,7 +6101,7 @@
         <v/>
       </c>
       <c r="N121" t="str">
-        <v>¥1,051 - ¥1,229</v>
+        <v>¥1,376 - ¥1,470</v>
       </c>
       <c r="O121" t="str">
         <v>在售</v>
@@ -6092,13 +6109,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SRE1048</v>
+        <v>SRE5053</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122" t="str">
-        <v>EXSENCE BB</v>
+        <v>SLX DC</v>
       </c>
       <c r="D122" t="str">
         <v/>
@@ -6113,16 +6130,16 @@
         <v/>
       </c>
       <c r="H122" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I122" t="str">
-        <v>images/shimano_reels/EXSENCE BB_main.jpg</v>
+        <v>images/shimano_reels/SLX DC_main.jpg</v>
       </c>
       <c r="J122" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K122" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L122" t="str">
         <v/>
@@ -6131,7 +6148,7 @@
         <v/>
       </c>
       <c r="N122" t="str">
-        <v>¥1,168 - ¥1,221</v>
+        <v>¥1,425</v>
       </c>
       <c r="O122" t="str">
         <v>在售</v>
@@ -6139,13 +6156,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SRE1049</v>
+        <v>SRE5054</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123" t="str">
-        <v>AERO XR</v>
+        <v>CURADO</v>
       </c>
       <c r="D123" t="str">
         <v/>
@@ -6160,16 +6177,16 @@
         <v/>
       </c>
       <c r="H123" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I123" t="str">
-        <v>images/shimano_reels/AERO XR_main.jpg</v>
+        <v>images/shimano_reels/CURADO_main.jpg</v>
       </c>
       <c r="J123" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K123" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L123" t="str">
         <v/>
@@ -6178,7 +6195,7 @@
         <v/>
       </c>
       <c r="N123" t="str">
-        <v>¥1,071 - ¥1,168</v>
+        <v>¥1,254 - ¥1,307</v>
       </c>
       <c r="O123" t="str">
         <v>在售</v>
@@ -6186,13 +6203,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SRE1050</v>
+        <v>SRE5055</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124" t="str">
-        <v>ULTEGRA</v>
+        <v>CURADO 150</v>
       </c>
       <c r="D124" t="str">
         <v/>
@@ -6207,16 +6224,16 @@
         <v/>
       </c>
       <c r="H124" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I124" t="str">
-        <v>images/shimano_reels/ULTEGRA_main.jpg</v>
+        <v>images/shimano_reels/CURADO 150_main.jpg</v>
       </c>
       <c r="J124" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K124" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L124" t="str">
         <v/>
@@ -6225,7 +6242,7 @@
         <v/>
       </c>
       <c r="N124" t="str">
-        <v>¥964 - ¥1,126</v>
+        <v>¥1,286</v>
       </c>
       <c r="O124" t="str">
         <v>在售</v>
@@ -6233,13 +6250,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SRE1051</v>
+        <v>SRE5056</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125" t="str">
-        <v>Soare BB</v>
+        <v>CURADO MGL</v>
       </c>
       <c r="D125" t="str">
         <v/>
@@ -6254,16 +6271,16 @@
         <v/>
       </c>
       <c r="H125" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I125" t="str">
-        <v>images/shimano_reels/Soare BB_main.jpg</v>
+        <v>images/shimano_reels/CURADO MGL_main.jpg</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L125" t="str">
         <v/>
@@ -6272,7 +6289,7 @@
         <v/>
       </c>
       <c r="N125" t="str">
-        <v>¥1,031 - ¥1,061</v>
+        <v>¥1,239 - ¥1,254</v>
       </c>
       <c r="O125" t="str">
         <v>在售</v>
@@ -6280,13 +6297,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SRE1052</v>
+        <v>SRE5057</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" t="str">
-        <v>AERLEX XTC</v>
+        <v>CURADO BFS</v>
       </c>
       <c r="D126" t="str">
         <v/>
@@ -6301,16 +6318,16 @@
         <v/>
       </c>
       <c r="H126" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I126" t="str">
-        <v>images/shimano_reels/AERLEX XTC_main.jpg</v>
+        <v>images/shimano_reels/CURADO BFS_main.jpg</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L126" t="str">
         <v/>
@@ -6319,7 +6336,7 @@
         <v/>
       </c>
       <c r="N126" t="str">
-        <v>¥1,050</v>
+        <v>¥1,204</v>
       </c>
       <c r="O126" t="str">
         <v>在售</v>
@@ -6327,13 +6344,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>SRE1053</v>
+        <v>SRE5058</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127" t="str">
-        <v>AERLEX XSC</v>
+        <v>SLX</v>
       </c>
       <c r="D127" t="str">
         <v/>
@@ -6348,16 +6365,16 @@
         <v/>
       </c>
       <c r="H127" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I127" t="str">
-        <v>images/shimano_reels/AERLEX XSC_main.jpg</v>
+        <v>images/shimano_reels/SLX_main.jpg</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L127" t="str">
         <v/>
@@ -6366,7 +6383,7 @@
         <v/>
       </c>
       <c r="N127" t="str">
-        <v>¥1,050</v>
+        <v>¥697 - ¥1,181</v>
       </c>
       <c r="O127" t="str">
         <v>在售</v>
@@ -6374,13 +6391,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SRE1054</v>
+        <v>SRE5059</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128" t="str">
-        <v>AERO</v>
+        <v>BARCHETTA BB</v>
       </c>
       <c r="D128" t="str">
         <v/>
@@ -6395,16 +6412,16 @@
         <v/>
       </c>
       <c r="H128" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I128" t="str">
-        <v>images/shimano_reels/AERO_main.jpg</v>
+        <v>images/shimano_reels/BARCHETTA BB_main.jpg</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L128" t="str">
         <v/>
@@ -6413,7 +6430,7 @@
         <v/>
       </c>
       <c r="N128" t="str">
-        <v>¥869 - ¥976</v>
+        <v>¥1,046 - ¥1,091</v>
       </c>
       <c r="O128" t="str">
         <v>在售</v>
@@ -6421,13 +6438,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SRE1055</v>
+        <v>SRE5060</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129" t="str">
-        <v>MIRAVEL</v>
+        <v>SLX BFS</v>
       </c>
       <c r="D129" t="str">
         <v/>
@@ -6442,16 +6459,16 @@
         <v/>
       </c>
       <c r="H129" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I129" t="str">
-        <v>images/shimano_reels/MIRAVEL_main.jpg</v>
+        <v>images/shimano_reels/SLX BFS_main.jpg</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L129" t="str">
         <v/>
@@ -6460,7 +6477,7 @@
         <v/>
       </c>
       <c r="N129" t="str">
-        <v>¥857 - ¥922</v>
+        <v>¥1,048</v>
       </c>
       <c r="O129" t="str">
         <v>在售</v>
@@ -6468,13 +6485,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SRE1056</v>
+        <v>SRE5061</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130" t="str">
-        <v>NASCI</v>
+        <v>GRAPPLER BB</v>
       </c>
       <c r="D130" t="str">
         <v/>
@@ -6489,16 +6506,16 @@
         <v/>
       </c>
       <c r="H130" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I130" t="str">
-        <v>images/shimano_reels/NASCI_main.jpg</v>
+        <v>images/shimano_reels/GRAPPLER BB_main.jpg</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L130" t="str">
         <v/>
@@ -6507,7 +6524,7 @@
         <v/>
       </c>
       <c r="N130" t="str">
-        <v>¥672 - ¥735</v>
+        <v>¥925</v>
       </c>
       <c r="O130" t="str">
         <v>在售</v>
@@ -6515,13 +6532,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SRE1057</v>
+        <v>SRE5062</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131" t="str">
-        <v>SOCORRO SW</v>
+        <v>SLX XT</v>
       </c>
       <c r="D131" t="str">
         <v/>
@@ -6536,16 +6553,16 @@
         <v/>
       </c>
       <c r="H131" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I131" t="str">
-        <v>images/shimano_reels/SOCORRO SW_main.jpg</v>
+        <v>images/shimano_reels/SLX XT_main.jpg</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L131" t="str">
         <v/>
@@ -6554,7 +6571,7 @@
         <v/>
       </c>
       <c r="N131" t="str">
-        <v>¥735</v>
+        <v>¥861 - ¥879</v>
       </c>
       <c r="O131" t="str">
         <v>在售</v>
@@ -6562,13 +6579,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SRE1058</v>
+        <v>SRE5063</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132" t="str">
-        <v>AERO BB</v>
+        <v>小船</v>
       </c>
       <c r="D132" t="str">
         <v/>
@@ -6583,16 +6600,16 @@
         <v/>
       </c>
       <c r="H132" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I132" t="str">
-        <v>images/shimano_reels/AERO BB_main.jpg</v>
+        <v>images/shimano_reels/小船_main.jpg</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L132" t="str">
         <v/>
@@ -6601,7 +6618,7 @@
         <v/>
       </c>
       <c r="N132" t="str">
-        <v>¥515 - ¥622</v>
+        <v>¥746 - ¥851</v>
       </c>
       <c r="O132" t="str">
         <v>在售</v>
@@ -6609,13 +6626,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SRE1059</v>
+        <v>SRE5064</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133" t="str">
-        <v>SAHARA</v>
+        <v>CARDIFF</v>
       </c>
       <c r="D133" t="str">
         <v/>
@@ -6630,16 +6647,16 @@
         <v/>
       </c>
       <c r="H133" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I133" t="str">
-        <v>images/shimano_reels/SAHARA_main.jpg</v>
+        <v>images/shimano_reels/CARDIFF_main.jpg</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L133" t="str">
         <v/>
@@ -6648,7 +6665,7 @@
         <v/>
       </c>
       <c r="N133" t="str">
-        <v>¥552 - ¥622</v>
+        <v>¥693 - ¥830</v>
       </c>
       <c r="O133" t="str">
         <v>在售</v>
@@ -6656,13 +6673,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SRE1060</v>
+        <v>SRE5065</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134" t="str">
-        <v>ACTIVECAST</v>
+        <v>幻风 XT</v>
       </c>
       <c r="D134" t="str">
         <v/>
@@ -6677,16 +6694,16 @@
         <v/>
       </c>
       <c r="H134" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I134" t="str">
-        <v>images/shimano_reels/ACTIVECAST_main.jpg</v>
+        <v>images/shimano_reels/幻风 XT_main.jpg</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L134" t="str">
         <v/>
@@ -6695,7 +6712,7 @@
         <v/>
       </c>
       <c r="N134" t="str">
-        <v>¥541 - ¥563</v>
+        <v>¥719</v>
       </c>
       <c r="O134" t="str">
         <v>在售</v>
@@ -6703,13 +6720,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SRE1061</v>
+        <v>SRE5066</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135" t="str">
-        <v>SEDONA</v>
+        <v>TITANOS FUNE GT</v>
       </c>
       <c r="D135" t="str">
         <v/>
@@ -6724,16 +6741,16 @@
         <v/>
       </c>
       <c r="H135" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I135" t="str">
-        <v>images/shimano_reels/SEDONA_main.jpg</v>
+        <v>images/shimano_reels/TITANOS FUNE GT_main.jpg</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L135" t="str">
         <v/>
@@ -6742,7 +6759,7 @@
         <v/>
       </c>
       <c r="N135" t="str">
-        <v>¥411 - ¥557</v>
+        <v>¥583 - ¥678</v>
       </c>
       <c r="O135" t="str">
         <v>在售</v>
@@ -6750,13 +6767,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SRE1062</v>
+        <v>SRE5067</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136" t="str">
-        <v>ALIVIO</v>
+        <v>BASS ONE XT</v>
       </c>
       <c r="D136" t="str">
         <v/>
@@ -6771,16 +6788,16 @@
         <v/>
       </c>
       <c r="H136" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I136" t="str">
-        <v>images/shimano_reels/ALIVIO_main.jpg</v>
+        <v>images/shimano_reels/BASS ONE XT_main.jpg</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L136" t="str">
         <v/>
@@ -6789,7 +6806,7 @@
         <v/>
       </c>
       <c r="N136" t="str">
-        <v>¥394 - ¥422</v>
+        <v>¥590</v>
       </c>
       <c r="O136" t="str">
         <v>在售</v>
@@ -6797,13 +6814,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SRE1063</v>
+        <v>SRE5068</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137" t="str">
-        <v>NEXAVE</v>
+        <v>CAIUS</v>
       </c>
       <c r="D137" t="str">
         <v/>
@@ -6818,16 +6835,16 @@
         <v/>
       </c>
       <c r="H137" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I137" t="str">
-        <v>images/shimano_reels/NEXAVE_main.jpg</v>
+        <v>images/shimano_reels/CAIUS_main.jpg</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L137" t="str">
         <v/>
@@ -6836,7 +6853,7 @@
         <v/>
       </c>
       <c r="N137" t="str">
-        <v>¥347 - ¥419</v>
+        <v>¥580</v>
       </c>
       <c r="O137" t="str">
         <v>在售</v>
@@ -6844,13 +6861,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SRE1064</v>
+        <v>SRE5069</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138" t="str">
-        <v>CATANA</v>
+        <v>BASS RISE</v>
       </c>
       <c r="D138" t="str">
         <v/>
@@ -6865,16 +6882,16 @@
         <v/>
       </c>
       <c r="H138" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I138" t="str">
-        <v>images/shimano_reels/CATANA_main.jpg</v>
+        <v>images/shimano_reels/BASS RISE_main.jpg</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L138" t="str">
         <v/>
@@ -6883,7 +6900,7 @@
         <v/>
       </c>
       <c r="N138" t="str">
-        <v>¥290 - ¥333</v>
+        <v>¥509 - ¥521</v>
       </c>
       <c r="O138" t="str">
         <v>在售</v>
@@ -6891,13 +6908,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SRE1065</v>
+        <v>SRE5070</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139" t="str">
-        <v>SIENNA</v>
+        <v>幻风</v>
       </c>
       <c r="D139" t="str">
         <v/>
@@ -6912,16 +6929,16 @@
         <v/>
       </c>
       <c r="H139" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I139" t="str">
-        <v>images/shimano_reels/SIENNA_main.jpg</v>
+        <v>images/shimano_reels/幻风_main.jpg</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L139" t="str">
         <v/>
@@ -6930,7 +6947,7 @@
         <v/>
       </c>
       <c r="N139" t="str">
-        <v>¥216 - ¥237</v>
+        <v>¥469</v>
       </c>
       <c r="O139" t="str">
         <v>在售</v>
@@ -6938,13 +6955,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SRE1066</v>
+        <v>SRE5071</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140" t="str">
-        <v>FX</v>
+        <v>CHINU SPECIAL</v>
       </c>
       <c r="D140" t="str">
         <v/>
@@ -6959,16 +6976,16 @@
         <v/>
       </c>
       <c r="H140" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I140" t="str">
-        <v>images/shimano_reels/FX_main.jpg</v>
+        <v>images/shimano_reels/CHINU SPECIAL_main.jpg</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L140" t="str">
         <v/>
@@ -6977,7 +6994,7 @@
         <v/>
       </c>
       <c r="N140" t="str">
-        <v>¥179 - ¥200</v>
+        <v>¥275 - ¥303</v>
       </c>
       <c r="O140" t="str">
         <v>在售</v>
@@ -7012,10 +7029,10 @@
         <v>images/daiwa_reels/IM_Z_リミットブレイカー_TW_HD-C_main.jpg</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L141" t="str">
         <v/>
@@ -7063,10 +7080,10 @@
         <v>images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L142" t="str">
         <v/>
@@ -7114,10 +7131,10 @@
         <v>images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L143" t="str">
         <v/>
@@ -7166,10 +7183,10 @@
         <v>images/daiwa_reels/スティーズ_リミテッド_CT_SV_TW_main.jpg</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L144" t="str">
         <v/>
@@ -7217,10 +7234,10 @@
         <v>images/daiwa_reels/スティーズ_SV_ライト_TW_main.jpg</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L145" t="str">
         <v/>
@@ -7266,10 +7283,10 @@
         <v>images/daiwa_reels/スティーズ_SV_TW100_main.jpg</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L146" t="str">
         <v/>
@@ -7317,10 +7334,10 @@
         <v/>
       </c>
       <c r="J147" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L147" t="str">
         <v/>
@@ -7368,10 +7385,10 @@
         <v>images/daiwa_reels/リョウガ_main.jpg</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L148" t="str">
         <v/>
@@ -7421,10 +7438,10 @@
         <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L149" t="str">
         <v/>
@@ -7470,10 +7487,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_tw_hd_22/__icsFiles/afieldfile/2022/04/08/main.jpg?rev=dd8848fe936e4b268b8bdb9e4b33a4df</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L150" t="str">
         <v/>
@@ -7522,10 +7539,10 @@
         <v>images/daiwa_reels/月下美人_BF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L151" t="str">
         <v/>
@@ -7574,10 +7591,10 @@
         <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L152" t="str">
         <v/>
@@ -7624,10 +7641,10 @@
         <v>images/daiwa_reels/シルバーウルフ_CT_SV_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L153" t="str">
         <v/>
@@ -7677,10 +7694,10 @@
         <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L154" t="str">
         <v/>
@@ -7726,10 +7743,10 @@
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L155" t="str">
         <v/>
@@ -7777,10 +7794,10 @@
         <v>images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L156" t="str">
         <v/>
@@ -7830,10 +7847,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/salt_rl/silverwolf_sv_tw/__icsFiles/artimage/2022/04/01/c_041110017/main_tx_im01_1.jpg?rev=6d195f85744643bda6ef194759f4c436</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L157" t="str">
         <v/>
@@ -7879,10 +7896,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/silvercreek_air_tw_sc/__icsFiles/artimage/2022/03/29/c_041101086/main_tx_im01_3.jpg?rev=d0db4f46700344e7893e0f732daf59a2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L158" t="str">
         <v/>
@@ -7930,10 +7947,10 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L159" t="str">
         <v/>
@@ -7982,10 +7999,10 @@
         <v>images/daiwa_reels/アルファスBF_TW_main.jpg</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L160" t="str">
         <v/>
@@ -8035,10 +8052,10 @@
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_sv_tw21/__icsFiles/artimage/2022/05/02/c_041101076/main_bg02_1.jpg?rev=eb0a7bf7b3584f528da16f4584f37003</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L161" t="str">
         <v/>
@@ -8086,10 +8103,10 @@
         <v>images/daiwa_reels/ソルティスト_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L162" t="str">
         <v/>
@@ -8138,10 +8155,10 @@
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L163" t="str">
         <v/>
@@ -8189,10 +8206,10 @@
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L164" t="str">
         <v/>
@@ -8238,10 +8255,10 @@
         <v>images/daiwa_reels/タトゥーラ_BF_TW_main.jpg</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L165" t="str">
         <v/>
@@ -8291,10 +8308,10 @@
         <v>images/daiwa_reels/タトゥーラ_TW_200_main.jpg</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L166" t="str">
         <v/>
@@ -8345,10 +8362,10 @@
         <v>images/daiwa_reels/タトゥーラ_SV_TW_main.jpg</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L167" t="str">
         <v/>
@@ -8397,10 +8414,10 @@
         <v>images/daiwa_reels/タトゥーラ_TW_100_main.jpg</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L168" t="str">
         <v/>
@@ -8449,10 +8466,10 @@
         <v>images/daiwa_reels/バス__X__100_main.jpg</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L169" t="str">
         <v/>
@@ -8498,10 +8515,10 @@
         <v/>
       </c>
       <c r="J170" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-04-08T16:35:43.751Z</v>
+        <v>2026-04-09T06:29:15.200Z</v>
       </c>
       <c r="L170" t="str">
         <v/>
@@ -8518,21 +8535,21 @@
         <v>On Sale</v>
       </c>
     </row>
-    <row r="171" xml:space="preserve">
+    <row r="171">
       <c r="A171" t="str">
-        <v>DRE1000</v>
+        <v>MRE5000</v>
       </c>
       <c r="B171">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C171" t="str">
-        <v>ソルティガ</v>
+        <v>GAUS 20X</v>
       </c>
       <c r="D171" t="str">
-        <v/>
+        <v>GAUS 20X</v>
       </c>
       <c r="E171" t="str">
-        <v>2025</v>
+        <v/>
       </c>
       <c r="F171" t="str">
         <v/>
@@ -8544,46 +8561,63 @@
         <v>spinning</v>
       </c>
       <c r="I171" t="str">
-        <v>images/daiwa_reels/ソルティガ_main.jpg</v>
+        <v/>
       </c>
       <c r="J171" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K171" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L171" t="str">
         <v/>
       </c>
-      <c r="M171" t="str" xml:space="preserve">
-        <v xml:space="preserve">BREAK YOUR RECORD　-夢を掴み獲れ-「いつか、あの魚を。」アングラーの夢を叶えるために誕生したもの、「SALTIGA」。DAIWAオフショア最強の遺伝子を受け継ぎ、最新のテクノロジーで進化し続ける。前提は、未知の大物との対峙。タックルとしての限界に挑み続け、あらゆる箇所の強度、使いやすく優位になる性能を追求する。ソルティガが課せられているのは、確実に夢の魚へと近づくタックルであるということ。その存在意義をかなえ続けることは、すなわちアングラーの夢がかなうこと。その信頼の性能は、世界中のアングラーの夢をサポートする。 | MONOCOQUE BODY
-                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。
-                                                                        フルメタル（AL製)モノコックボディを採用。高剛性且つ軽量コンパクトハウジングに最大径のタフデジギアを封入する。 | POWERDRIVE DESIGN
-                                                                    パワードライブデザインは、世界中の大型魚と安心して渡り合える高い信頼性を追求した次世代大型スピニングリールの設計思想。このパワードライブデザインは、高効率で力強い巻き上げ力を実現するボディユニット[パワードライブエンジン]と、合理的な球体形状で高剛性と低イナーシャの両立を実現したローターユニット[パワードライブローター]の２つのテクノロジーユニットからなる。ボディユニットの[パワードライブエンジン]は、[オーバーサイズドパワーデジギア]と[ローラーパワーオシレーション]の２つのテクノロジーによって構成される。[オーバーサイズドパワーデジギア]は大口径化・肉厚化と、最適化された歯面形状により、ギアの駆動効率を大幅にアップ。[ローラーパワーオシレーション]はオシレート機構にベアリング方式を採用することで、摩擦抵抗を大幅に低減し、初動レスポンスの向上と、軽い巻き上げを実現した。一方、フロントユニットは、[クランクパワーベール]と[タフラインローラーシステム]の２つのテクノロジーを搭載した[パワードライブローター]によって構成される。[クランクパワーベール]は、ベールの開閉力を強化するとともに、クランク形状を採用することで、ラインローラーへの確実な糸送りを実現。[タフラインローラーシステム]は、ラインローラーの支持構造や形状を見直すことで、耐久性やトラブルレス性を向上させた。これらのテクノロジーの相乗効果により、大型魚をターゲットとしたキャスティングゲームやジギングゲームにおいて、剛性・パワー・耐久性を高次元で実現する。獲るための“強さ”を、ビッグゲームを愛する、すべてのアングラーに。
-                                                                        ※25SALTIGAではPOWERDRIVE DESIGNのオーバーサイズドパワーデジギア、ローラーパワーオシレーション、クランクパワーベール、タフラインローラーシステムをフル搭載。</v>
+      <c r="M171" t="str">
+        <v/>
       </c>
       <c r="N171" t="str">
-        <v>¥155,000 - ¥200,000</v>
+        <v/>
       </c>
       <c r="O171" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="172" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S171" t="str">
+        <v/>
+      </c>
+      <c r="T171" t="str">
+        <v>https://www.megabass.co.jp/site/products/gaus-20x/</v>
+      </c>
+      <c r="U171" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_GAUS_20X-2.jpg</v>
+      </c>
+      <c r="V171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
       <c r="A172" t="str">
-        <v>DRE1001</v>
+        <v>MRE5001</v>
       </c>
       <c r="B172">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C172" t="str">
-        <v>ソルティガ</v>
+        <v>GAUS 30X</v>
       </c>
       <c r="D172" t="str">
-        <v/>
+        <v>GAUS 30X</v>
       </c>
       <c r="E172" t="str">
-        <v>2023</v>
+        <v/>
       </c>
       <c r="F172" t="str">
         <v/>
@@ -8595,44 +8629,63 @@
         <v>spinning</v>
       </c>
       <c r="I172" t="str">
-        <v>images/daiwa_reels/ソルティガ_4000_5000_6000_main.jpg</v>
+        <v/>
       </c>
       <c r="J172" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K172" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L172" t="str">
         <v/>
       </c>
-      <c r="M172" t="str" xml:space="preserve">
-        <v xml:space="preserve">BREAK YOUR RECORD　-夢を掴み獲れ-「いつか、あの魚を。」アングラーの夢を叶えるために誕生したもの、「SALTIGA」。DAIWAオフショア最強の遺伝子を受け継ぎ、最新のテクノロジーで進化し続ける。前提は、未知の大物との対峙。タックルとしての限界に挑み続け、あらゆる箇所の強度、使いやすく優位になる性能を追求する。ソルティガが課せられているのは、確実に夢の魚へと近づくタックルであるということ。その存在意義をかなえ続けることは、すなわちアングラーの夢がかなうこと。その信頼の性能は、世界中のアングラーの夢をサポートする。 | “MQ” meets “AIRDRIVE DESIGN”一本の魚の価値が高い“激戦区”(人的プレッシャーが高いフィールド)における「最大魚クラスのトロフィー」そして「自己記録」を獲る為の”圧倒的パワー・タフさ”と”回転・操作性”を備えた新時代のハイスペックリールの誕生！フルメタル(AL製)モノコックボディに大口径Ｇ１ジュラルミン製MC(マシンカット)タフデジギアを搭載し、破格の「巻きの強さ」と「ギアの強さ」を実現。「強靭」かつ「低慣性」を高次元で両立したAL製 AIRDRIVE ROTORが水中の潮の変化や魚の追従によるルアーの挙動変化といった水中の情報量UPをもたらし、テクニカルな大物狙いにおいて圧倒的なアドバンテージをアングラーに与えてくれる。 “BREAK YOUR RECORD” 全く新しいSALTIGA 4000/5000/6000が新時代のSWゲームを切り拓く！ | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23SALTIGA4000/5000/6000においては、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SHAFT の3つを搭載。</v>
+      <c r="M172" t="str">
+        <v/>
       </c>
       <c r="N172" t="str">
-        <v>¥105,000 - ¥115,000</v>
+        <v/>
       </c>
       <c r="O172" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="173" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+      <c r="R172" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S172" t="str">
+        <v/>
+      </c>
+      <c r="T172" t="str">
+        <v>https://www.megabass.co.jp/site/products/gaus-30x/</v>
+      </c>
+      <c r="U172" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_GAUS_30X-1.jpg</v>
+      </c>
+      <c r="V172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
       <c r="A173" t="str">
-        <v>DRE1002</v>
+        <v>MRE5002</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C173" t="str">
-        <v>EXIST</v>
+        <v>LIN258HM</v>
       </c>
       <c r="D173" t="str">
-        <v/>
+        <v>LIN258HM</v>
       </c>
       <c r="E173" t="str">
-        <v>2022</v>
+        <v/>
       </c>
       <c r="F173" t="str">
         <v/>
@@ -8641,48 +8694,66 @@
         <v/>
       </c>
       <c r="H173" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I173" t="str">
-        <v>images/daiwa_reels/EXIST_main.jpg</v>
+        <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K173" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L173" t="str">
         <v/>
       </c>
-      <c r="M173" t="str" xml:space="preserve">
-        <v xml:space="preserve">小型スピニングリールに求められる機能と美。ダイワのクラフトマンシップから生み出された、ひとつの結晶。それが、EXIST。その基幹をなすテクノロジー「AIRDRIVE DESIGN」。釣り人が求める、意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。このAIRDRIVE DESIGNは、最大4つのテクノロジーで構成される。その中でも象徴となるのが、エアドライブローター。心揺さぶるような軽快な回転フィーリングを実現している。そこからは想像もできないような、確かな剛性感を生み出すのが、モノコックボディ。たわみにくく、安定した回転を生み出す源である。その屈強なボディに守られ、限りなくノイズレスな回転を実現するタフデジギアには、ギア硬度を高めるために特殊表面処理を施し、万全を期した。ダイワ独自の防水・耐久テクノロジーであるマグシールドは、ピニオン部とラインローラー部に搭載するとともに、ドライブギア両端部にはマグシールドボールベアリングで、高度な防水性能を実現（SFモデルはピニオン部の1箇所のみ）。ドラグは、魚の引きに合わせて滑らかに効き続けるATDの特性をそのままに、初動レスポンスをさらに向上させ、ライトライン使用時でも安心してファイトが可能なATD TYPE-Lを搭載した。これらから生み出されるパフォーマンスを、単なる道具としてだけではなく、アングラーと心通わせるものにするために、EXISTは、そのデザインやサービスにも想いを込めている。ショア、オフショアを問わず、あらゆるフィールドで調和するピュアな造形。末永く安心してお使いいただくためのユーザーサポート。すべては、未来のルアーフィッシングシーンを切り拓く存在であるために。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※LTモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。SFモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      <c r="M173" t="str">
+        <v/>
       </c>
       <c r="N173" t="str">
-        <v>¥102,000 - ¥110,000</v>
+        <v/>
       </c>
       <c r="O173" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="174" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+      <c r="T173" t="str">
+        <v>https://www.megabass.co.jp/site/products/lin258hm/</v>
+      </c>
+      <c r="U173" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_LIN258HM.jpg</v>
+      </c>
+      <c r="V173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
       <c r="A174" t="str">
-        <v>DRE1003</v>
+        <v>MRE5003</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C174" t="str">
-        <v>セルテート SW</v>
+        <v>RC-IDATEN 256</v>
       </c>
       <c r="D174" t="str">
-        <v/>
+        <v>RC-IDATEN 256</v>
       </c>
       <c r="E174" t="str">
-        <v>2026</v>
+        <v/>
       </c>
       <c r="F174" t="str">
         <v/>
@@ -8691,48 +8762,66 @@
         <v/>
       </c>
       <c r="H174" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I174" t="str">
-        <v>images/daiwa_reels/セルテート_SW_8000___10000___14000___18000___20000_main.jpg</v>
+        <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K174" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L174" t="str">
         <v/>
       </c>
-      <c r="M174" t="str" xml:space="preserve">
-        <v xml:space="preserve">MONOCOQUE BODY
-                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。 | POWERDRIVE DESIGN
-                                                                    パワードライブデザインは、世界中の大型魚と安心して渡り合える高い信頼性を追求した次世代大型スピニングリールの設計思想。このパワードライブデザインは、高効率で力強い巻き上げ力を実現するボディユニット[パワードライブエンジン]と、合理的な球体形状で高剛性と低イナーシャの両立を実現したローターユニット[パワードライブローター]の２つのテクノロジーユニットからなる。ボディユニットの[パワードライブエンジン]は、[オーバーサイズドパワーデジギア]と[ローラーパワーオシレーション]の２つのテクノロジーによって構成される。[オーバーサイズドパワーデジギア]は大口径化・肉厚化と、最適化された歯面形状により、ギアの駆動効率を大幅にアップ。[ローラーパワーオシレーション]はオシレート機構にベアリング方式を採用することで、摩擦抵抗を大幅に低減し、初動レスポンスの向上と、軽い巻き上げを実現した。一方、フロントユニットは、[クランクパワーベール]と[タフラインローラーシステム]の２つのテクノロジーを搭載した[パワードライブローター]によって構成される。[クランクパワーベール]は、ベールの開閉力を強化するとともに、クランク形状を採用することで、ラインローラーへの確実な糸送りを実現。[タフラインローラーシステム]は、ラインローラーの支持構造や形状を見直すことで、耐久性やトラブルレス性を向上させた。これらのテクノロジーの相乗効果により、大型魚をターゲットとしたキャスティングゲームやジギングゲームにおいて、剛性・パワー・耐久性を高次元で実現する。獲るための“強さ”を、ビッグゲームを愛する、すべてのアングラーに。 | ROLLER POWER OSCILLATION
-                                                                    高負荷が絶え間なく続く大型魚とのファイトでは、巻き上げで生じるオシレート部の摩擦抵抗がパワーの伝達ロスに繋がる。その摩擦を極限まで減らすべく、摺動部分は従来のピラー式から2ベアリング式オシレートに変更。これによりオシレート効率は約30%向上し、高負荷時でもスムーズな初動レスポンスと、軽くてパワフルな巻き上げを実現した。※当社比較テストによる。</v>
+      <c r="M174" t="str">
+        <v/>
       </c>
       <c r="N174" t="str">
-        <v>¥93,100 - ¥104,500</v>
+        <v/>
       </c>
       <c r="O174" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="175" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+      <c r="R174" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S174" t="str">
+        <v/>
+      </c>
+      <c r="T174" t="str">
+        <v>https://www.megabass.co.jp/site/products/rc-idaten256/</v>
+      </c>
+      <c r="U174" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2014/06/main_001_megabass_idaten-x_256.jpg</v>
+      </c>
+      <c r="V174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
       <c r="A175" t="str">
-        <v>DRE1004</v>
+        <v>MRE5004</v>
       </c>
       <c r="B175">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C175" t="str">
-        <v>トーナメントサーフ 45</v>
+        <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
       <c r="D175" t="str">
-        <v/>
+        <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
       <c r="E175" t="str">
-        <v>2019</v>
+        <v/>
       </c>
       <c r="F175" t="str">
         <v/>
@@ -8741,46 +8830,66 @@
         <v/>
       </c>
       <c r="H175" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I175" t="str">
         <v/>
       </c>
       <c r="J175" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K175" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L175" t="str">
         <v/>
       </c>
-      <c r="M175" t="str" xml:space="preserve">
-        <v xml:space="preserve">さらに先に。「TOURNAMENT」。TOURNAMENTは、トーナメンターを勝利に導くために、先進・先鋭のテクノロジーを搭載し、進化し続ける。「さらに遠くへ」「さらに感度よく」。激化するトーナメントシーンを勝ち残るための、トーナメンターの要求は厳しい。目指すのは、釣りの技術に革新をもたらし、アングラーの満足感へと繋がるプロダクト。最先端の技術をいち早く採り入れ、トーナメントの新しい基準を築き上げていく。TOURNAMENTの勝利への探求が終わることはなく、常にトーナメンターとともにある。 | すべては勝つために。現在のキストーナメントシーンにおいて求められる性能とは何か。リール形状そのものから見直し、まさにゼロから新たなTOURNAMENTを創り上げた。45mmストロークだからこそ実現可能な中近距離から遠距離までカバーできる対応力。遠投域からトルクフル&amp;スムーズな巻き上げ性能。起伏変化をキャスターへ伝えるブレのない回転性能。過酷なキストーナメントシーンで、初期性能を維持する高耐久性能。これらは単にスペックの向上ではない、とことん実釣にこだわり、キャスターの武器になるための進化だ。テーパー角別専用設計「LCスプール」搭載により、理想の放出性能を実現。強さと軽さをもたらすZAIONハウジング、心臓部には高負荷でも屈しないアルミマシンカットタフデジギアで武装し、さらなる高耐久性を実現。ワンピースエアベールによる至極の回転性能は、より快適に、より精悍に。シリーズ最速となるギア比「4.9」の登場により、キストーナメントシーンに衝撃を与える。「DAIWA TECHNOLOGY」のすべてを惜しむことなく投入し、飛距離、回転性能を追い求めた答えが、今ここにある。※ハンドルノブS交換可※ソルト対応 | TOUGH DIGIGEAR
-                                                                    過酷な環境に耐え抜くにはリールを支える強靭な心臓部が必要です。滑らかな回転がより長く続く「タフデジギア」。</v>
+      <c r="M175" t="str">
+        <v/>
       </c>
       <c r="N175" t="str">
-        <v>¥98,000</v>
+        <v/>
       </c>
       <c r="O175" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="176" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+      <c r="R175" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S175" t="str">
+        <v/>
+      </c>
+      <c r="T175" t="str">
+        <v>https://www.megabass.co.jp/site/products/monoblock_sp_grigio_stone/</v>
+      </c>
+      <c r="U175" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2016/12/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
+      </c>
+      <c r="V175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
       <c r="A176" t="str">
-        <v>DRE1005</v>
+        <v>MRE5005</v>
       </c>
       <c r="B176">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C176" t="str">
-        <v>セルテート HD</v>
+        <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
       <c r="D176" t="str">
-        <v/>
+        <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
       <c r="E176" t="str">
-        <v>2026</v>
+        <v/>
       </c>
       <c r="F176" t="str">
         <v/>
@@ -8789,48 +8898,66 @@
         <v/>
       </c>
       <c r="H176" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I176" t="str">
-        <v>images/daiwa_reels/セルテート_HD_main.jpg</v>
+        <v/>
       </c>
       <c r="J176" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K176" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L176" t="str">
         <v/>
       </c>
-      <c r="M176" t="str" xml:space="preserve">
-        <v xml:space="preserve">AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
-                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
+      <c r="M176" t="str">
+        <v/>
       </c>
       <c r="N176" t="str">
-        <v>¥79,500 - ¥88,000</v>
+        <v/>
       </c>
       <c r="O176" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="177" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+      <c r="T176" t="str">
+        <v>https://www.megabass.co.jp/site/products/monoblock_ito-gambler/</v>
+      </c>
+      <c r="U176" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
+      </c>
+      <c r="V176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
       <c r="A177" t="str">
-        <v>DRE1006</v>
+        <v>MRE5006</v>
       </c>
       <c r="B177">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C177" t="str">
-        <v>セルテート SW</v>
+        <v>MONOBLOCK SPECIALE</v>
       </c>
       <c r="D177" t="str">
-        <v/>
+        <v>MONOBLOCK SPECIALE</v>
       </c>
       <c r="E177" t="str">
-        <v>2024</v>
+        <v/>
       </c>
       <c r="F177" t="str">
         <v/>
@@ -8839,51 +8966,66 @@
         <v/>
       </c>
       <c r="H177" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I177" t="str">
-        <v>images/daiwa_reels/セルテート_SW_4000_5000_6000_main.jpg</v>
+        <v/>
       </c>
       <c r="J177" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K177" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L177" t="str">
         <v/>
       </c>
-      <c r="M177" t="str" xml:space="preserve">
-        <v xml:space="preserve">MONOCOQUE BODY
-                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。
-                                                                        フルメタル（AL製)モノコックボディを採用。高剛性且つ軽量コンパクトハウジングに最大径のタフデジギアを封入する。 | TOUGH DIGIGEAR
-                                                                    過酷な環境に耐え抜くにはリールを支える強靭な心臓部が必要です。滑らかな回転がより長く続く「タフデジギア」。
-                                                                        24CERTATE SWに搭載しているG1ジュラルミン（超高強度アルミ）は強度と軽量性を併せ持つ。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24CERTATE SW4000/5000/6000においては、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SHAFTの3つを搭載。</v>
+      <c r="M177" t="str">
+        <v/>
       </c>
       <c r="N177" t="str">
-        <v>¥67,000 - ¥72,700</v>
+        <v/>
       </c>
       <c r="O177" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="178" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+      <c r="R177" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S177" t="str">
+        <v/>
+      </c>
+      <c r="T177" t="str">
+        <v>https://www.megabass.co.jp/site/products/monoblock-speciale/</v>
+      </c>
+      <c r="U177" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2015/04/main_001_MONOBLOCK_SPECIALE.jpg</v>
+      </c>
+      <c r="V177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
       <c r="A178" t="str">
-        <v>DRE1007</v>
+        <v>MRE5007</v>
       </c>
       <c r="B178">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C178" t="str">
-        <v>サーフ ベーシア 45</v>
+        <v>RHODIUM 73</v>
       </c>
       <c r="D178" t="str">
-        <v/>
+        <v>RHODIUM 73</v>
       </c>
       <c r="E178" t="str">
-        <v>2021</v>
+        <v/>
       </c>
       <c r="F178" t="str">
         <v/>
@@ -8892,47 +9034,66 @@
         <v/>
       </c>
       <c r="H178" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I178" t="str">
         <v/>
       </c>
       <c r="J178" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K178" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L178" t="str">
         <v/>
       </c>
-      <c r="M178" t="str" xml:space="preserve">
-        <v xml:space="preserve">19トーナメントサーフ45から受け継いだ飛距離と回転・耐久性能を実現した投釣り専用機。大口径2°テーパーのロングキャスト（LC）スプール、ラインを綾巻きし、ライン同士の食い込みを抑えるクロスラップを搭載し、スムーズなライン放出を実現。パワフルさと巻き易さを追求したギア比「4.1」を全アイテムにて採用。ZAIONボディとタフデジギアの絶妙なバランスによる滑らかな巻上げとマグシールドによる回転耐久性を実現。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      <c r="M178" t="str">
+        <v/>
       </c>
       <c r="N178" t="str">
-        <v>¥68,000 - ¥71,000</v>
+        <v/>
       </c>
       <c r="O178" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="179" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S178" t="str">
+        <v/>
+      </c>
+      <c r="T178" t="str">
+        <v>https://www.megabass.co.jp/site/products/rhodium73/</v>
+      </c>
+      <c r="U178" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_megabass_rhodium_73.jpg</v>
+      </c>
+      <c r="V178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
       <c r="A179" t="str">
-        <v>DRE1008</v>
+        <v>MRE5008</v>
       </c>
       <c r="B179">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C179" t="str">
-        <v>エアリティ</v>
+        <v>RHODIUM 81</v>
       </c>
       <c r="D179" t="str">
-        <v/>
+        <v>RHODIUM 81</v>
       </c>
       <c r="E179" t="str">
-        <v>2023</v>
+        <v/>
       </c>
       <c r="F179" t="str">
         <v/>
@@ -8941,48 +9102,66 @@
         <v/>
       </c>
       <c r="H179" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I179" t="str">
-        <v>images/daiwa_reels/エアリティ_main.jpg</v>
+        <v/>
       </c>
       <c r="J179" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K179" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L179" t="str">
         <v/>
       </c>
-      <c r="M179" t="str" xml:space="preserve">
-        <v xml:space="preserve">かつてない軽さと強さの両立を果たした、超軽量スピニングリール「AIRITY」。LT2500Sで150gと、自重としての軽さはDAIWA史上最高レベルに到達。同時に、“自重以外の軽さ”も手に入れた。それは、タックルとの一体感が得られる軽快な回転フィールと、持ち重りのない最適な重量バランス。その基幹となるテクノロジーが、「エアドライブデザイン」。釣り人が求める、意のままにルアーを操作することを追求した次世代スピニングリールの設計思想で、最大4つのテクノロジーで構成される。そのエアドライブデザインをフル装備することで、リーリング性能とロッドの操作性の向上を高次元で実現。アングラーの意志に対して素直に応える、そのレスポンスが釣る歓びを高めてくれる。軽さを貫くいっぽうで、強さへのこだわりにも、妥協は一切ない。そこに込められているのは、「十分な実釣性能をともなわない軽さには意味がない」というダイワのリール設計における原点。その信念を受け継ぐテクノロジーのひとつが、一体成型構造のモノコックボディ。たわみやゆがみを抑え、力強い巻き上げを生み出す確かな土台。その素材にはマグネシウムを採用。その内部に格納されるのは、滑らかで静かな回転を生み出すタフデジギア。ギア硬度を高める特殊表面処理を施すことで、初期性能が長く続くよう、耐久性も向上させている。防水・防塵も万全を期し、ダイワ独自の防水・耐久テクノロジーであるマグシールドを、ピニオン部とラインローラー部に搭載。ドラグは、ラインへの負荷を低減し、スムーズで安定した滑り出しで、安心してファイトを愉しめるATD TYPE-Lを搭載。スプールには、リップ形状を見直すことで約5％の飛距離アップを実現したLC-ABSを採用など、ダイワテクノロジーの粋を集めた。「AIR＝軽さ」と「REALITY＝真実・実用性」の高次元での融合。高度な実釣性能を備えた超軽量スピニングリール。ライトゲームからライトショアジギングまで、タックルとひとつになれる自由と愉しさを、AIRITYで――。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23AIRITYは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      <c r="M179" t="str">
+        <v/>
       </c>
       <c r="N179" t="str">
-        <v>¥65,000 - ¥69,500</v>
+        <v/>
       </c>
       <c r="O179" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="180" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+      <c r="T179" t="str">
+        <v>https://www.megabass.co.jp/site/products/rhodium81/</v>
+      </c>
+      <c r="U179" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2018/04/main_001_RHODIUM_81.jpg</v>
+      </c>
+      <c r="V179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
       <c r="A180" t="str">
-        <v>DRE1009</v>
+        <v>MRE5009</v>
       </c>
       <c r="B180">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C180" t="str">
-        <v>エアリティ ST</v>
+        <v>RHODIUM 63</v>
       </c>
       <c r="D180" t="str">
-        <v/>
+        <v>RHODIUM 63</v>
       </c>
       <c r="E180" t="str">
-        <v>2023</v>
+        <v/>
       </c>
       <c r="F180" t="str">
         <v/>
@@ -8991,48 +9170,66 @@
         <v/>
       </c>
       <c r="H180" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I180" t="str">
-        <v>images/daiwa_reels/エアリティ_ST_main.jpg</v>
+        <v/>
       </c>
       <c r="J180" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K180" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L180" t="str">
         <v/>
       </c>
-      <c r="M180" t="str" xml:space="preserve">
-        <v xml:space="preserve">エリアトラウトやネイティブトラウト、バスフィッシングにおいて、リールの回転性能を追求するエキスパートアングラーの渇望は、とどまることを知らない。巻き心地をもっと軽く、巻き感度をもっと高く――その飽くなき願いを真摯に受け止め、回転を突き詰めたスペシャルチューン。それが、23AIRITY ST（センシティブチューン）。超軽量スピニングリール「AIRITY」を、さらに繊細かつダイレクトな巻き心地を実現する、もうひとつのAIRITY。ラインナップは、STとST SFを合わせ、フィネスフィッシングに特化した6モデル。23AIRITY／23AIRITY SFの持つ基本性能を維持したまま、ハンドル回転の軽さに直結する回転主要部のBB（ボールベアリング）を、ノーマルモデルのグリス仕様BBからオイル仕様BBに変更。グリスBBの特質である高い耐久性をあえて捨ててまで、粘性の低いオイル仕様BBを選択し、回転の軽さを高次元で突き詰めた。それだけではない。防水・防塵の要であるピニオン部のマグシールドを、あえて採用せず、スペックには表記されないわずかな軽量化にまでこだわり抜いた。それによってアングラーが手にするのは、研ぎ澄まされた回転性能。極めて無感覚に近い指先へのリーリング抵抗、ハンドルを回す手元に伝わる圧倒的な情報量。“ダイレクトな回転フィール”を求めるアングラーに、AIRITY STの矜持を。【23AIRITY ノーマルモデルとの違い】①回転主要部のBBをオイル仕様BB化②マグシールド非搭載③一目でセンシティブチューンモデルと分かるデザイン | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23AIRITY STは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。23AIRITY ST SFは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      <c r="M180" t="str">
+        <v/>
       </c>
       <c r="N180" t="str">
-        <v>¥65,000 - ¥67,500</v>
+        <v/>
       </c>
       <c r="O180" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="181" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+      <c r="T180" t="str">
+        <v>https://www.megabass.co.jp/site/products/rhodium63/</v>
+      </c>
+      <c r="U180" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2018/04/main_001_RHODIUM_63.jpg</v>
+      </c>
+      <c r="V180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
       <c r="A181" t="str">
-        <v>DRE1010</v>
+        <v>MRE5010</v>
       </c>
       <c r="B181">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C181" t="str">
-        <v>セルテート</v>
+        <v>Pagani R100</v>
       </c>
       <c r="D181" t="str">
-        <v/>
+        <v>Pagani R100</v>
       </c>
       <c r="E181" t="str">
-        <v>2024</v>
+        <v/>
       </c>
       <c r="F181" t="str">
         <v/>
@@ -9041,48 +9238,66 @@
         <v/>
       </c>
       <c r="H181" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I181" t="str">
-        <v>images/daiwa_reels/セルテート_main.jpg</v>
+        <v/>
       </c>
       <c r="J181" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K181" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L181" t="str">
         <v/>
       </c>
-      <c r="M181" t="str" xml:space="preserve">
-        <v xml:space="preserve">いつまでも愛着を持って使い込んでもらえるようなスピニングリールを創りたい。特定の誰かのためではなく、すべてのアングラーのために――。そのために目指したのは、使い手を選ばない快適な操作性、不安を感じさせない確かな剛性。CERTATEに込められた、その理念は20年の時を経た今も、何ひとつ変わることはない。NEW CERTATEに搭載された、次世代スピニングリールの設計思想「エアドライブデザイン」は、快適な操作性を求め続けた、CERTATEのひとつの到達点。釣り人が求める、意のままにルアーを操作することを目指した設計思想で、最大4つのテクノロジーで構成される。このエアドライブデザインをフル装備することで得られる恩恵は、あまりにも大きい。最適な重量バランスからなる軽やかな操作性。タックルとの一体感を得られる軽快な回転フィール。わずかな魚のアタリや流れの変化も感じられる巻き感度。ライントラブルの大幅な低頻度化。それは、現代のアングラーに向けたCERTATEの明快な答え。新型ドラグのATD TYPE-Lは、ラインへの負担を軽減し、ハイレスポンスでスムーズな滑り出しによる安心で心地よいファイトを約束してくれる。この操作性は、確かな剛性なくしては得られない。だからこそCERTATEは、一貫して剛性にこだわり続けてきた。その象徴ともいえるのが、アルミ素材による一体成型構造の「モノコックボディ」。従来構造のスピニングリールで弱点だった、高負荷時のボディのたわみを極力抑え、強い巻き上げパワーを実現するダイワ独自のテクノロジー。そこにねじ込まれるエンジンプレートもまた、アルミ製。つまり、アルミ製のフルメタルボディによって、心臓部である内部構造は、がっしりとサポートされている。その内部に組み込まれるドライブギアには、硬度を高める特殊表面処理を施し、高負荷時のギアへのダメージを軽減。その動力をフロントユニットに伝えるメインシャフトには、アルミよりもさらに剛性の高いSUSを採用することで、パワーロスすることなく、パフォーマンスを最大限に発揮する。確かな剛性と快適な操作性。この一環した質実剛健こそ、積み重ねた信頼の証。正統進化を果たした20年目のNEW CERTATE、新時代のスタンダード・スピニングリールを、すべてのアングラーに。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24CERTATEは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      <c r="M181" t="str">
+        <v/>
       </c>
       <c r="N181" t="str">
-        <v>¥54,600 - ¥61,600</v>
+        <v/>
       </c>
       <c r="O181" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="182" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+      <c r="T181" t="str">
+        <v>https://www.megabass.co.jp/site/products/pagani-r100/</v>
+      </c>
+      <c r="U181" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_R100-1.jpg</v>
+      </c>
+      <c r="V181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
       <c r="A182" t="str">
-        <v>DRE1011</v>
+        <v>MRE5011</v>
       </c>
       <c r="B182">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C182" t="str">
-        <v>エメラルダス AIR</v>
+        <v>Pagani P200</v>
       </c>
       <c r="D182" t="str">
-        <v/>
+        <v>Pagani P200</v>
       </c>
       <c r="E182" t="str">
-        <v>2025</v>
+        <v/>
       </c>
       <c r="F182" t="str">
         <v/>
@@ -9091,48 +9306,66 @@
         <v/>
       </c>
       <c r="H182" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I182" t="str">
-        <v>images/daiwa_reels/エメラルダス_AIR_main.jpg</v>
+        <v/>
       </c>
       <c r="J182" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K182" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L182" t="str">
         <v/>
       </c>
-      <c r="M182" t="str" xml:space="preserve">
-        <v xml:space="preserve">イカと関わるすべての時間を、感動で満たすために。「エメラルダス」。それはDAIWAが世界に先駆けて立ち上げた、スクイッド・ゲーミングのトータルタックルブランド。その手にイカをもたらすために。そして、その最高の瞬間が訪れるまでの、イカと関わるすべての時間を、感動で満たすために。爽快なキャストフィールを。フォール、ステイ、フッキングまでの、ただ待つだけだった時間に、変化と予兆を伝え続けてくれる感度を。大物とのファイトでも安心な信頼感を。そして、トータルデザインだからこそ成せる、快適な操作感と、カメラロールで映えるフォトジェニックさを。エメラルダス。手にしたそのときから、いつでも、いつまでも感動を贈りたい。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※25EMERALDAS AIRでは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      <c r="M182" t="str">
+        <v/>
       </c>
       <c r="N182" t="str">
-        <v>¥57,700 - ¥61,500</v>
+        <v/>
       </c>
       <c r="O182" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="183" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+      <c r="R182" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S182" t="str">
+        <v/>
+      </c>
+      <c r="T182" t="str">
+        <v>https://www.megabass.co.jp/site/products/pagani-p200/</v>
+      </c>
+      <c r="U182" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_P200_black-chrome.jpg</v>
+      </c>
+      <c r="V182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
       <c r="A183" t="str">
-        <v>DRE1012</v>
+        <v>MRE5012</v>
       </c>
       <c r="B183">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C183" t="str">
-        <v>ルビアス</v>
+        <v>Pagani P300</v>
       </c>
       <c r="D183" t="str">
-        <v/>
+        <v>Pagani P300</v>
       </c>
       <c r="E183" t="str">
-        <v>2024</v>
+        <v/>
       </c>
       <c r="F183" t="str">
         <v/>
@@ -9141,49 +9374,66 @@
         <v/>
       </c>
       <c r="H183" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I183" t="str">
-        <v>images/daiwa_reels/ルビアス_main.jpg</v>
+        <v/>
       </c>
       <c r="J183" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K183" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L183" t="str">
         <v/>
       </c>
-      <c r="M183" t="str" xml:space="preserve">
-        <v xml:space="preserve">AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※LTモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。SFモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
-                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
+      <c r="M183" t="str">
+        <v/>
       </c>
       <c r="N183" t="str">
-        <v>¥46,700 - ¥54,500</v>
+        <v/>
       </c>
       <c r="O183" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="184" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+      <c r="R183" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S183" t="str">
+        <v/>
+      </c>
+      <c r="T183" t="str">
+        <v>https://www.megabass.co.jp/site/products/pagani-p300/</v>
+      </c>
+      <c r="U183" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
+      </c>
+      <c r="V183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
       <c r="A184" t="str">
-        <v>DRE1013</v>
+        <v>MRE5013</v>
       </c>
       <c r="B184">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C184" t="str">
-        <v>プレッソ</v>
+        <v>LAUDA58</v>
       </c>
       <c r="D184" t="str">
-        <v/>
+        <v>LAUDA58</v>
       </c>
       <c r="E184" t="str">
-        <v>2021</v>
+        <v/>
       </c>
       <c r="F184" t="str">
         <v/>
@@ -9192,46 +9442,66 @@
         <v/>
       </c>
       <c r="H184" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I184" t="str">
         <v/>
       </c>
       <c r="J184" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K184" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L184" t="str">
         <v/>
       </c>
-      <c r="M184" t="str" xml:space="preserve">
-        <v xml:space="preserve">釣り方までもスタイリッシュになっていく。エリアフィッシングの攻略に必要なのは、自然のフィールドとは異なる独自の戦略と技術、そして専用のタックル。エリアフィッシング専用のスペシャルギアとして開発されたのは、イタリア語に語源を持つ『PRESSO』。PRESSOの開発の根底にあるもの。いかにスマートに、いかにクールに釣るか。その釣り方にまでこだわる美意識を集約させたデザインは、タックルをセットした瞬間から、強烈なアイデンティティとともに、アングラーのスイッチを入れる。プロダクトの追求が新しいスタイルまでも提案していく。手にしたあなた自身が、ムーブメントになる。 | DAIWAエリアトラウトブランド「PRESSO」の名を冠するスピニングリールが、ZAION製モノコックボディで新登場。PRESSOリール史上、最軽量の自重、145g（1000S-P）を達成し、またギア部のボールベアリングをオイル仕様化することで、より軽く繊細な巻き心地を実現した。ZAION製モノコックボディ：高い回転精度を維持しながら、自重アンダー150ｇを達成。オイルボールベアリング仕様：巻き感度にこだわったボールベアリングのオイル仕様化。エリアならではのローギア設定（4.9：1）＋ラインキャパ（2.5ｌｂ-100ｍ）超々ジュラルミン製MCタフデジギアATD（スプール2BB仕様）薄肉軽量LC-ABSスプール40mmハンドルアーム＆ハイグリップI シェイプフィネスノブ※淡水専用※ハンドルノブSサイズ交換可 | MONOCOQUE BODY
-                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。</v>
+      <c r="M184" t="str">
+        <v/>
       </c>
       <c r="N184" t="str">
-        <v>¥54,200</v>
+        <v/>
       </c>
       <c r="O184" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="185" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+      <c r="T184" t="str">
+        <v>https://www.megabass.co.jp/site/products/lauda58/</v>
+      </c>
+      <c r="U184" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_LAUDA_58.jpg</v>
+      </c>
+      <c r="V184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
       <c r="A185" t="str">
-        <v>DRE1014</v>
+        <v>MRE5014</v>
       </c>
       <c r="B185">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C185" t="str">
-        <v>カルディア SW</v>
+        <v>LAUDA72</v>
       </c>
       <c r="D185" t="str">
-        <v/>
+        <v>LAUDA72</v>
       </c>
       <c r="E185" t="str">
-        <v>2022</v>
+        <v/>
       </c>
       <c r="F185" t="str">
         <v/>
@@ -9240,47 +9510,66 @@
         <v/>
       </c>
       <c r="H185" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I185" t="str">
         <v/>
       </c>
       <c r="J185" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K185" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L185" t="str">
         <v/>
       </c>
-      <c r="M185" t="str" xml:space="preserve">
-        <v xml:space="preserve">フルメタル（AL製）モノコックボディに大口径タフデジギアを搭載し、パワフルかつ軽快な巻き上げ。4000サイズ～18000サイズという幅広いラインナップで人気のライトショアキャスティングやSLJ（スーパーライトジギング）～大型青物、マグロまで、ソルトルアーゲームを完全網羅。ライトショアジギングやボートサワラゲームに最適な5000-CXHと待望のパワーギアモデル 8000-P &amp; 10000-Pが登場ブリクラスが混じるフィールドでのライトショアジギングやサワラ狙いのボートからのブレードジギング、ライトキャスティングゲームに最適な「5000-CXH」、PE3号～4号前後を使用する青物ジギングに最適な「8000-P」、エビングを筆頭とした相模湾キハダゲームやマグロジギングに最適な80mmロングハンドルを搭載した「10000-P」が登場。※ハンドルノブ S 交換可（4000～6000）※ハンドルノブ L 交換可（8000～18000）※ソルト対応 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | MONOCOQUE BODY
-                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。</v>
+      <c r="M185" t="str">
+        <v/>
       </c>
       <c r="N185" t="str">
-        <v>¥34,800 - ¥49,300</v>
+        <v/>
       </c>
       <c r="O185" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="186" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+      <c r="T185" t="str">
+        <v>https://www.megabass.co.jp/site/products/lauda72/</v>
+      </c>
+      <c r="U185" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2016/12/main_001_LAUDA_72.jpg</v>
+      </c>
+      <c r="V185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
       <c r="A186" t="str">
-        <v>DRE1015</v>
+        <v>MRE5015</v>
       </c>
       <c r="B186">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C186" t="str">
-        <v>ルビアス ST</v>
+        <v>LAUDA72 LIMITED EDITION</v>
       </c>
       <c r="D186" t="str">
-        <v/>
+        <v>LAUDA72 LIMITED EDITION</v>
       </c>
       <c r="E186" t="str">
-        <v>2024</v>
+        <v/>
       </c>
       <c r="F186" t="str">
         <v/>
@@ -9289,49 +9578,66 @@
         <v/>
       </c>
       <c r="H186" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I186" t="str">
-        <v>images/daiwa_reels/ルビアス_ST_main.jpg</v>
+        <v/>
       </c>
       <c r="J186" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K186" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L186" t="str">
         <v/>
       </c>
-      <c r="M186" t="str" xml:space="preserve">
-        <v xml:space="preserve">AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24LUVIAS ST LTは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。24LUVIAS ST SFは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
-                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
+      <c r="M186" t="str">
+        <v/>
       </c>
       <c r="N186" t="str">
-        <v>¥46,700 - ¥47,700</v>
+        <v/>
       </c>
       <c r="O186" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="187" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+      <c r="T186" t="str">
+        <v>https://www.megabass.co.jp/site/products/lauda72ltd/</v>
+      </c>
+      <c r="U186" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
+      </c>
+      <c r="V186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
       <c r="A187" t="str">
-        <v>DRE1016</v>
+        <v>MRE5016</v>
       </c>
       <c r="B187">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C187" t="str">
-        <v>キャスティズム 25</v>
+        <v>IP79</v>
       </c>
       <c r="D187" t="str">
-        <v/>
+        <v>IP79</v>
       </c>
       <c r="E187" t="str">
-        <v>2019</v>
+        <v/>
       </c>
       <c r="F187" t="str">
         <v/>
@@ -9340,44 +9646,63 @@
         <v/>
       </c>
       <c r="H187" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I187" t="str">
         <v/>
       </c>
       <c r="J187" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K187" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L187" t="str">
         <v/>
       </c>
-      <c r="M187" t="str" xml:space="preserve">
-        <v xml:space="preserve">様々な魚種をターゲットにするキャスティズムに必要な性能を追求。アルミマシンカットタフデジギアを搭載し、耐久性を向上させた。ねじ込み式ハンドルを採用しでガタを徹底的に排除。また、より軽量なスプールの採用などにより全体の軽量化を図り、更なるキャスティング性能向上を達成。キャスティングとリトリーブを何度も繰り返すキャスティズムにはさらに心強い仕様となった。ドラグは、置き竿釣法等で有効なクイックドラグと不意の強い引きにもスムーズに作動するATDの2タイプを用意。スプールには、巻いてあるラインの種類が一目で分かるラインメモリー搭載、さらに、力糸や太いリーダーに対応したラインクリップを搭載し、より快適性を高めた。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      <c r="M187" t="str">
+        <v/>
       </c>
       <c r="N187" t="str">
-        <v>¥40,000</v>
+        <v/>
       </c>
       <c r="O187" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="188" xml:space="preserve">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+      <c r="R187" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S187" t="str">
+        <v/>
+      </c>
+      <c r="T187" t="str">
+        <v>https://www.megabass.co.jp/site/products/ip79/</v>
+      </c>
+      <c r="U187" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/08/main_001_IP79.jpg</v>
+      </c>
+      <c r="V187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
       <c r="A188" t="str">
-        <v>DRE1017</v>
+        <v>MRE5017</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C188" t="str">
-        <v>ロングビーム 35</v>
+        <v>IP68</v>
       </c>
       <c r="D188" t="str">
-        <v/>
+        <v>IP68</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -9389,1465 +9714,54 @@
         <v/>
       </c>
       <c r="H188" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="I188" t="str">
         <v/>
       </c>
       <c r="J188" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="K188" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v/>
       </c>
       <c r="L188" t="str">
         <v/>
       </c>
-      <c r="M188" t="str" xml:space="preserve">
-        <v xml:space="preserve">●ZAION Vを採用　ボディ・ボディカバー・ローター素材にZAION Vを投げリールで初めて採用し、強度をキープした上で軽量化を実現。●LCスプール&amp;クロスラップ　35mmストロークでは初のLC（ロングキャスト）スプールを搭載。更にはラインを綾巻きし、ライン同士の食い込みを抑えるクロスラップを搭載し、キャスト時のトラブルが少なく軽快なライン放出を実現。※スプールテーパー角度2°●軽量ハンドルアーム　85mmアルミマシンカット軽量ハンドルアーム採用。　安定した巻き上げ感覚をもたらす高剛性マシンカットハンドル。●ハンドルノブ交換可　Sサイズノブ対応。●35mmスプール互換性あり　過去のダイワ35mmストロークリールのスプールが取付可能。　ドラグ無し同士、QD同士でのスプール互換性あり。　※ドラグ無し⇔QDとの互換性はありません。 | ZAION V
-                                                                    リールを、もっと軽く、強く。そのために開発されたカーボンハイブリッド樹脂が、ザイオン V（ブイ）。ハイブリッドするカーボン量を緻密にコントロールすることで、金属を凌駕する軽量性と金属に比肩するほどの強度をハイレベルで実現するとともに、多くのリールに搭載可能なバーサタイル性をあわせ持たせました。カーボンハイブリッド樹脂のMAXスペックともいえるザイオンのエッセンスを受け継いでいます。 | LC-ABS（ロングキャストABS)
-                                                                    ABSⅡの接触抵抗を減らす思想はそのままに、接点を前にだすことでよりスムーズなライン放出を実現。リング部が前に出た効果でリング上にラインが乗りにくくなり、従来のABSⅡ以上に約5%の距離UPとトラブルレスの向上に成功しました。LC（=LONG CAST）を実現する次世代のABSスプールです。</v>
+      <c r="M188" t="str">
+        <v/>
       </c>
       <c r="N188" t="str">
-        <v>¥36,000 - ¥38,000</v>
+        <v/>
       </c>
       <c r="O188" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="189" xml:space="preserve">
-      <c r="A189" t="str">
-        <v>DRE1018</v>
-      </c>
-      <c r="B189">
-        <v>2</v>
-      </c>
-      <c r="C189" t="str">
-        <v>エメラルダス RX</v>
-      </c>
-      <c r="D189" t="str">
-        <v/>
-      </c>
-      <c r="E189" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F189" t="str">
-        <v/>
-      </c>
-      <c r="G189" t="str">
-        <v/>
-      </c>
-      <c r="H189" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I189" t="str">
-        <v>images/daiwa_reels/エメラルダス_RX_main.jpg</v>
-      </c>
-      <c r="J189" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K189" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L189" t="str">
-        <v/>
-      </c>
-      <c r="M189" t="str" xml:space="preserve">
-        <v xml:space="preserve">イカと関わるすべての時間を、感動で満たすために。「エメラルダス」。それはDAIWAが世界に先駆けて立ち上げた、スクイッド・ゲーミングのトータルタックルブランド。その手にイカをもたらすために。そして、その最高の瞬間が訪れるまでの、イカと関わるすべての時間を、感動で満たすために。爽快なキャストフィールを。フォール、ステイ、フッキングまでの、ただ待つだけだった時間に、変化と予兆を伝え続けてくれる感度を。大物とのファイトでも安心な信頼感を。そして、トータルデザインだからこそ成せる、快適な操作感と、カメラロールで映えるフォトジェニックさを。エメラルダス。手にしたそのときから、いつでも、いつまでも感動を贈りたい。 | AIRDRIVE DESIGN採用により、操作性に磨きをかけた23EMERALDAS RXAIRDRIVE DESIGNのもたらす高次元の操作性は、「巻く」「シャクる」を繰り返すエギングにとって大きなメリットとなる。「十分な実釣性能をともなわない軽さには意味がない」というダイワのリール設計思想を元に強さへのこだわりにも、妥協は一切ない。ZAION V製MQボディにより、「強さ」も担保。リールへの負荷が大きいエギングに対しても、安心して使い込める設計になっている。滑らかで静かな回転を生み出すタフデジギアとダイワ独自の防水・耐久テクノロジーであるマグシールドを搭載。初期性能の持続により、ストレスフリーな釣りをサポート。ドラグには、ATD TYPE-Lを採用。ドラグの初動レスポンスを向上させたことで、追従性が大幅に向上した。バラシやラインブレイクを大幅に軽減し、不意の大型アオリに対しても安心して対峙できる。シーズンを通して使用できるオールラウンドモデルのノーマルLT2500番は、高剛性でトルクフルな巻き上げが可能。 FCモデルの2500番は、よりフィネスな2.5号～3.0号のエギを使用し、浅場をランガンする秋の数釣りシーズンに特化した設計。1サイズ小型のボディを採用することで、圧倒的な軽量化を達成。操作性の向上に寄与。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23EMERALDAS RXは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。</v>
-      </c>
-      <c r="N189" t="str">
-        <v>¥33,700 - ¥35,700</v>
-      </c>
-      <c r="O189" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="190" xml:space="preserve">
-      <c r="A190" t="str">
-        <v>DRE1019</v>
-      </c>
-      <c r="B190">
-        <v>2</v>
-      </c>
-      <c r="C190" t="str">
-        <v>パワーサーフQD</v>
-      </c>
-      <c r="D190" t="str">
-        <v/>
-      </c>
-      <c r="E190" t="str">
-        <v>2015</v>
-      </c>
-      <c r="F190" t="str">
-        <v/>
-      </c>
-      <c r="G190" t="str">
-        <v/>
-      </c>
-      <c r="H190" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I190" t="str">
-        <v/>
-      </c>
-      <c r="J190" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K190" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L190" t="str">
-        <v/>
-      </c>
-      <c r="M190" t="str" xml:space="preserve">
-        <v xml:space="preserve">ダイワの防水・耐久テクノロジー『マグシールド』による防水・防塵性能の向上、ローターバランスが向上し、レスポンスの良い回転フィーリングをもたらすエアローターなど基本性能を磨き上げることにこだわってダイワテクノロジーを惜しみなく搭載。ドラグのON/OFFが瞬時に可能なクイックドラグ（QD）も採用。使い込むほどにその深化を体感できる、パワフルなサーフキャスティングリールの大定番。※ハンドルノブS交換可 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
-      </c>
-      <c r="N190" t="str">
-        <v>¥33,700 - ¥35,200</v>
-      </c>
-      <c r="O190" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="191" xml:space="preserve">
-      <c r="A191" t="str">
-        <v>DRE1020</v>
-      </c>
-      <c r="B191">
-        <v>2</v>
-      </c>
-      <c r="C191" t="str">
-        <v>カルディア</v>
-      </c>
-      <c r="D191" t="str">
-        <v/>
-      </c>
-      <c r="E191" t="str">
-        <v>2025</v>
-      </c>
-      <c r="F191" t="str">
-        <v/>
-      </c>
-      <c r="G191" t="str">
-        <v/>
-      </c>
-      <c r="H191" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I191" t="str">
-        <v>images/daiwa_reels/カルディア_main.jpg</v>
-      </c>
-      <c r="J191" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K191" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L191" t="str">
-        <v/>
-      </c>
-      <c r="M191" t="str" xml:space="preserve">
-        <v xml:space="preserve">釣り人が求める、意のままにルアーを操作することを目指した設計思想エアドライブデザインが、ついにCALDIAに採用。ボディとローターというメインパーツには、ZAIONのエッセンスを受け継ぐZAION Vを採用し、軽量性と高剛性をハイレベルで実現。新たに5000番サイズを追加し、サーフフィッシングやライトショアジギング等、今まで以上に幅広い釣種をターゲットに。エアドライブデザインとモノコックボディという、ダイワの小型スピニングリールにおける2大テクノロジーを採用し、新たなステージへと昇華されたCALDIAで、ダイワの本気を体感して欲しい。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※25CALDIAでは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
-      </c>
-      <c r="N191" t="str">
-        <v>¥28,800 - ¥33,800</v>
-      </c>
-      <c r="O191" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="192" xml:space="preserve">
-      <c r="A192" t="str">
-        <v>DRE1021</v>
-      </c>
-      <c r="B192">
-        <v>2</v>
-      </c>
-      <c r="C192" t="str">
-        <v>パワーサーフ SS QD</v>
-      </c>
-      <c r="D192" t="str">
-        <v/>
-      </c>
-      <c r="E192" t="str">
-        <v>2018</v>
-      </c>
-      <c r="F192" t="str">
-        <v/>
-      </c>
-      <c r="G192" t="str">
-        <v/>
-      </c>
-      <c r="H192" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I192" t="str">
-        <v/>
-      </c>
-      <c r="J192" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K192" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L192" t="str">
-        <v/>
-      </c>
-      <c r="M192" t="str" xml:space="preserve">
-        <v xml:space="preserve">クイックドラグで楽しむ。軽量コンパクトで操作性を追求したサーフリールの決定版。25mmストロークで軽量コンパクトを実現。更に糸落ち防止機構をリニューアル。アイテムに応じたギヤー比を採用。パワフルな巻取りでリーリングをサポートするパワーTノブを搭載。瞬時に緩める/締めるが切り替えられるクイックドラグにより、サーフや堤防、磯からの大物狙いにも対応する。※ハンドルノブS交換可※ソルト対応 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
-      </c>
-      <c r="N192" t="str">
-        <v>¥32,000 - ¥33,500</v>
-      </c>
-      <c r="O192" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="193" xml:space="preserve">
-      <c r="A193" t="str">
-        <v>DRE1022</v>
-      </c>
-      <c r="B193">
-        <v>2</v>
-      </c>
-      <c r="C193" t="str">
-        <v>プロカーゴ SS 遠投</v>
-      </c>
-      <c r="D193" t="str">
-        <v/>
-      </c>
-      <c r="E193" t="str">
-        <v>2018</v>
-      </c>
-      <c r="F193" t="str">
-        <v/>
-      </c>
-      <c r="G193" t="str">
-        <v/>
-      </c>
-      <c r="H193" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I193" t="str">
-        <v/>
-      </c>
-      <c r="J193" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K193" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L193" t="str">
-        <v/>
-      </c>
-      <c r="M193" t="str" xml:space="preserve">
-        <v xml:space="preserve">人気のショートストロークカゴ遠投リールが新たな糸落ち防止機構を搭載してリニューアル。パワーTノブ搭載でマダイや小型青物とのやり取りでもパワフルな巻上げが可能。さらに「ATD」搭載で大物とのやり取りも安心。■ZAIONボディ× 25mmストロークボディにZAIONを採用し、ボディ全体の軽量化。合わせて、タックルバランスにも大きく影響するスプールを徹底軽量化。25mmストロークならではのコンパクトサーフリールで、快適な投げ釣りをサポート。■新型糸落ち防止機構搭載（従来の機構から更に進化）ライントラブルの多いショートスカートスプールに独自の糸落ち抑制機構を搭載。メインシャフトまでの侵入を抑制。糸落ち発生時、スプールへ巻きつける構造を採用。クローズベールのまま、ドラグを緩めて引き出すことが可能となり、トラブル復帰が改善された。※注意：上記方法で復帰できない場合、スプールを外してライン絡みを解除してください。■スプール互換性ダイワカゴリールにおいても優位性として挙げられる「スプール互換性」。カゴ遠投では、状況に応じてのメインライン交換が頻繁に行われるため、スプール互換性は無くてはならない機能の一つ。※新型糸落ち防止機構搭載により、互換性を一部保持した状態です。ハンドルノブS交換可。ソルト対応。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | ATD
-                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
-      </c>
-      <c r="N193" t="str">
-        <v>¥31,000 - ¥31,500</v>
-      </c>
-      <c r="O193" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="194" xml:space="preserve">
-      <c r="A194" t="str">
-        <v>DRE1023</v>
-      </c>
-      <c r="B194">
-        <v>2</v>
-      </c>
-      <c r="C194" t="str">
-        <v>月下美人</v>
-      </c>
-      <c r="D194" t="str">
-        <v/>
-      </c>
-      <c r="E194" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F194" t="str">
-        <v/>
-      </c>
-      <c r="G194" t="str">
-        <v/>
-      </c>
-      <c r="H194" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I194" t="str">
-        <v>images/daiwa_reels/月下美人_main.jpg</v>
-      </c>
-      <c r="J194" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K194" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L194" t="str">
-        <v/>
-      </c>
-      <c r="M194" t="str" xml:space="preserve">
-        <v xml:space="preserve">夜に咲く花は、輝きを増し続ける。2005年、DAIWAのラインナップに初めて登場したライトソルトゲーム専用タックル『月下美人』。艶やかに咲くその花のように月下美人は舞い、アングラーは躍動する。身近なターゲットでありながら、時には極めて繊細なアプローチを必要とするアジや、岩陰や藻の切れ目に身を隠し、周囲を警戒しながらベイトが近くに現れるのを待ち続ける老獪な大型メバルを相手に進化してきた月下美人タックル。これからも月下美人は、アングラーと共に進化し、これまでに味わったことのないような悦び、楽しみを提供する。月下美人の艶やかな輝きがライトソルトゲームを照らし続ける。 | 軽量性、高剛性を兼ね備えた、ライトソルト専用設計のスピニングリール”月下美人”軽量ルアーを操るライトソルトゲームのあらゆるシチュエーションにおいて、AIRDRIVE DESIGNのもたらす高次元の操作性は大きなメリットとなる。特に、AIRDRIVE DESIGNのキーテクノロジーである、軽量かつ低慣性なAIRDRIVE ROTORが、巻き感度の飛躍的な向上をもたらし、今まで感じ取れなかったような繊細なアタリをも確実に捉えることを可能にした。ビスがなく、球体から切り出したかのような独自の形状をしたAIRDRIVE ROTORと、最適な傾斜セッティングを施したAIRDRVE BAILがライントラブルを大幅に軽減。トラブルレス性能は、ライトライン使用時のストレスフリーな釣りをサポート。165gという軽量性を達成しながらも、モノコックボディを採用することで、高い剛性を実現。ドラグにはATD TYPE-Lを採用。ドラグの初動レスポンスを向上させたことで、追従性が大幅に向上した。極細ラインを多用するライトソルトにおいて、バラシやラインブレイクの軽減は大きなアドバンテージになる。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23月下美人は、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。</v>
-      </c>
-      <c r="N194" t="str">
-        <v>¥31,100</v>
-      </c>
-      <c r="O194" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="195" xml:space="preserve">
-      <c r="A195" t="str">
-        <v>DRE1024</v>
-      </c>
-      <c r="B195">
-        <v>2</v>
-      </c>
-      <c r="C195" t="str">
-        <v>タトゥーラ</v>
-      </c>
-      <c r="D195" t="str">
-        <v/>
-      </c>
-      <c r="E195" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F195" t="str">
-        <v/>
-      </c>
-      <c r="G195" t="str">
-        <v/>
-      </c>
-      <c r="H195" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I195" t="str">
-        <v/>
-      </c>
-      <c r="J195" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K195" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L195" t="str">
-        <v/>
-      </c>
-      <c r="M195" t="str" xml:space="preserve">
-        <v xml:space="preserve">バスフィッシングの本場アメリカで生まれ、日米の多くのバサーに愛されてきた「TATULA」ブランドが10周年を迎える。実戦で鍛え抜き、「モノコックボディ×AIRDRIVE DESIGN」により進化を遂げたTATULA。軽さと強さを両立するZAION V製のモノコックボディは、負荷が掛かった状態でもたわみや歪みを抑えて力強い巻き上げをアシスト。一方でZAION V製エアドライブローターの搭載により、低慣性化による軽い巻き出しも実現している。またドラグには、スムーズな滑り出しと安定した効きでラインへの負荷を低減するATD TYPE-Lを採用。少ないノブの回転で瞬時にテンションを調整できるクイックドラグとの相乗効果で、ライトライン使用時においても、バスとのファイトを楽しみつつスピーディにビッグフィッシュを獲ることを可能とした。パワー系の釣りも視野に入れてオールラウンドに使用できるノーマルLT2500番と、フィネス性能の向上を狙って1サイズコンパクトなボディで開発したFC（フィネスカスタム）モデルをラインナップ。このTATULAが、フィールドのタフ化が進む現代のバスフィッシングシーンをリードする。淡水専用。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23TATULAは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
-      </c>
-      <c r="N195" t="str">
-        <v>¥31,100</v>
-      </c>
-      <c r="O195" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="196" xml:space="preserve">
-      <c r="A196" t="str">
-        <v>DRE1025</v>
-      </c>
-      <c r="B196">
-        <v>2</v>
-      </c>
-      <c r="C196" t="str">
-        <v>ブラスト LT</v>
-      </c>
-      <c r="D196" t="str">
-        <v/>
-      </c>
-      <c r="E196" t="str">
-        <v>2018</v>
-      </c>
-      <c r="F196" t="str">
-        <v/>
-      </c>
-      <c r="G196" t="str">
-        <v/>
-      </c>
-      <c r="H196" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I196" t="str">
-        <v/>
-      </c>
-      <c r="J196" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K196" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L196" t="str">
-        <v/>
-      </c>
-      <c r="M196" t="str" xml:space="preserve">
-        <v xml:space="preserve">近海域でのライトジギングやキャスティングゲーム、ショアからのショアジギゲーム、スーパーライトジギングなど幅広く対応。SWシーンで活躍する高剛性LTスピニング。高強度アルミハウジングパワフルに！そして快適に。『アルミマシンカットデジギア』搭載パワーライトノブを標準装備。ショア・オフショアでの使用感にこだわったハンドルセッティング※ハンドルノブS交換可※ソルト対応 | LT-Concept
-                                                                    ダイワの軽量＆タフコンセプト。ボディ、スプール、ハンドルといった細部までの徹底した軽量化へのこだわりと、リールの心臓部となるギアとそれを包み込むボディの構造や素材の進化のバランスをトータルで高め続け生まれた、ダイワ小型スピニングの新基準「LT」。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。</v>
-      </c>
-      <c r="N196" t="str">
-        <v>¥28,000 - ¥29,000</v>
-      </c>
-      <c r="O196" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="197" xml:space="preserve">
-      <c r="A197" t="str">
-        <v>DRE1026</v>
-      </c>
-      <c r="B197">
-        <v>2</v>
-      </c>
-      <c r="C197" t="str">
-        <v>BG SW</v>
-      </c>
-      <c r="D197" t="str">
-        <v/>
-      </c>
-      <c r="E197" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F197" t="str">
-        <v/>
-      </c>
-      <c r="G197" t="str">
-        <v/>
-      </c>
-      <c r="H197" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I197" t="str">
-        <v/>
-      </c>
-      <c r="J197" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K197" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L197" t="str">
-        <v/>
-      </c>
-      <c r="M197" t="str" xml:space="preserve">
-        <v xml:space="preserve">フルメタル（AL製）ボディにねじ込みハンドル式の大口径タフデジギアを搭載しパワフルな巻き上げを実現。LC-ABS搭載で「トラブルレス」&amp;「飛距離UP」。濡れても滑りにくく力が込めやすいEVAラウンドノブを標準装備。4000サイズ～18000サイズという充実のラインナップで人気のライトショアジギング～オフショアの大物狙いまで幅広いソルトルアーゲームに対応。※ハンドルノブS 交換可（4000～6000）。※ハンドルノブL 交換可（8000～18000）。※ソルト対応。 | TOUGH DIGIGEAR
-                                                                    過酷な環境に耐え抜くにはリールを支える強靭な心臓部が必要です。滑らかな回転がより長く続く「タフデジギア」。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
-      </c>
-      <c r="N197" t="str">
-        <v>¥19,400 - ¥28,500</v>
-      </c>
-      <c r="O197" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="198" xml:space="preserve">
-      <c r="A198" t="str">
-        <v>DRE1027</v>
-      </c>
-      <c r="B198">
-        <v>2</v>
-      </c>
-      <c r="C198" t="str">
-        <v>レグザ</v>
-      </c>
-      <c r="D198" t="str">
-        <v/>
-      </c>
-      <c r="E198" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F198" t="str">
-        <v/>
-      </c>
-      <c r="G198" t="str">
-        <v/>
-      </c>
-      <c r="H198" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I198" t="str">
-        <v>images/daiwa_reels/レグザ_main.jpg</v>
-      </c>
-      <c r="J198" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K198" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L198" t="str">
-        <v/>
-      </c>
-      <c r="M198" t="str" xml:space="preserve">
-        <v xml:space="preserve">過酷なフィッシングシーンを想定し、開発されたタフリール「LEXA」リールの心臓部であるドライブギアには、タフデジギアを搭載。外殻となるボディ素材は、高強度のアルミを採用した。さらにピニオン部にマグシールドを搭載することで、LEXAの代名詞である高剛性・高耐久性を実現。新たにAIRDRIVE DESIGNを採用することで、巻き出しの軽さと重量バランスを改善し、高次元の操作性を手に入れた。ショアジギング、シーバス、SLJ、ロックフィッシュゲームなど、タフさが求められるシーンでこそ、真価を発揮する。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23LEXAは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
-      </c>
-      <c r="N198" t="str">
-        <v>¥24,400 - ¥27,400</v>
-      </c>
-      <c r="O198" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="199" xml:space="preserve">
-      <c r="A199" t="str">
-        <v>DRE1028</v>
-      </c>
-      <c r="B199">
-        <v>2</v>
-      </c>
-      <c r="C199" t="str">
-        <v>シーパラダイス</v>
-      </c>
-      <c r="D199" t="str">
-        <v/>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v/>
-      </c>
-      <c r="G199" t="str">
-        <v/>
-      </c>
-      <c r="H199" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I199" t="str">
-        <v/>
-      </c>
-      <c r="J199" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K199" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L199" t="str">
-        <v/>
-      </c>
-      <c r="M199" t="str" xml:space="preserve">
-        <v xml:space="preserve">マダイや大型青物とのやり取りに求められる堅牢さと最適な巻糸量を備えた海上釣堀専用スピニングリール。なめらかな回転を長期間維持するダイワ独自の防水・耐久テクノロジー「マグシールド」を筆頭に、剛性に優れた「スーパーメタルボディ」、安定した滑り出しの「UTD（アルティメットトーナメントドラグ）」など、ダイワだからこそ可能な先進テクノロジーを搭載。しっかり握り込めるEVA製大型ラウンドノブとの相乗効果によるトルクフルな巻き上げで、大型青物とのゴリ巻きファイトでも力負けしないタフな1台。※ハンドルノブS交換可。※ソルト対応。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
-      </c>
-      <c r="N199" t="str">
-        <v>¥25,900</v>
-      </c>
-      <c r="O199" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="200" xml:space="preserve">
-      <c r="A200" t="str">
-        <v>DRE1029</v>
-      </c>
-      <c r="B200">
-        <v>2</v>
-      </c>
-      <c r="C200" t="str">
-        <v>フリームス</v>
-      </c>
-      <c r="D200" t="str">
-        <v/>
-      </c>
-      <c r="E200" t="str">
-        <v>2026</v>
-      </c>
-      <c r="F200" t="str">
-        <v/>
-      </c>
-      <c r="G200" t="str">
-        <v/>
-      </c>
-      <c r="H200" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I200" t="str">
-        <v>images/daiwa_reels/フリームス_main.jpg</v>
-      </c>
-      <c r="J200" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K200" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L200" t="str">
-        <v/>
-      </c>
-      <c r="M200" t="str" xml:space="preserve">
-        <v xml:space="preserve">新たに「AIRDRIVE DESIGN」を採用した、グローバルスタンダードモデル。「AIRDRIVE ROTOR」と「AIRDRIVE BAIL」、2つのテクノロジーを搭載し、アングラーの思い通りの操作を実現する。リール操作時の慣性を極限まで抑えることで、巻き出しの軽さ、ルアー操作のキレ、感度の高さ――そのすべてがこれまでのスタンダードを超えていく。さらにドラグには「ATD TYPE-L」と「スプール別体ラチェット」を採用。初動レスポンスの向上と心地よいドラグサウンドが、ファイトシーンを一層快適にサポートする。そして、「MAGSEALED」をピニオン部に搭載。マグオイルを用いた機構で、水や砂塵を気にすることなく釣りの時間を愉しめる。このリールが、あなたの“夢のカタチ”を描き出す。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※26FREAMSでは、ZAION V製AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
-      </c>
-      <c r="N200" t="str">
-        <v>¥18,700 - ¥25,100</v>
-      </c>
-      <c r="O200" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="201" xml:space="preserve">
-      <c r="A201" t="str">
-        <v>DRE1030</v>
-      </c>
-      <c r="B201">
-        <v>2</v>
-      </c>
-      <c r="C201" t="str">
-        <v>ウインドキャスト</v>
-      </c>
-      <c r="D201" t="str">
-        <v/>
-      </c>
-      <c r="E201" t="str">
-        <v>2017</v>
-      </c>
-      <c r="F201" t="str">
-        <v/>
-      </c>
-      <c r="G201" t="str">
-        <v/>
-      </c>
-      <c r="H201" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I201" t="str">
-        <v/>
-      </c>
-      <c r="J201" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K201" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L201" t="str">
-        <v/>
-      </c>
-      <c r="M201" t="str" xml:space="preserve">
-        <v xml:space="preserve">タフさが求められる磯遠投リールにおいてメリットの大きいダイワの防水･耐久テクノロジー「マグシールド」を搭載。エアローターにより、快適な回転性能を手に入れ、遠投時の巻き取り効率も向上。スプールには遠投性能に定評のある35mmストロークアルミスプールを採用。パワーと遠投性能の両立により、カゴ･磯投げで狙える幅広いターゲットに対応。エアベール、クロスラップ、糸落ち防止機能を搭載し、ライントラブルに対しても強化。ハンドルは遠投の際の巻取りのしやすさを考慮した85mm仕様。4000QD、6000QDは置き竿の釣りで不意の大物が期待できる時などに便利なクイックドラグ搭載モデル。ドラグノブを約1回転するだけで緩める・締めるが可能なドラグ機能で、掛かるまではドラグを緩め、掛かった後は迅速にドラグを締めることができるのでやり取りまでにもたつかない。6000QDは大型タマン（ハマフエフキ）にも対応可能。※ソルト対応。※ハンドルノブS交換可。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
-      </c>
-      <c r="N201" t="str">
-        <v>¥21,300 - ¥24,300</v>
-      </c>
-      <c r="O201" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="202" xml:space="preserve">
-      <c r="A202" t="str">
-        <v>DRE1031</v>
-      </c>
-      <c r="B202">
-        <v>2</v>
-      </c>
-      <c r="C202" t="str">
-        <v>イプリミ</v>
-      </c>
-      <c r="D202" t="str">
-        <v/>
-      </c>
-      <c r="E202" t="str">
-        <v>2025</v>
-      </c>
-      <c r="F202" t="str">
-        <v/>
-      </c>
-      <c r="G202" t="str">
-        <v/>
-      </c>
-      <c r="H202" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I202" t="str">
-        <v>images/daiwa_reels/イプリミ_main.jpg</v>
-      </c>
-      <c r="J202" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K202" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L202" t="str">
-        <v/>
-      </c>
-      <c r="M202" t="str" xml:space="preserve">
-        <v xml:space="preserve">AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※25IPRIMIは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
-                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
-      </c>
-      <c r="N202" t="str">
-        <v>¥23,300</v>
-      </c>
-      <c r="O202" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="203" xml:space="preserve">
-      <c r="A203" t="str">
-        <v>DRE1032</v>
-      </c>
-      <c r="B203">
-        <v>2</v>
-      </c>
-      <c r="C203" t="str">
-        <v>エメラルダス X</v>
-      </c>
-      <c r="D203" t="str">
-        <v/>
-      </c>
-      <c r="E203" t="str">
-        <v>2024</v>
-      </c>
-      <c r="F203" t="str">
-        <v/>
-      </c>
-      <c r="G203" t="str">
-        <v/>
-      </c>
-      <c r="H203" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I203" t="str">
-        <v>images/daiwa_reels/エメラルダス_X_main.jpg</v>
-      </c>
-      <c r="J203" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K203" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L203" t="str">
-        <v/>
-      </c>
-      <c r="M203" t="str" xml:space="preserve">
-        <v xml:space="preserve">イカと関わるすべての時間を、感動で満たすために。「エメラルダス」。それはDAIWAが世界に先駆けて立ち上げた、スクイッド・ゲーミングのトータルタックルブランド。その手にイカをもたらすために。そして、その最高の瞬間が訪れるまでの、イカと関わるすべての時間を、感動で満たすために。爽快なキャストフィールを。フォール、ステイ、フッキングまでの、ただ待つだけだった時間に、変化と予兆を伝え続けてくれる感度を。大物とのファイトでも安心な信頼感を。そして、トータルデザインだからこそ成せる、快適な操作感と、カメラロールで映えるフォトジェニックさを。エメラルダス。手にしたそのときから、いつでも、いつまでも感動を贈りたい。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24EMERALDAS Xは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
-      </c>
-      <c r="N203" t="str">
-        <v>¥20,700 - ¥22,000</v>
-      </c>
-      <c r="O203" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="204" xml:space="preserve">
-      <c r="A204" t="str">
-        <v>DRE1033</v>
-      </c>
-      <c r="B204">
-        <v>2</v>
-      </c>
-      <c r="C204" t="str">
-        <v>ウインドサーフ 35</v>
-      </c>
-      <c r="D204" t="str">
-        <v/>
-      </c>
-      <c r="E204" t="str">
-        <v>2017</v>
-      </c>
-      <c r="F204" t="str">
-        <v/>
-      </c>
-      <c r="G204" t="str">
-        <v/>
-      </c>
-      <c r="H204" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I204" t="str">
-        <v/>
-      </c>
-      <c r="J204" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K204" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L204" t="str">
-        <v/>
-      </c>
-      <c r="M204" t="str" xml:space="preserve">
-        <v xml:space="preserve">ダイワ独自の防水･耐久テクノロジー「マグシールド」を搭載し、初期性能の維持を追求。初期の滑らかな回転性能が持続することは、雨や波しぶき、風に運ばれる塵や砂など厳しい環境下に置かれる投げリールにとって大きなアドバンテージとなる。軽快な回転性能を支えるエアローターと中空構造のエアベールは、中・近距離での釣りにはもちろん遠投時に投げリールに求められる重要なファクターであるスムーズな巻き感の向上につながる。回転初動が軽いため、止める・動かすに瞬時に対応可能。そして単純な飛距離だけでは成り立たないのが投げリール。トラブルは大敵であり、「35mmストローク」と「クロスラップ」の相乗効果で糸を問わずライントラブルを最少限に抑えることに成功。またハンドルは、ゴミなどが引っ掛かると相当の負荷が掛かることもある投げ釣りにおいて最も使いやすい長さを考慮した85mmロングハンドルを搭載。ノブもTノブを採用し、上位機種に肉薄する充実のスペックに仕上がっている。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
-      </c>
-      <c r="N204" t="str">
-        <v>¥21,500</v>
-      </c>
-      <c r="O204" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="205" xml:space="preserve">
-      <c r="A205" t="str">
-        <v>DRE1034</v>
-      </c>
-      <c r="B205">
-        <v>2</v>
-      </c>
-      <c r="C205" t="str">
-        <v>アオリマチックBR LT</v>
-      </c>
-      <c r="D205" t="str">
-        <v/>
-      </c>
-      <c r="E205" t="str">
-        <v>2026</v>
-      </c>
-      <c r="F205" t="str">
-        <v/>
-      </c>
-      <c r="G205" t="str">
-        <v/>
-      </c>
-      <c r="H205" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I205" t="str">
-        <v>images/daiwa_reels/アオリマチックBR_LT_main.jpg</v>
-      </c>
-      <c r="J205" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K205" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L205" t="str">
-        <v/>
-      </c>
-      <c r="M205" t="str" xml:space="preserve">
-        <v xml:space="preserve">AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
-                                                                    ワイヤータイプのAIRDRIVE BAILを採用。ローターユニットのさらなる軽量化を実現するために実釣時における必要強度を維持したまま、大幅軽量化を実現。ベールを含むローターユニットの軽量化により、回転慣性の大幅低減に寄与。回転レスポンスに磨きをかけ、操作性を向上させました。アームレバー部も新形状を採用し、糸絡みを大幅軽減しました。 | ATD TYPE-L
-                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。その初動レスポンスを高めたATD TYPE-L。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
-      </c>
-      <c r="N205" t="str">
-        <v>¥19,400</v>
-      </c>
-      <c r="O205" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="206" xml:space="preserve">
-      <c r="A206" t="str">
-        <v>DRE1035</v>
-      </c>
-      <c r="B206">
-        <v>2</v>
-      </c>
-      <c r="C206" t="str">
-        <v>月下美人 X</v>
-      </c>
-      <c r="D206" t="str">
-        <v/>
-      </c>
-      <c r="E206" t="str">
-        <v>2024</v>
-      </c>
-      <c r="F206" t="str">
-        <v/>
-      </c>
-      <c r="G206" t="str">
-        <v/>
-      </c>
-      <c r="H206" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I206" t="str">
-        <v>images/daiwa_reels/月下美人_X_main.jpg</v>
-      </c>
-      <c r="J206" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K206" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L206" t="str">
-        <v/>
-      </c>
-      <c r="M206" t="str" xml:space="preserve">
-        <v xml:space="preserve">夜に咲く花は、輝きを増し続ける。2005年、DAIWAのラインナップに初めて登場したライトソルトゲーム専用タックル『月下美人』。艶やかに咲くその花のように月下美人は舞い、アングラーは躍動する。身近なターゲットでありながら、時には極めて繊細なアプローチを必要とするアジや、岩陰や藻の切れ目に身を隠し、周囲を警戒しながらベイトが近くに現れるのを待ち続ける老獪な大型メバルを相手に進化してきた月下美人タックル。これからも月下美人は、アングラーと共に進化し、これまでに味わったことのないような悦び、楽しみを提供する。月下美人の艶やかな輝きがライトソルトゲームを照らし続ける。 | 繊細な操作を求められるライトソルトゲーム。24月下美人Xは、巻き感度、操作性、トラブルレス性能を大幅に向上させたライトソルトゲーム専用設計。意のままにルアーを操作することを追求した、次世代スピニングリールの設計思想であるAIRDRIVE DESIGNを採用。軽量ルアーを操作するライトソルトゲームにとって、操作性の向上は魚をキャッチするための大きなメリットとなる。AIRDRIVE DESIGNの基幹テクノロジーであり、巻き出しの軽さと巻き感度に大きく寄与するローターには、ZAION V製のAIRDRIVE ROTORを採用。軽量で低慣性なローターは巻き感度向上に大きく寄与し、繊細なアジのアタリや水流の変化など、水中の情報を感じ取る。また、細糸を多用するライトソルトゲームでは、ライントラブルは大きなストレスとなる。ビスがなく、球体から切り出したかのような形状であるAIRDRIVE ROTOR、そして新形状アームレバーとAIRDRIVE BAILの相乗効果によってトラブルレス性能を向上させ、ストレスから解放する。ドラグには、初動レスポンスを向上させたATD TYPE-Lを採用。ライトライン使用時のラインブレイクを減少させることで、安心したファイトを可能にする。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24月下美人Xは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。</v>
-      </c>
-      <c r="N206" t="str">
-        <v>¥18,700</v>
-      </c>
-      <c r="O206" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="207" xml:space="preserve">
-      <c r="A207" t="str">
-        <v>DRE1036</v>
-      </c>
-      <c r="B207">
-        <v>2</v>
-      </c>
-      <c r="C207" t="str">
-        <v>レガリス</v>
-      </c>
-      <c r="D207" t="str">
-        <v/>
-      </c>
-      <c r="E207" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F207" t="str">
-        <v/>
-      </c>
-      <c r="G207" t="str">
-        <v/>
-      </c>
-      <c r="H207" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I207" t="str">
-        <v>images/daiwa_reels/レガリス_main.jpg</v>
-      </c>
-      <c r="J207" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K207" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L207" t="str">
-        <v/>
-      </c>
-      <c r="M207" t="str" xml:space="preserve">
-        <v xml:space="preserve">ベストセラースピニングリール「LEGALIS」がフルモデルチェンジ！AIRDRIVE DESIGN ＆ ZAION Vで大幅な進化。新たにボディ&amp;ローターにZAION Vを採用し、剛性と軽量性が大幅UP（LT2500S-XHで、前モデル比▲20g軽量化）ZAION V製AIRDRIVE ROTORでより軽快な「巻く」「止める」操作が可能。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23LEGALISは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
-      </c>
-      <c r="N207" t="str">
-        <v>¥12,600 - ¥16,100</v>
-      </c>
-      <c r="O207" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="208" xml:space="preserve">
-      <c r="A208" t="str">
-        <v>DRE1037</v>
-      </c>
-      <c r="B208">
-        <v>2</v>
-      </c>
-      <c r="C208" t="str">
-        <v>クロスキャスト</v>
-      </c>
-      <c r="D208" t="str">
-        <v/>
-      </c>
-      <c r="E208" t="str">
-        <v>2017</v>
-      </c>
-      <c r="F208" t="str">
-        <v/>
-      </c>
-      <c r="G208" t="str">
-        <v/>
-      </c>
-      <c r="H208" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I208" t="str">
-        <v/>
-      </c>
-      <c r="J208" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K208" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L208" t="str">
-        <v/>
-      </c>
-      <c r="M208" t="str" xml:space="preserve">
-        <v xml:space="preserve">35mmストローク仕様により、カゴ･磯遠投で重要な「飛距離」にこだわったエントリーモデル。エアローター採用により回転性能、遠投の際の巻き取り効率が向上。ライントラブルを軽減するクロスラップはもちろん、大物にも対応する耐久性に優れた「デジギヤⅡ」搭載と、妥協なしのスペック。4000QDは置き竿の釣りで不意の大物が期待できる時などに便利なクイックドラグ搭載モデル。ドラグノブを約1回転するだけで緩める・締めるが可能なドラグ機能で、掛かるまではドラグを緩め、掛かった後は迅速にドラグを締めることができるのでやり取りまでにもたつかない。※ソルト対応 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。 | QUICK  DRAG
-                                                                    瞬時の「クイック」な調整が可能なドラグ。少ないドラグノブの回転で、即座に設定を大きく変えることができる。使用ラインやタックル、釣法に応じて様々に活用可能です。
-                                                                        ※4000QDのみ</v>
-      </c>
-      <c r="N208" t="str">
-        <v>¥12,000 - ¥13,300</v>
-      </c>
-      <c r="O208" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="209" xml:space="preserve">
-      <c r="A209" t="str">
-        <v>DRE1038</v>
-      </c>
-      <c r="B209">
-        <v>2</v>
-      </c>
-      <c r="C209" t="str">
-        <v>レブロス</v>
-      </c>
-      <c r="D209" t="str">
-        <v/>
-      </c>
-      <c r="E209" t="str">
-        <v>2024</v>
-      </c>
-      <c r="F209" t="str">
-        <v/>
-      </c>
-      <c r="G209" t="str">
-        <v/>
-      </c>
-      <c r="H209" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I209" t="str">
-        <v>images/daiwa_reels/レブロス_main.jpg</v>
-      </c>
-      <c r="J209" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K209" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L209" t="str">
-        <v/>
-      </c>
-      <c r="M209" t="str" xml:space="preserve">
-        <v xml:space="preserve">新型AIRDRIVE ROTOR+AIRDRIVE BAIL（ワイヤー）+アームレバーによりローターユニットの軽量化を実現し、全体の軽量化に貢献。（2500S-XHで210ｇ　20レブロスLT2500S-H比▲10ｇの軽量化）また、AIRDRIVE ROTORでリール操作の基本である「巻く」「止める」の操作がより軽快になった。※カスタムパーツに関しては、SLPウェブサイト上の製品対応検索システムをご参照ください。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24REVROSは、エアドライブローター、エアドライブベールを搭載。 | AIRDRIVE BAIL
-                                                                    ワイヤータイプのAIRDRIVE BAILを採用。ローターユニットのさらなる軽量化を実現するために実釣時における必要強度を維持したまま、大幅軽量化を実現。ベールを含むローターユニットの軽量化により、回転慣性の大幅低減に寄与。回転レスポンスに磨きをかけ、操作性を向上させました。アームレバー部も新形状を採用し、糸絡みを大幅軽減しました。</v>
-      </c>
-      <c r="N209" t="str">
-        <v>¥10,000 - ¥12,800</v>
-      </c>
-      <c r="O209" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="210" xml:space="preserve">
-      <c r="A210" t="str">
-        <v>DRE1039</v>
-      </c>
-      <c r="B210">
-        <v>2</v>
-      </c>
-      <c r="C210" t="str">
-        <v>ファインサーフ35</v>
-      </c>
-      <c r="D210" t="str">
-        <v/>
-      </c>
-      <c r="E210" t="str">
-        <v>2017</v>
-      </c>
-      <c r="F210" t="str">
-        <v/>
-      </c>
-      <c r="G210" t="str">
-        <v/>
-      </c>
-      <c r="H210" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I210" t="str">
-        <v/>
-      </c>
-      <c r="J210" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K210" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L210" t="str">
-        <v/>
-      </c>
-      <c r="M210" t="str" xml:space="preserve">
-        <v xml:space="preserve">35mmストロークで、投げ釣りの醍醐味である「飛び」にこだわったエントリーモデル。快適に最大の飛距離を出すため、ダイワテクノロジーを惜しみなく投入。中・近距離での釣りにはもちろん、遠投時の巻き感は投げリールに求められる重要なファクター。軽快な回転性能を支えるエアローターは回転初動が軽く、止める・動かすに瞬時に対応。また投げリールの大敵であるライントラブルを最小限に抑えるため「クロスラップ」「ツイストバスターII」を採用。上位機種に肉薄するパフォーマンスで、投げ釣りを始めたい方にも最適な1台。※ソルト対応※ハンドルノブ交換不可 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。</v>
-      </c>
-      <c r="N210" t="str">
-        <v>¥12,000</v>
-      </c>
-      <c r="O210" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="211" xml:space="preserve">
-      <c r="A211" t="str">
-        <v>DRE1040</v>
-      </c>
-      <c r="B211">
-        <v>2</v>
-      </c>
-      <c r="C211" t="str">
-        <v>アオリトライアル BR</v>
-      </c>
-      <c r="D211" t="str">
-        <v/>
-      </c>
-      <c r="E211" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F211" t="str">
-        <v/>
-      </c>
-      <c r="G211" t="str">
-        <v/>
-      </c>
-      <c r="H211" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I211" t="str">
-        <v/>
-      </c>
-      <c r="J211" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K211" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L211" t="str">
-        <v/>
-      </c>
-      <c r="M211" t="str" xml:space="preserve">
-        <v xml:space="preserve">マニュアルリターン仕様アオリクラッチ搭載アオリクラッチを従来のオートリターン仕様からマニュアルリターン仕様に変更。ハンドル回転時の意図しないクラッチ戻りを防ぎ、より使い易くなった。※アオリクラッチ　アオリイカに違和感なくアジを抱かせることが必要なヤエン釣法に不可欠な機構でフロントとリアのドラグ切り替えを行うためのクラッチのこと。（このリールはフロントとリアに2種類の独立したドラグを備えたリールです。）スプールフリー調整ダイヤルダイヤルは細かいクリック設定で微調整が可能。ATDアオリイカの引きに合わせスムーズに作動し、滑らかに効き続けるドラグ。LC-ABSスプールの軽量化とスプールリップの形状の見直しにより、快適なライン放出性を実現。※BR＝BITE&amp;RUN※ハンドルノブS 交換可。※ソルト対応。 | ATD
-                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。 | LC-ABS（ロングキャストABS)
-                                                                    ABSⅡの接触抵抗を減らす思想はそのままに、接点を前にだすことでよりスムーズなライン放出を実現。リング部が前に出た効果でリング上にラインが乗りにくくなり、従来のABSⅡ以上に約5%の距離UPとトラブルレスの向上に成功しました。LC（=LONG CAST）を実現する次世代のABSスプールです。</v>
-      </c>
-      <c r="N211" t="str">
-        <v>¥10,300</v>
-      </c>
-      <c r="O211" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="212" xml:space="preserve">
-      <c r="A212" t="str">
-        <v>DRE1041</v>
-      </c>
-      <c r="B212">
-        <v>2</v>
-      </c>
-      <c r="C212" t="str">
-        <v>クレスト</v>
-      </c>
-      <c r="D212" t="str">
-        <v/>
-      </c>
-      <c r="E212" t="str">
-        <v>2020</v>
-      </c>
-      <c r="F212" t="str">
-        <v/>
-      </c>
-      <c r="G212" t="str">
-        <v/>
-      </c>
-      <c r="H212" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I212" t="str">
-        <v/>
-      </c>
-      <c r="J212" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K212" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L212" t="str">
-        <v/>
-      </c>
-      <c r="M212" t="str" xml:space="preserve">
-        <v xml:space="preserve">LTコンセプトにより大幅軽量化を実現！（前モデル2500番比で、なんとマイナス40ｇの軽量化！）ATD採用によりドラグ性能UP！LC-ABSにより飛距離UP！小型スピニングリール新基準「LT」仕様。LTコンセプトによりこの価格帯で、235ｇ（2500番）を達成！タフデジギア、ATD、LC(ロングキャスト）ABSスプール搭載。ソルト対応。 | LT-Concept
-                                                                    ダイワの軽量＆タフコンセプト。ボディ、スプール、ハンドルといった細部までの徹底した軽量化へのこだわりと、リールの心臓部となるギアとそれを包み込むボディの構造や素材の進化のバランスをトータルで高め続け生まれた、ダイワ小型スピニングの新基準「LT」。 | ATD
-                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
-      </c>
-      <c r="N212" t="str">
-        <v>¥6,400 - ¥8,300</v>
-      </c>
-      <c r="O212" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>DRE1042</v>
-      </c>
-      <c r="B213">
-        <v>2</v>
-      </c>
-      <c r="C213" t="str">
-        <v>MR</v>
-      </c>
-      <c r="D213" t="str">
-        <v/>
-      </c>
-      <c r="E213" t="str">
-        <v>2019</v>
-      </c>
-      <c r="F213" t="str">
-        <v/>
-      </c>
-      <c r="G213" t="str">
-        <v/>
-      </c>
-      <c r="H213" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I213" t="str">
-        <v/>
-      </c>
-      <c r="J213" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K213" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L213" t="str">
-        <v/>
-      </c>
-      <c r="M213" t="str">
-        <v>お手軽に釣りを楽しめる 軽量＆コンパクトリール。入門機として充実のスペックを搭載。165g 軽量（MR750）でコンパクトリール。コンパクトで握り易いIシェイプノブ、45㎜マシンカットハンドル搭載。※ソルト対応 | 4ボールベアリング+インフィニットストッパー付。最大ドラグ力3kgと充実の基本性能。 | 安定した巻上げ感をもたらす45mmマシンカットハンドル。折りたたみ式なので持ち運びにも便利。</v>
-      </c>
-      <c r="N213" t="str">
-        <v>¥7,000 - ¥7,500</v>
-      </c>
-      <c r="O213" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="214" xml:space="preserve">
-      <c r="A214" t="str">
-        <v>DRE1043</v>
-      </c>
-      <c r="B214">
-        <v>2</v>
-      </c>
-      <c r="C214" t="str">
-        <v>ジョイナス</v>
-      </c>
-      <c r="D214" t="str">
-        <v/>
-      </c>
-      <c r="E214" t="str">
-        <v>2016</v>
-      </c>
-      <c r="F214" t="str">
-        <v/>
-      </c>
-      <c r="G214" t="str">
-        <v/>
-      </c>
-      <c r="H214" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I214" t="str">
-        <v/>
-      </c>
-      <c r="J214" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K214" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L214" t="str">
-        <v/>
-      </c>
-      <c r="M214" t="str" xml:space="preserve">
-        <v xml:space="preserve">新型ボディにより、前作に比べて回転フィーリングが大幅に向上。ギヤには耐久性で定評のあるデジギヤIIを搭載。糸絡みトラブルを激減させて快適な飛距離をもたらすABS II、ツイストバスターIIなど機能も充実。ナイロンラインがスプールに巻いてあるため買ってすぐに釣り場で使える万能スピニングリール。淡水・海水どちらのフィールドでも使用可能。またこのクラスでは新提案となる4500、5000の大型サイズもラインナップ。※ソルト対応。 | ABSⅡ
-                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。 | TWIST BUSTER Ⅱ
-                                                                    ラインローラーにテーパーをかけて、ラインをころがすことにより、ローター回転で発生する糸ヨレを相殺。スピニングリールの宿命といわれた糸ヨレを大幅に解消します。</v>
-      </c>
-      <c r="N214" t="str">
-        <v/>
-      </c>
-      <c r="O214" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="215" xml:space="preserve">
-      <c r="A215" t="str">
-        <v>DRE1044</v>
-      </c>
-      <c r="B215">
-        <v>2</v>
-      </c>
-      <c r="C215" t="str">
-        <v>リーガル PE付</v>
-      </c>
-      <c r="D215" t="str">
-        <v/>
-      </c>
-      <c r="E215" t="str">
-        <v>2016</v>
-      </c>
-      <c r="F215" t="str">
-        <v/>
-      </c>
-      <c r="G215" t="str">
-        <v/>
-      </c>
-      <c r="H215" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I215" t="str">
-        <v/>
-      </c>
-      <c r="J215" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K215" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L215" t="str">
-        <v/>
-      </c>
-      <c r="M215" t="str" xml:space="preserve">
-        <v xml:space="preserve">軽さと剛性の高さを両立した新型ボディにインフィニットストッパーを搭載することで、巻心地はしっかり＆滑らか。PEラインがはじめからスプールに巻いてあるため、買ってすぐに釣り場で使える点もメリット。高剛性のデジギヤII、ライントラブルを激減させて快適な飛びをもたらすABS II、クロスラップ、ツイストバスターIIなどのダイワテクノロジーを豊富に搭載した充実の仕様。ブラックですっきりまとめられたデザインは様々なロッドに違和感なくマッチする。もちろん淡水・海水どちらのフィールドでも使用可能。 | ABSⅡ
-                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。</v>
-      </c>
-      <c r="N215" t="str">
-        <v/>
-      </c>
-      <c r="O215" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="216" xml:space="preserve">
-      <c r="A216" t="str">
-        <v>DRE1045</v>
-      </c>
-      <c r="B216">
-        <v>2</v>
-      </c>
-      <c r="C216" t="str">
-        <v>タマンモンスター</v>
-      </c>
-      <c r="D216" t="str">
-        <v/>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v/>
-      </c>
-      <c r="G216" t="str">
-        <v/>
-      </c>
-      <c r="H216" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I216" t="str">
-        <v/>
-      </c>
-      <c r="J216" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K216" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L216" t="str">
-        <v/>
-      </c>
-      <c r="M216" t="str" xml:space="preserve">
-        <v xml:space="preserve">大型遠投リールとして実績の高い「ウィンドキャスト6000」をベースに、大型タマン（ハマフエフキ）とのガチンコ勝負にも負けないタフな仕様にブラッシュアップ。ロングストローク35mm正テーパーアルミスプールが確かな遠投性能をもたらし、デジギヤII、85mmロングハンドル＆パワーノブなどで力強い巻き上げが可能。パワーと遠投性能をバランスよく兼備した、タマン専用リールの決定版。 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。 | AIRBAIL
-                                                                    ラインがラインローラーまで流れるように送り出される凹凸のない滑らかなベール形状により、糸ガラミトラブルを大幅に減少します。さらにベール自体を中空構造にしたことで、重量を変えずに大幅な強度アップを実現しました。</v>
-      </c>
-      <c r="N216" t="str">
-        <v/>
-      </c>
-      <c r="O216" t="str">
-        <v>在售</v>
-      </c>
-    </row>
-    <row r="217" xml:space="preserve">
-      <c r="A217" t="str">
-        <v>DRE1046</v>
-      </c>
-      <c r="B217">
-        <v>2</v>
-      </c>
-      <c r="C217" t="str">
-        <v>ワールドスピン</v>
-      </c>
-      <c r="D217" t="str">
-        <v/>
-      </c>
-      <c r="E217" t="str">
-        <v>2017</v>
-      </c>
-      <c r="F217" t="str">
-        <v/>
-      </c>
-      <c r="G217" t="str">
-        <v/>
-      </c>
-      <c r="H217" t="str">
-        <v>spinning</v>
-      </c>
-      <c r="I217" t="str">
-        <v/>
-      </c>
-      <c r="J217" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="K217" t="str">
-        <v>2026-04-09 00:35:43</v>
-      </c>
-      <c r="L217" t="str">
-        <v/>
-      </c>
-      <c r="M217" t="str" xml:space="preserve">
-        <v xml:space="preserve">高剛性でスムーズな巻上げ感をもたらすデジギヤII、ライントラブルを減少させるABS II・クロスラップ・ツイストバスターII、ガタつきのない快適な巻き上げが可能なインフィニットストッパーなど、快適な実釣性能をもたらすダイワテクノロジーをしっかり搭載。折りたたみ式アルミハンドルで持ち運びもしやすい。さらにソルト対応のため、淡水はもちろん海のエサ釣りからルアーゲームまで幅広く対応。買ってすぐに釣り場で使える便利な糸付き（CFは糸なし）。※ソルト対応 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。 | ABSⅡ
-                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。</v>
-      </c>
-      <c r="N217" t="str">
-        <v/>
-      </c>
-      <c r="O217" t="str">
-        <v>在售</v>
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+      <c r="R188" t="str">
+        <v>freshwater</v>
+      </c>
+      <c r="S188" t="str">
+        <v/>
+      </c>
+      <c r="T188" t="str">
+        <v>https://www.megabass.co.jp/site/products/ip68/</v>
+      </c>
+      <c r="U188" t="str">
+        <v>https://www.megabass.co.jp/site/wp-content/uploads/2014/06/main_001_IP68.jpg</v>
+      </c>
+      <c r="V188" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O217"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -397,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V188"/>
+  <dimension ref="A1:O188"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,27 +448,6 @@
       </c>
       <c r="O1" t="str">
         <v>market_status</v>
-      </c>
-      <c r="P1" t="str">
-        <v>series</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>series_cn</v>
-      </c>
-      <c r="R1" t="str">
-        <v>water_type</v>
-      </c>
-      <c r="S1" t="str">
-        <v>description</v>
-      </c>
-      <c r="T1" t="str">
-        <v>source_url</v>
-      </c>
-      <c r="U1" t="str">
-        <v>main_image_url</v>
-      </c>
-      <c r="V1" t="str">
-        <v>local_image_path</v>
       </c>
     </row>
     <row r="2">
@@ -8561,13 +8544,13 @@
         <v>spinning</v>
       </c>
       <c r="I171" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_20X-2.jpg</v>
       </c>
       <c r="J171" t="str">
-        <v/>
+        <v>2026-04-09T16:03:04.387Z</v>
       </c>
       <c r="K171" t="str">
-        <v/>
+        <v>2026-04-09T16:03:04.387Z</v>
       </c>
       <c r="L171" t="str">
         <v/>
@@ -8579,27 +8562,6 @@
         <v/>
       </c>
       <c r="O171" t="str">
-        <v/>
-      </c>
-      <c r="P171" t="str">
-        <v/>
-      </c>
-      <c r="Q171" t="str">
-        <v/>
-      </c>
-      <c r="R171" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S171" t="str">
-        <v/>
-      </c>
-      <c r="T171" t="str">
-        <v>https://www.megabass.co.jp/site/products/gaus-20x/</v>
-      </c>
-      <c r="U171" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_GAUS_20X-2.jpg</v>
-      </c>
-      <c r="V171" t="str">
         <v/>
       </c>
     </row>
@@ -8629,13 +8591,13 @@
         <v>spinning</v>
       </c>
       <c r="I172" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_30X-1.jpg</v>
       </c>
       <c r="J172" t="str">
-        <v/>
+        <v>2026-04-09T16:03:04.751Z</v>
       </c>
       <c r="K172" t="str">
-        <v/>
+        <v>2026-04-09T16:03:04.751Z</v>
       </c>
       <c r="L172" t="str">
         <v/>
@@ -8647,27 +8609,6 @@
         <v/>
       </c>
       <c r="O172" t="str">
-        <v/>
-      </c>
-      <c r="P172" t="str">
-        <v/>
-      </c>
-      <c r="Q172" t="str">
-        <v/>
-      </c>
-      <c r="R172" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S172" t="str">
-        <v/>
-      </c>
-      <c r="T172" t="str">
-        <v>https://www.megabass.co.jp/site/products/gaus-30x/</v>
-      </c>
-      <c r="U172" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_GAUS_30X-1.jpg</v>
-      </c>
-      <c r="V172" t="str">
         <v/>
       </c>
     </row>
@@ -8697,13 +8638,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I173" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LIN258HM.jpg</v>
       </c>
       <c r="J173" t="str">
-        <v/>
+        <v>2026-04-09T16:03:05.113Z</v>
       </c>
       <c r="K173" t="str">
-        <v/>
+        <v>2026-04-09T16:03:05.113Z</v>
       </c>
       <c r="L173" t="str">
         <v/>
@@ -8715,27 +8656,6 @@
         <v/>
       </c>
       <c r="O173" t="str">
-        <v/>
-      </c>
-      <c r="P173" t="str">
-        <v/>
-      </c>
-      <c r="Q173" t="str">
-        <v/>
-      </c>
-      <c r="R173" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S173" t="str">
-        <v/>
-      </c>
-      <c r="T173" t="str">
-        <v>https://www.megabass.co.jp/site/products/lin258hm/</v>
-      </c>
-      <c r="U173" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_LIN258HM.jpg</v>
-      </c>
-      <c r="V173" t="str">
         <v/>
       </c>
     </row>
@@ -8765,13 +8685,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I174" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_idaten-x_256.jpg</v>
       </c>
       <c r="J174" t="str">
-        <v/>
+        <v>2026-04-09T16:03:05.419Z</v>
       </c>
       <c r="K174" t="str">
-        <v/>
+        <v>2026-04-09T16:03:05.419Z</v>
       </c>
       <c r="L174" t="str">
         <v/>
@@ -8783,27 +8703,6 @@
         <v/>
       </c>
       <c r="O174" t="str">
-        <v/>
-      </c>
-      <c r="P174" t="str">
-        <v/>
-      </c>
-      <c r="Q174" t="str">
-        <v/>
-      </c>
-      <c r="R174" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S174" t="str">
-        <v/>
-      </c>
-      <c r="T174" t="str">
-        <v>https://www.megabass.co.jp/site/products/rc-idaten256/</v>
-      </c>
-      <c r="U174" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2014/06/main_001_megabass_idaten-x_256.jpg</v>
-      </c>
-      <c r="V174" t="str">
         <v/>
       </c>
     </row>
@@ -8833,13 +8732,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I175" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
       </c>
       <c r="J175" t="str">
-        <v/>
+        <v>2026-04-09T16:03:05.733Z</v>
       </c>
       <c r="K175" t="str">
-        <v/>
+        <v>2026-04-09T16:03:05.733Z</v>
       </c>
       <c r="L175" t="str">
         <v/>
@@ -8851,27 +8750,6 @@
         <v/>
       </c>
       <c r="O175" t="str">
-        <v/>
-      </c>
-      <c r="P175" t="str">
-        <v/>
-      </c>
-      <c r="Q175" t="str">
-        <v/>
-      </c>
-      <c r="R175" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S175" t="str">
-        <v/>
-      </c>
-      <c r="T175" t="str">
-        <v>https://www.megabass.co.jp/site/products/monoblock_sp_grigio_stone/</v>
-      </c>
-      <c r="U175" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2016/12/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
-      </c>
-      <c r="V175" t="str">
         <v/>
       </c>
     </row>
@@ -8901,13 +8779,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I176" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
       </c>
       <c r="J176" t="str">
-        <v/>
+        <v>2026-04-09T16:03:06.104Z</v>
       </c>
       <c r="K176" t="str">
-        <v/>
+        <v>2026-04-09T16:03:06.104Z</v>
       </c>
       <c r="L176" t="str">
         <v/>
@@ -8919,27 +8797,6 @@
         <v/>
       </c>
       <c r="O176" t="str">
-        <v/>
-      </c>
-      <c r="P176" t="str">
-        <v/>
-      </c>
-      <c r="Q176" t="str">
-        <v/>
-      </c>
-      <c r="R176" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S176" t="str">
-        <v/>
-      </c>
-      <c r="T176" t="str">
-        <v>https://www.megabass.co.jp/site/products/monoblock_ito-gambler/</v>
-      </c>
-      <c r="U176" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
-      </c>
-      <c r="V176" t="str">
         <v/>
       </c>
     </row>
@@ -8969,13 +8826,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I177" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE.jpg</v>
       </c>
       <c r="J177" t="str">
-        <v/>
+        <v>2026-04-09T16:03:06.704Z</v>
       </c>
       <c r="K177" t="str">
-        <v/>
+        <v>2026-04-09T16:03:06.704Z</v>
       </c>
       <c r="L177" t="str">
         <v/>
@@ -8987,27 +8844,6 @@
         <v/>
       </c>
       <c r="O177" t="str">
-        <v/>
-      </c>
-      <c r="P177" t="str">
-        <v/>
-      </c>
-      <c r="Q177" t="str">
-        <v/>
-      </c>
-      <c r="R177" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S177" t="str">
-        <v/>
-      </c>
-      <c r="T177" t="str">
-        <v>https://www.megabass.co.jp/site/products/monoblock-speciale/</v>
-      </c>
-      <c r="U177" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2015/04/main_001_MONOBLOCK_SPECIALE.jpg</v>
-      </c>
-      <c r="V177" t="str">
         <v/>
       </c>
     </row>
@@ -9037,13 +8873,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I178" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_rhodium_73.jpg</v>
       </c>
       <c r="J178" t="str">
-        <v/>
+        <v>2026-04-09T16:03:07.101Z</v>
       </c>
       <c r="K178" t="str">
-        <v/>
+        <v>2026-04-09T16:03:07.101Z</v>
       </c>
       <c r="L178" t="str">
         <v/>
@@ -9055,27 +8891,6 @@
         <v/>
       </c>
       <c r="O178" t="str">
-        <v/>
-      </c>
-      <c r="P178" t="str">
-        <v/>
-      </c>
-      <c r="Q178" t="str">
-        <v/>
-      </c>
-      <c r="R178" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S178" t="str">
-        <v/>
-      </c>
-      <c r="T178" t="str">
-        <v>https://www.megabass.co.jp/site/products/rhodium73/</v>
-      </c>
-      <c r="U178" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_megabass_rhodium_73.jpg</v>
-      </c>
-      <c r="V178" t="str">
         <v/>
       </c>
     </row>
@@ -9105,13 +8920,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I179" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_81.jpg</v>
       </c>
       <c r="J179" t="str">
-        <v/>
+        <v>2026-04-09T16:03:07.457Z</v>
       </c>
       <c r="K179" t="str">
-        <v/>
+        <v>2026-04-09T16:03:07.457Z</v>
       </c>
       <c r="L179" t="str">
         <v/>
@@ -9123,27 +8938,6 @@
         <v/>
       </c>
       <c r="O179" t="str">
-        <v/>
-      </c>
-      <c r="P179" t="str">
-        <v/>
-      </c>
-      <c r="Q179" t="str">
-        <v/>
-      </c>
-      <c r="R179" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S179" t="str">
-        <v/>
-      </c>
-      <c r="T179" t="str">
-        <v>https://www.megabass.co.jp/site/products/rhodium81/</v>
-      </c>
-      <c r="U179" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2018/04/main_001_RHODIUM_81.jpg</v>
-      </c>
-      <c r="V179" t="str">
         <v/>
       </c>
     </row>
@@ -9173,13 +8967,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I180" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_63.jpg</v>
       </c>
       <c r="J180" t="str">
-        <v/>
+        <v>2026-04-09T16:03:07.869Z</v>
       </c>
       <c r="K180" t="str">
-        <v/>
+        <v>2026-04-09T16:03:07.869Z</v>
       </c>
       <c r="L180" t="str">
         <v/>
@@ -9191,27 +8985,6 @@
         <v/>
       </c>
       <c r="O180" t="str">
-        <v/>
-      </c>
-      <c r="P180" t="str">
-        <v/>
-      </c>
-      <c r="Q180" t="str">
-        <v/>
-      </c>
-      <c r="R180" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S180" t="str">
-        <v/>
-      </c>
-      <c r="T180" t="str">
-        <v>https://www.megabass.co.jp/site/products/rhodium63/</v>
-      </c>
-      <c r="U180" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2018/04/main_001_RHODIUM_63.jpg</v>
-      </c>
-      <c r="V180" t="str">
         <v/>
       </c>
     </row>
@@ -9241,13 +9014,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I181" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_R100-1.jpg</v>
       </c>
       <c r="J181" t="str">
-        <v/>
+        <v>2026-04-09T16:03:08.227Z</v>
       </c>
       <c r="K181" t="str">
-        <v/>
+        <v>2026-04-09T16:03:08.227Z</v>
       </c>
       <c r="L181" t="str">
         <v/>
@@ -9259,27 +9032,6 @@
         <v/>
       </c>
       <c r="O181" t="str">
-        <v/>
-      </c>
-      <c r="P181" t="str">
-        <v/>
-      </c>
-      <c r="Q181" t="str">
-        <v/>
-      </c>
-      <c r="R181" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S181" t="str">
-        <v/>
-      </c>
-      <c r="T181" t="str">
-        <v>https://www.megabass.co.jp/site/products/pagani-r100/</v>
-      </c>
-      <c r="U181" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_R100-1.jpg</v>
-      </c>
-      <c r="V181" t="str">
         <v/>
       </c>
     </row>
@@ -9309,13 +9061,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I182" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P200_black-chrome.jpg</v>
       </c>
       <c r="J182" t="str">
-        <v/>
+        <v>2026-04-09T16:03:08.638Z</v>
       </c>
       <c r="K182" t="str">
-        <v/>
+        <v>2026-04-09T16:03:08.638Z</v>
       </c>
       <c r="L182" t="str">
         <v/>
@@ -9327,27 +9079,6 @@
         <v/>
       </c>
       <c r="O182" t="str">
-        <v/>
-      </c>
-      <c r="P182" t="str">
-        <v/>
-      </c>
-      <c r="Q182" t="str">
-        <v/>
-      </c>
-      <c r="R182" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S182" t="str">
-        <v/>
-      </c>
-      <c r="T182" t="str">
-        <v>https://www.megabass.co.jp/site/products/pagani-p200/</v>
-      </c>
-      <c r="U182" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_P200_black-chrome.jpg</v>
-      </c>
-      <c r="V182" t="str">
         <v/>
       </c>
     </row>
@@ -9377,13 +9108,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I183" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
       </c>
       <c r="J183" t="str">
-        <v/>
+        <v>2026-04-09T16:03:09.002Z</v>
       </c>
       <c r="K183" t="str">
-        <v/>
+        <v>2026-04-09T16:03:09.002Z</v>
       </c>
       <c r="L183" t="str">
         <v/>
@@ -9395,27 +9126,6 @@
         <v/>
       </c>
       <c r="O183" t="str">
-        <v/>
-      </c>
-      <c r="P183" t="str">
-        <v/>
-      </c>
-      <c r="Q183" t="str">
-        <v/>
-      </c>
-      <c r="R183" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S183" t="str">
-        <v/>
-      </c>
-      <c r="T183" t="str">
-        <v>https://www.megabass.co.jp/site/products/pagani-p300/</v>
-      </c>
-      <c r="U183" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/07/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
-      </c>
-      <c r="V183" t="str">
         <v/>
       </c>
     </row>
@@ -9445,13 +9155,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I184" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_58.jpg</v>
       </c>
       <c r="J184" t="str">
-        <v/>
+        <v>2026-04-09T16:03:09.406Z</v>
       </c>
       <c r="K184" t="str">
-        <v/>
+        <v>2026-04-09T16:03:09.406Z</v>
       </c>
       <c r="L184" t="str">
         <v/>
@@ -9463,27 +9173,6 @@
         <v/>
       </c>
       <c r="O184" t="str">
-        <v/>
-      </c>
-      <c r="P184" t="str">
-        <v/>
-      </c>
-      <c r="Q184" t="str">
-        <v/>
-      </c>
-      <c r="R184" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S184" t="str">
-        <v/>
-      </c>
-      <c r="T184" t="str">
-        <v>https://www.megabass.co.jp/site/products/lauda58/</v>
-      </c>
-      <c r="U184" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_LAUDA_58.jpg</v>
-      </c>
-      <c r="V184" t="str">
         <v/>
       </c>
     </row>
@@ -9513,13 +9202,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I185" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72.jpg</v>
       </c>
       <c r="J185" t="str">
-        <v/>
+        <v>2026-04-09T16:03:09.802Z</v>
       </c>
       <c r="K185" t="str">
-        <v/>
+        <v>2026-04-09T16:03:09.802Z</v>
       </c>
       <c r="L185" t="str">
         <v/>
@@ -9531,27 +9220,6 @@
         <v/>
       </c>
       <c r="O185" t="str">
-        <v/>
-      </c>
-      <c r="P185" t="str">
-        <v/>
-      </c>
-      <c r="Q185" t="str">
-        <v/>
-      </c>
-      <c r="R185" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S185" t="str">
-        <v/>
-      </c>
-      <c r="T185" t="str">
-        <v>https://www.megabass.co.jp/site/products/lauda72/</v>
-      </c>
-      <c r="U185" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2016/12/main_001_LAUDA_72.jpg</v>
-      </c>
-      <c r="V185" t="str">
         <v/>
       </c>
     </row>
@@ -9581,13 +9249,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I186" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
       </c>
       <c r="J186" t="str">
-        <v/>
+        <v>2026-04-09T16:03:10.384Z</v>
       </c>
       <c r="K186" t="str">
-        <v/>
+        <v>2026-04-09T16:03:10.384Z</v>
       </c>
       <c r="L186" t="str">
         <v/>
@@ -9599,27 +9267,6 @@
         <v/>
       </c>
       <c r="O186" t="str">
-        <v/>
-      </c>
-      <c r="P186" t="str">
-        <v/>
-      </c>
-      <c r="Q186" t="str">
-        <v/>
-      </c>
-      <c r="R186" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S186" t="str">
-        <v/>
-      </c>
-      <c r="T186" t="str">
-        <v>https://www.megabass.co.jp/site/products/lauda72ltd/</v>
-      </c>
-      <c r="U186" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2017/02/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
-      </c>
-      <c r="V186" t="str">
         <v/>
       </c>
     </row>
@@ -9649,13 +9296,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I187" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP79.jpg</v>
       </c>
       <c r="J187" t="str">
-        <v/>
+        <v>2026-04-09T16:03:10.796Z</v>
       </c>
       <c r="K187" t="str">
-        <v/>
+        <v>2026-04-09T16:03:10.796Z</v>
       </c>
       <c r="L187" t="str">
         <v/>
@@ -9667,27 +9314,6 @@
         <v/>
       </c>
       <c r="O187" t="str">
-        <v/>
-      </c>
-      <c r="P187" t="str">
-        <v/>
-      </c>
-      <c r="Q187" t="str">
-        <v/>
-      </c>
-      <c r="R187" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S187" t="str">
-        <v/>
-      </c>
-      <c r="T187" t="str">
-        <v>https://www.megabass.co.jp/site/products/ip79/</v>
-      </c>
-      <c r="U187" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2013/08/main_001_IP79.jpg</v>
-      </c>
-      <c r="V187" t="str">
         <v/>
       </c>
     </row>
@@ -9717,13 +9343,13 @@
         <v>baitcasting</v>
       </c>
       <c r="I188" t="str">
-        <v/>
+        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP68.jpg</v>
       </c>
       <c r="J188" t="str">
-        <v/>
+        <v>2026-04-09T16:03:11.194Z</v>
       </c>
       <c r="K188" t="str">
-        <v/>
+        <v>2026-04-09T16:03:11.194Z</v>
       </c>
       <c r="L188" t="str">
         <v/>
@@ -9735,33 +9361,12 @@
         <v/>
       </c>
       <c r="O188" t="str">
-        <v/>
-      </c>
-      <c r="P188" t="str">
-        <v/>
-      </c>
-      <c r="Q188" t="str">
-        <v/>
-      </c>
-      <c r="R188" t="str">
-        <v>freshwater</v>
-      </c>
-      <c r="S188" t="str">
-        <v/>
-      </c>
-      <c r="T188" t="str">
-        <v>https://www.megabass.co.jp/site/products/ip68/</v>
-      </c>
-      <c r="U188" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2014/06/main_001_IP68.jpg</v>
-      </c>
-      <c r="V188" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -479,10 +479,10 @@
         <v>images/shimano_reels/STELLA SW_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -526,10 +526,10 @@
         <v>images/shimano_reels/BB-X TECHNIUM FIRE BLOOD_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>images/shimano_reels/BB-X TECHNIUM_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -620,10 +620,10 @@
         <v>images/shimano_reels/KISU SPECIAL 45_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -667,10 +667,10 @@
         <v>images/shimano_reels/AERO TECHNIUM MGS XTD_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -714,10 +714,10 @@
         <v>images/shimano_reels/AERO TECHNIUM MGS XSD_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -761,10 +761,10 @@
         <v>images/shimano_reels/STELLA_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -808,10 +808,10 @@
         <v>images/shimano_reels/EXSENCE_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -855,10 +855,10 @@
         <v>images/shimano_reels/TWINPOWER SW_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -902,10 +902,10 @@
         <v>images/shimano_reels/POWER AERO XTC_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -949,10 +949,10 @@
         <v>images/shimano_reels/POWER AERO XSC_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -996,10 +996,10 @@
         <v>images/shimano_reels/BB-X HYPER FORCE TYPE2_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1043,10 +1043,10 @@
         <v>images/shimano_reels/FLIEGEN_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1090,10 +1090,10 @@
         <v>images/shimano_reels/Vanquish CE_main.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1137,10 +1137,10 @@
         <v>images/shimano_reels/Vanquish_main.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1184,10 +1184,10 @@
         <v>images/shimano_reels/SARAGOSA SW_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1231,10 +1231,10 @@
         <v>images/shimano_reels/BB-X HYPER FORCE_main.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1278,10 +1278,10 @@
         <v>images/shimano_reels/BB-X Remare_main.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1325,10 +1325,10 @@
         <v>images/shimano_reels/TWINPOWER_main.jpg</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1372,10 +1372,10 @@
         <v>images/shimano_reels/TWINPOWER XD_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1419,10 +1419,10 @@
         <v>images/shimano_reels/HYPER FORCE LB_main.jpg</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1466,10 +1466,10 @@
         <v>images/shimano_reels/POWER AERO TD_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1513,10 +1513,10 @@
         <v>images/shimano_reels/ULTEGRA XR BIG PIT XTD_main.jpg</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1560,10 +1560,10 @@
         <v>images/shimano_reels/ULTEGRA XR BIG PIT XSD_main.jpg</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1607,10 +1607,10 @@
         <v>images/shimano_reels/BB-X HYPER FORCE 1700_C2000_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1654,10 +1654,10 @@
         <v>images/shimano_reels/BB-X Rinkai SP_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1701,10 +1701,10 @@
         <v>images/shimano_reels/EXSENCE XR_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1748,10 +1748,10 @@
         <v>images/shimano_reels/STRADIC SW_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1795,10 +1795,10 @@
         <v>images/shimano_reels/Sephia XR_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1842,10 +1842,10 @@
         <v>images/shimano_reels/SUSTAIN_main.jpg</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1889,10 +1889,10 @@
         <v>images/shimano_reels/Soare XR_main.jpg</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1936,10 +1936,10 @@
         <v>images/shimano_reels/CARDIFF XR_main.jpg</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1983,10 +1983,10 @@
         <v>images/shimano_reels/BB-X DESPINA_main.jpg</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -2030,10 +2030,10 @@
         <v>images/shimano_reels/BULL‘S EYE_main.jpg</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -2077,10 +2077,10 @@
         <v>images/shimano_reels/COMPLEX XR_main.jpg</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2124,10 +2124,10 @@
         <v>images/shimano_reels/BAITRUNNER CI4+ XTB_main.jpg</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2171,10 +2171,10 @@
         <v>images/shimano_reels/SURF LEADER_main.png</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2218,10 +2218,10 @@
         <v>images/shimano_reels/Sephia SS_main.jpg</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2265,10 +2265,10 @@
         <v>images/shimano_reels/VANFORD_main.jpg</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2312,10 +2312,10 @@
         <v>images/shimano_reels/ULTEGRA XS_main.jpg</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2359,10 +2359,10 @@
         <v>images/shimano_reels/ULTEGRA XT_main.jpg</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2406,10 +2406,10 @@
         <v>images/shimano_reels/BB-X LARISSA_main.jpg</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2453,10 +2453,10 @@
         <v>images/shimano_reels/SPHEROS SW_main.jpg</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2500,10 +2500,10 @@
         <v>images/shimano_reels/SPEEDMASTER XTD_main.jpg</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2547,10 +2547,10 @@
         <v>images/shimano_reels/STRADIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2594,10 +2594,10 @@
         <v>images/shimano_reels/SUPER AERO SpinJoy_main.jpg</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2641,10 +2641,10 @@
         <v>images/shimano_reels/SPEEDMASTER XSD_main.jpg</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2688,10 +2688,10 @@
         <v>images/shimano_reels/Sephia BB_main.jpg</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2735,10 +2735,10 @@
         <v>images/shimano_reels/EXSENCE BB_main.jpg</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2782,10 +2782,10 @@
         <v>images/shimano_reels/AERO XR_main.jpg</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2829,10 +2829,10 @@
         <v>images/shimano_reels/ULTEGRA_main.jpg</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2876,10 +2876,10 @@
         <v>images/shimano_reels/Soare BB_main.jpg</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2923,10 +2923,10 @@
         <v>images/shimano_reels/AERLEX XTC_main.jpg</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2970,10 +2970,10 @@
         <v>images/shimano_reels/AERLEX XSC_main.jpg</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -3017,10 +3017,10 @@
         <v>images/shimano_reels/AERO_main.jpg</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -3064,10 +3064,10 @@
         <v>images/shimano_reels/MIRAVEL_main.jpg</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -3111,10 +3111,10 @@
         <v>images/shimano_reels/NASCI_main.jpg</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -3158,10 +3158,10 @@
         <v>images/shimano_reels/SOCORRO SW_main.jpg</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3205,10 +3205,10 @@
         <v>images/shimano_reels/AERO BB_main.jpg</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3252,10 +3252,10 @@
         <v>images/shimano_reels/SAHARA_main.jpg</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3299,10 +3299,10 @@
         <v>images/shimano_reels/ACTIVECAST_main.jpg</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3346,10 +3346,10 @@
         <v>images/shimano_reels/SEDONA_main.jpg</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3393,10 +3393,10 @@
         <v>images/shimano_reels/ALIVIO_main.jpg</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3440,10 +3440,10 @@
         <v>images/shimano_reels/NEXAVE_main.jpg</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3487,10 +3487,10 @@
         <v>images/shimano_reels/CATANA_main.jpg</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3534,10 +3534,10 @@
         <v>images/shimano_reels/SIENNA_main.jpg</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3581,10 +3581,10 @@
         <v>images/shimano_reels/FX_main.jpg</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3628,10 +3628,10 @@
         <v>images/shimano_reels/TIAGRA_main.jpg</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3675,10 +3675,10 @@
         <v>images/shimano_reels/TALICA_main.jpg</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>images/shimano_reels/EXSENCE DC_main.jpg</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3769,10 +3769,10 @@
         <v>images/shimano_reels/ANTARES DC_main.jpg</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3816,10 +3816,10 @@
         <v>images/shimano_reels/ANTARES DC MD_main.png</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3863,10 +3863,10 @@
         <v>images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpg</v>
       </c>
       <c r="J74" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K74" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -3910,10 +3910,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST DC_main.jpg</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K75" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -3957,10 +3957,10 @@
         <v>images/shimano_reels/OCEA JIGGER LD_main.jpg</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K76" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -4004,10 +4004,10 @@
         <v>images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpg</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K77" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -4051,10 +4051,10 @@
         <v>images/shimano_reels/OCEA CONQUEST CT_main.jpg</v>
       </c>
       <c r="J78" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K78" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -4098,10 +4098,10 @@
         <v>images/shimano_reels/KAIKON_main.jpg</v>
       </c>
       <c r="J79" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K79" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -4145,10 +4145,10 @@
         <v>images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="J80" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K80" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -4192,10 +4192,10 @@
         <v>images/shimano_reels/OCEA JIGGER_main.jpg</v>
       </c>
       <c r="J81" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K81" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -4239,10 +4239,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST MD_main.jpg</v>
       </c>
       <c r="J82" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K82" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -4286,10 +4286,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpg</v>
       </c>
       <c r="J83" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K83" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -4333,10 +4333,10 @@
         <v>images/shimano_reels/Metanium DC_main.jpg</v>
       </c>
       <c r="J84" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K84" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -4380,10 +4380,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST_main.jpg</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K85" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -4427,10 +4427,10 @@
         <v>images/shimano_reels/OCEA CONQUEST_main.jpg</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K86" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -4474,10 +4474,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K87" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -4521,10 +4521,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpg</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K88" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -4568,10 +4568,10 @@
         <v>images/shimano_reels/OCEA CONQUEST FT_main.jpg</v>
       </c>
       <c r="J89" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K89" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -4615,10 +4615,10 @@
         <v>images/shimano_reels/ALDEBARAN DC_main.jpg</v>
       </c>
       <c r="J90" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K90" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -4662,10 +4662,10 @@
         <v>images/shimano_reels/STILE_main.jpg</v>
       </c>
       <c r="J91" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K91" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -4709,10 +4709,10 @@
         <v>images/shimano_reels/BARCHETTA PREMIUM_main.jpg</v>
       </c>
       <c r="J92" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K92" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -4756,10 +4756,10 @@
         <v>images/shimano_reels/GRAPPLER PREMIUM_main.jpg</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K93" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -4803,10 +4803,10 @@
         <v>images/shimano_reels/ALDEBARAN BFS_main.jpg</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K94" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -4850,10 +4850,10 @@
         <v>images/shimano_reels/ALDEBARAN MGL_main.jpg</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K95" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -4897,10 +4897,10 @@
         <v>images/shimano_reels/Metanium SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K96" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -4944,10 +4944,10 @@
         <v>images/shimano_reels/Metanium_main.jpg</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K97" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -4991,10 +4991,10 @@
         <v>images/shimano_reels/SPEEDMASTER 石鲷_main.jpg</v>
       </c>
       <c r="J98" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K98" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L98" t="str">
         <v/>
@@ -5038,10 +5038,10 @@
         <v>images/shimano_reels/TYRNOS_main.jpg</v>
       </c>
       <c r="J99" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K99" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L99" t="str">
         <v/>
@@ -5085,10 +5085,10 @@
         <v>images/shimano_reels/EXSENCE DC SS_main.jpg</v>
       </c>
       <c r="J100" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K100" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L100" t="str">
         <v/>
@@ -5132,10 +5132,10 @@
         <v>images/shimano_reels/TRANX 400_main.jpg</v>
       </c>
       <c r="J101" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K101" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L101" t="str">
         <v/>
@@ -5179,10 +5179,10 @@
         <v>images/shimano_reels/Bantam_main.jpg</v>
       </c>
       <c r="J102" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K102" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L102" t="str">
         <v/>
@@ -5226,10 +5226,10 @@
         <v>images/shimano_reels/TRANX 300_main.jpg</v>
       </c>
       <c r="J103" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K103" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -5273,10 +5273,10 @@
         <v>images/shimano_reels/BAYGAME_main.jpg</v>
       </c>
       <c r="J104" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K104" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L104" t="str">
         <v/>
@@ -5320,10 +5320,10 @@
         <v>images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J105" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K105" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L105" t="str">
         <v/>
@@ -5367,10 +5367,10 @@
         <v>images/shimano_reels/BARCHETTA F CUSTOM_main.jpg</v>
       </c>
       <c r="J106" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K106" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L106" t="str">
         <v/>
@@ -5414,10 +5414,10 @@
         <v>images/shimano_reels/Scorpion DC MD_main.jpg</v>
       </c>
       <c r="J107" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K107" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -5461,10 +5461,10 @@
         <v>images/shimano_reels/SLX DC XT_main.jpg</v>
       </c>
       <c r="J108" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K108" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L108" t="str">
         <v/>
@@ -5508,10 +5508,10 @@
         <v>images/shimano_reels/Scorpion DC_main.jpg</v>
       </c>
       <c r="J109" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K109" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L109" t="str">
         <v/>
@@ -5555,10 +5555,10 @@
         <v>images/shimano_reels/Scorpion MD 300_main.jpg</v>
       </c>
       <c r="J110" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K110" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L110" t="str">
         <v/>
@@ -5602,10 +5602,10 @@
         <v>images/shimano_reels/GRAPPLER CT_main.jpg</v>
       </c>
       <c r="J111" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K111" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -5649,10 +5649,10 @@
         <v>images/shimano_reels/CURADO DC_main.jpg</v>
       </c>
       <c r="J112" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K112" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L112" t="str">
         <v/>
@@ -5696,10 +5696,10 @@
         <v>images/shimano_reels/CHINUMATIC_main.jpg</v>
       </c>
       <c r="J113" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K113" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L113" t="str">
         <v/>
@@ -5743,10 +5743,10 @@
         <v>images/shimano_reels/Stephano SS_main.jpg</v>
       </c>
       <c r="J114" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K114" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L114" t="str">
         <v/>
@@ -5790,10 +5790,10 @@
         <v>images/shimano_reels/STILE SS_main.jpg</v>
       </c>
       <c r="J115" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K115" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L115" t="str">
         <v/>
@@ -5837,10 +5837,10 @@
         <v>images/shimano_reels/Scorpion MD 200_main.jpg</v>
       </c>
       <c r="J116" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K116" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L116" t="str">
         <v/>
@@ -5884,10 +5884,10 @@
         <v>images/shimano_reels/TORIUM_main.jpg</v>
       </c>
       <c r="J117" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K117" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L117" t="str">
         <v/>
@@ -5931,10 +5931,10 @@
         <v>images/shimano_reels/TRANX 200_main.jpg</v>
       </c>
       <c r="J118" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K118" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L118" t="str">
         <v/>
@@ -5978,10 +5978,10 @@
         <v>images/shimano_reels/TRANX_main.jpg</v>
       </c>
       <c r="J119" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K119" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L119" t="str">
         <v/>
@@ -6025,10 +6025,10 @@
         <v>images/shimano_reels/BARCHETTA_main.jpg</v>
       </c>
       <c r="J120" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K120" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L120" t="str">
         <v/>
@@ -6072,10 +6072,10 @@
         <v>images/shimano_reels/BARCHETTA SC_main.jpg</v>
       </c>
       <c r="J121" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K121" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L121" t="str">
         <v/>
@@ -6119,10 +6119,10 @@
         <v>images/shimano_reels/SLX DC_main.jpg</v>
       </c>
       <c r="J122" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K122" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L122" t="str">
         <v/>
@@ -6166,10 +6166,10 @@
         <v>images/shimano_reels/CURADO_main.jpg</v>
       </c>
       <c r="J123" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K123" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L123" t="str">
         <v/>
@@ -6213,10 +6213,10 @@
         <v>images/shimano_reels/CURADO 150_main.jpg</v>
       </c>
       <c r="J124" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K124" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L124" t="str">
         <v/>
@@ -6260,10 +6260,10 @@
         <v>images/shimano_reels/CURADO MGL_main.jpg</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L125" t="str">
         <v/>
@@ -6307,10 +6307,10 @@
         <v>images/shimano_reels/CURADO BFS_main.jpg</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L126" t="str">
         <v/>
@@ -6354,10 +6354,10 @@
         <v>images/shimano_reels/SLX_main.jpg</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L127" t="str">
         <v/>
@@ -6401,10 +6401,10 @@
         <v>images/shimano_reels/BARCHETTA BB_main.jpg</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L128" t="str">
         <v/>
@@ -6448,10 +6448,10 @@
         <v>images/shimano_reels/SLX BFS_main.jpg</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L129" t="str">
         <v/>
@@ -6495,10 +6495,10 @@
         <v>images/shimano_reels/GRAPPLER BB_main.jpg</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L130" t="str">
         <v/>
@@ -6542,10 +6542,10 @@
         <v>images/shimano_reels/SLX XT_main.jpg</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L131" t="str">
         <v/>
@@ -6589,10 +6589,10 @@
         <v>images/shimano_reels/小船_main.jpg</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L132" t="str">
         <v/>
@@ -6636,10 +6636,10 @@
         <v>images/shimano_reels/CARDIFF_main.jpg</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L133" t="str">
         <v/>
@@ -6683,10 +6683,10 @@
         <v>images/shimano_reels/幻风 XT_main.jpg</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L134" t="str">
         <v/>
@@ -6730,10 +6730,10 @@
         <v>images/shimano_reels/TITANOS FUNE GT_main.jpg</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L135" t="str">
         <v/>
@@ -6777,10 +6777,10 @@
         <v>images/shimano_reels/BASS ONE XT_main.jpg</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L136" t="str">
         <v/>
@@ -6824,10 +6824,10 @@
         <v>images/shimano_reels/CAIUS_main.jpg</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L137" t="str">
         <v/>
@@ -6871,10 +6871,10 @@
         <v>images/shimano_reels/BASS RISE_main.jpg</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L138" t="str">
         <v/>
@@ -6918,10 +6918,10 @@
         <v>images/shimano_reels/幻风_main.jpg</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L139" t="str">
         <v/>
@@ -6965,10 +6965,10 @@
         <v>images/shimano_reels/CHINU SPECIAL_main.jpg</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L140" t="str">
         <v/>
@@ -8544,7 +8544,7 @@
         <v>spinning</v>
       </c>
       <c r="I171" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_20X-2.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 20X_main.jpg</v>
       </c>
       <c r="J171" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
@@ -8591,7 +8591,7 @@
         <v>spinning</v>
       </c>
       <c r="I172" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_GAUS_30X-1.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 30X_main.jpg</v>
       </c>
       <c r="J172" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
@@ -8638,7 +8638,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I173" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LIN258HM.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LIN258HM_main.jpg</v>
       </c>
       <c r="J173" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
@@ -8685,7 +8685,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I174" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_idaten-x_256.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RC-IDATEN 256_main.jpg</v>
       </c>
       <c r="J174" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
@@ -8732,7 +8732,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I175" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE GRIGIO STONE_main.jpg</v>
       </c>
       <c r="J175" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
@@ -8779,7 +8779,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I176" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE ITO-GAMBLER_main.jpg</v>
       </c>
       <c r="J176" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
@@ -8826,7 +8826,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I177" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_MONOBLOCK_SPECIALE.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE_main.jpg</v>
       </c>
       <c r="J177" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
@@ -8873,7 +8873,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I178" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_megabass_rhodium_73.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 73_main.jpg</v>
       </c>
       <c r="J178" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
@@ -8920,7 +8920,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I179" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_81.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 81_main.jpg</v>
       </c>
       <c r="J179" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
@@ -8967,7 +8967,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I180" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_RHODIUM_63.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 63_main.jpg</v>
       </c>
       <c r="J180" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
@@ -9014,7 +9014,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I181" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_R100-1.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani R100_main.jpg</v>
       </c>
       <c r="J181" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
@@ -9061,7 +9061,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I182" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P200_black-chrome.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P200_main.jpg</v>
       </c>
       <c r="J182" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
@@ -9108,7 +9108,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I183" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P300_main.jpg</v>
       </c>
       <c r="J183" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
@@ -9155,7 +9155,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I184" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_58.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA58_main.jpg</v>
       </c>
       <c r="J184" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
@@ -9202,7 +9202,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I185" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72_main.jpg</v>
       </c>
       <c r="J185" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
@@ -9249,7 +9249,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I186" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72 LIMITED EDITION_main.jpg</v>
       </c>
       <c r="J186" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
@@ -9296,7 +9296,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I187" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP79.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/IP79_main.jpg</v>
       </c>
       <c r="J187" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
@@ -9343,7 +9343,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I188" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/main_001_IP68.jpg</v>
+        <v>/Users/tommy/Pictures/images/megabass_reels/IP68_main.jpg</v>
       </c>
       <c r="J188" t="str">
         <v>2026-04-09T16:03:11.194Z</v>

--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:O235"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6985,144 +6985,2471 @@
     </row>
     <row r="141" xml:space="preserve">
       <c r="A141" t="str">
-        <v>DRE5000</v>
+        <v>DRE1000</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141" t="str">
+        <v>ソルティガ</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141" t="str">
+        <v>2025</v>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I141" t="str">
+        <v>images/daiwa_reels/ソルティガ_main.jpg</v>
+      </c>
+      <c r="J141" t="str">
+        <v>2026-04-05T14:36:58.671126Z</v>
+      </c>
+      <c r="K141" t="str">
+        <v>2026-04-05T14:36:58.671126Z</v>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str" xml:space="preserve">
+        <v xml:space="preserve">BREAK YOUR RECORD　-夢を掴み獲れ-「いつか、あの魚を。」アングラーの夢を叶えるために誕生したもの、「SALTIGA」。DAIWAオフショア最強の遺伝子を受け継ぎ、最新のテクノロジーで進化し続ける。前提は、未知の大物との対峙。タックルとしての限界に挑み続け、あらゆる箇所の強度、使いやすく優位になる性能を追求する。ソルティガが課せられているのは、確実に夢の魚へと近づくタックルであるということ。その存在意義をかなえ続けることは、すなわちアングラーの夢がかなうこと。その信頼の性能は、世界中のアングラーの夢をサポートする。 | MONOCOQUE BODY
+                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。
+                                                                        フルメタル（AL製)モノコックボディを採用。高剛性且つ軽量コンパクトハウジングに最大径のタフデジギアを封入する。 | POWERDRIVE DESIGN
+                                                                    パワードライブデザインは、世界中の大型魚と安心して渡り合える高い信頼性を追求した次世代大型スピニングリールの設計思想。このパワードライブデザインは、高効率で力強い巻き上げ力を実現するボディユニット[パワードライブエンジン]と、合理的な球体形状で高剛性と低イナーシャの両立を実現したローターユニット[パワードライブローター]の２つのテクノロジーユニットからなる。ボディユニットの[パワードライブエンジン]は、[オーバーサイズドパワーデジギア]と[ローラーパワーオシレーション]の２つのテクノロジーによって構成される。[オーバーサイズドパワーデジギア]は大口径化・肉厚化と、最適化された歯面形状により、ギアの駆動効率を大幅にアップ。[ローラーパワーオシレーション]はオシレート機構にベアリング方式を採用することで、摩擦抵抗を大幅に低減し、初動レスポンスの向上と、軽い巻き上げを実現した。一方、フロントユニットは、[クランクパワーベール]と[タフラインローラーシステム]の２つのテクノロジーを搭載した[パワードライブローター]によって構成される。[クランクパワーベール]は、ベールの開閉力を強化するとともに、クランク形状を採用することで、ラインローラーへの確実な糸送りを実現。[タフラインローラーシステム]は、ラインローラーの支持構造や形状を見直すことで、耐久性やトラブルレス性を向上させた。これらのテクノロジーの相乗効果により、大型魚をターゲットとしたキャスティングゲームやジギングゲームにおいて、剛性・パワー・耐久性を高次元で実現する。獲るための“強さ”を、ビッグゲームを愛する、すべてのアングラーに。
+                                                                        ※25SALTIGAではPOWERDRIVE DESIGNのオーバーサイズドパワーデジギア、ローラーパワーオシレーション、クランクパワーベール、タフラインローラーシステムをフル搭載。</v>
+      </c>
+      <c r="N141" t="str">
+        <v>¥155,000 - ¥200,000</v>
+      </c>
+      <c r="O141" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="142" xml:space="preserve">
+      <c r="A142" t="str">
+        <v>DRE1001</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
+      </c>
+      <c r="C142" t="str">
+        <v>ソルティガ</v>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+      <c r="E142" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I142" t="str">
+        <v>images/daiwa_reels/ソルティガ_4000_5000_6000_main.jpg</v>
+      </c>
+      <c r="J142" t="str">
+        <v>2026-04-05T14:37:04.963194Z</v>
+      </c>
+      <c r="K142" t="str">
+        <v>2026-04-05T14:37:04.963194Z</v>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str" xml:space="preserve">
+        <v xml:space="preserve">BREAK YOUR RECORD　-夢を掴み獲れ-「いつか、あの魚を。」アングラーの夢を叶えるために誕生したもの、「SALTIGA」。DAIWAオフショア最強の遺伝子を受け継ぎ、最新のテクノロジーで進化し続ける。前提は、未知の大物との対峙。タックルとしての限界に挑み続け、あらゆる箇所の強度、使いやすく優位になる性能を追求する。ソルティガが課せられているのは、確実に夢の魚へと近づくタックルであるということ。その存在意義をかなえ続けることは、すなわちアングラーの夢がかなうこと。その信頼の性能は、世界中のアングラーの夢をサポートする。 | “MQ” meets “AIRDRIVE DESIGN”一本の魚の価値が高い“激戦区”(人的プレッシャーが高いフィールド)における「最大魚クラスのトロフィー」そして「自己記録」を獲る為の”圧倒的パワー・タフさ”と”回転・操作性”を備えた新時代のハイスペックリールの誕生！フルメタル(AL製)モノコックボディに大口径Ｇ１ジュラルミン製MC(マシンカット)タフデジギアを搭載し、破格の「巻きの強さ」と「ギアの強さ」を実現。「強靭」かつ「低慣性」を高次元で両立したAL製 AIRDRIVE ROTORが水中の潮の変化や魚の追従によるルアーの挙動変化といった水中の情報量UPをもたらし、テクニカルな大物狙いにおいて圧倒的なアドバンテージをアングラーに与えてくれる。 “BREAK YOUR RECORD” 全く新しいSALTIGA 4000/5000/6000が新時代のSWゲームを切り拓く！ | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23SALTIGA4000/5000/6000においては、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SHAFT の3つを搭載。</v>
+      </c>
+      <c r="N142" t="str">
+        <v>¥105,000 - ¥115,000</v>
+      </c>
+      <c r="O142" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="143" xml:space="preserve">
+      <c r="A143" t="str">
+        <v>DRE1002</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143" t="str">
+        <v>EXIST</v>
+      </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
+      <c r="E143" t="str">
+        <v>2022</v>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I143" t="str">
+        <v>images/daiwa_reels/EXIST_main.jpg</v>
+      </c>
+      <c r="J143" t="str">
+        <v>2026-04-05T14:37:11.658942Z</v>
+      </c>
+      <c r="K143" t="str">
+        <v>2026-04-05T14:37:11.658942Z</v>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str" xml:space="preserve">
+        <v xml:space="preserve">小型スピニングリールに求められる機能と美。ダイワのクラフトマンシップから生み出された、ひとつの結晶。それが、EXIST。その基幹をなすテクノロジー「AIRDRIVE DESIGN」。釣り人が求める、意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。このAIRDRIVE DESIGNは、最大4つのテクノロジーで構成される。その中でも象徴となるのが、エアドライブローター。心揺さぶるような軽快な回転フィーリングを実現している。そこからは想像もできないような、確かな剛性感を生み出すのが、モノコックボディ。たわみにくく、安定した回転を生み出す源である。その屈強なボディに守られ、限りなくノイズレスな回転を実現するタフデジギアには、ギア硬度を高めるために特殊表面処理を施し、万全を期した。ダイワ独自の防水・耐久テクノロジーであるマグシールドは、ピニオン部とラインローラー部に搭載するとともに、ドライブギア両端部にはマグシールドボールベアリングで、高度な防水性能を実現（SFモデルはピニオン部の1箇所のみ）。ドラグは、魚の引きに合わせて滑らかに効き続けるATDの特性をそのままに、初動レスポンスをさらに向上させ、ライトライン使用時でも安心してファイトが可能なATD TYPE-Lを搭載した。これらから生み出されるパフォーマンスを、単なる道具としてだけではなく、アングラーと心通わせるものにするために、EXISTは、そのデザインやサービスにも想いを込めている。ショア、オフショアを問わず、あらゆるフィールドで調和するピュアな造形。末永く安心してお使いいただくためのユーザーサポート。すべては、未来のルアーフィッシングシーンを切り拓く存在であるために。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※LTモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。SFモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N143" t="str">
+        <v>¥102,000 - ¥110,000</v>
+      </c>
+      <c r="O143" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="144" xml:space="preserve">
+      <c r="A144" t="str">
+        <v>DRE1003</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144" t="str">
+        <v>セルテート SW</v>
+      </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+      <c r="E144" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I144" t="str">
+        <v>images/daiwa_reels/セルテート_SW_8000___10000___14000___18000___20000_main.jpg</v>
+      </c>
+      <c r="J144" t="str">
+        <v>2026-04-05T14:37:13.603365Z</v>
+      </c>
+      <c r="K144" t="str">
+        <v>2026-04-05T14:37:13.603365Z</v>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str" xml:space="preserve">
+        <v xml:space="preserve">MONOCOQUE BODY
+                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。 | POWERDRIVE DESIGN
+                                                                    パワードライブデザインは、世界中の大型魚と安心して渡り合える高い信頼性を追求した次世代大型スピニングリールの設計思想。このパワードライブデザインは、高効率で力強い巻き上げ力を実現するボディユニット[パワードライブエンジン]と、合理的な球体形状で高剛性と低イナーシャの両立を実現したローターユニット[パワードライブローター]の２つのテクノロジーユニットからなる。ボディユニットの[パワードライブエンジン]は、[オーバーサイズドパワーデジギア]と[ローラーパワーオシレーション]の２つのテクノロジーによって構成される。[オーバーサイズドパワーデジギア]は大口径化・肉厚化と、最適化された歯面形状により、ギアの駆動効率を大幅にアップ。[ローラーパワーオシレーション]はオシレート機構にベアリング方式を採用することで、摩擦抵抗を大幅に低減し、初動レスポンスの向上と、軽い巻き上げを実現した。一方、フロントユニットは、[クランクパワーベール]と[タフラインローラーシステム]の２つのテクノロジーを搭載した[パワードライブローター]によって構成される。[クランクパワーベール]は、ベールの開閉力を強化するとともに、クランク形状を採用することで、ラインローラーへの確実な糸送りを実現。[タフラインローラーシステム]は、ラインローラーの支持構造や形状を見直すことで、耐久性やトラブルレス性を向上させた。これらのテクノロジーの相乗効果により、大型魚をターゲットとしたキャスティングゲームやジギングゲームにおいて、剛性・パワー・耐久性を高次元で実現する。獲るための“強さ”を、ビッグゲームを愛する、すべてのアングラーに。 | ROLLER POWER OSCILLATION
+                                                                    高負荷が絶え間なく続く大型魚とのファイトでは、巻き上げで生じるオシレート部の摩擦抵抗がパワーの伝達ロスに繋がる。その摩擦を極限まで減らすべく、摺動部分は従来のピラー式から2ベアリング式オシレートに変更。これによりオシレート効率は約30%向上し、高負荷時でもスムーズな初動レスポンスと、軽くてパワフルな巻き上げを実現した。※当社比較テストによる。</v>
+      </c>
+      <c r="N144" t="str">
+        <v>¥93,100 - ¥104,500</v>
+      </c>
+      <c r="O144" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str">
+        <v>DRE1004</v>
+      </c>
+      <c r="B145">
+        <v>2</v>
+      </c>
+      <c r="C145" t="str">
+        <v>トーナメントサーフ 45</v>
+      </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
+      <c r="E145" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v>2026-04-05T14:37:20.635215Z</v>
+      </c>
+      <c r="K145" t="str">
+        <v>2026-04-05T14:37:20.635215Z</v>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str" xml:space="preserve">
+        <v xml:space="preserve">さらに先に。「TOURNAMENT」。TOURNAMENTは、トーナメンターを勝利に導くために、先進・先鋭のテクノロジーを搭載し、進化し続ける。「さらに遠くへ」「さらに感度よく」。激化するトーナメントシーンを勝ち残るための、トーナメンターの要求は厳しい。目指すのは、釣りの技術に革新をもたらし、アングラーの満足感へと繋がるプロダクト。最先端の技術をいち早く採り入れ、トーナメントの新しい基準を築き上げていく。TOURNAMENTの勝利への探求が終わることはなく、常にトーナメンターとともにある。 | すべては勝つために。現在のキストーナメントシーンにおいて求められる性能とは何か。リール形状そのものから見直し、まさにゼロから新たなTOURNAMENTを創り上げた。45mmストロークだからこそ実現可能な中近距離から遠距離までカバーできる対応力。遠投域からトルクフル&amp;スムーズな巻き上げ性能。起伏変化をキャスターへ伝えるブレのない回転性能。過酷なキストーナメントシーンで、初期性能を維持する高耐久性能。これらは単にスペックの向上ではない、とことん実釣にこだわり、キャスターの武器になるための進化だ。テーパー角別専用設計「LCスプール」搭載により、理想の放出性能を実現。強さと軽さをもたらすZAIONハウジング、心臓部には高負荷でも屈しないアルミマシンカットタフデジギアで武装し、さらなる高耐久性を実現。ワンピースエアベールによる至極の回転性能は、より快適に、より精悍に。シリーズ最速となるギア比「4.9」の登場により、キストーナメントシーンに衝撃を与える。「DAIWA TECHNOLOGY」のすべてを惜しむことなく投入し、飛距離、回転性能を追い求めた答えが、今ここにある。※ハンドルノブS交換可※ソルト対応 | TOUGH DIGIGEAR
+                                                                    過酷な環境に耐え抜くにはリールを支える強靭な心臓部が必要です。滑らかな回転がより長く続く「タフデジギア」。</v>
+      </c>
+      <c r="N145" t="str">
+        <v>¥98,000</v>
+      </c>
+      <c r="O145" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str">
+        <v>DRE1005</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146" t="str">
+        <v>セルテート HD</v>
+      </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
+      <c r="E146" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I146" t="str">
+        <v>images/daiwa_reels/セルテート_HD_main.jpg</v>
+      </c>
+      <c r="J146" t="str">
+        <v>2026-04-05T14:37:21.734163Z</v>
+      </c>
+      <c r="K146" t="str">
+        <v>2026-04-05T14:37:21.734163Z</v>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str" xml:space="preserve">
+        <v xml:space="preserve">AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
+                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
+      </c>
+      <c r="N146" t="str">
+        <v>¥79,500 - ¥88,000</v>
+      </c>
+      <c r="O146" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="147" xml:space="preserve">
+      <c r="A147" t="str">
+        <v>DRE1006</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147" t="str">
+        <v>セルテート SW</v>
+      </c>
+      <c r="D147" t="str">
+        <v/>
+      </c>
+      <c r="E147" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I147" t="str">
+        <v>images/daiwa_reels/セルテート_SW_4000_5000_6000_main.jpg</v>
+      </c>
+      <c r="J147" t="str">
+        <v>2026-04-05T14:37:28.669103Z</v>
+      </c>
+      <c r="K147" t="str">
+        <v>2026-04-05T14:37:28.669103Z</v>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str" xml:space="preserve">
+        <v xml:space="preserve">MONOCOQUE BODY
+                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。
+                                                                        フルメタル（AL製)モノコックボディを採用。高剛性且つ軽量コンパクトハウジングに最大径のタフデジギアを封入する。 | TOUGH DIGIGEAR
+                                                                    過酷な環境に耐え抜くにはリールを支える強靭な心臓部が必要です。滑らかな回転がより長く続く「タフデジギア」。
+                                                                        24CERTATE SWに搭載しているG1ジュラルミン（超高強度アルミ）は強度と軽量性を併せ持つ。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※24CERTATE SW4000/5000/6000においては、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SHAFTの3つを搭載。</v>
+      </c>
+      <c r="N147" t="str">
+        <v>¥67,000 - ¥72,700</v>
+      </c>
+      <c r="O147" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="148" xml:space="preserve">
+      <c r="A148" t="str">
+        <v>DRE1007</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148" t="str">
+        <v>サーフ ベーシア 45</v>
+      </c>
+      <c r="D148" t="str">
+        <v/>
+      </c>
+      <c r="E148" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v>2026-04-05T14:37:34.521204Z</v>
+      </c>
+      <c r="K148" t="str">
+        <v>2026-04-05T14:37:34.521204Z</v>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str" xml:space="preserve">
+        <v xml:space="preserve">19トーナメントサーフ45から受け継いだ飛距離と回転・耐久性能を実現した投釣り専用機。大口径2°テーパーのロングキャスト（LC）スプール、ラインを綾巻きし、ライン同士の食い込みを抑えるクロスラップを搭載し、スムーズなライン放出を実現。パワフルさと巻き易さを追求したギア比「4.1」を全アイテムにて採用。ZAIONボディとタフデジギアの絶妙なバランスによる滑らかな巻上げとマグシールドによる回転耐久性を実現。 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N148" t="str">
+        <v>¥68,000 - ¥71,000</v>
+      </c>
+      <c r="O148" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="149" xml:space="preserve">
+      <c r="A149" t="str">
+        <v>DRE1008</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149" t="str">
+        <v>エアリティ</v>
+      </c>
+      <c r="D149" t="str">
+        <v/>
+      </c>
+      <c r="E149" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I149" t="str">
+        <v>images/daiwa_reels/エアリティ_main.jpg</v>
+      </c>
+      <c r="J149" t="str">
+        <v>2026-04-05T14:37:40.618600Z</v>
+      </c>
+      <c r="K149" t="str">
+        <v>2026-04-05T14:37:40.618600Z</v>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str" xml:space="preserve">
+        <v xml:space="preserve">かつてない軽さと強さの両立を果たした、超軽量スピニングリール「AIRITY」。LT2500Sで150gと、自重としての軽さはDAIWA史上最高レベルに到達。同時に、“自重以外の軽さ”も手に入れた。それは、タックルとの一体感が得られる軽快な回転フィールと、持ち重りのない最適な重量バランス。その基幹となるテクノロジーが、「エアドライブデザイン」。釣り人が求める、意のままにルアーを操作することを追求した次世代スピニングリールの設計思想で、最大4つのテクノロジーで構成される。そのエアドライブデザインをフル装備することで、リーリング性能とロッドの操作性の向上を高次元で実現。アングラーの意志に対して素直に応える、そのレスポンスが釣る歓びを高めてくれる。軽さを貫くいっぽうで、強さへのこだわりにも、妥協は一切ない。そこに込められているのは、「十分な実釣性能をともなわない軽さには意味がない」というダイワのリール設計における原点。その信念を受け継ぐテクノロジーのひとつが、一体成型構造のモノコックボディ。たわみやゆがみを抑え、力強い巻き上げを生み出す確かな土台。その素材にはマグネシウムを採用。その内部に格納されるのは、滑らかで静かな回転を生み出すタフデジギア。ギア硬度を高める特殊表面処理を施すことで、初期性能が長く続くよう、耐久性も向上させている。防水・防塵も万全を期し、ダイワ独自の防水・耐久テクノロジーであるマグシールドを、ピニオン部とラインローラー部に搭載。ドラグは、ラインへの負荷を低減し、スムーズで安定した滑り出しで、安心してファイトを愉しめるATD TYPE-Lを搭載。スプールには、リップ形状を見直すことで約5％の飛距離アップを実現したLC-ABSを採用など、ダイワテクノロジーの粋を集めた。「AIR＝軽さ」と「REALITY＝真実・実用性」の高次元での融合。高度な実釣性能を備えた超軽量スピニングリール。ライトゲームからライトショアジギングまで、タックルとひとつになれる自由と愉しさを、AIRITYで――。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23AIRITYは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N149" t="str">
+        <v>¥65,000 - ¥69,500</v>
+      </c>
+      <c r="O149" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="150" xml:space="preserve">
+      <c r="A150" t="str">
+        <v>DRE1009</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150" t="str">
+        <v>エアリティ ST</v>
+      </c>
+      <c r="D150" t="str">
+        <v/>
+      </c>
+      <c r="E150" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I150" t="str">
+        <v>images/daiwa_reels/エアリティ_ST_main.jpg</v>
+      </c>
+      <c r="J150" t="str">
+        <v>2026-04-05T14:37:46.839914Z</v>
+      </c>
+      <c r="K150" t="str">
+        <v>2026-04-05T14:37:46.839914Z</v>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str" xml:space="preserve">
+        <v xml:space="preserve">エリアトラウトやネイティブトラウト、バスフィッシングにおいて、リールの回転性能を追求するエキスパートアングラーの渇望は、とどまることを知らない。巻き心地をもっと軽く、巻き感度をもっと高く――その飽くなき願いを真摯に受け止め、回転を突き詰めたスペシャルチューン。それが、23AIRITY ST（センシティブチューン）。超軽量スピニングリール「AIRITY」を、さらに繊細かつダイレクトな巻き心地を実現する、もうひとつのAIRITY。ラインナップは、STとST SFを合わせ、フィネスフィッシングに特化した6モデル。23AIRITY／23AIRITY SFの持つ基本性能を維持したまま、ハンドル回転の軽さに直結する回転主要部のBB（ボールベアリング）を、ノーマルモデルのグリス仕様BBからオイル仕様BBに変更。グリスBBの特質である高い耐久性をあえて捨ててまで、粘性の低いオイル仕様BBを選択し、回転の軽さを高次元で突き詰めた。それだけではない。防水・防塵の要であるピニオン部のマグシールドを、あえて採用せず、スペックには表記されないわずかな軽量化にまでこだわり抜いた。それによってアングラーが手にするのは、研ぎ澄まされた回転性能。極めて無感覚に近い指先へのリーリング抵抗、ハンドルを回す手元に伝わる圧倒的な情報量。“ダイレクトな回転フィール”を求めるアングラーに、AIRITY STの矜持を。【23AIRITY ノーマルモデルとの違い】①回転主要部のBBをオイル仕様BB化②マグシールド非搭載③一目でセンシティブチューンモデルと分かるデザイン | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23AIRITY STは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。23AIRITY ST SFは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N150" t="str">
+        <v>¥65,000 - ¥67,500</v>
+      </c>
+      <c r="O150" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="151" xml:space="preserve">
+      <c r="A151" t="str">
+        <v>DRE1010</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="str">
+        <v>セルテート</v>
+      </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
+      <c r="E151" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I151" t="str">
+        <v>images/daiwa_reels/セルテート_main.jpg</v>
+      </c>
+      <c r="J151" t="str">
+        <v>2026-04-05T14:37:47.828581Z</v>
+      </c>
+      <c r="K151" t="str">
+        <v>2026-04-05T14:37:47.828581Z</v>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str" xml:space="preserve">
+        <v xml:space="preserve">いつまでも愛着を持って使い込んでもらえるようなスピニングリールを創りたい。特定の誰かのためではなく、すべてのアングラーのために――。そのために目指したのは、使い手を選ばない快適な操作性、不安を感じさせない確かな剛性。CERTATEに込められた、その理念は20年の時を経た今も、何ひとつ変わることはない。NEW CERTATEに搭載された、次世代スピニングリールの設計思想「エアドライブデザイン」は、快適な操作性を求め続けた、CERTATEのひとつの到達点。釣り人が求める、意のままにルアーを操作することを目指した設計思想で、最大4つのテクノロジーで構成される。このエアドライブデザインをフル装備することで得られる恩恵は、あまりにも大きい。最適な重量バランスからなる軽やかな操作性。タックルとの一体感を得られる軽快な回転フィール。わずかな魚のアタリや流れの変化も感じられる巻き感度。ライントラブルの大幅な低頻度化。それは、現代のアングラーに向けたCERTATEの明快な答え。新型ドラグのATD TYPE-Lは、ラインへの負担を軽減し、ハイレスポンスでスムーズな滑り出しによる安心で心地よいファイトを約束してくれる。この操作性は、確かな剛性なくしては得られない。だからこそCERTATEは、一貫して剛性にこだわり続けてきた。その象徴ともいえるのが、アルミ素材による一体成型構造の「モノコックボディ」。従来構造のスピニングリールで弱点だった、高負荷時のボディのたわみを極力抑え、強い巻き上げパワーを実現するダイワ独自のテクノロジー。そこにねじ込まれるエンジンプレートもまた、アルミ製。つまり、アルミ製のフルメタルボディによって、心臓部である内部構造は、がっしりとサポートされている。その内部に組み込まれるドライブギアには、硬度を高める特殊表面処理を施し、高負荷時のギアへのダメージを軽減。その動力をフロントユニットに伝えるメインシャフトには、アルミよりもさらに剛性の高いSUSを採用することで、パワーロスすることなく、パフォーマンスを最大限に発揮する。確かな剛性と快適な操作性。この一環した質実剛健こそ、積み重ねた信頼の証。正統進化を果たした20年目のNEW CERTATE、新時代のスタンダード・スピニングリールを、すべてのアングラーに。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※24CERTATEは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N151" t="str">
+        <v>¥54,600 - ¥61,600</v>
+      </c>
+      <c r="O151" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="152" xml:space="preserve">
+      <c r="A152" t="str">
+        <v>DRE1011</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152" t="str">
+        <v>エメラルダス AIR</v>
+      </c>
+      <c r="D152" t="str">
+        <v/>
+      </c>
+      <c r="E152" t="str">
+        <v>2025</v>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I152" t="str">
+        <v>images/daiwa_reels/エメラルダス_AIR_main.jpg</v>
+      </c>
+      <c r="J152" t="str">
+        <v>2026-04-05T14:37:50.096730Z</v>
+      </c>
+      <c r="K152" t="str">
+        <v>2026-04-05T14:37:50.096730Z</v>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str" xml:space="preserve">
+        <v xml:space="preserve">イカと関わるすべての時間を、感動で満たすために。「エメラルダス」。それはDAIWAが世界に先駆けて立ち上げた、スクイッド・ゲーミングのトータルタックルブランド。その手にイカをもたらすために。そして、その最高の瞬間が訪れるまでの、イカと関わるすべての時間を、感動で満たすために。爽快なキャストフィールを。フォール、ステイ、フッキングまでの、ただ待つだけだった時間に、変化と予兆を伝え続けてくれる感度を。大物とのファイトでも安心な信頼感を。そして、トータルデザインだからこそ成せる、快適な操作感と、カメラロールで映えるフォトジェニックさを。エメラルダス。手にしたそのときから、いつでも、いつまでも感動を贈りたい。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※25EMERALDAS AIRでは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N152" t="str">
+        <v>¥57,700 - ¥61,500</v>
+      </c>
+      <c r="O152" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="153" xml:space="preserve">
+      <c r="A153" t="str">
+        <v>DRE1012</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153" t="str">
+        <v>ルビアス</v>
+      </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
+      <c r="E153" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I153" t="str">
+        <v>images/daiwa_reels/ルビアス_main.jpg</v>
+      </c>
+      <c r="J153" t="str">
+        <v>2026-04-05T14:37:57.793850Z</v>
+      </c>
+      <c r="K153" t="str">
+        <v>2026-04-05T14:37:57.793850Z</v>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str" xml:space="preserve">
+        <v xml:space="preserve">AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※LTモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。SFモデルは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
+                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
+      </c>
+      <c r="N153" t="str">
+        <v>¥46,700 - ¥54,500</v>
+      </c>
+      <c r="O153" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="154" xml:space="preserve">
+      <c r="A154" t="str">
+        <v>DRE1013</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154" t="str">
+        <v>プレッソ</v>
+      </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
+      <c r="E154" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v>2026-04-05T14:38:04.826152Z</v>
+      </c>
+      <c r="K154" t="str">
+        <v>2026-04-05T14:38:04.826152Z</v>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str" xml:space="preserve">
+        <v xml:space="preserve">釣り方までもスタイリッシュになっていく。エリアフィッシングの攻略に必要なのは、自然のフィールドとは異なる独自の戦略と技術、そして専用のタックル。エリアフィッシング専用のスペシャルギアとして開発されたのは、イタリア語に語源を持つ『PRESSO』。PRESSOの開発の根底にあるもの。いかにスマートに、いかにクールに釣るか。その釣り方にまでこだわる美意識を集約させたデザインは、タックルをセットした瞬間から、強烈なアイデンティティとともに、アングラーのスイッチを入れる。プロダクトの追求が新しいスタイルまでも提案していく。手にしたあなた自身が、ムーブメントになる。 | DAIWAエリアトラウトブランド「PRESSO」の名を冠するスピニングリールが、ZAION製モノコックボディで新登場。PRESSOリール史上、最軽量の自重、145g（1000S-P）を達成し、またギア部のボールベアリングをオイル仕様化することで、より軽く繊細な巻き心地を実現した。ZAION製モノコックボディ：高い回転精度を維持しながら、自重アンダー150ｇを達成。オイルボールベアリング仕様：巻き感度にこだわったボールベアリングのオイル仕様化。エリアならではのローギア設定（4.9：1）＋ラインキャパ（2.5ｌｂ-100ｍ）超々ジュラルミン製MCタフデジギアATD（スプール2BB仕様）薄肉軽量LC-ABSスプール40mmハンドルアーム＆ハイグリップI シェイプフィネスノブ※淡水専用※ハンドルノブSサイズ交換可 | MONOCOQUE BODY
+                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。</v>
+      </c>
+      <c r="N154" t="str">
+        <v>¥54,200</v>
+      </c>
+      <c r="O154" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="155" xml:space="preserve">
+      <c r="A155" t="str">
+        <v>DRE1014</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155" t="str">
+        <v>カルディア SW</v>
+      </c>
+      <c r="D155" t="str">
+        <v/>
+      </c>
+      <c r="E155" t="str">
+        <v>2022</v>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v>2026-04-05T14:38:06.624875Z</v>
+      </c>
+      <c r="K155" t="str">
+        <v>2026-04-05T14:38:06.624875Z</v>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str" xml:space="preserve">
+        <v xml:space="preserve">フルメタル（AL製）モノコックボディに大口径タフデジギアを搭載し、パワフルかつ軽快な巻き上げ。4000サイズ～18000サイズという幅広いラインナップで人気のライトショアキャスティングやSLJ（スーパーライトジギング）～大型青物、マグロまで、ソルトルアーゲームを完全網羅。ライトショアジギングやボートサワラゲームに最適な5000-CXHと待望のパワーギアモデル 8000-P &amp; 10000-Pが登場ブリクラスが混じるフィールドでのライトショアジギングやサワラ狙いのボートからのブレードジギング、ライトキャスティングゲームに最適な「5000-CXH」、PE3号～4号前後を使用する青物ジギングに最適な「8000-P」、エビングを筆頭とした相模湾キハダゲームやマグロジギングに最適な80mmロングハンドルを搭載した「10000-P」が登場。※ハンドルノブ S 交換可（4000～6000）※ハンドルノブ L 交換可（8000～18000）※ソルト対応 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | MONOCOQUE BODY
+                                                                    強靭・耐久テクノロジー、モノコックボディ。従来スピニングリールは、ボディとボディカバーでドライブギアの両端を支持し、それを数箇所のスクリューで固定する方式が一般的でした。この構造から、更なる精度と剛性の向上を目指し、ボディカバーを廃し、ボディに直接高精度のプレートをねじ込むことで固定したのがモノコックボディ。これによりギアの支持精度が高まり、また剛性･気密性も向上しました。更には、従来スクリューに取られていたスペースを活用し、ドライブギアのサイズを極限まで拡大することにも成功。モノコックボディとは、MONO（ひとつの） - COQUE（殻）という意味。一枚貝の殻がそうであるような強靭さを象徴する、まったく新しい形状はリール構造の常識を打ち破ります。</v>
+      </c>
+      <c r="N155" t="str">
+        <v>¥34,800 - ¥49,300</v>
+      </c>
+      <c r="O155" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="156" xml:space="preserve">
+      <c r="A156" t="str">
+        <v>DRE1015</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156" t="str">
+        <v>ルビアス ST</v>
+      </c>
+      <c r="D156" t="str">
+        <v/>
+      </c>
+      <c r="E156" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I156" t="str">
+        <v>images/daiwa_reels/ルビアス_ST_main.jpg</v>
+      </c>
+      <c r="J156" t="str">
+        <v>2026-04-05T14:38:07.769091Z</v>
+      </c>
+      <c r="K156" t="str">
+        <v>2026-04-05T14:38:07.769091Z</v>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str" xml:space="preserve">
+        <v xml:space="preserve">AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※24LUVIAS ST LTは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOL、AIRDRIVE SHAFTを搭載。24LUVIAS ST SFは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。リニアシャフト仕様。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
+                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
+      </c>
+      <c r="N156" t="str">
+        <v>¥46,700 - ¥47,700</v>
+      </c>
+      <c r="O156" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="157" xml:space="preserve">
+      <c r="A157" t="str">
+        <v>DRE1016</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157" t="str">
+        <v>キャスティズム 25</v>
+      </c>
+      <c r="D157" t="str">
+        <v/>
+      </c>
+      <c r="E157" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v>2026-04-05T14:38:08.826491Z</v>
+      </c>
+      <c r="K157" t="str">
+        <v>2026-04-05T14:38:08.826491Z</v>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str" xml:space="preserve">
+        <v xml:space="preserve">様々な魚種をターゲットにするキャスティズムに必要な性能を追求。アルミマシンカットタフデジギアを搭載し、耐久性を向上させた。ねじ込み式ハンドルを採用しでガタを徹底的に排除。また、より軽量なスプールの採用などにより全体の軽量化を図り、更なるキャスティング性能向上を達成。キャスティングとリトリーブを何度も繰り返すキャスティズムにはさらに心強い仕様となった。ドラグは、置き竿釣法等で有効なクイックドラグと不意の強い引きにもスムーズに作動するATDの2タイプを用意。スプールには、巻いてあるラインの種類が一目で分かるラインメモリー搭載、さらに、力糸や太いリーダーに対応したラインクリップを搭載し、より快適性を高めた。 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N157" t="str">
+        <v>¥40,000</v>
+      </c>
+      <c r="O157" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="158" xml:space="preserve">
+      <c r="A158" t="str">
+        <v>DRE1017</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="C158" t="str">
+        <v>ロングビーム 35</v>
+      </c>
+      <c r="D158" t="str">
+        <v/>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v>2026-04-05T14:38:09.882028Z</v>
+      </c>
+      <c r="K158" t="str">
+        <v>2026-04-05T14:38:09.882028Z</v>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str" xml:space="preserve">
+        <v xml:space="preserve">●ZAION Vを採用　ボディ・ボディカバー・ローター素材にZAION Vを投げリールで初めて採用し、強度をキープした上で軽量化を実現。●LCスプール&amp;クロスラップ　35mmストロークでは初のLC（ロングキャスト）スプールを搭載。更にはラインを綾巻きし、ライン同士の食い込みを抑えるクロスラップを搭載し、キャスト時のトラブルが少なく軽快なライン放出を実現。※スプールテーパー角度2°●軽量ハンドルアーム　85mmアルミマシンカット軽量ハンドルアーム採用。　安定した巻き上げ感覚をもたらす高剛性マシンカットハンドル。●ハンドルノブ交換可　Sサイズノブ対応。●35mmスプール互換性あり　過去のダイワ35mmストロークリールのスプールが取付可能。　ドラグ無し同士、QD同士でのスプール互換性あり。　※ドラグ無し⇔QDとの互換性はありません。 | ZAION V
+                                                                    リールを、もっと軽く、強く。そのために開発されたカーボンハイブリッド樹脂が、ザイオン V（ブイ）。ハイブリッドするカーボン量を緻密にコントロールすることで、金属を凌駕する軽量性と金属に比肩するほどの強度をハイレベルで実現するとともに、多くのリールに搭載可能なバーサタイル性をあわせ持たせました。カーボンハイブリッド樹脂のMAXスペックともいえるザイオンのエッセンスを受け継いでいます。 | LC-ABS（ロングキャストABS)
+                                                                    ABSⅡの接触抵抗を減らす思想はそのままに、接点を前にだすことでよりスムーズなライン放出を実現。リング部が前に出た効果でリング上にラインが乗りにくくなり、従来のABSⅡ以上に約5%の距離UPとトラブルレスの向上に成功しました。LC（=LONG CAST）を実現する次世代のABSスプールです。</v>
+      </c>
+      <c r="N158" t="str">
+        <v>¥36,000 - ¥38,000</v>
+      </c>
+      <c r="O158" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="159" xml:space="preserve">
+      <c r="A159" t="str">
+        <v>DRE1018</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="str">
+        <v>エメラルダス RX</v>
+      </c>
+      <c r="D159" t="str">
+        <v/>
+      </c>
+      <c r="E159" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I159" t="str">
+        <v>images/daiwa_reels/エメラルダス_RX_main.jpg</v>
+      </c>
+      <c r="J159" t="str">
+        <v>2026-04-05T14:38:12.642500Z</v>
+      </c>
+      <c r="K159" t="str">
+        <v>2026-04-05T14:38:12.642500Z</v>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str" xml:space="preserve">
+        <v xml:space="preserve">イカと関わるすべての時間を、感動で満たすために。「エメラルダス」。それはDAIWAが世界に先駆けて立ち上げた、スクイッド・ゲーミングのトータルタックルブランド。その手にイカをもたらすために。そして、その最高の瞬間が訪れるまでの、イカと関わるすべての時間を、感動で満たすために。爽快なキャストフィールを。フォール、ステイ、フッキングまでの、ただ待つだけだった時間に、変化と予兆を伝え続けてくれる感度を。大物とのファイトでも安心な信頼感を。そして、トータルデザインだからこそ成せる、快適な操作感と、カメラロールで映えるフォトジェニックさを。エメラルダス。手にしたそのときから、いつでも、いつまでも感動を贈りたい。 | AIRDRIVE DESIGN採用により、操作性に磨きをかけた23EMERALDAS RXAIRDRIVE DESIGNのもたらす高次元の操作性は、「巻く」「シャクる」を繰り返すエギングにとって大きなメリットとなる。「十分な実釣性能をともなわない軽さには意味がない」というダイワのリール設計思想を元に強さへのこだわりにも、妥協は一切ない。ZAION V製MQボディにより、「強さ」も担保。リールへの負荷が大きいエギングに対しても、安心して使い込める設計になっている。滑らかで静かな回転を生み出すタフデジギアとダイワ独自の防水・耐久テクノロジーであるマグシールドを搭載。初期性能の持続により、ストレスフリーな釣りをサポート。ドラグには、ATD TYPE-Lを採用。ドラグの初動レスポンスを向上させたことで、追従性が大幅に向上した。バラシやラインブレイクを大幅に軽減し、不意の大型アオリに対しても安心して対峙できる。シーズンを通して使用できるオールラウンドモデルのノーマルLT2500番は、高剛性でトルクフルな巻き上げが可能。 FCモデルの2500番は、よりフィネスな2.5号～3.0号のエギを使用し、浅場をランガンする秋の数釣りシーズンに特化した設計。1サイズ小型のボディを採用することで、圧倒的な軽量化を達成。操作性の向上に寄与。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23EMERALDAS RXは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。</v>
+      </c>
+      <c r="N159" t="str">
+        <v>¥33,700 - ¥35,700</v>
+      </c>
+      <c r="O159" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="160" xml:space="preserve">
+      <c r="A160" t="str">
+        <v>DRE1019</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="C160" t="str">
+        <v>パワーサーフQD</v>
+      </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
+      <c r="E160" t="str">
+        <v>2015</v>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v>2026-04-05T14:38:19.598691Z</v>
+      </c>
+      <c r="K160" t="str">
+        <v>2026-04-05T14:38:19.598691Z</v>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str" xml:space="preserve">
+        <v xml:space="preserve">ダイワの防水・耐久テクノロジー『マグシールド』による防水・防塵性能の向上、ローターバランスが向上し、レスポンスの良い回転フィーリングをもたらすエアローターなど基本性能を磨き上げることにこだわってダイワテクノロジーを惜しみなく搭載。ドラグのON/OFFが瞬時に可能なクイックドラグ（QD）も採用。使い込むほどにその深化を体感できる、パワフルなサーフキャスティングリールの大定番。※ハンドルノブS交換可 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N160" t="str">
+        <v>¥33,700 - ¥35,200</v>
+      </c>
+      <c r="O160" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="161" xml:space="preserve">
+      <c r="A161" t="str">
+        <v>DRE1020</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+      <c r="C161" t="str">
+        <v>カルディア</v>
+      </c>
+      <c r="D161" t="str">
+        <v/>
+      </c>
+      <c r="E161" t="str">
+        <v>2025</v>
+      </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I161" t="str">
+        <v>images/daiwa_reels/カルディア_main.jpg</v>
+      </c>
+      <c r="J161" t="str">
+        <v>2026-04-05T14:38:25.700195Z</v>
+      </c>
+      <c r="K161" t="str">
+        <v>2026-04-05T14:38:25.700195Z</v>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str" xml:space="preserve">
+        <v xml:space="preserve">釣り人が求める、意のままにルアーを操作することを目指した設計思想エアドライブデザインが、ついにCALDIAに採用。ボディとローターというメインパーツには、ZAIONのエッセンスを受け継ぐZAION Vを採用し、軽量性と高剛性をハイレベルで実現。新たに5000番サイズを追加し、サーフフィッシングやライトショアジギング等、今まで以上に幅広い釣種をターゲットに。エアドライブデザインとモノコックボディという、ダイワの小型スピニングリールにおける2大テクノロジーを採用し、新たなステージへと昇華されたCALDIAで、ダイワの本気を体感して欲しい。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※25CALDIAでは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N161" t="str">
+        <v>¥28,800 - ¥33,800</v>
+      </c>
+      <c r="O161" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="162" xml:space="preserve">
+      <c r="A162" t="str">
+        <v>DRE1021</v>
+      </c>
+      <c r="B162">
+        <v>2</v>
+      </c>
+      <c r="C162" t="str">
+        <v>パワーサーフ SS QD</v>
+      </c>
+      <c r="D162" t="str">
+        <v/>
+      </c>
+      <c r="E162" t="str">
+        <v>2018</v>
+      </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v>2026-04-05T14:38:32.644728Z</v>
+      </c>
+      <c r="K162" t="str">
+        <v>2026-04-05T14:38:32.644728Z</v>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str" xml:space="preserve">
+        <v xml:space="preserve">クイックドラグで楽しむ。軽量コンパクトで操作性を追求したサーフリールの決定版。25mmストロークで軽量コンパクトを実現。更に糸落ち防止機構をリニューアル。アイテムに応じたギヤー比を採用。パワフルな巻取りでリーリングをサポートするパワーTノブを搭載。瞬時に緩める/締めるが切り替えられるクイックドラグにより、サーフや堤防、磯からの大物狙いにも対応する。※ハンドルノブS交換可※ソルト対応 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N162" t="str">
+        <v>¥32,000 - ¥33,500</v>
+      </c>
+      <c r="O162" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="163" xml:space="preserve">
+      <c r="A163" t="str">
+        <v>DRE1022</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163" t="str">
+        <v>プロカーゴ SS 遠投</v>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+      <c r="E163" t="str">
+        <v>2018</v>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v>2026-04-05T14:38:33.681131Z</v>
+      </c>
+      <c r="K163" t="str">
+        <v>2026-04-05T14:38:33.681131Z</v>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str" xml:space="preserve">
+        <v xml:space="preserve">人気のショートストロークカゴ遠投リールが新たな糸落ち防止機構を搭載してリニューアル。パワーTノブ搭載でマダイや小型青物とのやり取りでもパワフルな巻上げが可能。さらに「ATD」搭載で大物とのやり取りも安心。■ZAIONボディ× 25mmストロークボディにZAIONを採用し、ボディ全体の軽量化。合わせて、タックルバランスにも大きく影響するスプールを徹底軽量化。25mmストロークならではのコンパクトサーフリールで、快適な投げ釣りをサポート。■新型糸落ち防止機構搭載（従来の機構から更に進化）ライントラブルの多いショートスカートスプールに独自の糸落ち抑制機構を搭載。メインシャフトまでの侵入を抑制。糸落ち発生時、スプールへ巻きつける構造を採用。クローズベールのまま、ドラグを緩めて引き出すことが可能となり、トラブル復帰が改善された。※注意：上記方法で復帰できない場合、スプールを外してライン絡みを解除してください。■スプール互換性ダイワカゴリールにおいても優位性として挙げられる「スプール互換性」。カゴ遠投では、状況に応じてのメインライン交換が頻繁に行われるため、スプール互換性は無くてはならない機能の一つ。※新型糸落ち防止機構搭載により、互換性を一部保持した状態です。ハンドルノブS交換可。ソルト対応。 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | ATD
+                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
+      </c>
+      <c r="N163" t="str">
+        <v>¥31,000 - ¥31,500</v>
+      </c>
+      <c r="O163" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="164" xml:space="preserve">
+      <c r="A164" t="str">
+        <v>DRE1023</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164" t="str">
+        <v>月下美人</v>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+      <c r="E164" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I164" t="str">
+        <v>images/daiwa_reels/月下美人_main.jpg</v>
+      </c>
+      <c r="J164" t="str">
+        <v>2026-04-05T14:38:34.700529Z</v>
+      </c>
+      <c r="K164" t="str">
+        <v>2026-04-05T14:38:34.700529Z</v>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str" xml:space="preserve">
+        <v xml:space="preserve">夜に咲く花は、輝きを増し続ける。2005年、DAIWAのラインナップに初めて登場したライトソルトゲーム専用タックル『月下美人』。艶やかに咲くその花のように月下美人は舞い、アングラーは躍動する。身近なターゲットでありながら、時には極めて繊細なアプローチを必要とするアジや、岩陰や藻の切れ目に身を隠し、周囲を警戒しながらベイトが近くに現れるのを待ち続ける老獪な大型メバルを相手に進化してきた月下美人タックル。これからも月下美人は、アングラーと共に進化し、これまでに味わったことのないような悦び、楽しみを提供する。月下美人の艶やかな輝きがライトソルトゲームを照らし続ける。 | 軽量性、高剛性を兼ね備えた、ライトソルト専用設計のスピニングリール”月下美人”軽量ルアーを操るライトソルトゲームのあらゆるシチュエーションにおいて、AIRDRIVE DESIGNのもたらす高次元の操作性は大きなメリットとなる。特に、AIRDRIVE DESIGNのキーテクノロジーである、軽量かつ低慣性なAIRDRIVE ROTORが、巻き感度の飛躍的な向上をもたらし、今まで感じ取れなかったような繊細なアタリをも確実に捉えることを可能にした。ビスがなく、球体から切り出したかのような独自の形状をしたAIRDRIVE ROTORと、最適な傾斜セッティングを施したAIRDRVE BAILがライントラブルを大幅に軽減。トラブルレス性能は、ライトライン使用時のストレスフリーな釣りをサポート。165gという軽量性を達成しながらも、モノコックボディを採用することで、高い剛性を実現。ドラグにはATD TYPE-Lを採用。ドラグの初動レスポンスを向上させたことで、追従性が大幅に向上した。極細ラインを多用するライトソルトにおいて、バラシやラインブレイクの軽減は大きなアドバンテージになる。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23月下美人は、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。</v>
+      </c>
+      <c r="N164" t="str">
+        <v>¥31,100</v>
+      </c>
+      <c r="O164" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="165" xml:space="preserve">
+      <c r="A165" t="str">
+        <v>DRE1024</v>
+      </c>
+      <c r="B165">
+        <v>2</v>
+      </c>
+      <c r="C165" t="str">
+        <v>タトゥーラ</v>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+      <c r="E165" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v>2026-04-05T14:38:40.792539Z</v>
+      </c>
+      <c r="K165" t="str">
+        <v>2026-04-05T14:38:40.792539Z</v>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str" xml:space="preserve">
+        <v xml:space="preserve">バスフィッシングの本場アメリカで生まれ、日米の多くのバサーに愛されてきた「TATULA」ブランドが10周年を迎える。実戦で鍛え抜き、「モノコックボディ×AIRDRIVE DESIGN」により進化を遂げたTATULA。軽さと強さを両立するZAION V製のモノコックボディは、負荷が掛かった状態でもたわみや歪みを抑えて力強い巻き上げをアシスト。一方でZAION V製エアドライブローターの搭載により、低慣性化による軽い巻き出しも実現している。またドラグには、スムーズな滑り出しと安定した効きでラインへの負荷を低減するATD TYPE-Lを採用。少ないノブの回転で瞬時にテンションを調整できるクイックドラグとの相乗効果で、ライトライン使用時においても、バスとのファイトを楽しみつつスピーディにビッグフィッシュを獲ることを可能とした。パワー系の釣りも視野に入れてオールラウンドに使用できるノーマルLT2500番と、フィネス性能の向上を狙って1サイズコンパクトなボディで開発したFC（フィネスカスタム）モデルをラインナップ。このTATULAが、フィールドのタフ化が進む現代のバスフィッシングシーンをリードする。淡水専用。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23TATULAは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N165" t="str">
+        <v>¥31,100</v>
+      </c>
+      <c r="O165" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="166" xml:space="preserve">
+      <c r="A166" t="str">
+        <v>DRE1025</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+      <c r="C166" t="str">
+        <v>ブラスト LT</v>
+      </c>
+      <c r="D166" t="str">
+        <v/>
+      </c>
+      <c r="E166" t="str">
+        <v>2018</v>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v>2026-04-05T14:38:47.666864Z</v>
+      </c>
+      <c r="K166" t="str">
+        <v>2026-04-05T14:38:47.666864Z</v>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str" xml:space="preserve">
+        <v xml:space="preserve">近海域でのライトジギングやキャスティングゲーム、ショアからのショアジギゲーム、スーパーライトジギングなど幅広く対応。SWシーンで活躍する高剛性LTスピニング。高強度アルミハウジングパワフルに！そして快適に。『アルミマシンカットデジギア』搭載パワーライトノブを標準装備。ショア・オフショアでの使用感にこだわったハンドルセッティング※ハンドルノブS交換可※ソルト対応 | LT-Concept
+                                                                    ダイワの軽量＆タフコンセプト。ボディ、スプール、ハンドルといった細部までの徹底した軽量化へのこだわりと、リールの心臓部となるギアとそれを包み込むボディの構造や素材の進化のバランスをトータルで高め続け生まれた、ダイワ小型スピニングの新基準「LT」。 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。</v>
+      </c>
+      <c r="N166" t="str">
+        <v>¥28,000 - ¥29,000</v>
+      </c>
+      <c r="O166" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="167" xml:space="preserve">
+      <c r="A167" t="str">
+        <v>DRE1026</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167" t="str">
+        <v>BG SW</v>
+      </c>
+      <c r="D167" t="str">
+        <v/>
+      </c>
+      <c r="E167" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v>2026-04-05T14:38:51.628942Z</v>
+      </c>
+      <c r="K167" t="str">
+        <v>2026-04-05T14:38:51.628942Z</v>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str" xml:space="preserve">
+        <v xml:space="preserve">フルメタル（AL製）ボディにねじ込みハンドル式の大口径タフデジギアを搭載しパワフルな巻き上げを実現。LC-ABS搭載で「トラブルレス」&amp;「飛距離UP」。濡れても滑りにくく力が込めやすいEVAラウンドノブを標準装備。4000サイズ～18000サイズという充実のラインナップで人気のライトショアジギング～オフショアの大物狙いまで幅広いソルトルアーゲームに対応。※ハンドルノブS 交換可（4000～6000）。※ハンドルノブL 交換可（8000～18000）。※ソルト対応。 | TOUGH DIGIGEAR
+                                                                    過酷な環境に耐え抜くにはリールを支える強靭な心臓部が必要です。滑らかな回転がより長く続く「タフデジギア」。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N167" t="str">
+        <v>¥19,400 - ¥28,500</v>
+      </c>
+      <c r="O167" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="168" xml:space="preserve">
+      <c r="A168" t="str">
+        <v>DRE1027</v>
+      </c>
+      <c r="B168">
+        <v>2</v>
+      </c>
+      <c r="C168" t="str">
+        <v>レグザ</v>
+      </c>
+      <c r="D168" t="str">
+        <v/>
+      </c>
+      <c r="E168" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I168" t="str">
+        <v>images/daiwa_reels/レグザ_main.jpg</v>
+      </c>
+      <c r="J168" t="str">
+        <v>2026-04-05T14:38:58.278242Z</v>
+      </c>
+      <c r="K168" t="str">
+        <v>2026-04-05T14:38:58.278242Z</v>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str" xml:space="preserve">
+        <v xml:space="preserve">過酷なフィッシングシーンを想定し、開発されたタフリール「LEXA」リールの心臓部であるドライブギアには、タフデジギアを搭載。外殻となるボディ素材は、高強度のアルミを採用した。さらにピニオン部にマグシールドを搭載することで、LEXAの代名詞である高剛性・高耐久性を実現。新たにAIRDRIVE DESIGNを採用することで、巻き出しの軽さと重量バランスを改善し、高次元の操作性を手に入れた。ショアジギング、シーバス、SLJ、ロックフィッシュゲームなど、タフさが求められるシーンでこそ、真価を発揮する。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23LEXAは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N168" t="str">
+        <v>¥24,400 - ¥27,400</v>
+      </c>
+      <c r="O168" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="169" xml:space="preserve">
+      <c r="A169" t="str">
+        <v>DRE1028</v>
+      </c>
+      <c r="B169">
+        <v>2</v>
+      </c>
+      <c r="C169" t="str">
+        <v>シーパラダイス</v>
+      </c>
+      <c r="D169" t="str">
+        <v/>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v>2026-04-05T14:39:02.188132Z</v>
+      </c>
+      <c r="K169" t="str">
+        <v>2026-04-05T14:39:02.188132Z</v>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str" xml:space="preserve">
+        <v xml:space="preserve">マダイや大型青物とのやり取りに求められる堅牢さと最適な巻糸量を備えた海上釣堀専用スピニングリール。なめらかな回転を長期間維持するダイワ独自の防水・耐久テクノロジー「マグシールド」を筆頭に、剛性に優れた「スーパーメタルボディ」、安定した滑り出しの「UTD（アルティメットトーナメントドラグ）」など、ダイワだからこそ可能な先進テクノロジーを搭載。しっかり握り込めるEVA製大型ラウンドノブとの相乗効果によるトルクフルな巻き上げで、大型青物とのゴリ巻きファイトでも力負けしないタフな1台。※ハンドルノブS交換可。※ソルト対応。 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N169" t="str">
+        <v>¥25,900</v>
+      </c>
+      <c r="O169" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="170" xml:space="preserve">
+      <c r="A170" t="str">
+        <v>DRE1029</v>
+      </c>
+      <c r="B170">
+        <v>2</v>
+      </c>
+      <c r="C170" t="str">
+        <v>フリームス</v>
+      </c>
+      <c r="D170" t="str">
+        <v/>
+      </c>
+      <c r="E170" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I170" t="str">
+        <v>images/daiwa_reels/フリームス_main.jpg</v>
+      </c>
+      <c r="J170" t="str">
+        <v>2026-04-05T14:39:04.561638Z</v>
+      </c>
+      <c r="K170" t="str">
+        <v>2026-04-05T14:39:04.561638Z</v>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str" xml:space="preserve">
+        <v xml:space="preserve">新たに「AIRDRIVE DESIGN」を採用した、グローバルスタンダードモデル。「AIRDRIVE ROTOR」と「AIRDRIVE BAIL」、2つのテクノロジーを搭載し、アングラーの思い通りの操作を実現する。リール操作時の慣性を極限まで抑えることで、巻き出しの軽さ、ルアー操作のキレ、感度の高さ――そのすべてがこれまでのスタンダードを超えていく。さらにドラグには「ATD TYPE-L」と「スプール別体ラチェット」を採用。初動レスポンスの向上と心地よいドラグサウンドが、ファイトシーンを一層快適にサポートする。そして、「MAGSEALED」をピニオン部に搭載。マグオイルを用いた機構で、水や砂塵を気にすることなく釣りの時間を愉しめる。このリールが、あなたの“夢のカタチ”を描き出す。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※26FREAMSでは、ZAION V製AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N170" t="str">
+        <v>¥18,700 - ¥25,100</v>
+      </c>
+      <c r="O170" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="171" xml:space="preserve">
+      <c r="A171" t="str">
+        <v>DRE1030</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171" t="str">
+        <v>ウインドキャスト</v>
+      </c>
+      <c r="D171" t="str">
+        <v/>
+      </c>
+      <c r="E171" t="str">
+        <v>2017</v>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v>2026-04-05T14:39:16.714731Z</v>
+      </c>
+      <c r="K171" t="str">
+        <v>2026-04-05T14:39:16.714731Z</v>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str" xml:space="preserve">
+        <v xml:space="preserve">タフさが求められる磯遠投リールにおいてメリットの大きいダイワの防水･耐久テクノロジー「マグシールド」を搭載。エアローターにより、快適な回転性能を手に入れ、遠投時の巻き取り効率も向上。スプールには遠投性能に定評のある35mmストロークアルミスプールを採用。パワーと遠投性能の両立により、カゴ･磯投げで狙える幅広いターゲットに対応。エアベール、クロスラップ、糸落ち防止機能を搭載し、ライントラブルに対しても強化。ハンドルは遠投の際の巻取りのしやすさを考慮した85mm仕様。4000QD、6000QDは置き竿の釣りで不意の大物が期待できる時などに便利なクイックドラグ搭載モデル。ドラグノブを約1回転するだけで緩める・締めるが可能なドラグ機能で、掛かるまではドラグを緩め、掛かった後は迅速にドラグを締めることができるのでやり取りまでにもたつかない。6000QDは大型タマン（ハマフエフキ）にも対応可能。※ソルト対応。※ハンドルノブS交換可。 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N171" t="str">
+        <v>¥21,300 - ¥24,300</v>
+      </c>
+      <c r="O171" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="172" xml:space="preserve">
+      <c r="A172" t="str">
+        <v>DRE1031</v>
+      </c>
+      <c r="B172">
+        <v>2</v>
+      </c>
+      <c r="C172" t="str">
+        <v>イプリミ</v>
+      </c>
+      <c r="D172" t="str">
+        <v/>
+      </c>
+      <c r="E172" t="str">
+        <v>2025</v>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I172" t="str">
+        <v>images/daiwa_reels/イプリミ_main.jpg</v>
+      </c>
+      <c r="J172" t="str">
+        <v>2026-04-05T14:39:18.443898Z</v>
+      </c>
+      <c r="K172" t="str">
+        <v>2026-04-05T14:39:18.443898Z</v>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str" xml:space="preserve">
+        <v xml:space="preserve">AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※25IPRIMIは、AIRDRIVE ROTOR、AIRDRIVE BAIL、AIRDRIVE SPOOLを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
+                                                                    剛性と軽量性をもたらす中空パイプ構造を採用してきたエアベールを、さらなる軽量化を実現するべく、必要強度を維持しながら小径化。ラインがベールからラインローラーヘと、よりスムーズに移行可能な最適なベール角度に傾斜セッティング。さらなる軽量性、トラブルレスを実現しました。</v>
+      </c>
+      <c r="N172" t="str">
+        <v>¥23,300</v>
+      </c>
+      <c r="O172" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="173" xml:space="preserve">
+      <c r="A173" t="str">
+        <v>DRE1032</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
+      <c r="C173" t="str">
+        <v>エメラルダス X</v>
+      </c>
+      <c r="D173" t="str">
+        <v/>
+      </c>
+      <c r="E173" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I173" t="str">
+        <v>images/daiwa_reels/エメラルダス_X_main.jpg</v>
+      </c>
+      <c r="J173" t="str">
+        <v>2026-04-05T14:39:24.533666Z</v>
+      </c>
+      <c r="K173" t="str">
+        <v>2026-04-05T14:39:24.533666Z</v>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str" xml:space="preserve">
+        <v xml:space="preserve">イカと関わるすべての時間を、感動で満たすために。「エメラルダス」。それはDAIWAが世界に先駆けて立ち上げた、スクイッド・ゲーミングのトータルタックルブランド。その手にイカをもたらすために。そして、その最高の瞬間が訪れるまでの、イカと関わるすべての時間を、感動で満たすために。爽快なキャストフィールを。フォール、ステイ、フッキングまでの、ただ待つだけだった時間に、変化と予兆を伝え続けてくれる感度を。大物とのファイトでも安心な信頼感を。そして、トータルデザインだからこそ成せる、快適な操作感と、カメラロールで映えるフォトジェニックさを。エメラルダス。手にしたそのときから、いつでも、いつまでも感動を贈りたい。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※24EMERALDAS Xは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N173" t="str">
+        <v>¥20,700 - ¥22,000</v>
+      </c>
+      <c r="O173" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="174" xml:space="preserve">
+      <c r="A174" t="str">
+        <v>DRE1033</v>
+      </c>
+      <c r="B174">
+        <v>2</v>
+      </c>
+      <c r="C174" t="str">
+        <v>ウインドサーフ 35</v>
+      </c>
+      <c r="D174" t="str">
+        <v/>
+      </c>
+      <c r="E174" t="str">
+        <v>2017</v>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v>2026-04-05T14:39:26.663511Z</v>
+      </c>
+      <c r="K174" t="str">
+        <v>2026-04-05T14:39:26.663511Z</v>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str" xml:space="preserve">
+        <v xml:space="preserve">ダイワ独自の防水･耐久テクノロジー「マグシールド」を搭載し、初期性能の維持を追求。初期の滑らかな回転性能が持続することは、雨や波しぶき、風に運ばれる塵や砂など厳しい環境下に置かれる投げリールにとって大きなアドバンテージとなる。軽快な回転性能を支えるエアローターと中空構造のエアベールは、中・近距離での釣りにはもちろん遠投時に投げリールに求められる重要なファクターであるスムーズな巻き感の向上につながる。回転初動が軽いため、止める・動かすに瞬時に対応可能。そして単純な飛距離だけでは成り立たないのが投げリール。トラブルは大敵であり、「35mmストローク」と「クロスラップ」の相乗効果で糸を問わずライントラブルを最少限に抑えることに成功。またハンドルは、ゴミなどが引っ掛かると相当の負荷が掛かることもある投げ釣りにおいて最も使いやすい長さを考慮した85mmロングハンドルを搭載。ノブもTノブを採用し、上位機種に肉薄する充実のスペックに仕上がっている。 | MAGSEALED
+                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+      </c>
+      <c r="N174" t="str">
+        <v>¥21,500</v>
+      </c>
+      <c r="O174" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="175" xml:space="preserve">
+      <c r="A175" t="str">
+        <v>DRE1034</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+      <c r="C175" t="str">
+        <v>アオリマチックBR LT</v>
+      </c>
+      <c r="D175" t="str">
+        <v/>
+      </c>
+      <c r="E175" t="str">
+        <v>2026</v>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I175" t="str">
+        <v>images/daiwa_reels/アオリマチックBR_LT_main.jpg</v>
+      </c>
+      <c r="J175" t="str">
+        <v>2026-04-05T14:39:33.655150Z</v>
+      </c>
+      <c r="K175" t="str">
+        <v>2026-04-05T14:39:33.655150Z</v>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str" xml:space="preserve">
+        <v xml:space="preserve">AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
+                                                                    ワイヤータイプのAIRDRIVE BAILを採用。ローターユニットのさらなる軽量化を実現するために実釣時における必要強度を維持したまま、大幅軽量化を実現。ベールを含むローターユニットの軽量化により、回転慣性の大幅低減に寄与。回転レスポンスに磨きをかけ、操作性を向上させました。アームレバー部も新形状を採用し、糸絡みを大幅軽減しました。 | ATD TYPE-L
+                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。その初動レスポンスを高めたATD TYPE-L。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
+      </c>
+      <c r="N175" t="str">
+        <v>¥19,400</v>
+      </c>
+      <c r="O175" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="176" xml:space="preserve">
+      <c r="A176" t="str">
+        <v>DRE1035</v>
+      </c>
+      <c r="B176">
+        <v>2</v>
+      </c>
+      <c r="C176" t="str">
+        <v>月下美人 X</v>
+      </c>
+      <c r="D176" t="str">
+        <v/>
+      </c>
+      <c r="E176" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I176" t="str">
+        <v>images/daiwa_reels/月下美人_X_main.jpg</v>
+      </c>
+      <c r="J176" t="str">
+        <v>2026-04-05T14:39:35.787707Z</v>
+      </c>
+      <c r="K176" t="str">
+        <v>2026-04-05T14:39:35.787707Z</v>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str" xml:space="preserve">
+        <v xml:space="preserve">夜に咲く花は、輝きを増し続ける。2005年、DAIWAのラインナップに初めて登場したライトソルトゲーム専用タックル『月下美人』。艶やかに咲くその花のように月下美人は舞い、アングラーは躍動する。身近なターゲットでありながら、時には極めて繊細なアプローチを必要とするアジや、岩陰や藻の切れ目に身を隠し、周囲を警戒しながらベイトが近くに現れるのを待ち続ける老獪な大型メバルを相手に進化してきた月下美人タックル。これからも月下美人は、アングラーと共に進化し、これまでに味わったことのないような悦び、楽しみを提供する。月下美人の艶やかな輝きがライトソルトゲームを照らし続ける。 | 繊細な操作を求められるライトソルトゲーム。24月下美人Xは、巻き感度、操作性、トラブルレス性能を大幅に向上させたライトソルトゲーム専用設計。意のままにルアーを操作することを追求した、次世代スピニングリールの設計思想であるAIRDRIVE DESIGNを採用。軽量ルアーを操作するライトソルトゲームにとって、操作性の向上は魚をキャッチするための大きなメリットとなる。AIRDRIVE DESIGNの基幹テクノロジーであり、巻き出しの軽さと巻き感度に大きく寄与するローターには、ZAION V製のAIRDRIVE ROTORを採用。軽量で低慣性なローターは巻き感度向上に大きく寄与し、繊細なアジのアタリや水流の変化など、水中の情報を感じ取る。また、細糸を多用するライトソルトゲームでは、ライントラブルは大きなストレスとなる。ビスがなく、球体から切り出したかのような形状であるAIRDRIVE ROTOR、そして新形状アームレバーとAIRDRIVE BAILの相乗効果によってトラブルレス性能を向上させ、ストレスから解放する。ドラグには、初動レスポンスを向上させたATD TYPE-Lを採用。ライトライン使用時のラインブレイクを減少させることで、安心したファイトを可能にする。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※24月下美人Xは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。</v>
+      </c>
+      <c r="N176" t="str">
+        <v>¥18,700</v>
+      </c>
+      <c r="O176" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="177" xml:space="preserve">
+      <c r="A177" t="str">
+        <v>DRE1036</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
+      </c>
+      <c r="C177" t="str">
+        <v>レガリス</v>
+      </c>
+      <c r="D177" t="str">
+        <v/>
+      </c>
+      <c r="E177" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I177" t="str">
+        <v>images/daiwa_reels/レガリス_main.jpg</v>
+      </c>
+      <c r="J177" t="str">
+        <v>2026-04-05T14:39:42.740714Z</v>
+      </c>
+      <c r="K177" t="str">
+        <v>2026-04-05T14:39:42.740714Z</v>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str" xml:space="preserve">
+        <v xml:space="preserve">ベストセラースピニングリール「LEGALIS」がフルモデルチェンジ！AIRDRIVE DESIGN ＆ ZAION Vで大幅な進化。新たにボディ&amp;ローターにZAION Vを採用し、剛性と軽量性が大幅UP（LT2500S-XHで、前モデル比▲20g軽量化）ZAION V製AIRDRIVE ROTORでより軽快な「巻く」「止める」操作が可能。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※23LEGALISは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。 | AIRDRIVE ROTOR
+                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+      </c>
+      <c r="N177" t="str">
+        <v>¥12,600 - ¥16,100</v>
+      </c>
+      <c r="O177" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="178" xml:space="preserve">
+      <c r="A178" t="str">
+        <v>DRE1037</v>
+      </c>
+      <c r="B178">
+        <v>2</v>
+      </c>
+      <c r="C178" t="str">
+        <v>クロスキャスト</v>
+      </c>
+      <c r="D178" t="str">
+        <v/>
+      </c>
+      <c r="E178" t="str">
+        <v>2017</v>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v>2026-04-05T14:39:49.593963Z</v>
+      </c>
+      <c r="K178" t="str">
+        <v>2026-04-05T14:39:49.593963Z</v>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str" xml:space="preserve">
+        <v xml:space="preserve">35mmストローク仕様により、カゴ･磯遠投で重要な「飛距離」にこだわったエントリーモデル。エアローター採用により回転性能、遠投の際の巻き取り効率が向上。ライントラブルを軽減するクロスラップはもちろん、大物にも対応する耐久性に優れた「デジギヤⅡ」搭載と、妥協なしのスペック。4000QDは置き竿の釣りで不意の大物が期待できる時などに便利なクイックドラグ搭載モデル。ドラグノブを約1回転するだけで緩める・締めるが可能なドラグ機能で、掛かるまではドラグを緩め、掛かった後は迅速にドラグを締めることができるのでやり取りまでにもたつかない。※ソルト対応 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。 | QUICK  DRAG
+                                                                    瞬時の「クイック」な調整が可能なドラグ。少ないドラグノブの回転で、即座に設定を大きく変えることができる。使用ラインやタックル、釣法に応じて様々に活用可能です。
+                                                                        ※4000QDのみ</v>
+      </c>
+      <c r="N178" t="str">
+        <v>¥12,000 - ¥13,300</v>
+      </c>
+      <c r="O178" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="179" xml:space="preserve">
+      <c r="A179" t="str">
+        <v>DRE1038</v>
+      </c>
+      <c r="B179">
+        <v>2</v>
+      </c>
+      <c r="C179" t="str">
+        <v>レブロス</v>
+      </c>
+      <c r="D179" t="str">
+        <v/>
+      </c>
+      <c r="E179" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I179" t="str">
+        <v>images/daiwa_reels/レブロス_main.jpg</v>
+      </c>
+      <c r="J179" t="str">
+        <v>2026-04-05T14:39:55.715342Z</v>
+      </c>
+      <c r="K179" t="str">
+        <v>2026-04-05T14:39:55.715342Z</v>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str" xml:space="preserve">
+        <v xml:space="preserve">新型AIRDRIVE ROTOR+AIRDRIVE BAIL（ワイヤー）+アームレバーによりローターユニットの軽量化を実現し、全体の軽量化に貢献。（2500S-XHで210ｇ　20レブロスLT2500S-H比▲10ｇの軽量化）また、AIRDRIVE ROTORでリール操作の基本である「巻く」「止める」の操作がより軽快になった。※カスタムパーツに関しては、SLPウェブサイト上の製品対応検索システムをご参照ください。 | AIRDRIVE DESIGN
+                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
+                                                                        ※24REVROSは、エアドライブローター、エアドライブベールを搭載。 | AIRDRIVE BAIL
+                                                                    ワイヤータイプのAIRDRIVE BAILを採用。ローターユニットのさらなる軽量化を実現するために実釣時における必要強度を維持したまま、大幅軽量化を実現。ベールを含むローターユニットの軽量化により、回転慣性の大幅低減に寄与。回転レスポンスに磨きをかけ、操作性を向上させました。アームレバー部も新形状を採用し、糸絡みを大幅軽減しました。</v>
+      </c>
+      <c r="N179" t="str">
+        <v>¥10,000 - ¥12,800</v>
+      </c>
+      <c r="O179" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="180" xml:space="preserve">
+      <c r="A180" t="str">
+        <v>DRE1039</v>
+      </c>
+      <c r="B180">
+        <v>2</v>
+      </c>
+      <c r="C180" t="str">
+        <v>ファインサーフ35</v>
+      </c>
+      <c r="D180" t="str">
+        <v/>
+      </c>
+      <c r="E180" t="str">
+        <v>2017</v>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v>2026-04-05T14:40:02.769370Z</v>
+      </c>
+      <c r="K180" t="str">
+        <v>2026-04-05T14:40:02.769370Z</v>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str" xml:space="preserve">
+        <v xml:space="preserve">35mmストロークで、投げ釣りの醍醐味である「飛び」にこだわったエントリーモデル。快適に最大の飛距離を出すため、ダイワテクノロジーを惜しみなく投入。中・近距離での釣りにはもちろん、遠投時の巻き感は投げリールに求められる重要なファクター。軽快な回転性能を支えるエアローターは回転初動が軽く、止める・動かすに瞬時に対応。また投げリールの大敵であるライントラブルを最小限に抑えるため「クロスラップ」「ツイストバスターII」を採用。上位機種に肉薄するパフォーマンスで、投げ釣りを始めたい方にも最適な1台。※ソルト対応※ハンドルノブ交換不可 | AIRROTOR
+                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。 | DIGIGEAR・DIGIGEARII
+                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。</v>
+      </c>
+      <c r="N180" t="str">
+        <v>¥12,000</v>
+      </c>
+      <c r="O180" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="181" xml:space="preserve">
+      <c r="A181" t="str">
+        <v>DRE1040</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
+      </c>
+      <c r="C181" t="str">
+        <v>アオリトライアル BR</v>
+      </c>
+      <c r="D181" t="str">
+        <v/>
+      </c>
+      <c r="E181" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v>2026-04-05T14:40:09.686164Z</v>
+      </c>
+      <c r="K181" t="str">
+        <v>2026-04-05T14:40:09.686164Z</v>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str" xml:space="preserve">
+        <v xml:space="preserve">マニュアルリターン仕様アオリクラッチ搭載アオリクラッチを従来のオートリターン仕様からマニュアルリターン仕様に変更。ハンドル回転時の意図しないクラッチ戻りを防ぎ、より使い易くなった。※アオリクラッチ　アオリイカに違和感なくアジを抱かせることが必要なヤエン釣法に不可欠な機構でフロントとリアのドラグ切り替えを行うためのクラッチのこと。（このリールはフロントとリアに2種類の独立したドラグを備えたリールです。）スプールフリー調整ダイヤルダイヤルは細かいクリック設定で微調整が可能。ATDアオリイカの引きに合わせスムーズに作動し、滑らかに効き続けるドラグ。LC-ABSスプールの軽量化とスプールリップの形状の見直しにより、快適なライン放出性を実現。※BR＝BITE&amp;RUN※ハンドルノブS 交換可。※ソルト対応。 | ATD
+                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。 | LC-ABS（ロングキャストABS)
+                                                                    ABSⅡの接触抵抗を減らす思想はそのままに、接点を前にだすことでよりスムーズなライン放出を実現。リング部が前に出た効果でリング上にラインが乗りにくくなり、従来のABSⅡ以上に約5%の距離UPとトラブルレスの向上に成功しました。LC（=LONG CAST）を実現する次世代のABSスプールです。</v>
+      </c>
+      <c r="N181" t="str">
+        <v>¥10,300</v>
+      </c>
+      <c r="O181" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="182" xml:space="preserve">
+      <c r="A182" t="str">
+        <v>DRE1041</v>
+      </c>
+      <c r="B182">
+        <v>2</v>
+      </c>
+      <c r="C182" t="str">
+        <v>クレスト</v>
+      </c>
+      <c r="D182" t="str">
+        <v/>
+      </c>
+      <c r="E182" t="str">
+        <v>2020</v>
+      </c>
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v>2026-04-05T14:40:13.112571Z</v>
+      </c>
+      <c r="K182" t="str">
+        <v>2026-04-05T14:40:13.112571Z</v>
+      </c>
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str" xml:space="preserve">
+        <v xml:space="preserve">LTコンセプトにより大幅軽量化を実現！（前モデル2500番比で、なんとマイナス40ｇの軽量化！）ATD採用によりドラグ性能UP！LC-ABSにより飛距離UP！小型スピニングリール新基準「LT」仕様。LTコンセプトによりこの価格帯で、235ｇ（2500番）を達成！タフデジギア、ATD、LC(ロングキャスト）ABSスプール搭載。ソルト対応。 | LT-Concept
+                                                                    ダイワの軽量＆タフコンセプト。ボディ、スプール、ハンドルといった細部までの徹底した軽量化へのこだわりと、リールの心臓部となるギアとそれを包み込むボディの構造や素材の進化のバランスをトータルで高め続け生まれた、ダイワ小型スピニングの新基準「LT」。 | ATD
+                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
+      </c>
+      <c r="N182" t="str">
+        <v>¥6,400 - ¥8,300</v>
+      </c>
+      <c r="O182" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>DRE1042</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183" t="str">
+        <v>MR</v>
+      </c>
+      <c r="D183" t="str">
+        <v/>
+      </c>
+      <c r="E183" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v>2026-04-05T14:40:13.995115Z</v>
+      </c>
+      <c r="K183" t="str">
+        <v>2026-04-05T14:40:13.995115Z</v>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v>お手軽に釣りを楽しめる 軽量＆コンパクトリール。入門機として充実のスペックを搭載。165g 軽量（MR750）でコンパクトリール。コンパクトで握り易いIシェイプノブ、45㎜マシンカットハンドル搭載。※ソルト対応 | 4ボールベアリング+インフィニットストッパー付。最大ドラグ力3kgと充実の基本性能。 | 安定した巻上げ感をもたらす45mmマシンカットハンドル。折りたたみ式なので持ち運びにも便利。</v>
+      </c>
+      <c r="N183" t="str">
+        <v>¥7,000 - ¥7,500</v>
+      </c>
+      <c r="O183" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="184" xml:space="preserve">
+      <c r="A184" t="str">
+        <v>DRE1043</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184" t="str">
+        <v>ジョイナス</v>
+      </c>
+      <c r="D184" t="str">
+        <v/>
+      </c>
+      <c r="E184" t="str">
+        <v>2016</v>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v>2026-04-05T14:40:21.016336Z</v>
+      </c>
+      <c r="K184" t="str">
+        <v>2026-04-05T14:40:21.016336Z</v>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str" xml:space="preserve">
+        <v xml:space="preserve">新型ボディにより、前作に比べて回転フィーリングが大幅に向上。ギヤには耐久性で定評のあるデジギヤIIを搭載。糸絡みトラブルを激減させて快適な飛距離をもたらすABS II、ツイストバスターIIなど機能も充実。ナイロンラインがスプールに巻いてあるため買ってすぐに釣り場で使える万能スピニングリール。淡水・海水どちらのフィールドでも使用可能。またこのクラスでは新提案となる4500、5000の大型サイズもラインナップ。※ソルト対応。 | ABSⅡ
+                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。 | TWIST BUSTER Ⅱ
+                                                                    ラインローラーにテーパーをかけて、ラインをころがすことにより、ローター回転で発生する糸ヨレを相殺。スピニングリールの宿命といわれた糸ヨレを大幅に解消します。</v>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="185" xml:space="preserve">
+      <c r="A185" t="str">
+        <v>DRE1044</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+      <c r="C185" t="str">
+        <v>リーガル PE付</v>
+      </c>
+      <c r="D185" t="str">
+        <v/>
+      </c>
+      <c r="E185" t="str">
+        <v>2016</v>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v>2026-04-05T14:40:27.535715Z</v>
+      </c>
+      <c r="K185" t="str">
+        <v>2026-04-05T14:40:27.535715Z</v>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str" xml:space="preserve">
+        <v xml:space="preserve">軽さと剛性の高さを両立した新型ボディにインフィニットストッパーを搭載することで、巻心地はしっかり＆滑らか。PEラインがはじめからスプールに巻いてあるため、買ってすぐに釣り場で使える点もメリット。高剛性のデジギヤII、ライントラブルを激減させて快適な飛びをもたらすABS II、クロスラップ、ツイストバスターIIなどのダイワテクノロジーを豊富に搭載した充実の仕様。ブラックですっきりまとめられたデザインは様々なロッドに違和感なくマッチする。もちろん淡水・海水どちらのフィールドでも使用可能。 | ABSⅡ
+                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。 | DIGIGEAR・DIGIGEARII
+                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。</v>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="186" xml:space="preserve">
+      <c r="A186" t="str">
+        <v>DRE1045</v>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+      <c r="C186" t="str">
+        <v>タマンモンスター</v>
+      </c>
+      <c r="D186" t="str">
+        <v/>
+      </c>
+      <c r="E186" t="str">
+        <v/>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v>2026-04-05T14:40:29.654844Z</v>
+      </c>
+      <c r="K186" t="str">
+        <v>2026-04-05T14:40:29.654844Z</v>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str" xml:space="preserve">
+        <v xml:space="preserve">大型遠投リールとして実績の高い「ウィンドキャスト6000」をベースに、大型タマン（ハマフエフキ）とのガチンコ勝負にも負けないタフな仕様にブラッシュアップ。ロングストローク35mm正テーパーアルミスプールが確かな遠投性能をもたらし、デジギヤII、85mmロングハンドル＆パワーノブなどで力強い巻き上げが可能。パワーと遠投性能をバランスよく兼備した、タマン専用リールの決定版。 | DIGIGEAR・DIGIGEARII
+                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。 | AIRBAIL
+                                                                    ラインがラインローラーまで流れるように送り出される凹凸のない滑らかなベール形状により、糸ガラミトラブルを大幅に減少します。さらにベール自体を中空構造にしたことで、重量を変えずに大幅な強度アップを実現しました。</v>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="187" xml:space="preserve">
+      <c r="A187" t="str">
+        <v>DRE1046</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187" t="str">
+        <v>ワールドスピン</v>
+      </c>
+      <c r="D187" t="str">
+        <v/>
+      </c>
+      <c r="E187" t="str">
+        <v>2017</v>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v>2026-04-05T14:40:36.686921Z</v>
+      </c>
+      <c r="K187" t="str">
+        <v>2026-04-05T14:40:36.686921Z</v>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str" xml:space="preserve">
+        <v xml:space="preserve">高剛性でスムーズな巻上げ感をもたらすデジギヤII、ライントラブルを減少させるABS II・クロスラップ・ツイストバスターII、ガタつきのない快適な巻き上げが可能なインフィニットストッパーなど、快適な実釣性能をもたらすダイワテクノロジーをしっかり搭載。折りたたみ式アルミハンドルで持ち運びもしやすい。さらにソルト対応のため、淡水はもちろん海のエサ釣りからルアーゲームまで幅広く対応。買ってすぐに釣り場で使える便利な糸付き（CFは糸なし）。※ソルト対応 | DIGIGEAR・DIGIGEARII
+                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。 | ABSⅡ
+                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。</v>
+      </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v>在售</v>
+      </c>
+    </row>
+    <row r="188" xml:space="preserve">
+      <c r="A188" t="str">
+        <v>DRE5000</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188" t="str">
         <v>IM Z リミットブレイカー TW HD-C</v>
       </c>
-      <c r="D141" t="str">
-        <v/>
-      </c>
-      <c r="E141" t="str">
-        <v/>
-      </c>
-      <c r="F141" t="str">
-        <v/>
-      </c>
-      <c r="G141" t="str">
-        <v/>
-      </c>
-      <c r="H141" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I141" t="str">
+      <c r="D188" t="str">
+        <v/>
+      </c>
+      <c r="E188" t="str">
+        <v/>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I188" t="str">
         <v>images/daiwa_reels/IM_Z_リミットブレイカー_TW_HD-C_main.jpg</v>
       </c>
-      <c r="J141" t="str">
+      <c r="J188" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K141" t="str">
+      <c r="K188" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L141" t="str">
-        <v/>
-      </c>
-      <c r="M141" t="str" xml:space="preserve">
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str" xml:space="preserve">
         <v xml:space="preserve">“HYPERDRIVE DESIGN”、“TWS”、 “DAIWA CONNECTING-SYSTEM”、 “INTELLIGENT MAGFORCE”を搭載した、新しい体験と価値観を提案する次世代ベイトリールが登場。デジタル制御ブレーキによる抜けるような気持ちのいいキャストフィールを実現するINTELLIGENT MAGFORCEは、DAIWAアプリと繋げることで機能に拡張性も持ち、状況対応力に優れる。ヘビーデューティー＆ロングキャストモデルとして、中・重量級ルアーであるヘビキャロやジグの超遠投、さらに繊細かつスピーディなルアー操作が求められるビッグベイトゲーム、シーバスや青物といったソルトのストロングゲームに最適。φ38mmG1ジュラルミン製スプールにはフロロ20lb、PE4号100mをストック。さらに最大ドラグ力7kgをマーク。ハイスピードリーリングやラインスラックコントロールに長けた巻取り長さ100cmを誇るギア比8.4を展開。淡水・海水や魚種問わず、ひるむことなくモンスターフィッシュ挑むことができる。ユーザーの日々のフィッシングスタイルに寄り添い、ともに成長し続ける新時代のベイトリールを体現する。それがIM Z LIMITBREAKER TW HD-C。※ソルト対応※製品名解説①IM＝インテリジェントマグフォース②LIMITBREAKER＝対大物仕様③TW＝TWS④HD =ヘビーデューティー⑤-C＝DAIWA CONNECTING-SYSTEM
 DAIWA CONNECTEDはフィッシングシーンに新たな価値を提供するため、「簡単設定」「機能進化」「新たな体験」の実現を目指した。DAIWA CONNECTEDとは「電動モバイルセッティング」と「DAIWAコネクティングシステム」この2つのテクノロジーで構成され“スマートフォンとつながるリール”を表す。DAIWA CONNECTEDの1つである「DAIWAコネクティングシステム」はベイト両軸リール、ワカサギリールに搭載される。「DAIWAコネクティングシステム」はワイヤレス接続対応のリール（末尾に“-C”が記載されたベイト両軸とワカサギリール）と連動することで、機能のアップデートやリールから取得したデータを確認することができる。さらに2025年春、ウェアラブル端末（サブディスプレイ・ヒアラブル）と連動した新たな機能がリリースされた。DAIWA CONNECTEDの発想がフィッシングシーンに新たな価値をもたらし、釣りの楽しみをさらに広げてくれる。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N141" t="str">
-        <v/>
-      </c>
-      <c r="O141" t="str">
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="142" xml:space="preserve">
-      <c r="A142" t="str">
+    <row r="189" xml:space="preserve">
+      <c r="A189" t="str">
         <v>DRE5001</v>
       </c>
-      <c r="B142">
+      <c r="B189">
         <v>2</v>
       </c>
-      <c r="C142" t="str">
+      <c r="C189" t="str">
         <v>IM Z TW 200-C</v>
       </c>
-      <c r="D142" t="str">
-        <v/>
-      </c>
-      <c r="E142" t="str">
+      <c r="D189" t="str">
+        <v/>
+      </c>
+      <c r="E189" t="str">
         <v>2024</v>
       </c>
-      <c r="F142" t="str">
-        <v/>
-      </c>
-      <c r="G142" t="str">
-        <v/>
-      </c>
-      <c r="H142" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I142" t="str">
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I189" t="str">
         <v>images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
       </c>
-      <c r="J142" t="str">
+      <c r="J189" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K142" t="str">
+      <c r="K189" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L142" t="str">
-        <v/>
-      </c>
-      <c r="M142" t="str" xml:space="preserve">
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str" xml:space="preserve">
         <v xml:space="preserve">DAIWAコネクティングシステムを通じて、リール本体のアップデートによる拡張性を備えた次世代ベイトリールシリーズIM Z。新たに200シリーズがデビュー。200シリーズに搭載するスプール開発で目指したのは、DAIWA MAGFORCEブレーキシステムの特性全部載せ。LCコンセプトだけでなくSVコンセプト、さらにはPEライン使用時における際の超遠投スタイルまでをイメージし、スプール特性を検証。具体的には、糸を巻いた状態でのスプールユニット単位におけるウェイトバランスの調整に加え、インダクトローター新規形状を開発するに至った。LIMITBREAKER搭載スプールで目指した超遠投性能の方向性と大きく差別化を図った結果、10ｇ前後～110ｇ（4oz）とルアー対応幅が大きく、φ38ｍｍ大口径スプールの割に使い易さと安定したキャスト性能を手にした。IM Zシリーズ初のギア比7.3（ハンドル1回転87cm）を展開。巻きの釣りに対応する90ｍｍAL製ハンドルに、新型ハイグリップIシェイプパワーラージノブ（S）を初採用。高い基本性能は、“HYPERDRIVE DESIGN”、“TWS”、 “DAIWA CONNECTING-SYSTEM”、 “INTELLIGENT MAGFORCE”で完全武装。淡水・海水や魚種問わず、ひるむことなくモンスターフィッシュに挑むことが可能だ。そして200-CシリーズもDAIWA CONNECTING-SYSTEMに対応。基本となる4つのブレーキモードに加えて、「釣行回数5回達成」と「総飛距離10.0km達成」のバッジを獲得すれば（インストール条件を満たせば）2023年10月30日に配信をスタートした「PEロングキャスト」の使用も可能となる。また、バスフィッシングへの適性が高い200-Cは、キャスト数が多いこの釣りにおいて、アングラーが自己分析するためにより有益なデータの収集・蓄積への期待も高まる。※ソルト対応
 DAIWA CONNECTEDはフィッシングシーンに新たな価値を提供するため、「簡単設定」「機能進化」「新たな体験」の実現を目指した。DAIWA CONNECTEDとは「電動モバイルセッティング」と「DAIWAコネクティングシステム」この2つのテクノロジーで構成され“スマートフォンとつながるリール”を表す。DAIWA CONNECTEDの1つである「DAIWAコネクティングシステム」はベイト両軸リール、ワカサギリールに搭載される。「DAIWAコネクティングシステム」はワイヤレス接続対応のリール（末尾に“-C”が記載されたベイト両軸とワカサギリール）と連動することで、機能のアップデートやリールから取得したデータを確認することができる。さらに2025年春、ウェアラブル端末（サブディスプレイ・ヒアラブル）と連動した新たな機能がリリースされた。DAIWA CONNECTEDの発想がフィッシングシーンに新たな価値をもたらし、釣りの楽しみをさらに広げてくれる。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N142" t="str">
-        <v/>
-      </c>
-      <c r="O142" t="str">
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="143" xml:space="preserve">
-      <c r="A143" t="str">
+    <row r="190" xml:space="preserve">
+      <c r="A190" t="str">
         <v>DRE5002</v>
       </c>
-      <c r="B143">
+      <c r="B190">
         <v>2</v>
       </c>
-      <c r="C143" t="str">
+      <c r="C190" t="str">
         <v>IM Z TW100-C</v>
       </c>
-      <c r="D143" t="str">
-        <v/>
-      </c>
-      <c r="E143" t="str">
+      <c r="D190" t="str">
+        <v/>
+      </c>
+      <c r="E190" t="str">
         <v>2025</v>
       </c>
-      <c r="F143" t="str">
-        <v/>
-      </c>
-      <c r="G143" t="str">
-        <v/>
-      </c>
-      <c r="H143" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I143" t="str">
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I190" t="str">
         <v>images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
       </c>
-      <c r="J143" t="str">
+      <c r="J190" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K143" t="str">
+      <c r="K190" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L143" t="str">
-        <v/>
-      </c>
-      <c r="M143" t="str" xml:space="preserve">
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str" xml:space="preserve">
         <v xml:space="preserve">DAIWA CONNECTEDはフィッシングシーンに新たな価値を提供するため、「簡単設定」「機能進化」「新たな体験」の実現を目指した。DAIWA CONNECTEDとは「電動モバイルセッティング」と「DAIWAコネクティングシステム」この2つのテクノロジーで構成され“スマートフォンとつながるリール”を表す。DAIWA CONNECTEDの1つである「DAIWAコネクティングシステム」はベイト両軸リール、ワカサギリールに搭載される。「DAIWAコネクティングシステム」はワイヤレス接続対応のリール（末尾に“-C”が記載されたベイト両軸とワカサギリール）と連動することで、機能のアップデートやリールから取得したデータを確認することができる。さらに2025年春、ウェアラブル端末（サブディスプレイ・ヒアラブル）と連動した新たな機能がリリースされた。DAIWA CONNECTEDの発想がフィッシングシーンに新たな価値をもたらし、釣りの楽しみをさらに広げてくれる。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
@@ -7130,253 +9457,253 @@
 HYPERDRIVE DIGIGEAR
                                                                     強く滑らかな回転が持続し続けることを追求した新設計のギアシステム｡耐久性に直結するギアの歯のモジュール（大きさ）は小さくせず噛合い率アップを達成したことにより､初期の滑らかさが長く続くことを実現したDAIWA独自のテクノロジーです｡</v>
       </c>
-      <c r="N143" t="str">
-        <v/>
-      </c>
-      <c r="O143" t="str">
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="144" xml:space="preserve">
-      <c r="A144" t="str">
+    <row r="191" xml:space="preserve">
+      <c r="A191" t="str">
         <v>DRE5003</v>
       </c>
-      <c r="B144">
+      <c r="B191">
         <v>2</v>
       </c>
-      <c r="C144" t="str">
+      <c r="C191" t="str">
         <v>スティーズ リミテッド CT SV TW</v>
       </c>
-      <c r="D144" t="str">
-        <v/>
-      </c>
-      <c r="E144" t="str">
-        <v/>
-      </c>
-      <c r="F144" t="str">
-        <v/>
-      </c>
-      <c r="G144" t="str">
-        <v/>
-      </c>
-      <c r="H144" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I144" t="str">
+      <c r="D191" t="str">
+        <v/>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I191" t="str">
         <v>images/daiwa_reels/スティーズ_リミテッド_CT_SV_TW_main.jpg</v>
       </c>
-      <c r="J144" t="str">
+      <c r="J191" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K144" t="str">
+      <c r="K191" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L144" t="str">
-        <v/>
-      </c>
-      <c r="M144" t="str" xml:space="preserve">
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str" xml:space="preserve">
         <v xml:space="preserve">バスフィッシングに 本気で向き合う人々のために。バスフィッシングこそがライフスタイルの中核に位置するような、本気でバスに向き合う人々と共感できるプロダクトを。DAIWAが持つバスへの本気をプロダクトとメッセージで共有できるような、心の通ったブランドを目指した開発陣の秘めた想いを具現化したもの。そのために、DAIWAが持つ技術と想いでストイックに創り込む。ロッドだけではない、リールだけでもない、バスに立ち向かうためのすべてのものに想いをこめて。本気のバスアングラーの熱い想いと一緒に・・・それが「STEEZ」。
 CT=コンパクト＆タフコンセプトにおける集大成、それがSTEEZ LTD CT SV TW。SV＝スーパーバーサタイルコンセプトシリーズ最小径となるG1ジュラルミン製φ30mmCT SVスプールを搭載するLIMITED CTでは、ラインキャパシティを敢えて絞り込み、最大巻糸量に制限を掛けた。それは超軽量級、5gを下回るリグにも対応する優れた高回転性能を実現する“究極の高レスポンス化”のため他ならない。未曾有の低弾道性能を追い求めるトーナメンターたちへの挑戦でもある。フロロライン10lb.～13lb.を軸にバーサタイル域、時に6lb.～8lb.を用いてベイトフィネス域へと激変するシフトチェンジが魅力。さらにPEライン使用も想定し、ジグ撃ちや小型フロッグ、トップウォータープラグやカバー攻略などとの相性は更に極まる。敢えて制限を設けることで、より強烈に特化した低弾道キャストフィールは、CTコンセプトシリーズ随一の存在と成し得る。ライン放出を妨げないTWSには、24STEEZシリーズで新たに開発したテーパードTWSをインストール。従来サイズ以上の放出性能を手にすることで、トラブルなく圧倒的ライン放出性能を手にした。結果、軽いスイング、またスナップのみを活かしたコンパクトなキャストでも抜群の飛距離をマーク。無駄な動作を徹底排除、集中力を研ぎ澄まし、より繊細に、より多彩なアプローチで現代のタフなフィールドを迎え撃つ。中・近距離戦においてこれ以上ない正確無比な低弾道キャストを武器に、多くのベイトキャスターを魅了する。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N144" t="str">
-        <v/>
-      </c>
-      <c r="O144" t="str">
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="145" xml:space="preserve">
-      <c r="A145" t="str">
+    <row r="192" xml:space="preserve">
+      <c r="A192" t="str">
         <v>DRE5004</v>
       </c>
-      <c r="B145">
+      <c r="B192">
         <v>2</v>
       </c>
-      <c r="C145" t="str">
+      <c r="C192" t="str">
         <v>スティーズ SV ライト TW</v>
       </c>
-      <c r="D145" t="str">
-        <v/>
-      </c>
-      <c r="E145" t="str">
+      <c r="D192" t="str">
+        <v/>
+      </c>
+      <c r="E192" t="str">
         <v>2026</v>
       </c>
-      <c r="F145" t="str">
-        <v/>
-      </c>
-      <c r="G145" t="str">
-        <v/>
-      </c>
-      <c r="H145" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I145" t="str">
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I192" t="str">
         <v>images/daiwa_reels/スティーズ_SV_ライト_TW_main.jpg</v>
       </c>
-      <c r="J145" t="str">
+      <c r="J192" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K145" t="str">
+      <c r="K192" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L145" t="str">
-        <v/>
-      </c>
-      <c r="M145" t="str" xml:space="preserve">
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str" xml:space="preserve">
         <v xml:space="preserve">バスフィッシングに 本気で向き合う人々のために。バスフィッシングこそがライフスタイルの中核に位置するような、本気でバスに向き合う人々と共感できるプロダクトを。DAIWAが持つバスへの本気をプロダクトとメッセージで共有できるような、心の通ったブランドを目指した開発陣の秘めた想いを具現化したもの。そのために、DAIWAが持つ技術と想いでストイックに創り込む。ロッドだけではない、リールだけでもない、バスに立ち向かうためのすべてのものに想いをこめて。本気のバスアングラーの熱い想いと一緒に・・・それが「STEEZ」。
 スプールの高レスポンス化により、さらなる低弾道キャストと、キャストアキュラシーの向上を実現した26STEEZ SV LIGHT TW。ギア比は7.8とシリーズ最速となる9.2をラインナップ。ギア比7.8は撃ちと巻きの双方の釣りスタイルに対応したオールラウンダー。ギア比9.2は、ハンドル一回転あたり92cmという巻き取り量を確保し、手返しの良さだけでなく、糸ふけの素早い回収やカバーから魚を引きはがす際にも威力を発揮する。ラインガイドにはテーパーTWSを採用し、SV BOOSTとの相乗効果でキャスト後半の伸びをサポートする。複雑で高精度なキャストが要求されるハイプレッシャーフィールドでこそ真価を発揮する、究極のライトバーサタイルモデルが完成した。
 2018年、並木敏成監修の元、初のφ32ｍｍ SV LIGHTスプールを搭載したSV LIGHT LTDが誕生した。「ベイトフィネス機に近づけながらも、SVのアドバンテージが欲しい」そんな並木の思いを形にしたリールだ。いかなる状況でもバーサタイル性能があることはもちろんのこと、フィネス専用機並みのキャストフィールを実現させた。まさにBFとSVの両立だ。そこから8年、新たなφ32ｍｍ SV LIGHTスプールを搭載した26STEEZ SV LIGHT TWが誕生。キャスト後半の伸びを実現させるSV BOOST、新設計低イナーシャスプール、高いライン放出性能のテーパーTWS、これら全ての相乗効果により、オンリーワンのキャスト性能が更なる高みに昇華した。「フィネス寄りの軽量ルアーがまるで矢を刺すかのように低弾道で飛んで行く。ヤバいよねこのフィーリング。」並木も唸った。特徴は、キャストフィーリングだけではない。軽量ルアーへの対応力の向上だ。これまでベイトフィネス機種で行っていたような釣りを、太糸でも難なくこなすことができる。もちろん重量級ルアーへの対応力はそのままに。これぞ ”究極のライトバーサタイル” 26STEEZ SV LIGHT TWが提唱する、SV CONCEPT(スーパーバーサタイル)の新たな形だ。</v>
       </c>
-      <c r="N145" t="str">
-        <v/>
-      </c>
-      <c r="O145" t="str">
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="146" xml:space="preserve">
-      <c r="A146" t="str">
+    <row r="193" xml:space="preserve">
+      <c r="A193" t="str">
         <v>DRE5005</v>
       </c>
-      <c r="B146">
+      <c r="B193">
         <v>2</v>
       </c>
-      <c r="C146" t="str">
+      <c r="C193" t="str">
         <v>スティーズ SV TW100</v>
       </c>
-      <c r="D146" t="str">
-        <v/>
-      </c>
-      <c r="E146" t="str">
+      <c r="D193" t="str">
+        <v/>
+      </c>
+      <c r="E193" t="str">
         <v>2024</v>
       </c>
-      <c r="F146" t="str">
-        <v/>
-      </c>
-      <c r="G146" t="str">
-        <v/>
-      </c>
-      <c r="H146" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I146" t="str">
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I193" t="str">
         <v>images/daiwa_reels/スティーズ_SV_TW100_main.jpg</v>
       </c>
-      <c r="J146" t="str">
+      <c r="J193" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K146" t="str">
+      <c r="K193" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L146" t="str">
-        <v/>
-      </c>
-      <c r="M146" t="str" xml:space="preserve">
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str" xml:space="preserve">
         <v xml:space="preserve">バスフィッシングに 本気で向き合う人々のために。バスフィッシングこそがライフスタイルの中核に位置するような、本気でバスに向き合う人々と共感できるプロダクトを。DAIWAが持つバスへの本気をプロダクトとメッセージで共有できるような、心の通ったブランドを目指した開発陣の秘めた想いを具現化したもの。そのために、DAIWAが持つ技術と想いでストイックに創り込む。ロッドだけではない、リールだけでもない、バスに立ち向かうためのすべてのものに想いをこめて。本気のバスアングラーの熱い想いと一緒に・・・それが「STEEZ」。
 STEEZベイトリールは、スプール径が2mm刻みでラインナップされている。φ28mm（AIR）　φ30mm（CT）　φ34mm（LIMITED・AⅡ）　φ36mm（HLC）そのド真ん中に長らく開いていたΦ32mmの穴を埋めるザ・バーサタイル。次世代ベイト戦略の絵を完成させるマスターピースが、φ32mmのSV BOOSTスプールを積んだ第3世代STEEZ SV TWだ。この第三世代にはゼロアジャスター（旧メカニカルブレーキ）が存在しない。第二世代 16STEEZの時点で、すでにDAIWAリールはMAGFORCEダイヤルのみでブレーキ調整を完結していた。そして第3世代は、かつてメカニカルブレーキと呼ばれた機構を完全に取り除き、まったく新しいサブブレーキレス構造に生まれ変わっている。その高剛性かつコンパクトな筐体に“巻きと耐久性”を司るHYPERDRIVE DESIGNをインストール。投げの性能も大幅に向上しており、G1ジュラルミン製φ32mm SV BOOSTスプール、TWS、サブブレーキレスの各機構は、DAIWAが長年追い求め、ついに完成させた“投げの設計思想”ULTIMATECASTING DESIGNに準拠している。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N146" t="str">
-        <v/>
-      </c>
-      <c r="O146" t="str">
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="147" xml:space="preserve">
-      <c r="A147" t="str">
+    <row r="194" xml:space="preserve">
+      <c r="A194" t="str">
         <v>DRE5006</v>
       </c>
-      <c r="B147">
+      <c r="B194">
         <v>2</v>
       </c>
-      <c r="C147" t="str">
+      <c r="C194" t="str">
         <v>スティーズ AIR TW</v>
       </c>
-      <c r="D147" t="str">
-        <v/>
-      </c>
-      <c r="E147" t="str">
-        <v/>
-      </c>
-      <c r="F147" t="str">
-        <v/>
-      </c>
-      <c r="G147" t="str">
-        <v/>
-      </c>
-      <c r="H147" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I147" t="str">
-        <v/>
-      </c>
-      <c r="J147" t="str">
+      <c r="D194" t="str">
+        <v/>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K147" t="str">
+      <c r="K194" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L147" t="str">
-        <v/>
-      </c>
-      <c r="M147" t="str" xml:space="preserve">
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str" xml:space="preserve">
         <v xml:space="preserve">バスフィッシングに 本気で向き合う人々のために。バスフィッシングこそがライフスタイルの中核に位置するような、本気でバスに向き合う人々と共感できるプロダクトを。DAIWAが持つバスへの本気をプロダクトとメッセージで共有できるような、心の通ったブランドを目指した開発陣の秘めた想いを具現化したもの。そのために、DAIWAが持つ技術と想いでストイックに創り込む。ロッドだけではない、リールだけでもない、バスに立ち向かうためのすべてのものに想いをこめて。本気のバスアングラーの熱い想いと一緒に・・・それが「STEEZ」。
 フラッグシップ「STEEZ」、遂にベイトフィネス専用機が登場。フィネスを極める超小口径φ28mmG1ジュラルミン製AIRスプールを搭載。異次元の超小口径スプールは、今までのベイトフィネス機よりも軽いルアーへの対応力を増し、フィネスの概念を覆す。超高速に回転するスプール性能を最大限に生かすTWSシステム、コンパクトボディによる自重のメリットはまさに新次元のベイトフィネス機としての歴史を変えるだろう。※淡水専用
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N147" t="str">
-        <v/>
-      </c>
-      <c r="O147" t="str">
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="148" xml:space="preserve">
-      <c r="A148" t="str">
+    <row r="195" xml:space="preserve">
+      <c r="A195" t="str">
         <v>DRE5007</v>
       </c>
-      <c r="B148">
+      <c r="B195">
         <v>2</v>
       </c>
-      <c r="C148" t="str">
+      <c r="C195" t="str">
         <v>リョウガ</v>
       </c>
-      <c r="D148" t="str">
-        <v/>
-      </c>
-      <c r="E148" t="str">
+      <c r="D195" t="str">
+        <v/>
+      </c>
+      <c r="E195" t="str">
         <v>2026</v>
       </c>
-      <c r="F148" t="str">
-        <v/>
-      </c>
-      <c r="G148" t="str">
-        <v/>
-      </c>
-      <c r="H148" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I148" t="str">
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I195" t="str">
         <v>images/daiwa_reels/リョウガ_main.jpg</v>
       </c>
-      <c r="J148" t="str">
+      <c r="J195" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K148" t="str">
+      <c r="K195" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L148" t="str">
-        <v/>
-      </c>
-      <c r="M148" t="str" xml:space="preserve">
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str" xml:space="preserve">
         <v xml:space="preserve">HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る
@@ -7385,100 +9712,100 @@
 HYPER DOUBLE SUPPORT
                                                                     滑らかさの持続と､巻きの強さ･軽さを実現した駆動サポートシステム｡ピニオンギアの両端を2つのボールベアリングで高精度に支持することで､ハンドルからの入力を減衰せず､負荷が掛かった時でも力強く､軽く巻上げることを可能にしました｡</v>
       </c>
-      <c r="N148" t="str">
-        <v/>
-      </c>
-      <c r="O148" t="str">
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="149" xml:space="preserve">
-      <c r="A149" t="str">
+    <row r="196" xml:space="preserve">
+      <c r="A196" t="str">
         <v>DRE5008</v>
       </c>
-      <c r="B149">
+      <c r="B196">
         <v>2</v>
       </c>
-      <c r="C149" t="str">
+      <c r="C196" t="str">
         <v>スティーズ CT SV TW</v>
       </c>
-      <c r="D149" t="str">
-        <v/>
-      </c>
-      <c r="E149" t="str">
-        <v/>
-      </c>
-      <c r="F149" t="str">
-        <v/>
-      </c>
-      <c r="G149" t="str">
-        <v/>
-      </c>
-      <c r="H149" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I149" t="str">
-        <v/>
-      </c>
-      <c r="J149" t="str">
+      <c r="D196" t="str">
+        <v/>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K149" t="str">
+      <c r="K196" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L149" t="str">
-        <v/>
-      </c>
-      <c r="M149" t="str" xml:space="preserve">
+      <c r="L196" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str" xml:space="preserve">
         <v xml:space="preserve">バスフィッシングに 本気で向き合う人々のために。バスフィッシングこそがライフスタイルの中核に位置するような、本気でバスに向き合う人々と共感できるプロダクトを。DAIWAが持つバスへの本気をプロダクトとメッセージで共有できるような、心の通ったブランドを目指した開発陣の秘めた想いを具現化したもの。そのために、DAIWAが持つ技術と想いでストイックに創り込む。ロッドだけではない、リールだけでもない、バスに立ち向かうためのすべてのものに想いをこめて。本気のバスアングラーの熱い想いと一緒に・・・それが「STEEZ」。
 CT（COMPACT＆TOUGH）、新たなコンセプトでSTEEZが更なる進化を遂げた。コンパクトボディ、そしてφ30mmのG1ジュラルミン製CT SVスプールを搭載。初速の立ち上がりが抜群なCT SVスプールはバーサタイル性能はもちろん、フィネス性能の領域までをカバーし、今までを凌駕するキャストフィールを実現している。STEEZ SV TWから継承している滑らかな巻き心地はG1ジュラルミンマシンカットドライブギアの賜物。そして、700サイズのスプールに合わせた新型「TWS」は「SV CONCEPT」と相乗効果を発揮し驚異のアキュラシー性能を実現する。CT SVが新たなバーサタイルスタイルを提唱する。
 2016年、スティーズ新世代を象徴するバーサタイルモデルのSVが誕生。圧倒的な軽さに加え、さらなる遠投性能とトラブルレス性を備えた極限スペックが世の耳目を集めたことは記憶に新しい。翌2017年、タフコンセプトを掲げ登場したのはA。スーパーメタルハウジングによる確かな剛性感、太糸に対応して激務を全うする堅牢性はスティーズが躍動する新たなシーンを開拓した。そして2019年、いよいよ第3のスティーズベイトリール・CT SVが産声を上げる。既存2モデルとは一線を画すフル新型のコンパクトボディには、超小型高性能エンジンを積み込み使用ルアーの幅を大きく拡大。現代バスアングラーが求める真実の回答、現場のリアルに応えた次世代バーサタイル機がそこにある。CT＝コンパクト&amp;タフ。新機を象徴するのは、実に30φmmとDAIWA史上最小となる超小口径のCT SVスプールだ。軽量ルアーからビッグベイト級まで、おおよそ考え得るベイトタックルでの釣りはオリジナルのSVが既に網羅。次なるCT SVが目指したのはさらなる超軽量級、5gを下回るリグにも対応する優れた高回転性能。もはやベイトフィネス機と遜色ないばかりか、スピニングに迫る領域まで到達している。素材にはG1ジュラルミンを採用。高い剛性と軽量化を両立しながらも、存分な肉厚を持たせることで強度を確保。もはや脆弱さに不安はない。10～14lb.を軸にバーサタイル域、時に6～8lb.を用いてベイトフィネス域へとシフトが可能。さらにはPEラインでヘビーカバーへと挑むことも想定内。実戦上で必要十分な10lb.×80mの枠内で、あらゆるシーンに挑むことが可能となる。超小口径30φmmと存分な強度を誇るCTSVスプールが実現するのは、既存2モデルに搭載された34Φを遥かに凌ぐ高回転力。超軽量リグでも立ち上がりに優れ、瞬時にトップスピードへと到達。ライン放出を妨げないTWSとの相乗効果で、トラブルなくスムーズな飛びを実現。軽いスイング、またスナップのみを活かしたコンパクトなキャストでも抜群の飛距離をマーク。スキルを要するバックハンドやフリップキャストも即時のマスターへと後押ししそうだ。ギア比は6.3の700H と8.1の700XH 。ハンドル1回転で59cmと76cm、巻きと撃ち、それぞれを完遂すべく2モデルを揃えた。より繊細に、より多彩なアプローチで現代のタフなフィールドを迎え撃つ準備はこれで整った。</v>
       </c>
-      <c r="N149" t="str">
-        <v/>
-      </c>
-      <c r="O149" t="str">
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="150" xml:space="preserve">
-      <c r="A150" t="str">
+    <row r="197" xml:space="preserve">
+      <c r="A197" t="str">
         <v>DRE5009</v>
       </c>
-      <c r="B150">
+      <c r="B197">
         <v>2</v>
       </c>
-      <c r="C150" t="str">
+      <c r="C197" t="str">
         <v>ジリオン TW HD</v>
       </c>
-      <c r="D150" t="str">
-        <v/>
-      </c>
-      <c r="E150" t="str">
+      <c r="D197" t="str">
+        <v/>
+      </c>
+      <c r="E197" t="str">
         <v>2022</v>
       </c>
-      <c r="F150" t="str">
-        <v/>
-      </c>
-      <c r="G150" t="str">
-        <v/>
-      </c>
-      <c r="H150" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I150" t="str">
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I197" t="str">
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_tw_hd_22/__icsFiles/afieldfile/2022/04/08/main.jpg?rev=dd8848fe936e4b268b8bdb9e4b33a4df</v>
       </c>
-      <c r="J150" t="str">
+      <c r="J197" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K150" t="str">
+      <c r="K197" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L150" t="str">
-        <v/>
-      </c>
-      <c r="M150" t="str" xml:space="preserve">
+      <c r="L197" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str" xml:space="preserve">
         <v xml:space="preserve">高強度真鍮をドライブギアに、そして、高耐食銅合金をピニオンギアに採用した新たなHYPERDRIVE DIGIGEAR搭載で、強く滑らかな回転を実現し、HYPER ARMED HOUSING（FULL AL）でコンパクトながら、強靭なボディ剛性を実現。新開発Φ34mmG1ジュラルミン製超高精度MAG-Z BOOSTスプールを搭載し、ロングキャスト性能を極める。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
@@ -7486,51 +9813,51 @@
 HYPERDRIVE DIGIGEAR
                                                                     強く滑らかな回転が持続し続けることを追求した新設計のギアシステム｡耐久性に直結するギアの歯のモジュール（大きさ）は小さくせず噛合い率アップを達成したことにより､初期の滑らかさが長く続くことを実現したDAIWA独自のテクノロジーです｡</v>
       </c>
-      <c r="N150" t="str">
-        <v/>
-      </c>
-      <c r="O150" t="str">
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="151" xml:space="preserve">
-      <c r="A151" t="str">
+    <row r="198" xml:space="preserve">
+      <c r="A198" t="str">
         <v>DRE5010</v>
       </c>
-      <c r="B151">
+      <c r="B198">
         <v>2</v>
       </c>
-      <c r="C151" t="str">
+      <c r="C198" t="str">
         <v>月下美人 BF TW PE SP</v>
       </c>
-      <c r="D151" t="str">
-        <v/>
-      </c>
-      <c r="E151" t="str">
+      <c r="D198" t="str">
+        <v/>
+      </c>
+      <c r="E198" t="str">
         <v>2026</v>
       </c>
-      <c r="F151" t="str">
-        <v/>
-      </c>
-      <c r="G151" t="str">
-        <v/>
-      </c>
-      <c r="H151" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I151" t="str">
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I198" t="str">
         <v>images/daiwa_reels/月下美人_BF_TW_PE_SP_main.jpg</v>
       </c>
-      <c r="J151" t="str">
+      <c r="J198" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K151" t="str">
+      <c r="K198" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L151" t="str">
-        <v/>
-      </c>
-      <c r="M151" t="str" xml:space="preserve">
+      <c r="L198" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str" xml:space="preserve">
         <v xml:space="preserve">夜に咲く花は、輝きを増し続ける。2005年、DAIWAのラインナップに初めて登場したライトソルトゲーム専用タックル『月下美人』。艶やかに咲くその花のように月下美人は舞い、アングラーは躍動する。身近なターゲットでありながら、時には極めて繊細なアプローチを必要とするアジや、岩陰や藻の切れ目に身を隠し、周囲を警戒しながらベイトが近くに現れるのを待ち続ける老獪な大型メバルを相手に進化してきた月下美人タックル。これからも月下美人は、アングラーと共に進化し、これまでに味わったことのないような悦び、楽しみを提供する。月下美人の艶やかな輝きがライトソルトゲームを照らし続ける。
 TWS（T-WING SYSTEM）
                                                                     TWSは､スプール回転数が一番上がるスプール至近のラインガイドでの抵抗を大幅に削減することに成功しました。飛距離への抵抗部分を減らすことにより､従来以上の飛距離・コントロール性の向上に加え､フォールも速くバックラッシュを減少することができます。巻き取り時だけではない、キャスト時の新たなレベルワインドの可能性を実現したのです。
@@ -7538,101 +9865,101 @@
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N151" t="str">
-        <v/>
-      </c>
-      <c r="O151" t="str">
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="152" xml:space="preserve">
-      <c r="A152" t="str">
+    <row r="199" xml:space="preserve">
+      <c r="A199" t="str">
         <v>DRE5011</v>
       </c>
-      <c r="B152">
+      <c r="B199">
         <v>2</v>
       </c>
-      <c r="C152" t="str">
+      <c r="C199" t="str">
         <v>モアザン PE TW</v>
       </c>
-      <c r="D152" t="str">
-        <v/>
-      </c>
-      <c r="E152" t="str">
-        <v/>
-      </c>
-      <c r="F152" t="str">
-        <v/>
-      </c>
-      <c r="G152" t="str">
-        <v/>
-      </c>
-      <c r="H152" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I152" t="str">
-        <v/>
-      </c>
-      <c r="J152" t="str">
+      <c r="D199" t="str">
+        <v/>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K152" t="str">
+      <c r="K199" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L152" t="str">
-        <v/>
-      </c>
-      <c r="M152" t="str" xml:space="preserve">
+      <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str" xml:space="preserve">
         <v xml:space="preserve">もっと遠くへ、もっと楽しく、もっと釣るために。シーバス。日本各地に生息し、海水域から汽水域まで様々なフィールドに生息するこの魚は、獰猛・繊細・大胆、様々な性格を見せ、アングラーを困惑させ、魅了する。「morethan」はこの魅力あるシーバスと対峙し、その魅力を最大に味わうために生まれた。爽快にキャストし、ルアーを想いのままに操り、シーバスの気配やアタリを明快にキャッチし、引き寄せる。そのためのあらゆるタックルを総合プロデュースするブランドmorethan。専用であるからこそ見える世界が存在する。
 シーバス専用ベイトリールとして高い評価を受けるmorethan PE。ボディだけでなく、両サイドもアルミ化したことで、非常に高い剛性を獲得。力強く安定した巻き上げにより、流れの変化も明確に手元に伝えるのはもちろん、引き重りするルアーも軽快にリトリーブできるうえ、大物をグイグイ引き寄せる。パーミングしやすいコンパクトボディと、力強い巻上げをサポートする100mmのロングハンドルが、剛性をさらに実感させる。ブレーキにおいてもPEでバックラッシュさせない守りの設定から、極限まで飛ばす、後半も伸びる攻めの設定に変更。鉄板系バイブレーションの遠投から、ミノーなどのピンスポットキャストまで、そのポテンシャルに隙はない。※ハンドルノブS交換可※ソルト対応
 MAGSEALED BALL BEARING
                                                                     DAIWAは独自の技術で、世界で初めてボールベアリングそのものをマグシールド化することに成功しました。磁性を持つ液体の壁によって、ボールベアリング内部への水・異物の侵入が抑えられ、ボールベアリング本来の回転性能を維持しながら、錆・塩ガミ・異音を大幅に解消します。</v>
       </c>
-      <c r="N152" t="str">
-        <v/>
-      </c>
-      <c r="O152" t="str">
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="153" xml:space="preserve">
-      <c r="A153" t="str">
+    <row r="200" xml:space="preserve">
+      <c r="A200" t="str">
         <v>DRE5012</v>
       </c>
-      <c r="B153">
+      <c r="B200">
         <v>2</v>
       </c>
-      <c r="C153" t="str">
+      <c r="C200" t="str">
         <v>シルバーウルフ CT SV TW　PE SPECIAL</v>
       </c>
-      <c r="D153" t="str">
-        <v/>
-      </c>
-      <c r="E153" t="str">
-        <v/>
-      </c>
-      <c r="F153" t="str">
-        <v/>
-      </c>
-      <c r="G153" t="str">
-        <v/>
-      </c>
-      <c r="H153" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I153" t="str">
+      <c r="D200" t="str">
+        <v/>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I200" t="str">
         <v>images/daiwa_reels/シルバーウルフ_CT_SV_TW_PE_SPECIAL_main.jpg</v>
       </c>
-      <c r="J153" t="str">
+      <c r="J200" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K153" t="str">
+      <c r="K200" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L153" t="str">
-        <v/>
-      </c>
-      <c r="M153" t="str" xml:space="preserve">
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str" xml:space="preserve">
         <v xml:space="preserve">HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る
@@ -7641,151 +9968,151 @@
 HYPER DOUBLE SUPPORT
                                                                     滑らかさの持続と､巻きの強さ･軽さを実現した駆動サポートシステム｡ピニオンギアの両端を2つのボールベアリングで高精度に支持することで､ハンドルからの入力を減衰せず､負荷が掛かった時でも力強く､軽く巻上げることを可能にしました｡</v>
       </c>
-      <c r="N153" t="str">
-        <v/>
-      </c>
-      <c r="O153" t="str">
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="154" xml:space="preserve">
-      <c r="A154" t="str">
+    <row r="201" xml:space="preserve">
+      <c r="A201" t="str">
         <v>DRE5013</v>
       </c>
-      <c r="B154">
+      <c r="B201">
         <v>2</v>
       </c>
-      <c r="C154" t="str">
+      <c r="C201" t="str">
         <v>スティーズ A II TW</v>
       </c>
-      <c r="D154" t="str">
-        <v/>
-      </c>
-      <c r="E154" t="str">
-        <v/>
-      </c>
-      <c r="F154" t="str">
-        <v/>
-      </c>
-      <c r="G154" t="str">
-        <v/>
-      </c>
-      <c r="H154" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I154" t="str">
-        <v/>
-      </c>
-      <c r="J154" t="str">
+      <c r="D201" t="str">
+        <v/>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K154" t="str">
+      <c r="K201" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L154" t="str">
-        <v/>
-      </c>
-      <c r="M154" t="str" xml:space="preserve">
+      <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str" xml:space="preserve">
         <v xml:space="preserve">バスフィッシングに 本気で向き合う人々のために。バスフィッシングこそがライフスタイルの中核に位置するような、本気でバスに向き合う人々と共感できるプロダクトを。DAIWAが持つバスへの本気をプロダクトとメッセージで共有できるような、心の通ったブランドを目指した開発陣の秘めた想いを具現化したもの。そのために、DAIWAが持つ技術と想いでストイックに創り込む。ロッドだけではない、リールだけでもない、バスに立ち向かうためのすべてのものに想いをこめて。本気のバスアングラーの熱い想いと一緒に・・・それが「STEEZ」。
 多くの人にタフさと安定感のある巻きをお届けしてきた、STEEZ A TWが第2世代へと進化を遂げる。アメリカのタフなトーナメントトレイルで培ったタフさに、次世代ベイトリールの設計思想「HYPERDRIVE DESIGN」で完全武装。アングラーの手に馴染んできたHYPER ARMED HOUSING（FULL-AL）の堅牢さはそのままに、HYPERDRIVE DIGIGEARが回転性能をさらに磨き込み、高負荷でも滑らかかつハイパワーな巻きを実現。高い耐久性能も無論、備えている。　STEEZ A II TWには、新開発φ34mmG1ジュラルミン製超高精度MAG-Z BOOSTスプールを搭載。浅溝化により”必要なライン量だけ”をストックすることでスプールトータルウェイトを軽量化。結果、スプールの立ち上がりが向上し、タフフィールドで必要とされる実践的なキャスト性能が魅力の1台と仕上がった。　確かな巻きをアシストするハイグリップIシェイプラージノブ（Sノブタイプ）と新設計の90mmAL製ハンドル。またスタードラグさえもAL化を施して、ドラグ調整&amp;ドラグ引き出しクリックやMAGSEALEDボールベアリングも標準装備。バスのみならず、ソルトにも盤石のタフ遠投モデル“STEEZ A II TW“。現代アングラーの求める真回答がそこに凝縮されている。
 STEEZ A II TWでは、巻きのみならず、飛びの革命にも果敢に挑んだ。超軽量かつ高剛性のG1マテリアル、Φ34mmのスプール径は先代と共通だが、新たにメスを入れたのはスプールの糸巻き面、いわゆる浅溝化。そしてブレーキユニットの刷新だ。　絞り込まれたラインキャパシティは、14lb.-100m/16lb.-90m。これまでの基幹ベイトリールの代名詞とも言える16lb.-100mをわずかに下回るその数字。太糸を存分にストックしながらも、従来比マイナス10メートルとは何を意味するのか。そこには現代シーンが求める真の回答が存在する。　スプールの自重は軽ければ軽いほどに回転性能とレスポンスを高めていくのが真理だ。タフな現代を戦い抜くには、魚との直接の接点となるラインをより絞り込むことでスプール全体の自重を軽量化することもまた真理だ。1尾と出会う確率をより高めるには、全てがスムーズかつトラブルレス、そして遠投性能だけでなく低弾道で撃ち込める精度の高さが求められる。　だとするならば、スプールに収納するラインは実戦上で必要十分なストックがあれば良い。16lb.×10m分を犠牲にした新たなスプールは、糸を巻いた状態でのスプールユニット単位で、従来比約5%の軽量化をマーク。キャストフィールをさらに向上すべく、贅肉のない現代仕様の高レスポンススプールへと仕上がった。　一方、飛距離の要となるブレーキユニットには、MAG-Z BOOSTという傑物を組み込んだ。中重量級ルアーと高相性のMAGFORCE-Zを起源とする、遠投性能を極限まで引き出した飛距離重視のセッティング。2段階インダクトローターは、バックラッシュゾーンを回避した後、瞬時に1段階戻ることでキャストの中盤から着水間際まで淀みなく飛距離を伸ばしていく。大開口部を備えたレベルワインド・TWSとの相乗効果で、未知のゾーンへと踏み込むことを可能にしている。　優れた遠投性能は、誰もが思い描く理想のポテンシャル。魚との距離を縮めることは、単純にバイトチャンスの確立を高めることに直結する。またアングラーの気配を消してプレッシャーや違和感を与えず、魚本来の素直なバイトも期待できる。フルキャストは無論だが、ショートピッチのキャストでも最後のひと伸びで明らかな差を生み出すことに繋げるだろう。</v>
       </c>
-      <c r="N154" t="str">
-        <v/>
-      </c>
-      <c r="O154" t="str">
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="155" xml:space="preserve">
-      <c r="A155" t="str">
+    <row r="202" xml:space="preserve">
+      <c r="A202" t="str">
         <v>DRE5014</v>
       </c>
-      <c r="B155">
+      <c r="B202">
         <v>2</v>
       </c>
-      <c r="C155" t="str">
+      <c r="C202" t="str">
         <v>スティーズ A TW HLC</v>
       </c>
-      <c r="D155" t="str">
-        <v/>
-      </c>
-      <c r="E155" t="str">
-        <v/>
-      </c>
-      <c r="F155" t="str">
-        <v/>
-      </c>
-      <c r="G155" t="str">
-        <v/>
-      </c>
-      <c r="H155" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I155" t="str">
-        <v/>
-      </c>
-      <c r="J155" t="str">
+      <c r="D202" t="str">
+        <v/>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K155" t="str">
+      <c r="K202" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L155" t="str">
-        <v/>
-      </c>
-      <c r="M155" t="str" xml:space="preserve">
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str" xml:space="preserve">
         <v xml:space="preserve">バスフィッシングに 本気で向き合う人々のために。バスフィッシングこそがライフスタイルの中核に位置するような、本気でバスに向き合う人々と共感できるプロダクトを。DAIWAが持つバスへの本気をプロダクトとメッセージで共有できるような、心の通ったブランドを目指した開発陣の秘めた想いを具現化したもの。そのために、DAIWAが持つ技術と想いでストイックに創り込む。ロッドだけではない、リールだけでもない、バスに立ち向かうためのすべてのものに想いをこめて。本気のバスアングラーの熱い想いと一緒に・・・それが「STEEZ」。
 遠投性を極めたスティーズ A TW HLC に待望のエクストラハイスピードモデルが追加。「HYPERDRIVE DESIGN」による初期性能が永く続くことを目指した設計思想の次世代ベイトリールが登場。HYPERDRIVE DIGIGEAR搭載で、強度UPと回転フィーリングUPを実現し、HYPER ARMED HOUSING（Al）でコンパクトながら、強靭なボディ剛性を実現。タフで堅牢で好評のSTEEZ Aモデルを更に遠投性能に磨きをかけスプールφ36mmMAG-Z BOOSTスプールを搭載。BOOST機構により、更なる遠投性能を手に入れたSTEEZのフラッグシップブランドの遠投リールを提案する。ハンドルノブS 交換可。ソルト対応。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N155" t="str">
-        <v/>
-      </c>
-      <c r="O155" t="str">
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="156" xml:space="preserve">
-      <c r="A156" t="str">
+    <row r="203" xml:space="preserve">
+      <c r="A203" t="str">
         <v>DRE5015</v>
       </c>
-      <c r="B156">
+      <c r="B203">
         <v>2</v>
       </c>
-      <c r="C156" t="str">
+      <c r="C203" t="str">
         <v>HRF TW PE SP</v>
       </c>
-      <c r="D156" t="str">
-        <v/>
-      </c>
-      <c r="E156" t="str">
+      <c r="D203" t="str">
+        <v/>
+      </c>
+      <c r="E203" t="str">
         <v>2025</v>
       </c>
-      <c r="F156" t="str">
-        <v/>
-      </c>
-      <c r="G156" t="str">
-        <v/>
-      </c>
-      <c r="H156" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I156" t="str">
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I203" t="str">
         <v>images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
       </c>
-      <c r="J156" t="str">
+      <c r="J203" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K156" t="str">
+      <c r="K203" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L156" t="str">
-        <v/>
-      </c>
-      <c r="M156" t="str" xml:space="preserve">
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str" xml:space="preserve">
         <v xml:space="preserve">HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る
@@ -7794,151 +10121,151 @@
 HYPER DOUBLE SUPPORT
                                                                     滑らかさの持続と､巻きの強さ･軽さを実現した駆動サポートシステム｡ピニオンギアの両端を2つのボールベアリングで高精度に支持することで､ハンドルからの入力を減衰せず､負荷が掛かった時でも力強く､軽く巻上げることを可能にしました｡</v>
       </c>
-      <c r="N156" t="str">
-        <v/>
-      </c>
-      <c r="O156" t="str">
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="157" xml:space="preserve">
-      <c r="A157" t="str">
+    <row r="204" xml:space="preserve">
+      <c r="A204" t="str">
         <v>DRE5016</v>
       </c>
-      <c r="B157">
+      <c r="B204">
         <v>2</v>
       </c>
-      <c r="C157" t="str">
+      <c r="C204" t="str">
         <v>シルバーウルフ SV TW PE SPECIAL</v>
       </c>
-      <c r="D157" t="str">
-        <v/>
-      </c>
-      <c r="E157" t="str">
-        <v/>
-      </c>
-      <c r="F157" t="str">
-        <v/>
-      </c>
-      <c r="G157" t="str">
-        <v/>
-      </c>
-      <c r="H157" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I157" t="str">
+      <c r="D204" t="str">
+        <v/>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I204" t="str">
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/salt_rl/silverwolf_sv_tw/__icsFiles/artimage/2022/04/01/c_041110017/main_tx_im01_1.jpg?rev=6d195f85744643bda6ef194759f4c436</v>
       </c>
-      <c r="J157" t="str">
+      <c r="J204" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K157" t="str">
+      <c r="K204" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L157" t="str">
-        <v/>
-      </c>
-      <c r="M157" t="str" xml:space="preserve">
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str" xml:space="preserve">
         <v xml:space="preserve">チニングアングラー待望のPE対応力。圧倒的なアドバンテージを秘めたベイトリール。チヌは警戒心が強く、敏感だ。当たり前のことだが、ラインは細く、飛距離が出るほうがチヌから気づかれにくくて有利だ。また、細いラインは水の抵抗が減るので、流れに対してもアドバンテージとなる。フリーリグ（通称：フリリグ）が押し流されにくいので水流抵抗によるリグの不本意な動きを減らすばかりか、シンカーを軽くできることによる根がかり防止効果とナチュラルなルアーアクションによって、より自然に釣りを展開することができる。であれば、従来のスピニングタックルがいいか。答えは否。最新のチニングは面を巻くように探り、ハイレスポンスでかけていく釣り。手返しや感度、応答性においてベイトタックルが断然有利なのだ。しかし、これらの恩恵を受けられるのは細いPEという特殊なシチュエーションでもバックラッシュや高切れといったトラブルを誘発しないベイトリールだけ。チニングを極めるには、これまでになかった領域を開拓する新兵器が必須となる。
 安心で爽快なキャストフィールでチニングアングラーをソルトキャスティングゲームの高みへ誘う0.8号、0.6号といったPEラインの先に、時には20gを超えるルアーを付けてフルキャストする。きっと、経験が豊富なアングラーほど思いっきり振り抜くのをためらうだろう。その先には、高切れによるルアーロスや、酷いライントラブルが待ちうけることとなるからだ。SILVER WOLF SV TW PE SPECIALは圧倒的なライン放出を実現するTWSと、0.8号以下のPEラインの使用を前提に専用設計されたPE専用SV BOOSTスプールの組み合わせによって、未開の域に到達。細糸PEラインでもトラブルレスかつキャスト後半には伸びのある飛びを実現した。SILVER WOLFと細やかな操作が必要なフリリグが、新たなチニングを築く。
 「巻き」から得られる感動をいつまでもラインを細くするとラインが水流を切ることでラインの弛みが減少し、感度が上がる。そこに加わるのが滑らかなリトリーブ性能だ。ボトムを手元で鮮明に感じられるので地形変化や地質変化を的確に読み取り、次のステップへと釣りが展開される。情報量が増え、戦略が明確化するからだ。さらに、チヌがかかれば強い巻上げ力を発揮。滑らかで強いHYPERDRIVE DESIGNは新スタイルのチニングに理想的なカードなのだ。</v>
       </c>
-      <c r="N157" t="str">
-        <v/>
-      </c>
-      <c r="O157" t="str">
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="158" xml:space="preserve">
-      <c r="A158" t="str">
+    <row r="205" xml:space="preserve">
+      <c r="A205" t="str">
         <v>DRE5017</v>
       </c>
-      <c r="B158">
+      <c r="B205">
         <v>2</v>
       </c>
-      <c r="C158" t="str">
+      <c r="C205" t="str">
         <v>シルバークリーク エア TW ストリームカスタム</v>
       </c>
-      <c r="D158" t="str">
-        <v/>
-      </c>
-      <c r="E158" t="str">
-        <v/>
-      </c>
-      <c r="F158" t="str">
-        <v/>
-      </c>
-      <c r="G158" t="str">
-        <v/>
-      </c>
-      <c r="H158" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I158" t="str">
+      <c r="D205" t="str">
+        <v/>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I205" t="str">
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/silvercreek_air_tw_sc/__icsFiles/artimage/2022/03/29/c_041101086/main_tx_im01_3.jpg?rev=d0db4f46700344e7893e0f732daf59a2</v>
       </c>
-      <c r="J158" t="str">
+      <c r="J205" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K158" t="str">
+      <c r="K205" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L158" t="str">
-        <v/>
-      </c>
-      <c r="M158" t="str" xml:space="preserve">
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str" xml:space="preserve">
         <v xml:space="preserve">Φ28mmG1ジュラルミン製ストリームトラウトブレーキチューンスプール搭載（インダクトローター固定式）により、安定したブレーキ力を発揮。渓流でのピンポイント攻略においてアキュラシー向上！
 渓流～源流域の釣りにおいては、変化に富んだポイント攻略において、変則的なフォームでのキャスト、入力が一定で無いキャストの頻度が高い。通常のAIRブレーキシステムでは、ショートキャストでのルアーのリリースから着水までの短い時間の中で、インダクトローターの作動が起こる。超ショートキャストや極めて小さい入力のキャストでは、インダクトローターは作動しないことが起こったりする。 このように、アングラーの実際のイメージとインダクトローターの作動にズレが生まれ、キャストアキュラシーのバラつきを生む。その様なストレスを解消する為、ストリームトラウトブレーキチューンは、インダクトローターを固定し、 微弱な一定のブレーキをかける精度の高いポイント攻略とトラブルの少ない快適な釣りを実現する。※推奨巻糸量でのPEラインにてブレーキセッティングを施した渓流ベイトフィネス専用機。　ナイロンラインやフロロカーボンラインも使用できるブレーキセッティングになっています。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N158" t="str">
-        <v/>
-      </c>
-      <c r="O158" t="str">
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="159" xml:space="preserve">
-      <c r="A159" t="str">
+    <row r="206" xml:space="preserve">
+      <c r="A206" t="str">
         <v>DRE5018</v>
       </c>
-      <c r="B159">
+      <c r="B206">
         <v>2</v>
       </c>
-      <c r="C159" t="str">
+      <c r="C206" t="str">
         <v>SS AIR TW</v>
       </c>
-      <c r="D159" t="str">
-        <v/>
-      </c>
-      <c r="E159" t="str">
-        <v/>
-      </c>
-      <c r="F159" t="str">
-        <v/>
-      </c>
-      <c r="G159" t="str">
-        <v/>
-      </c>
-      <c r="H159" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I159" t="str">
-        <v/>
-      </c>
-      <c r="J159" t="str">
+      <c r="D206" t="str">
+        <v/>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K159" t="str">
+      <c r="K206" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L159" t="str">
-        <v/>
-      </c>
-      <c r="M159" t="str" xml:space="preserve">
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str" xml:space="preserve">
         <v xml:space="preserve">10年目の跳躍進化10年ぶりに新生を果たしたベイトフィネス機の雄“SS AIR TW”。ブラック×レッドの精悍な佇まいを継承したコンパクトボディに、全く新しい発想から生まれたブレーキシステム“SS MAGFORCE”と、近年好評を得ているDAIWAテクノロジーを搭載。10年の進化がたしかに感じられる、DAIWAベイトフィネスリールの革命機がここに誕生した。進化は、大きく2点。新たに開発したブレーキシステム“SS MAGFORCE”によるかつてないキャスタビリティと、TWSやHYPERDRIVE DESIGNの標準搭載による基本性能の底上げだ。新たなブレーキシステムは、キャスタビリティの向上にとどまらず、ボディのコンパクト化にも寄与している。そのボディデザインとブレーキセッティングにはベイトフィネスの父・K.T.F.代表の沢村幸弘氏が参画。ベイトフィネスを実践する釣り場において最も重要な、ピッチングとキャスティングの両立を高いレベルで実現している。特筆すべきは、コンパクトなフォルムから放たれる極めてストレスのない安定したキャスタビリティ。マグネットブレーキを長年磨き続けてきたDAIWAと、日々最前線の現場を見つめる沢村氏との相乗効果によって辿り着いた新境地といえる。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
@@ -7946,51 +10273,51 @@
 HYPERDRIVE DIGIGEAR
                                                                     強く滑らかな回転が持続し続けることを追求した新設計のギアシステム｡耐久性に直結するギアの歯のモジュール（大きさ）は小さくせず噛合い率アップを達成したことにより､初期の滑らかさが長く続くことを実現したDAIWA独自のテクノロジーです｡</v>
       </c>
-      <c r="N159" t="str">
-        <v/>
-      </c>
-      <c r="O159" t="str">
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="160" xml:space="preserve">
-      <c r="A160" t="str">
+    <row r="207" xml:space="preserve">
+      <c r="A207" t="str">
         <v>DRE5019</v>
       </c>
-      <c r="B160">
+      <c r="B207">
         <v>2</v>
       </c>
-      <c r="C160" t="str">
+      <c r="C207" t="str">
         <v>アルファスBF TW</v>
       </c>
-      <c r="D160" t="str">
-        <v/>
-      </c>
-      <c r="E160" t="str">
+      <c r="D207" t="str">
+        <v/>
+      </c>
+      <c r="E207" t="str">
         <v>2025</v>
       </c>
-      <c r="F160" t="str">
-        <v/>
-      </c>
-      <c r="G160" t="str">
-        <v/>
-      </c>
-      <c r="H160" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I160" t="str">
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I207" t="str">
         <v>images/daiwa_reels/アルファスBF_TW_main.jpg</v>
       </c>
-      <c r="J160" t="str">
+      <c r="J207" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K160" t="str">
+      <c r="K207" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L160" t="str">
-        <v/>
-      </c>
-      <c r="M160" t="str" xml:space="preserve">
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str" xml:space="preserve">
         <v xml:space="preserve">HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る
@@ -7999,102 +10326,102 @@
 HYPER DOUBLE SUPPORT
                                                                     滑らかさの持続と､巻きの強さ･軽さを実現した駆動サポートシステム｡ピニオンギアの両端を2つのボールベアリングで高精度に支持することで､ハンドルからの入力を減衰せず､負荷が掛かった時でも力強く､軽く巻上げることを可能にしました｡</v>
       </c>
-      <c r="N160" t="str">
-        <v/>
-      </c>
-      <c r="O160" t="str">
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="161" xml:space="preserve">
-      <c r="A161" t="str">
+    <row r="208" xml:space="preserve">
+      <c r="A208" t="str">
         <v>DRE5020</v>
       </c>
-      <c r="B161">
+      <c r="B208">
         <v>2</v>
       </c>
-      <c r="C161" t="str">
+      <c r="C208" t="str">
         <v>ZILLION SV TW</v>
       </c>
-      <c r="D161" t="str">
-        <v/>
-      </c>
-      <c r="E161" t="str">
+      <c r="D208" t="str">
+        <v/>
+      </c>
+      <c r="E208" t="str">
         <v>2021</v>
       </c>
-      <c r="F161" t="str">
-        <v/>
-      </c>
-      <c r="G161" t="str">
-        <v/>
-      </c>
-      <c r="H161" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I161" t="str">
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I208" t="str">
         <v>https://390386bd-1bf0-4900-aa10-cac1793c9a23-afd-dqdkdpcqgcc6hahm.z01.azurefd.net/-/media/Project/globeride/daiwa_com_jp/resources/fishing/item/reel/bait_rl/zillion_sv_tw21/__icsFiles/artimage/2022/05/02/c_041101076/main_bg02_1.jpg?rev=eb0a7bf7b3584f528da16f4584f37003</v>
       </c>
-      <c r="J161" t="str">
+      <c r="J208" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K161" t="str">
+      <c r="K208" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L161" t="str">
-        <v/>
-      </c>
-      <c r="M161" t="str" xml:space="preserve">
+      <c r="L208" t="str">
+        <v/>
+      </c>
+      <c r="M208" t="str" xml:space="preserve">
         <v xml:space="preserve">2021年、無限の可能性を秘めたZILLIONの新章が開幕。100万を意味するmillion、10億のbillionでもない。形而上の途方もない数字、いわば無限を象徴するその称号にもはや偽りはない。ハードワークに耐えるタフモデルのレガシーは受け継ぎ、インサイドとアウトサイド共にすべての機能が出力無尽蔵。そのすべてがブーストアップを遂げることに成功した。もはやすべての基準を塗り替えたと言ってもいい。NEW ZILLION、今こそ雄弁に語れ。
 我々DAIWAWORKSが両軸リールに求めること、それをひとことで表すなら“ユーザビリティ”に尽きる。すべてのアングラーが乗りこなすことができるマシンは、結果を裏切ることはない。たとえ想定外のシーンに直面したとしても、出力を限界まで引き出すことができる安心のスペックとは耐久性能、回転性能、そして操作性能の3本柱。それらすべてがシンクロして可能となるものだ。これまでDAIWAは他より突出したテクノロジーのみを訴求して、付随する優れた機能の数々は、複雑化を避けるべく敢えて開示することはなかった。2021年、DAIWAは技術と経験が何よりの武器であることを改めて謳う。NEW ZILLION登場を機に、DAIWAテクノロジーのすべてをグローバルに公開することにした。
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る</v>
       </c>
-      <c r="N161" t="str">
-        <v/>
-      </c>
-      <c r="O161" t="str">
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="162" xml:space="preserve">
-      <c r="A162" t="str">
+    <row r="209" xml:space="preserve">
+      <c r="A209" t="str">
         <v>DRE5021</v>
       </c>
-      <c r="B162">
+      <c r="B209">
         <v>2</v>
       </c>
-      <c r="C162" t="str">
+      <c r="C209" t="str">
         <v>ソルティスト TW PE SPECIAL</v>
       </c>
-      <c r="D162" t="str">
-        <v/>
-      </c>
-      <c r="E162" t="str">
+      <c r="D209" t="str">
+        <v/>
+      </c>
+      <c r="E209" t="str">
         <v>2023</v>
       </c>
-      <c r="F162" t="str">
-        <v/>
-      </c>
-      <c r="G162" t="str">
-        <v/>
-      </c>
-      <c r="H162" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I162" t="str">
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I209" t="str">
         <v>images/daiwa_reels/ソルティスト_TW_PE_SPECIAL_main.jpg</v>
       </c>
-      <c r="J162" t="str">
+      <c r="J209" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K162" t="str">
+      <c r="K209" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L162" t="str">
-        <v/>
-      </c>
-      <c r="M162" t="str" xml:space="preserve">
+      <c r="L209" t="str">
+        <v/>
+      </c>
+      <c r="M209" t="str" xml:space="preserve">
         <v xml:space="preserve">SALTIST TW PE SPはソルトでのPEベイトキャスティングに特化させることで、トラブル無く使用できることを目指した。これまでベイトリールでのPEラインの使用に抵抗があったアングラーでも安心して「振り切る」ことが可能。それを実現させたのがライン放出性が極めて高い「TWS」と、糸巻き状態を大幅に改善しPE専用のセッティングを施した「PE専用スプール」。さらに基本性能を「HYPERDRIVE DESIGN」で磨きをかけ、ソルトでの幅広いシーンにも対応する。サイズはBF/80/100/150/300/400で展開し、ソルト領域のより幅広い魚種に対応することが可能。これからPEベイトキャスティングを楽しみたいユーザーやPE対応力を求めるユーザーに向けたSWベイトキャスティングリールのニュースタンダード。※ソルト対応
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
@@ -8102,151 +10429,151 @@
 HYPERDRIVE DIGIGEAR
                                                                     強く滑らかな回転が持続し続けることを追求した新設計のギアシステム｡耐久性に直結するギアの歯のモジュール（大きさ）は小さくせず噛合い率アップを達成したことにより､初期の滑らかさが長く続くことを実現したDAIWA独自のテクノロジーです｡</v>
       </c>
-      <c r="N162" t="str">
-        <v/>
-      </c>
-      <c r="O162" t="str">
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="163" xml:space="preserve">
-      <c r="A163" t="str">
+    <row r="210" xml:space="preserve">
+      <c r="A210" t="str">
         <v>DRE5022</v>
       </c>
-      <c r="B163">
+      <c r="B210">
         <v>2</v>
       </c>
-      <c r="C163" t="str">
+      <c r="C210" t="str">
         <v>TATULA TW 300/400</v>
       </c>
-      <c r="D163" t="str">
-        <v/>
-      </c>
-      <c r="E163" t="str">
-        <v/>
-      </c>
-      <c r="F163" t="str">
-        <v/>
-      </c>
-      <c r="G163" t="str">
-        <v/>
-      </c>
-      <c r="H163" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I163" t="str">
-        <v/>
-      </c>
-      <c r="J163" t="str">
+      <c r="D210" t="str">
+        <v/>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
+      <c r="J210" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K163" t="str">
+      <c r="K210" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L163" t="str">
-        <v/>
-      </c>
-      <c r="M163" t="str" xml:space="preserve">
+      <c r="L210" t="str">
+        <v/>
+      </c>
+      <c r="M210" t="str" xml:space="preserve">
         <v xml:space="preserve">「HYPERDRIVE DESIGN」による初期性能が長く続くことを目指した設計思想の次世代ベイトリール。滑らかな回転が持続するHYPERDRIVE DIGIGEAR搭載。HYPER ARMED HOUSING、ギアとスプールを強く高精度で支持。Φ43ｍｍ超々ジュラルミンマグフォーススプール搭載。
 HYPERDRIVE DIGIGEAR
                                                                     強く滑らかな回転が持続し続けることを追求した新設計のギアシステム｡耐久性に直結するギアの歯のモジュール（大きさ）は小さくせず噛合い率アップを達成したことにより､初期の滑らかさが長く続くことを実現したDAIWA独自のテクノロジーです｡
 HYPER DOUBLE SUPPORT
                                                                     滑らかさの持続と､巻きの強さ･軽さを実現した駆動サポートシステム｡ピニオンギアの両端を2つのボールベアリングで高精度に支持することで､ハンドルからの入力を減衰せず､負荷が掛かった時でも力強く､軽く巻上げることを可能にしました｡</v>
       </c>
-      <c r="N163" t="str">
-        <v/>
-      </c>
-      <c r="O163" t="str">
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="164" xml:space="preserve">
-      <c r="A164" t="str">
+    <row r="211" xml:space="preserve">
+      <c r="A211" t="str">
         <v>DRE5023</v>
       </c>
-      <c r="B164">
+      <c r="B211">
         <v>2</v>
       </c>
-      <c r="C164" t="str">
+      <c r="C211" t="str">
         <v>アルファス SV TW</v>
       </c>
-      <c r="D164" t="str">
-        <v/>
-      </c>
-      <c r="E164" t="str">
+      <c r="D211" t="str">
+        <v/>
+      </c>
+      <c r="E211" t="str">
         <v>2021</v>
       </c>
-      <c r="F164" t="str">
-        <v/>
-      </c>
-      <c r="G164" t="str">
-        <v/>
-      </c>
-      <c r="H164" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I164" t="str">
-        <v/>
-      </c>
-      <c r="J164" t="str">
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K164" t="str">
+      <c r="K211" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L164" t="str">
-        <v/>
-      </c>
-      <c r="M164" t="str" xml:space="preserve">
+      <c r="L211" t="str">
+        <v/>
+      </c>
+      <c r="M211" t="str" xml:space="preserve">
         <v xml:space="preserve">アルファスフル新型 TWS&amp;SVスプール搭載機登場！HYPERDRIVEデザインによる初期性能が永く続くことを目指した設計思想の次世代ベイトリールが登場。HYPERDRIVEデジギア搭載で、強度UPと回転フィーリングUPを実現し、HYPER ARMED HOUSING（Al）でコンパクトながら、強靭なボディ剛性を実現。キャストアキュラシーもスプールφ32mmSVスプールを搭載し、軽量ルアーから幅広いルアーウエイトに対応。ソルト対応とし、様々な釣種に対応することはもちろんコアアングラーからビギナーまで、使いやすさはALPHASシリーズの特徴を継承している。ソルト対応。
 Φ32mm超々ジュラルミン製SVシャロースプールの開発・搭載で、フィネス領域から太糸を使用したカバーのパワーフィッシングまで対応。スプールレスポンス向上と、ALPHASならではのコンパクトフォルムによりキャストの入力を上げずともコンパクトスイングでキャストが決まる。低弾道キャストはもちろん、高いキャストアキュラシーにより、ピンスポットを正確に撃ち抜くことが可能となる。
 新たに開発したギア比8.5。ハイパードライブデジギアで、巻きの耐久性も兼ね備えたハイスペック。（ギア比7.1もラインナップ）</v>
       </c>
-      <c r="N164" t="str">
-        <v/>
-      </c>
-      <c r="O164" t="str">
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="165" xml:space="preserve">
-      <c r="A165" t="str">
+    <row r="212" xml:space="preserve">
+      <c r="A212" t="str">
         <v>DRE5024</v>
       </c>
-      <c r="B165">
+      <c r="B212">
         <v>2</v>
       </c>
-      <c r="C165" t="str">
+      <c r="C212" t="str">
         <v>タトゥーラ BF TW</v>
       </c>
-      <c r="D165" t="str">
-        <v/>
-      </c>
-      <c r="E165" t="str">
+      <c r="D212" t="str">
+        <v/>
+      </c>
+      <c r="E212" t="str">
         <v>2026</v>
       </c>
-      <c r="F165" t="str">
-        <v/>
-      </c>
-      <c r="G165" t="str">
-        <v/>
-      </c>
-      <c r="H165" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I165" t="str">
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I212" t="str">
         <v>images/daiwa_reels/タトゥーラ_BF_TW_main.jpg</v>
       </c>
-      <c r="J165" t="str">
+      <c r="J212" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K165" t="str">
+      <c r="K212" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L165" t="str">
-        <v/>
-      </c>
-      <c r="M165" t="str" xml:space="preserve">
+      <c r="L212" t="str">
+        <v/>
+      </c>
+      <c r="M212" t="str" xml:space="preserve">
         <v xml:space="preserve">HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る
@@ -8255,51 +10582,51 @@
 HYPER ARMED HOUSING
                                                                     内部構造を高剛性､高精度でしっかりと支え､精緻な巻き心地とパワーを生む筐体システム｡要であるフレームに金属素材を用いることが必要条件で､サイドプレートやセットプレートとの組合せにより､基本性能をさらに長く発揮し続けることを可能にします｡</v>
       </c>
-      <c r="N165" t="str">
-        <v/>
-      </c>
-      <c r="O165" t="str">
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="166" xml:space="preserve">
-      <c r="A166" t="str">
+    <row r="213" xml:space="preserve">
+      <c r="A213" t="str">
         <v>DRE5025</v>
       </c>
-      <c r="B166">
+      <c r="B213">
         <v>2</v>
       </c>
-      <c r="C166" t="str">
+      <c r="C213" t="str">
         <v>タトゥーラ TW 200</v>
       </c>
-      <c r="D166" t="str">
-        <v/>
-      </c>
-      <c r="E166" t="str">
+      <c r="D213" t="str">
+        <v/>
+      </c>
+      <c r="E213" t="str">
         <v>2025</v>
       </c>
-      <c r="F166" t="str">
-        <v/>
-      </c>
-      <c r="G166" t="str">
-        <v/>
-      </c>
-      <c r="H166" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I166" t="str">
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I213" t="str">
         <v>images/daiwa_reels/タトゥーラ_TW_200_main.jpg</v>
       </c>
-      <c r="J166" t="str">
+      <c r="J213" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K166" t="str">
+      <c r="K213" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L166" t="str">
-        <v/>
-      </c>
-      <c r="M166" t="str" xml:space="preserve">
+      <c r="L213" t="str">
+        <v/>
+      </c>
+      <c r="M213" t="str" xml:space="preserve">
         <v xml:space="preserve">HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
                                                 詳しく見る
@@ -8309,51 +10636,51 @@
                                                                     内部構造を高剛性､高精度でしっかりと支え､精緻な巻き心地とパワーを生む筐体システム｡要であるフレームに金属素材を用いることが必要条件で､サイドプレートやセットプレートとの組合せにより､基本性能をさらに長く発揮し続けることを可能にします｡
                                                                         本モデルは、フレーム・ギア側サイドプレートにALを採用しており、パワーゲームに対応したタフなハウジング仕様を実現。</v>
       </c>
-      <c r="N166" t="str">
-        <v/>
-      </c>
-      <c r="O166" t="str">
+      <c r="N213" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="167" xml:space="preserve">
-      <c r="A167" t="str">
+    <row r="214" xml:space="preserve">
+      <c r="A214" t="str">
         <v>DRE5026</v>
       </c>
-      <c r="B167">
+      <c r="B214">
         <v>2</v>
       </c>
-      <c r="C167" t="str">
+      <c r="C214" t="str">
         <v>タトゥーラ SV TW</v>
       </c>
-      <c r="D167" t="str">
-        <v/>
-      </c>
-      <c r="E167" t="str">
+      <c r="D214" t="str">
+        <v/>
+      </c>
+      <c r="E214" t="str">
         <v>2025</v>
       </c>
-      <c r="F167" t="str">
-        <v/>
-      </c>
-      <c r="G167" t="str">
-        <v/>
-      </c>
-      <c r="H167" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I167" t="str">
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I214" t="str">
         <v>images/daiwa_reels/タトゥーラ_SV_TW_main.jpg</v>
       </c>
-      <c r="J167" t="str">
+      <c r="J214" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K167" t="str">
+      <c r="K214" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L167" t="str">
-        <v/>
-      </c>
-      <c r="M167" t="str" xml:space="preserve">
+      <c r="L214" t="str">
+        <v/>
+      </c>
+      <c r="M214" t="str" xml:space="preserve">
         <v xml:space="preserve">TATULA第3世代の次世代ワールドスタンダードモデル。セーフティーさと後半の伸びを両立するスーパーバーサタイルリール。高い基本性能を磨き込み、巻上げ性能も大幅UP。TATULAシリーズの核であるタフコンセプト踏襲！
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
@@ -8361,51 +10688,51 @@
 HYPERDRIVE DIGIGEAR
                                                                     強く滑らかな回転が持続し続けることを追求した新設計のギアシステム｡耐久性に直結するギアの歯のモジュール（大きさ）は小さくせず噛合い率アップを達成したことにより､初期の滑らかさが長く続くことを実現したDAIWA独自のテクノロジーです｡</v>
       </c>
-      <c r="N167" t="str">
-        <v/>
-      </c>
-      <c r="O167" t="str">
+      <c r="N214" t="str">
+        <v/>
+      </c>
+      <c r="O214" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="168" xml:space="preserve">
-      <c r="A168" t="str">
+    <row r="215" xml:space="preserve">
+      <c r="A215" t="str">
         <v>DRE5027</v>
       </c>
-      <c r="B168">
+      <c r="B215">
         <v>2</v>
       </c>
-      <c r="C168" t="str">
+      <c r="C215" t="str">
         <v>タトゥーラ TW 100</v>
       </c>
-      <c r="D168" t="str">
-        <v/>
-      </c>
-      <c r="E168" t="str">
+      <c r="D215" t="str">
+        <v/>
+      </c>
+      <c r="E215" t="str">
         <v>2024</v>
       </c>
-      <c r="F168" t="str">
-        <v/>
-      </c>
-      <c r="G168" t="str">
-        <v/>
-      </c>
-      <c r="H168" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I168" t="str">
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v/>
+      </c>
+      <c r="H215" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I215" t="str">
         <v>images/daiwa_reels/タトゥーラ_TW_100_main.jpg</v>
       </c>
-      <c r="J168" t="str">
+      <c r="J215" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K168" t="str">
+      <c r="K215" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L168" t="str">
-        <v/>
-      </c>
-      <c r="M168" t="str" xml:space="preserve">
+      <c r="L215" t="str">
+        <v/>
+      </c>
+      <c r="M215" t="str" xml:space="preserve">
         <v xml:space="preserve">TATULA TW 100シリーズに「ＨＹＰＥＲＤＲＩＶＥ　ＤＥＳＩＧＮ」を初搭載した新型TATULAデビュー！TATULAシリーズの核であるタフコンセプト ＆ 高い基本性能を磨き込み、 基本性能大幅UP！グローバルで「HYPERDRIVE DESIGN」 を展開・注力したモデル！※ソルト対応
 HYPERDRIVE DESIGN
                                                                     高い初期性能が長く続くことを目指し､全ての基本性能の水準を大幅に高めたベイト(両軸)リールにおける次世代の設計思想｡ ハイパードライブデザインは､最大4つのテクノロジーで構成されています｡ 滑らかな回転が長く持続するハイパードライブデジギアの搭載を必要条件とし､ギアの駆動を援けて強く軽い巻上げをもたらすハイパーダブルサポート。内部構造を強く支持し､撓みにくく歪みづらいハイパーアームドハウジング。過酷なロケーションでも作動し続け､塩ガミによる固着を激減させた絶縁構造のハイパータフクラッチ。これらの相乗効果で､あらゆるフィールドにおいて安定した性能を発揮し続けます｡
@@ -8413,960 +10740,960 @@
 HYPERDRIVE DIGIGEAR
                                                                     強く滑らかな回転が持続し続けることを追求した新設計のギアシステム｡耐久性に直結するギアの歯のモジュール（大きさ）は小さくせず噛合い率アップを達成したことにより､初期の滑らかさが長く続くことを実現したDAIWA独自のテクノロジーです｡</v>
       </c>
-      <c r="N168" t="str">
-        <v/>
-      </c>
-      <c r="O168" t="str">
+      <c r="N215" t="str">
+        <v/>
+      </c>
+      <c r="O215" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="169" xml:space="preserve">
-      <c r="A169" t="str">
+    <row r="216" xml:space="preserve">
+      <c r="A216" t="str">
         <v>DRE5028</v>
       </c>
-      <c r="B169">
+      <c r="B216">
         <v>2</v>
       </c>
-      <c r="C169" t="str">
+      <c r="C216" t="str">
         <v>バス  X  100</v>
       </c>
-      <c r="D169" t="str">
-        <v/>
-      </c>
-      <c r="E169" t="str">
+      <c r="D216" t="str">
+        <v/>
+      </c>
+      <c r="E216" t="str">
         <v>2024</v>
       </c>
-      <c r="F169" t="str">
-        <v/>
-      </c>
-      <c r="G169" t="str">
-        <v/>
-      </c>
-      <c r="H169" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I169" t="str">
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+      <c r="H216" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I216" t="str">
         <v>images/daiwa_reels/バス__X__100_main.jpg</v>
       </c>
-      <c r="J169" t="str">
+      <c r="J216" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K169" t="str">
+      <c r="K216" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L169" t="str">
-        <v/>
-      </c>
-      <c r="M169" t="str" xml:space="preserve">
+      <c r="L216" t="str">
+        <v/>
+      </c>
+      <c r="M216" t="str" xml:space="preserve">
         <v xml:space="preserve">高級感溢れる外観にてリニューアル。「誰でも使い易い！」 安心の基本性能を満たしたハイバリューベイト。スプール形状をアルミ製φ32ｍｍスプールへ変更し巻糸量を確保。MAGFORCE、90ｍｍアルミクランクハンドル+フラットタイプハイグリップノブ、4BB+1RB搭載。右ハンドルモデル＆左ハンドルモデル展開。ソルト対応モデル。
 ２トーンカラーにて、外観美にも拘ったモデル。基本性能を満たしたハイバリューベイト。「誰でも使い易い！」オールラウンダーモデル。
 スプール形状を変更し、巻糸量確保。＃100にリニューアルし、巻糸量は12lb－120m、14lb-110mに。アルミ製Φ32ｍｍスプール搭載。　立ち上がりが良く、ブランキング（穴あけ）効果で軽量化とスプール回転性能アップ。</v>
       </c>
-      <c r="N169" t="str">
-        <v/>
-      </c>
-      <c r="O169" t="str">
+      <c r="N216" t="str">
+        <v/>
+      </c>
+      <c r="O216" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="170" xml:space="preserve">
-      <c r="A170" t="str">
+    <row r="217" xml:space="preserve">
+      <c r="A217" t="str">
         <v>DRE5029</v>
       </c>
-      <c r="B170">
+      <c r="B217">
         <v>2</v>
       </c>
-      <c r="C170" t="str">
+      <c r="C217" t="str">
         <v>PR100</v>
       </c>
-      <c r="D170" t="str">
-        <v/>
-      </c>
-      <c r="E170" t="str">
-        <v/>
-      </c>
-      <c r="F170" t="str">
-        <v/>
-      </c>
-      <c r="G170" t="str">
-        <v/>
-      </c>
-      <c r="H170" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I170" t="str">
-        <v/>
-      </c>
-      <c r="J170" t="str">
+      <c r="D217" t="str">
+        <v/>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+      <c r="H217" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
+      <c r="J217" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="K170" t="str">
+      <c r="K217" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
       </c>
-      <c r="L170" t="str">
-        <v/>
-      </c>
-      <c r="M170" t="str" xml:space="preserve">
+      <c r="L217" t="str">
+        <v/>
+      </c>
+      <c r="M217" t="str" xml:space="preserve">
         <v xml:space="preserve">入門～中級者用ベイトリールの決定版。バスだけでなくソルト使用時でも安心。船の小物釣りもバッチリ。アルミ製φ32mmスプール搭載。立ち上がりが良い、アルミスプール搭載で回転性能アップ。3.5号糸付モデル（右モデル、ギア比6.3のみ）もラインナップ。※ソルト対応
 基本性能がしっかりしたベイト。回転が良く、軽量で扱い易いモデル。"誰でも使い易い！"オールラウンダーモデル。
 立ち上がりが良い、アルミスプール搭載で回転性能アップ。14lb-110m。鮮やかなレッド色スプールで外観でもアピール！</v>
       </c>
-      <c r="N170" t="str">
-        <v/>
-      </c>
-      <c r="O170" t="str">
+      <c r="N217" t="str">
+        <v/>
+      </c>
+      <c r="O217" t="str">
         <v>On Sale</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="str">
+    <row r="218">
+      <c r="A218" t="str">
         <v>MRE5000</v>
       </c>
-      <c r="B171">
+      <c r="B218">
         <v>7</v>
       </c>
-      <c r="C171" t="str">
+      <c r="C218" t="str">
         <v>GAUS 20X</v>
       </c>
-      <c r="D171" t="str">
+      <c r="D218" t="str">
         <v>GAUS 20X</v>
       </c>
-      <c r="E171" t="str">
-        <v/>
-      </c>
-      <c r="F171" t="str">
-        <v/>
-      </c>
-      <c r="G171" t="str">
-        <v/>
-      </c>
-      <c r="H171" t="str">
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+      <c r="H218" t="str">
         <v>spinning</v>
       </c>
-      <c r="I171" t="str">
+      <c r="I218" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 20X_main.jpg</v>
       </c>
-      <c r="J171" t="str">
+      <c r="J218" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
       </c>
-      <c r="K171" t="str">
+      <c r="K218" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
       </c>
-      <c r="L171" t="str">
-        <v/>
-      </c>
-      <c r="M171" t="str">
-        <v/>
-      </c>
-      <c r="N171" t="str">
-        <v/>
-      </c>
-      <c r="O171" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
+      <c r="L218" t="str">
+        <v/>
+      </c>
+      <c r="M218" t="str">
+        <v/>
+      </c>
+      <c r="N218" t="str">
+        <v/>
+      </c>
+      <c r="O218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
         <v>MRE5001</v>
       </c>
-      <c r="B172">
+      <c r="B219">
         <v>7</v>
       </c>
-      <c r="C172" t="str">
+      <c r="C219" t="str">
         <v>GAUS 30X</v>
       </c>
-      <c r="D172" t="str">
+      <c r="D219" t="str">
         <v>GAUS 30X</v>
       </c>
-      <c r="E172" t="str">
-        <v/>
-      </c>
-      <c r="F172" t="str">
-        <v/>
-      </c>
-      <c r="G172" t="str">
-        <v/>
-      </c>
-      <c r="H172" t="str">
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v/>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+      <c r="H219" t="str">
         <v>spinning</v>
       </c>
-      <c r="I172" t="str">
+      <c r="I219" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 30X_main.jpg</v>
       </c>
-      <c r="J172" t="str">
+      <c r="J219" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
       </c>
-      <c r="K172" t="str">
+      <c r="K219" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
       </c>
-      <c r="L172" t="str">
-        <v/>
-      </c>
-      <c r="M172" t="str">
-        <v/>
-      </c>
-      <c r="N172" t="str">
-        <v/>
-      </c>
-      <c r="O172" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
+      <c r="L219" t="str">
+        <v/>
+      </c>
+      <c r="M219" t="str">
+        <v/>
+      </c>
+      <c r="N219" t="str">
+        <v/>
+      </c>
+      <c r="O219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
         <v>MRE5002</v>
       </c>
-      <c r="B173">
+      <c r="B220">
         <v>7</v>
       </c>
-      <c r="C173" t="str">
+      <c r="C220" t="str">
         <v>LIN258HM</v>
       </c>
-      <c r="D173" t="str">
+      <c r="D220" t="str">
         <v>LIN258HM</v>
       </c>
-      <c r="E173" t="str">
-        <v/>
-      </c>
-      <c r="F173" t="str">
-        <v/>
-      </c>
-      <c r="G173" t="str">
-        <v/>
-      </c>
-      <c r="H173" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I173" t="str">
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+      <c r="H220" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I220" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/LIN258HM_main.jpg</v>
       </c>
-      <c r="J173" t="str">
+      <c r="J220" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
       </c>
-      <c r="K173" t="str">
+      <c r="K220" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
       </c>
-      <c r="L173" t="str">
-        <v/>
-      </c>
-      <c r="M173" t="str">
-        <v/>
-      </c>
-      <c r="N173" t="str">
-        <v/>
-      </c>
-      <c r="O173" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
+      <c r="L220" t="str">
+        <v/>
+      </c>
+      <c r="M220" t="str">
+        <v/>
+      </c>
+      <c r="N220" t="str">
+        <v/>
+      </c>
+      <c r="O220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
         <v>MRE5003</v>
       </c>
-      <c r="B174">
+      <c r="B221">
         <v>7</v>
       </c>
-      <c r="C174" t="str">
+      <c r="C221" t="str">
         <v>RC-IDATEN 256</v>
       </c>
-      <c r="D174" t="str">
+      <c r="D221" t="str">
         <v>RC-IDATEN 256</v>
       </c>
-      <c r="E174" t="str">
-        <v/>
-      </c>
-      <c r="F174" t="str">
-        <v/>
-      </c>
-      <c r="G174" t="str">
-        <v/>
-      </c>
-      <c r="H174" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I174" t="str">
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+      <c r="H221" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I221" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/RC-IDATEN 256_main.jpg</v>
       </c>
-      <c r="J174" t="str">
+      <c r="J221" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
       </c>
-      <c r="K174" t="str">
+      <c r="K221" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
       </c>
-      <c r="L174" t="str">
-        <v/>
-      </c>
-      <c r="M174" t="str">
-        <v/>
-      </c>
-      <c r="N174" t="str">
-        <v/>
-      </c>
-      <c r="O174" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
+      <c r="L221" t="str">
+        <v/>
+      </c>
+      <c r="M221" t="str">
+        <v/>
+      </c>
+      <c r="N221" t="str">
+        <v/>
+      </c>
+      <c r="O221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
         <v>MRE5004</v>
       </c>
-      <c r="B175">
+      <c r="B222">
         <v>7</v>
       </c>
-      <c r="C175" t="str">
+      <c r="C222" t="str">
         <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
-      <c r="D175" t="str">
+      <c r="D222" t="str">
         <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
-      <c r="E175" t="str">
-        <v/>
-      </c>
-      <c r="F175" t="str">
-        <v/>
-      </c>
-      <c r="G175" t="str">
-        <v/>
-      </c>
-      <c r="H175" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I175" t="str">
+      <c r="E222" t="str">
+        <v/>
+      </c>
+      <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v/>
+      </c>
+      <c r="H222" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I222" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE GRIGIO STONE_main.jpg</v>
       </c>
-      <c r="J175" t="str">
+      <c r="J222" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
       </c>
-      <c r="K175" t="str">
+      <c r="K222" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
       </c>
-      <c r="L175" t="str">
-        <v/>
-      </c>
-      <c r="M175" t="str">
-        <v/>
-      </c>
-      <c r="N175" t="str">
-        <v/>
-      </c>
-      <c r="O175" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
+      <c r="L222" t="str">
+        <v/>
+      </c>
+      <c r="M222" t="str">
+        <v/>
+      </c>
+      <c r="N222" t="str">
+        <v/>
+      </c>
+      <c r="O222" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
         <v>MRE5005</v>
       </c>
-      <c r="B176">
+      <c r="B223">
         <v>7</v>
       </c>
-      <c r="C176" t="str">
+      <c r="C223" t="str">
         <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
-      <c r="D176" t="str">
+      <c r="D223" t="str">
         <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
-      <c r="E176" t="str">
-        <v/>
-      </c>
-      <c r="F176" t="str">
-        <v/>
-      </c>
-      <c r="G176" t="str">
-        <v/>
-      </c>
-      <c r="H176" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I176" t="str">
+      <c r="E223" t="str">
+        <v/>
+      </c>
+      <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+      <c r="H223" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I223" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE ITO-GAMBLER_main.jpg</v>
       </c>
-      <c r="J176" t="str">
+      <c r="J223" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
       </c>
-      <c r="K176" t="str">
+      <c r="K223" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
       </c>
-      <c r="L176" t="str">
-        <v/>
-      </c>
-      <c r="M176" t="str">
-        <v/>
-      </c>
-      <c r="N176" t="str">
-        <v/>
-      </c>
-      <c r="O176" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
+      <c r="L223" t="str">
+        <v/>
+      </c>
+      <c r="M223" t="str">
+        <v/>
+      </c>
+      <c r="N223" t="str">
+        <v/>
+      </c>
+      <c r="O223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
         <v>MRE5006</v>
       </c>
-      <c r="B177">
+      <c r="B224">
         <v>7</v>
       </c>
-      <c r="C177" t="str">
+      <c r="C224" t="str">
         <v>MONOBLOCK SPECIALE</v>
       </c>
-      <c r="D177" t="str">
+      <c r="D224" t="str">
         <v>MONOBLOCK SPECIALE</v>
       </c>
-      <c r="E177" t="str">
-        <v/>
-      </c>
-      <c r="F177" t="str">
-        <v/>
-      </c>
-      <c r="G177" t="str">
-        <v/>
-      </c>
-      <c r="H177" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I177" t="str">
+      <c r="E224" t="str">
+        <v/>
+      </c>
+      <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+      <c r="H224" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I224" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE_main.jpg</v>
       </c>
-      <c r="J177" t="str">
+      <c r="J224" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
       </c>
-      <c r="K177" t="str">
+      <c r="K224" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
       </c>
-      <c r="L177" t="str">
-        <v/>
-      </c>
-      <c r="M177" t="str">
-        <v/>
-      </c>
-      <c r="N177" t="str">
-        <v/>
-      </c>
-      <c r="O177" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
+      <c r="L224" t="str">
+        <v/>
+      </c>
+      <c r="M224" t="str">
+        <v/>
+      </c>
+      <c r="N224" t="str">
+        <v/>
+      </c>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
         <v>MRE5007</v>
       </c>
-      <c r="B178">
+      <c r="B225">
         <v>7</v>
       </c>
-      <c r="C178" t="str">
+      <c r="C225" t="str">
         <v>RHODIUM 73</v>
       </c>
-      <c r="D178" t="str">
+      <c r="D225" t="str">
         <v>RHODIUM 73</v>
       </c>
-      <c r="E178" t="str">
-        <v/>
-      </c>
-      <c r="F178" t="str">
-        <v/>
-      </c>
-      <c r="G178" t="str">
-        <v/>
-      </c>
-      <c r="H178" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I178" t="str">
+      <c r="E225" t="str">
+        <v/>
+      </c>
+      <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+      <c r="H225" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I225" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 73_main.jpg</v>
       </c>
-      <c r="J178" t="str">
+      <c r="J225" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
       </c>
-      <c r="K178" t="str">
+      <c r="K225" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
       </c>
-      <c r="L178" t="str">
-        <v/>
-      </c>
-      <c r="M178" t="str">
-        <v/>
-      </c>
-      <c r="N178" t="str">
-        <v/>
-      </c>
-      <c r="O178" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
+      <c r="L225" t="str">
+        <v/>
+      </c>
+      <c r="M225" t="str">
+        <v/>
+      </c>
+      <c r="N225" t="str">
+        <v/>
+      </c>
+      <c r="O225" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
         <v>MRE5008</v>
       </c>
-      <c r="B179">
+      <c r="B226">
         <v>7</v>
       </c>
-      <c r="C179" t="str">
+      <c r="C226" t="str">
         <v>RHODIUM 81</v>
       </c>
-      <c r="D179" t="str">
+      <c r="D226" t="str">
         <v>RHODIUM 81</v>
       </c>
-      <c r="E179" t="str">
-        <v/>
-      </c>
-      <c r="F179" t="str">
-        <v/>
-      </c>
-      <c r="G179" t="str">
-        <v/>
-      </c>
-      <c r="H179" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I179" t="str">
+      <c r="E226" t="str">
+        <v/>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v/>
+      </c>
+      <c r="H226" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I226" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 81_main.jpg</v>
       </c>
-      <c r="J179" t="str">
+      <c r="J226" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
       </c>
-      <c r="K179" t="str">
+      <c r="K226" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
       </c>
-      <c r="L179" t="str">
-        <v/>
-      </c>
-      <c r="M179" t="str">
-        <v/>
-      </c>
-      <c r="N179" t="str">
-        <v/>
-      </c>
-      <c r="O179" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
+      <c r="L226" t="str">
+        <v/>
+      </c>
+      <c r="M226" t="str">
+        <v/>
+      </c>
+      <c r="N226" t="str">
+        <v/>
+      </c>
+      <c r="O226" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
         <v>MRE5009</v>
       </c>
-      <c r="B180">
+      <c r="B227">
         <v>7</v>
       </c>
-      <c r="C180" t="str">
+      <c r="C227" t="str">
         <v>RHODIUM 63</v>
       </c>
-      <c r="D180" t="str">
+      <c r="D227" t="str">
         <v>RHODIUM 63</v>
       </c>
-      <c r="E180" t="str">
-        <v/>
-      </c>
-      <c r="F180" t="str">
-        <v/>
-      </c>
-      <c r="G180" t="str">
-        <v/>
-      </c>
-      <c r="H180" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I180" t="str">
+      <c r="E227" t="str">
+        <v/>
+      </c>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+      <c r="H227" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I227" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 63_main.jpg</v>
       </c>
-      <c r="J180" t="str">
+      <c r="J227" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
       </c>
-      <c r="K180" t="str">
+      <c r="K227" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
       </c>
-      <c r="L180" t="str">
-        <v/>
-      </c>
-      <c r="M180" t="str">
-        <v/>
-      </c>
-      <c r="N180" t="str">
-        <v/>
-      </c>
-      <c r="O180" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
+      <c r="L227" t="str">
+        <v/>
+      </c>
+      <c r="M227" t="str">
+        <v/>
+      </c>
+      <c r="N227" t="str">
+        <v/>
+      </c>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
         <v>MRE5010</v>
       </c>
-      <c r="B181">
+      <c r="B228">
         <v>7</v>
       </c>
-      <c r="C181" t="str">
+      <c r="C228" t="str">
         <v>Pagani R100</v>
       </c>
-      <c r="D181" t="str">
+      <c r="D228" t="str">
         <v>Pagani R100</v>
       </c>
-      <c r="E181" t="str">
-        <v/>
-      </c>
-      <c r="F181" t="str">
-        <v/>
-      </c>
-      <c r="G181" t="str">
-        <v/>
-      </c>
-      <c r="H181" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I181" t="str">
+      <c r="E228" t="str">
+        <v/>
+      </c>
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+      <c r="H228" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I228" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/Pagani R100_main.jpg</v>
       </c>
-      <c r="J181" t="str">
+      <c r="J228" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
       </c>
-      <c r="K181" t="str">
+      <c r="K228" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
       </c>
-      <c r="L181" t="str">
-        <v/>
-      </c>
-      <c r="M181" t="str">
-        <v/>
-      </c>
-      <c r="N181" t="str">
-        <v/>
-      </c>
-      <c r="O181" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
+      <c r="L228" t="str">
+        <v/>
+      </c>
+      <c r="M228" t="str">
+        <v/>
+      </c>
+      <c r="N228" t="str">
+        <v/>
+      </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
         <v>MRE5011</v>
       </c>
-      <c r="B182">
+      <c r="B229">
         <v>7</v>
       </c>
-      <c r="C182" t="str">
+      <c r="C229" t="str">
         <v>Pagani P200</v>
       </c>
-      <c r="D182" t="str">
+      <c r="D229" t="str">
         <v>Pagani P200</v>
       </c>
-      <c r="E182" t="str">
-        <v/>
-      </c>
-      <c r="F182" t="str">
-        <v/>
-      </c>
-      <c r="G182" t="str">
-        <v/>
-      </c>
-      <c r="H182" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I182" t="str">
+      <c r="E229" t="str">
+        <v/>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+      <c r="H229" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I229" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P200_main.jpg</v>
       </c>
-      <c r="J182" t="str">
+      <c r="J229" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
       </c>
-      <c r="K182" t="str">
+      <c r="K229" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
       </c>
-      <c r="L182" t="str">
-        <v/>
-      </c>
-      <c r="M182" t="str">
-        <v/>
-      </c>
-      <c r="N182" t="str">
-        <v/>
-      </c>
-      <c r="O182" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
+      <c r="L229" t="str">
+        <v/>
+      </c>
+      <c r="M229" t="str">
+        <v/>
+      </c>
+      <c r="N229" t="str">
+        <v/>
+      </c>
+      <c r="O229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
         <v>MRE5012</v>
       </c>
-      <c r="B183">
+      <c r="B230">
         <v>7</v>
       </c>
-      <c r="C183" t="str">
+      <c r="C230" t="str">
         <v>Pagani P300</v>
       </c>
-      <c r="D183" t="str">
+      <c r="D230" t="str">
         <v>Pagani P300</v>
       </c>
-      <c r="E183" t="str">
-        <v/>
-      </c>
-      <c r="F183" t="str">
-        <v/>
-      </c>
-      <c r="G183" t="str">
-        <v/>
-      </c>
-      <c r="H183" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I183" t="str">
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I230" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P300_main.jpg</v>
       </c>
-      <c r="J183" t="str">
+      <c r="J230" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
       </c>
-      <c r="K183" t="str">
+      <c r="K230" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
       </c>
-      <c r="L183" t="str">
-        <v/>
-      </c>
-      <c r="M183" t="str">
-        <v/>
-      </c>
-      <c r="N183" t="str">
-        <v/>
-      </c>
-      <c r="O183" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
+      <c r="L230" t="str">
+        <v/>
+      </c>
+      <c r="M230" t="str">
+        <v/>
+      </c>
+      <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
         <v>MRE5013</v>
       </c>
-      <c r="B184">
+      <c r="B231">
         <v>7</v>
       </c>
-      <c r="C184" t="str">
+      <c r="C231" t="str">
         <v>LAUDA58</v>
       </c>
-      <c r="D184" t="str">
+      <c r="D231" t="str">
         <v>LAUDA58</v>
       </c>
-      <c r="E184" t="str">
-        <v/>
-      </c>
-      <c r="F184" t="str">
-        <v/>
-      </c>
-      <c r="G184" t="str">
-        <v/>
-      </c>
-      <c r="H184" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I184" t="str">
+      <c r="E231" t="str">
+        <v/>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+      <c r="H231" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I231" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA58_main.jpg</v>
       </c>
-      <c r="J184" t="str">
+      <c r="J231" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
       </c>
-      <c r="K184" t="str">
+      <c r="K231" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
       </c>
-      <c r="L184" t="str">
-        <v/>
-      </c>
-      <c r="M184" t="str">
-        <v/>
-      </c>
-      <c r="N184" t="str">
-        <v/>
-      </c>
-      <c r="O184" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
+      <c r="L231" t="str">
+        <v/>
+      </c>
+      <c r="M231" t="str">
+        <v/>
+      </c>
+      <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
         <v>MRE5014</v>
       </c>
-      <c r="B185">
+      <c r="B232">
         <v>7</v>
       </c>
-      <c r="C185" t="str">
+      <c r="C232" t="str">
         <v>LAUDA72</v>
       </c>
-      <c r="D185" t="str">
+      <c r="D232" t="str">
         <v>LAUDA72</v>
       </c>
-      <c r="E185" t="str">
-        <v/>
-      </c>
-      <c r="F185" t="str">
-        <v/>
-      </c>
-      <c r="G185" t="str">
-        <v/>
-      </c>
-      <c r="H185" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I185" t="str">
+      <c r="E232" t="str">
+        <v/>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I232" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72_main.jpg</v>
       </c>
-      <c r="J185" t="str">
+      <c r="J232" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
       </c>
-      <c r="K185" t="str">
+      <c r="K232" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
       </c>
-      <c r="L185" t="str">
-        <v/>
-      </c>
-      <c r="M185" t="str">
-        <v/>
-      </c>
-      <c r="N185" t="str">
-        <v/>
-      </c>
-      <c r="O185" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="str">
+      <c r="L232" t="str">
+        <v/>
+      </c>
+      <c r="M232" t="str">
+        <v/>
+      </c>
+      <c r="N232" t="str">
+        <v/>
+      </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
         <v>MRE5015</v>
       </c>
-      <c r="B186">
+      <c r="B233">
         <v>7</v>
       </c>
-      <c r="C186" t="str">
+      <c r="C233" t="str">
         <v>LAUDA72 LIMITED EDITION</v>
       </c>
-      <c r="D186" t="str">
+      <c r="D233" t="str">
         <v>LAUDA72 LIMITED EDITION</v>
       </c>
-      <c r="E186" t="str">
-        <v/>
-      </c>
-      <c r="F186" t="str">
-        <v/>
-      </c>
-      <c r="G186" t="str">
-        <v/>
-      </c>
-      <c r="H186" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I186" t="str">
+      <c r="E233" t="str">
+        <v/>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I233" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72 LIMITED EDITION_main.jpg</v>
       </c>
-      <c r="J186" t="str">
+      <c r="J233" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
       </c>
-      <c r="K186" t="str">
+      <c r="K233" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
       </c>
-      <c r="L186" t="str">
-        <v/>
-      </c>
-      <c r="M186" t="str">
-        <v/>
-      </c>
-      <c r="N186" t="str">
-        <v/>
-      </c>
-      <c r="O186" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="str">
+      <c r="L233" t="str">
+        <v/>
+      </c>
+      <c r="M233" t="str">
+        <v/>
+      </c>
+      <c r="N233" t="str">
+        <v/>
+      </c>
+      <c r="O233" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
         <v>MRE5016</v>
       </c>
-      <c r="B187">
+      <c r="B234">
         <v>7</v>
       </c>
-      <c r="C187" t="str">
+      <c r="C234" t="str">
         <v>IP79</v>
       </c>
-      <c r="D187" t="str">
+      <c r="D234" t="str">
         <v>IP79</v>
       </c>
-      <c r="E187" t="str">
-        <v/>
-      </c>
-      <c r="F187" t="str">
-        <v/>
-      </c>
-      <c r="G187" t="str">
-        <v/>
-      </c>
-      <c r="H187" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I187" t="str">
+      <c r="E234" t="str">
+        <v/>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I234" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/IP79_main.jpg</v>
       </c>
-      <c r="J187" t="str">
+      <c r="J234" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
       </c>
-      <c r="K187" t="str">
+      <c r="K234" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
       </c>
-      <c r="L187" t="str">
-        <v/>
-      </c>
-      <c r="M187" t="str">
-        <v/>
-      </c>
-      <c r="N187" t="str">
-        <v/>
-      </c>
-      <c r="O187" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="str">
+      <c r="L234" t="str">
+        <v/>
+      </c>
+      <c r="M234" t="str">
+        <v/>
+      </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
         <v>MRE5017</v>
       </c>
-      <c r="B188">
+      <c r="B235">
         <v>7</v>
       </c>
-      <c r="C188" t="str">
+      <c r="C235" t="str">
         <v>IP68</v>
       </c>
-      <c r="D188" t="str">
+      <c r="D235" t="str">
         <v>IP68</v>
       </c>
-      <c r="E188" t="str">
-        <v/>
-      </c>
-      <c r="F188" t="str">
-        <v/>
-      </c>
-      <c r="G188" t="str">
-        <v/>
-      </c>
-      <c r="H188" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="I188" t="str">
+      <c r="E235" t="str">
+        <v/>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="I235" t="str">
         <v>/Users/tommy/Pictures/images/megabass_reels/IP68_main.jpg</v>
       </c>
-      <c r="J188" t="str">
+      <c r="J235" t="str">
         <v>2026-04-09T16:03:11.194Z</v>
       </c>
-      <c r="K188" t="str">
+      <c r="K235" t="str">
         <v>2026-04-09T16:03:11.194Z</v>
       </c>
-      <c r="L188" t="str">
-        <v/>
-      </c>
-      <c r="M188" t="str">
-        <v/>
-      </c>
-      <c r="N188" t="str">
-        <v/>
-      </c>
-      <c r="O188" t="str">
+      <c r="L235" t="str">
+        <v/>
+      </c>
+      <c r="M235" t="str">
+        <v/>
+      </c>
+      <c r="N235" t="str">
+        <v/>
+      </c>
+      <c r="O235" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O235"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">

--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -472,7 +472,7 @@
         <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>images/shimano_reels/STELLA SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA%20SW_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -519,7 +519,7 @@
         <v>spinning</v>
       </c>
       <c r="I3" t="str">
-        <v>images/shimano_reels/BB-X TECHNIUM FIRE BLOOD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20TECHNIUM%20FIRE%20BLOOD_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -566,7 +566,7 @@
         <v>spinning</v>
       </c>
       <c r="I4" t="str">
-        <v>images/shimano_reels/BB-X TECHNIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20TECHNIUM%20FIRE%20BLOOD_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -613,7 +613,7 @@
         <v>spinning</v>
       </c>
       <c r="I5" t="str">
-        <v>images/shimano_reels/KISU SPECIAL 45_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/KISU%20SPECIAL%2045_main.jpg</v>
       </c>
       <c r="J5" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -660,7 +660,7 @@
         <v>spinning</v>
       </c>
       <c r="I6" t="str">
-        <v>images/shimano_reels/AERO TECHNIUM MGS XTD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20TECHNIUM%20MGS%20XTD_main.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -707,7 +707,7 @@
         <v>spinning</v>
       </c>
       <c r="I7" t="str">
-        <v>images/shimano_reels/AERO TECHNIUM MGS XSD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20TECHNIUM%20MGS%20XSD_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -754,7 +754,7 @@
         <v>spinning</v>
       </c>
       <c r="I8" t="str">
-        <v>images/shimano_reels/STELLA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -801,7 +801,7 @@
         <v>spinning</v>
       </c>
       <c r="I9" t="str">
-        <v>images/shimano_reels/EXSENCE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE_main.jpg</v>
       </c>
       <c r="J9" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -848,7 +848,7 @@
         <v>spinning</v>
       </c>
       <c r="I10" t="str">
-        <v>images/shimano_reels/TWINPOWER SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER%20SW_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -895,7 +895,7 @@
         <v>spinning</v>
       </c>
       <c r="I11" t="str">
-        <v>images/shimano_reels/POWER AERO XTC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/POWER%20AERO%20XTC_main.jpg</v>
       </c>
       <c r="J11" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -942,7 +942,7 @@
         <v>spinning</v>
       </c>
       <c r="I12" t="str">
-        <v>images/shimano_reels/POWER AERO XSC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/POWER%20AERO%20XSC_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -989,7 +989,7 @@
         <v>spinning</v>
       </c>
       <c r="I13" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE TYPE2_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20HYPER%20FORCE%20TYPE2_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1036,7 +1036,7 @@
         <v>spinning</v>
       </c>
       <c r="I14" t="str">
-        <v>images/shimano_reels/FLIEGEN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/FLIEGEN_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1083,7 +1083,7 @@
         <v>spinning</v>
       </c>
       <c r="I15" t="str">
-        <v>images/shimano_reels/Vanquish CE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Vanquish%20CE_main.jpg</v>
       </c>
       <c r="J15" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1130,7 +1130,7 @@
         <v>spinning</v>
       </c>
       <c r="I16" t="str">
-        <v>images/shimano_reels/Vanquish_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Vanquish_main.jpg</v>
       </c>
       <c r="J16" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1177,7 +1177,7 @@
         <v>spinning</v>
       </c>
       <c r="I17" t="str">
-        <v>images/shimano_reels/SARAGOSA SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SARAGOSA%20SW_main.jpg</v>
       </c>
       <c r="J17" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1224,7 +1224,7 @@
         <v>spinning</v>
       </c>
       <c r="I18" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20HYPER%20FORCE%201700_C2000_main.jpg</v>
       </c>
       <c r="J18" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1271,7 +1271,7 @@
         <v>spinning</v>
       </c>
       <c r="I19" t="str">
-        <v>images/shimano_reels/BB-X Remare_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20Remare_main.jpg</v>
       </c>
       <c r="J19" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1318,7 +1318,7 @@
         <v>spinning</v>
       </c>
       <c r="I20" t="str">
-        <v>images/shimano_reels/TWINPOWER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER_main.jpg</v>
       </c>
       <c r="J20" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1365,7 +1365,7 @@
         <v>spinning</v>
       </c>
       <c r="I21" t="str">
-        <v>images/shimano_reels/TWINPOWER XD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER%20XD_main.jpg</v>
       </c>
       <c r="J21" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1412,7 +1412,7 @@
         <v>spinning</v>
       </c>
       <c r="I22" t="str">
-        <v>images/shimano_reels/HYPER FORCE LB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/HYPER%20FORCE%20LB_main.jpg</v>
       </c>
       <c r="J22" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1459,7 +1459,7 @@
         <v>spinning</v>
       </c>
       <c r="I23" t="str">
-        <v>images/shimano_reels/POWER AERO TD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/POWER%20AERO%20TD_main.jpg</v>
       </c>
       <c r="J23" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1506,7 +1506,7 @@
         <v>spinning</v>
       </c>
       <c r="I24" t="str">
-        <v>images/shimano_reels/ULTEGRA XR BIG PIT XTD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XR%20BIG%20PIT%20XTD_main.jpg</v>
       </c>
       <c r="J24" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1553,7 +1553,7 @@
         <v>spinning</v>
       </c>
       <c r="I25" t="str">
-        <v>images/shimano_reels/ULTEGRA XR BIG PIT XSD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XR%20BIG%20PIT%20XSD_main.jpg</v>
       </c>
       <c r="J25" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1600,7 +1600,7 @@
         <v>spinning</v>
       </c>
       <c r="I26" t="str">
-        <v>images/shimano_reels/BB-X HYPER FORCE 1700_C2000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20HYPER%20FORCE%201700_C2000_main.jpg</v>
       </c>
       <c r="J26" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1647,7 +1647,7 @@
         <v>spinning</v>
       </c>
       <c r="I27" t="str">
-        <v>images/shimano_reels/BB-X Rinkai SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20Rinkai%20SP_main.jpg</v>
       </c>
       <c r="J27" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1694,7 +1694,7 @@
         <v>spinning</v>
       </c>
       <c r="I28" t="str">
-        <v>images/shimano_reels/EXSENCE XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20XR_main.jpg</v>
       </c>
       <c r="J28" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1741,7 +1741,7 @@
         <v>spinning</v>
       </c>
       <c r="I29" t="str">
-        <v>images/shimano_reels/STRADIC SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC%20SW_main.jpg</v>
       </c>
       <c r="J29" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1788,7 +1788,7 @@
         <v>spinning</v>
       </c>
       <c r="I30" t="str">
-        <v>images/shimano_reels/Sephia XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20XR_main.jpg</v>
       </c>
       <c r="J30" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1835,7 +1835,7 @@
         <v>spinning</v>
       </c>
       <c r="I31" t="str">
-        <v>images/shimano_reels/SUSTAIN_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SUSTAIN_main.jpg</v>
       </c>
       <c r="J31" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1882,7 +1882,7 @@
         <v>spinning</v>
       </c>
       <c r="I32" t="str">
-        <v>images/shimano_reels/Soare XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare%20XR_main.jpg</v>
       </c>
       <c r="J32" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1929,7 +1929,7 @@
         <v>spinning</v>
       </c>
       <c r="I33" t="str">
-        <v>images/shimano_reels/CARDIFF XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CARDIFF%20XR_main.jpg</v>
       </c>
       <c r="J33" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1976,7 +1976,7 @@
         <v>spinning</v>
       </c>
       <c r="I34" t="str">
-        <v>images/shimano_reels/BB-X DESPINA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20DESPINA_main.jpg</v>
       </c>
       <c r="J34" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2023,7 +2023,7 @@
         <v>spinning</v>
       </c>
       <c r="I35" t="str">
-        <v>images/shimano_reels/BULL‘S EYE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BULL%E2%80%98S%20EYE_main.jpg</v>
       </c>
       <c r="J35" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2070,7 +2070,7 @@
         <v>spinning</v>
       </c>
       <c r="I36" t="str">
-        <v>images/shimano_reels/COMPLEX XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/COMPLEX%20XR_main.jpg</v>
       </c>
       <c r="J36" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2117,7 +2117,7 @@
         <v>spinning</v>
       </c>
       <c r="I37" t="str">
-        <v>images/shimano_reels/BAITRUNNER CI4+ XTB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BAITRUNNER%20CI4%2B%20XTB_main.jpg</v>
       </c>
       <c r="J37" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2164,7 +2164,7 @@
         <v>spinning</v>
       </c>
       <c r="I38" t="str">
-        <v>images/shimano_reels/SURF LEADER_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SURF%20LEADER_main.png</v>
       </c>
       <c r="J38" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2211,7 +2211,7 @@
         <v>spinning</v>
       </c>
       <c r="I39" t="str">
-        <v>images/shimano_reels/Sephia SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20SS_main.jpg</v>
       </c>
       <c r="J39" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2258,7 +2258,7 @@
         <v>spinning</v>
       </c>
       <c r="I40" t="str">
-        <v>images/shimano_reels/VANFORD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/VANFORD_main.jpg</v>
       </c>
       <c r="J40" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2305,7 +2305,7 @@
         <v>spinning</v>
       </c>
       <c r="I41" t="str">
-        <v>images/shimano_reels/ULTEGRA XS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XS_main.jpg</v>
       </c>
       <c r="J41" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2352,7 +2352,7 @@
         <v>spinning</v>
       </c>
       <c r="I42" t="str">
-        <v>images/shimano_reels/ULTEGRA XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA%20XT_main.jpg</v>
       </c>
       <c r="J42" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2399,7 +2399,7 @@
         <v>spinning</v>
       </c>
       <c r="I43" t="str">
-        <v>images/shimano_reels/BB-X LARISSA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BB-X%20LARISSA_main.jpg</v>
       </c>
       <c r="J43" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2446,7 +2446,7 @@
         <v>spinning</v>
       </c>
       <c r="I44" t="str">
-        <v>images/shimano_reels/SPHEROS SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPHEROS%20SW_main.jpg</v>
       </c>
       <c r="J44" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2493,7 +2493,7 @@
         <v>spinning</v>
       </c>
       <c r="I45" t="str">
-        <v>images/shimano_reels/SPEEDMASTER XTD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPEEDMASTER%20XTD_main.jpg</v>
       </c>
       <c r="J45" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2540,7 +2540,7 @@
         <v>spinning</v>
       </c>
       <c r="I46" t="str">
-        <v>images/shimano_reels/STRADIC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2587,7 +2587,7 @@
         <v>spinning</v>
       </c>
       <c r="I47" t="str">
-        <v>images/shimano_reels/SUPER AERO SpinJoy_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SUPER%20AERO%20SpinJoy_main.jpg</v>
       </c>
       <c r="J47" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2634,7 +2634,7 @@
         <v>spinning</v>
       </c>
       <c r="I48" t="str">
-        <v>images/shimano_reels/SPEEDMASTER XSD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPEEDMASTER%20XSD_main.jpg</v>
       </c>
       <c r="J48" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2681,7 +2681,7 @@
         <v>spinning</v>
       </c>
       <c r="I49" t="str">
-        <v>images/shimano_reels/Sephia BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20BB_main.jpg</v>
       </c>
       <c r="J49" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2728,7 +2728,7 @@
         <v>spinning</v>
       </c>
       <c r="I50" t="str">
-        <v>images/shimano_reels/EXSENCE BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20BB_main.jpg</v>
       </c>
       <c r="J50" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2775,7 +2775,7 @@
         <v>spinning</v>
       </c>
       <c r="I51" t="str">
-        <v>images/shimano_reels/AERO XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20XR_main.jpg</v>
       </c>
       <c r="J51" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2822,7 +2822,7 @@
         <v>spinning</v>
       </c>
       <c r="I52" t="str">
-        <v>images/shimano_reels/ULTEGRA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ULTEGRA_main.jpg</v>
       </c>
       <c r="J52" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2869,7 +2869,7 @@
         <v>spinning</v>
       </c>
       <c r="I53" t="str">
-        <v>images/shimano_reels/Soare BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare%20BB_main.jpg</v>
       </c>
       <c r="J53" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2916,7 +2916,7 @@
         <v>spinning</v>
       </c>
       <c r="I54" t="str">
-        <v>images/shimano_reels/AERLEX XTC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERLEX%20XTC_main.jpg</v>
       </c>
       <c r="J54" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2963,7 +2963,7 @@
         <v>spinning</v>
       </c>
       <c r="I55" t="str">
-        <v>images/shimano_reels/AERLEX XSC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERLEX%20XSC_main.jpg</v>
       </c>
       <c r="J55" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3010,7 +3010,7 @@
         <v>spinning</v>
       </c>
       <c r="I56" t="str">
-        <v>images/shimano_reels/AERO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO_main.jpg</v>
       </c>
       <c r="J56" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3057,7 +3057,7 @@
         <v>spinning</v>
       </c>
       <c r="I57" t="str">
-        <v>images/shimano_reels/MIRAVEL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/MIRAVEL_main.jpg</v>
       </c>
       <c r="J57" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3104,7 +3104,7 @@
         <v>spinning</v>
       </c>
       <c r="I58" t="str">
-        <v>images/shimano_reels/NASCI_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/NASCI_main.jpg</v>
       </c>
       <c r="J58" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3151,7 +3151,7 @@
         <v>spinning</v>
       </c>
       <c r="I59" t="str">
-        <v>images/shimano_reels/SOCORRO SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SOCORRO%20SW_main.jpg</v>
       </c>
       <c r="J59" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3198,7 +3198,7 @@
         <v>spinning</v>
       </c>
       <c r="I60" t="str">
-        <v>images/shimano_reels/AERO BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20BB_main.jpg</v>
       </c>
       <c r="J60" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3245,7 +3245,7 @@
         <v>spinning</v>
       </c>
       <c r="I61" t="str">
-        <v>images/shimano_reels/SAHARA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SAHARA_main.jpg</v>
       </c>
       <c r="J61" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3292,7 +3292,7 @@
         <v>spinning</v>
       </c>
       <c r="I62" t="str">
-        <v>images/shimano_reels/ACTIVECAST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ACTIVECAST_main.jpg</v>
       </c>
       <c r="J62" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3339,7 +3339,7 @@
         <v>spinning</v>
       </c>
       <c r="I63" t="str">
-        <v>images/shimano_reels/SEDONA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SEDONA_main.jpg</v>
       </c>
       <c r="J63" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3386,7 +3386,7 @@
         <v>spinning</v>
       </c>
       <c r="I64" t="str">
-        <v>images/shimano_reels/ALIVIO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALIVIO_main.jpg</v>
       </c>
       <c r="J64" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3433,7 +3433,7 @@
         <v>spinning</v>
       </c>
       <c r="I65" t="str">
-        <v>images/shimano_reels/NEXAVE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/NEXAVE_main.jpg</v>
       </c>
       <c r="J65" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3480,7 +3480,7 @@
         <v>spinning</v>
       </c>
       <c r="I66" t="str">
-        <v>images/shimano_reels/CATANA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CATANA_main.jpg</v>
       </c>
       <c r="J66" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3527,7 +3527,7 @@
         <v>spinning</v>
       </c>
       <c r="I67" t="str">
-        <v>images/shimano_reels/SIENNA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SIENNA_main.jpg</v>
       </c>
       <c r="J67" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3574,7 +3574,7 @@
         <v>spinning</v>
       </c>
       <c r="I68" t="str">
-        <v>images/shimano_reels/FX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/FX_main.jpg</v>
       </c>
       <c r="J68" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3621,7 +3621,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I69" t="str">
-        <v>images/shimano_reels/TIAGRA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TIAGRA_main.jpg</v>
       </c>
       <c r="J69" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3668,7 +3668,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I70" t="str">
-        <v>images/shimano_reels/TALICA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TALICA_main.jpg</v>
       </c>
       <c r="J70" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3715,7 +3715,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I71" t="str">
-        <v>images/shimano_reels/EXSENCE DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC%20SS_main.jpg</v>
       </c>
       <c r="J71" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3762,7 +3762,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I72" t="str">
-        <v>images/shimano_reels/ANTARES DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.png</v>
       </c>
       <c r="J72" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3809,7 +3809,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I73" t="str">
-        <v>images/shimano_reels/ANTARES DC MD_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.png</v>
       </c>
       <c r="J73" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3856,7 +3856,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I74" t="str">
-        <v>images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%204000_4000HG_main.jpg</v>
       </c>
       <c r="J74" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3903,7 +3903,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I75" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20DC_main.jpg</v>
       </c>
       <c r="J75" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3950,7 +3950,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I76" t="str">
-        <v>images/shimano_reels/OCEA JIGGER LD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%20LD_main.jpg</v>
       </c>
       <c r="J76" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3997,7 +3997,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I77" t="str">
-        <v>images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%20F%20CUSTOM_main.jpg</v>
       </c>
       <c r="J77" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4044,7 +4044,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I78" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST CT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST%20CT_main.jpg</v>
       </c>
       <c r="J78" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4091,7 +4091,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I79" t="str">
-        <v>images/shimano_reels/KAIKON_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/KAIKON_main.jpg</v>
       </c>
       <c r="J79" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4138,7 +4138,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I80" t="str">
-        <v>images/shimano_reels/ANTARES_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="J80" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4185,7 +4185,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I81" t="str">
-        <v>images/shimano_reels/OCEA JIGGER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%204000_4000HG_main.jpg</v>
       </c>
       <c r="J81" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4232,7 +4232,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I82" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST MD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20MD_main.jpg</v>
       </c>
       <c r="J82" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4279,7 +4279,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I83" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="J83" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4326,7 +4326,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I84" t="str">
-        <v>images/shimano_reels/Metanium DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium%20DC_main.jpg</v>
       </c>
       <c r="J84" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4373,7 +4373,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I85" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="J85" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4420,7 +4420,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I86" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST%20CT_main.jpg</v>
       </c>
       <c r="J86" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4467,7 +4467,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I87" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20SHALLOW%20EDITION_main.jpg</v>
       </c>
       <c r="J87" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4514,7 +4514,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I88" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="J88" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4561,7 +4561,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I89" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST FT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST%20FT_main.jpg</v>
       </c>
       <c r="J89" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4608,7 +4608,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I90" t="str">
-        <v>images/shimano_reels/ALDEBARAN DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20DC_main.jpg</v>
       </c>
       <c r="J90" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4655,7 +4655,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I91" t="str">
-        <v>images/shimano_reels/STILE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STILE_main.jpg</v>
       </c>
       <c r="J91" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4702,7 +4702,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I92" t="str">
-        <v>images/shimano_reels/BARCHETTA PREMIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20PREMIUM_main.jpg</v>
       </c>
       <c r="J92" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4749,7 +4749,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I93" t="str">
-        <v>images/shimano_reels/GRAPPLER PREMIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%20PREMIUM_main.jpg</v>
       </c>
       <c r="J93" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4796,7 +4796,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I94" t="str">
-        <v>images/shimano_reels/ALDEBARAN BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20BFS_main.jpg</v>
       </c>
       <c r="J94" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4843,7 +4843,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I95" t="str">
-        <v>images/shimano_reels/ALDEBARAN MGL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20MGL_main.jpg</v>
       </c>
       <c r="J95" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4890,7 +4890,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I96" t="str">
-        <v>images/shimano_reels/Metanium SHALLOW EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium%20SHALLOW%20EDITION_main.jpg</v>
       </c>
       <c r="J96" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4937,7 +4937,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I97" t="str">
-        <v>images/shimano_reels/Metanium_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium_main.jpg</v>
       </c>
       <c r="J97" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4984,7 +4984,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I98" t="str">
-        <v>images/shimano_reels/SPEEDMASTER 石鲷_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPEEDMASTER%20%E7%9F%B3%E9%B2%B7_main.jpg</v>
       </c>
       <c r="J98" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5031,7 +5031,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I99" t="str">
-        <v>images/shimano_reels/TYRNOS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TYRNOS_main.jpg</v>
       </c>
       <c r="J99" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5078,7 +5078,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I100" t="str">
-        <v>images/shimano_reels/EXSENCE DC SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC%20SS_main.jpg</v>
       </c>
       <c r="J100" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5125,7 +5125,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I101" t="str">
-        <v>images/shimano_reels/TRANX 400_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX%20400_main.jpg</v>
       </c>
       <c r="J101" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5172,7 +5172,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I102" t="str">
-        <v>images/shimano_reels/Bantam_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Bantam_main.jpg</v>
       </c>
       <c r="J102" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5219,7 +5219,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I103" t="str">
-        <v>images/shimano_reels/TRANX 300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX%20300_main.jpg</v>
       </c>
       <c r="J103" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5266,7 +5266,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I104" t="str">
-        <v>images/shimano_reels/BAYGAME_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BAYGAME_main.jpg</v>
       </c>
       <c r="J104" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5313,7 +5313,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I105" t="str">
-        <v>images/shimano_reels/GRAPPLER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J105" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5360,7 +5360,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I106" t="str">
-        <v>images/shimano_reels/BARCHETTA F CUSTOM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20F%20CUSTOM_main.jpg</v>
       </c>
       <c r="J106" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5407,7 +5407,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I107" t="str">
-        <v>images/shimano_reels/Scorpion DC MD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC%20MD_main.jpg</v>
       </c>
       <c r="J107" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5454,7 +5454,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I108" t="str">
-        <v>images/shimano_reels/SLX DC XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20DC%20XT_main.jpg</v>
       </c>
       <c r="J108" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5501,7 +5501,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I109" t="str">
-        <v>images/shimano_reels/Scorpion DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC%20MD_main.jpg</v>
       </c>
       <c r="J109" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5548,7 +5548,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I110" t="str">
-        <v>images/shimano_reels/Scorpion MD 300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20MD%20300_main.jpg</v>
       </c>
       <c r="J110" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5595,7 +5595,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I111" t="str">
-        <v>images/shimano_reels/GRAPPLER CT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%20CT_main.jpg</v>
       </c>
       <c r="J111" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5642,7 +5642,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I112" t="str">
-        <v>images/shimano_reels/CURADO DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20DC_main.jpg</v>
       </c>
       <c r="J112" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5689,7 +5689,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I113" t="str">
-        <v>images/shimano_reels/CHINUMATIC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CHINUMATIC_main.jpg</v>
       </c>
       <c r="J113" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5736,7 +5736,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I114" t="str">
-        <v>images/shimano_reels/Stephano SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Stephano%20SS_main.jpg</v>
       </c>
       <c r="J114" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5783,7 +5783,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I115" t="str">
-        <v>images/shimano_reels/STILE SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STILE%20SS_main.jpg</v>
       </c>
       <c r="J115" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5830,7 +5830,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I116" t="str">
-        <v>images/shimano_reels/Scorpion MD 200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20MD%20200_main.jpg</v>
       </c>
       <c r="J116" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5877,7 +5877,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I117" t="str">
-        <v>images/shimano_reels/TORIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TORIUM_main.jpg</v>
       </c>
       <c r="J117" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5924,7 +5924,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I118" t="str">
-        <v>images/shimano_reels/TRANX 200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX%20200_main.jpg</v>
       </c>
       <c r="J118" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5971,7 +5971,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I119" t="str">
-        <v>images/shimano_reels/TRANX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX_main.jpg</v>
       </c>
       <c r="J119" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6018,7 +6018,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I120" t="str">
-        <v>images/shimano_reels/BARCHETTA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA_main.jpg</v>
       </c>
       <c r="J120" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6065,7 +6065,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I121" t="str">
-        <v>images/shimano_reels/BARCHETTA SC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20SC_main.jpg</v>
       </c>
       <c r="J121" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6112,7 +6112,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I122" t="str">
-        <v>images/shimano_reels/SLX DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20DC%20XT_main.jpg</v>
       </c>
       <c r="J122" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6159,7 +6159,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I123" t="str">
-        <v>images/shimano_reels/CURADO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO_main.jpg</v>
       </c>
       <c r="J123" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6206,7 +6206,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I124" t="str">
-        <v>images/shimano_reels/CURADO 150_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20150_main.jpg</v>
       </c>
       <c r="J124" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6253,7 +6253,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I125" t="str">
-        <v>images/shimano_reels/CURADO MGL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20MGL_main.jpg</v>
       </c>
       <c r="J125" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6300,7 +6300,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I126" t="str">
-        <v>images/shimano_reels/CURADO BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20BFS_main.jpg</v>
       </c>
       <c r="J126" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6347,7 +6347,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I127" t="str">
-        <v>images/shimano_reels/SLX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX_main.jpg</v>
       </c>
       <c r="J127" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6394,7 +6394,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I128" t="str">
-        <v>images/shimano_reels/BARCHETTA BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20BB_main.jpg</v>
       </c>
       <c r="J128" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6441,7 +6441,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I129" t="str">
-        <v>images/shimano_reels/SLX BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20BFS_main.jpg</v>
       </c>
       <c r="J129" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6488,7 +6488,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I130" t="str">
-        <v>images/shimano_reels/GRAPPLER BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%20BB_main.jpg</v>
       </c>
       <c r="J130" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6535,7 +6535,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I131" t="str">
-        <v>images/shimano_reels/SLX XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20XT_main.jpg</v>
       </c>
       <c r="J131" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6582,7 +6582,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I132" t="str">
-        <v>images/shimano_reels/小船_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/%E5%B0%8F%E8%88%B9_main.jpg</v>
       </c>
       <c r="J132" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6629,7 +6629,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I133" t="str">
-        <v>images/shimano_reels/CARDIFF_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CARDIFF_main.jpg</v>
       </c>
       <c r="J133" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6676,7 +6676,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I134" t="str">
-        <v>images/shimano_reels/幻风 XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/%E5%B9%BB%E9%A3%8E%20XT_main.jpg</v>
       </c>
       <c r="J134" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6723,7 +6723,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I135" t="str">
-        <v>images/shimano_reels/TITANOS FUNE GT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TITANOS%20FUNE%20GT_main.jpg</v>
       </c>
       <c r="J135" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6770,7 +6770,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I136" t="str">
-        <v>images/shimano_reels/BASS ONE XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BASS%20ONE%20XT_main.jpg</v>
       </c>
       <c r="J136" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6817,7 +6817,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I137" t="str">
-        <v>images/shimano_reels/CAIUS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CAIUS_main.jpg</v>
       </c>
       <c r="J137" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6864,7 +6864,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I138" t="str">
-        <v>images/shimano_reels/BASS RISE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BASS%20RISE_main.jpg</v>
       </c>
       <c r="J138" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6911,7 +6911,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I139" t="str">
-        <v>images/shimano_reels/幻风_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/%E5%B9%BB%E9%A3%8E%20XT_main.jpg</v>
       </c>
       <c r="J139" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6958,7 +6958,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I140" t="str">
-        <v>images/shimano_reels/CHINU SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CHINU%20SPECIAL_main.jpg</v>
       </c>
       <c r="J140" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -7005,7 +7005,7 @@
         <v>spinning</v>
       </c>
       <c r="I141" t="str">
-        <v>images/daiwa_reels/ソルティガ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J141" t="str">
         <v>2026-04-05T14:36:58.671126Z</v>
@@ -7056,7 +7056,7 @@
         <v>spinning</v>
       </c>
       <c r="I142" t="str">
-        <v>images/daiwa_reels/ソルティガ_4000_5000_6000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J142" t="str">
         <v>2026-04-05T14:37:04.963194Z</v>
@@ -7105,7 +7105,7 @@
         <v>spinning</v>
       </c>
       <c r="I143" t="str">
-        <v>images/daiwa_reels/EXIST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/EXIST_main.jpg</v>
       </c>
       <c r="J143" t="str">
         <v>2026-04-05T14:37:11.658942Z</v>
@@ -7155,7 +7155,7 @@
         <v>spinning</v>
       </c>
       <c r="I144" t="str">
-        <v>images/daiwa_reels/セルテート_SW_8000___10000___14000___18000___20000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_SW_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J144" t="str">
         <v>2026-04-05T14:37:13.603365Z</v>
@@ -7253,7 +7253,7 @@
         <v>spinning</v>
       </c>
       <c r="I146" t="str">
-        <v>images/daiwa_reels/セルテート_HD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_HD_main.jpg</v>
       </c>
       <c r="J146" t="str">
         <v>2026-04-05T14:37:21.734163Z</v>
@@ -7303,7 +7303,7 @@
         <v>spinning</v>
       </c>
       <c r="I147" t="str">
-        <v>images/daiwa_reels/セルテート_SW_4000_5000_6000_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_SW_4000_5000_6000_main.jpg</v>
       </c>
       <c r="J147" t="str">
         <v>2026-04-05T14:37:28.669103Z</v>
@@ -7405,7 +7405,7 @@
         <v>spinning</v>
       </c>
       <c r="I149" t="str">
-        <v>images/daiwa_reels/エアリティ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%82%A2%E3%83%AA%E3%83%86%E3%82%A3_ST_main.jpg</v>
       </c>
       <c r="J149" t="str">
         <v>2026-04-05T14:37:40.618600Z</v>
@@ -7455,7 +7455,7 @@
         <v>spinning</v>
       </c>
       <c r="I150" t="str">
-        <v>images/daiwa_reels/エアリティ_ST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%82%A2%E3%83%AA%E3%83%86%E3%82%A3_ST_main.jpg</v>
       </c>
       <c r="J150" t="str">
         <v>2026-04-05T14:37:46.839914Z</v>
@@ -7505,7 +7505,7 @@
         <v>spinning</v>
       </c>
       <c r="I151" t="str">
-        <v>images/daiwa_reels/セルテート_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BB%E3%83%AB%E3%83%86%E3%83%BC%E3%83%88_HD_main.jpg</v>
       </c>
       <c r="J151" t="str">
         <v>2026-04-05T14:37:47.828581Z</v>
@@ -7555,7 +7555,7 @@
         <v>spinning</v>
       </c>
       <c r="I152" t="str">
-        <v>images/daiwa_reels/エメラルダス_AIR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9_AIR_main.jpg</v>
       </c>
       <c r="J152" t="str">
         <v>2026-04-05T14:37:50.096730Z</v>
@@ -7605,7 +7605,7 @@
         <v>spinning</v>
       </c>
       <c r="I153" t="str">
-        <v>images/daiwa_reels/ルビアス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AB%E3%83%93%E3%82%A2%E3%82%B9_ST_main.jpg</v>
       </c>
       <c r="J153" t="str">
         <v>2026-04-05T14:37:57.793850Z</v>
@@ -7753,7 +7753,7 @@
         <v>spinning</v>
       </c>
       <c r="I156" t="str">
-        <v>images/daiwa_reels/ルビアス_ST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AB%E3%83%93%E3%82%A2%E3%82%B9_ST_main.jpg</v>
       </c>
       <c r="J156" t="str">
         <v>2026-04-05T14:38:07.769091Z</v>
@@ -7902,7 +7902,7 @@
         <v>spinning</v>
       </c>
       <c r="I159" t="str">
-        <v>images/daiwa_reels/エメラルダス_RX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9_RX_main.jpg</v>
       </c>
       <c r="J159" t="str">
         <v>2026-04-05T14:38:12.642500Z</v>
@@ -8000,7 +8000,7 @@
         <v>spinning</v>
       </c>
       <c r="I161" t="str">
-        <v>images/daiwa_reels/カルディア_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%AB%E3%83%AB%E3%83%87%E3%82%A3%E3%82%A2_main.jpg</v>
       </c>
       <c r="J161" t="str">
         <v>2026-04-05T14:38:25.700195Z</v>
@@ -8148,7 +8148,7 @@
         <v>spinning</v>
       </c>
       <c r="I164" t="str">
-        <v>images/daiwa_reels/月下美人_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA_BF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J164" t="str">
         <v>2026-04-05T14:38:34.700529Z</v>
@@ -8197,7 +8197,7 @@
         <v>spinning</v>
       </c>
       <c r="I165" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_BF_TW_main.jpg</v>
       </c>
       <c r="J165" t="str">
         <v>2026-04-05T14:38:40.792539Z</v>
@@ -8345,7 +8345,7 @@
         <v>spinning</v>
       </c>
       <c r="I168" t="str">
-        <v>images/daiwa_reels/レグザ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AC%E3%82%B0%E3%82%B6_main.jpg</v>
       </c>
       <c r="J168" t="str">
         <v>2026-04-05T14:38:58.278242Z</v>
@@ -8444,7 +8444,7 @@
         <v>spinning</v>
       </c>
       <c r="I170" t="str">
-        <v>images/daiwa_reels/フリームス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%95%E3%83%AA%E3%83%BC%E3%83%A0%E3%82%B9_main.jpg</v>
       </c>
       <c r="J170" t="str">
         <v>2026-04-05T14:39:04.561638Z</v>
@@ -8543,7 +8543,7 @@
         <v>spinning</v>
       </c>
       <c r="I172" t="str">
-        <v>images/daiwa_reels/イプリミ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A4%E3%83%97%E3%83%AA%E3%83%9F_main.jpg</v>
       </c>
       <c r="J172" t="str">
         <v>2026-04-05T14:39:18.443898Z</v>
@@ -8594,7 +8594,7 @@
         <v>spinning</v>
       </c>
       <c r="I173" t="str">
-        <v>images/daiwa_reels/エメラルダス_X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9_X_main.jpg</v>
       </c>
       <c r="J173" t="str">
         <v>2026-04-05T14:39:24.533666Z</v>
@@ -8693,7 +8693,7 @@
         <v>spinning</v>
       </c>
       <c r="I175" t="str">
-        <v>images/daiwa_reels/アオリマチックBR_LT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A2%E3%82%AA%E3%83%AA%E3%83%9E%E3%83%81%E3%83%83%E3%82%AFBR_LT_main.jpg</v>
       </c>
       <c r="J175" t="str">
         <v>2026-04-05T14:39:33.655150Z</v>
@@ -8743,7 +8743,7 @@
         <v>spinning</v>
       </c>
       <c r="I176" t="str">
-        <v>images/daiwa_reels/月下美人_X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA_X_main.jpg</v>
       </c>
       <c r="J176" t="str">
         <v>2026-04-05T14:39:35.787707Z</v>
@@ -8792,7 +8792,7 @@
         <v>spinning</v>
       </c>
       <c r="I177" t="str">
-        <v>images/daiwa_reels/レガリス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AC%E3%82%AC%E3%83%AA%E3%82%B9_main.jpg</v>
       </c>
       <c r="J177" t="str">
         <v>2026-04-05T14:39:42.740714Z</v>
@@ -8892,7 +8892,7 @@
         <v>spinning</v>
       </c>
       <c r="I179" t="str">
-        <v>images/daiwa_reels/レブロス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AC%E3%83%96%E3%83%AD%E3%82%B9_main.jpg</v>
       </c>
       <c r="J179" t="str">
         <v>2026-04-05T14:39:55.715342Z</v>
@@ -9332,7 +9332,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I188" t="str">
-        <v>images/daiwa_reels/IM_Z_リミットブレイカー_TW_HD-C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM_Z_%E3%83%AA%E3%83%9F%E3%83%83%E3%83%88%E3%83%96%E3%83%AC%E3%82%A4%E3%82%AB%E3%83%BC_TW_HD-C_main.jpg</v>
       </c>
       <c r="J188" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9383,7 +9383,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I189" t="str">
-        <v>images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM_Z_TW_200-C_main.jpg</v>
       </c>
       <c r="J189" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9434,7 +9434,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I190" t="str">
-        <v>images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM_Z_TW100-C_main.jpg</v>
       </c>
       <c r="J190" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9486,7 +9486,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I191" t="str">
-        <v>images/daiwa_reels/スティーズ_リミテッド_CT_SV_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA_%E3%83%AA%E3%83%9F%E3%83%86%E3%83%83%E3%83%89_CT_SV_TW_main.jpg</v>
       </c>
       <c r="J191" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9537,7 +9537,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I192" t="str">
-        <v>images/daiwa_reels/スティーズ_SV_ライト_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA_SV_%E3%83%A9%E3%82%A4%E3%83%88_TW_main.jpg</v>
       </c>
       <c r="J192" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9586,7 +9586,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I193" t="str">
-        <v>images/daiwa_reels/スティーズ_SV_TW100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA_SV_TW100_main.jpg</v>
       </c>
       <c r="J193" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9688,7 +9688,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I195" t="str">
-        <v>images/daiwa_reels/リョウガ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%AA%E3%83%A7%E3%82%A6%E3%82%AC_main.jpg</v>
       </c>
       <c r="J195" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9842,7 +9842,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I198" t="str">
-        <v>images/daiwa_reels/月下美人_BF_TW_PE_SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA_BF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J198" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -9944,7 +9944,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I200" t="str">
-        <v>images/daiwa_reels/シルバーウルフ_CT_SV_TW_PE_SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%A6%E3%83%AB%E3%83%95_CT_SV_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J200" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10097,7 +10097,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I203" t="str">
-        <v>images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/HRF_TW_PE_SP_main.jpg</v>
       </c>
       <c r="J203" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10302,7 +10302,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I207" t="str">
-        <v>images/daiwa_reels/アルファスBF_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%A2%E3%83%AB%E3%83%95%E3%82%A1%E3%82%B9BF_TW_main.jpg</v>
       </c>
       <c r="J207" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10406,7 +10406,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I209" t="str">
-        <v>images/daiwa_reels/ソルティスト_TW_PE_SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%B9%E3%83%88_TW_PE_SPECIAL_main.jpg</v>
       </c>
       <c r="J209" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10558,7 +10558,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I212" t="str">
-        <v>images/daiwa_reels/タトゥーラ_BF_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_BF_TW_main.jpg</v>
       </c>
       <c r="J212" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10611,7 +10611,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I213" t="str">
-        <v>images/daiwa_reels/タトゥーラ_TW_200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_TW_200_main.jpg</v>
       </c>
       <c r="J213" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10665,7 +10665,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I214" t="str">
-        <v>images/daiwa_reels/タトゥーラ_SV_TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_SV_TW_main.jpg</v>
       </c>
       <c r="J214" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10717,7 +10717,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I215" t="str">
-        <v>images/daiwa_reels/タトゥーラ_TW_100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9_TW_100_main.jpg</v>
       </c>
       <c r="J215" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10769,7 +10769,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I216" t="str">
-        <v>images/daiwa_reels/バス__X__100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E3%83%90%E3%82%B9__X__100_main.jpg</v>
       </c>
       <c r="J216" t="str">
         <v>2026-04-09T06:29:15.200Z</v>
@@ -10867,7 +10867,7 @@
         <v>spinning</v>
       </c>
       <c r="I218" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 20X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2020X_main.jpg</v>
       </c>
       <c r="J218" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
@@ -10914,7 +10914,7 @@
         <v>spinning</v>
       </c>
       <c r="I219" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/GAUS 30X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2030X_main.jpg</v>
       </c>
       <c r="J219" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
@@ -10961,7 +10961,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I220" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LIN258HM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LIN258HM_main.jpg</v>
       </c>
       <c r="J220" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
@@ -11008,7 +11008,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I221" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RC-IDATEN 256_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RC-IDATEN%20256_main.jpg</v>
       </c>
       <c r="J221" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
@@ -11055,7 +11055,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I222" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE GRIGIO STONE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
       </c>
       <c r="J222" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
@@ -11102,7 +11102,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I223" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE ITO-GAMBLER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20ITO-GAMBLER_main.jpg</v>
       </c>
       <c r="J223" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
@@ -11149,7 +11149,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I224" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/MONOBLOCK SPECIALE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
       </c>
       <c r="J224" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
@@ -11196,7 +11196,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I225" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 73_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2073_main.jpg</v>
       </c>
       <c r="J225" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
@@ -11243,7 +11243,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I226" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 81_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2081_main.jpg</v>
       </c>
       <c r="J226" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
@@ -11290,7 +11290,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I227" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/RHODIUM 63_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2063_main.jpg</v>
       </c>
       <c r="J227" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
@@ -11337,7 +11337,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I228" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani R100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20R100_main.jpg</v>
       </c>
       <c r="J228" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
@@ -11384,7 +11384,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I229" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P200_main.jpg</v>
       </c>
       <c r="J229" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
@@ -11431,7 +11431,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I230" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/Pagani P300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P300_main.jpg</v>
       </c>
       <c r="J230" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
@@ -11478,7 +11478,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I231" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA58_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA58_main.jpg</v>
       </c>
       <c r="J231" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
@@ -11525,7 +11525,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I232" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72_main.jpg</v>
       </c>
       <c r="J232" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
@@ -11572,7 +11572,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I233" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/LAUDA72 LIMITED EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72%20LIMITED%20EDITION_main.jpg</v>
       </c>
       <c r="J233" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
@@ -11619,7 +11619,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I234" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/IP79_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP79_main.jpg</v>
       </c>
       <c r="J234" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
@@ -11666,7 +11666,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I235" t="str">
-        <v>/Users/tommy/Pictures/images/megabass_reels/IP68_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP68_main.jpg</v>
       </c>
       <c r="J235" t="str">
         <v>2026-04-09T16:03:11.194Z</v>

--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -1076,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q235"/>
+  <dimension ref="A1:T235"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.642857142857141" defaultRowHeight="17.6"/>
   <cols>
     <col width="51.6428571428571" customWidth="1" style="1" min="4" max="4"/>
@@ -1166,6 +1166,21 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>market_reference_price</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>player_positioning</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>player_selling_points</t>
         </is>
       </c>
     </row>

--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -488,7 +488,7 @@
         <v>spinning</v>
       </c>
       <c r="I2" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA%20SW_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -509,7 +509,7 @@
         <v>在售</v>
       </c>
       <c r="P2" t="str">
-        <v>在国内外有着出色成绩的STELLA SW加入新的技术后实现进化。XX TOUGH DRAG技术提升卸力性能，INFINITYLOOP技术提升抛投精度，INFINITYXROSS提升齿轮强度和耐久性，ANTI-TWIST FIN减少缠线问题，实现了性能的大幅进化。另外握把握丸做了密封设计，卸力旋钮大直径化等细节部分也做了升级。打磨在海水场合和大物一决胜负所需要的性能，得到这款新生的STELLA SW。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。※4000HG、4000XG：2026年05月预计上市、18000HG、20000PG、25000PG：2026年04月预计上市、5000HG、5000XG、6000PG、6000HG、6000XG、30000：2026年05月预计上市</v>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -547,7 +547,7 @@
         <v>spinning</v>
       </c>
       <c r="I3" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA%20SW_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -568,7 +568,7 @@
         <v>在售</v>
       </c>
       <c r="P3" t="str">
-        <v>NEW STELLA SW和大物对抗时的力量、耐久性以及操作性进一步提升。和旧款产品对比搭载了具有更轻和更强大的收线性能的INFINITY DRIVE，以及能对抗大物并有效抑制卸力发热造成缠线部温度上升的HEAT SINK DRAG。同时，新的X PROTECT设计能有效抵抗水压，过线罗拉在严酷环境下也能保护渔轮，搭载的各种技术实现坚韧的全身防护，完成进化的新款STELLA SW在同类产品中体现了强大性能。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q3" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v>在售</v>
       </c>
       <c r="P5" t="str">
-        <v>作为不断挑战海鲈钓法顶点的高端规格，EXSENCE进一步进化后重新登场。启动和停止的反馈力很出色，对于假饵的波动和轻微的水流变化可以感觉很明显的MGL ROTOR，加上实现顺滑转动手感的金属机身设计。不吝惜搭载了INFINITYXROSS、INFINITYDRIVE、INFINITYLOOP技术，实现了收线强度、抛投性能、卸力性能的大幅进化。来吧，去探索更深远的钓鱼吧，在这里寻找钓海鲈所需要的性能吧。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q5" t="str">
         <v/>
@@ -724,7 +724,7 @@
         <v>spinning</v>
       </c>
       <c r="I6" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER%20SW_main.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -745,7 +745,7 @@
         <v>在售</v>
       </c>
       <c r="P6" t="str">
-        <v>海水钓渔轮追求的【强度】是十分多样性的，严酷环境下使用需要足够刚性和坚韧性，还需要防海水性能，另外强大收线力量也是很重要的。新款TWIN POWER SW搭载了INFINITY DRIVE、HEAT SINK DRAG等来自STELLA SW的技术，在拥有了超越一般水准的收线力量和耐久性后，带来了压倒性信赖感，无论哪种钓法都能让你全身心投入，享受钓鱼的乐趣。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -804,7 +804,7 @@
         <v>在售</v>
       </c>
       <c r="P7" t="str">
-        <v>次世代海鲈专用轮诞生！比旧款轻20g以上，搭载轻量顺滑手感精密齿轮Ⅱ、提升抛投距离的加长线杯、抑制卡顿的静音驱动、值得信赖的防水技术X PROTECT等SHIMANO最新构造。兼顾海鲈钓法的高强度和细腻操作，这款高规格产品请务必感受一下。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q7" t="str">
         <v/>
@@ -842,7 +842,7 @@
         <v>spinning</v>
       </c>
       <c r="I8" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Vanquish CE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Vanquish%20CE_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -863,7 +863,7 @@
         <v>在售</v>
       </c>
       <c r="P8" t="str">
-        <v>作为SHIMANO MGL系列的旗舰产品，适用于技巧型钓法的Vanquish在2026年推出限定的CE规格。和23款Vanquish关注不同的特别领域。正如它的名字COMPETITION EDITION所表示的，它专注于在管理鳟鱼或者鲈鱼比赛中发挥作钓者潜力。它的特色是其出色的感度。它削减了一部分23Vanquish所具备的防水性能，专注降低转动扭矩，彻底打磨实现高感度、高反馈力和收线轻量。直接操作感和信息传达力唤醒快感和感动，有着仿佛可以忽视其存在。从1000到2500一共8个规格。沿袭23款Vanquish的核心技术INFINITYXROSS、INFINITYDRIVE等，追求极致的感度给予比赛型钓友和核心钓友以支持。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q8" t="str">
         <v/>
@@ -960,7 +960,7 @@
         <v>spinning</v>
       </c>
       <c r="I10" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SARAGOSA SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SARAGOSA%20SW_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -981,7 +981,7 @@
         <v>在售</v>
       </c>
       <c r="P10" t="str">
-        <v>HAGANE机身+HAGANE齿轮的组合保证了海水环境作钓的可靠性，无论是面对大型目标时所需要的强大收线力，还是面对小型目标时顺滑的收线手感，都能满足需求。除此之外，X PROTECT+X SHIELD的防水组合让你在严酷的海水环境下能长久使用，高性价比搭配多个规格让你在外出游钓时十分安心。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q10" t="str">
         <v/>
@@ -1078,7 +1078,7 @@
         <v>spinning</v>
       </c>
       <c r="I12" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER XD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TWINPOWER%20XD_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1099,7 +1099,7 @@
         <v>在售</v>
       </c>
       <c r="P12" t="str">
-        <v>MGL系列渔轮发挥碳纤维强化树脂CI4+材质的低惯性旋转盘的特性，在技术性钓法中发挥价值。TWINPOWER XD则是其中注重强度的规格。HAGANE BODY技术给以渔轮厚重感，再加上新搭载的INFINITYXROSS，INFINITYDIRVE技术提升齿轮耐久性和收线强度。新材质的卸力垫片DURACORSS有着出色的耐磨损性能，实现顺滑且安心的卸力。另外INFINITYLOOP提升抛投手感，X-PROTECT减少异物入侵罗拉盘，ANTI-TWIST FIN技术减少缠线问题，即使在艰苦环境下也能放心使用。型号上有从淡海水都能使用的C3000型到适合轻型岸投铁板的C5000型共6个型号。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q12" t="str">
         <v/>
@@ -1137,7 +1137,7 @@
         <v>spinning</v>
       </c>
       <c r="I13" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20XR_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1158,7 +1158,7 @@
         <v>在售</v>
       </c>
       <c r="P13" t="str">
-        <v>EXSENCE CI4+进一步磨练设计，内部功能大幅升级后，就是EXSENCE XR。堪比旗舰规格的性能，在情报量稀少的夜钓中，想必能成为钓手值得信赖的武器吧。这款渔轮带给不断探究海鲈世界的钓手，向着更高高度进发。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q13" t="str">
         <v/>
@@ -1196,7 +1196,7 @@
         <v>spinning</v>
       </c>
       <c r="I14" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC%20SW_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1217,7 +1217,7 @@
         <v>在售</v>
       </c>
       <c r="P14" t="str">
-        <v>搭载INFINITY DRIVE后，轻量转动即可实现强大收线力，保持主导权的同时尽情搏鱼。另外罗拉部采用的X-PROTECT技术有效防止水的入侵并提升了耐久性，让喜爱出海的钓友有了这款强大且坚韧的产品。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q14" t="str">
         <v/>
@@ -1255,7 +1255,7 @@
         <v>spinning</v>
       </c>
       <c r="I15" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20XR_main.jpg</v>
       </c>
       <c r="J15" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1276,7 +1276,7 @@
         <v>在售</v>
       </c>
       <c r="P15" t="str">
-        <v>激烈作钓的情况下对会变得十分依赖渔轮性能，而且根据不同的钓种又有着不一样的需求。NEW Sephia XR具备细腻操控木虾饵的操作性，快速收线的反馈性能，C3000规格的卸力顺滑性也能让你和大型目标搏斗。另外，INFINITYDRIVE有着强有力的收线性能，INFINITYXROSS也提升了齿轮耐久性，而鲨鱼鳍也减少了线在过线环的问题，产品阵容还追加了适合轻木虾的小型C2000S。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q15" t="str">
         <v/>
@@ -1314,7 +1314,7 @@
         <v>spinning</v>
       </c>
       <c r="I16" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STRADIC%20SW_main.jpg</v>
       </c>
       <c r="J16" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1335,7 +1335,7 @@
         <v>在售</v>
       </c>
       <c r="P16" t="str">
-        <v>沿袭上位产品的力量和坚韧，出色的防水性能使其可以在严苛的海水环境作钓。作为实践派渔轮在合适的地方提升了性能。4000型对应轻型钓法，以广受好评的23STRADIC为基础，搭载了INFINITYXROSS、INFINITYDRIVE、ANTI TWIST FIN等技术提升齿轮耐久性并减少缠线问题，追求使用舒适感。5000型~10000型搭载了X TOUGH DRAG，大幅提升了卸力的耐久性、散热性、最大卸力值等，可以应对重型假饵以及和大型目标搏鱼的需求。高性价比的9个型号皆在满足钓友实战中的需求。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q16" t="str">
         <v/>
@@ -1394,7 +1394,7 @@
         <v>在售</v>
       </c>
       <c r="P17" t="str">
-        <v>磨砺4年的沉淀，SHIMANO中等价位段的核心系列SUSTAIN焕新登场。专为近岸海钓和淡水作钓环境所设计，融合了SHIMANO的先进技术，显著提升渔轮的操控性、强度和精准度。作为轻量化（MAGNUMLITE）系列的一员，新款SUSTAIN 搭载了灵敏反应的 MGL 旋转盘，有助于实现精准的拟饵操控。同时，新款也搭载了其他由STELLA下放的旗舰技术，包括：无限驱动技术（INFINITYDRIVE），有效减少齿轮件传动的阻力，实现流畅收线；无限交叉技术（INFINITYXROSS），提高齿轮咬合面的契合度，带来持久的使用强度；致密排线技术（INFINITYLOOP）和防缠线鳍（ANTI-TWIST FIN），优化了线杯的排线效果与控制力，减少缠线并提升抛投性能；最后再配合稳定的新型卸力材料技术（DURACROSS），打造完成这款兼具轻量和坚韧的SUSTAIN，时刻准备以卓越性能迎接每一次抛投。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q17" t="str">
         <v/>
@@ -1432,7 +1432,7 @@
         <v>spinning</v>
       </c>
       <c r="I18" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20XR_main.jpg</v>
       </c>
       <c r="J18" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1453,7 +1453,7 @@
         <v>在售</v>
       </c>
       <c r="P18" t="str">
-        <v>木虾钓法对渔轮会有如何要求呢？反复操控渔轮抽竿的耐久性、持续抽竿所需的轻量性，收线时所需的静肃性，Sephia XR追求着这些要素。我们采用碳纤维强化素材CI4+成型了高强度机身，另外海采用了第二代精密齿轮提升了耐久性和抑制卡顿的静音驱动，另外海搭载加长线杯进一步提升了远投性能，RAGID SUPPORT DRAG也让钓友面对乌贼喷墨时能够柔软对应，请务必体感一下这款专用轮。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q18" t="str">
         <v/>
@@ -1491,7 +1491,7 @@
         <v>spinning</v>
       </c>
       <c r="I19" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare%20XR_main.jpg</v>
       </c>
       <c r="J19" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1512,7 +1512,7 @@
         <v>在售</v>
       </c>
       <c r="P19" t="str">
-        <v>Soare XR通过MGL旋转盘来获得轻快的操作性和高感度，就算细小的咬讯也易感知并顺滑收线。在搭载INFINITYDRIVE维持强有力的转动性能，还采用扭力强的长握把，齿轮搭载INFINITYXROSS也提升了耐久性，还采用了HIGH RESPONSE DRAG让卸力顺滑作用并放出细线，顺着鱼的游动情形出线也能减少细线切线的风险。鲨鱼鳍也能减少渔线从过线环掉下，135g的自重的超精细规格500SPG到强力精细的C2500SHG，总计4种规格。Soare XR适合轻饵作钓，也能帮助钓手更好地掌握钓况。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q19" t="str">
         <v/>
@@ -1550,7 +1550,7 @@
         <v>spinning</v>
       </c>
       <c r="I20" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CARDIFF XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CARDIFF%20XR_main.jpg</v>
       </c>
       <c r="J20" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1571,7 +1571,7 @@
         <v>在售</v>
       </c>
       <c r="P20" t="str">
-        <v>新搭载第二代精密齿轮、静音驱动、加长线杯和X PROTECT等技术，大幅提升了产品性能。另外，通过重新设计后大幅减少了重量，更易感知细微的咬讯，使用轻量假饵也容易抛得远，请享受溪流钓法设计所带来的乐趣。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q20" t="str">
         <v/>
@@ -1609,7 +1609,7 @@
         <v>spinning</v>
       </c>
       <c r="I21" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/COMPLEX XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/COMPLEX%20XR_main.jpg</v>
       </c>
       <c r="J21" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1630,7 +1630,7 @@
         <v>在售</v>
       </c>
       <c r="P21" t="str">
-        <v>对于淡水路亚需要的性能进行升级。采用降低驱动部件摩擦阻力实现强力收线的INFINITYDRIVE技术，提升驱动齿轮耐久性的INFINITYXROSS技术，以及减少过线环部位缠线问题的ANTI-TWIST FIN技术。用很小的力量就能转动渔轮，并且可以快速停止转动，收线轻快感和感度也不作妥协。为每个规格选择合适的卸力，注重细节设计的淡水路亚渔轮。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -1668,7 +1668,7 @@
         <v>spinning</v>
       </c>
       <c r="I22" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare%20XR_main.jpg</v>
       </c>
       <c r="J22" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1689,7 +1689,7 @@
         <v>在售</v>
       </c>
       <c r="P22" t="str">
-        <v>Soare经典规格XR登场，搭载第二代精密齿轮和静音驱动让你转动手把收线时手感更好，顺滑的收线手感让你能更好集中精神判断咬讯。采用加长线杯后提升了抛投距离，搭配新的HIGH RESPONSE DRAG能够快速调整卸力，让你更快应对特殊情况，这次还追加了500PGS规格，让你可以使用小饵攻略。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q22" t="str">
         <v/>
@@ -1701,7 +1701,7 @@
         <v>轻咸高端 / 细腻路亚 / 灵敏操控</v>
       </c>
     </row>
-    <row r="23" xml:space="preserve">
+    <row r="23">
       <c r="A23" t="str">
         <v>SRE1021</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>spinning</v>
       </c>
       <c r="I23" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20SS_main.jpg</v>
       </c>
       <c r="J23" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1747,10 +1747,8 @@
       <c r="O23" t="str">
         <v>在售</v>
       </c>
-      <c r="P23" t="str" xml:space="preserve">
-        <v xml:space="preserve">浓缩木虾钓所需性能的NEW Sephia SS。
-容线量PE0.8号~150m的浅线杯、操作时易握的EVA握丸、RAPID FIRE DRAG等，搭载标准木虾钓渔轮所需的性能。
-以Sephia代表性的红色为基础，采用更华丽的设计，和Sephia鱼竿组合，有着更鲜明的存在感。</v>
+      <c r="P23" t="str">
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q23" t="str">
         <v/>
@@ -1847,7 +1845,7 @@
         <v>spinning</v>
       </c>
       <c r="I25" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPHEROS SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPHEROS%20SW_main.jpg</v>
       </c>
       <c r="J25" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1868,7 +1866,7 @@
         <v>在售</v>
       </c>
       <c r="P25" t="str">
-        <v>搭载了相当于IPX-8级别防水性能的X SHIELD和X PROTECT、以及X-SHIP、HAGANE机身等高端机种才有的技术，让SPHEROWS SW能够对应严酷的海水环境。21新款追加了HAGANE齿轮和碳纤维十字纹垫片，进一步提升了产品耐久性和性价比。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q25" t="str">
         <v/>
@@ -1965,7 +1963,7 @@
         <v>spinning</v>
       </c>
       <c r="I27" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Sephia%20BB_main.jpg</v>
       </c>
       <c r="J27" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1986,7 +1984,7 @@
         <v>在售</v>
       </c>
       <c r="P27" t="str">
-        <v>具备例如浅线杯、RAPID FIRE DRAG、EVA握丸、双手把型号等特性，非常适合木虾钓法。MICROMODULE GEAR Ⅱ，SILENTDRIVE，X PROTECT，加长线杯等技术充实其性能，大幅提升收线手感、防水性能、抛投距离等性能。另外，采用CI4+机身相比前作实现了大幅轻量化。契合Sephia之名且性能优秀的高性价比渔轮诞生。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q27" t="str">
         <v/>
@@ -2024,7 +2022,7 @@
         <v>spinning</v>
       </c>
       <c r="I28" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20BB_main.jpg</v>
       </c>
       <c r="J28" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2045,7 +2043,7 @@
         <v>在售</v>
       </c>
       <c r="P28" t="str">
-        <v>作为海鲈专用规格，EXSENCE系列一直回应着钓友们的高要求。保有BB系列规格惯有的特性，搭载第二代MICROMODULE齿轮和SILENT DRIVE技术，在你夜钓时可以更好地感知水中的情报。另外，机身采用CI4+素材比旧款轻量了15g（20EXSENCE BB 4000MXG对比），搭配加长线杯让你拥有更好的抛投性能。并且，RAPID FIRE DRAG让你在结构位置攻略海鲈时可以快速调整卸力，作为海鲈专用渔轮具备了高规格。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q28" t="str">
         <v/>
@@ -2083,7 +2081,7 @@
         <v>spinning</v>
       </c>
       <c r="I29" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO XR_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20XR_main.jpg</v>
       </c>
       <c r="J29" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2104,7 +2102,7 @@
         <v>在售</v>
       </c>
       <c r="P29" t="str">
-        <v>HAGANE齿轮加上CI4+材质机身，强度和轻量性同时提升了一个档次后全新登场。除此以外，搭载SILENTDRIVE和X-SHIP后，抛投手感和力传达效率也更优秀，4000型仅250g的重量，让你长在时间抛投时也不易感受到疲劳感，整个系列都比旧款大幅减重，让你更舒适作钓。请务必体验一下全新升级后的产品带给你的乐趣吧。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q29" t="str">
         <v/>
@@ -2163,7 +2161,7 @@
         <v>在售</v>
       </c>
       <c r="P30" t="str">
-        <v>ULTEGRA有着优秀的转动性能和耐久性，深受许多钓友的喜爱。追求更加顺滑稳定的CORESOLID系列设计，在以一定速度持续收线或者栓饵等阻大的钓法中发挥其真正价值。通过增加INFINITYXROSS、INFINITYDRIVE、ANTI-TWIST FIN等技术，进一步提高了基本性能，初学者自不必说，经验老道的钓友也会喜欢它的性能。产品阵容包括新登场的C2500SHG在内共11个型号。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q30" t="str">
         <v/>
@@ -2201,7 +2199,7 @@
         <v>spinning</v>
       </c>
       <c r="I31" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Soare%20BB_main.jpg</v>
       </c>
       <c r="J31" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2222,7 +2220,7 @@
         <v>在售</v>
       </c>
       <c r="P31" t="str">
-        <v>专门为轻型钓法设计的型号。发挥细线强度的HI-RESPONSE DRAG搭配浅线杯。C2000的型号通过采用CI4+实现了大幅度的轻量化。充实的性能使您的轻型钓再上一层楼。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q31" t="str">
         <v/>
@@ -2281,7 +2279,7 @@
         <v>在售</v>
       </c>
       <c r="P32" t="str">
-        <v>除了HAGANE相关技术外，搭载SILENTDRIVE和G FREE BODY，让岸投攻略变得更有效率。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q32" t="str">
         <v/>
@@ -2319,7 +2317,7 @@
         <v>spinning</v>
       </c>
       <c r="I33" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPHEROS SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPHEROS%20SW_main.jpg</v>
       </c>
       <c r="J33" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2340,7 +2338,7 @@
         <v>在售</v>
       </c>
       <c r="P33" t="str">
-        <v>SPHEROS SW推出了精巧化规格，拥有不输给大物的强度和坚韧性，核心部位采用冷锻制造的HAGANE齿轮、机身采用铝制HAGANE机身，面对大物时提供给钓友足够的齿轮强度和收线力量。另外手把采用不易卡顿的样式，卸力垫片也是高耐久性的碳纤维素材，让渔轮保持精巧的同时也能放心对抗大物。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q33" t="str">
         <v/>
@@ -2399,7 +2397,7 @@
         <v>在售</v>
       </c>
       <c r="P34" t="str">
-        <v>以轻量转动，追求自身轻量的MGL系列里，诞生了以全世界为目标的MIRAVEL。机身和大型部位采用CI4+材质，达成了超越其级别的轻量化。另外采用静音驱动和旋入式手把可以抑制收线过程中的噪音和晃动。请尝试一下感受轻量所带来的提升吧。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q34" t="str">
         <v/>
@@ -2458,7 +2456,7 @@
         <v>在售</v>
       </c>
       <c r="P35" t="str">
-        <v>SHIMANO全新的NASCI提供更高端的性能和友好的使用手感，凭借INFINITYDRIVE、一体成型导线环和ANTI-TWIST FIN等技术，提供了更平稳力量，减少渔线在作钓过程中可能出现问题的概率，这款渔轮可用于鲈钓、鳟鱼、海鲈、轻型岸钓铁板等不同的钓法，产品规格从500型到5000型，阵容十分丰富。值得信赖的技术和规格，应该能满足初学者和专业玩家的需求。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q35" t="str">
         <v/>
@@ -2496,7 +2494,7 @@
         <v>spinning</v>
       </c>
       <c r="I36" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SOCORRO SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SOCORRO%20SW_main.jpg</v>
       </c>
       <c r="J36" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2517,7 +2515,7 @@
         <v>在售</v>
       </c>
       <c r="P36" t="str">
-        <v>SHIMANO入门级的海水轮，AR-C线杯让你在抛投时出线更顺，增加抛投的距离。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q36" t="str">
         <v/>
@@ -2555,7 +2553,7 @@
         <v>spinning</v>
       </c>
       <c r="I37" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/AERO%20BB_main.jpg</v>
       </c>
       <c r="J37" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2576,7 +2574,7 @@
         <v>在售</v>
       </c>
       <c r="P37" t="str">
-        <v>入门级高性价比的BB规格也全新升级，HAGANE齿轮保证了强度和更好的力传输效率，无论是抛投和搏鱼都能帮助你不少，AR-C线杯的整流出线效果也能更好出线，尽情抛投出去攻略海边巨物吧。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q37" t="str">
         <v/>
@@ -2635,7 +2633,7 @@
         <v>在售</v>
       </c>
       <c r="P38" t="str">
-        <v>AR-C线杯抑制了远投时的缠线问题。并且通过采用SILENTDRIVE和旋钮式手把大幅减轻收线时产生的杂音，提升了收线手感。尤其在用假饵作钓的时候，收线的感度是十分重要的，顺滑的收线性能可以提高使用者对咬讯或者鱼的细微动作的捕捉能力，提高中鱼效率。本次提供了从500至C5000全型号尺寸的商品，以适用于不同的场景和需求。C5000XG型号上采用圆形握把让钓手从各方向都可以轻松握住。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q38" t="str">
         <v/>
@@ -2694,7 +2692,7 @@
         <v>在售</v>
       </c>
       <c r="P39" t="str">
-        <v>入门级钓友的好搭档。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q39" t="str">
         <v/>
@@ -2753,7 +2751,7 @@
         <v>在售</v>
       </c>
       <c r="P40" t="str">
-        <v>具备切实的实钓性能以及合理的价格，获得广大钓手支持的SEDONA系列也终于迎来了全新升级。搭载了在旗舰级产品上，核心进化技术之一的SILENTDRIVE，渔轮内部部件间细微的卡顿、间隙、晃动等问题大幅减少，伴随着顺滑的转动性能和静肃性，让渔轮焕然一新。在路亚作钓时，细腻的收线手感是十分重要的一个因素，让你能更易攻略目标。从轻型的500规格到攻略大物的C5000规格，从初学者到老玩家之间都获得肯定，献给您这款性能优秀且规格丰富的产品。</v>
+        <v>2023年8月预计上市。※500、1000、C2000S、C2000SHG：2023年9月预计上市。※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q40" t="str">
         <v/>
@@ -2812,7 +2810,7 @@
         <v>在售</v>
       </c>
       <c r="P41" t="str">
-        <v>附带渔线！ 高性价比入门款！</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q41" t="str">
         <v/>
@@ -2871,7 +2869,7 @@
         <v>在售</v>
       </c>
       <c r="P42" t="str">
-        <v>搭载抑制缠线问题的AR-C线杯，追求无论是海水还是淡水都能适用的泛用性。采用了这个级别产品从未有过的涂装，加上了演绎高级感的镀金部件。线杯打孔提升时尚感的同时提高轻快感。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q42" t="str">
         <v/>
@@ -2930,7 +2928,7 @@
         <v>在售</v>
       </c>
       <c r="P43" t="str">
-        <v>适合入门玩家使用的路亚钓型号，顺畅的旋转，帮助你更容易感知鱼讯，高刚性结构，支持强力收线；减少故障的设计，让一系列操作更加舒适。全新NEXAVE搭载先进技术，减少卡顿松动的SILTENTDRIVE、减少缠线的ANTI-TWIST FIN，让您享受更愉快的钓鱼体验。产品阵容从1000型到C5000型，目标鱼种从淡水的鲈鱼、鳟鱼，到海水的海鲈、轻海水和沙滩钓等目标鱼。以更亲民的价格实现让人安心的SHIMANO品质。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。※1000、C2000S、C2000SHG：2026年06月预计上市其余型号：2026年05月预计上市</v>
       </c>
       <c r="Q43" t="str">
         <v/>
@@ -2989,7 +2987,7 @@
         <v>在售</v>
       </c>
       <c r="P44" t="str">
-        <v>就算初学者也能安心使用的入门规格，搭载AR-C线杯后出线更顺畅、实现不易缠线的高远投性能，在海水环境下也能使用。低价位的黑色基调搭配亮色系设计，实现了SHIMANO高性价比品质。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q44" t="str">
         <v/>
@@ -3048,7 +3046,7 @@
         <v>在售</v>
       </c>
       <c r="P45" t="str">
-        <v>搭载AR-C线杯，有效提升了抛投性能，从1000至4000的丰富规格让你根据需求和钓况可以选择需要的型号，这是无论新手玩家还是经常出行钓游的发烧友都不容错过一个产品。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q45" t="str">
         <v/>
@@ -3107,7 +3105,7 @@
         <v>在售</v>
       </c>
       <c r="P46" t="str">
-        <v>SIENNA目标是带给所有钓友舒适愉快作钓的一款渔轮，通过三次元解析设计的齿轮实现了顺滑且无卡顿的收线手感。另外，搭载AR-C线杯在抛投时可以减少缠线问题。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q46" t="str">
         <v/>
@@ -3166,7 +3164,7 @@
         <v>在售</v>
       </c>
       <c r="P47" t="str">
-        <v>FX目标是带给所有钓友舒适愉快作钓的一款渔轮，通过三次元解析设计的齿轮实现了顺滑且无卡顿的收线手感。另外，搭载AR-C线杯在抛投时可以减少缠线问题。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
       <c r="Q47" t="str">
         <v/>
@@ -3676,7 +3674,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I56" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Exsence%20DC_main.jpg</v>
       </c>
       <c r="J56" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3735,7 +3733,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I57" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/21%20Antares%20DC_main.jpg</v>
       </c>
       <c r="J57" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3794,7 +3792,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I58" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.jpg</v>
       </c>
       <c r="J58" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3912,7 +3910,7 @@
         <v>drum</v>
       </c>
       <c r="I60" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/19%20CALCUTTA%20CONQUEST%20DC_main.jpg</v>
       </c>
       <c r="J60" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4207,7 +4205,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I65" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="J65" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4325,7 +4323,7 @@
         <v>drum</v>
       </c>
       <c r="I67" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20MD_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20MD_main.jpg</v>
       </c>
       <c r="J67" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4384,7 +4382,7 @@
         <v>drum</v>
       </c>
       <c r="I68" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/26%20CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="J68" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4443,7 +4441,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I69" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/24%20Metanium%20DC_main.jpg</v>
       </c>
       <c r="J69" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4502,7 +4500,7 @@
         <v>drum</v>
       </c>
       <c r="I70" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/21%20CALCUTTA%20CONQUEST_main.jpg</v>
       </c>
       <c r="J70" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4561,7 +4559,7 @@
         <v>drum</v>
       </c>
       <c r="I71" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST_main.jpg</v>
       </c>
       <c r="J71" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4620,7 +4618,7 @@
         <v>drum</v>
       </c>
       <c r="I72" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20SHALLOW%20EDITION_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20SHALLOW%20EDITION_main.jpg</v>
       </c>
       <c r="J72" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4679,7 +4677,7 @@
         <v>drum</v>
       </c>
       <c r="I73" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/23%20Calcutta%20Conquest%20BFS_main.jpg</v>
       </c>
       <c r="J73" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4738,7 +4736,7 @@
         <v>drum</v>
       </c>
       <c r="I74" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST%20FT_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/26%20OCEA%20CONQUEST%20FT_main.jpg</v>
       </c>
       <c r="J74" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4797,7 +4795,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I75" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/25%20ALDEBARAN%20DC_main.jpg</v>
       </c>
       <c r="J75" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5033,7 +5031,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I79" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20BFS_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Aldebaran%20BFS_main.jpg</v>
       </c>
       <c r="J79" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5092,7 +5090,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I80" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20MGL_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20MGL_main.jpg</v>
       </c>
       <c r="J80" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5151,7 +5149,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I81" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium%20SHALLOW%20EDITION_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Metanium%20SHALLOW%20EDITION_main.jpeg</v>
       </c>
       <c r="J81" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5210,7 +5208,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I82" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/20%20Metanium_main.jpg</v>
       </c>
       <c r="J82" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5446,7 +5444,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I86" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Bantam_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Bantam_main.jpg</v>
       </c>
       <c r="J86" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5623,7 +5621,7 @@
         <v>drum</v>
       </c>
       <c r="I89" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J89" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5741,7 +5739,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I91" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC%20MD_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC%20MD_main.jpg</v>
       </c>
       <c r="J91" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5859,7 +5857,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I93" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/21%20Scorpion%20DC_main.jpg</v>
       </c>
       <c r="J93" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -5918,7 +5916,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I94" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20MD%20300_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/25%20Scorpion%20MD%20300_main.jpg</v>
       </c>
       <c r="J94" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6213,7 +6211,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I99" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20MD%20200_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/24%20Scorpion%20MD%20200_main.jpg</v>
       </c>
       <c r="J99" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -6744,7 +6742,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I108" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/24%20SLX%2070_main.jpeg</v>
       </c>
       <c r="J108" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -8632,7 +8630,7 @@
         <v>drum</v>
       </c>
       <c r="I140" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%EF%BC%88300%E7%BA%BF%E6%9D%AF%EF%BC%89_main.jpg</v>
       </c>
       <c r="J140" t="str">
         <v>2026-04-16 22:59:05</v>
@@ -8691,7 +8689,7 @@
         <v>drum</v>
       </c>
       <c r="I141" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%EF%BC%88150%E7%BA%BF%E6%9D%AF%EF%BC%89_main.jpg</v>
       </c>
       <c r="J141" t="str">
         <v>2026-04-16 22:59:19</v>
@@ -8750,7 +8748,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I142" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20CURADO%20DC%20200_main.jpg</v>
       </c>
       <c r="J142" t="str">
         <v>2026-04-16 22:59:23</v>
@@ -8809,7 +8807,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I143" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20DC%EF%BC%88150%E7%BA%BF%E6%9D%AF%EF%BC%89_main.jpg</v>
       </c>
       <c r="J143" t="str">
         <v>2026-04-16 22:59:32</v>
@@ -8927,7 +8925,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I145" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20CURADO%20300_main.jpg</v>
       </c>
       <c r="J145" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -9104,7 +9102,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I148" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/24%20SLX%2070_main.jpeg</v>
       </c>
       <c r="J148" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -9163,7 +9161,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I149" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20XT_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/24%20SLX%20XT%20150_main.jpeg</v>
       </c>
       <c r="J149" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -12349,7 +12347,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I203" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20CURADO%20200_main.jpg</v>
       </c>
       <c r="J203" t="str">
         <v>2026-04-16 23:00:03</v>
@@ -12408,7 +12406,7 @@
         <v>drum</v>
       </c>
       <c r="I204" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J204" t="str">
         <v>2026-04-16 22:58:55</v>

--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T276"/>
+  <dimension ref="A1:T262"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15097,21 +15097,21 @@
         <v>基础规格和低门槛 / 适合淡水、轻盐、备用轮和入门日常使用</v>
       </c>
     </row>
-    <row r="238" xml:space="preserve">
+    <row r="238">
       <c r="A238" t="str">
-        <v>DRE1033</v>
+        <v>DRE5000</v>
       </c>
       <c r="B238">
         <v>2</v>
       </c>
       <c r="C238" t="str">
-        <v>ウインドサーフ 35</v>
+        <v>SILVER WOLF CT SV TW PE SPECIAL</v>
       </c>
       <c r="D238" t="str">
         <v/>
       </c>
       <c r="E238" t="str">
-        <v>2017</v>
+        <v/>
       </c>
       <c r="F238" t="str">
         <v/>
@@ -15120,56 +15120,54 @@
         <v/>
       </c>
       <c r="H238" t="str">
-        <v/>
+        <v>精细,海水</v>
       </c>
       <c r="I238" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J238" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SILVER%20WOLF%20CT%20SV%20TW%20PE%20SPECIAL_main.jpg</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-04-05T14:39:26.663511Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L238" t="str">
-        <v>2026-04-05T14:39:26.663511Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M238" t="str">
-        <v/>
-      </c>
-      <c r="N238" t="str" xml:space="preserve">
-        <v xml:space="preserve">ダイワ独自の防水･耐久テクノロジー「マグシールド」を搭載し、初期性能の維持を追求。初期の滑らかな回転性能が持続することは、雨や波しぶき、風に運ばれる塵や砂など厳しい環境下に置かれる投げリールにとって大きなアドバンテージとなる。軽快な回転性能を支えるエアローターと中空構造のエアベールは、中・近距離での釣りにはもちろん遠投時に投げリールに求められる重要なファクターであるスムーズな巻き感の向上につながる。回転初動が軽いため、止める・動かすに瞬時に対応可能。そして単純な飛距離だけでは成り立たないのが投げリール。トラブルは大敵であり、「35mmストローク」と「クロスラップ」の相乗効果で糸を問わずライントラブルを最少限に抑えることに成功。またハンドルは、ゴミなどが引っ掛かると相当の負荷が掛かることもある投げ釣りにおいて最も使いやすい長さを考慮した85mmロングハンドルを搭載。ノブもTノブを採用し、上位機種に肉薄する充実のスペックに仕上がっている。 | MAGSEALED
-                                                                    ボディとローターの隙間に磁性を持つマグオイルの壁を作り、海水や埃などの侵入をシャットアウトするDAIWA独自の防水構造。 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。</v>
+        <v>黑鲷PE特化</v>
+      </c>
+      <c r="N238" t="str">
+        <v>廣泛對應各種路亞的 PE 線專用機種 / SILVER WOLF CT SV TW PE SPECIAL 是一款能以 PE 線廣泛對應從輕量路亞到重型路亞的全能型款式 / SS MAGFORCE Φ30mm G1 硬鋁合金製 PE 專用 SV 線杯，搭配能將出線性能發揮至極致的 TWS，唯有兼具這兩項性能才能實現未竟之領域 / 引領黑鯛釣手邁向更高境界</v>
       </c>
       <c r="O238" t="str">
-        <v>¥21,500</v>
+        <v>¥56,800</v>
       </c>
       <c r="P238" t="str">
         <v>在售</v>
       </c>
       <c r="Q238" t="str">
-        <v/>
+        <v>獻給黑鯛路亞釣法的專家。廣泛對應各種路亞的 PE 線專用機種。 SILVER WOLF CT SV TW PE SPECIAL 是一款能以 PE 線廣泛對應從輕量路亞到重型路亞的全能型款式。 SS MAGFORCE Φ30mm G1 硬鋁合金製 PE 專用 SV 線杯，搭配能將出線性能發揮至極致的 TWS，唯有兼具這兩項性能才能實現未竟之領域。引領黑鯛釣手邁向更高境界。 除了進一步的小型化，機身框架與齒輪側側板採用鎂合金（Mg），固定板則採用鋁合金（AL），兼顧了輕量化與高剛性。透過搭載 HYPERDRIVE DIGIGEAR，即便齒輪比高達 8.5，仍能長效發揮滑順的轉動性能。 此外，透過出線聲機構，在線張力接近極限邊緣的攻防戰中，以出線聲輔助釣手應戰。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (全金屬) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 本系列在機殼與齒輪側側板（手把側）採用了鎂合金材質，而在握把側的固定板則使用鋁合金壓鑄，並透過高精度的機械切削加工完成，展現出穩固不動的剛性。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■SS MAGFORCE 全新的磁力剎車結構SS MAGFORCE目標實現「更低慣性的線杯」，進一步突破未踏領域。其特性為具備對抗惡劣條件的優異能力，能夠配合不同釣友及各式各樣的情況，兼容性很強的投擲性能。瞬間提升的線杯旋轉反應，使得從小幅度的拋竿中拋出的路亞能夠描繪出低且延伸出去的軌跡擊中瞄準的釣點。 ■SV-CONCEPT SV-CONCEPT（Super Versatile Concept） 徹底對應各類路亞與環境，實現無壓力拋投的舒適體驗。這是一款具備極致通用性的煞車概念，無論近距離精準拋投、中距離搜索還是遠投，都能輕鬆應對。從輕量、中量到重量級路亞，皆能穩定掌控並將拋投可能發生的意外降至最低。由於該系統對釣竿與路亞的相容性極高，不論是在淡水或海水領域，都能在針對多種魚種的釣法中大顯身手。 ※僅限使用 PE 線。因本產品是針對 PE 線進行極致設定調校，若使用延展性較大的尼龍線或碳纖線，可能會對線杯強度造成損害，因此禁止使用。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■HIGH SPEED LEVEL WIND 當釣線以鬆散狀態捲繞在線杯時，在使用 PE 線的情況下，產生的纏線問題尤為明顯。而 HIGH SPEED LEVEL WIND 技術正是為了大幅減少此類問題而設計。其結果能顯著降低捲線平面上，表層線體咬入底層線縫的問題，進而帶來順暢且舒適的實釣性能。 ■G1 硬鋁合金製 φ30mm SV 線杯（PE 專用） 專為 SS MAGFORCE 系統開發的 SV 線杯，能廣泛對應從微型路亞到重型擬餌的重量區間。不僅能隨心所欲地操控小型釣組，更能實現「更遠距離的投射與極其輕巧的落水」。是在極端嚴苛的釣場環境中，不放過任何一條可能上鉤的魚、將其成功獵取的強力武器。 ※本線杯針對 PE 線進行極致設定，由於尼龍線或碳纖線的延展性較大，容易對線杯強度造成損傷，因此禁止使用 PE 線以外的線種。 ■TAPER TWS 為了追求拋投時的釣線釋放阻力降至最低，即「擴展無阻力範圍」，本機搭載了 TAPER TWS。除了擴充無阻力空間，更結合特殊表面處理 DLC 的加乘效應，力求將出線性能發揮至極限。DAIWA 持續鑽研這項獨一無二的技術，不斷追求讓人「想一投再投」的拋投手感。 ■DRAG CLICK DRAG CLICK 是指在與魚搏鬥、釣線被拉出時，能透過聲音判別出線狀態的報警聲機構。 在遊走於釣線張力極限邊緣的攻防戰中，能透過聲音判別出線動作，對釣手而言是極大的優勢。 尤其在使用細號數 PE LINE 的釣法中，這更是不可或缺的必備功能。 ■培林配置位置 小齒輪部：2BB（CRBB） 齒輪軸兩端：2BB（CRBB） 線杯兩端：2BB（CRBB） 機能比較 機能名稱 26SILVER WOLF CT SV TW PE SPECIAL SILVER WOLF SV TW1000XH PE SPECIAL 設計思想 HYPERDRIVE DESIGN HYPERDRIVE DESIGN 導線規系統 錐形TWS 高速導線規系統 TWS 高速導線規系統 剎車系統 SS MAGFORCE SV SV BOOST 線杯徑（mm） φ30 φ34 線杯材質 G1超硬鋁合金 G1超硬鋁合金 捲線量PE 0.6-150/0.8-120 0.6-180/0.8-150 重量（g） 160 185 拉力系統 UTD UTD 手把長度（mm） 85 90 軸承(滾珠/滾輪) 6/1 10/1 發售日期 2026.03</v>
       </c>
       <c r="R238" t="str">
         <v/>
       </c>
       <c r="S238" t="str">
-        <v/>
+        <v>黑鲷路亚PE特化</v>
       </c>
       <c r="T238" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="239" xml:space="preserve">
+        <v>PE细线专用 / 高速回收 / 黑鲷细致操控</v>
+      </c>
+    </row>
+    <row r="239">
       <c r="A239" t="str">
-        <v>DRE1034</v>
+        <v>DRE5001</v>
       </c>
       <c r="B239">
         <v>2</v>
       </c>
       <c r="C239" t="str">
-        <v>アオリマチックBR LT</v>
+        <v>TATULA BF TW</v>
       </c>
       <c r="D239" t="str">
         <v/>
@@ -15178,133 +15176,128 @@
         <v>2026</v>
       </c>
       <c r="F239" t="str">
-        <v/>
+        <v>26 TATULA BF TW</v>
       </c>
       <c r="G239" t="str">
         <v/>
       </c>
       <c r="H239" t="str">
-        <v/>
+        <v>精细,泛用,bass</v>
       </c>
       <c r="I239" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J239" t="str">
-        <v>images/daiwa_reels/アオリマチックBR_LT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20BF%20TW_main.jpg</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-04-05T14:39:33.655150Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L239" t="str">
-        <v>2026-04-05T14:39:33.655150Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M239" t="str">
-        <v/>
-      </c>
-      <c r="N239" t="str" xml:space="preserve">
-        <v xml:space="preserve">AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。 | AIRDRIVE BAIL
-                                                                    ワイヤータイプのAIRDRIVE BAILを採用。ローターユニットのさらなる軽量化を実現するために実釣時における必要強度を維持したまま、大幅軽量化を実現。ベールを含むローターユニットの軽量化により、回転慣性の大幅低減に寄与。回転レスポンスに磨きをかけ、操作性を向上させました。アームレバー部も新形状を採用し、糸絡みを大幅軽減しました。 | ATD TYPE-L
-                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。その初動レスポンスを高めたATD TYPE-L。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
+        <v>BF泛用主力</v>
+      </c>
+      <c r="N239" t="str">
+        <v>源自日本，引領全球 BAIT FINESSE 基準的指標機型 搭載專為 TATULA 設計的 φ30mm 超硬鋁製 BF 線杯 / 僅需設定一次磁力調控旋鈕，即可順應並兼容各種不同的拋投方式，其優異的適應性能正是這款捲線器的最大魅力 / 透過 TWS 的相乘效果，讓釋放出的釣線完全不失速，進而體現將路亞以低彈道、流暢地送往目標點的卓越拋投精準度 / 無論是以 SMALL RUBBER JIG、NO SINKER 為主的輕量軟蟲釣組，或是小型硬餌皆能全面對應</v>
       </c>
       <c r="O239" t="str">
-        <v>¥19,400</v>
+        <v>¥36,300</v>
       </c>
       <c r="P239" t="str">
         <v>在售</v>
       </c>
       <c r="Q239" t="str">
-        <v/>
+        <v>源自日本，引領全球 BAIT FINESSE 基準的指標機型 搭載專為 TATULA 設計的 φ30mm 超硬鋁製 BF 線杯。煞車系統由 K.T.F. 沢村幸弘氏親自參與開發。僅需設定一次磁力調控旋鈕，即可順應並兼容各種不同的拋投方式，其優異的適應性能正是這款捲線器的最大魅力。 透過 TWS 的相乘效果，讓釋放出的釣線完全不失速，進而體現將路亞以低彈道、流暢地送往目標點的卓越拋投精準度。無論是以 SMALL RUBBER JIG、NO SINKER 為主的輕量軟蟲釣組，或是小型硬餌皆能全面對應。 全機搭載能使初期旋轉性能長久維持的 「HYPERDRIVE DESIGN」 技術，且機身框架與齒輪側側板均採用鋁合金材質。即使在高負荷狀態下，也能以令人安心的紮實感、滑順的旋轉性能與剛性，為釣手提供強力支援。 此外，更進一步精進了煞車性能，並搭載出線警示音功能。憑藉全方位的強悍性能，讓您在面對大型鱸魚的挑戰時更加游刃有餘。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■BF-CONCEPT 透過簡易設定，自在投擲“超”輕量級的魚餌 專為超輕量魚餌設計。當你用力晃動竿子進行擲投時，魚餌會以低彈道平穩飛出，而在一般的拋投中，其飛行距離可與紡車捲線器相媲美。這款「DAIWA BF」的一大特點是可以在不重新調整剎車力的情況下，隨意交替使用擲投和拋竿方式。 搭載將細膩釣法性能發揮到極致的BF線杯。為了應對超輕量路亞，這款線杯超級輕量且搭載微型BB。不僅可以靈活操作更小更輕的魚餌，還能實現「更長的拋投距離以及柔和的入水」。在挑戰艱難環境時，它將成為捕捉到最後一條魚的強力武器。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 產品詳情 ■Φ30mm 超硬鋁製 BF 線杯 在執行 BAIT FINESSE 釣法的實戰場域中，實現了 PITCHING 與 CASTING 兩種拋投方式最高水準的兼容性。僅需設定在相同的煞車數值下，即可享受無壓力且舒適的作釣體驗。 ■HYPER ARMED HOUSING 高剛性金屬機殼 機身材質（框架、齒輪側側板）均採用 ALUMINUM 鋁合金打造。透過將機身結構設計得更加緊湊精實，實現了不感重負、卻極其強韌耐用的機體規格。 ■K.T.F. 合作研發 與 K.T.F. 代表——沢村幸弘先生共同開發。身為自 2000 年代中期便率先倡導 BAIT FINESSE 戰術價值的業界先驅，他是至今仍活躍於國內外賽事最前線的「MR. BAIT FINESSE」。為了證明本機能提供頂尖的微拋性能，其合作標誌也特別刻印於產品外盒。 ■DRAG CLICK（出線警示音） 本機搭載了 DRAG CLICK 構造。當與魚搏鬥且釣線被拉出時，能透過音響訊號即時判別煞車的運作狀態。對於追求利用細線來取得對戰優勢的釣法而言，這是不可或缺的核心功能之一。 ■培林配置位置 小齒輪部：2BB（1CRBB） 齒輪軸兩端：2BB（CRBB） 線杯兩端：2BB（1CRBB） 發售時間 2026.03</v>
       </c>
       <c r="R239" t="str">
         <v/>
       </c>
       <c r="S239" t="str">
-        <v/>
+        <v>BF泛用进阶</v>
       </c>
       <c r="T239" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="240" xml:space="preserve">
+        <v>轻饵低弹道 / 微物到小硬饵兼容 / 易控性高</v>
+      </c>
+    </row>
+    <row r="240">
       <c r="A240" t="str">
-        <v>DRE1035</v>
+        <v>DRE5002</v>
       </c>
       <c r="B240">
         <v>2</v>
       </c>
       <c r="C240" t="str">
-        <v>月下美人 X</v>
+        <v>月下美人 BF TW PE SP</v>
       </c>
       <c r="D240" t="str">
         <v/>
       </c>
       <c r="E240" t="str">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F240" t="str">
-        <v/>
+        <v>26 月下美人 BF TW PE SP</v>
       </c>
       <c r="G240" t="str">
         <v/>
       </c>
       <c r="H240" t="str">
-        <v/>
+        <v>精细,海水</v>
       </c>
       <c r="I240" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J240" t="str">
-        <v>images/daiwa_reels/月下美人_X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20BF%20TW%20PE%20SP_main.jpg</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-04-05T14:39:35.787707Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L240" t="str">
-        <v>2026-04-05T14:39:35.787707Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M240" t="str">
-        <v/>
-      </c>
-      <c r="N240" t="str" xml:space="preserve">
-        <v xml:space="preserve">夜に咲く花は、輝きを増し続ける。2005年、DAIWAのラインナップに初めて登場したライトソルトゲーム専用タックル『月下美人』。艶やかに咲くその花のように月下美人は舞い、アングラーは躍動する。身近なターゲットでありながら、時には極めて繊細なアプローチを必要とするアジや、岩陰や藻の切れ目に身を隠し、周囲を警戒しながらベイトが近くに現れるのを待ち続ける老獪な大型メバルを相手に進化してきた月下美人タックル。これからも月下美人は、アングラーと共に進化し、これまでに味わったことのないような悦び、楽しみを提供する。月下美人の艶やかな輝きがライトソルトゲームを照らし続ける。 | 繊細な操作を求められるライトソルトゲーム。24月下美人Xは、巻き感度、操作性、トラブルレス性能を大幅に向上させたライトソルトゲーム専用設計。意のままにルアーを操作することを追求した、次世代スピニングリールの設計思想であるAIRDRIVE DESIGNを採用。軽量ルアーを操作するライトソルトゲームにとって、操作性の向上は魚をキャッチするための大きなメリットとなる。AIRDRIVE DESIGNの基幹テクノロジーであり、巻き出しの軽さと巻き感度に大きく寄与するローターには、ZAION V製のAIRDRIVE ROTORを採用。軽量で低慣性なローターは巻き感度向上に大きく寄与し、繊細なアジのアタリや水流の変化など、水中の情報を感じ取る。また、細糸を多用するライトソルトゲームでは、ライントラブルは大きなストレスとなる。ビスがなく、球体から切り出したかのような形状であるAIRDRIVE ROTOR、そして新形状アームレバーとAIRDRIVE BAILの相乗効果によってトラブルレス性能を向上させ、ストレスから解放する。ドラグには、初動レスポンスを向上させたATD TYPE-Lを採用。ライトライン使用時のラインブレイクを減少させることで、安心したファイトを可能にする。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24月下美人Xは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。</v>
+        <v>轻海水BF特化</v>
+      </c>
+      <c r="N240" t="str">
+        <v>夜裡綻放的花朵，光芒愈發耀眼 / 2005 年，DAIWA 首次推出專為輕海水路亞打造的系列——「月下美人」 / 如同在月光下綻放的艷麗之花般，月下美人舞動著，而釣者的心也隨之躍動 / 面對看似親近、卻有時需要極度細膩操作的目標魚種——如鯵魚（Aji），以及那些藏身於岩縫或海藻間隙、時刻警戒、等待獵物靠近的狡猾岩魚（Mebaru），月下美人系列一路隨之進化</v>
       </c>
       <c r="O240" t="str">
-        <v>¥18,700</v>
+        <v>¥56,800</v>
       </c>
       <c r="P240" t="str">
         <v>在售</v>
       </c>
       <c r="Q240" t="str">
-        <v/>
+        <v>夜裡綻放的花朵，光芒愈發耀眼。 2005 年，DAIWA 首次推出專為輕海水路亞打造的系列——「月下美人」。如同在月光下綻放的艷麗之花般，月下美人舞動著，而釣者的心也隨之躍動。面對看似親近、卻有時需要極度細膩操作的目標魚種——如鯵魚（Aji），以及那些藏身於岩縫或海藻間隙、時刻警戒、等待獵物靠近的狡猾岩魚（Mebaru），月下美人系列一路隨之進化。今後，月下美人也將持續與釣者一同成長，帶來前所未有的悸動與樂趣。她那迷人的光輝，將持續照亮整個輕海水路亞世界。 PE專用的 Bait Finesse 雙軸捲線器，展現巔峰性能。 PE專用的 Bait Finesse 雙軸捲線器，展現巔峰性能。 「月下美人 BF TW PE SPECIAL」是專為 PE 線打造的 Bait Finesse 雙軸捲線器，可輕鬆應對微型路亞的低彈道拋投，並大幅提升遠投性能。 搭載 SS MAGFORCE 專用 Φ28mm G1 鋁合金 PE 專用線杯，以及最大化放線性能的 TWS 系統，兩者結合實現前所未有的釣魚領域，將資深玩家帶向更高境界。 機身進一步小型化，主框架與齒輪側側板採用鎂合金、側蓋部位採用AL鋁合金，兼顧輕量化與高剛性。配備 HYPERDRIVE DIGIGEAR，即使在 8.5 的高速齒比下，也能長時間保持順滑旋轉。 此外，透過煞車出線警示音的設計，讓玩家在與魚的極限拉鋸中，能清楚掌握線張力，精準操作每一次攻防。 建議路亞重量：0.8g～5g 單鉤鉛頭（Jighead） DAIWA 技術 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■SS MAGFORCE 全新的磁力剎車結構SS MAGFORCE目標實現「更低慣性的線杯」，進一步突破未踏領域。其特性為具備對抗惡劣條件的優異能力，能夠配合不同釣友及各式各樣的情況，兼容性很強的投擲性能。瞬間提升的線杯旋轉反應，使得從小幅度的拋竿中拋出的路亞能夠描繪出低且延伸出去的軌跡擊中瞄準的釣點。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 ■ZAION 透過 DAIWA 的獨家技術，以高密度碳纖維成形的碳纖樹脂製成，擁有輕盈、強韌、耐腐蝕特性，重量強度比超過鎂合金，堪稱化不可能為可能的材料。 主要應用於機身、轉盤等主體部件，可兼顧強固與輕量這兩種背道而馳的特性。 產品詳情 ■G1 鋁合金 φ28mm BF 專用線杯（PE 專用） 搭載專為精細釣法打造的 Bait Finesse 專用 BF 線杯，追求極致的細膩操作性能。 開發了 SS MAGFORCE 專用 BF 線杯，與傳統線杯相比，實現更低的慣性，使超輕量路亞拋投更加順暢。 此外，搭載超輕量微型軸承，不僅能輕鬆操作小型路亞與精緻魚鉤，還能達成更遠的距離拋投與輕盈的落水。 即使在嚴苛釣場中，也能確保捕獲每一尾魚，成為可靠的強力武器。 ※ 推薦線量：PE 0.4 號 – 50 m ※ 注意事項： PE 1 號以上的線材，或使用 10g 以上路亞，將超出本款捲線器的適用範圍，請勿使用。 PE 專用線杯：此線杯專為 PE 線設計，高延展性的線材，如尼龍或氟碳線可能對線杯強度造成損害，請勿使用。 ■出線警示音 當釣線在博魚過程中被拉出時，拖曳系統會發出「滴答聲」的結構設計。 在拉鋸對抗中，玩家可以透過聲音清楚判斷拖曳系統的作動，掌握線張力，提升操作精準度。 這項功能對使用細線 PE 線的釣法尤其重要，是不可或缺的實用設計。 ■TWS系統 為了降低拋投時的線材阻力，也就是 擴大「無阻力範圍」，捲線器採用了錐形 TWS。 除了擴大無阻力範圍外，配合 DLC 類鑽碳特殊表面處理，在兩者的相乘下，進一步最大化線材放出的性能。 DAIWA 持續精進這項獨家技術，只為追求令人一次又一次想拋投的順暢手感。 ※ 本線杯專為 PE 線設計，請勿使用 PE 以外的線材。使用其他線材可能因線材伸縮導致線杯變形等風險。 ※ 由於為 Bait Finesse 專用機種，請勿使用強度超過 PE 1 號以上 的線材，否則將超出本款捲線器的適用範圍。 ※ 捲線量僅供參考，實際數值會因製造商、產品及線張力而有所不同。 ※ 收線長度為手柄每轉一圈的收線距離。 發售日期 2025.12</v>
       </c>
       <c r="R240" t="str">
         <v/>
       </c>
       <c r="S240" t="str">
-        <v/>
+        <v>轻海水PE BF特化</v>
       </c>
       <c r="T240" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="241" xml:space="preserve">
+        <v>Ajing根鱼细饵 / PE专用线杯 / 轻海水精细操控</v>
+      </c>
+    </row>
+    <row r="241">
       <c r="A241" t="str">
-        <v>DRE1036</v>
+        <v>DRE5003</v>
       </c>
       <c r="B241">
         <v>2</v>
       </c>
       <c r="C241" t="str">
-        <v>レガリス</v>
+        <v>STEEZ SV LIGHT TW</v>
       </c>
       <c r="D241" t="str">
         <v/>
       </c>
       <c r="E241" t="str">
-        <v>2023</v>
+        <v/>
       </c>
       <c r="F241" t="str">
         <v/>
@@ -15313,66 +15306,63 @@
         <v/>
       </c>
       <c r="H241" t="str">
-        <v/>
+        <v>精细,泛用,bass</v>
       </c>
       <c r="I241" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J241" t="str">
-        <v>images/daiwa_reels/レガリス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20SV%20LIGHT%20TW_main.jpg</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-04-05T14:39:42.740714Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L241" t="str">
-        <v>2026-04-05T14:39:42.740714Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M241" t="str">
-        <v/>
-      </c>
-      <c r="N241" t="str" xml:space="preserve">
-        <v xml:space="preserve">ベストセラースピニングリール「LEGALIS」がフルモデルチェンジ！AIRDRIVE DESIGN ＆ ZAION Vで大幅な進化。新たにボディ&amp;ローターにZAION Vを採用し、剛性と軽量性が大幅UP（LT2500S-XHで、前モデル比▲20g軽量化）ZAION V製AIRDRIVE ROTORでより軽快な「巻く」「止める」操作が可能。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※23LEGALISは、AIRDRIVE ROTOR、AIRDRIVE BAILを搭載。 | AIRDRIVE ROTOR
-                                                                    独自の理論により、球体からそのまま切り出したかのような新形状を導き出し、そこからさらに不要な肉を徹底的に削ぎ落すことで、剛性を維持したまま、大幅な軽量化を実現します。操作性、感度の向上に繋がる巻き出しの軽さが飛躍的に向上しました。</v>
+        <v>旗舰轻量泛用</v>
+      </c>
+      <c r="N241" t="str">
+        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴 / 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化 / 為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品 / 這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」</v>
       </c>
       <c r="O241" t="str">
-        <v>¥12,600 - ¥16,100</v>
+        <v>¥79,500</v>
       </c>
       <c r="P241" t="str">
         <v>在售</v>
       </c>
       <c r="Q241" t="str">
-        <v/>
+        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 「Ultimate Light Versatile」更低、更深。攻略節奏不斷加快 ⸺ 透過讓線杯實現更高的反應性能，「26 STEEZ SV LIGHT TW」達成了更低彈道的拋投軌跡，並進一步提升了拋投精準度。 齒比提供兩種規格：7.8 與系列中最快速的 9.2。齒比 7.8 為兼顧「打點與平捲」兩種釣法的全能款式；而齒比 9.2 則具備每圈收線量 92cm 的高速捲線性能，不僅能提升收線效率，還能迅速收回滯線。在將魚從障礙區拉出的瞬間，亦能發揮出色的控制力。 導線環採用了錐形 TWS 設計，與 SV BOOST 技術產生協同效果，支撐拋投後段的穩定延伸力。 在需要高精度、複雜拋投操作的高壓釣場中，這款「究極輕量多功能型」捲線器，終於達成了完美境界。 不斷進化的 SV LIGHT 2018年，在並木敏成的監修之下，搭載首款 φ32mm SV LIGHT 線杯的 SV LIGHT LTD 誕生。「在追求貼近 BF 機型特性的同時，也想保留 SV 系列優勢」⸺這款捲線器正是將並木的這份想法化為現實的作品。不僅在各種情況下都具備高水準的多功能性能，更展現出 BF 機型的順暢拋投手感。可謂是 BF（Bait Finesse）與 SV 的完美融合。而今，經過八年進化，全新搭載 φ32mm SV LIGHT 線杯的 26 STEEZ SV LIGHT TW 誕生。配備能在拋投後段帶來延伸力的 SV BOOST、全新設計的低慣性線杯、以及具備高出線性能的錐形 TWS，三者相互作用，讓唯一無二的拋投性能昇華至全新境界。「輕量路亞能以極低的拋物線，像箭矢般筆直飛出⸺這種感覺真的太驚人了。」連並木本人也由衷讚嘆。亮點不僅在於卓越的拋投手感，輕量路亞的適應能力也大幅提升。以往必須仰賴 BF 機型才能進行的釣法，如今即使用粗線也能輕鬆應對。同時，對應重量級路亞的能力依舊毫不妥協。這正是所謂的⸺「終極輕量萬用機」。由 26 STEEZ SV LIGHT TW 所提出的，SV CONCEPT（Super Versatile 超泛用理念）迎來了全新的進化形態。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (全金屬) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 本系列在機殼與齒輪側側板（手把側）採用了鎂合金材質，而在握把側的固定板則使用鋁合金壓鑄，並透過高精度的機械切削加工完成，展現出穩固不動的剛性。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座NDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTAIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 ■SV-BOOST BOOST結構的最大特點在於能夠分2個階段伸出的可變電磁感應旋轉底座部分。SV-BOOST 在保留SV CONCEPT的零故障性基礎上，根據線軸轉速瞬時提供兩段最佳的制動力，實現投擲後半段的延展。這一系統在保持舒適性能的同時，也具備出色的遠投性能。拋投時的立起過程在拋投後半段的延展中，對於初速的反捲區域，瞬間發揮最大的制動力以進行控制，然後在中段到後段逐漸減少制動力，實現後半段的延伸。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 產品詳情 ■SV BOOST 透過 SV BOOST × 淺線杯 × 錐形TWS 的協同效應，實現了低彈道且拋投後段延伸性極佳的拋投性能。 即使在稍微用力的拋投中，線也不會浮起；而輕力的拋投時，也能獲得充足的延伸距離。這樣的特性讓釣者能夠從比以往更遠的位置，將誘餌靜悄悄地送入覆蓋區深處或精準的目標點，同時降低入水聲。 這樣的性能，在釣場條件越嚴苛時越能展現其真正價值，最終化為確實的釣獲成果。 ■SV LIGHT 線杯 上滿線後的線杯重量減輕約14.8%（與 24 STEEZ SV TW 相比）。 透過約22%的慣性降低（與 24 STEEZ SV TW 相比），實現了低彈道拋投。 結合低彈道與拋投後段延伸性的表現，讓釣者能夠從更遠的位置進行精準的釣點攻略。 在現今競爭激烈、魚情嚴峻的水域中，拋投與接近角度的差異往往決定釣果。 左圖：24 STEEZ SV TW 右圖：26 STEEZ SV LIGHT TW *以 STEEZ Fluoro X’LINK 12lb 全滿線狀態下比較。 ■G1超硬鋁合金製線杯 G1超硬鋁合金是一種特殊的鋁合金，具有鎂的兩倍以及超硬鋁合金1.3倍的強度。這種超輕量且具有卓越剛性的材料是航空器結構材料和精密儀器等輕量合金中的最高等級。 為了在保持相同強度的同時實現壓倒性的輕量感，G1超硬鋁合金線軸在不進行任何加壓變形加工，僅通過減少厚度來維持足夠的強度。這種輕量帶來的旋轉感受反饋和高剛性帶來的精確旋轉，均達到無與倫比的水準。 ■錐形TWS 在追求提高控制性的同時減少拋投時的放線所產生的阻力，即追求“無阻力範圍的擴展”目標的過程中，搭載了錐形TWS。 除了擴展無阻力範圍外，還結合了特殊表面處理“DLC”，將線放出性能最大化。DAIWA對於其獨有技術也不斷精益求精，持續探求 “令人欲罷不能地想不斷拋投”的拋投手感。 ■HYPERDRIVE DIGIGEAR 首次推出 9.2 齒比版本 新增每轉一圈可回收 92cm 線長的機型。 不僅提升拋投與回收的效率，還能在迅速收回鬆線或將魚從障礙區強行拉離時發揮強大威力。 尤其在快節奏的打點釣法中，更能展現明顯的優勢。 ■注油蓋 隨著無輔助剎車構造，移除了ZERO ADJUSTER。26STEEZ SV LIGHT TW搭載了注油蓋。 使用附屬的專用工具可以取下注油蓋。取下蓋子後，可以對小齒輪滾珠培林進行注油和維護。 ■實心小齒輪 與以往的中空小齒輪相比，透過 UCD（Ultimate Casting Design） 技術實現的實心結構小齒輪，在齒輪強力咬合時具備更高的抗負荷性能。 在相同直徑與齒比條件下，強度提升超過20％。 小齒輪的強化，讓齒輪系統在不依賴加大直徑的情況下，仍能具備高剛性結構，並大幅提升了以高強度著稱的 HYPERDRIVE DIGIGEAR 的旋轉耐久性。 ■ 鋁製星型煞車 搭載以操控性為重點開發的星型煞車，甚至重新設計了內部棘齒結構。在每次調整聲上也精益求精，實現了清脆而細膩的星形煞車調整警示音，帶來更舒適的操作體驗。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能，目標是成為同級別中的No.1。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■培林配置位置 ■對應之可改裝零件 ■對</v>
       </c>
       <c r="R241" t="str">
         <v/>
       </c>
       <c r="S241" t="str">
-        <v/>
+        <v>鲈鱼高端轻量</v>
       </c>
       <c r="T241" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="242" xml:space="preserve">
+        <v>轻量低弹道 / 高精度抛投 / 高压场精细控制</v>
+      </c>
+    </row>
+    <row r="242">
       <c r="A242" t="str">
-        <v>DRE1037</v>
+        <v>DRE5004</v>
       </c>
       <c r="B242">
         <v>2</v>
       </c>
       <c r="C242" t="str">
-        <v>クロスキャスト</v>
+        <v>RYOGA</v>
       </c>
       <c r="D242" t="str">
         <v/>
       </c>
       <c r="E242" t="str">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="F242" t="str">
-        <v/>
+        <v>26 RYOGA</v>
       </c>
       <c r="G242" t="str">
         <v/>
@@ -15381,63 +15371,60 @@
         <v/>
       </c>
       <c r="I242" t="str">
-        <v>spinning</v>
+        <v>drum</v>
       </c>
       <c r="J242" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/RYOGA_main.jpg</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-04-05T14:39:49.593963Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L242" t="str">
-        <v>2026-04-05T14:39:49.593963Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M242" t="str">
-        <v/>
-      </c>
-      <c r="N242" t="str" xml:space="preserve">
-        <v xml:space="preserve">35mmストローク仕様により、カゴ･磯遠投で重要な「飛距離」にこだわったエントリーモデル。エアローター採用により回転性能、遠投の際の巻き取り効率が向上。ライントラブルを軽減するクロスラップはもちろん、大物にも対応する耐久性に優れた「デジギヤⅡ」搭載と、妥協なしのスペック。4000QDは置き竿の釣りで不意の大物が期待できる時などに便利なクイックドラグ搭載モデル。ドラグノブを約1回転するだけで緩める・締めるが可能なドラグ機能で、掛かるまではドラグを緩め、掛かった後は迅速にドラグを締めることができるのでやり取りまでにもたつかない。※ソルト対応 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。 | QUICK  DRAG
-                                                                    瞬時の「クイック」な調整が可能なドラグ。少ないドラグノブの回転で、即座に設定を大きく変えることができる。使用ラインやタックル、釣法に応じて様々に活用可能です。
-                                                                        ※4000QDのみ</v>
+        <v>圆鼓旗舰</v>
+      </c>
+      <c r="N242" t="str">
+        <v>「重視捲線，就非RYOGA不可了 / 」⸺ 那不是選擇，而是信念 / 持續支撐著那份「永不褪色的捲線工藝」 / 延續歷代 RYOGA 一貫堅持，搭載以機械切削工法打造的高精度、高剛性機身「HYPER ARMED HOUSING」，再結合「HYPERDRIVE DIGIGEAR」</v>
       </c>
       <c r="O242" t="str">
-        <v>¥12,000 - ¥13,300</v>
+        <v>¥67,500 - ¥68,000</v>
       </c>
       <c r="P242" t="str">
         <v>在售</v>
       </c>
       <c r="Q242" t="str">
-        <v/>
+        <v>「重視捲線，就非RYOGA不可了！」⸺ 那不是選擇，而是信念。 持續支撐著那份「永不褪色的捲線工藝」。 延續歷代 RYOGA 一貫堅持，搭載以機械切削工法打造的高精度、高剛性機身「HYPER ARMED HOUSING」，再結合「HYPERDRIVE DIGIGEAR」。 兩者的綜效實現了極致的剛性，幾乎徹底消除鬆動，並帶來如絲般順暢又強勁有力的捲線體驗。 100 與 150 兩種尺寸各自擁有明確的煞車設計概念⸺ 100 型採用 SV 概念，150 型採用 LC 概念，兩者皆搭載 BOOST SYSTEM。 100 型（搭載 SV BOOST）能抑制高空氣阻力路亞飛行時的線浮現象，確保穩定的拋投軌跡，在不需施力的情況下，於拋投後段依然能輕鬆延伸飛行距離。 150 型（搭載 MAG-Z BOOST）則能有效抑制中至重量級路亞拋投初期容易出現的過度線軸轉速，穩定路亞姿態，實現如劃破風般的遠投性能。 在齒比設計上極致講究，將「捲線」這個動作昇華至極致境界。 機械切削所造就的雄渾外觀與存在感，成就了鼓式捲線器的巔峰之作。 獻給每一位對「捲線」充滿熱情的釣者，以及所有愛 RYOGA 的粉絲。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■SV-CONCEPT 以可變電磁感應旋轉底座(INDUCT/INDUCTION ROTOR)為核心的DAIWA雙軸捲線器的煞車系統已進入第三代。新增了能夠在SV（FINESS精細方向）中具有優勢的煞車系統，進一步增強遠投性能。通過將傳統的1階的(INDUCT/INDUCTION ROTOR)可變電磁感應旋轉底座改為2階，創新的結構在精細投擲領域中能夠發揮最佳效能。 ※ 僅適用於 SV100 型。 ■SV-BOOST BOOST結構的最大特點在於能夠分2個階段伸出的可變電磁感應旋轉底座部分。SV-BOOST 在保留SV CONCEPT的零故障性基礎上，根據線軸轉速瞬時提供兩段最佳的制動力，實現投擲後半段的延展。這一系統在保持舒適性能的同時，也具備出色的遠投性能。拋投時的立起過程在拋投後半段的延展中，對於初速的反捲區域，瞬間發揮最大的制動力以進行控制，然後在中段到後段逐漸減少制動力，實現後半段的延伸。 ※ 僅適用於 SV100 型。 ■LC-CONCEPT 實現拋投後半段穩定延展的卓越遠投煞車性能概念。特別適合中至重型路亞，隨著釣竿越用力揮出，飛行距離便越長。此外，LC 概念帶來的運動感與爽快的拋投手感，更是其主要魅力所在。 ※ 僅適用於 150 型。 ■MAG-Z BOOST BOOST SYSTEM 將 MAGFORCE-Z 的遠投性能發揮至極限。MAG-Z BOOST 採用以飛距離為重點的設定，專為 MAGFORCE-Z 設計。MAGFORCE-Z 透過離心力操作煞車轉子，因此不適合輕量級路亞，但對中至重量級路亞的遠投卻最為理想，施力越大，飛距離越遠。 BOOST 系統的革命性設計：避開容易失控纏線的區段後，煞車瞬間回位，讓拋投中段到落水都保持順暢飛行，發揮最大遠投性能。 ※ 僅適用於 150 型。 ■ATD ATD（Advanced Tournament Drag）是一種先進的比賽用出線系統，它根據魚的拉力平滑地作出反應，追求平順出線的效果，讓您可以專注搏魚，無需擔心出線力道設置。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 產品詳情 ■運轉耐久性能提升 與 18RYOGA 相比，即使在高負荷或長時間使用下，運轉性能也不易下降。 26RYOGA 搭載的「HYPERDRIVE DIGIGEAR」，在滑順運轉與齒輪耐久性上達到更高水準。 左：18RYOGA 搭載 高強度黃銅製 HYPERMESH GEAR 右：26RYOGA 搭載 高強度黃銅製 HYPERDRIVE DIGIGEAR ■採用機械切削製法的高精度高剛性機身 「重視捲線，就非RYOGA不可了！」。 歷代 RYOGA 一直堅持的機械切削製法，造就了高精度、高剛性的機身。與 HYPERDRIVE 設計相互作用，帶來紮實的手感與順暢的運轉性能，專為重視「捲線手感」的釣者打造。 ■新形狀線杯（150型） 經多次實地測試後，採用了全新的窄型設計。 在線放出時，將角度調整得比以往淺 3.4%，使拋投時的線路更順暢、更輕快。 在線容量充足的同時，透過優化線杯的直徑與寬度平衡，實現了更筆直、更穩定的拋投軌跡。 ■2.0mm厚不鏽鋼製捲線器腳座 講究僅僅 0.5mm 的厚度差，將原本 1.5mm 厚度升級至 2.0mm。 此改良徹底消除了在拋投、高負荷路亞操作及搏魚時可能出現的晃動。 同時，材質也從鋁改為不鏽鋼，確保與海水用鼓式捲線器相同等級的強度。 對細節毫不妥協的設計，成就了堅實可靠的剛性表現。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能，目標是成為同級別中的 No.1。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■培林配置位置 ■對應之可改裝零件 ■線杯相容性 小齒輪部：2BB（CRBB） 齒輪軸兩端：2BB（CRBB） 線杯兩端：2BB（CRBB） 搖臂握把：2BB（每個握把內含1顆不鏽鋼BB） 握丸：可對應 S 尺寸握丸 搖臂：可搭配各式 RCSB 搖臂 RCSB BF 搖臂組／RCSB 曲柄搖臂組／RCSB 碳纖曲柄搖臂／23RCSB 100mm 碳纖曲柄搖臂／RCSB ESD 100mm 曲柄搖臂 100：對應 RCSB1000 線杯系統 150：對應 RCSB1500 線杯系統 產品介紹 品名 說明 SV100 線軸採用 φ34mm G1超級杜拉鋁材質，搭載 SV BOOST 系統，實現輕鬆拋投即可獲得理想飛距離的性能。 即使是拋投時容易產生空氣阻力的「捲動系路亞」，也能透過 SV 概念特有的低拋物線軌跡與高精度拋投，實現穩定、準確的操作。再加上 BOOST 系統，使拋投後段的延伸性進一步提升，無論中、近距離或遠投區域，都能穩定發揮。 對於微型Crankbait、1/4oz級旋轉亮片等阻力較輕的路亞，或淺水區攻略時，更能發揮最佳性能。 齒比提供兩種版本可選：5.3（每轉收線長56cm）與6.3（每轉收線長67cm）。 150 線杯採用 φ36mm 高強度鋁材質，搭載 MAG-Z BOOST 系統。經過多次實地測試驗證各種材質後，最終選用高強度鋁材，以確保中至重量級路亞在竿上穩定運行，同時提供中遠距離所需的慣性力，實現優異的遠投性能。 在線量部分，重新設計線杯形狀，以優化捲線排列。這些改良的相互作用，使 LC 概念 能夠呈現流暢的拋投軌跡及爽快的拋投手感。 齒比提供兩種版本： 5.3（每轉收線長 59cm）：適合深水型 Crankbait、Magnum Crank、大型爬行路亞，以及大型路亞的中層 Dead Walk 和 Cranking 操作。 7.3（每轉收線長 82cm）：滿足深水型 Crankbait拋投時對高速齒比的需求，特別適合操作大型路亞或重型平捲釣法。 在較重負荷的平捲釣法下，也能提供舒適的操作感。值得一提的是，7.3 齒比（150H/HL 型）搭載 100mm 長手柄及 Power Light M 握丸，即使進行快速拉線或高負荷操作，也能輕鬆收線。 此外，為避免大型路亞拋投斷線的風險，此款線杯可支援粗線需求（尼龍 20lb.-100m、PE 4號-100m），並同時滿足海水釣需求的規格。 機能比較 機能名稱 18RYOGA1016 26RYOGA SV100 18RYOGA1520 26RYOGA 150 設計思想 Detective Rotation 設計 HYPERDRIVE DESIGN Detective Rotation 設計 HYPERDRIVE DESIGN 剎車系統 MAG FORCE Z SV BOOST MAG FORCE Z MAG-Z BOOST 機身材質 G1超硬鋁合金 G1超硬鋁合金 G1超硬鋁合金 高強度鋁合金 捲線量(Ib-m) 16-100 12-100 14-90 16-80 20-100 16-125 20-100 25-80 捲線量PE(号-m) 1.5-200 2.0-150 3.0-90 2.0-230 2.0-230 3.0-150 4.0-100 重量 255g 265g 270g P齒輪：285g H齒輪：290g 握丸形狀 高抓握I形輕量握丸 高抓握I形強力大型握丸 高抓握I形強力握丸 P齒輪：高抓握I形強力大型握丸 H齒輪：強力輕量M中型握丸 手把長度 90mm 90mm 90mm P齒輪：90mm H齒輪：100mm 軸承(滾珠/滾輪) 12/1 8/1 12/1 8/1 附屬品 ・使用說明書（日文版） ・使用說明書（四國語言版） ・展開圖 ・問卷登錄 ID 卡 ※ 捲線量僅供參考，實際數值會因製造商、產品及線張力而有所不同。 ※ 收線長度為手柄每轉一圈的收線距離。 ※ 關於拋投時的聲音 搭載 BOOST 結構的線杯，在拋投（路亞飛行）時，可能會聽到煞車轉子（Induct Rotor）復位時發出的「卡嗒」聲。 BOOST 系統中，負責控制煞車力的煞車轉子被設計為比傳統更快、更強地回位，並延長作動行程，以最大化遠投效果。因此，相較於傳統捲線器，誘導轉子的回位聲可能會明顯一些，並非異常現象。 BOOST 採用兩段式作動結構，最多可發生兩次聲音。聲音的大小與發生次數會依拋投時施加的力道不同而有所變化。 發售日期 2025.12＝SV 100 2026.01＝150</v>
       </c>
       <c r="R242" t="str">
         <v/>
       </c>
       <c r="S242" t="str">
-        <v/>
+        <v>高刚性卷收旗舰</v>
       </c>
       <c r="T242" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="243" xml:space="preserve">
+        <v>切削机身 / 卷收强悍 / 中重型路亚与船钓兼顾</v>
+      </c>
+    </row>
+    <row r="243">
       <c r="A243" t="str">
-        <v>DRE1038</v>
+        <v>DRE5005</v>
       </c>
       <c r="B243">
         <v>2</v>
       </c>
       <c r="C243" t="str">
-        <v>レブロス</v>
+        <v>SALTIGA 10</v>
       </c>
       <c r="D243" t="str">
         <v/>
       </c>
       <c r="E243" t="str">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F243" t="str">
-        <v/>
+        <v>25 SALTIGA 10</v>
       </c>
       <c r="G243" t="str">
         <v/>
@@ -15446,63 +15433,60 @@
         <v/>
       </c>
       <c r="I243" t="str">
-        <v>spinning</v>
+        <v>drum</v>
       </c>
       <c r="J243" t="str">
-        <v>images/daiwa_reels/レブロス_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%2010_main.jpg</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-04-05T14:39:55.715342Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L243" t="str">
-        <v>2026-04-05T14:39:55.715342Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M243" t="str">
-        <v/>
-      </c>
-      <c r="N243" t="str" xml:space="preserve">
-        <v xml:space="preserve">新型AIRDRIVE ROTOR+AIRDRIVE BAIL（ワイヤー）+アームレバーによりローターユニットの軽量化を実現し、全体の軽量化に貢献。（2500S-XHで210ｇ　20レブロスLT2500S-H比▲10ｇの軽量化）また、AIRDRIVE ROTORでリール操作の基本である「巻く」「止める」の操作がより軽快になった。※カスタムパーツに関しては、SLPウェブサイト上の製品対応検索システムをご参照ください。 | AIRDRIVE DESIGN
-                                                                    エアドライブデザインは、釣り人が求める意のままにルアーを操作することを追求した次世代スピニングリールの設計思想。エアドライブデザインは、最大4つのテクノロジーで構成されています。巻き出しが軽く、ハイレスポンスな回転を生み出すエアドライブローターの搭載を必要条件とし、軽量、トラブルレスなエアドライブベール、不要な肉を限界まで削ぎ落し、軽量化を突き詰めた薄肉設計のエアドライブスプール、メインシャフトを高精度カラーで支持し、さらにピニオンギアと非接触構造とすることで、高負荷時でも回転ノイズの極めて少ない軽い巻き上げを可能としたエアドライブシャフト。これらの相乗効果とリールの重量バランスの改善により、高次元での操作性を実現します。
-                                                                        ※24REVROSは、エアドライブローター、エアドライブベールを搭載。 | AIRDRIVE BAIL
-                                                                    ワイヤータイプのAIRDRIVE BAILを採用。ローターユニットのさらなる軽量化を実現するために実釣時における必要強度を維持したまま、大幅軽量化を実現。ベールを含むローターユニットの軽量化により、回転慣性の大幅低減に寄与。回転レスポンスに磨きをかけ、操作性を向上させました。アームレバー部も新形状を採用し、糸絡みを大幅軽減しました。</v>
+        <v>近海铁板旗舰</v>
+      </c>
+      <c r="N243" t="str">
+        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚 / 」為了實現釣手的夢想而誕生的「SALTIGA」 / 它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術 / 它的前提是與未知的大物對峙</v>
       </c>
       <c r="O243" t="str">
-        <v>¥10,000 - ¥12,800</v>
+        <v>¥65,000</v>
       </c>
       <c r="P243" t="str">
         <v>在售</v>
       </c>
       <c r="Q243" t="str">
-        <v/>
+        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚。」為了實現釣手的夢想而誕生的「SALTIGA」。它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術。 它的前提是與未知的大物對峙。不斷挑戰裝備的極限，追求各個方面的強度，致力於成為易於使用且性能優越的好夥伴。SALTIGA所肩負的責任是成為確實能夠接近夢想魚的助力。持續實現存在價值，即實現釣手的夢想。其可靠性能支持著世界各地釣手的夢想。 近海鐵板釣的新戰力登場。 近海鐵板系列推出兼具「小型化」與「高強度」的新尺寸！ 為了應對大型青物、根魚以及中深海等嚴苛的離岸鐵板釣場景，SALTIGA 10 以「極致緊湊、極致剛強」為開發目標。 核心性能搭載 HYPERDRIVE DESIGN，全面提升耐用度與操作順暢性，完美覆蓋各種近海釣況。 此次的 SALTIGA 10 在實現 PE1.5號-650m／3號-300m 的驚人收線量同時，成功打造出更加緊湊的小型化設計。 齒輪尺寸與 15 系列相同，最大煞車力在齒比 6.3 時達 11kg（齒比 7.1：9kg）。 體積輕巧、握持舒適，即使長時間操作也不易疲勞，仍能以強悍的力量壓制目標魚，展現近海鐵板釣的真正實力。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING（FULL AL） 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING 應用於本體與導線輪上的防水、耐用技術革命已擴展至滾珠軸承這個對於線杯迴轉有著莫大影響的小零件。DAIWA靠著獨家技術，成功領先世界研製出具備磁油防水功能的滾珠軸承。 透過帶有磁性的液體油膜，使水和異物無法入侵滾珠軸承內部。滾珠軸承不僅可以維持原本的滑順性能，也能在不靠墊圈輔助下大幅減低生鏽、卡鹽、發出異常聲響等問題的發生，提升防水性及耐用度，可長時間維持初始性能。 ■ATD ATD（Advanced Tournament Drag）是一種先進的比賽用出線系統，它根據魚的拉力平滑地作出反應，追求平順出線的效果，讓您可以專注搏魚，無需擔心出線力道設置。 ■PERFECT DOUBLE STOPPER 除了標準的單向止逆裝置外，還搭載了機械式止逆裝置。即使在關鍵時刻其中一側止逆發生反轉，也能不中斷釣魚作業——專為嚴苛釣況下的強悍釣法打造的可靠支援功能。 產品詳情 ■煞車拉出提示音 「以聲音掌握每一刻的緊張對決」 在與大型魚的對抗中，精準的煞車設定至關重要。 當魚突然猛拉時，能透過聲音判斷煞車作動情況，能為釣者帶來極大的操作優勢。 ■拇指持握模組 「持握手法的轉變」 通過分析各種釣手的握持方式，追求更貼合手形的形狀。開發了拇指握持模組，旨在實現更容易握持並減少指頭滑出的拇指置放位置。考慮了拇指在關閉離合器後的位置，顯著提高了舒適性。 這種全新的握持體驗大大改變了以往的“握持”概念。 ■陽極保護 「抗腐蝕，卓越耐用」 陽極保護是一種減緩金屬腐蝕的技術。當金屬腐蝕時，陽極（鋅）會承擔腐蝕。通過將這項技術應用於捲線器上，將腐蝕集中在陽極板上，以保持其耐用性能。 ※圖片為 25 SALTIGA 35。 ■75–85mm 鋁合金曲柄手把臂 「強韌、耐用的鋁合金手把臂」 這款 75–85mm 的鋁合金曲柄手把臂， 長度設定適合用於One-Pitch Jerk釣大青物等，操作順手且兼顧力量與耐久性。 ※出廠時為 85mm。 ■85mm T形把手 「無可比擬的握持感」 專為握持時的貼合感和手感所設計，追求最舒適的握姿，讓收線時的擁有舒適操作感的T形狀把手。 為了更容易搏魚，特別追求了中心的厚度，以方便進行搏魚的相關動作。在拉升時，牢牢握持，展現穩定的收線動作。 ■ 捲線器鎖定 「在垂釣場景中發揮作用的實用功能」 這是一種完全固定捲線器並鎖定捲線器逆轉的機制。 在掛底時，如果強行拉扯，可能不僅會損壞線，還可能損壞齒輪和滾珠軸承。然而，通過使用捲線器鎖定機制，可以將捲線器和齒輪分開，並在不損壞齒輪和滾珠軸承的情況下進行扯斷。 使用方法非常簡單。 1. 將捲線器鎖定切換到「開啟」位置。 2. 關閉離合器。 3. 在這個狀態下，第一次施加張力並拉斷線。 ※將捲線器和齒輪分開是關鍵。 這是一個必不可少的功能，能夠安心、安全地快速應對。 ■φ48mm 大口徑線杯 「專為近海餌鐵板釣設計的最佳線杯尺寸」 比 15 系列更小口徑的 φ48mm 線杯， 可收納 PE1.5號-650m / PE2號-450m / PE3號-300m。 線杯形狀經過精密設計，兼顧放線時對收線速度的影響，達到最佳平衡。 煞車發揮精準，收線順暢，輕鬆收線的同時，也能快速縮短釣距。 ■線杯更換系統 「簡單且方便的線杯更換功能」 只需拆下齒輪箱側的 3 顆側板螺絲，即可輕鬆更換線杯。 準備好備用線杯，可以根據突然的斷線或突發狀況，立即進行線杯更換。 隨附的線杯更換扳手（T8），解開齒輪側蓋的側板螺絲3個，即可拆卸齒輪側蓋。 側板螺絲採完全鬆開也不會掉落的防脫結構，避免丟失的麻煩。 產品附屬配件 ■ 取扱説明書 ■ 問卷登記ID卡 ■ 線杯更換專用扳手（T10） ■ 絨面捲線器收納袋 ■ 腳座墊片 → 用於防止捲線器與釣竿受到刮傷，並提升與各種捲線器座的契合度，防止晃動。 發售日期 2025.10</v>
       </c>
       <c r="R243" t="str">
         <v/>
       </c>
       <c r="S243" t="str">
-        <v/>
+        <v>近海铁板高端</v>
       </c>
       <c r="T243" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="244" xml:space="preserve">
+        <v>小型化高强度 / 近海大物 / 深水铁板取向</v>
+      </c>
+    </row>
+    <row r="244">
       <c r="A244" t="str">
-        <v>DRE1039</v>
+        <v>DRE5006</v>
       </c>
       <c r="B244">
         <v>2</v>
       </c>
       <c r="C244" t="str">
-        <v>ファインサーフ35</v>
+        <v>SALTIGA 35</v>
       </c>
       <c r="D244" t="str">
         <v/>
       </c>
       <c r="E244" t="str">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="F244" t="str">
-        <v/>
+        <v>25 SALTIGA 35</v>
       </c>
       <c r="G244" t="str">
         <v/>
@@ -15511,59 +15495,57 @@
         <v/>
       </c>
       <c r="I244" t="str">
-        <v>spinning</v>
+        <v>drum</v>
       </c>
       <c r="J244" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%2035_main.jpg</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-04-05T14:40:02.769370Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L244" t="str">
-        <v>2026-04-05T14:40:02.769370Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M244" t="str">
-        <v/>
-      </c>
-      <c r="N244" t="str" xml:space="preserve">
-        <v xml:space="preserve">35mmストロークで、投げ釣りの醍醐味である「飛び」にこだわったエントリーモデル。快適に最大の飛距離を出すため、ダイワテクノロジーを惜しみなく投入。中・近距離での釣りにはもちろん、遠投時の巻き感は投げリールに求められる重要なファクター。軽快な回転性能を支えるエアローターは回転初動が軽く、止める・動かすに瞬時に対応。また投げリールの大敵であるライントラブルを最小限に抑えるため「クロスラップ」「ツイストバスターII」を採用。上位機種に肉薄するパフォーマンスで、投げ釣りを始めたい方にも最適な1台。※ソルト対応※ハンドルノブ交換不可 | AIRROTOR
-                                                                    ローターにかかる負荷を分散する独特のアーチ形状は、同等の強度で大幅な軽量化を達成しました。ローターバランスも向上し、レスポンスのよい軽い回転も実現します。 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。</v>
+        <v>近海大物旗舰</v>
+      </c>
+      <c r="N244" t="str">
+        <v>回應大型魚的挑戰，展現真正的強悍力量 鐵板雙軸系列迎來了大型尺寸 / 為了應對更嚴苛的環境，我們在「HYPERDRIVE DESIGN」技術的基礎上進一步強化了基本性能，實現了強大的捲收能力 / 在這一尺寸中，重點考量的最大煞車力達到了「實釣時所預想13公斤」的標準 / 此次，我們選用了「UTD」系統，進一步提升了煞車力的穩定性與持久性</v>
       </c>
       <c r="O244" t="str">
-        <v>¥12,000</v>
+        <v>¥86,500</v>
       </c>
       <c r="P244" t="str">
         <v>在售</v>
       </c>
       <c r="Q244" t="str">
-        <v/>
+        <v>回應大型魚的挑戰，展現真正的強悍力量 鐵板雙軸系列迎來了大型尺寸！為了應對更嚴苛的環境，我們在「HYPERDRIVE DESIGN」技術的基礎上進一步強化了基本性能，實現了強大的捲收能力。在這一尺寸中，重點考量的最大煞車力達到了「實釣時所預想13公斤」的標準。此次，我們選用了「UTD」系統，進一步提升了煞車力的穩定性與持久性。 這款產品配備了適用於大型黃鰭鮪、青魽(平政)、紅魽等大型魚類，以及深場的大口徑線杯，並具備豐富的線容量。在保證大線容量的同時，線杯的直徑、寬度及本體尺寸也經過精心設計，確保釣手能在整天釣魚時保持舒適的使用感。 為提升操作的便利性，本體上設計了「拇指支撐框架」，讓釣手能以更少的力量穩定握住捲線器。此外，新開發的大型握丸符合人體工學設計，便於施力操作。為追求前所未有的耐用性，我們還搭載了陽極保護技術，有效減緩金屬腐蝕的風險。 SALTIGA 35的誕生，是為了幫助釣手突破極限、創造新紀錄「BREAK YOUR RECORD」。這款產品將成為幫助您夢想成真的最強武器。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING(磁油防水滾珠軸承) 應用於本體與導線輪上的防水、耐用技術革命已擴展至滾珠軸承這個對於線杯迴轉有著莫大影響的小零件。DAIWA靠著獨家技術，成功領先世界研製出具備磁油防水功能的滾珠軸承。 透過帶有磁性的液體油膜，使水和異物無法入侵滾珠軸承內部。滾珠軸承不僅可以維持原本的滑順性能，也能在不靠墊圈輔助下大幅減低生鏽、卡鹽、發出異常聲響等問題的發生，提升防水性及耐用度，可長時間維持初始性能。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■煞車警示音 「以聲音支援極限攻防戰」 在與大型魚對抗時，必須進行精準的煞車力調整設定。當魚突然猛衝發力時，透過聲音掌握煞車的啟動狀態，能為釣手帶來巨大的優勢。 ※圖片為22 SALTIGA 15。 ■拇指支撐框架 「從持握的概念，轉向指頭輕觸的創新轉換」 透過分析各類釣手的握法，我們研發出更貼合手型的框架設計，提升握感。這款拇指支撐框架讓釣手能輕鬆進行「拇指操作」（Thumbing），同時有效減少手指滑脫的情況。 我們還考慮到釣手在關閉離合器後拇指的自然位置，大幅提升操作時的舒適感。這項創新設計帶來全新的「掌控」體驗，徹底顛覆了傳統的持握概念。 ※圖片為22 SALTIGA 15。 ■陽極保護技術 「不朽且卓越的耐久性」 陽極保護技術是減緩金屬腐蝕的一種方法，也稱為犧牲陽極技術。其原理是讓陽極材料（如鋅）替代金屬零件承受腐蝕。透過將這項技術應用於捲線器，我們將腐蝕集中於陽極板，從而有效維持整體耐久性能。這是Daiwa捲線器中首次搭載的全新功能。 ■100-110mm 鋁合金曲柄握把臂 「強韌且耐用的鋁合金握把臂」 為了應對深海釣時使用的大重量鐵板或大型魚，我們選擇了100-110mm的握把長度。使用5mm厚的板材設計，提供高剛性，即使在進行強力的擺動或與大型魚搏鬥時，也不會變形，確保捲線穩定。 ※出廠時握把長度為110mm。 ■105mm T型動力握丸 「最大化釣手力量的大型握丸」 105mm的T型旋鈕符合人體工學設計，提升抓握時的舒適感與施力效果。不論在進行攘鐵板或捲收時，都能發揮優異的操作性。 雙軸鐵板的專家清水一成先生從基礎草稿設計並削磨出來的講究形狀。慢鐵是絕對應對，深場的手動快跳也能對應 ■線杯鎖定結構 「在鐵板釣法中發揮作用的切線(LINE CUTT)功能」 此結構可完全固定線杯，防止線杯逆轉。當卡底時，若強拉可能會損傷齒輪或滾珠軸承。透過線杯鎖定機構，您可將線杯與主齒輪分離，安全地進行拉線，避免損傷內部結構。 使用方法： 將線杯鎖定桿切換至「開啟」。 關閉離合器。 在此狀態下拉緊線並進行切割。 重點：確保線杯與齒輪分離，避免損壞齒輪與軸承。 這是一項安全可靠且快速處理卡底問題的必備功能。 ■φ65mm 大口徑線杯 「應對深場與粗線的高容量線杯」 新款65mm大口徑線杯相較15系列更為加大，可容納PE3號600米、PE4號500米、PE6號300米的魚線。此設計使釣手能針對更大型的魚種或深場進行準備。 此外，線杯形狀依然沿用15尺寸的設計，保持線放出時的速度穩定，確保最佳的煞車力表現。線杯的容量變化量經過精密設計，提供流暢的捲線操作與充足的捲線力量。 ■可更換線杯 「簡便且靈活的線杯更換功能」 在35系列中，齒輪側的側蓋螺絲從15系列的3個增加至5個，使本體與側蓋更加穩固。準備備用線杯後，可根據釣況或意外斷線快速更換。 更換步驟： 使用隨附的T10扳手卸下齒輪箱側的5個側板螺絲。 取下齒輪側蓋，即可進行線杯更換。 螺絲採用防脫設計，即使完全鬆開也不會掉落，避免螺絲遺失的麻煩。 ※圖片為22 SALTIGA 15。 品名 說明 35/35L 具備強大捲力的5.1標準齒輪型號 此款標準齒輪型號具有5.1：1的齒比，單次旋轉捲線長度達104厘米，是標準型雙軸鐵板捲線器的典範。 無論是針對大型黃鰭鮪的激烈搏鬥，還是在中大型魚咬鉤瞬間決勝負的搶線操作，抑或是進行深場鐵板及游動丸等高負荷釣況，這款捲線器都能憑藉其強大的捲線扭力發揮關鍵作用。 35H/35HL 高齒比的高速型號 此高速齒輪型號齒比為5.8：1，單次旋轉捲線長度達118厘米。它專為大型魚種的攻擊性釣法設計，在高速反應操作中能有效對付大型鰤魚。此外，在深場釣魚時，隨著PE線放出而線容量減少，捲線長度也會下降，因此這款捲線器可確保誘餌動作精準且連貫，特別適合深場釣魚的需求。 產品附屬配件 ■ 取扱説明書 ■ 問卷登記ID卡 ■ 線杯更換專用扳手（T10） ■ 絨面捲線器收納袋 ■ 腳座墊片 → 用於防止捲線器與釣竿受到刮傷，並提升與各種捲線器座的契合度，防止晃動。 發售時間 2025.05＝35 2025.06＝35L 2025.07＝35H、35HL</v>
       </c>
       <c r="R244" t="str">
         <v/>
       </c>
       <c r="S244" t="str">
-        <v/>
+        <v>重型船钓旗舰</v>
       </c>
       <c r="T244" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="245" xml:space="preserve">
+        <v>深海与大型鱼取向 / 大线容量 / 大号鼓轮</v>
+      </c>
+    </row>
+    <row r="245">
       <c r="A245" t="str">
-        <v>DRE1040</v>
+        <v>DRE5007</v>
       </c>
       <c r="B245">
         <v>2</v>
       </c>
       <c r="C245" t="str">
-        <v>アオリトライアル BR</v>
+        <v>STEEZ LIMITED CT SV TW</v>
       </c>
       <c r="D245" t="str">
         <v/>
       </c>
       <c r="E245" t="str">
-        <v>2023</v>
+        <v/>
       </c>
       <c r="F245" t="str">
         <v/>
@@ -15572,65 +15554,63 @@
         <v/>
       </c>
       <c r="H245" t="str">
-        <v/>
+        <v>精细,bass</v>
       </c>
       <c r="I245" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J245" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20LIMITED%20CT%20SV%20TW_main.jpg</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-04-05T14:40:09.686164Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L245" t="str">
-        <v>2026-04-05T14:40:09.686164Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M245" t="str">
-        <v/>
-      </c>
-      <c r="N245" t="str" xml:space="preserve">
-        <v xml:space="preserve">マニュアルリターン仕様アオリクラッチ搭載アオリクラッチを従来のオートリターン仕様からマニュアルリターン仕様に変更。ハンドル回転時の意図しないクラッチ戻りを防ぎ、より使い易くなった。※アオリクラッチ　アオリイカに違和感なくアジを抱かせることが必要なヤエン釣法に不可欠な機構でフロントとリアのドラグ切り替えを行うためのクラッチのこと。（このリールはフロントとリアに2種類の独立したドラグを備えたリールです。）スプールフリー調整ダイヤルダイヤルは細かいクリック設定で微調整が可能。ATDアオリイカの引きに合わせスムーズに作動し、滑らかに効き続けるドラグ。LC-ABSスプールの軽量化とスプールリップの形状の見直しにより、快適なライン放出性を実現。※BR＝BITE&amp;RUN※ハンドルノブS 交換可。※ソルト対応。 | ATD
-                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。 | LC-ABS（ロングキャストABS)
-                                                                    ABSⅡの接触抵抗を減らす思想はそのままに、接点を前にだすことでよりスムーズなライン放出を実現。リング部が前に出た効果でリング上にラインが乗りにくくなり、従来のABSⅡ以上に約5%の距離UPとトラブルレスの向上に成功しました。LC（=LONG CAST）を実現する次世代のABSスプールです。</v>
+        <v>限量高端精细</v>
+      </c>
+      <c r="N245" t="str">
+        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴 / 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化 / 為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品 / 這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」</v>
       </c>
       <c r="O245" t="str">
-        <v>¥10,300</v>
+        <v>¥82,500</v>
       </c>
       <c r="P245" t="str">
         <v>在售</v>
       </c>
       <c r="Q245" t="str">
-        <v/>
+        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 Evolution of STEEZ 每次投擲都能讓釣友充滿喜悅。 CT = 小巧與耐用概念的集大成，这就是STEEZ LTD CT SV TW。 SV = 具備超高多功能概念系列的最小直徑G1鋁合金製φ30mm CT SV線杯，搭載於LIMITED CT，刻意縮小了線量容量，對最大線量作出限制。 這是為了實現超輕量級、低於5g的鉤餌能夠使用的優秀高轉速性能，達到“極致的高回應性”。 這也是對尋求前所未有低彈道拋投性能的競技釣手們的一種挑戰。 無論是使用10lb至13lb的碳纖維線在多功能領域，還是使用6lb至8lb進入餌輕的領域，這種轉換的吸引力無可比擬。 此外，這款設計也考慮到使用PE線的需求，無論是投擲小型誘餌、頂水誘餌，還是打擊障礙物等，皆能展現最佳匹配。 通過刻意的限制設計，這款低彈道拋投手感展現了CT概念系列中最強的特性。 其TWS不會妨礙線的釋放，並且搭載了在24 STEEZ系列中開發的新型TAPER TWS。 相比傳統尺寸，開口擴大了約46%，這樣不僅提升了放線性能，並且毫無阻礙地實現了卓越的放線效果。 即使是輕微的擺動或僅利用SNAP的簡短投擲，也能實現出色的飛行距離。 無多餘動作，集中精力，精確且多變的應對現代困難的釣魚場景。 在中近距離作戰中，以無比精準的低彈道拋投技術，成功吸引了大量的拋投釣手。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座NDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTAIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■SV CONCEPT 以可變電磁感應旋轉底座(INDUCT/INDUCTION ROTOR)為核心的DAIWA雙軸捲線器的煞車系統已進入第三代。新增了能夠在SV（FINESS精細方向）中具有優勢的煞車系統，進一步增強遠投性能。通過將傳統的1階的(INDUCT/INDUCTION ROTOR)可變電磁感應旋轉底座改為2階，創新的結構在精細投擲領域中能夠發揮最佳效能。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■小巧耐用概念 / 小巧耐用 SV線杯 配備小巧型機身，並搭載φ30mm的G1鋁合金製CT SV線杯。 初速反應優異，能夠涵蓋多功能性能及精細性能。 小直徑設計顯著提升了低彈道的精確度，並且具備比專為餌輕設計的線杯更強的強度與耐久性，能夠應對16lb以上的粗線。 ■ 新型TWS 為了減少拋投時的放線所產生的阻力，即追求“無阻力範圍的擴展”，對DAIWA的獨家技術TWS進行了改進。 除了由於錐形結構帶來的無阻力範圍擴展，還加入了特殊表面處理"DLC"，最大化線釋放性能（如右圖所示）。 與19 STEEZ CT SV TW700（左圖）相比，開口增大了約46%。 DAIWA不僅在進一步改良自家獨特技術，更在不斷追求“令人欲罷不能地想不斷拋投”的拋擲手感。 ■ G1鋁合金線杯 G1鋁合金是一種強度是鎂的2倍，超鋁的1.3倍的特殊鋁合金。 這種超輕且剛性優異的材料，廣泛應用於航空機結構及精密儀器等領域。 為了實現更輕的重量，保持高強度，捲線盤表面經過精細加工，並保持足夠的強度。 輕量感帶來的回應性極高，並且高剛性提供了無與倫比的精確旋轉。 ■捲線後線杯重量比較 捲線後的線杯重量比19 STEEZ CT SV TW減輕了約23%。 藉此減少慣性，實現了低彈道投擲。 ■CT系列最快，捲線每圈長度80cm 搭載CT系列最快的齒輪比8.5。 隨著齒輪比的提升，捲線長度也提升約5%。 無論是打擊、捲收，這款線杯都能適應廣泛的需求。 ■注油蓋 拆下注油蓋即可對齒輪軸部的滾珠軸承進行加油。 請在維護時使用隨附的專用工具卸下注油蓋。重新安裝時，請調整為無間隙狀態。詳細請參見使用 ■新設計的星形煞車結構 採用經過精心設計的斜角形狀手柄，更加適合手指的觸感。 當調整星形煞車時，指尖能夠穩固且舒適地施力。 這樣的設計使得在緊急情況下，放鬆拖力變得更加順滑。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■ PE線兼容性 搭載φ30mm線杯和TAPER TWS設計的STEEZ LTD CT SV TW，具備優秀的PE線兼容性。 可使用1~1.5號PE線進行小餌或NEKO釣組等所謂的“力量餌輕釣法”。 使用雙軸捲線器所特有的快速操作、投擲精度和操控性，無論是在投擲還是繞線方面，都能提供比釣竿投擲更出色的性能。 這款產品無論在線重或線徑上都不受限，CT SV線杯的高回應性將充分發揮。 ■ 滾珠軸承搭載位置 ■ 支援的客製化配件 ■ 線杯互換系統 齒輪軸部：2個CRBB滾珠軸承 齒輪軸兩端：2個CRBB滾珠軸承 捲線盤兩端：2個CRBB滾珠軸承 緩衝軸兩端：2個CRBB滾珠軸承 手柄握把：4個CRBB（每個握把搭載2個） 因為是雙手柄，所以是4個滾珠軸承配置 手柄握把：適配S型握把 手柄：RCSB系列各型 RCSB BF手柄組 / RCSB 曲柄手柄組 / RCSB 碳纖曲柄手柄 / 23RCSB 100mm 碳纖曲柄手柄 / RCSB ESD 100mm曲柄手柄 適配RCSB CT SV700系列線杯。 實釣寫真</v>
       </c>
       <c r="R245" t="str">
         <v/>
       </c>
       <c r="S245" t="str">
-        <v/>
+        <v>鲈鱼高端CT限量</v>
       </c>
       <c r="T245" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="246" xml:space="preserve">
+        <v>精细抛投 / 小体积高反应 / 限量实战与收藏兼顾</v>
+      </c>
+    </row>
+    <row r="246">
       <c r="A246" t="str">
-        <v>DRE1041</v>
+        <v>DRE5008</v>
       </c>
       <c r="B246">
         <v>2</v>
       </c>
       <c r="C246" t="str">
-        <v>クレスト</v>
+        <v>SALTIGA 300</v>
       </c>
       <c r="D246" t="str">
         <v/>
       </c>
       <c r="E246" t="str">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="F246" t="str">
-        <v/>
+        <v>25 SALTIGA 300</v>
       </c>
       <c r="G246" t="str">
         <v/>
@@ -15639,316 +15619,308 @@
         <v/>
       </c>
       <c r="I246" t="str">
-        <v>spinning</v>
+        <v>drum</v>
       </c>
       <c r="J246" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%20300_main.jpg</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-04-05T14:40:13.112571Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L246" t="str">
-        <v>2026-04-05T14:40:13.112571Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M246" t="str">
-        <v/>
-      </c>
-      <c r="N246" t="str" xml:space="preserve">
-        <v xml:space="preserve">LTコンセプトにより大幅軽量化を実現！（前モデル2500番比で、なんとマイナス40ｇの軽量化！）ATD採用によりドラグ性能UP！LC-ABSにより飛距離UP！小型スピニングリール新基準「LT」仕様。LTコンセプトによりこの価格帯で、235ｇ（2500番）を達成！タフデジギア、ATD、LC(ロングキャスト）ABSスプール搭載。ソルト対応。 | LT-Concept
-                                                                    ダイワの軽量＆タフコンセプト。ボディ、スプール、ハンドルといった細部までの徹底した軽量化へのこだわりと、リールの心臓部となるギアとそれを包み込むボディの構造や素材の進化のバランスをトータルで高め続け生まれた、ダイワ小型スピニングの新基準「LT」。 | ATD
-                                                                    魚の引きに合わせスムーズに作動し、滑らかに効き続けるATD。滑り出しと追従性を追求し、ドラグ設定を気にすることなく、ファイトに集中することが可能となりました。</v>
+        <v>近海铁板主力</v>
+      </c>
+      <c r="N246" t="str">
+        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚 / 」為了實現釣手的夢想而誕生的「SALTIGA」 / 它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術 / 它的前提是與未知的大物對峙</v>
       </c>
       <c r="O246" t="str">
-        <v>¥6,400 - ¥8,300</v>
+        <v>¥63,000</v>
       </c>
       <c r="P246" t="str">
         <v>在售</v>
       </c>
       <c r="Q246" t="str">
-        <v/>
+        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚。」為了實現釣手的夢想而誕生的「SALTIGA」。它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術。 它的前提是與未知的大物對峙。不斷挑戰裝備的極限，追求各個方面的強度，致力於成為易於使用且性能優越的好夥伴。SALTIGA所肩負的責任是成為確實能夠接近夢想魚的助力。持續實現存在價值，即實現釣手的夢想。其可靠性能支持著世界各地釣手的夢想。 稱霸近海鐵板 近海鐵板釣捲線器的全面升級，搭載強化的HYPERDRIVE DIGIGEAR。而在搭載排線器的機種中，首次加入了Daiwa的捲線器鎖定機構，完美適應急流的明石海域、瀨戶內海域等近海釣場的所有狀況。SALTIGA 300的HYPERDRIVE DIGIGEAR採用加寬齒幅設計，無論低負荷還是高負荷都能展現順暢且強勁的旋轉性能。此外，它還搭載了HYPER DOUBLE SUPPORT、HYPER TOUGH CLUTCH和HYPER ARMED HOUSING等高規格配置，力求完美。其採用舒適的握持框架設計，提供出色的手感並提升操作穩定性。手柄側邊則配備了陽極保護，專為嚴苛環境打造的SALTIGA 300將成為征服近海鐵板的全新利器。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (全鋁強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING(磁油防水滾珠軸承) 應用於本體與導線輪上的防水、耐用技術革命已擴展至滾珠軸承這個對於線杯迴轉有著莫大影響的小零件。DAIWA靠著獨家技術，成功領先世界研製出具備磁油防水功能的滾珠軸承。 透過帶有磁性的液體油膜，使水和異物無法入侵滾珠軸承內部。滾珠軸承不僅可以維持原本的滑順性能，也能在不靠墊圈輔助下大幅減低生鏽、卡鹽、發出異常聲響等問題的發生，提升防水性及耐用度，可長時間維持初始性能。 ■ATD(拉力調節系統) ATD（Advanced Tournament Drag）是一種先進的比賽用出線系統，它根據魚的拉力平滑地作出反應，追求平順出線的效果，讓您可以專注搏魚，無需擔心出線力道設置。 產品詳情 ■陽極保護技術（※圖片為25SALTIGA 35） 「堅不可摧，無與倫比的耐久性」 陽極保護（Anode Protection）是一種減緩金屬腐蝕的技術，也稱為犧牲陽極。該技術通過讓陽極（如鋅）優先腐蝕，從而保護金屬本體。在捲線器上搭載此技術，旨在集中腐蝕於陽極板，從而提升耐久性。 注意事項： 25SALTIGA 300的陽極保護板無法自行更換。 陽極保護板無法完全防止捲線器所有部位的生鏽和腐蝕。 陽極保護非免維護設計，屬於消耗品，隨著使用會自然腐蝕，屬正常現象。 請勿在陽極保護上塗抹任何塗料，否則會失去防腐功能。 陽極保護板的腐蝕速度會隨使用情況有所不同。請仔細閱讀說明書中的「重要！保養方法」，並在使用後盡早用清水沖洗。 ■同步排線器 「大幅提升放線與制動性能」 同步排線器是一種在釋放釣線時，排線器與釣線位置同步左右移動的機構。其優勢在於降低釣線放出時的阻力，同時提升制動的平滑性。SALTIGA 300進一步參照21 SALTIGA IC，對同步機構進行了結構重組：為實現「緊湊」設計，將以往位於手掌握持側的同步機構改置於手柄側。這一結構變更是達成緊湊設計的關鍵因素之一。 ■捲線器鎖定機構 「適合鐵板釣的快速止線功能」 捲線器鎖定機構可完全固定捲線器，防止其逆轉。在處理掛底等情況時，強行拉扯可能會損壞釣線、齒輪和滾珠軸承，而使用捲線器鎖定機構能將捲線器與小齒輪分離，避免對齒輪和軸承的損害，安全地弄斷釣線。 使用方法簡單： 切換捲線器鎖定桿至「開啟」狀態。 關閉離合器。 在此狀態下施加張力並拉斷釣線。 這種設置可有效弄斷釣線而不影響齒輪和小齒輪連接。 這項功能為安全快捷處理釣線的必備設計。 ※25SALTIGA 300的捲線器鎖定機構適用於3.0號及以下PE釣線。 ■拇指支撐框架 「從握持到拇指支撐的全新設計」 經過分析各類釣者的握持方式，追求更貼合手掌的形狀，開發出易於拇指支撐且減少指頭滑落的拇指支撐框架。該設計在關閉離合器後的拇指位置也經過精心考量，大幅提升舒適度。這種全新支撐體驗，顛覆了傳統「握持」的概念。 ■75-85mm 鋁製手柄 「堅韌耐用的鋁製手柄」 此款75-85mm鋁製手柄設計，適合釣青物時使用，特別適合一拍一收的晃餌節奏。 ※出廠設置為85mm。 ■85mm T形狀強力握丸 「無與倫比的握持感」 這款T形強力握丸專為提供極佳的手感和握持舒適度而設計，特別是在釣魚時的不同拇指位置。無論是晃餌還是收線，都能展現出卓越的操作舒適性。在進行一拍一收等動作時，通過精心設計的握丸，使得可以輕鬆抓住並進行更順暢的操作。此外，在慢鐵釣的提拉過程中，強力握丸可提供穩定的握持，避免抖動，從而實現穩定的拉動效果。適用於從近海鐵板釣到慢鐵釣的各種釣法。 另售選配零件相容 握把旋鈕：適用L尺寸旋鈕 SLPW85-95mm碳纖維握把 RCSB 60-70mm握把套件 RCSB 75-85mm握把套件 SLPW 130mm曲柄握把（NB） SLPW 140mm曲柄握把/BK SLPW 150mm曲柄握把/BK 發售日期 2025.02</v>
       </c>
       <c r="R246" t="str">
         <v/>
       </c>
       <c r="S246" t="str">
-        <v/>
+        <v>近海铁板中大型主力</v>
       </c>
       <c r="T246" t="str">
-        <v/>
+        <v>中大型青物 / 高扭矩 / 船钓鼓轮</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>DRE1042</v>
+        <v>DRE5009</v>
       </c>
       <c r="B247">
         <v>2</v>
       </c>
       <c r="C247" t="str">
-        <v>MR</v>
+        <v>TATULA SV TW 100</v>
       </c>
       <c r="D247" t="str">
         <v/>
       </c>
       <c r="E247" t="str">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="F247" t="str">
-        <v/>
+        <v>25 TATULA SV TW 100</v>
       </c>
       <c r="G247" t="str">
         <v/>
       </c>
       <c r="H247" t="str">
-        <v/>
+        <v>泛用,海水,bass</v>
       </c>
       <c r="I247" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J247" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20SV%20TW%20100_main.jpg</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-04-05T14:40:13.995115Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L247" t="str">
-        <v>2026-04-05T14:40:13.995115Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M247" t="str">
-        <v/>
+        <v>泛用主力</v>
       </c>
       <c r="N247" t="str">
-        <v>お手軽に釣りを楽しめる 軽量＆コンパクトリール。入門機として充実のスペックを搭載。165g 軽量（MR750）でコンパクトリール。コンパクトで握り易いIシェイプノブ、45㎜マシンカットハンドル搭載。※ソルト対応 | 4ボールベアリング+インフィニットストッパー付。最大ドラグ力3kgと充実の基本性能。 | 安定した巻上げ感をもたらす45mmマシンカットハンドル。折りたたみ式なので持ち運びにも便利。</v>
+        <v>TATULA第三代，次世代全球標準隆重登場 / Φ32mm超硬鋁合金線杯，搭載TATULA系列首款SV BOOST，追求真正的多功能性能 / TATULA系列的核心是強韌設計概念，經過砥礪後，大幅提升了基本性能 / 在全球推廣並傾注力量於 HYPERDRIVE DESIGN</v>
       </c>
       <c r="O247" t="str">
-        <v>¥7,000 - ¥7,500</v>
+        <v>¥32,400</v>
       </c>
       <c r="P247" t="str">
         <v>在售</v>
       </c>
       <c r="Q247" t="str">
-        <v/>
+        <v>TATULA第三代，次世代全球標準隆重登場！ Φ32mm超硬鋁合金線杯，搭載TATULA系列首款SV BOOST，追求真正的多功能性能。 TATULA系列的核心是強韌設計概念，經過砥礪後，大幅提升了基本性能。在全球推廣並傾注力量於 HYPERDRIVE DESIGN。 TATULA 第3代的次世代全球標準機型。 兼具安全性和後半段延展性的超級多用途捲線器。 磨練出高性能的基礎，捲線性能大幅提升。 延續 TATULA 系列的核心耐用概念！ DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER ARMED HOUSING (AL) (強力防護外殼-鋁) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■SV-BOOST BOOST結構的最大特點在於能夠分2個階段伸出的可變電磁感應旋轉底座部分。SV-BOOST 在保留SV CONCEPT的零故障性基礎上，根據線軸轉速瞬時提供兩段最佳的制動力，實現投擲後半段的延展。這一系統在保持舒適性能的同時，也具備出色的遠投性能。拋投時的立起過程在拋投後半段的延展中，對於初速的反捲區域，瞬間發揮最大的制動力以進行控制，然後在中段到後段逐漸減少制動力，實現後半段的延伸。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■搭載 φ32mm (寬24mm) 超硬鋁合金線杯 繼20 TATULA SV TW後再度搭載，展現出色的線杯反應性能與投擲能力。無論是 2克級的小餌(small rubber ) 還是 大型餌(Big Bait)，都能穩定實現遠距投擲，展現優異的表現。 ■搭載85mm鋁製曲柄握把及高抓力I型輕量握丸 有助於舒適的捲線體驗。 ※另售選購配件（推薦品項） 握丸：對應S尺寸握丸 握把：RCSB碳纖曲柄把手 （80ｍｍ～95ｍｍ） ：RCSB碳纖曲柄（80ｍｍ,90ｍｍ） ※考量捲線器的尺寸與平衡性，推薦使用 不超過95mm 的握把。 發售時間 2024.12</v>
       </c>
       <c r="R247" t="str">
         <v/>
       </c>
       <c r="S247" t="str">
-        <v/>
+        <v>淡海水泛用主力</v>
       </c>
       <c r="T247" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="248" xml:space="preserve">
+        <v>SV易控 / 一般路亚覆盖广 / 性能均衡</v>
+      </c>
+    </row>
+    <row r="248">
       <c r="A248" t="str">
-        <v>DRE1043</v>
+        <v>DRE5010</v>
       </c>
       <c r="B248">
         <v>2</v>
       </c>
       <c r="C248" t="str">
-        <v>ジョイナス</v>
+        <v>ALPHAS BF TW</v>
       </c>
       <c r="D248" t="str">
         <v/>
       </c>
       <c r="E248" t="str">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="F248" t="str">
-        <v/>
+        <v>25 ALPHAS BF TW</v>
       </c>
       <c r="G248" t="str">
         <v/>
       </c>
       <c r="H248" t="str">
-        <v/>
+        <v>精细,泛用,bass</v>
       </c>
       <c r="I248" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J248" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ALPHAS%20BF%20TW_main.jpg</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-04-05T14:40:21.016336Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L248" t="str">
-        <v>2026-04-05T14:40:21.016336Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M248" t="str">
-        <v/>
-      </c>
-      <c r="N248" t="str" xml:space="preserve">
-        <v xml:space="preserve">新型ボディにより、前作に比べて回転フィーリングが大幅に向上。ギヤには耐久性で定評のあるデジギヤIIを搭載。糸絡みトラブルを激減させて快適な飛距離をもたらすABS II、ツイストバスターIIなど機能も充実。ナイロンラインがスプールに巻いてあるため買ってすぐに釣り場で使える万能スピニングリール。淡水・海水どちらのフィールドでも使用可能。またこのクラスでは新提案となる4500、5000の大型サイズもラインナップ。※ソルト対応。 | ABSⅡ
-                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。 | TWIST BUSTER Ⅱ
-                                                                    ラインローラーにテーパーをかけて、ラインをころがすことにより、ローター回転で発生する糸ヨレを相殺。スピニングリールの宿命といわれた糸ヨレを大幅に解消します。</v>
+        <v>BF进阶主力</v>
+      </c>
+      <c r="N248" t="str">
+        <v>無與倫比、全方位的雙軸細膩釣組性能 進一步發揮細膩釣組性能，搭載“SS MAGFORCE”的ALPHAS系列登場 / 實現了前所未有的低彈道且延展力十足的投擲性能，並具備順暢的迴轉效果，以及堅固且簡約的結構，成為高標準的細膩釣組機型 / 其特點在於： 全新搭載的 G1超硬鋁合金製φ30mm細膩釣組線杯，透過搭配“SS MAGFORCE”的乘數作用，達到與超小口徑φ28mm AIR線杯匹敵的自重 / “SS MAGFORCE”煞車系統甚至顛覆了以往大口徑線杯的缺點，能徹底發揮線杯性能，再結合 TWS（T-Wing System） 最大化釋放拋線量，帶來獨特的投擲手感</v>
       </c>
       <c r="O248" t="str">
-        <v/>
+        <v>¥51,900</v>
       </c>
       <c r="P248" t="str">
         <v>在售</v>
       </c>
       <c r="Q248" t="str">
-        <v/>
+        <v>無與倫比、全方位的雙軸細膩釣組性能 進一步發揮細膩釣組性能，搭載“SS MAGFORCE”的ALPHAS系列登場。 實現了前所未有的低彈道且延展力十足的投擲性能，並具備順暢的迴轉效果，以及堅固且簡約的結構，成為高標準的細膩釣組機型。 其特點在於： 全新搭載的 G1超硬鋁合金製φ30mm細膩釣組線杯，透過搭配“SS MAGFORCE”的乘數作用，達到與超小口徑φ28mm AIR線杯匹敵的自重。“SS MAGFORCE”煞車系統甚至顛覆了以往大口徑線杯的缺點，能徹底發揮線杯性能，再結合 TWS（T-Wing System） 最大化釋放拋線量，帶來獨特的投擲手感。這款小烏龜將引領眾多細膩釣組玩家探索更廣闊的領域。 儘管這是一個擅長細膩釣組性能的系列，但始終不變的是專為追求大魚而設計的細膩捲線器的本質。作為次世代細膩機型，它實現了細膩捲線器設計理念“HYPERDRIVE DESIGN”。無論是淡水還是海水使用都能勝任，採用全金屬外殼，主結構、齒輪側面板和旋鈕側面板均使用鋁合金，實現了輕量與剛性兼具的結構。並且，期待已久的拖拉拉出點擊功能也已搭載。 在手掌側，進一步的薄型化實現了壓倒性的輕巧感。投擲精確度、操作性以及與手部的完美契合，提升了釣具操作的便捷性，並且穩定的投擲姿勢和竿的感受，隨時支持應對變化的環境。即使是調節旋鈕也經過徹底檢驗，追求大口徑帶來的調整便捷性與誤作動防止的平衡。 考量到在各種場域的使用，提供兩種齒輪比選擇。齒輪比6.3適合於溫暖的環境，特別適合小型餌、極小的I型餌，能穩定地提供直線性與流暢的回收。齒輪比8.5則完美支援各種細膩釣組的線張力控制，確保低彈道與迅速回收的無比準確。細膩釣組性能已經達到無懈可擊的陣容。 INDUCT ROTOR (可變電感旋轉底座) 比較 直徑約小14 % 重量減輕約27% ※所有值均在 20ALPHAS AIR TW 和 25ALPHAS BF 之間進行比較。 產品詳情 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座INDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 此外，24 STEEZ SV TW終於去除了「機械煞車結構」，實現了絕對精確的ZERO設定。不再需要依賴效果不穩定的機械式動作為輔助煞車，設定的不確定性和麻煩也完全消除了。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■BF CONCEPT 透過簡易設定，自在投擲“超”輕量級的魚餌 專為超輕量魚餌設計。當你用力晃動竿子進行擲投時，魚餌會以低彈道平穩飛出，而在一般的拋投中，其飛行距離可與紡車捲線器相媲美。這款「DAIWA BF」的一大特點是可以在不重新調整剎車力的情況下，隨意交替使用擲投和拋竿方式。 搭載將細膩釣法性能發揮到極致的BF線杯。為了應對超輕量路亞，這款線杯超級輕量且搭載微型BB。不僅可以靈活操作更小更輕的魚餌，還能實現「更長的拋投距離以及柔和的入水」。在挑戰艱難環境時，它將成為捕捉到最後一條魚的強力武器。 ■SS MAGFORCE 全新的磁力剎車結構SS MAGFORCE目標實現「更低慣性的線杯」，進一步突破未踏領域。其特性為具備對抗惡劣條件的優異能力，能夠配合不同釣友及各式各樣的情況，兼容性很強的投擲性能。瞬間提升的線杯旋轉反應，使得從小幅度的拋竿中拋出的路亞能夠描繪出低且延伸出去的軌跡擊中瞄準的釣點。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■φ30mm G1超硬鋁合金製BF線杯 首款專為SS MAGFORCE設計的φ30mm G1超硬鋁合金製BF線杯。為了超越之前徹底輕量化的φ28mm AIR線杯，SS MAGFORCE的引入使得我們對線杯的形狀進行了大幅度的重新設計。結果，25ALPHAS BF TW系列搭載的線杯由φ28mm擴大至φ30mm，但線杯元件的自重幾乎保持不變。 ■SS MAGFORCE（簡潔迅速的MAGFORCE） 全新的剎車系統，能夠在輕巧的揮竿中發揮出舒適的低彈道投擲性能。從零開始重新審視傳統結構，實現了壓倒性的輕量化和低慣性化，專為細線釣組設計的系統。極限追求側板內部和線杯元件的死角空間的輕巧化。能夠輕鬆發力進行投擲，實現比以往更高精度的投擲。透過SS MAGFORCE的設計，傳統結構的死角部分得以縮小，與20ALPHAS AIR TW相比，側板薄型化了6%。更加容易握持，變得更為輕巧。 ■KTF開發合作 與K.T.F.代表澤村幸弘氏的共同開發。自2000年代中期以來，他一直提倡貝特精釣的有效性，是這一領域的先驅，至今仍在國內外賽事中發光發熱，被稱為“Mr.貝特精釣”。為了提供最佳的貝特精釣性能，化妝盒上刻有其印記。 ■鋁製注油蓋 25ALPHAS BF TW搭載了鋁製注油蓋。出廠時進行了線杯零間隙設置（微小間隙約0.2mm），因此不需要調整機械剎車。使用隨附的專用工具可以拆卸蓋子，拆卸後可對小齒輪球軸承進行注油和維護。 ■拖曳聲音提示 搭載了備受期待的拖曳聲音提示。在與魚搏鬥時，當線被拉出時，拖曳裝置會發出聲音，方便判別剎車的運作。使用細線能夠在遊戲展開中佔得有利地位，這是一項必不可少的結構。 ■配備6BB 滾珠軸承 、小齒輪部分2BB(CRBB) 、齒輪軸兩端2BB(CRBB) 、線軸兩端2BB(CRBB) ■使用環境：海水對應 發售時間 2024.12</v>
       </c>
       <c r="R248" t="str">
         <v/>
       </c>
       <c r="S248" t="str">
-        <v/>
+        <v>BF进阶泛用</v>
       </c>
       <c r="T248" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="249" xml:space="preserve">
+        <v>轻饵投掷友好 / G1线杯 / 细腻操控</v>
+      </c>
+    </row>
+    <row r="249">
       <c r="A249" t="str">
-        <v>DRE1044</v>
+        <v>DRE5011</v>
       </c>
       <c r="B249">
         <v>2</v>
       </c>
       <c r="C249" t="str">
-        <v>リーガル PE付</v>
+        <v>STEEZ SV TW</v>
       </c>
       <c r="D249" t="str">
         <v/>
       </c>
       <c r="E249" t="str">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="F249" t="str">
-        <v/>
+        <v>24 STEEZ SV TW</v>
       </c>
       <c r="G249" t="str">
         <v/>
       </c>
       <c r="H249" t="str">
-        <v/>
+        <v>泛用,bass</v>
       </c>
       <c r="I249" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J249" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20SV%20TW_main.jpg</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-04-05T14:40:27.535715Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L249" t="str">
-        <v>2026-04-05T14:40:27.535715Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M249" t="str">
-        <v/>
-      </c>
-      <c r="N249" t="str" xml:space="preserve">
-        <v xml:space="preserve">軽さと剛性の高さを両立した新型ボディにインフィニットストッパーを搭載することで、巻心地はしっかり＆滑らか。PEラインがはじめからスプールに巻いてあるため、買ってすぐに釣り場で使える点もメリット。高剛性のデジギヤII、ライントラブルを激減させて快適な飛びをもたらすABS II、クロスラップ、ツイストバスターIIなどのダイワテクノロジーを豊富に搭載した充実の仕様。ブラックですっきりまとめられたデザインは様々なロッドに違和感なくマッチする。もちろん淡水・海水どちらのフィールドでも使用可能。 | ABSⅡ
-                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。</v>
+        <v>旗舰泛用</v>
+      </c>
+      <c r="N249" t="str">
+        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴 / 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化 / 為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品 / 這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」</v>
       </c>
       <c r="O249" t="str">
-        <v/>
+        <v>¥77,200</v>
       </c>
       <c r="P249" t="str">
         <v>在售</v>
       </c>
       <c r="Q249" t="str">
-        <v/>
+        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 Pride of STEEZ 第三世代STEEZ 開始啟動 STEEZ的雙軸捲線器，以2mm為單位有不同線杯徑規格。 φ28mm（AIR） φ30mm（CT） φ34mm（LIMITED・AⅡ） φ36mm（HLC） 而填補長久以來空缺的Φ32mm，是多功能型。搭載φ32mm SV BOOST線杯的第三代STEEZ SV TW，是完成次世代雙軸捲線器戰略藍圖的關鍵作品。 這第三代產品沒有Zero Adjuster（舊有的機械煞車）。早在第二代16STEEZ時，DAIWA捲線器已經只依賴MAGFORCE旋鈕來完成剎車調整。而第三代則完全去除了傳統的機械剎車結構，變成了全新的無輔助剎車構造。 其高剛性且簡約的外殼內安裝了掌管“捲收和耐久性”的HYPERDRIVE DESIGN。 拋投性能也大幅提升，G1超硬鋁合金φ32mm SV BOOST線杯、TWS、無輔助剎車結構，這些設計均遵循了DAIWA長年追求並最終完成的“拋投設計理念”ULTIMATE CASTING DESIGN。 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來得咬訊或青物暴衝時也能安心應對。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座INDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 此外，24 STEEZ SV TW終於去除了「機械煞車結構」，實現了絕對精確的ZERO設定。不再需要依賴效果不穩定的機械式動作為輔助煞車，設定的不確定性和麻煩也完全消除了。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 產品詳情 ■新型TWS 在追求提高控制性的同時減少拋投時的放線所產生的阻力，即追求“無阻力範圍的擴展”目標的過程中，DAIWA對其獨有技術TWS（T-Wing系統）進行了改進。 在DAIWA的小烏龜捲線器中，根據不同的線杯尺寸，使用相應適配的TWS。 此次為新型線軸尺寸設計的TWS（照片左），引入了全新開發的錐形設計。 在比較新型TWS尺寸中錐形設計開口部時，結果顯示擴展了27%。與16STEEZ SV TW搭載的TWS（照片右）相比，即便橫幅縮小，仍實現了開口部16%的擴展。 除了擴展無阻力範圍外，還結合了特殊表面處理“DLC”，將線放出性能最大化。 根據錐形設計有無的飛距離測試結果顯示，在配重7克時，飛距離最多提升了4.9%。 DAIWA即使對於其獨有技術也不斷精益求精，持續探求 “令人欲罷不能地想不斷拋投”的拋擲手感。 ■G1超硬鋁合金製線杯 G1超硬鋁合金是一種特殊的鋁合金，具有鎂的兩倍以及超硬鋁合金1.3倍的強度。這種超輕量且具有卓越剛性的材料是航空器結構材料和精密儀器等輕量合金中的最高等級。 為了在保持相同強度的同時實現壓倒性的輕量感，G1超硬鋁合金線軸在不進行任何加壓變形加工，僅通過減少厚度來維持足夠的強度。這種輕量帶來的旋轉感受反饋和高剛性帶來的精確旋轉，均達到無與倫比的水準。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。 ■注油蓋 隨著無輔助剎車構造，移除了ZERO ADJUSTER。24STEEZ SV TW搭載了注油蓋。 使用附屬的專用工具可以取下注油蓋。取下蓋子後，可以對小齒輪滾珠培林進行注油和維護。 ■全新設計的星形煞車結構 為了追求操作性，搭載了新形狀的星型煞車裝置（照片右）。相比傳統的星型煞車裝置（照片左），新形狀設計更為薄型化，並重新檢視了舊型結構。甚至在每次調整聲上也精益求精，實現了細微而清晰的星形煞車調整提示音。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能，目標是成為同級別中的No.1。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■HYPER ARMED HOUSING（全金屬結構）本系列產品本體和齒輪側板（手柄側）採用了鎂金屬；而在調整旋鈕側側板則採用了高強度壓鑄成型的鋁合金，加上經過精密的機械切割加工，從而展現出堅不可摧的剛性。 ■產品對應客製零件 握丸：對應S尺寸握丸 握把：RCSB各種握把 RCSB BF握把組 RCSB 曲柄握把組 RCSB 碳纖曲柄握把組 23RCSB 碳纖曲柄握把組 RCSB ESD 100mm曲柄握把組 ■線杯互換系統 目前沒有有互換性的線杯。 ■附屬品 ・使用說明書 ・展開圖 ・問卷登錄ID號碼卡 ・捲線器盒（有STEEZ LOGO） ・捲線器腳部用保護貼紙 ※對應海水 ※捲線量是大概。依據製造商、品項、張力會有不同。 ※捲收長度是握把轉一圈的長度。</v>
       </c>
       <c r="R249" t="str">
         <v/>
       </c>
       <c r="S249" t="str">
-        <v/>
+        <v>鲈鱼旗舰泛用</v>
       </c>
       <c r="T249" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="250" xml:space="preserve">
+        <v>SV抛投稳定 / 高端鲈鱼主线 / 适配面广</v>
+      </c>
+    </row>
+    <row r="250">
       <c r="A250" t="str">
-        <v>DRE1045</v>
+        <v>DRE5012</v>
       </c>
       <c r="B250">
         <v>2</v>
       </c>
       <c r="C250" t="str">
-        <v>タマンモンスター</v>
+        <v>TATULA TW 100</v>
       </c>
       <c r="D250" t="str">
         <v/>
       </c>
       <c r="E250" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="F250" t="str">
-        <v/>
+        <v>24 TATULA TW 100</v>
       </c>
       <c r="G250" t="str">
         <v/>
       </c>
       <c r="H250" t="str">
-        <v/>
+        <v>泛用,海水,bass</v>
       </c>
       <c r="I250" t="str">
-        <v>spinning</v>
+        <v>baitcasting</v>
       </c>
       <c r="J250" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20TW%20100_main.jpg</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-04-05T14:40:29.654844Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L250" t="str">
-        <v>2026-04-05T14:40:29.654844Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M250" t="str">
-        <v/>
-      </c>
-      <c r="N250" t="str" xml:space="preserve">
-        <v xml:space="preserve">大型遠投リールとして実績の高い「ウィンドキャスト6000」をベースに、大型タマン（ハマフエフキ）とのガチンコ勝負にも負けないタフな仕様にブラッシュアップ。ロングストローク35mm正テーパーアルミスプールが確かな遠投性能をもたらし、デジギヤII、85mmロングハンドル＆パワーノブなどで力強い巻き上げが可能。パワーと遠投性能をバランスよく兼備した、タマン専用リールの決定版。 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。 | AIRBAIL
-                                                                    ラインがラインローラーまで流れるように送り出される凹凸のない滑らかなベール形状により、糸ガラミトラブルを大幅に減少します。さらにベール自体を中空構造にしたことで、重量を変えずに大幅な強度アップを実現しました。</v>
+        <v>入门进阶主力</v>
+      </c>
+      <c r="N250" t="str">
+        <v>「TATULA系列慶祝10周年 / 」 迎接下一個10年的第三代TATULA登場 / 全新的TATULA首次搭載了「HYPERDRIVE DESIGN」於TATULA TW 100系列 / 進一步提升TATULA系列的核心概念和基本性能，基本性能大幅提升</v>
       </c>
       <c r="O250" t="str">
-        <v/>
+        <v>¥23,300</v>
       </c>
       <c r="P250" t="str">
         <v>在售</v>
       </c>
       <c r="Q250" t="str">
-        <v/>
+        <v>「TATULA系列慶祝10周年！」 迎接下一個10年的第三代TATULA登場！ 全新的TATULA首次搭載了「HYPERDRIVE DESIGN」於TATULA TW 100系列！ 進一步提升TATULA系列的核心概念和基本性能，基本性能大幅提升！ 將全球化的「HYPERDRIVE DESIGN」引入並注重的模式！ DAIWA 技術 ■HYPERDRIVE DESIGN 強力、滑順回準的永續，雙軸捲線器所需性能的集大成。從驅動齒輪到小齒輪，不間斷的傳導動能的動力裝置。從外側確實的持續支持驅動不，實現穩定且安靜驅動力的機殼。在任何環境下都能座動的多性能結構。實現高效率且遠遠超越寄往捲線力量及滑順迴轉性能的雙軸捲線器設計概念。以經驗為武器的DAIWA，創造初次世代的標準。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長嘯基本維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 ■ZERO ADJUSTER 首先，通過調整“ZERO ADJUSTER”並執行“零間隙”設定，通過磁煞的進步，可以僅通過磁煞調節來控制所有路亞。 “ZERO ADJUSTER”可在開始釣魚之前進行“零設定”，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※“零間隙”設定指的是在保留微小間隙（約0.2mm）的情況下，將捲線器設置在不會發生滑動的模式。 產品詳情 ■煞車特性 搭載MAGFORCE-Z磁性剎車系統。保持著磁力結構的MAGFORCE不變，通過根據線杯轉速平滑啟動感應，使得前半段煞車強度增強，後半段減弱，從而獲得有彈性的投擲感受。易於調整煞車力度，且具有對外部環境的強韌性等特點，是一種性能卓越的煞車系統。 ■線杯特性 採用直徑34mm（寬度24mm）的超級鋁合金製線杯。延續20TATULA SV TW的超級鋁合金製線杯，提高了線杯響應速度，提高了投擲穩定性，實現了從5克到110克（約4盎司）範圍內，包括大型魚餌在內的穩定遠投性能。 ■ 搭載TWS 大幅擴大了無阻力範圍。因此，飛行距離增加，控制性提高，形態加快，倒噴現象減少。TWS提升了餌輪的所有基本性能。 ■ 搭載TWS 大幅擴大了無阻力範圍。因此，飛行距離增加，控制性提高，形態加快，倒噴現象減少。TWS提升了餌輪的所有基本性能。</v>
       </c>
       <c r="R250" t="str">
         <v/>
       </c>
       <c r="S250" t="str">
-        <v/>
+        <v>淡海水入门进阶</v>
       </c>
       <c r="T250" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="251" xml:space="preserve">
+        <v>价格友好 / 基础性能完整 / 通用型</v>
+      </c>
+    </row>
+    <row r="251">
       <c r="A251" t="str">
-        <v>DRE1046</v>
+        <v>DRE5013</v>
       </c>
       <c r="B251">
         <v>2</v>
       </c>
       <c r="C251" t="str">
-        <v>ワールドスピン</v>
+        <v>SALTIGA 15</v>
       </c>
       <c r="D251" t="str">
         <v/>
       </c>
       <c r="E251" t="str">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F251" t="str">
-        <v/>
+        <v>22 SALTIGA 15</v>
       </c>
       <c r="G251" t="str">
         <v/>
@@ -15957,74 +15929,72 @@
         <v/>
       </c>
       <c r="I251" t="str">
-        <v>spinning</v>
+        <v>drum</v>
       </c>
       <c r="J251" t="str">
-        <v/>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%2015_main.jpg</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-04-05T14:40:36.686921Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="L251" t="str">
-        <v>2026-04-05T14:40:36.686921Z</v>
+        <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M251" t="str">
-        <v/>
-      </c>
-      <c r="N251" t="str" xml:space="preserve">
-        <v xml:space="preserve">高剛性でスムーズな巻上げ感をもたらすデジギヤII、ライントラブルを減少させるABS II・クロスラップ・ツイストバスターII、ガタつきのない快適な巻き上げが可能なインフィニットストッパーなど、快適な実釣性能をもたらすダイワテクノロジーをしっかり搭載。折りたたみ式アルミハンドルで持ち運びもしやすい。さらにソルト対応のため、淡水はもちろん海のエサ釣りからルアーゲームまで幅広く対応。買ってすぐに釣り場で使える便利な糸付き（CFは糸なし）。※ソルト対応 | DIGIGEAR・DIGIGEARII
-                                                                    不可能といわれたドライブギア歯面形状を完全デジタル化することに成功したデジギア。それをさらに理想の回転を生み出すために進化させたデジギアⅡは、さらなる強度の向上と滑らかな回転を実現します。 | ABSⅡ
-                                                                    ラインがトラブル無く放出され飛距離が伸びるスプール構造。スプールを大口径＆逆テーパーにすることでバックラッシュなどのトラブルを減少させます。ABSⅡではスプールリング形状を見直すことにより、さらに遠投性能を高めることに成功しました。</v>
+        <v>近海船钓旗舰</v>
+      </c>
+      <c r="N251" t="str">
+        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚 / 」為了實現釣手的夢想而誕生的「SALTIGA」 / 它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術 / 它的前提是與未知的大物對峙</v>
       </c>
       <c r="O251" t="str">
-        <v/>
+        <v>¥80,000</v>
       </c>
       <c r="P251" t="str">
         <v>在售</v>
       </c>
       <c r="Q251" t="str">
-        <v/>
+        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚。」為了實現釣手的夢想而誕生的「SALTIGA」。它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術。 它的前提是與未知的大物對峙。不斷挑戰裝備的極限，追求各個方面的強度，致力於成為易於使用且性能優越的好夥伴。SALTIGA所肩負的責任是成為確實能夠接近夢想魚的助力。持續實現存在價值，即實現釣手的夢想。其可靠性能支持著世界各地釣手的夢想。 極致旋轉、操作和耐久的旗艦型捲線器。 一切都是為了捕獲目標魚。 透過極致旋轉、操作和耐久，持續進化的SALTIGA。 DAIWA引導釣手前往更高峰。 DAIWA 技術 ■HYPERDRIVE DESIGN 強力、滑順回轉的永續，雙軸捲線器所需性能的集大成。從驅動齒輪到小齒輪，不間斷的傳導動能的動力裝置。從外側確實的持續支持驅動不，實現穩定且安靜驅動力的機殼。在任何環境下都能座動的多性能結構。實現高效率且遠遠超越寄往捲線力量及滑順迴轉性能的雙軸捲線器設計概念。以經驗為武器的DAIWA，創造初次世代的標準。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING〈磁油防水滾珠軸承〉 DAIWA以其獨特的技術，首次成功將滾珠軸承本身進行了磁油密封。通過具有磁性的液體油膜，抑制了水和異物進入滾珠軸承內部，同時保持了滾珠軸承的原始旋轉性能，大大減輕了鏽蝕、卡鹽和異音等問題。 ■ATD 根據魚的拉力平滑作動，持續平穩地運轉。ATD追求流暢的啟動和跟蹤性，讓您能夠專注於戰鬥，而無需擔心剎車設置。 產品詳情 ■陽極保護 「抗腐蝕，卓越耐用」 陽極保護是一種減緩金屬腐蝕的技術。當金屬腐蝕時，陽極（鋅）會承擔腐蝕。通過將這項技術應用於捲線器上，將腐蝕集中在陽極板上，以保持其耐用性能。這是第一次在DAIWA捲線器上應用這項功能。 ■拇指持握模組 「持握手法的轉變」 通過分析各種釣手的握持方式，追求更貼合手形的形狀。開發了拇指握持模組，旨在實現更容易握持並減少指頭滑出的拇指置放位置。考慮了拇指在關閉離合器後的位置，顯著提高了舒適性。 這種全新的握持體驗大大改變了以往的“握持”概念。 ■75-85mm 鋁製曲柄手柄臂 「堅韌耐用的鋁製搖臂」 適合於大物釣法，使用方便的75-85mm鋁製搖臂。 ※適用於22 SALTIGA 15系列 ※出貨時長度為85mm ■85-95mm 碳纖維製曲柄手柄臂 「高靈敏度・輕量化的碳纖維搖臂」 22SALTIGA 15-SJ系列採用了碳纖維製搖臂。透過高靈敏度和輕量化，提升了配備的平衡性。 5mm厚度的設計實現了高剛性。即使在進行強力的拋擲或者與大型魚對抗時，也能夠不彎曲地進行捲線。 ※適用於22SALTIGA 15-SJ系列 ※出貨時長度為95mm ■線杯更換系統 「簡單且方便的線杯更換功能」 使用側板螺絲的三點支撐結構。 準備好備用線杯，可以根據突然的斷線或突發狀況，立即進行線杯更換。 隨附的線杯更換扳手（T8），解開齒輪側蓋的側板螺絲3個，即可拆卸齒輪側蓋。 側板螺絲採完全鬆開也不會掉落的防脫結構，避免丟失的麻煩。 ■大口徑Φ52mm輪子 「最適合的線杯尺寸設計」 選擇Φ52mm輪子。 以線容量4號PE-300m自豪，實現了該領域NO.1的線容量。 線杯形狀考慮到放線速度變化的影響，實現了最佳平衡。並對輕巧的捲收和與獵物爭取距離的捲線功率產生重大影響。 ■煞車拉出提示音 「以聲音掌握每一刻的緊張對決」 在與大型魚的對抗中，精準的煞車設定至關重要。 當魚突然猛拉時，能透過聲音判斷煞車作動情況，能為釣者帶來極大的操作優勢。 ■85mm T形把手 「無可比擬的握持感」 專為握持時的貼合感和手感所設計，追求最舒適的握姿，讓收線時的擁有舒適操作感的T形狀把手。 為了更容易搏魚，特別追求了中心的厚度，以方便進行搏魚的相關動作。在拉升時，牢牢握持，展現穩定的收線動作。 ■ 捲線器 15/15L： 適用於PE線的深杯捲線器規格 實現PE4-300米的大容量。 可達到PE1.5號-800米，適用於中深場釣遊。 與15S捲線器相容。 ■ 捲線器鎖定 「在垂釣場景中發揮作用的實用功能」 這是一種完全固定捲線器並鎖定捲線器逆轉的機制。 在掛底時，如果強行拉扯，可能不僅會損壞線，還可能損壞齒輪和滾珠軸承。然而，通過使用捲線器鎖定機制，可以將捲線器和齒輪分開，並在不損壞齒輪和滾珠軸承的情況下進行扯斷。 使用方法非常簡單。 1. 將捲線器鎖定切換到「開啟」位置。 2. 關閉離合器。 3. 在這個狀態下，第一次施加張力並拉斷線。 ※將捲線器和齒輪分開是關鍵。 這是一個必不可少的功能，能夠安心、安全地快速應對。</v>
       </c>
       <c r="R251" t="str">
         <v/>
       </c>
       <c r="S251" t="str">
-        <v/>
+        <v>近海船钓高端</v>
       </c>
       <c r="T251" t="str">
-        <v/>
+        <v>深海与慢摇兼顾 / 大线容量 / 高负载</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>DRE5000</v>
+        <v>DRE5014</v>
       </c>
       <c r="B252">
         <v>2</v>
       </c>
       <c r="C252" t="str">
-        <v>SILVER WOLF CT SV TW PE SPECIAL</v>
+        <v>PR100 H</v>
       </c>
       <c r="D252" t="str">
         <v/>
       </c>
       <c r="E252" t="str">
-        <v/>
+        <v>2022</v>
       </c>
       <c r="F252" t="str">
-        <v/>
+        <v>22 PR100 H</v>
       </c>
       <c r="G252" t="str">
         <v/>
       </c>
       <c r="H252" t="str">
-        <v>精细,海水</v>
+        <v>泛用,海水</v>
       </c>
       <c r="I252" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J252" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SILVER%20WOLF%20CT%20SV%20TW%20PE%20SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/PR100%20H_main.jpg</v>
       </c>
       <c r="K252" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16033,60 +16003,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M252" t="str">
-        <v>黑鲷PE特化</v>
+        <v>基础入门</v>
       </c>
       <c r="N252" t="str">
-        <v>廣泛對應各種路亞的 PE 線專用機種 / SILVER WOLF CT SV TW PE SPECIAL 是一款能以 PE 線廣泛對應從輕量路亞到重型路亞的全能型款式 / SS MAGFORCE Φ30mm G1 硬鋁合金製 PE 專用 SV 線杯，搭配能將出線性能發揮至極致的 TWS，唯有兼具這兩項性能才能實現未竟之領域 / 引領黑鯛釣手邁向更高境界</v>
+        <v>DAIWA 2022年『 PR100H 』系列小烏龜路亞捲線器 超人氣入門平價款的捲線器，搭配迷彩設計，新手入門首選 / ● PR100H MA-綠迷彩 ● PR100H MN-灰迷彩 ● PR100H MM-黃迷彩 ※ H-右手捲 HL-左手捲</v>
       </c>
       <c r="O252" t="str">
-        <v>¥56,800</v>
+        <v>¥6,700</v>
       </c>
       <c r="P252" t="str">
         <v>在售</v>
       </c>
       <c r="Q252" t="str">
-        <v>獻給黑鯛路亞釣法的專家。廣泛對應各種路亞的 PE 線專用機種。 SILVER WOLF CT SV TW PE SPECIAL 是一款能以 PE 線廣泛對應從輕量路亞到重型路亞的全能型款式。 SS MAGFORCE Φ30mm G1 硬鋁合金製 PE 專用 SV 線杯，搭配能將出線性能發揮至極致的 TWS，唯有兼具這兩項性能才能實現未竟之領域。引領黑鯛釣手邁向更高境界。 除了進一步的小型化，機身框架與齒輪側側板採用鎂合金（Mg），固定板則採用鋁合金（AL），兼顧了輕量化與高剛性。透過搭載 HYPERDRIVE DIGIGEAR，即便齒輪比高達 8.5，仍能長效發揮滑順的轉動性能。 此外，透過出線聲機構，在線張力接近極限邊緣的攻防戰中，以出線聲輔助釣手應戰。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (全金屬) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 本系列在機殼與齒輪側側板（手把側）採用了鎂合金材質，而在握把側的固定板則使用鋁合金壓鑄，並透過高精度的機械切削加工完成，展現出穩固不動的剛性。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■SS MAGFORCE 全新的磁力剎車結構SS MAGFORCE目標實現「更低慣性的線杯」，進一步突破未踏領域。其特性為具備對抗惡劣條件的優異能力，能夠配合不同釣友及各式各樣的情況，兼容性很強的投擲性能。瞬間提升的線杯旋轉反應，使得從小幅度的拋竿中拋出的路亞能夠描繪出低且延伸出去的軌跡擊中瞄準的釣點。 ■SV-CONCEPT SV-CONCEPT（Super Versatile Concept） 徹底對應各類路亞與環境，實現無壓力拋投的舒適體驗。這是一款具備極致通用性的煞車概念，無論近距離精準拋投、中距離搜索還是遠投，都能輕鬆應對。從輕量、中量到重量級路亞，皆能穩定掌控並將拋投可能發生的意外降至最低。由於該系統對釣竿與路亞的相容性極高，不論是在淡水或海水領域，都能在針對多種魚種的釣法中大顯身手。 ※僅限使用 PE 線。因本產品是針對 PE 線進行極致設定調校，若使用延展性較大的尼龍線或碳纖線，可能會對線杯強度造成損害，因此禁止使用。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■HIGH SPEED LEVEL WIND 當釣線以鬆散狀態捲繞在線杯時，在使用 PE 線的情況下，產生的纏線問題尤為明顯。而 HIGH SPEED LEVEL WIND 技術正是為了大幅減少此類問題而設計。其結果能顯著降低捲線平面上，表層線體咬入底層線縫的問題，進而帶來順暢且舒適的實釣性能。 ■G1 硬鋁合金製 φ30mm SV 線杯（PE 專用） 專為 SS MAGFORCE 系統開發的 SV 線杯，能廣泛對應從微型路亞到重型擬餌的重量區間。不僅能隨心所欲地操控小型釣組，更能實現「更遠距離的投射與極其輕巧的落水」。是在極端嚴苛的釣場環境中，不放過任何一條可能上鉤的魚、將其成功獵取的強力武器。 ※本線杯針對 PE 線進行極致設定，由於尼龍線或碳纖線的延展性較大，容易對線杯強度造成損傷，因此禁止使用 PE 線以外的線種。 ■TAPER TWS 為了追求拋投時的釣線釋放阻力降至最低，即「擴展無阻力範圍」，本機搭載了 TAPER TWS。除了擴充無阻力空間，更結合特殊表面處理 DLC 的加乘效應，力求將出線性能發揮至極限。DAIWA 持續鑽研這項獨一無二的技術，不斷追求讓人「想一投再投」的拋投手感。 ■DRAG CLICK DRAG CLICK 是指在與魚搏鬥、釣線被拉出時，能透過聲音判別出線狀態的報警聲機構。 在遊走於釣線張力極限邊緣的攻防戰中，能透過聲音判別出線動作，對釣手而言是極大的優勢。 尤其在使用細號數 PE LINE 的釣法中，這更是不可或缺的必備功能。 ■培林配置位置 小齒輪部：2BB（CRBB） 齒輪軸兩端：2BB（CRBB） 線杯兩端：2BB（CRBB） 機能比較 機能名稱 26SILVER WOLF CT SV TW PE SPECIAL SILVER WOLF SV TW1000XH PE SPECIAL 設計思想 HYPERDRIVE DESIGN HYPERDRIVE DESIGN 導線規系統 錐形TWS 高速導線規系統 TWS 高速導線規系統 剎車系統 SS MAGFORCE SV SV BOOST 線杯徑（mm） φ30 φ34 線杯材質 G1超硬鋁合金 G1超硬鋁合金 捲線量PE 0.6-150/0.8-120 0.6-180/0.8-150 重量（g） 160 185 拉力系統 UTD UTD 手把長度（mm） 85 90 軸承(滾珠/滾輪) 6/1 10/1 發售日期 2026.03</v>
+        <v>DAIWA 2022年『 PR100H 』系列小烏龜路亞捲線器 超人氣入門平價款的捲線器，搭配迷彩設計，新手入門首選。 ● PR100H MA-綠迷彩 ● PR100H MN-灰迷彩 ● PR100H MM-黃迷彩 ※ H-右手捲 HL-左手捲</v>
       </c>
       <c r="R252" t="str">
         <v/>
       </c>
       <c r="S252" t="str">
-        <v>黑鲷路亚PE特化</v>
+        <v>淡海水基础入门</v>
       </c>
       <c r="T252" t="str">
-        <v>PE细线专用 / 高速回收 / 黑鲷细致操控</v>
+        <v>低预算 / 操作简单 / 入门练习友好</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>DRE5001</v>
+        <v>DRE5015</v>
       </c>
       <c r="B253">
         <v>2</v>
       </c>
       <c r="C253" t="str">
-        <v>TATULA BF TW</v>
+        <v>STEEZ AII TW</v>
       </c>
       <c r="D253" t="str">
         <v/>
       </c>
       <c r="E253" t="str">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="F253" t="str">
-        <v>26 TATULA BF TW</v>
+        <v>22 STEEZ AII TW</v>
       </c>
       <c r="G253" t="str">
         <v/>
       </c>
       <c r="H253" t="str">
-        <v>精细,泛用,bass</v>
+        <v>远投,强力,bass</v>
       </c>
       <c r="I253" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J253" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20BF%20TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20AII%20TW_main.jpg</v>
       </c>
       <c r="K253" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16095,60 +16065,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M253" t="str">
-        <v>BF泛用主力</v>
+        <v>高端重装主力</v>
       </c>
       <c r="N253" t="str">
-        <v>源自日本，引領全球 BAIT FINESSE 基準的指標機型 搭載專為 TATULA 設計的 φ30mm 超硬鋁製 BF 線杯 / 僅需設定一次磁力調控旋鈕，即可順應並兼容各種不同的拋投方式，其優異的適應性能正是這款捲線器的最大魅力 / 透過 TWS 的相乘效果，讓釋放出的釣線完全不失速，進而體現將路亞以低彈道、流暢地送往目標點的卓越拋投精準度 / 無論是以 SMALL RUBBER JIG、NO SINKER 為主的輕量軟蟲釣組，或是小型硬餌皆能全面對應</v>
+        <v>無論遠投或是近距離，都能實現更精確的拋投 / STEEZ A TW一直以來為眾多釣手提供了堅固耐用和穩定性，但第二代經歷了更進一步的淬鍊 / 將美國艱鉅的錦標賽經驗與下一代的Baitcasting Reel 設計理念「HYPERDRIVE DESIGN」相結合 / HYPER ARMED HOUSING（FULL-AL）的堅固性保持不變，而HYPERDRIVE DIGIGEAR則提高了捲動性能，即使在高負載情況下，也能實現平順且高功率的收捲</v>
       </c>
       <c r="O253" t="str">
-        <v>¥36,300</v>
+        <v>¥54,000</v>
       </c>
       <c r="P253" t="str">
         <v>在售</v>
       </c>
       <c r="Q253" t="str">
-        <v>源自日本，引領全球 BAIT FINESSE 基準的指標機型 搭載專為 TATULA 設計的 φ30mm 超硬鋁製 BF 線杯。煞車系統由 K.T.F. 沢村幸弘氏親自參與開發。僅需設定一次磁力調控旋鈕，即可順應並兼容各種不同的拋投方式，其優異的適應性能正是這款捲線器的最大魅力。 透過 TWS 的相乘效果，讓釋放出的釣線完全不失速，進而體現將路亞以低彈道、流暢地送往目標點的卓越拋投精準度。無論是以 SMALL RUBBER JIG、NO SINKER 為主的輕量軟蟲釣組，或是小型硬餌皆能全面對應。 全機搭載能使初期旋轉性能長久維持的 「HYPERDRIVE DESIGN」 技術，且機身框架與齒輪側側板均採用鋁合金材質。即使在高負荷狀態下，也能以令人安心的紮實感、滑順的旋轉性能與剛性，為釣手提供強力支援。 此外，更進一步精進了煞車性能，並搭載出線警示音功能。憑藉全方位的強悍性能，讓您在面對大型鱸魚的挑戰時更加游刃有餘。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■BF-CONCEPT 透過簡易設定，自在投擲“超”輕量級的魚餌 專為超輕量魚餌設計。當你用力晃動竿子進行擲投時，魚餌會以低彈道平穩飛出，而在一般的拋投中，其飛行距離可與紡車捲線器相媲美。這款「DAIWA BF」的一大特點是可以在不重新調整剎車力的情況下，隨意交替使用擲投和拋竿方式。 搭載將細膩釣法性能發揮到極致的BF線杯。為了應對超輕量路亞，這款線杯超級輕量且搭載微型BB。不僅可以靈活操作更小更輕的魚餌，還能實現「更長的拋投距離以及柔和的入水」。在挑戰艱難環境時，它將成為捕捉到最後一條魚的強力武器。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 產品詳情 ■Φ30mm 超硬鋁製 BF 線杯 在執行 BAIT FINESSE 釣法的實戰場域中，實現了 PITCHING 與 CASTING 兩種拋投方式最高水準的兼容性。僅需設定在相同的煞車數值下，即可享受無壓力且舒適的作釣體驗。 ■HYPER ARMED HOUSING 高剛性金屬機殼 機身材質（框架、齒輪側側板）均採用 ALUMINUM 鋁合金打造。透過將機身結構設計得更加緊湊精實，實現了不感重負、卻極其強韌耐用的機體規格。 ■K.T.F. 合作研發 與 K.T.F. 代表——沢村幸弘先生共同開發。身為自 2000 年代中期便率先倡導 BAIT FINESSE 戰術價值的業界先驅，他是至今仍活躍於國內外賽事最前線的「MR. BAIT FINESSE」。為了證明本機能提供頂尖的微拋性能，其合作標誌也特別刻印於產品外盒。 ■DRAG CLICK（出線警示音） 本機搭載了 DRAG CLICK 構造。當與魚搏鬥且釣線被拉出時，能透過音響訊號即時判別煞車的運作狀態。對於追求利用細線來取得對戰優勢的釣法而言，這是不可或缺的核心功能之一。 ■培林配置位置 小齒輪部：2BB（1CRBB） 齒輪軸兩端：2BB（CRBB） 線杯兩端：2BB（1CRBB） 發售時間 2026.03</v>
+        <v>無論遠投或是近距離，都能實現更精確的拋投。 STEEZ A TW一直以來為眾多釣手提供了堅固耐用和穩定性，但第二代經歷了更進一步的淬鍊。將美國艱鉅的錦標賽經驗與下一代的Baitcasting Reel 設計理念「HYPERDRIVE DESIGN」相結合。 HYPER ARMED HOUSING（FULL-AL）的堅固性保持不變，而HYPERDRIVE DIGIGEAR則提高了捲動性能，即使在高負載情況下，也能實現平順且高功率的收捲。 STEEZ A II TW採用了新開發的φ34mm G1航空鋁超高精度MAG-Z BOOST線杯。通過淺杯化，僅配備所需的線容量，使捲線器總重量更輕量。結果而言，這項設計提高了捲線器的初始啟動性能，成為實用投擲性能的迷人特色之一。 高抓握性的I型握丸和新設計的90mm 航空鋁製手柄實現更加的捲動體驗外，同時STEEZ A II TW還標配了星盤剎車和MAGSEALED滾珠軸承。這不僅僅是黑鱸釣，也能應對海釣的可靠遠投型號--「STEEZ A II TW」。現代釣手所需要的功能濃縮匯集而成的跨時代捲線器。 DAIWA 技術 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。。 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側，以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈的進行捲線操控。 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場環境使用後的卡鹽維修件數，達到減少99%的實績，以最先進的絕緣構造自豪。 ■TWS TWS（T-Wing System）是一種DAIWA獨創設計，可以大幅減少位於捲線器最上方、靠近機身的導線的阻力，這樣可以減少線圈的旋轉阻力，確保少發生糾結，提供舒適的釣魚體驗。TWS可以實現更遠的投擲距離，提高控制性，同時減少線材打結。TWS可以提升所有Baitcasting Reel的基本性能。 ■MAGSEALED BALL BEARING 由於Baitcasting Reel的結構，海水很難避免地從捲線器和機身之間的縫隙滲入，最容易受到鹽水侵害的是主齒輪部分的軸承。在STEEZ A II TW系列中，為了進一步提高防水性和耐久性，採用了MAGSEALED BALL BEARING在機械旋鈕的一側的主軸齒輪支撐部位。這有助於保持初始性能。 ■MAGSEALED BALL BEARING 由於Baitcasting Reel的結構，海水很難避免地從捲線器和機身之間的縫隙滲入，最容易受到鹽水侵害的是主齒輪部分的軸承。在STEEZ A II TW系列中，為了進一步提高防水性和耐久性，採用了MAGSEALED BALL BEARING在機械旋鈕的一側的主軸齒輪支撐部位。這有助於保持初始性能。 其他技術 &amp; 產品詳情 ■MAG-Z BOOST 『BOOST SYSTEM 將 MAGFORCE-Z 的遠投性能發揮到極致』 MAG-Z BOOST 是將 MAGFORCE-Z 的遠投性能發揮到極致，注重飛距離的設定。MAGFORCE-Z 由於遠心力作用特性，不適合輕餌。然而，對於中重量級的餌，它可是最佳選擇，可以根據輸入的力量伸展飛行距離。 ■G1鋁鎂合金製Φ34mm 線杯 G1鋁鎂合金是一種特殊的鋁合金，展現出比鎂多2倍和超級鋁鎂合金多1.3倍的強度。這種超輕且具有卓越剛性的材料被廣泛應用於航空器結構和精密儀器中。為了實現壓倒性的輕盈感，同時保持相同的強度，捲線器透過薄肉化來保持輕盈所帶來的高速旋轉反應，以及高剛性帶來的精確無比的旋轉，使其無與倫比，難以被其他產品超越。 ■出線音效 出線音效是指在與魚進行搏鬥時，當出線時可以通過聲音區分剎車作用的構造。 出線聲的音質和大小都受到精心設計的關注，清脆、舒適！ ■ZERO SHAFT 線杯僅由BB支撐。因為無軸，所以沒有多餘的阻力。可以達到理想的線杯迴轉。 這也表示是最重視遠投性能的高動力輸出引擎的重要關鍵。 這個曾被稱為Speed Shaft的卷線輪機構於2021年被重新命名為"ZERO SHAFT"。</v>
       </c>
       <c r="R253" t="str">
         <v/>
       </c>
       <c r="S253" t="str">
-        <v>BF泛用进阶</v>
+        <v>鲈鱼高端远投</v>
       </c>
       <c r="T253" t="str">
-        <v>轻饵低弹道 / 微物到小硬饵兼容 / 易控性高</v>
+        <v>AII重载取向 / 高刚性 / 中重型饵友好</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>DRE5002</v>
+        <v>DRE5016</v>
       </c>
       <c r="B254">
         <v>2</v>
       </c>
       <c r="C254" t="str">
-        <v>月下美人 BF TW PE SP</v>
+        <v>ZILLION TW HD</v>
       </c>
       <c r="D254" t="str">
         <v/>
       </c>
       <c r="E254" t="str">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="F254" t="str">
-        <v>26 月下美人 BF TW PE SP</v>
+        <v>22 ZILLION TW HD</v>
       </c>
       <c r="G254" t="str">
         <v/>
       </c>
       <c r="H254" t="str">
-        <v>精细,海水</v>
+        <v>远投,强力,海水,bass</v>
       </c>
       <c r="I254" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J254" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20BF%20TW%20PE%20SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ZILLION%20TW%20HD_main.jpg</v>
       </c>
       <c r="K254" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16157,60 +16127,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M254" t="str">
-        <v>轻海水BF特化</v>
+        <v>重载主力</v>
       </c>
       <c r="N254" t="str">
-        <v>夜裡綻放的花朵，光芒愈發耀眼 / 2005 年，DAIWA 首次推出專為輕海水路亞打造的系列——「月下美人」 / 如同在月光下綻放的艷麗之花般，月下美人舞動著，而釣者的心也隨之躍動 / 面對看似親近、卻有時需要極度細膩操作的目標魚種——如鯵魚（Aji），以及那些藏身於岩縫或海藻間隙、時刻警戒、等待獵物靠近的狡猾岩魚（Mebaru），月下美人系列一路隨之進化</v>
+        <v>新一代的HYPERDRIVE DIGIGEAR，使用高強度真鍮作為傳動齒輪，以及在小齒輪中使用高耐蝕銅合金，實現了強大而平滑的旋轉 / 採用HYPER ARMED HOUSING（全鋁）打造堅固的機身，使其在保持小巧的同時確保強大的機身剛性 / 新開發的Φ34mm G1鋁合金超高精度MAG-Z BOOST線輪實現了卓越的長距離投擲性能 / DAIWA 技術 &amp; 產品詳情 ◆MAGFORCE-Z BOOST MAGFORCE-Z BOOST是將MAGFORCE-Z的遠投性能極致發揮的設定</v>
       </c>
       <c r="O254" t="str">
-        <v>¥56,800</v>
+        <v>¥54,500</v>
       </c>
       <c r="P254" t="str">
         <v>在售</v>
       </c>
       <c r="Q254" t="str">
-        <v>夜裡綻放的花朵，光芒愈發耀眼。 2005 年，DAIWA 首次推出專為輕海水路亞打造的系列——「月下美人」。如同在月光下綻放的艷麗之花般，月下美人舞動著，而釣者的心也隨之躍動。面對看似親近、卻有時需要極度細膩操作的目標魚種——如鯵魚（Aji），以及那些藏身於岩縫或海藻間隙、時刻警戒、等待獵物靠近的狡猾岩魚（Mebaru），月下美人系列一路隨之進化。今後，月下美人也將持續與釣者一同成長，帶來前所未有的悸動與樂趣。她那迷人的光輝，將持續照亮整個輕海水路亞世界。 PE專用的 Bait Finesse 雙軸捲線器，展現巔峰性能。 PE專用的 Bait Finesse 雙軸捲線器，展現巔峰性能。 「月下美人 BF TW PE SPECIAL」是專為 PE 線打造的 Bait Finesse 雙軸捲線器，可輕鬆應對微型路亞的低彈道拋投，並大幅提升遠投性能。 搭載 SS MAGFORCE 專用 Φ28mm G1 鋁合金 PE 專用線杯，以及最大化放線性能的 TWS 系統，兩者結合實現前所未有的釣魚領域，將資深玩家帶向更高境界。 機身進一步小型化，主框架與齒輪側側板採用鎂合金、側蓋部位採用AL鋁合金，兼顧輕量化與高剛性。配備 HYPERDRIVE DIGIGEAR，即使在 8.5 的高速齒比下，也能長時間保持順滑旋轉。 此外，透過煞車出線警示音的設計，讓玩家在與魚的極限拉鋸中，能清楚掌握線張力，精準操作每一次攻防。 建議路亞重量：0.8g～5g 單鉤鉛頭（Jighead） DAIWA 技術 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■SS MAGFORCE 全新的磁力剎車結構SS MAGFORCE目標實現「更低慣性的線杯」，進一步突破未踏領域。其特性為具備對抗惡劣條件的優異能力，能夠配合不同釣友及各式各樣的情況，兼容性很強的投擲性能。瞬間提升的線杯旋轉反應，使得從小幅度的拋竿中拋出的路亞能夠描繪出低且延伸出去的軌跡擊中瞄準的釣點。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 ■ZAION 透過 DAIWA 的獨家技術，以高密度碳纖維成形的碳纖樹脂製成，擁有輕盈、強韌、耐腐蝕特性，重量強度比超過鎂合金，堪稱化不可能為可能的材料。 主要應用於機身、轉盤等主體部件，可兼顧強固與輕量這兩種背道而馳的特性。 產品詳情 ■G1 鋁合金 φ28mm BF 專用線杯（PE 專用） 搭載專為精細釣法打造的 Bait Finesse 專用 BF 線杯，追求極致的細膩操作性能。 開發了 SS MAGFORCE 專用 BF 線杯，與傳統線杯相比，實現更低的慣性，使超輕量路亞拋投更加順暢。 此外，搭載超輕量微型軸承，不僅能輕鬆操作小型路亞與精緻魚鉤，還能達成更遠的距離拋投與輕盈的落水。 即使在嚴苛釣場中，也能確保捕獲每一尾魚，成為可靠的強力武器。 ※ 推薦線量：PE 0.4 號 – 50 m ※ 注意事項： PE 1 號以上的線材，或使用 10g 以上路亞，將超出本款捲線器的適用範圍，請勿使用。 PE 專用線杯：此線杯專為 PE 線設計，高延展性的線材，如尼龍或氟碳線可能對線杯強度造成損害，請勿使用。 ■出線警示音 當釣線在博魚過程中被拉出時，拖曳系統會發出「滴答聲」的結構設計。 在拉鋸對抗中，玩家可以透過聲音清楚判斷拖曳系統的作動，掌握線張力，提升操作精準度。 這項功能對使用細線 PE 線的釣法尤其重要，是不可或缺的實用設計。 ■TWS系統 為了降低拋投時的線材阻力，也就是 擴大「無阻力範圍」，捲線器採用了錐形 TWS。 除了擴大無阻力範圍外，配合 DLC 類鑽碳特殊表面處理，在兩者的相乘下，進一步最大化線材放出的性能。 DAIWA 持續精進這項獨家技術，只為追求令人一次又一次想拋投的順暢手感。 ※ 本線杯專為 PE 線設計，請勿使用 PE 以外的線材。使用其他線材可能因線材伸縮導致線杯變形等風險。 ※ 由於為 Bait Finesse 專用機種，請勿使用強度超過 PE 1 號以上 的線材，否則將超出本款捲線器的適用範圍。 ※ 捲線量僅供參考，實際數值會因製造商、產品及線張力而有所不同。 ※ 收線長度為手柄每轉一圈的收線距離。 發售日期 2025.12</v>
+        <v>新一代的HYPERDRIVE DIGIGEAR，使用高強度真鍮作為傳動齒輪，以及在小齒輪中使用高耐蝕銅合金，實現了強大而平滑的旋轉。 採用HYPER ARMED HOUSING（全鋁）打造堅固的機身，使其在保持小巧的同時確保強大的機身剛性。 新開發的Φ34mm G1鋁合金超高精度MAG-Z BOOST線輪實現了卓越的長距離投擲性能。 DAIWA 技術 &amp; 產品詳情 ◆MAGFORCE-Z BOOST MAGFORCE-Z BOOST是將MAGFORCE-Z的遠投性能極致發揮的設定。由於MAGFORCE-Z的特性是遠心力驅動感應線杯，因此不適用於輕型路亞。然而，對於中到重型路亞的遠投卻非常理想，可以根據輸入的力量增加飛行距離。 ■TWS（T-Wing System） TWS（T-Wing System）是一項技術，顯著減少了在離開最高轉速的線杯的導線阻力，避免線組糾纏，使釣魚更加舒適。 ■UTD（Ultimate Tournament Drag） UTD（Ultimate Tournament Drag）消除初次起動時的阻力，實現無斷續的出線平順性，並且隨著收緊而具有更大的最大剎車力。 ■G1 鋁製線杯 G1 鋁合金是一種特殊的鋁合金，展現出比鎂多兩倍、超級鋁合金多1.3倍的強度。這種超輕量且優越的剛性材料被廣泛應用於航空器具的結構和精密儀器等領域。在保持相同強度的情況下表現驚人的輕巧感。這種輕巧性帶來的轉動回饋速度和高剛性帶來的精密旋轉是難以被其他產品超越的。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■ 零調整器 首先通過調整「零調整器」，實現「線杯無間隙」設定，因為磁煞的進步，可以僅通過磁煞系統控制所有的餌。 「零調整器」允許在開始釣魚之前進行「零設置」，從而在釣魚過程中不會發生誤差動作，讓您輕鬆享受釣魚。 ※「線杯無間隙」設定是指在保留微小間隙（約0.2mm）的情況下，設置線杯到達極限的設置。 ■ 出線聲 出線聲是指在與魚對抗時，當線被拉出時，剎車作動會發出聲音，以便通過聲音辨別剎車作動效果的結構。</v>
       </c>
       <c r="R254" t="str">
         <v/>
       </c>
       <c r="S254" t="str">
-        <v>轻海水PE BF特化</v>
+        <v>淡海水重载泛用</v>
       </c>
       <c r="T254" t="str">
-        <v>Ajing根鱼细饵 / PE专用线杯 / 轻海水精细操控</v>
+        <v>HD高负载 / 中大型饵 / 淡海水兼容</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>DRE5003</v>
+        <v>DRE5017</v>
       </c>
       <c r="B255">
         <v>2</v>
       </c>
       <c r="C255" t="str">
-        <v>STEEZ SV LIGHT TW</v>
+        <v>SALTIGA IC</v>
       </c>
       <c r="D255" t="str">
         <v/>
       </c>
       <c r="E255" t="str">
-        <v/>
+        <v>2021</v>
       </c>
       <c r="F255" t="str">
-        <v/>
+        <v>21 SALTIGA IC</v>
       </c>
       <c r="G255" t="str">
         <v/>
       </c>
       <c r="H255" t="str">
-        <v>精细,泛用,bass</v>
+        <v/>
       </c>
       <c r="I255" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J255" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20SV%20LIGHT%20TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%20IC_main.png</v>
       </c>
       <c r="K255" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16219,60 +16189,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M255" t="str">
-        <v>旗舰轻量泛用</v>
+        <v>近海船钓计数旗舰</v>
       </c>
       <c r="N255" t="str">
-        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴 / 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化 / 為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品 / 這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」</v>
+        <v>近海船钓与铁板兼顾 / 计数器辅助 / 中深水实战取向</v>
       </c>
       <c r="O255" t="str">
-        <v>¥79,500</v>
+        <v>¥70,400 - ¥71,500</v>
       </c>
       <c r="P255" t="str">
         <v>在售</v>
       </c>
       <c r="Q255" t="str">
-        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 「Ultimate Light Versatile」更低、更深。攻略節奏不斷加快 ⸺ 透過讓線杯實現更高的反應性能，「26 STEEZ SV LIGHT TW」達成了更低彈道的拋投軌跡，並進一步提升了拋投精準度。 齒比提供兩種規格：7.8 與系列中最快速的 9.2。齒比 7.8 為兼顧「打點與平捲」兩種釣法的全能款式；而齒比 9.2 則具備每圈收線量 92cm 的高速捲線性能，不僅能提升收線效率，還能迅速收回滯線。在將魚從障礙區拉出的瞬間，亦能發揮出色的控制力。 導線環採用了錐形 TWS 設計，與 SV BOOST 技術產生協同效果，支撐拋投後段的穩定延伸力。 在需要高精度、複雜拋投操作的高壓釣場中，這款「究極輕量多功能型」捲線器，終於達成了完美境界。 不斷進化的 SV LIGHT 2018年，在並木敏成的監修之下，搭載首款 φ32mm SV LIGHT 線杯的 SV LIGHT LTD 誕生。「在追求貼近 BF 機型特性的同時，也想保留 SV 系列優勢」⸺這款捲線器正是將並木的這份想法化為現實的作品。不僅在各種情況下都具備高水準的多功能性能，更展現出 BF 機型的順暢拋投手感。可謂是 BF（Bait Finesse）與 SV 的完美融合。而今，經過八年進化，全新搭載 φ32mm SV LIGHT 線杯的 26 STEEZ SV LIGHT TW 誕生。配備能在拋投後段帶來延伸力的 SV BOOST、全新設計的低慣性線杯、以及具備高出線性能的錐形 TWS，三者相互作用，讓唯一無二的拋投性能昇華至全新境界。「輕量路亞能以極低的拋物線，像箭矢般筆直飛出⸺這種感覺真的太驚人了。」連並木本人也由衷讚嘆。亮點不僅在於卓越的拋投手感，輕量路亞的適應能力也大幅提升。以往必須仰賴 BF 機型才能進行的釣法，如今即使用粗線也能輕鬆應對。同時，對應重量級路亞的能力依舊毫不妥協。這正是所謂的⸺「終極輕量萬用機」。由 26 STEEZ SV LIGHT TW 所提出的，SV CONCEPT（Super Versatile 超泛用理念）迎來了全新的進化形態。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (全金屬) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 本系列在機殼與齒輪側側板（手把側）採用了鎂合金材質，而在握把側的固定板則使用鋁合金壓鑄，並透過高精度的機械切削加工完成，展現出穩固不動的剛性。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座NDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTAIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 ■SV-BOOST BOOST結構的最大特點在於能夠分2個階段伸出的可變電磁感應旋轉底座部分。SV-BOOST 在保留SV CONCEPT的零故障性基礎上，根據線軸轉速瞬時提供兩段最佳的制動力，實現投擲後半段的延展。這一系統在保持舒適性能的同時，也具備出色的遠投性能。拋投時的立起過程在拋投後半段的延展中，對於初速的反捲區域，瞬間發揮最大的制動力以進行控制，然後在中段到後段逐漸減少制動力，實現後半段的延伸。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 產品詳情 ■SV BOOST 透過 SV BOOST × 淺線杯 × 錐形TWS 的協同效應，實現了低彈道且拋投後段延伸性極佳的拋投性能。 即使在稍微用力的拋投中，線也不會浮起；而輕力的拋投時，也能獲得充足的延伸距離。這樣的特性讓釣者能夠從比以往更遠的位置，將誘餌靜悄悄地送入覆蓋區深處或精準的目標點，同時降低入水聲。 這樣的性能，在釣場條件越嚴苛時越能展現其真正價值，最終化為確實的釣獲成果。 ■SV LIGHT 線杯 上滿線後的線杯重量減輕約14.8%（與 24 STEEZ SV TW 相比）。 透過約22%的慣性降低（與 24 STEEZ SV TW 相比），實現了低彈道拋投。 結合低彈道與拋投後段延伸性的表現，讓釣者能夠從更遠的位置進行精準的釣點攻略。 在現今競爭激烈、魚情嚴峻的水域中，拋投與接近角度的差異往往決定釣果。 左圖：24 STEEZ SV TW 右圖：26 STEEZ SV LIGHT TW *以 STEEZ Fluoro X’LINK 12lb 全滿線狀態下比較。 ■G1超硬鋁合金製線杯 G1超硬鋁合金是一種特殊的鋁合金，具有鎂的兩倍以及超硬鋁合金1.3倍的強度。這種超輕量且具有卓越剛性的材料是航空器結構材料和精密儀器等輕量合金中的最高等級。 為了在保持相同強度的同時實現壓倒性的輕量感，G1超硬鋁合金線軸在不進行任何加壓變形加工，僅通過減少厚度來維持足夠的強度。這種輕量帶來的旋轉感受反饋和高剛性帶來的精確旋轉，均達到無與倫比的水準。 ■錐形TWS 在追求提高控制性的同時減少拋投時的放線所產生的阻力，即追求“無阻力範圍的擴展”目標的過程中，搭載了錐形TWS。 除了擴展無阻力範圍外，還結合了特殊表面處理“DLC”，將線放出性能最大化。DAIWA對於其獨有技術也不斷精益求精，持續探求 “令人欲罷不能地想不斷拋投”的拋投手感。 ■HYPERDRIVE DIGIGEAR 首次推出 9.2 齒比版本 新增每轉一圈可回收 92cm 線長的機型。 不僅提升拋投與回收的效率，還能在迅速收回鬆線或將魚從障礙區強行拉離時發揮強大威力。 尤其在快節奏的打點釣法中，更能展現明顯的優勢。 ■注油蓋 隨著無輔助剎車構造，移除了ZERO ADJUSTER。26STEEZ SV LIGHT TW搭載了注油蓋。 使用附屬的專用工具可以取下注油蓋。取下蓋子後，可以對小齒輪滾珠培林進行注油和維護。 ■實心小齒輪 與以往的中空小齒輪相比，透過 UCD（Ultimate Casting Design） 技術實現的實心結構小齒輪，在齒輪強力咬合時具備更高的抗負荷性能。 在相同直徑與齒比條件下，強度提升超過20％。 小齒輪的強化，讓齒輪系統在不依賴加大直徑的情況下，仍能具備高剛性結構，並大幅提升了以高強度著稱的 HYPERDRIVE DIGIGEAR 的旋轉耐久性。 ■ 鋁製星型煞車 搭載以操控性為重點開發的星型煞車，甚至重新設計了內部棘齒結構。在每次調整聲上也精益求精，實現了清脆而細膩的星形煞車調整警示音，帶來更舒適的操作體驗。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能，目標是成為同級別中的No.1。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■培林配置位置 ■對應之可改裝零件 ■對</v>
+        <v/>
       </c>
       <c r="R255" t="str">
         <v/>
       </c>
       <c r="S255" t="str">
-        <v>鲈鱼高端轻量</v>
+        <v>近海船钓计数高端</v>
       </c>
       <c r="T255" t="str">
-        <v>轻量低弹道 / 高精度抛投 / 高压场精细控制</v>
+        <v>船钓与铁板兼顾 / 计数器 / 深水适配</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>DRE5004</v>
+        <v>DRE5018</v>
       </c>
       <c r="B256">
         <v>2</v>
       </c>
       <c r="C256" t="str">
-        <v>RYOGA</v>
+        <v>ZILLION SV TW</v>
       </c>
       <c r="D256" t="str">
         <v/>
       </c>
       <c r="E256" t="str">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="F256" t="str">
-        <v>26 RYOGA</v>
+        <v>21 ZILLION SV TW</v>
       </c>
       <c r="G256" t="str">
         <v/>
       </c>
       <c r="H256" t="str">
-        <v/>
+        <v>泛用,bass</v>
       </c>
       <c r="I256" t="str">
-        <v>drum</v>
+        <v>baitcasting</v>
       </c>
       <c r="J256" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/RYOGA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ZILLION%20SV%20TW_main.jpg</v>
       </c>
       <c r="K256" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16281,60 +16251,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M256" t="str">
-        <v>圆鼓旗舰</v>
+        <v>鲈鱼主力</v>
       </c>
       <c r="N256" t="str">
-        <v>「重視捲線，就非RYOGA不可了 / 」⸺ 那不是選擇，而是信念 / 持續支撐著那份「永不褪色的捲線工藝」 / 延續歷代 RYOGA 一貫堅持，搭載以機械切削工法打造的高精度、高剛性機身「HYPER ARMED HOUSING」，再結合「HYPERDRIVE DIGIGEAR」</v>
+        <v>ZILLION SV TW 下一代雙軸捲線器技術HYPERDRIVE設計 ■HYPER DRIVE DIGIGEAR 新型設計的(雙軸)齒輪系統，可實現滑順的旋轉與耐用性，主齒輪（尺寸）不會減少，並且提高咬合率 / DAIWA的獨家技術可以達到上述要求並實現持久的初始光滑度 / ■HYPER DOUBLE SUPPORT 可持續的保持滑順度，通過兩個培林支撐小齒輪的兩端，即使附加重量也不影響捲動的手感 / ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力</v>
       </c>
       <c r="O256" t="str">
-        <v>¥67,500 - ¥68,000</v>
+        <v>¥45,400</v>
       </c>
       <c r="P256" t="str">
         <v>在售</v>
       </c>
       <c r="Q256" t="str">
-        <v>「重視捲線，就非RYOGA不可了！」⸺ 那不是選擇，而是信念。 持續支撐著那份「永不褪色的捲線工藝」。 延續歷代 RYOGA 一貫堅持，搭載以機械切削工法打造的高精度、高剛性機身「HYPER ARMED HOUSING」，再結合「HYPERDRIVE DIGIGEAR」。 兩者的綜效實現了極致的剛性，幾乎徹底消除鬆動，並帶來如絲般順暢又強勁有力的捲線體驗。 100 與 150 兩種尺寸各自擁有明確的煞車設計概念⸺ 100 型採用 SV 概念，150 型採用 LC 概念，兩者皆搭載 BOOST SYSTEM。 100 型（搭載 SV BOOST）能抑制高空氣阻力路亞飛行時的線浮現象，確保穩定的拋投軌跡，在不需施力的情況下，於拋投後段依然能輕鬆延伸飛行距離。 150 型（搭載 MAG-Z BOOST）則能有效抑制中至重量級路亞拋投初期容易出現的過度線軸轉速，穩定路亞姿態，實現如劃破風般的遠投性能。 在齒比設計上極致講究，將「捲線」這個動作昇華至極致境界。 機械切削所造就的雄渾外觀與存在感，成就了鼓式捲線器的巔峰之作。 獻給每一位對「捲線」充滿熱情的釣者，以及所有愛 RYOGA 的粉絲。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■SV-CONCEPT 以可變電磁感應旋轉底座(INDUCT/INDUCTION ROTOR)為核心的DAIWA雙軸捲線器的煞車系統已進入第三代。新增了能夠在SV（FINESS精細方向）中具有優勢的煞車系統，進一步增強遠投性能。通過將傳統的1階的(INDUCT/INDUCTION ROTOR)可變電磁感應旋轉底座改為2階，創新的結構在精細投擲領域中能夠發揮最佳效能。 ※ 僅適用於 SV100 型。 ■SV-BOOST BOOST結構的最大特點在於能夠分2個階段伸出的可變電磁感應旋轉底座部分。SV-BOOST 在保留SV CONCEPT的零故障性基礎上，根據線軸轉速瞬時提供兩段最佳的制動力，實現投擲後半段的延展。這一系統在保持舒適性能的同時，也具備出色的遠投性能。拋投時的立起過程在拋投後半段的延展中，對於初速的反捲區域，瞬間發揮最大的制動力以進行控制，然後在中段到後段逐漸減少制動力，實現後半段的延伸。 ※ 僅適用於 SV100 型。 ■LC-CONCEPT 實現拋投後半段穩定延展的卓越遠投煞車性能概念。特別適合中至重型路亞，隨著釣竿越用力揮出，飛行距離便越長。此外，LC 概念帶來的運動感與爽快的拋投手感，更是其主要魅力所在。 ※ 僅適用於 150 型。 ■MAG-Z BOOST BOOST SYSTEM 將 MAGFORCE-Z 的遠投性能發揮至極限。MAG-Z BOOST 採用以飛距離為重點的設定，專為 MAGFORCE-Z 設計。MAGFORCE-Z 透過離心力操作煞車轉子，因此不適合輕量級路亞，但對中至重量級路亞的遠投卻最為理想，施力越大，飛距離越遠。 BOOST 系統的革命性設計：避開容易失控纏線的區段後，煞車瞬間回位，讓拋投中段到落水都保持順暢飛行，發揮最大遠投性能。 ※ 僅適用於 150 型。 ■ATD ATD（Advanced Tournament Drag）是一種先進的比賽用出線系統，它根據魚的拉力平滑地作出反應，追求平順出線的效果，讓您可以專注搏魚，無需擔心出線力道設置。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 產品詳情 ■運轉耐久性能提升 與 18RYOGA 相比，即使在高負荷或長時間使用下，運轉性能也不易下降。 26RYOGA 搭載的「HYPERDRIVE DIGIGEAR」，在滑順運轉與齒輪耐久性上達到更高水準。 左：18RYOGA 搭載 高強度黃銅製 HYPERMESH GEAR 右：26RYOGA 搭載 高強度黃銅製 HYPERDRIVE DIGIGEAR ■採用機械切削製法的高精度高剛性機身 「重視捲線，就非RYOGA不可了！」。 歷代 RYOGA 一直堅持的機械切削製法，造就了高精度、高剛性的機身。與 HYPERDRIVE 設計相互作用，帶來紮實的手感與順暢的運轉性能，專為重視「捲線手感」的釣者打造。 ■新形狀線杯（150型） 經多次實地測試後，採用了全新的窄型設計。 在線放出時，將角度調整得比以往淺 3.4%，使拋投時的線路更順暢、更輕快。 在線容量充足的同時，透過優化線杯的直徑與寬度平衡，實現了更筆直、更穩定的拋投軌跡。 ■2.0mm厚不鏽鋼製捲線器腳座 講究僅僅 0.5mm 的厚度差，將原本 1.5mm 厚度升級至 2.0mm。 此改良徹底消除了在拋投、高負荷路亞操作及搏魚時可能出現的晃動。 同時，材質也從鋁改為不鏽鋼，確保與海水用鼓式捲線器相同等級的強度。 對細節毫不妥協的設計，成就了堅實可靠的剛性表現。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能，目標是成為同級別中的 No.1。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■培林配置位置 ■對應之可改裝零件 ■線杯相容性 小齒輪部：2BB（CRBB） 齒輪軸兩端：2BB（CRBB） 線杯兩端：2BB（CRBB） 搖臂握把：2BB（每個握把內含1顆不鏽鋼BB） 握丸：可對應 S 尺寸握丸 搖臂：可搭配各式 RCSB 搖臂 RCSB BF 搖臂組／RCSB 曲柄搖臂組／RCSB 碳纖曲柄搖臂／23RCSB 100mm 碳纖曲柄搖臂／RCSB ESD 100mm 曲柄搖臂 100：對應 RCSB1000 線杯系統 150：對應 RCSB1500 線杯系統 產品介紹 品名 說明 SV100 線軸採用 φ34mm G1超級杜拉鋁材質，搭載 SV BOOST 系統，實現輕鬆拋投即可獲得理想飛距離的性能。 即使是拋投時容易產生空氣阻力的「捲動系路亞」，也能透過 SV 概念特有的低拋物線軌跡與高精度拋投，實現穩定、準確的操作。再加上 BOOST 系統，使拋投後段的延伸性進一步提升，無論中、近距離或遠投區域，都能穩定發揮。 對於微型Crankbait、1/4oz級旋轉亮片等阻力較輕的路亞，或淺水區攻略時，更能發揮最佳性能。 齒比提供兩種版本可選：5.3（每轉收線長56cm）與6.3（每轉收線長67cm）。 150 線杯採用 φ36mm 高強度鋁材質，搭載 MAG-Z BOOST 系統。經過多次實地測試驗證各種材質後，最終選用高強度鋁材，以確保中至重量級路亞在竿上穩定運行，同時提供中遠距離所需的慣性力，實現優異的遠投性能。 在線量部分，重新設計線杯形狀，以優化捲線排列。這些改良的相互作用，使 LC 概念 能夠呈現流暢的拋投軌跡及爽快的拋投手感。 齒比提供兩種版本： 5.3（每轉收線長 59cm）：適合深水型 Crankbait、Magnum Crank、大型爬行路亞，以及大型路亞的中層 Dead Walk 和 Cranking 操作。 7.3（每轉收線長 82cm）：滿足深水型 Crankbait拋投時對高速齒比的需求，特別適合操作大型路亞或重型平捲釣法。 在較重負荷的平捲釣法下，也能提供舒適的操作感。值得一提的是，7.3 齒比（150H/HL 型）搭載 100mm 長手柄及 Power Light M 握丸，即使進行快速拉線或高負荷操作，也能輕鬆收線。 此外，為避免大型路亞拋投斷線的風險，此款線杯可支援粗線需求（尼龍 20lb.-100m、PE 4號-100m），並同時滿足海水釣需求的規格。 機能比較 機能名稱 18RYOGA1016 26RYOGA SV100 18RYOGA1520 26RYOGA 150 設計思想 Detective Rotation 設計 HYPERDRIVE DESIGN Detective Rotation 設計 HYPERDRIVE DESIGN 剎車系統 MAG FORCE Z SV BOOST MAG FORCE Z MAG-Z BOOST 機身材質 G1超硬鋁合金 G1超硬鋁合金 G1超硬鋁合金 高強度鋁合金 捲線量(Ib-m) 16-100 12-100 14-90 16-80 20-100 16-125 20-100 25-80 捲線量PE(号-m) 1.5-200 2.0-150 3.0-90 2.0-230 2.0-230 3.0-150 4.0-100 重量 255g 265g 270g P齒輪：285g H齒輪：290g 握丸形狀 高抓握I形輕量握丸 高抓握I形強力大型握丸 高抓握I形強力握丸 P齒輪：高抓握I形強力大型握丸 H齒輪：強力輕量M中型握丸 手把長度 90mm 90mm 90mm P齒輪：90mm H齒輪：100mm 軸承(滾珠/滾輪) 12/1 8/1 12/1 8/1 附屬品 ・使用說明書（日文版） ・使用說明書（四國語言版） ・展開圖 ・問卷登錄 ID 卡 ※ 捲線量僅供參考，實際數值會因製造商、產品及線張力而有所不同。 ※ 收線長度為手柄每轉一圈的收線距離。 ※ 關於拋投時的聲音 搭載 BOOST 結構的線杯，在拋投（路亞飛行）時，可能會聽到煞車轉子（Induct Rotor）復位時發出的「卡嗒」聲。 BOOST 系統中，負責控制煞車力的煞車轉子被設計為比傳統更快、更強地回位，並延長作動行程，以最大化遠投效果。因此，相較於傳統捲線器，誘導轉子的回位聲可能會明顯一些，並非異常現象。 BOOST 採用兩段式作動結構，最多可發生兩次聲音。聲音的大小與發生次數會依拋投時施加的力道不同而有所變化。 發售日期 2025.12＝SV 100 2026.01＝150</v>
+        <v>ZILLION SV TW 下一代雙軸捲線器技術HYPERDRIVE設計 ■HYPER DRIVE DIGIGEAR 新型設計的(雙軸)齒輪系統，可實現滑順的旋轉與耐用性，主齒輪（尺寸）不會減少，並且提高咬合率。 DAIWA的獨家技術可以達到上述要求並實現持久的初始光滑度。 ■HYPER DOUBLE SUPPORT 可持續的保持滑順度，通過兩個培林支撐小齒輪的兩端，即使附加重量也不影響捲動的手感。 ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■SV BOOST 線杯 下一代SV概念，實現了令人振奮的高水平拋投性能，並增加了飛行距離。煞車系統的啟動從原本的一階段進化成二階段，在線杯低轉速時(拋輕克數餌)啟動較弱的第一階段煞車，線杯高轉速時(拋重克數餌)啟動較強的第二階段，並在餌飛行的後半段煞車會回到較弱的第一段，從而延伸餌的飛行距離。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■UTD消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。</v>
       </c>
       <c r="R256" t="str">
         <v/>
       </c>
       <c r="S256" t="str">
-        <v>高刚性卷收旗舰</v>
+        <v>鲈鱼泛用主力</v>
       </c>
       <c r="T256" t="str">
-        <v>切削机身 / 卷收强悍 / 中重型路亚与船钓兼顾</v>
+        <v>SV易控 / 抛投稳定 / 覆盖面广</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>DRE5005</v>
+        <v>DRE5019</v>
       </c>
       <c r="B257">
         <v>2</v>
       </c>
       <c r="C257" t="str">
-        <v>SALTIGA 10</v>
+        <v>ALPHAS SV TW 800H／22 ALPHAS SV TW 800S-XHL</v>
       </c>
       <c r="D257" t="str">
         <v/>
       </c>
       <c r="E257" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F257" t="str">
-        <v>25 SALTIGA 10</v>
+        <v>21 ALPHAS SV TW 800H／22 ALPHAS SV TW 800S-XHL</v>
       </c>
       <c r="G257" t="str">
         <v/>
       </c>
       <c r="H257" t="str">
-        <v/>
+        <v>精细,泛用,bass</v>
       </c>
       <c r="I257" t="str">
-        <v>drum</v>
+        <v>baitcasting</v>
       </c>
       <c r="J257" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%2010_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ALPHAS%20SV%20TW%20800H%EF%BC%8F22%20ALPHAS%20SV%20TW%20800S-XHL_main.jpg</v>
       </c>
       <c r="K257" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16343,60 +16313,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M257" t="str">
-        <v>近海铁板旗舰</v>
+        <v>轻量泛用</v>
       </c>
       <c r="N257" t="str">
-        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚 / 」為了實現釣手的夢想而誕生的「SALTIGA」 / 它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術 / 它的前提是與未知的大物對峙</v>
+        <v>■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力 / ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障 / ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統 / 他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性</v>
       </c>
       <c r="O257" t="str">
-        <v>¥65,000</v>
+        <v>¥33,700</v>
       </c>
       <c r="P257" t="str">
         <v>在售</v>
       </c>
       <c r="Q257" t="str">
-        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚。」為了實現釣手的夢想而誕生的「SALTIGA」。它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術。 它的前提是與未知的大物對峙。不斷挑戰裝備的極限，追求各個方面的強度，致力於成為易於使用且性能優越的好夥伴。SALTIGA所肩負的責任是成為確實能夠接近夢想魚的助力。持續實現存在價值，即實現釣手的夢想。其可靠性能支持著世界各地釣手的夢想。 近海鐵板釣的新戰力登場。 近海鐵板系列推出兼具「小型化」與「高強度」的新尺寸！ 為了應對大型青物、根魚以及中深海等嚴苛的離岸鐵板釣場景，SALTIGA 10 以「極致緊湊、極致剛強」為開發目標。 核心性能搭載 HYPERDRIVE DESIGN，全面提升耐用度與操作順暢性，完美覆蓋各種近海釣況。 此次的 SALTIGA 10 在實現 PE1.5號-650m／3號-300m 的驚人收線量同時，成功打造出更加緊湊的小型化設計。 齒輪尺寸與 15 系列相同，最大煞車力在齒比 6.3 時達 11kg（齒比 7.1：9kg）。 體積輕巧、握持舒適，即使長時間操作也不易疲勞，仍能以強悍的力量壓制目標魚，展現近海鐵板釣的真正實力。 DAIWA 技術 ■HYPERDRIVE DESIGN 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING（FULL AL） 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING 應用於本體與導線輪上的防水、耐用技術革命已擴展至滾珠軸承這個對於線杯迴轉有著莫大影響的小零件。DAIWA靠著獨家技術，成功領先世界研製出具備磁油防水功能的滾珠軸承。 透過帶有磁性的液體油膜，使水和異物無法入侵滾珠軸承內部。滾珠軸承不僅可以維持原本的滑順性能，也能在不靠墊圈輔助下大幅減低生鏽、卡鹽、發出異常聲響等問題的發生，提升防水性及耐用度，可長時間維持初始性能。 ■ATD ATD（Advanced Tournament Drag）是一種先進的比賽用出線系統，它根據魚的拉力平滑地作出反應，追求平順出線的效果，讓您可以專注搏魚，無需擔心出線力道設置。 ■PERFECT DOUBLE STOPPER 除了標準的單向止逆裝置外，還搭載了機械式止逆裝置。即使在關鍵時刻其中一側止逆發生反轉，也能不中斷釣魚作業——專為嚴苛釣況下的強悍釣法打造的可靠支援功能。 產品詳情 ■煞車拉出提示音 「以聲音掌握每一刻的緊張對決」 在與大型魚的對抗中，精準的煞車設定至關重要。 當魚突然猛拉時，能透過聲音判斷煞車作動情況，能為釣者帶來極大的操作優勢。 ■拇指持握模組 「持握手法的轉變」 通過分析各種釣手的握持方式，追求更貼合手形的形狀。開發了拇指握持模組，旨在實現更容易握持並減少指頭滑出的拇指置放位置。考慮了拇指在關閉離合器後的位置，顯著提高了舒適性。 這種全新的握持體驗大大改變了以往的“握持”概念。 ■陽極保護 「抗腐蝕，卓越耐用」 陽極保護是一種減緩金屬腐蝕的技術。當金屬腐蝕時，陽極（鋅）會承擔腐蝕。通過將這項技術應用於捲線器上，將腐蝕集中在陽極板上，以保持其耐用性能。 ※圖片為 25 SALTIGA 35。 ■75–85mm 鋁合金曲柄手把臂 「強韌、耐用的鋁合金手把臂」 這款 75–85mm 的鋁合金曲柄手把臂， 長度設定適合用於One-Pitch Jerk釣大青物等，操作順手且兼顧力量與耐久性。 ※出廠時為 85mm。 ■85mm T形把手 「無可比擬的握持感」 專為握持時的貼合感和手感所設計，追求最舒適的握姿，讓收線時的擁有舒適操作感的T形狀把手。 為了更容易搏魚，特別追求了中心的厚度，以方便進行搏魚的相關動作。在拉升時，牢牢握持，展現穩定的收線動作。 ■ 捲線器鎖定 「在垂釣場景中發揮作用的實用功能」 這是一種完全固定捲線器並鎖定捲線器逆轉的機制。 在掛底時，如果強行拉扯，可能不僅會損壞線，還可能損壞齒輪和滾珠軸承。然而，通過使用捲線器鎖定機制，可以將捲線器和齒輪分開，並在不損壞齒輪和滾珠軸承的情況下進行扯斷。 使用方法非常簡單。 1. 將捲線器鎖定切換到「開啟」位置。 2. 關閉離合器。 3. 在這個狀態下，第一次施加張力並拉斷線。 ※將捲線器和齒輪分開是關鍵。 這是一個必不可少的功能，能夠安心、安全地快速應對。 ■φ48mm 大口徑線杯 「專為近海餌鐵板釣設計的最佳線杯尺寸」 比 15 系列更小口徑的 φ48mm 線杯， 可收納 PE1.5號-650m / PE2號-450m / PE3號-300m。 線杯形狀經過精密設計，兼顧放線時對收線速度的影響，達到最佳平衡。 煞車發揮精準，收線順暢，輕鬆收線的同時，也能快速縮短釣距。 ■線杯更換系統 「簡單且方便的線杯更換功能」 只需拆下齒輪箱側的 3 顆側板螺絲，即可輕鬆更換線杯。 準備好備用線杯，可以根據突然的斷線或突發狀況，立即進行線杯更換。 隨附的線杯更換扳手（T8），解開齒輪側蓋的側板螺絲3個，即可拆卸齒輪側蓋。 側板螺絲採完全鬆開也不會掉落的防脫結構，避免丟失的麻煩。 產品附屬配件 ■ 取扱説明書 ■ 問卷登記ID卡 ■ 線杯更換專用扳手（T10） ■ 絨面捲線器收納袋 ■ 腳座墊片 → 用於防止捲線器與釣竿受到刮傷，並提升與各種捲線器座的契合度，防止晃動。 發售日期 2025.10</v>
+        <v>■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■SV CONCEPT 能將磁性煞車應有的實戰優勢發揮最大極限，輕鬆愉快準確拋投，只要微調磁煞旋鈕，不管是4~5克左右的輕裝到重量級路亞都能輕鬆應付。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。 ■UTD 消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。</v>
       </c>
       <c r="R257" t="str">
         <v/>
       </c>
       <c r="S257" t="str">
-        <v>近海铁板高端</v>
+        <v>轻量泛用进阶</v>
       </c>
       <c r="T257" t="str">
-        <v>小型化高强度 / 近海大物 / 深水铁板取向</v>
+        <v>小尺寸轻量 / 精细钓法 / 城市野场友好</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>DRE5006</v>
+        <v>DRE5020</v>
       </c>
       <c r="B258">
         <v>2</v>
       </c>
       <c r="C258" t="str">
-        <v>SALTIGA 35</v>
+        <v>STEEZ LTD SV TW</v>
       </c>
       <c r="D258" t="str">
         <v/>
       </c>
       <c r="E258" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F258" t="str">
-        <v>25 SALTIGA 35</v>
+        <v>21 STEEZ LTD SV TW</v>
       </c>
       <c r="G258" t="str">
         <v/>
       </c>
       <c r="H258" t="str">
-        <v/>
+        <v>精细,泛用,bass</v>
       </c>
       <c r="I258" t="str">
-        <v>drum</v>
+        <v>baitcasting</v>
       </c>
       <c r="J258" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%2035_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20LTD%20SV%20TW_main.jpg</v>
       </c>
       <c r="K258" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16405,39 +16375,39 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M258" t="str">
-        <v>近海大物旗舰</v>
+        <v>高端限量泛用</v>
       </c>
       <c r="N258" t="str">
-        <v>回應大型魚的挑戰，展現真正的強悍力量 鐵板雙軸系列迎來了大型尺寸 / 為了應對更嚴苛的環境，我們在「HYPERDRIVE DESIGN」技術的基礎上進一步強化了基本性能，實現了強大的捲收能力 / 在這一尺寸中，重點考量的最大煞車力達到了「實釣時所預想13公斤」的標準 / 此次，我們選用了「UTD」系統，進一步提升了煞車力的穩定性與持久性</v>
+        <v>採用｢HYPERDRIVE DESIGN｣,以長時間維持初期性能為目標所設計的次世代BAITREEL隆重登場｡搭配HYPERDRIVE DIGIGEAR,達成強度提升,迴轉感受更為良好,使用HYPER ARMED HOUSING(Mg)實現了輕盈機殼｡旗艦機種STEEZ SV TW搭配全新技術以限定型號登場｡ 配備φ34ｍｍSV BOOST線杯支援拋投精準度,從輕量路亞到重量級路亞都能廣泛對應,新型BOOST機構讓飛行距離與拋投性能更佳優秀｡ ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力 / ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障 / ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統 / 他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性</v>
       </c>
       <c r="O258" t="str">
-        <v>¥86,500</v>
+        <v>¥74,800</v>
       </c>
       <c r="P258" t="str">
         <v>在售</v>
       </c>
       <c r="Q258" t="str">
-        <v>回應大型魚的挑戰，展現真正的強悍力量 鐵板雙軸系列迎來了大型尺寸！為了應對更嚴苛的環境，我們在「HYPERDRIVE DESIGN」技術的基礎上進一步強化了基本性能，實現了強大的捲收能力。在這一尺寸中，重點考量的最大煞車力達到了「實釣時所預想13公斤」的標準。此次，我們選用了「UTD」系統，進一步提升了煞車力的穩定性與持久性。 這款產品配備了適用於大型黃鰭鮪、青魽(平政)、紅魽等大型魚類，以及深場的大口徑線杯，並具備豐富的線容量。在保證大線容量的同時，線杯的直徑、寬度及本體尺寸也經過精心設計，確保釣手能在整天釣魚時保持舒適的使用感。 為提升操作的便利性，本體上設計了「拇指支撐框架」，讓釣手能以更少的力量穩定握住捲線器。此外，新開發的大型握丸符合人體工學設計，便於施力操作。為追求前所未有的耐用性，我們還搭載了陽極保護技術，有效減緩金屬腐蝕的風險。 SALTIGA 35的誕生，是為了幫助釣手突破極限、創造新紀錄「BREAK YOUR RECORD」。這款產品將成為幫助您夢想成真的最強武器。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING(磁油防水滾珠軸承) 應用於本體與導線輪上的防水、耐用技術革命已擴展至滾珠軸承這個對於線杯迴轉有著莫大影響的小零件。DAIWA靠著獨家技術，成功領先世界研製出具備磁油防水功能的滾珠軸承。 透過帶有磁性的液體油膜，使水和異物無法入侵滾珠軸承內部。滾珠軸承不僅可以維持原本的滑順性能，也能在不靠墊圈輔助下大幅減低生鏽、卡鹽、發出異常聲響等問題的發生，提升防水性及耐用度，可長時間維持初始性能。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■煞車警示音 「以聲音支援極限攻防戰」 在與大型魚對抗時，必須進行精準的煞車力調整設定。當魚突然猛衝發力時，透過聲音掌握煞車的啟動狀態，能為釣手帶來巨大的優勢。 ※圖片為22 SALTIGA 15。 ■拇指支撐框架 「從持握的概念，轉向指頭輕觸的創新轉換」 透過分析各類釣手的握法，我們研發出更貼合手型的框架設計，提升握感。這款拇指支撐框架讓釣手能輕鬆進行「拇指操作」（Thumbing），同時有效減少手指滑脫的情況。 我們還考慮到釣手在關閉離合器後拇指的自然位置，大幅提升操作時的舒適感。這項創新設計帶來全新的「掌控」體驗，徹底顛覆了傳統的持握概念。 ※圖片為22 SALTIGA 15。 ■陽極保護技術 「不朽且卓越的耐久性」 陽極保護技術是減緩金屬腐蝕的一種方法，也稱為犧牲陽極技術。其原理是讓陽極材料（如鋅）替代金屬零件承受腐蝕。透過將這項技術應用於捲線器，我們將腐蝕集中於陽極板，從而有效維持整體耐久性能。這是Daiwa捲線器中首次搭載的全新功能。 ■100-110mm 鋁合金曲柄握把臂 「強韌且耐用的鋁合金握把臂」 為了應對深海釣時使用的大重量鐵板或大型魚，我們選擇了100-110mm的握把長度。使用5mm厚的板材設計，提供高剛性，即使在進行強力的擺動或與大型魚搏鬥時，也不會變形，確保捲線穩定。 ※出廠時握把長度為110mm。 ■105mm T型動力握丸 「最大化釣手力量的大型握丸」 105mm的T型旋鈕符合人體工學設計，提升抓握時的舒適感與施力效果。不論在進行攘鐵板或捲收時，都能發揮優異的操作性。 雙軸鐵板的專家清水一成先生從基礎草稿設計並削磨出來的講究形狀。慢鐵是絕對應對，深場的手動快跳也能對應 ■線杯鎖定結構 「在鐵板釣法中發揮作用的切線(LINE CUTT)功能」 此結構可完全固定線杯，防止線杯逆轉。當卡底時，若強拉可能會損傷齒輪或滾珠軸承。透過線杯鎖定機構，您可將線杯與主齒輪分離，安全地進行拉線，避免損傷內部結構。 使用方法： 將線杯鎖定桿切換至「開啟」。 關閉離合器。 在此狀態下拉緊線並進行切割。 重點：確保線杯與齒輪分離，避免損壞齒輪與軸承。 這是一項安全可靠且快速處理卡底問題的必備功能。 ■φ65mm 大口徑線杯 「應對深場與粗線的高容量線杯」 新款65mm大口徑線杯相較15系列更為加大，可容納PE3號600米、PE4號500米、PE6號300米的魚線。此設計使釣手能針對更大型的魚種或深場進行準備。 此外，線杯形狀依然沿用15尺寸的設計，保持線放出時的速度穩定，確保最佳的煞車力表現。線杯的容量變化量經過精密設計，提供流暢的捲線操作與充足的捲線力量。 ■可更換線杯 「簡便且靈活的線杯更換功能」 在35系列中，齒輪側的側蓋螺絲從15系列的3個增加至5個，使本體與側蓋更加穩固。準備備用線杯後，可根據釣況或意外斷線快速更換。 更換步驟： 使用隨附的T10扳手卸下齒輪箱側的5個側板螺絲。 取下齒輪側蓋，即可進行線杯更換。 螺絲採用防脫設計，即使完全鬆開也不會掉落，避免螺絲遺失的麻煩。 ※圖片為22 SALTIGA 15。 品名 說明 35/35L 具備強大捲力的5.1標準齒輪型號 此款標準齒輪型號具有5.1：1的齒比，單次旋轉捲線長度達104厘米，是標準型雙軸鐵板捲線器的典範。 無論是針對大型黃鰭鮪的激烈搏鬥，還是在中大型魚咬鉤瞬間決勝負的搶線操作，抑或是進行深場鐵板及游動丸等高負荷釣況，這款捲線器都能憑藉其強大的捲線扭力發揮關鍵作用。 35H/35HL 高齒比的高速型號 此高速齒輪型號齒比為5.8：1，單次旋轉捲線長度達118厘米。它專為大型魚種的攻擊性釣法設計，在高速反應操作中能有效對付大型鰤魚。此外，在深場釣魚時，隨著PE線放出而線容量減少，捲線長度也會下降，因此這款捲線器可確保誘餌動作精準且連貫，特別適合深場釣魚的需求。 產品附屬配件 ■ 取扱説明書 ■ 問卷登記ID卡 ■ 線杯更換專用扳手（T10） ■ 絨面捲線器收納袋 ■ 腳座墊片 → 用於防止捲線器與釣竿受到刮傷，並提升與各種捲線器座的契合度，防止晃動。 發售時間 2025.05＝35 2025.06＝35L 2025.07＝35H、35HL</v>
+        <v>採用｢HYPERDRIVE DESIGN｣,以長時間維持初期性能為目標所設計的次世代BAITREEL隆重登場｡搭配HYPERDRIVE DIGIGEAR,達成強度提升,迴轉感受更為良好,使用HYPER ARMED HOUSING(Mg)實現了輕盈機殼｡旗艦機種STEEZ SV TW搭配全新技術以限定型號登場｡ 配備φ34ｍｍSV BOOST線杯支援拋投精準度,從輕量路亞到重量級路亞都能廣泛對應,新型BOOST機構讓飛行距離與拋投性能更佳優秀｡ ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■SV CONCEPT 能將磁性煞車應有的實戰優勢發揮最大極限，輕鬆愉快準確拋投，只要微調磁煞旋鈕，不管是4~5克左右的輕裝到重量級路亞都能輕鬆應付。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。 ■UTD 消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。</v>
       </c>
       <c r="R258" t="str">
         <v/>
       </c>
       <c r="S258" t="str">
-        <v>重型船钓旗舰</v>
+        <v>鲈鱼限量高端</v>
       </c>
       <c r="T258" t="str">
-        <v>深海与大型鱼取向 / 大线容量 / 大号鼓轮</v>
+        <v>高端限量 / 轻量反应 / 收藏实战兼顾</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>DRE5007</v>
+        <v>DRE5021</v>
       </c>
       <c r="B259">
         <v>2</v>
       </c>
       <c r="C259" t="str">
-        <v>STEEZ LIMITED CT SV TW</v>
+        <v>LIGHT GAME IC</v>
       </c>
       <c r="D259" t="str">
         <v/>
@@ -16452,13 +16422,13 @@
         <v/>
       </c>
       <c r="H259" t="str">
-        <v>精细,bass</v>
+        <v/>
       </c>
       <c r="I259" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J259" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20LIMITED%20CT%20SV%20TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/LIGHT%20GAME%20IC_main.jpg</v>
       </c>
       <c r="K259" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16467,60 +16437,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M259" t="str">
-        <v>限量高端精细</v>
+        <v>轻船钓计数主力</v>
       </c>
       <c r="N259" t="str">
-        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴 / 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化 / 為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品 / 這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」</v>
+        <v>兼備平滑捲線和輕盈特點的高剛性IC輕量款 / 有IC計數器的輕量型號，可應對各種輕型釣法 / 期待已久的「HYPERDRIVE DESIGN」系列即將登場 / 這是一款以提高所有基本性能水平為目標，以確保優異的初始性能持久的新世代捲線器</v>
       </c>
       <c r="O259" t="str">
-        <v>¥82,500</v>
+        <v>¥33,000 - ¥36,600</v>
       </c>
       <c r="P259" t="str">
         <v>在售</v>
       </c>
       <c r="Q259" t="str">
-        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 Evolution of STEEZ 每次投擲都能讓釣友充滿喜悅。 CT = 小巧與耐用概念的集大成，这就是STEEZ LTD CT SV TW。 SV = 具備超高多功能概念系列的最小直徑G1鋁合金製φ30mm CT SV線杯，搭載於LIMITED CT，刻意縮小了線量容量，對最大線量作出限制。 這是為了實現超輕量級、低於5g的鉤餌能夠使用的優秀高轉速性能，達到“極致的高回應性”。 這也是對尋求前所未有低彈道拋投性能的競技釣手們的一種挑戰。 無論是使用10lb至13lb的碳纖維線在多功能領域，還是使用6lb至8lb進入餌輕的領域，這種轉換的吸引力無可比擬。 此外，這款設計也考慮到使用PE線的需求，無論是投擲小型誘餌、頂水誘餌，還是打擊障礙物等，皆能展現最佳匹配。 通過刻意的限制設計，這款低彈道拋投手感展現了CT概念系列中最強的特性。 其TWS不會妨礙線的釋放，並且搭載了在24 STEEZ系列中開發的新型TAPER TWS。 相比傳統尺寸，開口擴大了約46%，這樣不僅提升了放線性能，並且毫無阻礙地實現了卓越的放線效果。 即使是輕微的擺動或僅利用SNAP的簡短投擲，也能實現出色的飛行距離。 無多餘動作，集中精力，精確且多變的應對現代困難的釣魚場景。 在中近距離作戰中，以無比精準的低彈道拋投技術，成功吸引了大量的拋投釣手。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座NDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTAIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■SV CONCEPT 以可變電磁感應旋轉底座(INDUCT/INDUCTION ROTOR)為核心的DAIWA雙軸捲線器的煞車系統已進入第三代。新增了能夠在SV（FINESS精細方向）中具有優勢的煞車系統，進一步增強遠投性能。通過將傳統的1階的(INDUCT/INDUCTION ROTOR)可變電磁感應旋轉底座改為2階，創新的結構在精細投擲領域中能夠發揮最佳效能。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■小巧耐用概念 / 小巧耐用 SV線杯 配備小巧型機身，並搭載φ30mm的G1鋁合金製CT SV線杯。 初速反應優異，能夠涵蓋多功能性能及精細性能。 小直徑設計顯著提升了低彈道的精確度，並且具備比專為餌輕設計的線杯更強的強度與耐久性，能夠應對16lb以上的粗線。 ■ 新型TWS 為了減少拋投時的放線所產生的阻力，即追求“無阻力範圍的擴展”，對DAIWA的獨家技術TWS進行了改進。 除了由於錐形結構帶來的無阻力範圍擴展，還加入了特殊表面處理"DLC"，最大化線釋放性能（如右圖所示）。 與19 STEEZ CT SV TW700（左圖）相比，開口增大了約46%。 DAIWA不僅在進一步改良自家獨特技術，更在不斷追求“令人欲罷不能地想不斷拋投”的拋擲手感。 ■ G1鋁合金線杯 G1鋁合金是一種強度是鎂的2倍，超鋁的1.3倍的特殊鋁合金。 這種超輕且剛性優異的材料，廣泛應用於航空機結構及精密儀器等領域。 為了實現更輕的重量，保持高強度，捲線盤表面經過精細加工，並保持足夠的強度。 輕量感帶來的回應性極高，並且高剛性提供了無與倫比的精確旋轉。 ■捲線後線杯重量比較 捲線後的線杯重量比19 STEEZ CT SV TW減輕了約23%。 藉此減少慣性，實現了低彈道投擲。 ■CT系列最快，捲線每圈長度80cm 搭載CT系列最快的齒輪比8.5。 隨著齒輪比的提升，捲線長度也提升約5%。 無論是打擊、捲收，這款線杯都能適應廣泛的需求。 ■注油蓋 拆下注油蓋即可對齒輪軸部的滾珠軸承進行加油。 請在維護時使用隨附的專用工具卸下注油蓋。重新安裝時，請調整為無間隙狀態。詳細請參見使用 ■新設計的星形煞車結構 採用經過精心設計的斜角形狀手柄，更加適合手指的觸感。 當調整星形煞車時，指尖能夠穩固且舒適地施力。 這樣的設計使得在緊急情況下，放鬆拖力變得更加順滑。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■ PE線兼容性 搭載φ30mm線杯和TAPER TWS設計的STEEZ LTD CT SV TW，具備優秀的PE線兼容性。 可使用1~1.5號PE線進行小餌或NEKO釣組等所謂的“力量餌輕釣法”。 使用雙軸捲線器所特有的快速操作、投擲精度和操控性，無論是在投擲還是繞線方面，都能提供比釣竿投擲更出色的性能。 這款產品無論在線重或線徑上都不受限，CT SV線杯的高回應性將充分發揮。 ■ 滾珠軸承搭載位置 ■ 支援的客製化配件 ■ 線杯互換系統 齒輪軸部：2個CRBB滾珠軸承 齒輪軸兩端：2個CRBB滾珠軸承 捲線盤兩端：2個CRBB滾珠軸承 緩衝軸兩端：2個CRBB滾珠軸承 手柄握把：4個CRBB（每個握把搭載2個） 因為是雙手柄，所以是4個滾珠軸承配置 手柄握把：適配S型握把 手柄：RCSB系列各型 RCSB BF手柄組 / RCSB 曲柄手柄組 / RCSB 碳纖曲柄手柄 / 23RCSB 100mm 碳纖曲柄手柄 / RCSB ESD 100mm曲柄手柄 適配RCSB CT SV700系列線杯。 實釣寫真</v>
+        <v>兼備平滑捲線和輕盈特點的高剛性IC輕量款。 有IC計數器的輕量型號，可應對各種輕型釣法。期待已久的「HYPERDRIVE DESIGN」系列即將登場。這是一款以提高所有基本性能水平為目標，以確保優異的初始性能持久的新世代捲線器。 DAIWA 技術 ■HYPERDRIVE DIGIGEAR 這是針對BAIT(雙軸)捲線器設計的新齒輪系統，以追求長時間維持強力且滑順為目標。不縮小模數齒輪的模數（大小）的前提下，實現了咬合率與耐久性的提升，讓初期滑順度的長效維持得以實現，這是DAIWA獨有的技術。 ■HYPER ARMED HOUSING（AL） 以高剛性、高精度確實支持內部結構，帶來細緻的捲線感和強大的動力的機殼系統。使用金屬材料製作構架是實現這一目標的必要條件，通過兩側側板的完美組合，可以滿足進一步長效維持基本性能的訴求。在本系列中，機身採用了鋁合金，實現了無比堅固的強度。 ■HYPER TOUGH CLUTCH 在千次、萬次的使用中仍能保持開關性能，不僅如此，在高鹽度海水區域中也能大幅度減少故障的離合器系統。它以先進的絕緣結構自豪，與本公司數據相比，在苛刻的海水釣場使用後中的卡鹽維修件數已經減少了99%。 ■ATD 針對魚的拉力平滑作動並持續平穩出線的新一代煞車系統。通過設置能夠抑制大型魚類抗爭中捲線器煞車力下降問題的設置，確保在抗爭中也能安心應對大型魚。</v>
       </c>
       <c r="R259" t="str">
         <v/>
       </c>
       <c r="S259" t="str">
-        <v>鲈鱼高端CT限量</v>
+        <v>轻船钓计数</v>
       </c>
       <c r="T259" t="str">
-        <v>精细抛投 / 小体积高反应 / 限量实战与收藏兼顾</v>
+        <v>双摇臂船钓 / 小型船钓 / 计数辅助</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>DRE5008</v>
+        <v>DRE5022</v>
       </c>
       <c r="B260">
         <v>2</v>
       </c>
       <c r="C260" t="str">
-        <v>SALTIGA 300</v>
+        <v>TATULA TW 400</v>
       </c>
       <c r="D260" t="str">
         <v/>
       </c>
       <c r="E260" t="str">
-        <v>2025</v>
+        <v/>
       </c>
       <c r="F260" t="str">
-        <v>25 SALTIGA 300</v>
+        <v/>
       </c>
       <c r="G260" t="str">
         <v/>
       </c>
       <c r="H260" t="str">
-        <v/>
+        <v>强力,海水,bass</v>
       </c>
       <c r="I260" t="str">
-        <v>drum</v>
+        <v>baitcasting</v>
       </c>
       <c r="J260" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%20300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20TW%20400_main.jpg</v>
       </c>
       <c r="K260" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16529,60 +16499,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M260" t="str">
-        <v>近海铁板主力</v>
+        <v>重型大号主力</v>
       </c>
       <c r="N260" t="str">
-        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚 / 」為了實現釣手的夢想而誕生的「SALTIGA」 / 它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術 / 它的前提是與未知的大物對峙</v>
+        <v>大线杯大物取向 / 重装大饵友好 / 远投与强拉力并重</v>
       </c>
       <c r="O260" t="str">
-        <v>¥63,000</v>
+        <v>¥41,000</v>
       </c>
       <c r="P260" t="str">
         <v>在售</v>
       </c>
       <c r="Q260" t="str">
-        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚。」為了實現釣手的夢想而誕生的「SALTIGA」。它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術。 它的前提是與未知的大物對峙。不斷挑戰裝備的極限，追求各個方面的強度，致力於成為易於使用且性能優越的好夥伴。SALTIGA所肩負的責任是成為確實能夠接近夢想魚的助力。持續實現存在價值，即實現釣手的夢想。其可靠性能支持著世界各地釣手的夢想。 稱霸近海鐵板 近海鐵板釣捲線器的全面升級，搭載強化的HYPERDRIVE DIGIGEAR。而在搭載排線器的機種中，首次加入了Daiwa的捲線器鎖定機構，完美適應急流的明石海域、瀨戶內海域等近海釣場的所有狀況。SALTIGA 300的HYPERDRIVE DIGIGEAR採用加寬齒幅設計，無論低負荷還是高負荷都能展現順暢且強勁的旋轉性能。此外，它還搭載了HYPER DOUBLE SUPPORT、HYPER TOUGH CLUTCH和HYPER ARMED HOUSING等高規格配置，力求完美。其採用舒適的握持框架設計，提供出色的手感並提升操作穩定性。手柄側邊則配備了陽極保護，專為嚴苛環境打造的SALTIGA 300將成為征服近海鐵板的全新利器。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (全鋁強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING(磁油防水滾珠軸承) 應用於本體與導線輪上的防水、耐用技術革命已擴展至滾珠軸承這個對於線杯迴轉有著莫大影響的小零件。DAIWA靠著獨家技術，成功領先世界研製出具備磁油防水功能的滾珠軸承。 透過帶有磁性的液體油膜，使水和異物無法入侵滾珠軸承內部。滾珠軸承不僅可以維持原本的滑順性能，也能在不靠墊圈輔助下大幅減低生鏽、卡鹽、發出異常聲響等問題的發生，提升防水性及耐用度，可長時間維持初始性能。 ■ATD(拉力調節系統) ATD（Advanced Tournament Drag）是一種先進的比賽用出線系統，它根據魚的拉力平滑地作出反應，追求平順出線的效果，讓您可以專注搏魚，無需擔心出線力道設置。 產品詳情 ■陽極保護技術（※圖片為25SALTIGA 35） 「堅不可摧，無與倫比的耐久性」 陽極保護（Anode Protection）是一種減緩金屬腐蝕的技術，也稱為犧牲陽極。該技術通過讓陽極（如鋅）優先腐蝕，從而保護金屬本體。在捲線器上搭載此技術，旨在集中腐蝕於陽極板，從而提升耐久性。 注意事項： 25SALTIGA 300的陽極保護板無法自行更換。 陽極保護板無法完全防止捲線器所有部位的生鏽和腐蝕。 陽極保護非免維護設計，屬於消耗品，隨著使用會自然腐蝕，屬正常現象。 請勿在陽極保護上塗抹任何塗料，否則會失去防腐功能。 陽極保護板的腐蝕速度會隨使用情況有所不同。請仔細閱讀說明書中的「重要！保養方法」，並在使用後盡早用清水沖洗。 ■同步排線器 「大幅提升放線與制動性能」 同步排線器是一種在釋放釣線時，排線器與釣線位置同步左右移動的機構。其優勢在於降低釣線放出時的阻力，同時提升制動的平滑性。SALTIGA 300進一步參照21 SALTIGA IC，對同步機構進行了結構重組：為實現「緊湊」設計，將以往位於手掌握持側的同步機構改置於手柄側。這一結構變更是達成緊湊設計的關鍵因素之一。 ■捲線器鎖定機構 「適合鐵板釣的快速止線功能」 捲線器鎖定機構可完全固定捲線器，防止其逆轉。在處理掛底等情況時，強行拉扯可能會損壞釣線、齒輪和滾珠軸承，而使用捲線器鎖定機構能將捲線器與小齒輪分離，避免對齒輪和軸承的損害，安全地弄斷釣線。 使用方法簡單： 切換捲線器鎖定桿至「開啟」狀態。 關閉離合器。 在此狀態下施加張力並拉斷釣線。 這種設置可有效弄斷釣線而不影響齒輪和小齒輪連接。 這項功能為安全快捷處理釣線的必備設計。 ※25SALTIGA 300的捲線器鎖定機構適用於3.0號及以下PE釣線。 ■拇指支撐框架 「從握持到拇指支撐的全新設計」 經過分析各類釣者的握持方式，追求更貼合手掌的形狀，開發出易於拇指支撐且減少指頭滑落的拇指支撐框架。該設計在關閉離合器後的拇指位置也經過精心考量，大幅提升舒適度。這種全新支撐體驗，顛覆了傳統「握持」的概念。 ■75-85mm 鋁製手柄 「堅韌耐用的鋁製手柄」 此款75-85mm鋁製手柄設計，適合釣青物時使用，特別適合一拍一收的晃餌節奏。 ※出廠設置為85mm。 ■85mm T形狀強力握丸 「無與倫比的握持感」 這款T形強力握丸專為提供極佳的手感和握持舒適度而設計，特別是在釣魚時的不同拇指位置。無論是晃餌還是收線，都能展現出卓越的操作舒適性。在進行一拍一收等動作時，通過精心設計的握丸，使得可以輕鬆抓住並進行更順暢的操作。此外，在慢鐵釣的提拉過程中，強力握丸可提供穩定的握持，避免抖動，從而實現穩定的拉動效果。適用於從近海鐵板釣到慢鐵釣的各種釣法。 另售選配零件相容 握把旋鈕：適用L尺寸旋鈕 SLPW85-95mm碳纖維握把 RCSB 60-70mm握把套件 RCSB 75-85mm握把套件 SLPW 130mm曲柄握把（NB） SLPW 140mm曲柄握把/BK SLPW 150mm曲柄握把/BK 發售日期 2025.02</v>
+        <v/>
       </c>
       <c r="R260" t="str">
         <v/>
       </c>
       <c r="S260" t="str">
-        <v>近海铁板中大型主力</v>
+        <v>大饵重装泛用</v>
       </c>
       <c r="T260" t="str">
-        <v>中大型青物 / 高扭矩 / 船钓鼓轮</v>
+        <v>大线杯 / 大物 / 淡海水重装</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>DRE5009</v>
+        <v>DRE5023</v>
       </c>
       <c r="B261">
         <v>2</v>
       </c>
       <c r="C261" t="str">
-        <v>TATULA SV TW 100</v>
+        <v>SPARTAN IC</v>
       </c>
       <c r="D261" t="str">
         <v/>
       </c>
       <c r="E261" t="str">
-        <v>2025</v>
+        <v/>
       </c>
       <c r="F261" t="str">
-        <v>25 TATULA SV TW 100</v>
+        <v/>
       </c>
       <c r="G261" t="str">
         <v/>
       </c>
       <c r="H261" t="str">
-        <v>泛用,海水,bass</v>
+        <v/>
       </c>
       <c r="I261" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J261" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20SV%20TW%20100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SPARTAN%20IC_main.jpg</v>
       </c>
       <c r="K261" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16591,60 +16561,60 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M261" t="str">
-        <v>泛用主力</v>
+        <v>海水船钓入门</v>
       </c>
       <c r="N261" t="str">
-        <v>TATULA第三代，次世代全球標準隆重登場 / Φ32mm超硬鋁合金線杯，搭載TATULA系列首款SV BOOST，追求真正的多功能性能 / TATULA系列的核心是強韌設計概念，經過砥礪後，大幅提升了基本性能 / 在全球推廣並傾注力量於 HYPERDRIVE DESIGN</v>
+        <v>擁有PE2號-200M的飽滿線容量，兼具力量、輕巧、COMPACT的SPARTAN IC / 可廣泛對應各種LIGHT GAME / ATD(自動拉力調節系統)/超合金框架/LED背光/計時器顯示/可交換電池/105mm長強力手把＋混合式手把握丸/止線機能 日本官網</v>
       </c>
       <c r="O261" t="str">
-        <v>¥32,400</v>
+        <v>¥26,800</v>
       </c>
       <c r="P261" t="str">
         <v>在售</v>
       </c>
       <c r="Q261" t="str">
-        <v>TATULA第三代，次世代全球標準隆重登場！ Φ32mm超硬鋁合金線杯，搭載TATULA系列首款SV BOOST，追求真正的多功能性能。 TATULA系列的核心是強韌設計概念，經過砥礪後，大幅提升了基本性能。在全球推廣並傾注力量於 HYPERDRIVE DESIGN。 TATULA 第3代的次世代全球標準機型。 兼具安全性和後半段延展性的超級多用途捲線器。 磨練出高性能的基礎，捲線性能大幅提升。 延續 TATULA 系列的核心耐用概念！ DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER ARMED HOUSING (AL) (強力防護外殼-鋁) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■SV-BOOST BOOST結構的最大特點在於能夠分2個階段伸出的可變電磁感應旋轉底座部分。SV-BOOST 在保留SV CONCEPT的零故障性基礎上，根據線軸轉速瞬時提供兩段最佳的制動力，實現投擲後半段的延展。這一系統在保持舒適性能的同時，也具備出色的遠投性能。拋投時的立起過程在拋投後半段的延展中，對於初速的反捲區域，瞬間發揮最大的制動力以進行控制，然後在中段到後段逐漸減少制動力，實現後半段的延伸。 ■ZERO ADJUSTER 調整「ZERO ADJUSTER」並執行「零間隙」設定，通過磁煞的進步，可以僅透過磁煞調節來控制所有路亞。在開始釣魚前進行設定，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※「零間隙」設定指的是在保留微小間隙(約0.2mm)的情況下，將捲線器設置在不會發生滑動的模式。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■搭載 φ32mm (寬24mm) 超硬鋁合金線杯 繼20 TATULA SV TW後再度搭載，展現出色的線杯反應性能與投擲能力。無論是 2克級的小餌(small rubber ) 還是 大型餌(Big Bait)，都能穩定實現遠距投擲，展現優異的表現。 ■搭載85mm鋁製曲柄握把及高抓力I型輕量握丸 有助於舒適的捲線體驗。 ※另售選購配件（推薦品項） 握丸：對應S尺寸握丸 握把：RCSB碳纖曲柄把手 （80ｍｍ～95ｍｍ） ：RCSB碳纖曲柄（80ｍｍ,90ｍｍ） ※考量捲線器的尺寸與平衡性，推薦使用 不超過95mm 的握把。 發售時間 2024.12</v>
+        <v>擁有PE2號-200M的飽滿線容量，兼具力量、輕巧、COMPACT的SPARTAN IC。可廣泛對應各種LIGHT GAME。 ATD(自動拉力調節系統)/超合金框架/LED背光/計時器顯示/可交換電池/105mm長強力手把＋混合式手把握丸/止線機能 日本官網</v>
       </c>
       <c r="R261" t="str">
         <v/>
       </c>
       <c r="S261" t="str">
-        <v>淡海水泛用主力</v>
+        <v>船钓计数入门</v>
       </c>
       <c r="T261" t="str">
-        <v>SV易控 / 一般路亚覆盖广 / 性能均衡</v>
+        <v>计数鼓轮 / 实用取向 / 深水近海</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>DRE5010</v>
+        <v>DRE5024</v>
       </c>
       <c r="B262">
         <v>2</v>
       </c>
       <c r="C262" t="str">
-        <v>ALPHAS BF TW</v>
+        <v>STEEZ CT SV TW</v>
       </c>
       <c r="D262" t="str">
         <v/>
       </c>
       <c r="E262" t="str">
-        <v>2025</v>
+        <v/>
       </c>
       <c r="F262" t="str">
-        <v>25 ALPHAS BF TW</v>
+        <v/>
       </c>
       <c r="G262" t="str">
         <v/>
       </c>
       <c r="H262" t="str">
-        <v>精细,泛用,bass</v>
+        <v>精细,bass</v>
       </c>
       <c r="I262" t="str">
         <v>baitcasting</v>
       </c>
       <c r="J262" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ALPHAS%20BF%20TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20CT%20SV%20TW_main.png</v>
       </c>
       <c r="K262" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16653,901 +16623,33 @@
         <v>2026-04-21T10:52:09.016Z</v>
       </c>
       <c r="M262" t="str">
-        <v>BF进阶主力</v>
+        <v>精细CT旗舰</v>
       </c>
       <c r="N262" t="str">
-        <v>無與倫比、全方位的雙軸細膩釣組性能 進一步發揮細膩釣組性能，搭載“SS MAGFORCE”的ALPHAS系列登場 / 實現了前所未有的低彈道且延展力十足的投擲性能，並具備順暢的迴轉效果，以及堅固且簡約的結構，成為高標準的細膩釣組機型 / 其特點在於： 全新搭載的 G1超硬鋁合金製φ30mm細膩釣組線杯，透過搭配“SS MAGFORCE”的乘數作用，達到與超小口徑φ28mm AIR線杯匹敵的自重 / “SS MAGFORCE”煞車系統甚至顛覆了以往大口徑線杯的缺點，能徹底發揮線杯性能，再結合 TWS（T-Wing System） 最大化釋放拋線量，帶來獨特的投擲手感</v>
+        <v>CT(COMPACT&amp;TOUGH)、以全新的概念實現了STEEZ更進一步的進化 / 搭載精巧機身和30mm直徑的G1硬鋁合金製成的CT SV線杯更顯得相得益彰 / 初始速度提升出眾的CT SV線杯其多樣性能自不必多說，就連在微物精釣領域也能駕馭，並且拋投感也淩駕以往 / 從STEEZ SV TW那裡繼承的流暢卷上力是C1硬鋁合金切削製成的完美禮物</v>
       </c>
       <c r="O262" t="str">
-        <v>¥51,900</v>
+        <v>¥63,000</v>
       </c>
       <c r="P262" t="str">
         <v>在售</v>
       </c>
       <c r="Q262" t="str">
-        <v>無與倫比、全方位的雙軸細膩釣組性能 進一步發揮細膩釣組性能，搭載“SS MAGFORCE”的ALPHAS系列登場。 實現了前所未有的低彈道且延展力十足的投擲性能，並具備順暢的迴轉效果，以及堅固且簡約的結構，成為高標準的細膩釣組機型。 其特點在於： 全新搭載的 G1超硬鋁合金製φ30mm細膩釣組線杯，透過搭配“SS MAGFORCE”的乘數作用，達到與超小口徑φ28mm AIR線杯匹敵的自重。“SS MAGFORCE”煞車系統甚至顛覆了以往大口徑線杯的缺點，能徹底發揮線杯性能，再結合 TWS（T-Wing System） 最大化釋放拋線量，帶來獨特的投擲手感。這款小烏龜將引領眾多細膩釣組玩家探索更廣闊的領域。 儘管這是一個擅長細膩釣組性能的系列，但始終不變的是專為追求大魚而設計的細膩捲線器的本質。作為次世代細膩機型，它實現了細膩捲線器設計理念“HYPERDRIVE DESIGN”。無論是淡水還是海水使用都能勝任，採用全金屬外殼，主結構、齒輪側面板和旋鈕側面板均使用鋁合金，實現了輕量與剛性兼具的結構。並且，期待已久的拖拉拉出點擊功能也已搭載。 在手掌側，進一步的薄型化實現了壓倒性的輕巧感。投擲精確度、操作性以及與手部的完美契合，提升了釣具操作的便捷性，並且穩定的投擲姿勢和竿的感受，隨時支持應對變化的環境。即使是調節旋鈕也經過徹底檢驗，追求大口徑帶來的調整便捷性與誤作動防止的平衡。 考量到在各種場域的使用，提供兩種齒輪比選擇。齒輪比6.3適合於溫暖的環境，特別適合小型餌、極小的I型餌，能穩定地提供直線性與流暢的回收。齒輪比8.5則完美支援各種細膩釣組的線張力控制，確保低彈道與迅速回收的無比準確。細膩釣組性能已經達到無懈可擊的陣容。 INDUCT ROTOR (可變電感旋轉底座) 比較 直徑約小14 % 重量減輕約27% ※所有值均在 20ALPHAS AIR TW 和 25ALPHAS BF 之間進行比較。 產品詳情 ■HYPERDRIVE DESIGN(強力驅動設計) 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPERDRIVE DIGIGEAR (強力驅動齒輪) 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT (強力雙軸支撐系統) 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH (強力堅固板機) 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座INDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 此外，24 STEEZ SV TW終於去除了「機械煞車結構」，實現了絕對精確的ZERO設定。不再需要依賴效果不穩定的機械式動作為輔助煞車，設定的不確定性和麻煩也完全消除了。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■BF CONCEPT 透過簡易設定，自在投擲“超”輕量級的魚餌 專為超輕量魚餌設計。當你用力晃動竿子進行擲投時，魚餌會以低彈道平穩飛出，而在一般的拋投中，其飛行距離可與紡車捲線器相媲美。這款「DAIWA BF」的一大特點是可以在不重新調整剎車力的情況下，隨意交替使用擲投和拋竿方式。 搭載將細膩釣法性能發揮到極致的BF線杯。為了應對超輕量路亞，這款線杯超級輕量且搭載微型BB。不僅可以靈活操作更小更輕的魚餌，還能實現「更長的拋投距離以及柔和的入水」。在挑戰艱難環境時，它將成為捕捉到最後一條魚的強力武器。 ■SS MAGFORCE 全新的磁力剎車結構SS MAGFORCE目標實現「更低慣性的線杯」，進一步突破未踏領域。其特性為具備對抗惡劣條件的優異能力，能夠配合不同釣友及各式各樣的情況，兼容性很強的投擲性能。瞬間提升的線杯旋轉反應，使得從小幅度的拋竿中拋出的路亞能夠描繪出低且延伸出去的軌跡擊中瞄準的釣點。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 產品詳情 ■φ30mm G1超硬鋁合金製BF線杯 首款專為SS MAGFORCE設計的φ30mm G1超硬鋁合金製BF線杯。為了超越之前徹底輕量化的φ28mm AIR線杯，SS MAGFORCE的引入使得我們對線杯的形狀進行了大幅度的重新設計。結果，25ALPHAS BF TW系列搭載的線杯由φ28mm擴大至φ30mm，但線杯元件的自重幾乎保持不變。 ■SS MAGFORCE（簡潔迅速的MAGFORCE） 全新的剎車系統，能夠在輕巧的揮竿中發揮出舒適的低彈道投擲性能。從零開始重新審視傳統結構，實現了壓倒性的輕量化和低慣性化，專為細線釣組設計的系統。極限追求側板內部和線杯元件的死角空間的輕巧化。能夠輕鬆發力進行投擲，實現比以往更高精度的投擲。透過SS MAGFORCE的設計，傳統結構的死角部分得以縮小，與20ALPHAS AIR TW相比，側板薄型化了6%。更加容易握持，變得更為輕巧。 ■KTF開發合作 與K.T.F.代表澤村幸弘氏的共同開發。自2000年代中期以來，他一直提倡貝特精釣的有效性，是這一領域的先驅，至今仍在國內外賽事中發光發熱，被稱為“Mr.貝特精釣”。為了提供最佳的貝特精釣性能，化妝盒上刻有其印記。 ■鋁製注油蓋 25ALPHAS BF TW搭載了鋁製注油蓋。出廠時進行了線杯零間隙設置（微小間隙約0.2mm），因此不需要調整機械剎車。使用隨附的專用工具可以拆卸蓋子，拆卸後可對小齒輪球軸承進行注油和維護。 ■拖曳聲音提示 搭載了備受期待的拖曳聲音提示。在與魚搏鬥時，當線被拉出時，拖曳裝置會發出聲音，方便判別剎車的運作。使用細線能夠在遊戲展開中佔得有利地位，這是一項必不可少的結構。 ■配備6BB 滾珠軸承 、小齒輪部分2BB(CRBB) 、齒輪軸兩端2BB(CRBB) 、線軸兩端2BB(CRBB) ■使用環境：海水對應 發售時間 2024.12</v>
+        <v>CT(COMPACT&amp;TOUGH)、以全新的概念實現了STEEZ更進一步的進化。搭載精巧機身和30mm直徑的G1硬鋁合金製成的CT SV線杯更顯得相得益彰。初始速度提升出眾的CT SV線杯其多樣性能自不必多說，就連在微物精釣領域也能駕馭，並且拋投感也淩駕以往。從STEEZ SV TW那裡繼承的流暢卷上力是C1硬鋁合金切削製成的完美禮物。另外搭配700型線杯的新型[TWS]出線系統和[SV CONCEPT]之間發揮著相乘效果，實現了驚人的精密性能。新增加的SH捲線器規格型號，應對不同的做釣需求。 日本官網</v>
       </c>
       <c r="R262" t="str">
         <v/>
       </c>
       <c r="S262" t="str">
-        <v>BF进阶泛用</v>
+        <v>鲈鱼精细旗舰</v>
       </c>
       <c r="T262" t="str">
-        <v>轻饵投掷友好 / G1线杯 / 细腻操控</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="str">
-        <v>DRE5011</v>
-      </c>
-      <c r="B263">
-        <v>2</v>
-      </c>
-      <c r="C263" t="str">
-        <v>STEEZ SV TW</v>
-      </c>
-      <c r="D263" t="str">
-        <v/>
-      </c>
-      <c r="E263" t="str">
-        <v>2024</v>
-      </c>
-      <c r="F263" t="str">
-        <v>24 STEEZ SV TW</v>
-      </c>
-      <c r="G263" t="str">
-        <v/>
-      </c>
-      <c r="H263" t="str">
-        <v>泛用,bass</v>
-      </c>
-      <c r="I263" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J263" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20SV%20TW_main.jpg</v>
-      </c>
-      <c r="K263" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L263" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M263" t="str">
-        <v>旗舰泛用</v>
-      </c>
-      <c r="N263" t="str">
-        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴 / 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化 / 為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品 / 這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」</v>
-      </c>
-      <c r="O263" t="str">
-        <v>¥77,200</v>
-      </c>
-      <c r="P263" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q263" t="str">
-        <v>為了那些認真看待鱸魚釣的人們 DAIWA致力創造出的產品，與那些將鱸魚釣視為生活重心、認真看待鱸魚釣的人們產生共鳴。 這是DAIWA開發團隊將對鱸魚釣的熱忱，透過產品和訊息與大家分享的品牌理念具體化。為此，DAIWA憑藉其技術和熱情，嚴謹地打造出這些產品。這不僅僅只是釣竿與捲線器，而是將信念與驢魚釣友的熱情一同寄託在釣鱸魚所需要的一切物品……這就是「STEEZ」。 Pride of STEEZ 第三世代STEEZ 開始啟動 STEEZ的雙軸捲線器，以2mm為單位有不同線杯徑規格。 φ28mm（AIR） φ30mm（CT） φ34mm（LIMITED・AⅡ） φ36mm（HLC） 而填補長久以來空缺的Φ32mm，是多功能型。搭載φ32mm SV BOOST線杯的第三代STEEZ SV TW，是完成次世代雙軸捲線器戰略藍圖的關鍵作品。 這第三代產品沒有Zero Adjuster（舊有的機械煞車）。早在第二代16STEEZ時，DAIWA捲線器已經只依賴MAGFORCE旋鈕來完成剎車調整。而第三代則完全去除了傳統的機械剎車結構，變成了全新的無輔助剎車構造。 其高剛性且簡約的外殼內安裝了掌管“捲收和耐久性”的HYPERDRIVE DESIGN。 拋投性能也大幅提升，G1超硬鋁合金φ32mm SV BOOST線杯、TWS、無輔助剎車結構，這些設計均遵循了DAIWA長年追求並最終完成的“拋投設計理念”ULTIMATE CASTING DESIGN。 以維持高水準的初期迴轉性能為目標，大幅提升所有基本性能的BAIT(雙軸)捲線器的次世代設計概念。 DAIWA 技術 ■HYPERDRIVE DESIGN(強力驅動設計) HYPERDRIVE DESIGN由4個重要技術組成。以配備可長時間持續滑順迴轉的HYPERDRIVE DIGIGEAR 為必要條件， 承受齒輪驅動帶來強力又輕盈之回捲力的HYPER DOUBLE SUPPORT，強力支持內部結構，不易扭曲變形的HYPER ARMED HOUSING機殼，與在艱困環境也能持續運作，大幅降低卡鹽的絕緣結構的HYPER TOUGH CLUTCH 的加乘效果，能在各釣場中持續發揮穩定的性能。 ■HYPER ARMED HOUSING (強力防護外殼) 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD (ULTIMATE TOURNAMENT DRAG) 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來得咬訊或青物暴衝時也能安心應對。 ■ULTIMATECASTING DESIGN 將你心中所描繪的拋投軌跡變為現實。為了實現DAIWA長年追求的究極拋投設計，必須整合四個對拋投能力有重大影響的元素，並將其性能提升至極限。這些元素包括世界首創的DAIWA電磁感應剎車系統［MAGFORCE＋可變電磁感應旋轉底座INDUCT ROTOR］、［TWS（T-Wing系統）］、［G1超硬鋁製線杯］和［ZERO ADJUST］，這些都是DAIWA獨有的技術和概念。 DAIWA多年來的不斷技術創新，最終實現了究極拋投設計及其未來的進化，所有這一切，都是為了將釣魚者心中所描繪的拋投軌跡變為現實。 ■ULTIMATECASTING BRAKE 不變的優勢。可變的個性。完全「非接觸式」的煞車系統，因應電磁誘導的煞車[MAGFORCE]以及線杯的旋轉速度等等進出磁場。正式不倚賴摩擦的非接觸式，不受浸水、下雨、飛沫、溫度諸如此類使用環境影響，零件不會耗損的關係，性能能半永久地持續。另外正是MAGFORCE的效用非常安定，才能配合性格多元的INDUCT ROTOR，如對輕量級路亞的適性以及泛用性、2段可變的超遠投性。 ■ULTIMATECASTING ZERO ADJUST 消除輔助煞車的麻煩和設置的不確定性。對於DAIWA登峰造極的主煞車(MAGFORCE)來說，不需要輔助(機械式)煞車。由從[ZERO ADJUST]概念所誕生的［ZERO ADJUSTER](無調整器)，一旦完成了「線杯間隙ZERO設定」後，只需通過磁力調節旋鈕就能應對各種情況。 此外，24 STEEZ SV TW終於去除了「機械煞車結構」，實現了絕對精確的ZERO設定。不再需要依賴效果不穩定的機械式動作為輔助煞車，設定的不確定性和麻煩也完全消除了。 ■ULTIMATECASTING LINE GUIDE 將捲收與拋投的效果結合為一體的無雙結構TWS。「TWS」這個結構能同時實現釣線的緻密捲收和一舉擴大拋投時的無阻力範圍。通過這個結構，釣線的放線變得更加順暢，大幅提升了DAIWA雙軸捲線器的遠投性能。此外，TWS還有效防止了在導線規上發生的「釣線追撞事故」以及炒米粉現象。在24 STEEZ SV TW中，還配備了進一步減少釣線放線阻力的調子TWS。隨著近年來線杯高轉速化的進展，TWS的重要性愈加顯著。 ■ULTIMATECASTING SPOOL 利用特殊素材和加工技術實現高強度、低慣性線杯。雙軸捲線器的線杯通常使用鋁合金，其中最高強度和最高級別的是DAIWA所採用的G1超硬鋁合金。這種材料的強度是鎂的兩倍，超硬鋁合金的1.3倍，用於線杯時，在以強度為設計基準的前提下，可以實現極其輕量的特性。然而，要高精度加工G1超硬鋁合金，需要非常高的加工技術。只有能夠將材料的剛性以輕量的形式充分利用，才能設計和加工出極薄的線軸。 產品詳情 ■新型TWS 在追求提高控制性的同時減少拋投時的放線所產生的阻力，即追求“無阻力範圍的擴展”目標的過程中，DAIWA對其獨有技術TWS（T-Wing系統）進行了改進。 在DAIWA的小烏龜捲線器中，根據不同的線杯尺寸，使用相應適配的TWS。 此次為新型線軸尺寸設計的TWS（照片左），引入了全新開發的錐形設計。 在比較新型TWS尺寸中錐形設計開口部時，結果顯示擴展了27%。與16STEEZ SV TW搭載的TWS（照片右）相比，即便橫幅縮小，仍實現了開口部16%的擴展。 除了擴展無阻力範圍外，還結合了特殊表面處理“DLC”，將線放出性能最大化。 根據錐形設計有無的飛距離測試結果顯示，在配重7克時，飛距離最多提升了4.9%。 DAIWA即使對於其獨有技術也不斷精益求精，持續探求 “令人欲罷不能地想不斷拋投”的拋擲手感。 ■G1超硬鋁合金製線杯 G1超硬鋁合金是一種特殊的鋁合金，具有鎂的兩倍以及超硬鋁合金1.3倍的強度。這種超輕量且具有卓越剛性的材料是航空器結構材料和精密儀器等輕量合金中的最高等級。 為了在保持相同強度的同時實現壓倒性的輕量感，G1超硬鋁合金線軸在不進行任何加壓變形加工，僅通過減少厚度來維持足夠的強度。這種輕量帶來的旋轉感受反饋和高剛性帶來的精確旋轉，均達到無與倫比的水準。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。 ■注油蓋 隨著無輔助剎車構造，移除了ZERO ADJUSTER。24STEEZ SV TW搭載了注油蓋。 使用附屬的專用工具可以取下注油蓋。取下蓋子後，可以對小齒輪滾珠培林進行注油和維護。 ■全新設計的星形煞車結構 為了追求操作性，搭載了新形狀的星型煞車裝置（照片右）。相比傳統的星型煞車裝置（照片左），新形狀設計更為薄型化，並重新檢視了舊型結構。甚至在每次調整聲上也精益求精，實現了細微而清晰的星形煞車調整提示音。 ■煞車出線警示音 在追求捕獲大魚所需的高煞車性能，不僅是最大煞車力，還致力於實現釣線滑順對應魚拉力的平滑操作性能，目標是成為同級別中的No.1。 此外，還搭載了煞車出線警示音。這個功能可以對應魚兒突然猛衝時發出聲音，提示釣者煞車系統正處於極限對抗，從而為釣者提供極大的優勢。 ■HYPER ARMED HOUSING（全金屬結構）本系列產品本體和齒輪側板（手柄側）採用了鎂金屬；而在調整旋鈕側側板則採用了高強度壓鑄成型的鋁合金，加上經過精密的機械切割加工，從而展現出堅不可摧的剛性。 ■產品對應客製零件 握丸：對應S尺寸握丸 握把：RCSB各種握把 RCSB BF握把組 RCSB 曲柄握把組 RCSB 碳纖曲柄握把組 23RCSB 碳纖曲柄握把組 RCSB ESD 100mm曲柄握把組 ■線杯互換系統 目前沒有有互換性的線杯。 ■附屬品 ・使用說明書 ・展開圖 ・問卷登錄ID號碼卡 ・捲線器盒（有STEEZ LOGO） ・捲線器腳部用保護貼紙 ※對應海水 ※捲線量是大概。依據製造商、品項、張力會有不同。 ※捲收長度是握把轉一圈的長度。</v>
-      </c>
-      <c r="R263" t="str">
-        <v/>
-      </c>
-      <c r="S263" t="str">
-        <v>鲈鱼旗舰泛用</v>
-      </c>
-      <c r="T263" t="str">
-        <v>SV抛投稳定 / 高端鲈鱼主线 / 适配面广</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="str">
-        <v>DRE5012</v>
-      </c>
-      <c r="B264">
-        <v>2</v>
-      </c>
-      <c r="C264" t="str">
-        <v>TATULA TW 100</v>
-      </c>
-      <c r="D264" t="str">
-        <v/>
-      </c>
-      <c r="E264" t="str">
-        <v>2024</v>
-      </c>
-      <c r="F264" t="str">
-        <v>24 TATULA TW 100</v>
-      </c>
-      <c r="G264" t="str">
-        <v/>
-      </c>
-      <c r="H264" t="str">
-        <v>泛用,海水,bass</v>
-      </c>
-      <c r="I264" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J264" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20TW%20100_main.jpg</v>
-      </c>
-      <c r="K264" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L264" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M264" t="str">
-        <v>入门进阶主力</v>
-      </c>
-      <c r="N264" t="str">
-        <v>「TATULA系列慶祝10周年 / 」 迎接下一個10年的第三代TATULA登場 / 全新的TATULA首次搭載了「HYPERDRIVE DESIGN」於TATULA TW 100系列 / 進一步提升TATULA系列的核心概念和基本性能，基本性能大幅提升</v>
-      </c>
-      <c r="O264" t="str">
-        <v>¥23,300</v>
-      </c>
-      <c r="P264" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q264" t="str">
-        <v>「TATULA系列慶祝10周年！」 迎接下一個10年的第三代TATULA登場！ 全新的TATULA首次搭載了「HYPERDRIVE DESIGN」於TATULA TW 100系列！ 進一步提升TATULA系列的核心概念和基本性能，基本性能大幅提升！ 將全球化的「HYPERDRIVE DESIGN」引入並注重的模式！ DAIWA 技術 ■HYPERDRIVE DESIGN 強力、滑順回準的永續，雙軸捲線器所需性能的集大成。從驅動齒輪到小齒輪，不間斷的傳導動能的動力裝置。從外側確實的持續支持驅動不，實現穩定且安靜驅動力的機殼。在任何環境下都能座動的多性能結構。實現高效率且遠遠超越寄往捲線力量及滑順迴轉性能的雙軸捲線器設計概念。以經驗為武器的DAIWA，創造初次世代的標準。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長嘯基本維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 ■ZERO ADJUSTER 首先，通過調整“ZERO ADJUSTER”並執行“零間隙”設定，通過磁煞的進步，可以僅通過磁煞調節來控制所有路亞。 “ZERO ADJUSTER”可在開始釣魚之前進行“零設定”，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※“零間隙”設定指的是在保留微小間隙（約0.2mm）的情況下，將捲線器設置在不會發生滑動的模式。 產品詳情 ■煞車特性 搭載MAGFORCE-Z磁性剎車系統。保持著磁力結構的MAGFORCE不變，通過根據線杯轉速平滑啟動感應，使得前半段煞車強度增強，後半段減弱，從而獲得有彈性的投擲感受。易於調整煞車力度，且具有對外部環境的強韌性等特點，是一種性能卓越的煞車系統。 ■線杯特性 採用直徑34mm（寬度24mm）的超級鋁合金製線杯。延續20TATULA SV TW的超級鋁合金製線杯，提高了線杯響應速度，提高了投擲穩定性，實現了從5克到110克（約4盎司）範圍內，包括大型魚餌在內的穩定遠投性能。 ■ 搭載TWS 大幅擴大了無阻力範圍。因此，飛行距離增加，控制性提高，形態加快，倒噴現象減少。TWS提升了餌輪的所有基本性能。 ■ 搭載TWS 大幅擴大了無阻力範圍。因此，飛行距離增加，控制性提高，形態加快，倒噴現象減少。TWS提升了餌輪的所有基本性能。</v>
-      </c>
-      <c r="R264" t="str">
-        <v/>
-      </c>
-      <c r="S264" t="str">
-        <v>淡海水入门进阶</v>
-      </c>
-      <c r="T264" t="str">
-        <v>价格友好 / 基础性能完整 / 通用型</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="str">
-        <v>DRE5013</v>
-      </c>
-      <c r="B265">
-        <v>2</v>
-      </c>
-      <c r="C265" t="str">
-        <v>SALTIGA 15</v>
-      </c>
-      <c r="D265" t="str">
-        <v/>
-      </c>
-      <c r="E265" t="str">
-        <v>2022</v>
-      </c>
-      <c r="F265" t="str">
-        <v>22 SALTIGA 15</v>
-      </c>
-      <c r="G265" t="str">
-        <v/>
-      </c>
-      <c r="H265" t="str">
-        <v/>
-      </c>
-      <c r="I265" t="str">
-        <v>drum</v>
-      </c>
-      <c r="J265" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%2015_main.jpg</v>
-      </c>
-      <c r="K265" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L265" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M265" t="str">
-        <v>近海船钓旗舰</v>
-      </c>
-      <c r="N265" t="str">
-        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚 / 」為了實現釣手的夢想而誕生的「SALTIGA」 / 它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術 / 它的前提是與未知的大物對峙</v>
-      </c>
-      <c r="O265" t="str">
-        <v>¥80,000</v>
-      </c>
-      <c r="P265" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q265" t="str">
-        <v>BREAK YOUR RECORD -追逐夢想 「總有一天，我要釣到那條夢想中的魚。」為了實現釣手的夢想而誕生的「SALTIGA」。它承襲了DAIWA捲線器中最強大的基因，並不斷進化融入最新的技術。 它的前提是與未知的大物對峙。不斷挑戰裝備的極限，追求各個方面的強度，致力於成為易於使用且性能優越的好夥伴。SALTIGA所肩負的責任是成為確實能夠接近夢想魚的助力。持續實現存在價值，即實現釣手的夢想。其可靠性能支持著世界各地釣手的夢想。 極致旋轉、操作和耐久的旗艦型捲線器。 一切都是為了捕獲目標魚。 透過極致旋轉、操作和耐久，持續進化的SALTIGA。 DAIWA引導釣手前往更高峰。 DAIWA 技術 ■HYPERDRIVE DESIGN 強力、滑順回轉的永續，雙軸捲線器所需性能的集大成。從驅動齒輪到小齒輪，不間斷的傳導動能的動力裝置。從外側確實的持續支持驅動不，實現穩定且安靜驅動力的機殼。在任何環境下都能座動的多性能結構。實現高效率且遠遠超越寄往捲線力量及滑順迴轉性能的雙軸捲線器設計概念。以經驗為武器的DAIWA，創造初次世代的標準。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER DOUBLE SUPPORT 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈地進行捲線操控。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■MAGSEALED BALL BEARING〈磁油防水滾珠軸承〉 DAIWA以其獨特的技術，首次成功將滾珠軸承本身進行了磁油密封。通過具有磁性的液體油膜，抑制了水和異物進入滾珠軸承內部，同時保持了滾珠軸承的原始旋轉性能，大大減輕了鏽蝕、卡鹽和異音等問題。 ■ATD 根據魚的拉力平滑作動，持續平穩地運轉。ATD追求流暢的啟動和跟蹤性，讓您能夠專注於戰鬥，而無需擔心剎車設置。 產品詳情 ■陽極保護 「抗腐蝕，卓越耐用」 陽極保護是一種減緩金屬腐蝕的技術。當金屬腐蝕時，陽極（鋅）會承擔腐蝕。通過將這項技術應用於捲線器上，將腐蝕集中在陽極板上，以保持其耐用性能。這是第一次在DAIWA捲線器上應用這項功能。 ■拇指持握模組 「持握手法的轉變」 通過分析各種釣手的握持方式，追求更貼合手形的形狀。開發了拇指握持模組，旨在實現更容易握持並減少指頭滑出的拇指置放位置。考慮了拇指在關閉離合器後的位置，顯著提高了舒適性。 這種全新的握持體驗大大改變了以往的“握持”概念。 ■75-85mm 鋁製曲柄手柄臂 「堅韌耐用的鋁製搖臂」 適合於大物釣法，使用方便的75-85mm鋁製搖臂。 ※適用於22 SALTIGA 15系列 ※出貨時長度為85mm ■85-95mm 碳纖維製曲柄手柄臂 「高靈敏度・輕量化的碳纖維搖臂」 22SALTIGA 15-SJ系列採用了碳纖維製搖臂。透過高靈敏度和輕量化，提升了配備的平衡性。 5mm厚度的設計實現了高剛性。即使在進行強力的拋擲或者與大型魚對抗時，也能夠不彎曲地進行捲線。 ※適用於22SALTIGA 15-SJ系列 ※出貨時長度為95mm ■線杯更換系統 「簡單且方便的線杯更換功能」 使用側板螺絲的三點支撐結構。 準備好備用線杯，可以根據突然的斷線或突發狀況，立即進行線杯更換。 隨附的線杯更換扳手（T8），解開齒輪側蓋的側板螺絲3個，即可拆卸齒輪側蓋。 側板螺絲採完全鬆開也不會掉落的防脫結構，避免丟失的麻煩。 ■大口徑Φ52mm輪子 「最適合的線杯尺寸設計」 選擇Φ52mm輪子。 以線容量4號PE-300m自豪，實現了該領域NO.1的線容量。 線杯形狀考慮到放線速度變化的影響，實現了最佳平衡。並對輕巧的捲收和與獵物爭取距離的捲線功率產生重大影響。 ■煞車拉出提示音 「以聲音掌握每一刻的緊張對決」 在與大型魚的對抗中，精準的煞車設定至關重要。 當魚突然猛拉時，能透過聲音判斷煞車作動情況，能為釣者帶來極大的操作優勢。 ■85mm T形把手 「無可比擬的握持感」 專為握持時的貼合感和手感所設計，追求最舒適的握姿，讓收線時的擁有舒適操作感的T形狀把手。 為了更容易搏魚，特別追求了中心的厚度，以方便進行搏魚的相關動作。在拉升時，牢牢握持，展現穩定的收線動作。 ■ 捲線器 15/15L： 適用於PE線的深杯捲線器規格 實現PE4-300米的大容量。 可達到PE1.5號-800米，適用於中深場釣遊。 與15S捲線器相容。 ■ 捲線器鎖定 「在垂釣場景中發揮作用的實用功能」 這是一種完全固定捲線器並鎖定捲線器逆轉的機制。 在掛底時，如果強行拉扯，可能不僅會損壞線，還可能損壞齒輪和滾珠軸承。然而，通過使用捲線器鎖定機制，可以將捲線器和齒輪分開，並在不損壞齒輪和滾珠軸承的情況下進行扯斷。 使用方法非常簡單。 1. 將捲線器鎖定切換到「開啟」位置。 2. 關閉離合器。 3. 在這個狀態下，第一次施加張力並拉斷線。 ※將捲線器和齒輪分開是關鍵。 這是一個必不可少的功能，能夠安心、安全地快速應對。</v>
-      </c>
-      <c r="R265" t="str">
-        <v/>
-      </c>
-      <c r="S265" t="str">
-        <v>近海船钓高端</v>
-      </c>
-      <c r="T265" t="str">
-        <v>深海与慢摇兼顾 / 大线容量 / 高负载</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="str">
-        <v>DRE5014</v>
-      </c>
-      <c r="B266">
-        <v>2</v>
-      </c>
-      <c r="C266" t="str">
-        <v>PR100 H</v>
-      </c>
-      <c r="D266" t="str">
-        <v/>
-      </c>
-      <c r="E266" t="str">
-        <v>2022</v>
-      </c>
-      <c r="F266" t="str">
-        <v>22 PR100 H</v>
-      </c>
-      <c r="G266" t="str">
-        <v/>
-      </c>
-      <c r="H266" t="str">
-        <v>泛用,海水</v>
-      </c>
-      <c r="I266" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J266" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/PR100%20H_main.jpg</v>
-      </c>
-      <c r="K266" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L266" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M266" t="str">
-        <v>基础入门</v>
-      </c>
-      <c r="N266" t="str">
-        <v>DAIWA 2022年『 PR100H 』系列小烏龜路亞捲線器 超人氣入門平價款的捲線器，搭配迷彩設計，新手入門首選 / ● PR100H MA-綠迷彩 ● PR100H MN-灰迷彩 ● PR100H MM-黃迷彩 ※ H-右手捲 HL-左手捲</v>
-      </c>
-      <c r="O266" t="str">
-        <v>¥6,700</v>
-      </c>
-      <c r="P266" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q266" t="str">
-        <v>DAIWA 2022年『 PR100H 』系列小烏龜路亞捲線器 超人氣入門平價款的捲線器，搭配迷彩設計，新手入門首選。 ● PR100H MA-綠迷彩 ● PR100H MN-灰迷彩 ● PR100H MM-黃迷彩 ※ H-右手捲 HL-左手捲</v>
-      </c>
-      <c r="R266" t="str">
-        <v/>
-      </c>
-      <c r="S266" t="str">
-        <v>淡海水基础入门</v>
-      </c>
-      <c r="T266" t="str">
-        <v>低预算 / 操作简单 / 入门练习友好</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="str">
-        <v>DRE5015</v>
-      </c>
-      <c r="B267">
-        <v>2</v>
-      </c>
-      <c r="C267" t="str">
-        <v>STEEZ AII TW</v>
-      </c>
-      <c r="D267" t="str">
-        <v/>
-      </c>
-      <c r="E267" t="str">
-        <v>2022</v>
-      </c>
-      <c r="F267" t="str">
-        <v>22 STEEZ AII TW</v>
-      </c>
-      <c r="G267" t="str">
-        <v/>
-      </c>
-      <c r="H267" t="str">
-        <v>远投,强力,bass</v>
-      </c>
-      <c r="I267" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J267" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20AII%20TW_main.jpg</v>
-      </c>
-      <c r="K267" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L267" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M267" t="str">
-        <v>高端重装主力</v>
-      </c>
-      <c r="N267" t="str">
-        <v>無論遠投或是近距離，都能實現更精確的拋投 / STEEZ A TW一直以來為眾多釣手提供了堅固耐用和穩定性，但第二代經歷了更進一步的淬鍊 / 將美國艱鉅的錦標賽經驗與下一代的Baitcasting Reel 設計理念「HYPERDRIVE DESIGN」相結合 / HYPER ARMED HOUSING（FULL-AL）的堅固性保持不變，而HYPERDRIVE DIGIGEAR則提高了捲動性能，即使在高負載情況下，也能實現平順且高功率的收捲</v>
-      </c>
-      <c r="O267" t="str">
-        <v>¥54,000</v>
-      </c>
-      <c r="P267" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q267" t="str">
-        <v>無論遠投或是近距離，都能實現更精確的拋投。 STEEZ A TW一直以來為眾多釣手提供了堅固耐用和穩定性，但第二代經歷了更進一步的淬鍊。將美國艱鉅的錦標賽經驗與下一代的Baitcasting Reel 設計理念「HYPERDRIVE DESIGN」相結合。 HYPER ARMED HOUSING（FULL-AL）的堅固性保持不變，而HYPERDRIVE DIGIGEAR則提高了捲動性能，即使在高負載情況下，也能實現平順且高功率的收捲。 STEEZ A II TW採用了新開發的φ34mm G1航空鋁超高精度MAG-Z BOOST線杯。通過淺杯化，僅配備所需的線容量，使捲線器總重量更輕量。結果而言，這項設計提高了捲線器的初始啟動性能，成為實用投擲性能的迷人特色之一。 高抓握性的I型握丸和新設計的90mm 航空鋁製手柄實現更加的捲動體驗外，同時STEEZ A II TW還標配了星盤剎車和MAGSEALED滾珠軸承。這不僅僅是黑鱸釣，也能應對海釣的可靠遠投型號--「STEEZ A II TW」。現代釣手所需要的功能濃縮匯集而成的跨時代捲線器。 DAIWA 技術 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。。 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側，以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈的進行捲線操控。 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場環境使用後的卡鹽維修件數，達到減少99%的實績，以最先進的絕緣構造自豪。 ■TWS TWS（T-Wing System）是一種DAIWA獨創設計，可以大幅減少位於捲線器最上方、靠近機身的導線的阻力，這樣可以減少線圈的旋轉阻力，確保少發生糾結，提供舒適的釣魚體驗。TWS可以實現更遠的投擲距離，提高控制性，同時減少線材打結。TWS可以提升所有Baitcasting Reel的基本性能。 ■MAGSEALED BALL BEARING 由於Baitcasting Reel的結構，海水很難避免地從捲線器和機身之間的縫隙滲入，最容易受到鹽水侵害的是主齒輪部分的軸承。在STEEZ A II TW系列中，為了進一步提高防水性和耐久性，採用了MAGSEALED BALL BEARING在機械旋鈕的一側的主軸齒輪支撐部位。這有助於保持初始性能。 ■MAGSEALED BALL BEARING 由於Baitcasting Reel的結構，海水很難避免地從捲線器和機身之間的縫隙滲入，最容易受到鹽水侵害的是主齒輪部分的軸承。在STEEZ A II TW系列中，為了進一步提高防水性和耐久性，採用了MAGSEALED BALL BEARING在機械旋鈕的一側的主軸齒輪支撐部位。這有助於保持初始性能。 其他技術 &amp; 產品詳情 ■MAG-Z BOOST 『BOOST SYSTEM 將 MAGFORCE-Z 的遠投性能發揮到極致』 MAG-Z BOOST 是將 MAGFORCE-Z 的遠投性能發揮到極致，注重飛距離的設定。MAGFORCE-Z 由於遠心力作用特性，不適合輕餌。然而，對於中重量級的餌，它可是最佳選擇，可以根據輸入的力量伸展飛行距離。 ■G1鋁鎂合金製Φ34mm 線杯 G1鋁鎂合金是一種特殊的鋁合金，展現出比鎂多2倍和超級鋁鎂合金多1.3倍的強度。這種超輕且具有卓越剛性的材料被廣泛應用於航空器結構和精密儀器中。為了實現壓倒性的輕盈感，同時保持相同的強度，捲線器透過薄肉化來保持輕盈所帶來的高速旋轉反應，以及高剛性帶來的精確無比的旋轉，使其無與倫比，難以被其他產品超越。 ■出線音效 出線音效是指在與魚進行搏鬥時，當出線時可以通過聲音區分剎車作用的構造。 出線聲的音質和大小都受到精心設計的關注，清脆、舒適！ ■ZERO SHAFT 線杯僅由BB支撐。因為無軸，所以沒有多餘的阻力。可以達到理想的線杯迴轉。 這也表示是最重視遠投性能的高動力輸出引擎的重要關鍵。 這個曾被稱為Speed Shaft的卷線輪機構於2021年被重新命名為"ZERO SHAFT"。</v>
-      </c>
-      <c r="R267" t="str">
-        <v/>
-      </c>
-      <c r="S267" t="str">
-        <v>鲈鱼高端远投</v>
-      </c>
-      <c r="T267" t="str">
-        <v>AII重载取向 / 高刚性 / 中重型饵友好</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="str">
-        <v>DRE5016</v>
-      </c>
-      <c r="B268">
-        <v>2</v>
-      </c>
-      <c r="C268" t="str">
-        <v>ZILLION TW HD</v>
-      </c>
-      <c r="D268" t="str">
-        <v/>
-      </c>
-      <c r="E268" t="str">
-        <v>2022</v>
-      </c>
-      <c r="F268" t="str">
-        <v>22 ZILLION TW HD</v>
-      </c>
-      <c r="G268" t="str">
-        <v/>
-      </c>
-      <c r="H268" t="str">
-        <v>远投,强力,海水,bass</v>
-      </c>
-      <c r="I268" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J268" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ZILLION%20TW%20HD_main.jpg</v>
-      </c>
-      <c r="K268" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L268" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M268" t="str">
-        <v>重载主力</v>
-      </c>
-      <c r="N268" t="str">
-        <v>新一代的HYPERDRIVE DIGIGEAR，使用高強度真鍮作為傳動齒輪，以及在小齒輪中使用高耐蝕銅合金，實現了強大而平滑的旋轉 / 採用HYPER ARMED HOUSING（全鋁）打造堅固的機身，使其在保持小巧的同時確保強大的機身剛性 / 新開發的Φ34mm G1鋁合金超高精度MAG-Z BOOST線輪實現了卓越的長距離投擲性能 / DAIWA 技術 &amp; 產品詳情 ◆MAGFORCE-Z BOOST MAGFORCE-Z BOOST是將MAGFORCE-Z的遠投性能極致發揮的設定</v>
-      </c>
-      <c r="O268" t="str">
-        <v>¥54,500</v>
-      </c>
-      <c r="P268" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q268" t="str">
-        <v>新一代的HYPERDRIVE DIGIGEAR，使用高強度真鍮作為傳動齒輪，以及在小齒輪中使用高耐蝕銅合金，實現了強大而平滑的旋轉。 採用HYPER ARMED HOUSING（全鋁）打造堅固的機身，使其在保持小巧的同時確保強大的機身剛性。 新開發的Φ34mm G1鋁合金超高精度MAG-Z BOOST線輪實現了卓越的長距離投擲性能。 DAIWA 技術 &amp; 產品詳情 ◆MAGFORCE-Z BOOST MAGFORCE-Z BOOST是將MAGFORCE-Z的遠投性能極致發揮的設定。由於MAGFORCE-Z的特性是遠心力驅動感應線杯，因此不適用於輕型路亞。然而，對於中到重型路亞的遠投卻非常理想，可以根據輸入的力量增加飛行距離。 ■TWS（T-Wing System） TWS（T-Wing System）是一項技術，顯著減少了在離開最高轉速的線杯的導線阻力，避免線組糾纏，使釣魚更加舒適。 ■UTD（Ultimate Tournament Drag） UTD（Ultimate Tournament Drag）消除初次起動時的阻力，實現無斷續的出線平順性，並且隨著收緊而具有更大的最大剎車力。 ■G1 鋁製線杯 G1 鋁合金是一種特殊的鋁合金，展現出比鎂多兩倍、超級鋁合金多1.3倍的強度。這種超輕量且優越的剛性材料被廣泛應用於航空器具的結構和精密儀器等領域。在保持相同強度的情況下表現驚人的輕巧感。這種輕巧性帶來的轉動回饋速度和高剛性帶來的精密旋轉是難以被其他產品超越的。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■ 零調整器 首先通過調整「零調整器」，實現「線杯無間隙」設定，因為磁煞的進步，可以僅通過磁煞系統控制所有的餌。 「零調整器」允許在開始釣魚之前進行「零設置」，從而在釣魚過程中不會發生誤差動作，讓您輕鬆享受釣魚。 ※「線杯無間隙」設定是指在保留微小間隙（約0.2mm）的情況下，設置線杯到達極限的設置。 ■ 出線聲 出線聲是指在與魚對抗時，當線被拉出時，剎車作動會發出聲音，以便通過聲音辨別剎車作動效果的結構。</v>
-      </c>
-      <c r="R268" t="str">
-        <v/>
-      </c>
-      <c r="S268" t="str">
-        <v>淡海水重载泛用</v>
-      </c>
-      <c r="T268" t="str">
-        <v>HD高负载 / 中大型饵 / 淡海水兼容</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>DRE5017</v>
-      </c>
-      <c r="B269">
-        <v>2</v>
-      </c>
-      <c r="C269" t="str">
-        <v>SALTIGA IC</v>
-      </c>
-      <c r="D269" t="str">
-        <v/>
-      </c>
-      <c r="E269" t="str">
-        <v>2021</v>
-      </c>
-      <c r="F269" t="str">
-        <v>21 SALTIGA IC</v>
-      </c>
-      <c r="G269" t="str">
-        <v/>
-      </c>
-      <c r="H269" t="str">
-        <v/>
-      </c>
-      <c r="I269" t="str">
-        <v>drum</v>
-      </c>
-      <c r="J269" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIGA%20IC_main.png</v>
-      </c>
-      <c r="K269" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L269" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M269" t="str">
-        <v>近海船钓计数旗舰</v>
-      </c>
-      <c r="N269" t="str">
-        <v>近海船钓与铁板兼顾 / 计数器辅助 / 中深水实战取向</v>
-      </c>
-      <c r="O269" t="str">
-        <v>¥70,400 - ¥71,500</v>
-      </c>
-      <c r="P269" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q269" t="str">
-        <v/>
-      </c>
-      <c r="R269" t="str">
-        <v/>
-      </c>
-      <c r="S269" t="str">
-        <v>近海船钓计数高端</v>
-      </c>
-      <c r="T269" t="str">
-        <v>船钓与铁板兼顾 / 计数器 / 深水适配</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="str">
-        <v>DRE5018</v>
-      </c>
-      <c r="B270">
-        <v>2</v>
-      </c>
-      <c r="C270" t="str">
-        <v>ZILLION SV TW</v>
-      </c>
-      <c r="D270" t="str">
-        <v/>
-      </c>
-      <c r="E270" t="str">
-        <v>2021</v>
-      </c>
-      <c r="F270" t="str">
-        <v>21 ZILLION SV TW</v>
-      </c>
-      <c r="G270" t="str">
-        <v/>
-      </c>
-      <c r="H270" t="str">
-        <v>泛用,bass</v>
-      </c>
-      <c r="I270" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J270" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ZILLION%20SV%20TW_main.jpg</v>
-      </c>
-      <c r="K270" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L270" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M270" t="str">
-        <v>鲈鱼主力</v>
-      </c>
-      <c r="N270" t="str">
-        <v>ZILLION SV TW 下一代雙軸捲線器技術HYPERDRIVE設計 ■HYPER DRIVE DIGIGEAR 新型設計的(雙軸)齒輪系統，可實現滑順的旋轉與耐用性，主齒輪（尺寸）不會減少，並且提高咬合率 / DAIWA的獨家技術可以達到上述要求並實現持久的初始光滑度 / ■HYPER DOUBLE SUPPORT 可持續的保持滑順度，通過兩個培林支撐小齒輪的兩端，即使附加重量也不影響捲動的手感 / ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力</v>
-      </c>
-      <c r="O270" t="str">
-        <v>¥45,400</v>
-      </c>
-      <c r="P270" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q270" t="str">
-        <v>ZILLION SV TW 下一代雙軸捲線器技術HYPERDRIVE設計 ■HYPER DRIVE DIGIGEAR 新型設計的(雙軸)齒輪系統，可實現滑順的旋轉與耐用性，主齒輪（尺寸）不會減少，並且提高咬合率。 DAIWA的獨家技術可以達到上述要求並實現持久的初始光滑度。 ■HYPER DOUBLE SUPPORT 可持續的保持滑順度，通過兩個培林支撐小齒輪的兩端，即使附加重量也不影響捲動的手感。 ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■SV BOOST 線杯 下一代SV概念，實現了令人振奮的高水平拋投性能，並增加了飛行距離。煞車系統的啟動從原本的一階段進化成二階段，在線杯低轉速時(拋輕克數餌)啟動較弱的第一階段煞車，線杯高轉速時(拋重克數餌)啟動較強的第二階段，並在餌飛行的後半段煞車會回到較弱的第一段，從而延伸餌的飛行距離。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■UTD消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。</v>
-      </c>
-      <c r="R270" t="str">
-        <v/>
-      </c>
-      <c r="S270" t="str">
-        <v>鲈鱼泛用主力</v>
-      </c>
-      <c r="T270" t="str">
-        <v>SV易控 / 抛投稳定 / 覆盖面广</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="str">
-        <v>DRE5019</v>
-      </c>
-      <c r="B271">
-        <v>2</v>
-      </c>
-      <c r="C271" t="str">
-        <v>ALPHAS SV TW 800H／22 ALPHAS SV TW 800S-XHL</v>
-      </c>
-      <c r="D271" t="str">
-        <v/>
-      </c>
-      <c r="E271" t="str">
-        <v>2021</v>
-      </c>
-      <c r="F271" t="str">
-        <v>21 ALPHAS SV TW 800H／22 ALPHAS SV TW 800S-XHL</v>
-      </c>
-      <c r="G271" t="str">
-        <v/>
-      </c>
-      <c r="H271" t="str">
-        <v>精细,泛用,bass</v>
-      </c>
-      <c r="I271" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J271" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ALPHAS%20SV%20TW%20800H%EF%BC%8F22%20ALPHAS%20SV%20TW%20800S-XHL_main.jpg</v>
-      </c>
-      <c r="K271" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L271" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M271" t="str">
-        <v>轻量泛用</v>
-      </c>
-      <c r="N271" t="str">
-        <v>■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力 / ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障 / ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統 / 他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性</v>
-      </c>
-      <c r="O271" t="str">
-        <v>¥33,700</v>
-      </c>
-      <c r="P271" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q271" t="str">
-        <v>■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■SV CONCEPT 能將磁性煞車應有的實戰優勢發揮最大極限，輕鬆愉快準確拋投，只要微調磁煞旋鈕，不管是4~5克左右的輕裝到重量級路亞都能輕鬆應付。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。 ■UTD 消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。</v>
-      </c>
-      <c r="R271" t="str">
-        <v/>
-      </c>
-      <c r="S271" t="str">
-        <v>轻量泛用进阶</v>
-      </c>
-      <c r="T271" t="str">
-        <v>小尺寸轻量 / 精细钓法 / 城市野场友好</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="str">
-        <v>DRE5020</v>
-      </c>
-      <c r="B272">
-        <v>2</v>
-      </c>
-      <c r="C272" t="str">
-        <v>STEEZ LTD SV TW</v>
-      </c>
-      <c r="D272" t="str">
-        <v/>
-      </c>
-      <c r="E272" t="str">
-        <v>2021</v>
-      </c>
-      <c r="F272" t="str">
-        <v>21 STEEZ LTD SV TW</v>
-      </c>
-      <c r="G272" t="str">
-        <v/>
-      </c>
-      <c r="H272" t="str">
-        <v>精细,泛用,bass</v>
-      </c>
-      <c r="I272" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J272" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20LTD%20SV%20TW_main.jpg</v>
-      </c>
-      <c r="K272" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L272" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M272" t="str">
-        <v>高端限量泛用</v>
-      </c>
-      <c r="N272" t="str">
-        <v>採用｢HYPERDRIVE DESIGN｣,以長時間維持初期性能為目標所設計的次世代BAITREEL隆重登場｡搭配HYPERDRIVE DIGIGEAR,達成強度提升,迴轉感受更為良好,使用HYPER ARMED HOUSING(Mg)實現了輕盈機殼｡旗艦機種STEEZ SV TW搭配全新技術以限定型號登場｡ 配備φ34ｍｍSV BOOST線杯支援拋投精準度,從輕量路亞到重量級路亞都能廣泛對應,新型BOOST機構讓飛行距離與拋投性能更佳優秀｡ ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力 / ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障 / ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統 / 他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性</v>
-      </c>
-      <c r="O272" t="str">
-        <v>¥74,800</v>
-      </c>
-      <c r="P272" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q272" t="str">
-        <v>採用｢HYPERDRIVE DESIGN｣,以長時間維持初期性能為目標所設計的次世代BAITREEL隆重登場｡搭配HYPERDRIVE DIGIGEAR,達成強度提升,迴轉感受更為良好,使用HYPER ARMED HOUSING(Mg)實現了輕盈機殼｡旗艦機種STEEZ SV TW搭配全新技術以限定型號登場｡ 配備φ34ｍｍSV BOOST線杯支援拋投精準度,從輕量路亞到重量級路亞都能廣泛對應,新型BOOST機構讓飛行距離與拋投性能更佳優秀｡ ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■SV CONCEPT 能將磁性煞車應有的實戰優勢發揮最大極限，輕鬆愉快準確拋投，只要微調磁煞旋鈕，不管是4~5克左右的輕裝到重量級路亞都能輕鬆應付。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。 ■UTD 消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。</v>
-      </c>
-      <c r="R272" t="str">
-        <v/>
-      </c>
-      <c r="S272" t="str">
-        <v>鲈鱼限量高端</v>
-      </c>
-      <c r="T272" t="str">
-        <v>高端限量 / 轻量反应 / 收藏实战兼顾</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="str">
-        <v>DRE5021</v>
-      </c>
-      <c r="B273">
-        <v>2</v>
-      </c>
-      <c r="C273" t="str">
-        <v>LIGHT GAME IC</v>
-      </c>
-      <c r="D273" t="str">
-        <v/>
-      </c>
-      <c r="E273" t="str">
-        <v/>
-      </c>
-      <c r="F273" t="str">
-        <v/>
-      </c>
-      <c r="G273" t="str">
-        <v/>
-      </c>
-      <c r="H273" t="str">
-        <v/>
-      </c>
-      <c r="I273" t="str">
-        <v>drum</v>
-      </c>
-      <c r="J273" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/LIGHT%20GAME%20IC_main.jpg</v>
-      </c>
-      <c r="K273" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L273" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M273" t="str">
-        <v>轻船钓计数主力</v>
-      </c>
-      <c r="N273" t="str">
-        <v>兼備平滑捲線和輕盈特點的高剛性IC輕量款 / 有IC計數器的輕量型號，可應對各種輕型釣法 / 期待已久的「HYPERDRIVE DESIGN」系列即將登場 / 這是一款以提高所有基本性能水平為目標，以確保優異的初始性能持久的新世代捲線器</v>
-      </c>
-      <c r="O273" t="str">
-        <v>¥33,000 - ¥36,600</v>
-      </c>
-      <c r="P273" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q273" t="str">
-        <v>兼備平滑捲線和輕盈特點的高剛性IC輕量款。 有IC計數器的輕量型號，可應對各種輕型釣法。期待已久的「HYPERDRIVE DESIGN」系列即將登場。這是一款以提高所有基本性能水平為目標，以確保優異的初始性能持久的新世代捲線器。 DAIWA 技術 ■HYPERDRIVE DIGIGEAR 這是針對BAIT(雙軸)捲線器設計的新齒輪系統，以追求長時間維持強力且滑順為目標。不縮小模數齒輪的模數（大小）的前提下，實現了咬合率與耐久性的提升，讓初期滑順度的長效維持得以實現，這是DAIWA獨有的技術。 ■HYPER ARMED HOUSING（AL） 以高剛性、高精度確實支持內部結構，帶來細緻的捲線感和強大的動力的機殼系統。使用金屬材料製作構架是實現這一目標的必要條件，通過兩側側板的完美組合，可以滿足進一步長效維持基本性能的訴求。在本系列中，機身採用了鋁合金，實現了無比堅固的強度。 ■HYPER TOUGH CLUTCH 在千次、萬次的使用中仍能保持開關性能，不僅如此，在高鹽度海水區域中也能大幅度減少故障的離合器系統。它以先進的絕緣結構自豪，與本公司數據相比，在苛刻的海水釣場使用後中的卡鹽維修件數已經減少了99%。 ■ATD 針對魚的拉力平滑作動並持續平穩出線的新一代煞車系統。通過設置能夠抑制大型魚類抗爭中捲線器煞車力下降問題的設置，確保在抗爭中也能安心應對大型魚。</v>
-      </c>
-      <c r="R273" t="str">
-        <v/>
-      </c>
-      <c r="S273" t="str">
-        <v>轻船钓计数</v>
-      </c>
-      <c r="T273" t="str">
-        <v>双摇臂船钓 / 小型船钓 / 计数辅助</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="str">
-        <v>DRE5022</v>
-      </c>
-      <c r="B274">
-        <v>2</v>
-      </c>
-      <c r="C274" t="str">
-        <v>TATULA TW 400</v>
-      </c>
-      <c r="D274" t="str">
-        <v/>
-      </c>
-      <c r="E274" t="str">
-        <v/>
-      </c>
-      <c r="F274" t="str">
-        <v/>
-      </c>
-      <c r="G274" t="str">
-        <v/>
-      </c>
-      <c r="H274" t="str">
-        <v>强力,海水,bass</v>
-      </c>
-      <c r="I274" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J274" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20TW%20400_main.jpg</v>
-      </c>
-      <c r="K274" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L274" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M274" t="str">
-        <v>重型大号主力</v>
-      </c>
-      <c r="N274" t="str">
-        <v>大线杯大物取向 / 重装大饵友好 / 远投与强拉力并重</v>
-      </c>
-      <c r="O274" t="str">
-        <v>¥41,000</v>
-      </c>
-      <c r="P274" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q274" t="str">
-        <v/>
-      </c>
-      <c r="R274" t="str">
-        <v/>
-      </c>
-      <c r="S274" t="str">
-        <v>大饵重装泛用</v>
-      </c>
-      <c r="T274" t="str">
-        <v>大线杯 / 大物 / 淡海水重装</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="str">
-        <v>DRE5023</v>
-      </c>
-      <c r="B275">
-        <v>2</v>
-      </c>
-      <c r="C275" t="str">
-        <v>SPARTAN IC</v>
-      </c>
-      <c r="D275" t="str">
-        <v/>
-      </c>
-      <c r="E275" t="str">
-        <v/>
-      </c>
-      <c r="F275" t="str">
-        <v/>
-      </c>
-      <c r="G275" t="str">
-        <v/>
-      </c>
-      <c r="H275" t="str">
-        <v/>
-      </c>
-      <c r="I275" t="str">
-        <v>drum</v>
-      </c>
-      <c r="J275" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SPARTAN%20IC_main.jpg</v>
-      </c>
-      <c r="K275" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L275" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M275" t="str">
-        <v>海水船钓入门</v>
-      </c>
-      <c r="N275" t="str">
-        <v>擁有PE2號-200M的飽滿線容量，兼具力量、輕巧、COMPACT的SPARTAN IC / 可廣泛對應各種LIGHT GAME / ATD(自動拉力調節系統)/超合金框架/LED背光/計時器顯示/可交換電池/105mm長強力手把＋混合式手把握丸/止線機能 日本官網</v>
-      </c>
-      <c r="O275" t="str">
-        <v>¥26,800</v>
-      </c>
-      <c r="P275" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q275" t="str">
-        <v>擁有PE2號-200M的飽滿線容量，兼具力量、輕巧、COMPACT的SPARTAN IC。可廣泛對應各種LIGHT GAME。 ATD(自動拉力調節系統)/超合金框架/LED背光/計時器顯示/可交換電池/105mm長強力手把＋混合式手把握丸/止線機能 日本官網</v>
-      </c>
-      <c r="R275" t="str">
-        <v/>
-      </c>
-      <c r="S275" t="str">
-        <v>船钓计数入门</v>
-      </c>
-      <c r="T275" t="str">
-        <v>计数鼓轮 / 实用取向 / 深水近海</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="str">
-        <v>DRE5024</v>
-      </c>
-      <c r="B276">
-        <v>2</v>
-      </c>
-      <c r="C276" t="str">
-        <v>STEEZ CT SV TW</v>
-      </c>
-      <c r="D276" t="str">
-        <v/>
-      </c>
-      <c r="E276" t="str">
-        <v/>
-      </c>
-      <c r="F276" t="str">
-        <v/>
-      </c>
-      <c r="G276" t="str">
-        <v/>
-      </c>
-      <c r="H276" t="str">
-        <v>精细,bass</v>
-      </c>
-      <c r="I276" t="str">
-        <v>baitcasting</v>
-      </c>
-      <c r="J276" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20CT%20SV%20TW_main.png</v>
-      </c>
-      <c r="K276" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="L276" t="str">
-        <v>2026-04-21T10:52:09.016Z</v>
-      </c>
-      <c r="M276" t="str">
-        <v>精细CT旗舰</v>
-      </c>
-      <c r="N276" t="str">
-        <v>CT(COMPACT&amp;TOUGH)、以全新的概念實現了STEEZ更進一步的進化 / 搭載精巧機身和30mm直徑的G1硬鋁合金製成的CT SV線杯更顯得相得益彰 / 初始速度提升出眾的CT SV線杯其多樣性能自不必多說，就連在微物精釣領域也能駕馭，並且拋投感也淩駕以往 / 從STEEZ SV TW那裡繼承的流暢卷上力是C1硬鋁合金切削製成的完美禮物</v>
-      </c>
-      <c r="O276" t="str">
-        <v>¥63,000</v>
-      </c>
-      <c r="P276" t="str">
-        <v>在售</v>
-      </c>
-      <c r="Q276" t="str">
-        <v>CT(COMPACT&amp;TOUGH)、以全新的概念實現了STEEZ更進一步的進化。搭載精巧機身和30mm直徑的G1硬鋁合金製成的CT SV線杯更顯得相得益彰。初始速度提升出眾的CT SV線杯其多樣性能自不必多說，就連在微物精釣領域也能駕馭，並且拋投感也淩駕以往。從STEEZ SV TW那裡繼承的流暢卷上力是C1硬鋁合金切削製成的完美禮物。另外搭配700型線杯的新型[TWS]出線系統和[SV CONCEPT]之間發揮著相乘效果，實現了驚人的精密性能。新增加的SH捲線器規格型號，應對不同的做釣需求。 日本官網</v>
-      </c>
-      <c r="R276" t="str">
-        <v/>
-      </c>
-      <c r="S276" t="str">
-        <v>鲈鱼精细旗舰</v>
-      </c>
-      <c r="T276" t="str">
         <v>小体积高精度 / CT精细抛投 / 高端精细</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T276"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T262"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -401,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T262"/>
+  <dimension ref="A1:T269"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -476,7 +472,7 @@
         <v>STELLA SW</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>斯泰拉</v>
       </c>
       <c r="E2" t="str">
         <v>2026</v>
@@ -515,7 +511,7 @@
         <v>在售</v>
       </c>
       <c r="Q2" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。※4000HG、4000XG：2026年05月预计上市、18000HG、20000PG、25000PG：2026年04月预计上市、5000HG、5000XG、6000PG、6000HG、6000XG、30000：2026年05月预计上市</v>
+        <v>在国内外有着出色成绩的STELLA SW加入新的技术后实现进化。XX TOUGH DRAG技术提升卸力性能，INFINITYLOOP技术提升抛投精度，INFINITYXROSS提升齿轮强度和耐久性，ANTI-TWIST FIN减少缠线问题，实现了性能的大幅进化。另外握把握丸做了密封设计，卸力旋钮大直径化等细节部分也做了升级。打磨在海水场合和大物一决胜负所需要的性能，得到这款新生的STELLA SW。</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -538,7 +534,7 @@
         <v>STELLA SW</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>斯泰拉</v>
       </c>
       <c r="E3" t="str">
         <v>2020</v>
@@ -577,7 +573,7 @@
         <v>在售</v>
       </c>
       <c r="Q3" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>NEW STELLA SW和大物对抗时的力量、耐久性以及操作性进一步提升。和旧款产品对比搭载了具有更轻和更强大的收线性能的INFINITY DRIVE，以及能对抗大物并有效抑制卸力发热造成缠线部温度上升的HEAT SINK DRAG。同时，新的X PROTECT设计能有效抵抗水压，过线罗拉在严酷环境下也能保护渔轮，搭载的各种技术实现坚韧的全身防护，完成进化的新款STELLA SW在同类产品中体现了强大性能。</v>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -600,7 +596,7 @@
         <v>STELLA</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>斯泰拉</v>
       </c>
       <c r="E4" t="str">
         <v>2022</v>
@@ -701,7 +697,7 @@
         <v>在售</v>
       </c>
       <c r="Q5" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>作为不断挑战海鲈钓法顶点的高端规格，EXSENCE进一步进化后重新登场。启动和停止的反馈力很出色，对于假饵的波动和轻微的水流变化可以感觉很明显的MGL ROTOR，加上实现顺滑转动手感的金属机身设计。不吝惜搭载了INFINITYXROSS、INFINITYDRIVE、INFINITYLOOP技术，实现了收线强度、抛投性能、卸力性能的大幅进化。来吧，去探索更深远的钓鱼吧，在这里寻找钓海鲈所需要的性能吧。</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -763,7 +759,7 @@
         <v>在售</v>
       </c>
       <c r="Q6" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>海水钓渔轮追求的【强度】是十分多样性的，严酷环境下使用需要足够刚性和坚韧性，还需要防海水性能，另外强大收线力量也是很重要的。新款TWIN POWER SW搭载了INFINITY DRIVE、HEAT SINK DRAG等来自STELLA SW的技术，在拥有了超越一般水准的收线力量和耐久性后，带来了压倒性信赖感，无论哪种钓法都能让你全身心投入，享受钓鱼的乐趣。</v>
       </c>
       <c r="R6" t="str">
         <v/>
@@ -825,7 +821,7 @@
         <v>在售</v>
       </c>
       <c r="Q7" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>次世代海鲈专用轮诞生！比旧款轻20g以上，搭载轻量顺滑手感精密齿轮Ⅱ、提升抛投距离的加长线杯、抑制卡顿的静音驱动、值得信赖的防水技术X PROTECT等SHIMANO最新构造。兼顾海鲈钓法的高强度和细腻操作，这款高规格产品请务必感受一下。</v>
       </c>
       <c r="R7" t="str">
         <v/>
@@ -848,7 +844,7 @@
         <v>Vanquish CE</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>万奎士</v>
       </c>
       <c r="E8" t="str">
         <v>2026</v>
@@ -887,7 +883,7 @@
         <v>在售</v>
       </c>
       <c r="Q8" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>作为SHIMANO MGL系列的旗舰产品，适用于技巧型钓法的Vanquish在2026年推出限定的CE规格。和23款Vanquish关注不同的特别领域。正如它的名字COMPETITION EDITION所表示的，它专注于在管理鳟鱼或者鲈鱼比赛中发挥作钓者潜力。它的特色是其出色的感度。它削减了一部分23Vanquish所具备的防水性能，专注降低转动扭矩，彻底打磨实现高感度、高反馈力和收线轻量。直接操作感和信息传达力唤醒快感和感动，有着仿佛可以忽视其存在。从1000到2500一共8个规格。沿袭23款Vanquish的核心技术INFINITYXROSS、INFINITYDRIVE等，追求极致的感度给予比赛型钓友和核心钓友以支持。</v>
       </c>
       <c r="R8" t="str">
         <v/>
@@ -910,7 +906,7 @@
         <v>Vanquish</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>万奎士</v>
       </c>
       <c r="E9" t="str">
         <v>2023</v>
@@ -1011,7 +1007,7 @@
         <v>在售</v>
       </c>
       <c r="Q10" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>HAGANE机身+HAGANE齿轮的组合保证了海水环境作钓的可靠性，无论是面对大型目标时所需要的强大收线力，还是面对小型目标时顺滑的收线手感，都能满足需求。除此之外，X PROTECT+X SHIELD的防水组合让你在严酷的海水环境下能长久使用，高性价比搭配多个规格让你在外出游钓时十分安心。</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -1135,7 +1131,7 @@
         <v>在售</v>
       </c>
       <c r="Q12" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>MGL系列渔轮发挥碳纤维强化树脂CI4+材质的低惯性旋转盘的特性，在技术性钓法中发挥价值。TWINPOWER XD则是其中注重强度的规格。HAGANE BODY技术给以渔轮厚重感，再加上新搭载的INFINITYXROSS，INFINITYDIRVE技术提升齿轮耐久性和收线强度。新材质的卸力垫片DURACORSS有着出色的耐磨损性能，实现顺滑且安心的卸力。另外INFINITYLOOP提升抛投手感，X-PROTECT减少异物入侵罗拉盘，ANTI-TWIST FIN技术减少缠线问题，即使在艰苦环境下也能放心使用。型号上有从淡海水都能使用的C3000型到适合轻型岸投铁板的C5000型共6个型号。</v>
       </c>
       <c r="R12" t="str">
         <v/>
@@ -1197,7 +1193,7 @@
         <v>在售</v>
       </c>
       <c r="Q13" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>EXSENCE CI4+进一步磨练设计，内部功能大幅升级后，就是EXSENCE XR。堪比旗舰规格的性能，在情报量稀少的夜钓中，想必能成为钓手值得信赖的武器吧。这款渔轮带给不断探究海鲈世界的钓手，向着更高高度进发。</v>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -1220,7 +1216,7 @@
         <v>STRADIC SW</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>斯塔迪克</v>
       </c>
       <c r="E14" t="str">
         <v>2022</v>
@@ -1259,7 +1255,7 @@
         <v>在售</v>
       </c>
       <c r="Q14" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>搭载INFINITY DRIVE后，轻量转动即可实现强大收线力，保持主导权的同时尽情搏鱼。另外罗拉部采用的X-PROTECT技术有效防止水的入侵并提升了耐久性，让喜爱出海的钓友有了这款强大且坚韧的产品。</v>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -1321,7 +1317,7 @@
         <v>在售</v>
       </c>
       <c r="Q15" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>激烈作钓的情况下对会变得十分依赖渔轮性能，而且根据不同的钓种又有着不一样的需求。NEW Sephia XR具备细腻操控木虾饵的操作性，快速收线的反馈性能，C3000规格的卸力顺滑性也能让你和大型目标搏斗。另外，INFINITYDRIVE有着强有力的收线性能，INFINITYXROSS也提升了齿轮耐久性，而鲨鱼鳍也减少了线在过线环的问题，产品阵容还追加了适合轻木虾的小型C2000S。</v>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -1344,7 +1340,7 @@
         <v>STRADIC SW</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>斯塔迪克</v>
       </c>
       <c r="E16" t="str">
         <v>2024</v>
@@ -1383,7 +1379,7 @@
         <v>在售</v>
       </c>
       <c r="Q16" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>沿袭上位产品的力量和坚韧，出色的防水性能使其可以在严苛的海水环境作钓。作为实践派渔轮在合适的地方提升了性能。4000型对应轻型钓法，以广受好评的23STRADIC为基础，搭载了INFINITYXROSS、INFINITYDRIVE、ANTI TWIST FIN等技术提升齿轮耐久性并减少缠线问题，追求使用舒适感。5000型~10000型搭载了X TOUGH DRAG，大幅提升了卸力的耐久性、散热性、最大卸力值等，可以应对重型假饵以及和大型目标搏鱼的需求。高性价比的9个型号皆在满足钓友实战中的需求。</v>
       </c>
       <c r="R16" t="str">
         <v/>
@@ -1445,7 +1441,7 @@
         <v>在售</v>
       </c>
       <c r="Q17" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>磨砺4年的沉淀，SHIMANO中等价位段的核心系列SUSTAIN焕新登场。专为近岸海钓和淡水作钓环境所设计，融合了SHIMANO的先进技术，显著提升渔轮的操控性、强度和精准度。作为轻量化（MAGNUMLITE）系列的一员，新款SUSTAIN 搭载了灵敏反应的 MGL 旋转盘，有助于实现精准的拟饵操控。同时，新款也搭载了其他由STELLA下放的旗舰技术，包括：无限驱动技术（INFINITYDRIVE），有效减少齿轮件传动的阻力，实现流畅收线；无限交叉技术（INFINITYXROSS），提高齿轮咬合面的契合度，带来持久的使用强度；致密排线技术（INFINITYLOOP）和防缠线鳍（ANTI-TWIST FIN），优化了线杯的排线效果与控制力，减少缠线并提升抛投性能；最后再配合稳定的新型卸力材料技术（DURACROSS），打造完成这款兼具轻量和坚韧的SUSTAIN，时刻准备以卓越性能迎接每一次抛投。</v>
       </c>
       <c r="R17" t="str">
         <v/>
@@ -1507,7 +1503,7 @@
         <v>在售</v>
       </c>
       <c r="Q18" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>木虾钓法对渔轮会有如何要求呢？反复操控渔轮抽竿的耐久性、持续抽竿所需的轻量性，收线时所需的静肃性，Sephia XR追求着这些要素。我们采用碳纤维强化素材CI4+成型了高强度机身，另外海采用了第二代精密齿轮提升了耐久性和抑制卡顿的静音驱动，另外海搭载加长线杯进一步提升了远投性能，RAGID SUPPORT DRAG也让钓友面对乌贼喷墨时能够柔软对应，请务必体感一下这款专用轮。</v>
       </c>
       <c r="R18" t="str">
         <v/>
@@ -1530,7 +1526,7 @@
         <v>Soare XR</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>索阿雷</v>
       </c>
       <c r="E19" t="str">
         <v>2025</v>
@@ -1569,7 +1565,7 @@
         <v>在售</v>
       </c>
       <c r="Q19" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>Soare XR通过MGL旋转盘来获得轻快的操作性和高感度，就算细小的咬讯也易感知并顺滑收线。在搭载INFINITYDRIVE维持强有力的转动性能，还采用扭力强的长握把，齿轮搭载INFINITYXROSS也提升了耐久性，还采用了HIGH RESPONSE DRAG让卸力顺滑作用并放出细线，顺着鱼的游动情形出线也能减少细线切线的风险。鲨鱼鳍也能减少渔线从过线环掉下，135g的自重的超精细规格500SPG到强力精细的C2500SHG，总计4种规格。Soare XR适合轻饵作钓，也能帮助钓手更好地掌握钓况。</v>
       </c>
       <c r="R19" t="str">
         <v/>
@@ -1592,7 +1588,7 @@
         <v>CARDIFF XR</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>卡迪夫</v>
       </c>
       <c r="E20" t="str">
         <v>2023</v>
@@ -1631,7 +1627,7 @@
         <v>在售</v>
       </c>
       <c r="Q20" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>新搭载第二代精密齿轮、静音驱动、加长线杯和X PROTECT等技术，大幅提升了产品性能。另外，通过重新设计后大幅减少了重量，更易感知细微的咬讯，使用轻量假饵也容易抛得远，请享受溪流钓法设计所带来的乐趣。</v>
       </c>
       <c r="R20" t="str">
         <v/>
@@ -1693,7 +1689,7 @@
         <v>在售</v>
       </c>
       <c r="Q21" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>对于淡水路亚需要的性能进行升级。采用降低驱动部件摩擦阻力实现强力收线的INFINITYDRIVE技术，提升驱动齿轮耐久性的INFINITYXROSS技术，以及减少过线环部位缠线问题的ANTI-TWIST FIN技术。用很小的力量就能转动渔轮，并且可以快速停止转动，收线轻快感和感度也不作妥协。为每个规格选择合适的卸力，注重细节设计的淡水路亚渔轮。</v>
       </c>
       <c r="R21" t="str">
         <v/>
@@ -1716,7 +1712,7 @@
         <v>Soare XR</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>索阿雷</v>
       </c>
       <c r="E22" t="str">
         <v>2021</v>
@@ -1755,7 +1751,7 @@
         <v>在售</v>
       </c>
       <c r="Q22" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>Soare经典规格XR登场，搭载第二代精密齿轮和静音驱动让你转动手把收线时手感更好，顺滑的收线手感让你能更好集中精神判断咬讯。采用加长线杯后提升了抛投距离，搭配新的HIGH RESPONSE DRAG能够快速调整卸力，让你更快应对特殊情况，这次还追加了500PGS规格，让你可以使用小饵攻略。</v>
       </c>
       <c r="R22" t="str">
         <v/>
@@ -1817,7 +1813,7 @@
         <v>在售</v>
       </c>
       <c r="Q23" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>浓缩木虾钓所需性能的NEW Sephia SS。 容线量PE0.8号~150m的浅线杯、操作时易握的EVA握丸、RAPID FIRE DRAG等，搭载标准木虾钓渔轮所需的性能。 以Sephia代表性的红色为基础，采用更华丽的设计，和Sephia鱼竿组合，有着更鲜明的存在感。</v>
       </c>
       <c r="R23" t="str">
         <v/>
@@ -1840,7 +1836,7 @@
         <v>VANFORD</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>万福德</v>
       </c>
       <c r="E24" t="str">
         <v>2024</v>
@@ -1941,7 +1937,7 @@
         <v>在售</v>
       </c>
       <c r="Q25" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>搭载了相当于IPX-8级别防水性能的X SHIELD和X PROTECT、以及X-SHIP、HAGANE机身等高端机种才有的技术，让SPHEROWS SW能够对应严酷的海水环境。21新款追加了HAGANE齿轮和碳纤维十字纹垫片，进一步提升了产品耐久性和性价比。</v>
       </c>
       <c r="R25" t="str">
         <v/>
@@ -1964,7 +1960,7 @@
         <v>STRADIC</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>斯塔迪克</v>
       </c>
       <c r="E26" t="str">
         <v>2023</v>
@@ -2065,7 +2061,7 @@
         <v>在售</v>
       </c>
       <c r="Q27" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>具备例如浅线杯、RAPID FIRE DRAG、EVA握丸、双手把型号等特性，非常适合木虾钓法。MICROMODULE GEAR Ⅱ，SILENTDRIVE，X PROTECT，加长线杯等技术充实其性能，大幅提升收线手感、防水性能、抛投距离等性能。另外，采用CI4+机身相比前作实现了大幅轻量化。契合Sephia之名且性能优秀的高性价比渔轮诞生。</v>
       </c>
       <c r="R27" t="str">
         <v/>
@@ -2127,7 +2123,7 @@
         <v>在售</v>
       </c>
       <c r="Q28" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>作为海鲈专用规格，EXSENCE系列一直回应着钓友们的高要求。保有BB系列规格惯有的特性，搭载第二代MICROMODULE齿轮和SILENT DRIVE技术，在你夜钓时可以更好地感知水中的情报。另外，机身采用CI4+素材比旧款轻量了15g（20EXSENCE BB 4000MXG对比），搭配加长线杯让你拥有更好的抛投性能。并且，RAPID FIRE DRAG让你在结构位置攻略海鲈时可以快速调整卸力，作为海鲈专用渔轮具备了高规格。</v>
       </c>
       <c r="R28" t="str">
         <v/>
@@ -2189,7 +2185,7 @@
         <v>在售</v>
       </c>
       <c r="Q29" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>HAGANE齿轮加上CI4+材质机身，强度和轻量性同时提升了一个档次后全新登场。除此以外，搭载SILENTDRIVE和X-SHIP后，抛投手感和力传达效率也更优秀，4000型仅250g的重量，让你长在时间抛投时也不易感受到疲劳感，整个系列都比旧款大幅减重，让你更舒适作钓。请务必体验一下全新升级后的产品带给你的乐趣吧。</v>
       </c>
       <c r="R29" t="str">
         <v/>
@@ -2212,7 +2208,7 @@
         <v>ULTEGRA</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>尤特加</v>
       </c>
       <c r="E30" t="str">
         <v>2025</v>
@@ -2251,7 +2247,7 @@
         <v>在售</v>
       </c>
       <c r="Q30" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>ULTEGRA有着优秀的转动性能和耐久性，深受许多钓友的喜爱。追求更加顺滑稳定的CORESOLID系列设计，在以一定速度持续收线或者栓饵等阻大的钓法中发挥其真正价值。通过增加INFINITYXROSS、INFINITYDRIVE、ANTI-TWIST FIN等技术，进一步提高了基本性能，初学者自不必说，经验老道的钓友也会喜欢它的性能。产品阵容包括新登场的C2500SHG在内共11个型号。</v>
       </c>
       <c r="R30" t="str">
         <v/>
@@ -2274,7 +2270,7 @@
         <v>Soare BB</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>索阿雷</v>
       </c>
       <c r="E31" t="str">
         <v>2022</v>
@@ -2313,7 +2309,7 @@
         <v>在售</v>
       </c>
       <c r="Q31" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>专门为轻型钓法设计的型号。发挥细线强度的HI-RESPONSE DRAG搭配浅线杯。C2000的型号通过采用CI4+实现了大幅度的轻量化。充实的性能使您的轻型钓再上一层楼。</v>
       </c>
       <c r="R31" t="str">
         <v/>
@@ -2375,7 +2371,7 @@
         <v>在售</v>
       </c>
       <c r="Q32" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>除了HAGANE相关技术外，搭载SILENTDRIVE和G FREE BODY，让岸投攻略变得更有效率。</v>
       </c>
       <c r="R32" t="str">
         <v/>
@@ -2437,7 +2433,7 @@
         <v>在售</v>
       </c>
       <c r="Q33" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>SPHEROS SW推出了精巧化规格，拥有不输给大物的强度和坚韧性，核心部位采用冷锻制造的HAGANE齿轮、机身采用铝制HAGANE机身，面对大物时提供给钓友足够的齿轮强度和收线力量。另外手把采用不易卡顿的样式，卸力垫片也是高耐久性的碳纤维素材，让渔轮保持精巧的同时也能放心对抗大物。</v>
       </c>
       <c r="R33" t="str">
         <v/>
@@ -2499,7 +2495,7 @@
         <v>在售</v>
       </c>
       <c r="Q34" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>以轻量转动，追求自身轻量的MGL系列里，诞生了以全世界为目标的MIRAVEL。机身和大型部位采用CI4+材质，达成了超越其级别的轻量化。另外采用静音驱动和旋入式手把可以抑制收线过程中的噪音和晃动。请尝试一下感受轻量所带来的提升吧。</v>
       </c>
       <c r="R34" t="str">
         <v/>
@@ -2522,7 +2518,7 @@
         <v>NASCI</v>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>纳西</v>
       </c>
       <c r="E35" t="str">
         <v>2026</v>
@@ -2561,7 +2557,7 @@
         <v>在售</v>
       </c>
       <c r="Q35" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>SHIMANO全新的NASCI提供更高端的性能和友好的使用手感，凭借INFINITYDRIVE、一体成型导线环和ANTI-TWIST FIN等技术，提供了更平稳力量，减少渔线在作钓过程中可能出现问题的概率，这款渔轮可用于鲈钓、鳟鱼、海鲈、轻型岸钓铁板等不同的钓法，产品规格从500型到5000型，阵容十分丰富。值得信赖的技术和规格，应该能满足初学者和专业玩家的需求。</v>
       </c>
       <c r="R35" t="str">
         <v/>
@@ -2623,7 +2619,7 @@
         <v>在售</v>
       </c>
       <c r="Q36" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>SHIMANO入门级的海水轮，AR-C线杯让你在抛投时出线更顺，增加抛投的距离。</v>
       </c>
       <c r="R36" t="str">
         <v/>
@@ -2685,7 +2681,7 @@
         <v>在售</v>
       </c>
       <c r="Q37" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>入门级高性价比的BB规格也全新升级，HAGANE齿轮保证了强度和更好的力传输效率，无论是抛投和搏鱼都能帮助你不少，AR-C线杯的整流出线效果也能更好出线，尽情抛投出去攻略海边巨物吧。</v>
       </c>
       <c r="R37" t="str">
         <v/>
@@ -2747,7 +2743,7 @@
         <v>在售</v>
       </c>
       <c r="Q38" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>AR-C线杯抑制了远投时的缠线问题。并且通过采用SILENTDRIVE和旋钮式手把大幅减轻收线时产生的杂音，提升了收线手感。尤其在用假饵作钓的时候，收线的感度是十分重要的，顺滑的收线性能可以提高使用者对咬讯或者鱼的细微动作的捕捉能力，提高中鱼效率。本次提供了从500至C5000全型号尺寸的商品，以适用于不同的场景和需求。C5000XG型号上采用圆形握把让钓手从各方向都可以轻松握住。</v>
       </c>
       <c r="R38" t="str">
         <v/>
@@ -2809,7 +2805,7 @@
         <v>在售</v>
       </c>
       <c r="Q39" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>入门级钓友的好搭档。</v>
       </c>
       <c r="R39" t="str">
         <v/>
@@ -2871,7 +2867,7 @@
         <v>在售</v>
       </c>
       <c r="Q40" t="str">
-        <v>2023年8月预计上市。※500、1000、C2000S、C2000SHG：2023年9月预计上市。※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>具备切实的实钓性能以及合理的价格，获得广大钓手支持的SEDONA系列也终于迎来了全新升级。搭载了在旗舰级产品上，核心进化技术之一的SILENTDRIVE，渔轮内部部件间细微的卡顿、间隙、晃动等问题大幅减少，伴随着顺滑的转动性能和静肃性，让渔轮焕然一新。在路亚作钓时，细腻的收线手感是十分重要的一个因素，让你能更易攻略目标。从轻型的500规格到攻略大物的C5000规格，从初学者到老玩家之间都获得肯定，献给您这款性能优秀且规格丰富的产品。</v>
       </c>
       <c r="R40" t="str">
         <v/>
@@ -2933,7 +2929,7 @@
         <v>在售</v>
       </c>
       <c r="Q41" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>附带渔线！ 高性价比入门款！</v>
       </c>
       <c r="R41" t="str">
         <v/>
@@ -2995,7 +2991,7 @@
         <v>在售</v>
       </c>
       <c r="Q42" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>搭载抑制缠线问题的AR-C线杯，追求无论是海水还是淡水都能适用的泛用性。采用了这个级别产品从未有过的涂装，加上了演绎高级感的镀金部件。线杯打孔提升时尚感的同时提高轻快感。</v>
       </c>
       <c r="R42" t="str">
         <v/>
@@ -3057,7 +3053,7 @@
         <v>在售</v>
       </c>
       <c r="Q43" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。※1000、C2000S、C2000SHG：2026年06月预计上市其余型号：2026年05月预计上市</v>
+        <v>适合入门玩家使用的路亚钓型号，顺畅的旋转，帮助你更容易感知鱼讯，高刚性结构，支持强力收线；减少故障的设计，让一系列操作更加舒适。全新NEXAVE搭载先进技术，减少卡顿松动的SILTENTDRIVE、减少缠线的ANTI-TWIST FIN，让您享受更愉快的钓鱼体验。产品阵容从1000型到C5000型，目标鱼种从淡水的鲈鱼、鳟鱼，到海水的海鲈、轻海水和沙滩钓等目标鱼。以更亲民的价格实现让人安心的SHIMANO品质。</v>
       </c>
       <c r="R43" t="str">
         <v/>
@@ -3119,7 +3115,7 @@
         <v>在售</v>
       </c>
       <c r="Q44" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>就算初学者也能安心使用的入门规格，搭载AR-C线杯后出线更顺畅、实现不易缠线的高远投性能，在海水环境下也能使用。低价位的黑色基调搭配亮色系设计，实现了SHIMANO高性价比品质。</v>
       </c>
       <c r="R44" t="str">
         <v/>
@@ -3181,7 +3177,7 @@
         <v>在售</v>
       </c>
       <c r="Q45" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>搭载AR-C线杯，有效提升了抛投性能，从1000至4000的丰富规格让你根据需求和钓况可以选择需要的型号，这是无论新手玩家还是经常出行钓游的发烧友都不容错过一个产品。</v>
       </c>
       <c r="R45" t="str">
         <v/>
@@ -3243,7 +3239,7 @@
         <v>在售</v>
       </c>
       <c r="Q46" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>SIENNA目标是带给所有钓友舒适愉快作钓的一款渔轮，通过三次元解析设计的齿轮实现了顺滑且无卡顿的收线手感。另外，搭载AR-C线杯在抛投时可以减少缠线问题。</v>
       </c>
       <c r="R46" t="str">
         <v/>
@@ -3305,7 +3301,7 @@
         <v>在售</v>
       </c>
       <c r="Q47" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>FX目标是带给所有钓友舒适愉快作钓的一款渔轮，通过三次元解析设计的齿轮实现了顺滑且无卡顿的收线手感。另外，搭载AR-C线杯在抛投时可以减少缠线问题。</v>
       </c>
       <c r="R47" t="str">
         <v/>
@@ -3830,7 +3826,7 @@
         <v>2022</v>
       </c>
       <c r="F56" t="str">
-        <v>22 Exsence DC</v>
+        <v>22 EXSENCE DC</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3886,13 +3882,13 @@
         <v>ANTARES DC</v>
       </c>
       <c r="D57" t="str">
-        <v/>
+        <v>安塔列斯</v>
       </c>
       <c r="E57" t="str">
         <v>2021</v>
       </c>
       <c r="F57" t="str">
-        <v>21 Antares DC</v>
+        <v>21 ANTARES DC</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -4072,7 +4068,7 @@
         <v>CALCUTTA CONQUEST DC</v>
       </c>
       <c r="D60" t="str">
-        <v/>
+        <v>CQ</v>
       </c>
       <c r="E60" t="str">
         <v>2019</v>
@@ -4382,13 +4378,13 @@
         <v>ANTARES</v>
       </c>
       <c r="D65" t="str">
-        <v/>
-      </c>
-      <c r="E65" t="str">
-        <v/>
+        <v>安塔列斯</v>
+      </c>
+      <c r="E65">
+        <v>2025</v>
       </c>
       <c r="F65" t="str">
-        <v/>
+        <v>安塔列斯</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4506,7 +4502,7 @@
         <v>CALCUTTA CONQUEST MD</v>
       </c>
       <c r="D67" t="str">
-        <v/>
+        <v>CQ</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -4568,7 +4564,7 @@
         <v>CALCUTTA CONQUEST BFS LIMITED</v>
       </c>
       <c r="D68" t="str">
-        <v/>
+        <v>CQ</v>
       </c>
       <c r="E68" t="str">
         <v>2026</v>
@@ -4630,7 +4626,7 @@
         <v>Metanium DC</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>蒙塔尼</v>
       </c>
       <c r="E69" t="str">
         <v>2024</v>
@@ -4692,7 +4688,7 @@
         <v>CALCUTTA CONQUEST</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>CQ</v>
       </c>
       <c r="E70" t="str">
         <v>2021</v>
@@ -4816,13 +4812,13 @@
         <v>CALCUTTA CONQUEST SHALLOW EDITION</v>
       </c>
       <c r="D72" t="str">
-        <v/>
-      </c>
-      <c r="E72" t="str">
-        <v/>
+        <v>CQ</v>
+      </c>
+      <c r="E72">
+        <v>2024</v>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>24 CQ SHALLOW EDITION</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4878,13 +4874,13 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="D73" t="str">
-        <v/>
+        <v>CQ</v>
       </c>
       <c r="E73" t="str">
         <v>2023</v>
       </c>
       <c r="F73" t="str">
-        <v>23 Calcutta Conquest BFS</v>
+        <v>23 CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -5002,7 +4998,7 @@
         <v>ALDEBARAN DC</v>
       </c>
       <c r="D75" t="str">
-        <v/>
+        <v>阿德</v>
       </c>
       <c r="E75" t="str">
         <v>2025</v>
@@ -5250,7 +5246,7 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="D79" t="str">
-        <v>阿德巴兰 BFS</v>
+        <v>阿德</v>
       </c>
       <c r="E79" t="str">
         <v>2022</v>
@@ -5312,7 +5308,7 @@
         <v>ALDEBARAN MGL</v>
       </c>
       <c r="D80" t="str">
-        <v>阿德巴兰 MGL</v>
+        <v>阿德</v>
       </c>
       <c r="E80" t="str">
         <v>2018</v>
@@ -5374,7 +5370,7 @@
         <v>Metanium SHALLOW EDITION</v>
       </c>
       <c r="D81" t="str">
-        <v/>
+        <v>蒙塔尼</v>
       </c>
       <c r="E81" t="str">
         <v>2022</v>
@@ -5436,7 +5432,7 @@
         <v>Metanium</v>
       </c>
       <c r="D82" t="str">
-        <v/>
+        <v>蒙塔尼</v>
       </c>
       <c r="E82" t="str">
         <v>2020</v>
@@ -5994,7 +5990,7 @@
         <v>Scorpion DC MD</v>
       </c>
       <c r="D91" t="str">
-        <v/>
+        <v>红蝎</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -6118,7 +6114,7 @@
         <v>Scorpion DC</v>
       </c>
       <c r="D93" t="str">
-        <v/>
+        <v>红蝎</v>
       </c>
       <c r="E93" t="str">
         <v>2021</v>
@@ -6180,13 +6176,13 @@
         <v>Scorpion MD 300</v>
       </c>
       <c r="D94" t="str">
-        <v/>
+        <v>红蝎</v>
       </c>
       <c r="E94" t="str">
         <v>2025</v>
       </c>
       <c r="F94" t="str">
-        <v>25 Scorpion MD 300</v>
+        <v>25 红蝎 MD 300</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -6366,7 +6362,7 @@
         <v>Stephano SS</v>
       </c>
       <c r="D97" t="str">
-        <v/>
+        <v>红蝎</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -6490,7 +6486,7 @@
         <v>Scorpion MD 200</v>
       </c>
       <c r="D99" t="str">
-        <v/>
+        <v>红蝎</v>
       </c>
       <c r="E99" t="str">
         <v>2024</v>
@@ -6924,7 +6920,7 @@
         <v>CURADO 150</v>
       </c>
       <c r="D106" t="str">
-        <v/>
+        <v>库拉多</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -6986,7 +6982,7 @@
         <v>CURADO BFS</v>
       </c>
       <c r="D107" t="str">
-        <v/>
+        <v>库拉多</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -7872,7 +7868,7 @@
         <v>spinning</v>
       </c>
       <c r="J121" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2020X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_GAUS_20X-2.jpg</v>
       </c>
       <c r="K121" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
@@ -7934,7 +7930,7 @@
         <v>spinning</v>
       </c>
       <c r="J122" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2030X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_GAUS_30X-1.jpg</v>
       </c>
       <c r="K122" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
@@ -7993,10 +7989,10 @@
         <v>泛用,bass</v>
       </c>
       <c r="I123" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="J123" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LIN258HM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LIN258HM.jpg</v>
       </c>
       <c r="K123" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
@@ -8055,10 +8051,10 @@
         <v>精细,泛用,bass</v>
       </c>
       <c r="I124" t="str">
-        <v>baitcasting</v>
+        <v>spinning</v>
       </c>
       <c r="J124" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RC-IDATEN%20256_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_megabass_idaten-x_256.jpg</v>
       </c>
       <c r="K124" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
@@ -8120,7 +8116,7 @@
         <v>drum</v>
       </c>
       <c r="J125" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
       </c>
       <c r="K125" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
@@ -8182,7 +8178,7 @@
         <v>drum</v>
       </c>
       <c r="J126" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20ITO-GAMBLER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
       </c>
       <c r="K126" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
@@ -8244,7 +8240,7 @@
         <v>drum</v>
       </c>
       <c r="J127" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE.jpg</v>
       </c>
       <c r="K127" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
@@ -8306,7 +8302,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J128" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2073_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_megabass_rhodium_73.jpg</v>
       </c>
       <c r="K128" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
@@ -8368,7 +8364,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J129" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2081_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_RHODIUM_81.jpg</v>
       </c>
       <c r="K129" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
@@ -8430,7 +8426,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J130" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2063_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_RHODIUM_63.jpg</v>
       </c>
       <c r="K130" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
@@ -8492,7 +8488,7 @@
         <v>drum</v>
       </c>
       <c r="J131" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20R100_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_R100-1.jpg</v>
       </c>
       <c r="K131" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
@@ -8554,7 +8550,7 @@
         <v>drum</v>
       </c>
       <c r="J132" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_P200_black-chrome.jpg</v>
       </c>
       <c r="K132" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
@@ -8616,7 +8612,7 @@
         <v>drum</v>
       </c>
       <c r="J133" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
       </c>
       <c r="K133" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
@@ -8678,7 +8674,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J134" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA58_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_58.jpg</v>
       </c>
       <c r="K134" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
@@ -8740,7 +8736,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J135" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_72.jpg</v>
       </c>
       <c r="K135" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
@@ -8802,7 +8798,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J136" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72%20LIMITED%20EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
       </c>
       <c r="K136" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
@@ -8864,7 +8860,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J137" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP79_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_IP79.jpg</v>
       </c>
       <c r="K137" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
@@ -8926,7 +8922,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J138" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP68_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_IP68.jpg</v>
       </c>
       <c r="K138" t="str">
         <v>2026-04-09T16:03:11.194Z</v>
@@ -9156,13 +9152,13 @@
         <v>CURADO DC（200线杯）</v>
       </c>
       <c r="D142" t="str">
-        <v/>
+        <v>库拉多</v>
       </c>
       <c r="E142" t="str">
         <v>2022</v>
       </c>
       <c r="F142" t="str">
-        <v>22 CURADO DC 200</v>
+        <v>22 库拉多 DC 200</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -9218,7 +9214,7 @@
         <v>CURADO DC（150线杯）</v>
       </c>
       <c r="D143" t="str">
-        <v/>
+        <v>库拉多</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -9404,7 +9400,7 @@
         <v>CURADO MGL（70线杯）</v>
       </c>
       <c r="D146" t="str">
-        <v/>
+        <v>库拉多</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -9466,7 +9462,7 @@
         <v>CURADO MGL（150线杯）</v>
       </c>
       <c r="D147" t="str">
-        <v/>
+        <v>库拉多</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -12938,7 +12934,7 @@
         <v>CURADO（200线杯）</v>
       </c>
       <c r="D203" t="str">
-        <v/>
+        <v>库拉多</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -13576,7 +13572,7 @@
         <v>spinning</v>
       </c>
       <c r="J213" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/Airity%20ST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/AIRITY%ST_main.jpg</v>
       </c>
       <c r="K213" t="str">
         <v>2026-04-05T14:37:40.618600Z</v>
@@ -15882,16 +15878,16 @@
         <v>入门进阶主力</v>
       </c>
       <c r="N250" t="str">
-        <v>「TATULA系列慶祝10周年 / 」 迎接下一個10年的第三代TATULA登場 / 全新的TATULA首次搭載了「HYPERDRIVE DESIGN」於TATULA TW 100系列 / 進一步提升TATULA系列的核心概念和基本性能，基本性能大幅提升</v>
+        <v>「TATULA品牌10週年！」 展望下個十年的第三代TATULA登場！</v>
       </c>
       <c r="O250" t="str">
-        <v>¥23,300</v>
+        <v>¥24,000</v>
       </c>
       <c r="P250" t="str">
         <v>在售</v>
       </c>
       <c r="Q250" t="str">
-        <v>「TATULA系列慶祝10周年！」 迎接下一個10年的第三代TATULA登場！ 全新的TATULA首次搭載了「HYPERDRIVE DESIGN」於TATULA TW 100系列！ 進一步提升TATULA系列的核心概念和基本性能，基本性能大幅提升！ 將全球化的「HYPERDRIVE DESIGN」引入並注重的模式！ DAIWA 技術 ■HYPERDRIVE DESIGN 強力、滑順回準的永續，雙軸捲線器所需性能的集大成。從驅動齒輪到小齒輪，不間斷的傳導動能的動力裝置。從外側確實的持續支持驅動不，實現穩定且安靜驅動力的機殼。在任何環境下都能座動的多性能結構。實現高效率且遠遠超越寄往捲線力量及滑順迴轉性能的雙軸捲線器設計概念。以經驗為武器的DAIWA，創造初次世代的標準。 ■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的雙軸捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 ■HYPER ARMED HOUSING 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長嘯基本維持基本性能的訴求。 ■HYPER TOUGH CLUTCH 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也能最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場使用後的卡鹽維修件數，達到了減少99%的實績，以最先進的絕緣結構自豪。 ■TWS（T-WING SYSTEM） TWS是一種DAIWA獨創設計，可以大幅減少釣線通過導線規時的阻力，使得線杯迴轉時的阻力減少到最低。這不僅提高了拋投距離和控制性，提升出線速度的同時減少了纏線炒米粉的機率。 ■UTD 在煞車開始作動的同時，消除初期的不順、不穩定力量並實現煞車滑順度的同時，兼具最大煞車力的DAIWA煞車系統，越是鎖緊越能發揮效力。 具備使用細子線所需求的滑順度，耐用度相當優越。碰到突如其來的咬訊或青物暴衝時也能安心應對。 ■ZERO ADJUSTER 首先，通過調整“ZERO ADJUSTER”並執行“零間隙”設定，通過磁煞的進步，可以僅通過磁煞調節來控制所有路亞。 “ZERO ADJUSTER”可在開始釣魚之前進行“零設定”，以確保在釣魚過程中不會發生失誤或故障，讓您享受輕鬆的釣魚。 ※“零間隙”設定指的是在保留微小間隙（約0.2mm）的情況下，將捲線器設置在不會發生滑動的模式。 產品詳情 ■煞車特性 搭載MAGFORCE-Z磁性剎車系統。保持著磁力結構的MAGFORCE不變，通過根據線杯轉速平滑啟動感應，使得前半段煞車強度增強，後半段減弱，從而獲得有彈性的投擲感受。易於調整煞車力度，且具有對外部環境的強韌性等特點，是一種性能卓越的煞車系統。 ■線杯特性 採用直徑34mm（寬度24mm）的超級鋁合金製線杯。延續20TATULA SV TW的超級鋁合金製線杯，提高了線杯響應速度，提高了投擲穩定性，實現了從5克到110克（約4盎司）範圍內，包括大型魚餌在內的穩定遠投性能。 ■ 搭載TWS 大幅擴大了無阻力範圍。因此，飛行距離增加，控制性提高，形態加快，倒噴現象減少。TWS提升了餌輪的所有基本性能。 ■ 搭載TWS 大幅擴大了無阻力範圍。因此，飛行距離增加，控制性提高，形態加快，倒噴現象減少。TWS提升了餌輪的所有基本性能。</v>
+        <v>「TATULA品牌10週年！」 展望下個十年的第三代TATULA登場！</v>
       </c>
       <c r="R250" t="str">
         <v/>
@@ -15973,7 +15969,7 @@
         <v>2</v>
       </c>
       <c r="C252" t="str">
-        <v>PR100 H</v>
+        <v>PR100</v>
       </c>
       <c r="D252" t="str">
         <v/>
@@ -15994,7 +15990,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J252" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/PR100%20H_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/PR100_main.jpg</v>
       </c>
       <c r="K252" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16006,16 +16002,16 @@
         <v>基础入门</v>
       </c>
       <c r="N252" t="str">
-        <v>DAIWA 2022年『 PR100H 』系列小烏龜路亞捲線器 超人氣入門平價款的捲線器，搭配迷彩設計，新手入門首選 / ● PR100H MA-綠迷彩 ● PR100H MN-灰迷彩 ● PR100H MM-黃迷彩 ※ H-右手捲 HL-左手捲</v>
+        <v>基本性能與可靠性皆確實達標的高性價比魚餌。</v>
       </c>
       <c r="O252" t="str">
-        <v>¥6,700</v>
+        <v>¥6,900 - ¥7,700</v>
       </c>
       <c r="P252" t="str">
         <v>在售</v>
       </c>
       <c r="Q252" t="str">
-        <v>DAIWA 2022年『 PR100H 』系列小烏龜路亞捲線器 超人氣入門平價款的捲線器，搭配迷彩設計，新手入門首選。 ● PR100H MA-綠迷彩 ● PR100H MN-灰迷彩 ● PR100H MM-黃迷彩 ※ H-右手捲 HL-左手捲</v>
+        <v>基本性能與可靠性皆確實達標的高性價比魚餌。</v>
       </c>
       <c r="R252" t="str">
         <v/>
@@ -16035,7 +16031,7 @@
         <v>2</v>
       </c>
       <c r="C253" t="str">
-        <v>STEEZ AII TW</v>
+        <v>STEEZ A II TW</v>
       </c>
       <c r="D253" t="str">
         <v/>
@@ -16044,7 +16040,7 @@
         <v>2022</v>
       </c>
       <c r="F253" t="str">
-        <v>22 STEEZ AII TW</v>
+        <v>22 STEEZ A II TW</v>
       </c>
       <c r="G253" t="str">
         <v/>
@@ -16056,7 +16052,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J253" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20AII%20TW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20A%20II%20TW_main.jpg</v>
       </c>
       <c r="K253" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16068,16 +16064,16 @@
         <v>高端重装主力</v>
       </c>
       <c r="N253" t="str">
-        <v>無論遠投或是近距離，都能實現更精確的拋投 / STEEZ A TW一直以來為眾多釣手提供了堅固耐用和穩定性，但第二代經歷了更進一步的淬鍊 / 將美國艱鉅的錦標賽經驗與下一代的Baitcasting Reel 設計理念「HYPERDRIVE DESIGN」相結合 / HYPER ARMED HOUSING（FULL-AL）的堅固性保持不變，而HYPERDRIVE DIGIGEAR則提高了捲動性能，即使在高負載情況下，也能實現平順且高功率的收捲</v>
+        <v>飛躍・捲線・射擊。無論何種情境皆能展現高階性能的旗艦之作 STEEZ A II TW。</v>
       </c>
       <c r="O253" t="str">
-        <v>¥54,000</v>
+        <v>¥56,500</v>
       </c>
       <c r="P253" t="str">
         <v>在售</v>
       </c>
       <c r="Q253" t="str">
-        <v>無論遠投或是近距離，都能實現更精確的拋投。 STEEZ A TW一直以來為眾多釣手提供了堅固耐用和穩定性，但第二代經歷了更進一步的淬鍊。將美國艱鉅的錦標賽經驗與下一代的Baitcasting Reel 設計理念「HYPERDRIVE DESIGN」相結合。 HYPER ARMED HOUSING（FULL-AL）的堅固性保持不變，而HYPERDRIVE DIGIGEAR則提高了捲動性能，即使在高負載情況下，也能實現平順且高功率的收捲。 STEEZ A II TW採用了新開發的φ34mm G1航空鋁超高精度MAG-Z BOOST線杯。通過淺杯化，僅配備所需的線容量，使捲線器總重量更輕量。結果而言，這項設計提高了捲線器的初始啟動性能，成為實用投擲性能的迷人特色之一。 高抓握性的I型握丸和新設計的90mm 航空鋁製手柄實現更加的捲動體驗外，同時STEEZ A II TW還標配了星盤剎車和MAGSEALED滾珠軸承。這不僅僅是黑鱸釣，也能應對海釣的可靠遠投型號--「STEEZ A II TW」。現代釣手所需要的功能濃縮匯集而成的跨時代捲線器。 DAIWA 技術 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統。DAIWA獨家技術，在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下，達成咬合率的提升，讓初期滑順度的長效維持得以實現。 以高剛性、高精確度確實支持內部結構，帶來精緻捲線體驗以及力量的機殼系統。在主要零組件的外殼採用金屬素材為必要條件，和兩側側板完美組合，實現了長效維持基本性能的訴求。。 實現了持久的滑順度、捲線力量的強度、輕量化之驅動支持系統。小齒輪的兩側，以兩顆滾珠軸承高精密度地支持，因此不會減弱從把手傳導來的力量，即使是有負重的時候也能強力、輕盈的進行捲線操控。 除了持續作動數千次、數萬次，緩急分明的開關性能外，在鹽分濃度極高的海水域也最大限度減少惱人狀況的離合器系統。與本公司數據相比，在嚴峻的海水釣場環境使用後的卡鹽維修件數，達到減少99%的實績，以最先進的絕緣構造自豪。 ■TWS TWS（T-Wing System）是一種DAIWA獨創設計，可以大幅減少位於捲線器最上方、靠近機身的導線的阻力，這樣可以減少線圈的旋轉阻力，確保少發生糾結，提供舒適的釣魚體驗。TWS可以實現更遠的投擲距離，提高控制性，同時減少線材打結。TWS可以提升所有Baitcasting Reel的基本性能。 ■MAGSEALED BALL BEARING 由於Baitcasting Reel的結構，海水很難避免地從捲線器和機身之間的縫隙滲入，最容易受到鹽水侵害的是主齒輪部分的軸承。在STEEZ A II TW系列中，為了進一步提高防水性和耐久性，採用了MAGSEALED BALL BEARING在機械旋鈕的一側的主軸齒輪支撐部位。這有助於保持初始性能。 ■MAGSEALED BALL BEARING 由於Baitcasting Reel的結構，海水很難避免地從捲線器和機身之間的縫隙滲入，最容易受到鹽水侵害的是主齒輪部分的軸承。在STEEZ A II TW系列中，為了進一步提高防水性和耐久性，採用了MAGSEALED BALL BEARING在機械旋鈕的一側的主軸齒輪支撐部位。這有助於保持初始性能。 其他技術 &amp; 產品詳情 ■MAG-Z BOOST 『BOOST SYSTEM 將 MAGFORCE-Z 的遠投性能發揮到極致』 MAG-Z BOOST 是將 MAGFORCE-Z 的遠投性能發揮到極致，注重飛距離的設定。MAGFORCE-Z 由於遠心力作用特性，不適合輕餌。然而，對於中重量級的餌，它可是最佳選擇，可以根據輸入的力量伸展飛行距離。 ■G1鋁鎂合金製Φ34mm 線杯 G1鋁鎂合金是一種特殊的鋁合金，展現出比鎂多2倍和超級鋁鎂合金多1.3倍的強度。這種超輕且具有卓越剛性的材料被廣泛應用於航空器結構和精密儀器中。為了實現壓倒性的輕盈感，同時保持相同的強度，捲線器透過薄肉化來保持輕盈所帶來的高速旋轉反應，以及高剛性帶來的精確無比的旋轉，使其無與倫比，難以被其他產品超越。 ■出線音效 出線音效是指在與魚進行搏鬥時，當出線時可以通過聲音區分剎車作用的構造。 出線聲的音質和大小都受到精心設計的關注，清脆、舒適！ ■ZERO SHAFT 線杯僅由BB支撐。因為無軸，所以沒有多餘的阻力。可以達到理想的線杯迴轉。 這也表示是最重視遠投性能的高動力輸出引擎的重要關鍵。 這個曾被稱為Speed Shaft的卷線輪機構於2021年被重新命名為"ZERO SHAFT"。</v>
+        <v>飛躍・捲線・射擊。無論何種情境皆能展現高階性能的旗艦之作 STEEZ A II TW。</v>
       </c>
       <c r="R253" t="str">
         <v/>
@@ -16130,16 +16126,16 @@
         <v>重载主力</v>
       </c>
       <c r="N254" t="str">
-        <v>新一代的HYPERDRIVE DIGIGEAR，使用高強度真鍮作為傳動齒輪，以及在小齒輪中使用高耐蝕銅合金，實現了強大而平滑的旋轉 / 採用HYPER ARMED HOUSING（全鋁）打造堅固的機身，使其在保持小巧的同時確保強大的機身剛性 / 新開發的Φ34mm G1鋁合金超高精度MAG-Z BOOST線輪實現了卓越的長距離投擲性能 / DAIWA 技術 &amp; 產品詳情 ◆MAGFORCE-Z BOOST MAGFORCE-Z BOOST是將MAGFORCE-Z的遠投性能極致發揮的設定</v>
+        <v>以『HYPERDRIVE DESIGN』廣受好評的 ZILLION 系列，現正式推出搭載最新『MAG-Z BOOST』技術的高強度遠投機種！</v>
       </c>
       <c r="O254" t="str">
-        <v>¥54,500</v>
+        <v>¥57,100</v>
       </c>
       <c r="P254" t="str">
         <v>在售</v>
       </c>
       <c r="Q254" t="str">
-        <v>新一代的HYPERDRIVE DIGIGEAR，使用高強度真鍮作為傳動齒輪，以及在小齒輪中使用高耐蝕銅合金，實現了強大而平滑的旋轉。 採用HYPER ARMED HOUSING（全鋁）打造堅固的機身，使其在保持小巧的同時確保強大的機身剛性。 新開發的Φ34mm G1鋁合金超高精度MAG-Z BOOST線輪實現了卓越的長距離投擲性能。 DAIWA 技術 &amp; 產品詳情 ◆MAGFORCE-Z BOOST MAGFORCE-Z BOOST是將MAGFORCE-Z的遠投性能極致發揮的設定。由於MAGFORCE-Z的特性是遠心力驅動感應線杯，因此不適用於輕型路亞。然而，對於中到重型路亞的遠投卻非常理想，可以根據輸入的力量增加飛行距離。 ■TWS（T-Wing System） TWS（T-Wing System）是一項技術，顯著減少了在離開最高轉速的線杯的導線阻力，避免線組糾纏，使釣魚更加舒適。 ■UTD（Ultimate Tournament Drag） UTD（Ultimate Tournament Drag）消除初次起動時的阻力，實現無斷續的出線平順性，並且隨著收緊而具有更大的最大剎車力。 ■G1 鋁製線杯 G1 鋁合金是一種特殊的鋁合金，展現出比鎂多兩倍、超級鋁合金多1.3倍的強度。這種超輕量且優越的剛性材料被廣泛應用於航空器具的結構和精密儀器等領域。在保持相同強度的情況下表現驚人的輕巧感。這種輕巧性帶來的轉動回饋速度和高剛性帶來的精密旋轉是難以被其他產品超越的。 ■ZERO SHAFT 線杯僅由 BB 支撐。因為無軸所以無多餘的阻力，實現理想的線杯回轉。也就是說，這是優先考慮高輸出引擎的遠投性能的關鍵。曾經被稱為 Speed Shaft 的線杯結構於 2021 年被命名為「ZERO SHAFT」。 ■ 零調整器 首先通過調整「零調整器」，實現「線杯無間隙」設定，因為磁煞的進步，可以僅通過磁煞系統控制所有的餌。 「零調整器」允許在開始釣魚之前進行「零設置」，從而在釣魚過程中不會發生誤差動作，讓您輕鬆享受釣魚。 ※「線杯無間隙」設定是指在保留微小間隙（約0.2mm）的情況下，設置線杯到達極限的設置。 ■ 出線聲 出線聲是指在與魚對抗時，當線被拉出時，剎車作動會發出聲音，以便通過聲音辨別剎車作動效果的結構。</v>
+        <v>以『HYPERDRIVE DESIGN』廣受好評的 ZILLION 系列，現正式推出搭載最新『MAG-Z BOOST』技術的高強度遠投機種！</v>
       </c>
       <c r="R254" t="str">
         <v/>
@@ -16254,16 +16250,16 @@
         <v>鲈鱼主力</v>
       </c>
       <c r="N256" t="str">
-        <v>ZILLION SV TW 下一代雙軸捲線器技術HYPERDRIVE設計 ■HYPER DRIVE DIGIGEAR 新型設計的(雙軸)齒輪系統，可實現滑順的旋轉與耐用性，主齒輪（尺寸）不會減少，並且提高咬合率 / DAIWA的獨家技術可以達到上述要求並實現持久的初始光滑度 / ■HYPER DOUBLE SUPPORT 可持續的保持滑順度，通過兩個培林支撐小齒輪的兩端，即使附加重量也不影響捲動的手感 / ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力</v>
+        <v>次世代雙軸魚餌器 採用HYPER DRIVE設計 堅韌多用途魚餌器之真主登場</v>
       </c>
       <c r="O256" t="str">
-        <v>¥45,400</v>
+        <v>¥50,000</v>
       </c>
       <c r="P256" t="str">
         <v>在售</v>
       </c>
       <c r="Q256" t="str">
-        <v>ZILLION SV TW 下一代雙軸捲線器技術HYPERDRIVE設計 ■HYPER DRIVE DIGIGEAR 新型設計的(雙軸)齒輪系統，可實現滑順的旋轉與耐用性，主齒輪（尺寸）不會減少，並且提高咬合率。 DAIWA的獨家技術可以達到上述要求並實現持久的初始光滑度。 ■HYPER DOUBLE SUPPORT 可持續的保持滑順度，通過兩個培林支撐小齒輪的兩端，即使附加重量也不影響捲動的手感。 ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■SV BOOST 線杯 下一代SV概念，實現了令人振奮的高水平拋投性能，並增加了飛行距離。煞車系統的啟動從原本的一階段進化成二階段，在線杯低轉速時(拋輕克數餌)啟動較弱的第一階段煞車，線杯高轉速時(拋重克數餌)啟動較強的第二階段，並在餌飛行的後半段煞車會回到較弱的第一段，從而延伸餌的飛行距離。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■UTD消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。</v>
+        <v>次世代雙軸魚餌器 採用HYPER DRIVE設計 堅韌多用途魚餌器之真主登場</v>
       </c>
       <c r="R256" t="str">
         <v/>
@@ -16283,7 +16279,7 @@
         <v>2</v>
       </c>
       <c r="C257" t="str">
-        <v>ALPHAS SV TW 800H／22 ALPHAS SV TW 800S-XHL</v>
+        <v>ALPHAS SV TW</v>
       </c>
       <c r="D257" t="str">
         <v/>
@@ -16292,7 +16288,7 @@
         <v>2021</v>
       </c>
       <c r="F257" t="str">
-        <v>21 ALPHAS SV TW 800H／22 ALPHAS SV TW 800S-XHL</v>
+        <v>21/22 ALPHAS SV TW</v>
       </c>
       <c r="G257" t="str">
         <v/>
@@ -16304,7 +16300,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J257" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ALPHAS%20SV%20TW%20800H%EF%BC%8F22%20ALPHAS%20SV%20TW%20800S-XHL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/ALPHAS%20SV%20TW_main.jpg</v>
       </c>
       <c r="K257" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16316,16 +16312,16 @@
         <v>轻量泛用</v>
       </c>
       <c r="N257" t="str">
-        <v>■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力 / ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障 / ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統 / 他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性</v>
+        <v>採用 HYPERDRIVE DESIGN 的次世代雙軸小烏龜！搭載Φ32mm SV 線杯，兼具小型輕量與強韌性能的全方位機種。</v>
       </c>
       <c r="O257" t="str">
-        <v>¥33,700</v>
+        <v>¥37,600</v>
       </c>
       <c r="P257" t="str">
         <v>在售</v>
       </c>
       <c r="Q257" t="str">
-        <v>■HYPERDRIVE DIGIGEAR 追求長時間維持強力且滑順的迴轉為目標的BAIT(雙軸)捲線器之新齒輪系統｡DAIWA獨家技術,在不縮小與耐久性息息相關的齒輪齒的模數(大小)的前提下,達成咬合率的提升,讓初期滑順度的長效維持得以實現｡ ■HYPER DOUBLE SUPPORT 實現了持久的滑順度､捲線力量的強度､輕量化之驅動支持系統｡小齒輪的兩側,以兩顆滾珠軸承高精度地支持,因此不會減弱從把手傳導來的力量,即便是有負重的時候也能強力､輕盈地進行捲線操控｡ ■HYPER ARMED HOUSING （AL) 鋁材質製成可牢固的支撐內部結構的外殼，具有高剛性與高精度，必須使用金屬材質材料做為外殼，才能讓捲線器擁有舒適的捲動性和動力。 ■堅固的板機 可以持續操作成千上萬次開/關板機按鈕，即使在海水中板機按鈕也幾乎不會故障。 ■AIR BREAKE SYSTEM 大幅提升精準度，極力避免炸線，使用起來輕鬆無負擔的煞車系統。他的線杯總成是由輕量內轉軸構造愈輕量線杯組合而成，可大幅提升迴轉回饋性。再加上它的設定能與作動切換明確的磁性剎車發揮相乘效果，不僅全力遠投時煞車依舊能確實發揮效用，近拋低迴轉時內轉軸則不會彈出來，發揮延伸彈道狙擊目標功效。 ■SV CONCEPT 能將磁性煞車應有的實戰優勢發揮最大極限，輕鬆愉快準確拋投，只要微調磁煞旋鈕，不管是4~5克左右的輕裝到重量級路亞都能輕鬆應付。 ■TWS(T-WING SYSTEM) 能大幅減低阻力，讓線通過導環時更順暢，減少炸線機率。 ■UTD 消除煞車在剛啟動時容易卡住的情況，具備一般操控所沒有的滑順感，並兼具轉越緊越能發揮效用的最大拉力。</v>
+        <v>採用 HYPERDRIVE DESIGN 的次世代雙軸小烏龜！搭載Φ32mm SV 線杯，兼具小型輕量與強韌性能的全方位機種。</v>
       </c>
       <c r="R257" t="str">
         <v/>
@@ -16469,7 +16465,7 @@
         <v>2</v>
       </c>
       <c r="C260" t="str">
-        <v>TATULA TW 400</v>
+        <v>TATULA TW 300/400</v>
       </c>
       <c r="D260" t="str">
         <v/>
@@ -16490,7 +16486,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J260" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20TW%20400_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20TW%20300_400_main.jpg</v>
       </c>
       <c r="K260" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16502,16 +16498,16 @@
         <v>重型大号主力</v>
       </c>
       <c r="N260" t="str">
-        <v>大线杯大物取向 / 重装大饵友好 / 远投与强拉力并重</v>
+        <v>強韌耐用！期待已久的重型釣線專用TWS搭載機。專為巨型魚餌、巨型擬餌追捕巨物而生。亦適用於海水釣場。</v>
       </c>
       <c r="O260" t="str">
-        <v>¥41,000</v>
+        <v>¥43,500 - ¥45,000</v>
       </c>
       <c r="P260" t="str">
         <v>在售</v>
       </c>
       <c r="Q260" t="str">
-        <v/>
+        <v>強韌耐用！期待已久的重型釣線專用TWS搭載機。專為巨型魚餌、巨型擬餌追捕巨物而生。亦適用於海水釣場。</v>
       </c>
       <c r="R260" t="str">
         <v/>
@@ -16614,7 +16610,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J262" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20CT%20SV%20TW_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20CT%20SV%20TW_main.jpg</v>
       </c>
       <c r="K262" t="str">
         <v>2026-04-21T10:52:09.016Z</v>
@@ -16626,16 +16622,16 @@
         <v>精细CT旗舰</v>
       </c>
       <c r="N262" t="str">
-        <v>CT(COMPACT&amp;TOUGH)、以全新的概念實現了STEEZ更進一步的進化 / 搭載精巧機身和30mm直徑的G1硬鋁合金製成的CT SV線杯更顯得相得益彰 / 初始速度提升出眾的CT SV線杯其多樣性能自不必多說，就連在微物精釣領域也能駕馭，並且拋投感也淩駕以往 / 從STEEZ SV TW那裡繼承的流暢卷上力是C1硬鋁合金切削製成的完美禮物</v>
+        <v>CT（COMPACT＆TOUGH） SV線杯首度搭載的極限機器STEEZ次世代多功能型號，正式登場。</v>
       </c>
       <c r="O262" t="str">
-        <v>¥63,000</v>
+        <v>¥65,000</v>
       </c>
       <c r="P262" t="str">
         <v>在售</v>
       </c>
       <c r="Q262" t="str">
-        <v>CT(COMPACT&amp;TOUGH)、以全新的概念實現了STEEZ更進一步的進化。搭載精巧機身和30mm直徑的G1硬鋁合金製成的CT SV線杯更顯得相得益彰。初始速度提升出眾的CT SV線杯其多樣性能自不必多說，就連在微物精釣領域也能駕馭，並且拋投感也淩駕以往。從STEEZ SV TW那裡繼承的流暢卷上力是C1硬鋁合金切削製成的完美禮物。另外搭配700型線杯的新型[TWS]出線系統和[SV CONCEPT]之間發揮著相乘效果，實現了驚人的精密性能。新增加的SH捲線器規格型號，應對不同的做釣需求。 日本官網</v>
+        <v>CT（COMPACT＆TOUGH） SV線杯首度搭載的極限機器STEEZ次世代多功能型號，正式登場。</v>
       </c>
       <c r="R262" t="str">
         <v/>
@@ -16647,9 +16643,443 @@
         <v>小体积高精度 / CT精细抛投 / 高端精细</v>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>DRE5025</v>
+      </c>
+      <c r="B263">
+        <v>2</v>
+      </c>
+      <c r="C263" t="str">
+        <v>STEEZ AIR TW</v>
+      </c>
+      <c r="D263" t="str">
+        <v/>
+      </c>
+      <c r="E263" t="str">
+        <v>2020</v>
+      </c>
+      <c r="F263" t="str">
+        <v>20 STEEZ AIR TW</v>
+      </c>
+      <c r="G263" t="str">
+        <v/>
+      </c>
+      <c r="H263" t="str">
+        <v>精细,bass</v>
+      </c>
+      <c r="I263" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J263" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/STEEZ%20AIR%20TW_main.jpg</v>
+      </c>
+      <c r="K263" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="L263" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="M263" t="str">
+        <v>高端 BFS 精细旗舰</v>
+      </c>
+      <c r="N263" t="str">
+        <v>次世代魚餌フィネス 搭載極致精細化超小口徑AIR線杯</v>
+      </c>
+      <c r="O263" t="str">
+        <v>¥73,000</v>
+      </c>
+      <c r="P263" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q263" t="str">
+        <v>次世代魚餌フィネス 搭載極致精細化超小口徑AIR線杯</v>
+      </c>
+      <c r="R263" t="str">
+        <v/>
+      </c>
+      <c r="S263" t="str">
+        <v>鲈鱼精细 / BFS 旗舰</v>
+      </c>
+      <c r="T263" t="str">
+        <v>28mm AIR 线杯和轻量机身 / 适合轻饵、细线和高精度短中距离抛投</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>DRE5026</v>
+      </c>
+      <c r="B264">
+        <v>2</v>
+      </c>
+      <c r="C264" t="str">
+        <v>MORETHAN PE TW</v>
+      </c>
+      <c r="D264" t="str">
+        <v/>
+      </c>
+      <c r="E264" t="str">
+        <v/>
+      </c>
+      <c r="F264" t="str">
+        <v/>
+      </c>
+      <c r="G264" t="str">
+        <v/>
+      </c>
+      <c r="H264" t="str">
+        <v>远投,海水</v>
+      </c>
+      <c r="I264" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J264" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/MORETHAN%20PE%20TW_main.jpg</v>
+      </c>
+      <c r="K264" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="L264" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="M264" t="str">
+        <v>海鲈 PE 远投专用</v>
+      </c>
+      <c r="N264" t="str">
+        <v>針對海鱸魚設計的捲線器，實現「無可挑剔」的操作體驗。機身精巧堅韌，具備優異拋投距離，從岸釣到船釣皆能廣泛應對。</v>
+      </c>
+      <c r="O264" t="str">
+        <v>¥56,800</v>
+      </c>
+      <c r="P264" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q264" t="str">
+        <v>針對海鱸魚設計的捲線器，實現「無可挑剔」的操作體驗。機身精巧堅韌，具備優異拋投距離，從岸釣到船釣皆能廣泛應對。</v>
+      </c>
+      <c r="R264" t="str">
+        <v/>
+      </c>
+      <c r="S264" t="str">
+        <v>海鲈 / 岸船两用 PE 水滴轮</v>
+      </c>
+      <c r="T264" t="str">
+        <v>PE 1.5-200m 线杯 / 34mm 远投规格 / 面向海鲈硬饵与轻中量海水路亚</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>DRE5027</v>
+      </c>
+      <c r="B265">
+        <v>2</v>
+      </c>
+      <c r="C265" t="str">
+        <v>HRF TW PE SP</v>
+      </c>
+      <c r="D265" t="str">
+        <v/>
+      </c>
+      <c r="E265" t="str">
+        <v>2025</v>
+      </c>
+      <c r="F265" t="str">
+        <v>25 HRF TW PE SP</v>
+      </c>
+      <c r="G265" t="str">
+        <v/>
+      </c>
+      <c r="H265" t="str">
+        <v>远投,强力,海水</v>
+      </c>
+      <c r="I265" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J265" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/HRF%20TW%20PE%20SP_main.jpg</v>
+      </c>
+      <c r="K265" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="L265" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="M265" t="str">
+        <v>根鱼 PE 远投强力</v>
+      </c>
+      <c r="N265" t="str">
+        <v>岩魚專用魚餌捲線器 搭載實現一發超遠投性能的PE專用MAG-Z BOOST線杯</v>
+      </c>
+      <c r="O265" t="str">
+        <v>¥55,000</v>
+      </c>
+      <c r="P265" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q265" t="str">
+        <v>岩魚專用魚餌捲線器 搭載實現一發超遠投性能的PE專用MAG-Z BOOST線杯</v>
+      </c>
+      <c r="R265" t="str">
+        <v/>
+      </c>
+      <c r="S265" t="str">
+        <v>根鱼 / 岩礁 PE 专向</v>
+      </c>
+      <c r="T265" t="str">
+        <v>PE 专用 MAG-Z BOOST 线杯 / 34mm 规格 / 面向远投、障碍区和根鱼强拉场景</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>DRE5028</v>
+      </c>
+      <c r="B266">
+        <v>2</v>
+      </c>
+      <c r="C266" t="str">
+        <v>SS AIR TW</v>
+      </c>
+      <c r="D266" t="str">
+        <v/>
+      </c>
+      <c r="E266" t="str">
+        <v/>
+      </c>
+      <c r="F266" t="str">
+        <v/>
+      </c>
+      <c r="G266" t="str">
+        <v/>
+      </c>
+      <c r="H266" t="str">
+        <v>精细,海水,bass</v>
+      </c>
+      <c r="I266" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J266" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SS%20AIR%20TW_main.jpg</v>
+      </c>
+      <c r="K266" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="L266" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="M266" t="str">
+        <v>中高端 BFS 精细泛用</v>
+      </c>
+      <c r="N266" t="str">
+        <v>DAIWA魚餌精緻餌釣，邁向新領域</v>
+      </c>
+      <c r="O266" t="str">
+        <v>¥54,500</v>
+      </c>
+      <c r="P266" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q266" t="str">
+        <v>DAIWA魚餌精緻餌釣，邁向新領域</v>
+      </c>
+      <c r="R266" t="str">
+        <v/>
+      </c>
+      <c r="S266" t="str">
+        <v>精细饵 / 轻盐泛用 BFS</v>
+      </c>
+      <c r="T266" t="str">
+        <v>28mm 低惯量线杯 / SS MAGFORCE 宽容度高 / 可覆盖 bass、轻盐和溪流精细抛投</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>DRE5029</v>
+      </c>
+      <c r="B267">
+        <v>2</v>
+      </c>
+      <c r="C267" t="str">
+        <v>SALTIST TW PE SPECIAL</v>
+      </c>
+      <c r="D267" t="str">
+        <v/>
+      </c>
+      <c r="E267" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F267" t="str">
+        <v>23 SALTIST TW PE SPECIAL</v>
+      </c>
+      <c r="G267" t="str">
+        <v/>
+      </c>
+      <c r="H267" t="str">
+        <v>泛用,海水</v>
+      </c>
+      <c r="I267" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J267" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/SALTIST%20TW%20PE%20SPECIAL_main.jpg</v>
+      </c>
+      <c r="K267" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="L267" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="M267" t="str">
+        <v>海水 PE 泛用系列</v>
+      </c>
+      <c r="N267" t="str">
+        <v>盡情揮竿的爽快感！專為初入 PE 線路亞領域及享受卓越 PE 線應對力的玩家打造，定義海水路亞捲線器的新標準。</v>
+      </c>
+      <c r="O267" t="str">
+        <v>¥34,200 - ¥49,800</v>
+      </c>
+      <c r="P267" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q267" t="str">
+        <v>盡情揮竿的爽快感！專為初入 PE 線路亞領域及享受卓越 PE 線應對力的玩家打造，定義海水路亞捲線器的新標準。</v>
+      </c>
+      <c r="R267" t="str">
+        <v/>
+      </c>
+      <c r="S267" t="str">
+        <v>海水路亚 PE 泛用</v>
+      </c>
+      <c r="T267" t="str">
+        <v>覆盖 BF / SV / TW 多规格 / PE 线适配明确 / 入门到进阶海水路亚主力</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>DRE5030</v>
+      </c>
+      <c r="B268">
+        <v>2</v>
+      </c>
+      <c r="C268" t="str">
+        <v>TATULA TW 200</v>
+      </c>
+      <c r="D268" t="str">
+        <v/>
+      </c>
+      <c r="E268" t="str">
+        <v>2025</v>
+      </c>
+      <c r="F268" t="str">
+        <v>25 TATULA TW 200</v>
+      </c>
+      <c r="G268" t="str">
+        <v/>
+      </c>
+      <c r="H268" t="str">
+        <v>强力,海水,bass</v>
+      </c>
+      <c r="I268" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J268" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/TATULA%20TW%20200_main.jpg</v>
+      </c>
+      <c r="K268" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="L268" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="M268" t="str">
+        <v>TATULA 大线杯强力泛用</v>
+      </c>
+      <c r="N268" t="str">
+        <v>追求「TOUGH」的全球性TATULA系列</v>
+      </c>
+      <c r="O268" t="str">
+        <v>¥35,000</v>
+      </c>
+      <c r="P268" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q268" t="str">
+        <v>追求「TOUGH」的全球性TATULA系列</v>
+      </c>
+      <c r="R268" t="str">
+        <v/>
+      </c>
+      <c r="S268" t="str">
+        <v>大线杯 / 中大型饵泛用</v>
+      </c>
+      <c r="T268" t="str">
+        <v>38mm 线杯和大线容量 / 高强度黄铜齿 / 适合重装 bass 与轻海水强力泛用</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>DRE5031</v>
+      </c>
+      <c r="B269">
+        <v>2</v>
+      </c>
+      <c r="C269" t="str">
+        <v>BASS X 100</v>
+      </c>
+      <c r="D269" t="str">
+        <v/>
+      </c>
+      <c r="E269" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F269" t="str">
+        <v>24 BASS X 100</v>
+      </c>
+      <c r="G269" t="str">
+        <v/>
+      </c>
+      <c r="H269" t="str">
+        <v>泛用,海水,bass</v>
+      </c>
+      <c r="I269" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J269" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/BASS%20X%20100_main.jpg</v>
+      </c>
+      <c r="K269" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="L269" t="str">
+        <v>2026-05-03T12:54:53.004Z</v>
+      </c>
+      <c r="M269" t="str">
+        <v>入门 bass 泛用</v>
+      </c>
+      <c r="N269" t="str">
+        <v>全新升級！散發高級感的質感外觀，打造全能型高性價比雙軸捲線器。</v>
+      </c>
+      <c r="O269" t="str">
+        <v>¥11,000</v>
+      </c>
+      <c r="P269" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q269" t="str">
+        <v>全新升級！散發高級感的質感外觀，打造全能型高性價比雙軸捲線器。</v>
+      </c>
+      <c r="R269" t="str">
+        <v/>
+      </c>
+      <c r="S269" t="str">
+        <v>入门级 bass / 淡海水泛用</v>
+      </c>
+      <c r="T269" t="str">
+        <v>基础规格完整 / 32mm 线杯 / 适合入门 bass、轻中量路亚和预算优先场景</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T262"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T269"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T269"/>
+  <dimension ref="A1:T272"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3944,13 +3944,13 @@
         <v>ANTARES DC MD</v>
       </c>
       <c r="D58" t="str">
-        <v/>
+        <v>安塔列斯</v>
       </c>
       <c r="E58" t="str">
         <v>2023</v>
       </c>
       <c r="F58" t="str">
-        <v/>
+        <v>23 Antares DC MD Monster Drive</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3971,10 +3971,10 @@
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>巨物旗舰</v>
       </c>
       <c r="N58" t="str">
-        <v/>
+        <v>MGL III / 4x8 DC MD Tune / 巨物强化</v>
       </c>
       <c r="O58" t="str">
         <v>¥4,253</v>
@@ -3983,16 +3983,16 @@
         <v>在售</v>
       </c>
       <c r="Q58" t="str">
-        <v/>
+        <v>SHIMANO FREESTYLE的巅峰，ANTARES DC MD，作为奋斗在世界舞台的旗舰产品，搭载了MGL SPOOL Ⅲ和新4X8DC MD TUNE刹车系统后，进化成了更具战斗力的规格。第三代MGL线杯带来了抛投时更轻量的手感和更优秀的抛投距离，新4X8DC MD TUNE则在刹车介入时有着更好的精度，和以往抛投时相比抛投得更远且更不易发生缠线问题。另外，搭载精密齿轮后也带来了顺滑的转动性能，在驱动齿轮轴增加支撑培林让构造更强大坚固，转动手把时也能有效降低卡顿问题，带来更顺滑的收线手感。流线美丽的机身传达出的跃动感和信赖感，不断积累厚重的历史步伐，带着更高目标并带着钓手向着高处进发，SHIMANO FREESTYLE的顶点。</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v/>
+        <v>巨物远投旗舰</v>
       </c>
       <c r="T58" t="str">
-        <v/>
+        <v>4x8 DC MD Tune / 巨物向 / 宽线杯</v>
       </c>
     </row>
     <row r="59">
@@ -7868,7 +7868,7 @@
         <v>spinning</v>
       </c>
       <c r="J121" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_GAUS_20X-2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2020X_main.jpg</v>
       </c>
       <c r="K121" t="str">
         <v>2026-04-09T16:03:04.387Z</v>
@@ -7930,7 +7930,7 @@
         <v>spinning</v>
       </c>
       <c r="J122" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_GAUS_30X-1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/GAUS%2030X_main.jpg</v>
       </c>
       <c r="K122" t="str">
         <v>2026-04-09T16:03:04.751Z</v>
@@ -7992,7 +7992,7 @@
         <v>spinning</v>
       </c>
       <c r="J123" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LIN258HM.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LIN258HM_main.jpg</v>
       </c>
       <c r="K123" t="str">
         <v>2026-04-09T16:03:05.113Z</v>
@@ -8054,7 +8054,7 @@
         <v>spinning</v>
       </c>
       <c r="J124" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_megabass_idaten-x_256.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RC-IDATEN%20256_main.jpg</v>
       </c>
       <c r="K124" t="str">
         <v>2026-04-09T16:03:05.419Z</v>
@@ -8116,7 +8116,7 @@
         <v>drum</v>
       </c>
       <c r="J125" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_GRIGIO_STONE.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20GRIGIO%20STONE_main.jpg</v>
       </c>
       <c r="K125" t="str">
         <v>2026-04-09T16:03:05.733Z</v>
@@ -8178,7 +8178,7 @@
         <v>drum</v>
       </c>
       <c r="J126" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE_ITO-GAMBLER.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE%20ITO-GAMBLER_main.jpg</v>
       </c>
       <c r="K126" t="str">
         <v>2026-04-09T16:03:06.104Z</v>
@@ -8240,7 +8240,7 @@
         <v>drum</v>
       </c>
       <c r="J127" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_MONOBLOCK_SPECIALE.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/MONOBLOCK%20SPECIALE_main.jpg</v>
       </c>
       <c r="K127" t="str">
         <v>2026-04-09T16:03:06.704Z</v>
@@ -8302,7 +8302,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J128" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_megabass_rhodium_73.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2073_main.jpg</v>
       </c>
       <c r="K128" t="str">
         <v>2026-04-09T16:03:07.101Z</v>
@@ -8364,7 +8364,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J129" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_RHODIUM_81.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2081_main.jpg</v>
       </c>
       <c r="K129" t="str">
         <v>2026-04-09T16:03:07.457Z</v>
@@ -8426,7 +8426,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J130" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_RHODIUM_63.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/RHODIUM%2063_main.jpg</v>
       </c>
       <c r="K130" t="str">
         <v>2026-04-09T16:03:07.869Z</v>
@@ -8488,7 +8488,7 @@
         <v>drum</v>
       </c>
       <c r="J131" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_R100-1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20R100_main.jpg</v>
       </c>
       <c r="K131" t="str">
         <v>2026-04-09T16:03:08.227Z</v>
@@ -8550,7 +8550,7 @@
         <v>drum</v>
       </c>
       <c r="J132" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_P200_black-chrome.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P200_main.jpg</v>
       </c>
       <c r="K132" t="str">
         <v>2026-04-09T16:03:08.638Z</v>
@@ -8612,7 +8612,7 @@
         <v>drum</v>
       </c>
       <c r="J133" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_Pagani_P300_01_CHAMPAGNE_GOLD.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/Pagani%20P300_main.jpg</v>
       </c>
       <c r="K133" t="str">
         <v>2026-04-09T16:03:09.002Z</v>
@@ -8674,7 +8674,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J134" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_58.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA58_main.jpg</v>
       </c>
       <c r="K134" t="str">
         <v>2026-04-09T16:03:09.406Z</v>
@@ -8736,7 +8736,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J135" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_72.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72_main.jpg</v>
       </c>
       <c r="K135" t="str">
         <v>2026-04-09T16:03:09.802Z</v>
@@ -8798,7 +8798,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J136" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_LAUDA_72_LIMITED-EDITION.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/LAUDA72%20LIMITED%20EDITION_main.jpg</v>
       </c>
       <c r="K136" t="str">
         <v>2026-04-09T16:03:10.384Z</v>
@@ -8860,7 +8860,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J137" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_IP79.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP79_main.jpg</v>
       </c>
       <c r="K137" t="str">
         <v>2026-04-09T16:03:10.796Z</v>
@@ -8922,7 +8922,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J138" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/main_001_IP68.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_reels/IP68_main.jpg</v>
       </c>
       <c r="K138" t="str">
         <v>2026-04-09T16:03:11.194Z</v>
@@ -13572,7 +13572,7 @@
         <v>spinning</v>
       </c>
       <c r="J213" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/AIRITY%ST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/AIRITY%20ST_main.jpg</v>
       </c>
       <c r="K213" t="str">
         <v>2026-04-05T14:37:40.618600Z</v>
@@ -17077,9 +17077,195 @@
         <v>基础规格完整 / 32mm 线杯 / 适合入门 bass、轻中量路亚和预算优先场景</v>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>DRE5032</v>
+      </c>
+      <c r="B270">
+        <v>2</v>
+      </c>
+      <c r="C270" t="str">
+        <v>IM Z LIMITBREAKER TW HD-C</v>
+      </c>
+      <c r="D270" t="str">
+        <v/>
+      </c>
+      <c r="E270" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F270" t="str">
+        <v>23 IM Z LIMITBREAKER TW HD-C</v>
+      </c>
+      <c r="G270" t="str">
+        <v/>
+      </c>
+      <c r="H270" t="str">
+        <v>强力,远投,海水</v>
+      </c>
+      <c r="I270" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J270" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM%20Z%20LIMITBREAKER%20TW%20HD-C_main.jpg</v>
+      </c>
+      <c r="K270" t="str">
+        <v>2026-05-03T14:20:31.025Z</v>
+      </c>
+      <c r="L270" t="str">
+        <v>2026-05-03T14:20:31.025Z</v>
+      </c>
+      <c r="M270" t="str">
+        <v>IM Z 数字刹车重载远投旗舰</v>
+      </c>
+      <c r="N270" t="str">
+        <v>搭载 INTELLIGENT MAGFORCE、DAIWA CONNECTING-SYSTEM、HYPERDRIVE DESIGN 与 TWS，面向大饵、重型远投和海水强力场景。</v>
+      </c>
+      <c r="O270" t="str">
+        <v>¥125,000</v>
+      </c>
+      <c r="P270" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q270" t="str">
+        <v>面向重型远投、大饵、海鲈和青物等强力场景的 IM Z LIMITBREAKER。φ38mm G1 杜拉铝线杯可容纳氟碳 20lb-100m / PE 4号-100m，最大拖力 7kg，并支持 DAIWA CONNECTING-SYSTEM 扩展刹车模式。</v>
+      </c>
+      <c r="R270" t="str">
+        <v/>
+      </c>
+      <c r="S270" t="str">
+        <v>重载远投 / 大饵与海水强力</v>
+      </c>
+      <c r="T270" t="str">
+        <v>38mm 大容量线杯 / 电子控制刹车 / 7kg 拖力和出线点击 / 适合大饵、重型远投、海鲈和青物</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>DRE5033</v>
+      </c>
+      <c r="B271">
+        <v>2</v>
+      </c>
+      <c r="C271" t="str">
+        <v>IM Z TW 200-C</v>
+      </c>
+      <c r="D271" t="str">
+        <v/>
+      </c>
+      <c r="E271" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F271" t="str">
+        <v>24 IM Z TW 200-C</v>
+      </c>
+      <c r="G271" t="str">
+        <v/>
+      </c>
+      <c r="H271" t="str">
+        <v>强力,海水,bass</v>
+      </c>
+      <c r="I271" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J271" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM%20Z%20TW%20200-C_main.jpg</v>
+      </c>
+      <c r="K271" t="str">
+        <v>2026-05-03T14:20:31.025Z</v>
+      </c>
+      <c r="L271" t="str">
+        <v>2026-05-03T14:20:31.025Z</v>
+      </c>
+      <c r="M271" t="str">
+        <v>IM Z 200 数字刹车强力泛用</v>
+      </c>
+      <c r="N271" t="str">
+        <v>IM Z 200 系列使用 φ38mm 线杯和 INTELLIGENT MAGFORCE，覆盖约 10g 到 110g 的宽饵重范围，并支持 DAIWA CONNECTING-SYSTEM。</v>
+      </c>
+      <c r="O271" t="str">
+        <v>¥113,600</v>
+      </c>
+      <c r="P271" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q271" t="str">
+        <v>IM Z 200-C 是 IM Z 系列的 200 规格，面向大饵、远投和强力 bass / 淡海水泛用。官方说明其适配约 10g-110g，配备 90mm 铝手柄、TWS、HYPERDRIVE DESIGN 和智能数字刹车。</v>
+      </c>
+      <c r="R271" t="str">
+        <v/>
+      </c>
+      <c r="S271" t="str">
+        <v>强力 bass / 大饵与淡海水泛用</v>
+      </c>
+      <c r="T271" t="str">
+        <v>38mm 线杯和 200 规格线容量 / 10g-110g 饵重覆盖 / 数字刹车可更新 / 适合大饵、远投和强力卷物</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>DRE5034</v>
+      </c>
+      <c r="B272">
+        <v>2</v>
+      </c>
+      <c r="C272" t="str">
+        <v>IM Z TW100-C</v>
+      </c>
+      <c r="D272" t="str">
+        <v/>
+      </c>
+      <c r="E272" t="str">
+        <v>2025</v>
+      </c>
+      <c r="F272" t="str">
+        <v>25 IM Z TW100-C</v>
+      </c>
+      <c r="G272" t="str">
+        <v/>
+      </c>
+      <c r="H272" t="str">
+        <v>泛用,远投,海水</v>
+      </c>
+      <c r="I272" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J272" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/IM%20Z%20TW100-C_main.jpg</v>
+      </c>
+      <c r="K272" t="str">
+        <v>2026-05-03T14:20:31.025Z</v>
+      </c>
+      <c r="L272" t="str">
+        <v>2026-05-03T14:20:31.025Z</v>
+      </c>
+      <c r="M272" t="str">
+        <v>IM Z 100 数字刹车远投泛用</v>
+      </c>
+      <c r="N272" t="str">
+        <v>IM Z TW100-C 使用 φ34mm G1 杜拉铝 IM 线杯、新型 IM 单元和电子拖力声音，兼顾远投、紧凑机身和淡海水泛用。</v>
+      </c>
+      <c r="O272" t="str">
+        <v>¥107,500</v>
+      </c>
+      <c r="P272" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q272" t="str">
+        <v>IM Z TW100-C 以 φ34mm 线杯长距离表现为核心，采用全铝高刚性机身、新型 IM 单元和电子拖力声音。官方说明其覆盖淡水、海水、船钓、岸钓和涉水等多种风格。</v>
+      </c>
+      <c r="R272" t="str">
+        <v/>
+      </c>
+      <c r="S272" t="str">
+        <v>紧凑数字刹车 / 远投泛用</v>
+      </c>
+      <c r="T272" t="str">
+        <v>34mm 8.7g 线杯 / 205g 全铝机身 / 电子拖力声音 / 适合中近距离到远投的淡海水泛用</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T269"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T272"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -552,7 +552,7 @@
         <v>spinning</v>
       </c>
       <c r="J3" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA%20SW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STELLA%20SW%202019_main.jpg</v>
       </c>
       <c r="K3" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -15104,7 +15104,7 @@
         <v>SILVER WOLF CT SV TW PE SPECIAL</v>
       </c>
       <c r="D238" t="str">
-        <v/>
+        <v>银狼</v>
       </c>
       <c r="E238" t="str">
         <v/>
@@ -15166,7 +15166,7 @@
         <v>TATULA BF TW</v>
       </c>
       <c r="D239" t="str">
-        <v/>
+        <v>蜘蛛</v>
       </c>
       <c r="E239" t="str">
         <v>2026</v>
@@ -15228,7 +15228,7 @@
         <v>月下美人 BF TW PE SP</v>
       </c>
       <c r="D240" t="str">
-        <v/>
+        <v>月下美人</v>
       </c>
       <c r="E240" t="str">
         <v>2026</v>
@@ -15290,7 +15290,7 @@
         <v>STEEZ SV LIGHT TW</v>
       </c>
       <c r="D241" t="str">
-        <v/>
+        <v>史帝兹</v>
       </c>
       <c r="E241" t="str">
         <v/>
@@ -15352,7 +15352,7 @@
         <v>RYOGA</v>
       </c>
       <c r="D242" t="str">
-        <v/>
+        <v>肉鸽</v>
       </c>
       <c r="E242" t="str">
         <v>2026</v>
@@ -15414,7 +15414,7 @@
         <v>SALTIGA 10</v>
       </c>
       <c r="D243" t="str">
-        <v/>
+        <v>赛尔迪迦</v>
       </c>
       <c r="E243" t="str">
         <v>2025</v>
@@ -15476,7 +15476,7 @@
         <v>SALTIGA 35</v>
       </c>
       <c r="D244" t="str">
-        <v/>
+        <v>赛尔迪迦</v>
       </c>
       <c r="E244" t="str">
         <v>2025</v>
@@ -15538,7 +15538,7 @@
         <v>STEEZ LIMITED CT SV TW</v>
       </c>
       <c r="D245" t="str">
-        <v/>
+        <v>史帝兹</v>
       </c>
       <c r="E245" t="str">
         <v/>
@@ -15600,7 +15600,7 @@
         <v>SALTIGA 300</v>
       </c>
       <c r="D246" t="str">
-        <v/>
+        <v>赛尔迪迦</v>
       </c>
       <c r="E246" t="str">
         <v>2025</v>
@@ -15662,7 +15662,7 @@
         <v>TATULA SV TW 100</v>
       </c>
       <c r="D247" t="str">
-        <v/>
+        <v>蜘蛛</v>
       </c>
       <c r="E247" t="str">
         <v>2025</v>
@@ -15724,7 +15724,7 @@
         <v>ALPHAS BF TW</v>
       </c>
       <c r="D248" t="str">
-        <v/>
+        <v>阿尔法</v>
       </c>
       <c r="E248" t="str">
         <v>2025</v>
@@ -15786,7 +15786,7 @@
         <v>STEEZ SV TW</v>
       </c>
       <c r="D249" t="str">
-        <v/>
+        <v>史帝兹</v>
       </c>
       <c r="E249" t="str">
         <v>2024</v>
@@ -15848,7 +15848,7 @@
         <v>TATULA TW 100</v>
       </c>
       <c r="D250" t="str">
-        <v/>
+        <v>蜘蛛</v>
       </c>
       <c r="E250" t="str">
         <v>2024</v>
@@ -15910,7 +15910,7 @@
         <v>SALTIGA 15</v>
       </c>
       <c r="D251" t="str">
-        <v/>
+        <v>赛尔迪迦</v>
       </c>
       <c r="E251" t="str">
         <v>2022</v>
@@ -16034,7 +16034,7 @@
         <v>STEEZ A II TW</v>
       </c>
       <c r="D253" t="str">
-        <v/>
+        <v>史帝兹</v>
       </c>
       <c r="E253" t="str">
         <v>2022</v>
@@ -16096,7 +16096,7 @@
         <v>ZILLION TW HD</v>
       </c>
       <c r="D254" t="str">
-        <v/>
+        <v>子龙</v>
       </c>
       <c r="E254" t="str">
         <v>2022</v>
@@ -16158,7 +16158,7 @@
         <v>SALTIGA IC</v>
       </c>
       <c r="D255" t="str">
-        <v/>
+        <v>赛尔迪迦</v>
       </c>
       <c r="E255" t="str">
         <v>2021</v>
@@ -16220,7 +16220,7 @@
         <v>ZILLION SV TW</v>
       </c>
       <c r="D256" t="str">
-        <v/>
+        <v>子龙</v>
       </c>
       <c r="E256" t="str">
         <v>2021</v>
@@ -16282,7 +16282,7 @@
         <v>ALPHAS SV TW</v>
       </c>
       <c r="D257" t="str">
-        <v/>
+        <v>阿尔法</v>
       </c>
       <c r="E257" t="str">
         <v>2021</v>
@@ -16344,7 +16344,7 @@
         <v>STEEZ LTD SV TW</v>
       </c>
       <c r="D258" t="str">
-        <v/>
+        <v>史帝兹</v>
       </c>
       <c r="E258" t="str">
         <v>2021</v>
@@ -16468,7 +16468,7 @@
         <v>TATULA TW 300/400</v>
       </c>
       <c r="D260" t="str">
-        <v/>
+        <v>蜘蛛</v>
       </c>
       <c r="E260" t="str">
         <v/>
@@ -16592,7 +16592,7 @@
         <v>STEEZ CT SV TW</v>
       </c>
       <c r="D262" t="str">
-        <v/>
+        <v>史帝兹</v>
       </c>
       <c r="E262" t="str">
         <v/>
@@ -16654,7 +16654,7 @@
         <v>STEEZ AIR TW</v>
       </c>
       <c r="D263" t="str">
-        <v/>
+        <v>史帝兹</v>
       </c>
       <c r="E263" t="str">
         <v>2020</v>
@@ -16716,7 +16716,7 @@
         <v>MORETHAN PE TW</v>
       </c>
       <c r="D264" t="str">
-        <v/>
+        <v>猫赞</v>
       </c>
       <c r="E264" t="str">
         <v/>
@@ -16902,7 +16902,7 @@
         <v>SALTIST TW PE SPECIAL</v>
       </c>
       <c r="D267" t="str">
-        <v/>
+        <v>赛尔迪</v>
       </c>
       <c r="E267" t="str">
         <v>2023</v>
@@ -16964,7 +16964,7 @@
         <v>TATULA TW 200</v>
       </c>
       <c r="D268" t="str">
-        <v/>
+        <v>蜘蛛</v>
       </c>
       <c r="E268" t="str">
         <v>2025</v>

--- a/GearSage-client/rate/excel/reel.xlsx
+++ b/GearSage-client/rate/excel/reel.xlsx
@@ -7850,7 +7850,7 @@
         <v>GAUS 20X</v>
       </c>
       <c r="D121" t="str">
-        <v>GAUS 20X</v>
+        <v/>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -7912,7 +7912,7 @@
         <v>GAUS 30X</v>
       </c>
       <c r="D122" t="str">
-        <v>GAUS 30X</v>
+        <v/>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -7974,7 +7974,7 @@
         <v>LIN258HM</v>
       </c>
       <c r="D123" t="str">
-        <v>LIN258HM</v>
+        <v/>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -8036,7 +8036,7 @@
         <v>RC-IDATEN 256</v>
       </c>
       <c r="D124" t="str">
-        <v>RC-IDATEN 256</v>
+        <v/>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -8098,7 +8098,7 @@
         <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
       </c>
       <c r="D125" t="str">
-        <v>MONOBLOCK SPECIALE GRIGIO STONE</v>
+        <v/>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -8160,7 +8160,7 @@
         <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
       </c>
       <c r="D126" t="str">
-        <v>MONOBLOCK SPECIALE ITO-GAMBLER</v>
+        <v/>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -8222,7 +8222,7 @@
         <v>MONOBLOCK SPECIALE</v>
       </c>
       <c r="D127" t="str">
-        <v>MONOBLOCK SPECIALE</v>
+        <v/>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -8284,7 +8284,7 @@
         <v>RHODIUM 73</v>
       </c>
       <c r="D128" t="str">
-        <v>RHODIUM 73</v>
+        <v/>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -8346,7 +8346,7 @@
         <v>RHODIUM 81</v>
       </c>
       <c r="D129" t="str">
-        <v>RHODIUM 81</v>
+        <v/>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -8408,7 +8408,7 @@
         <v>RHODIUM 63</v>
       </c>
       <c r="D130" t="str">
-        <v>RHODIUM 63</v>
+        <v/>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -8470,7 +8470,7 @@
         <v>Pagani R100</v>
       </c>
       <c r="D131" t="str">
-        <v>Pagani R100</v>
+        <v/>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -8532,7 +8532,7 @@
         <v>Pagani P200</v>
       </c>
       <c r="D132" t="str">
-        <v>Pagani P200</v>
+        <v/>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -8594,7 +8594,7 @@
         <v>Pagani P300</v>
       </c>
       <c r="D133" t="str">
-        <v>Pagani P300</v>
+        <v/>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -8656,7 +8656,7 @@
         <v>LAUDA58</v>
       </c>
       <c r="D134" t="str">
-        <v>LAUDA58</v>
+        <v/>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -8718,7 +8718,7 @@
         <v>LAUDA72</v>
       </c>
       <c r="D135" t="str">
-        <v>LAUDA72</v>
+        <v/>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -8780,7 +8780,7 @@
         <v>LAUDA72 LIMITED EDITION</v>
       </c>
       <c r="D136" t="str">
-        <v>LAUDA72 LIMITED EDITION</v>
+        <v/>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -8842,7 +8842,7 @@
         <v>IP79</v>
       </c>
       <c r="D137" t="str">
-        <v>IP79</v>
+        <v/>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -8904,7 +8904,7 @@
         <v>IP68</v>
       </c>
       <c r="D138" t="str">
-        <v>IP68</v>
+        <v/>
       </c>
       <c r="E138" t="str">
         <v/>
